--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,6 +687,81 @@
       <c r="U3" t="inlineStr">
         <is>
           <t>Disponibilidade_02_07_2026.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L4" t="n">
+        <v>21</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2703, 2708, 2709, 2741</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>22</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2721, 2723</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>10070:00</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4317:55</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="T4" t="n">
+        <v>24</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Disponibilidade_06_07_2026.txt</t>
         </is>
       </c>
     </row>
@@ -701,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2559,858 @@
         <v>46205</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Agd parecer do AT do PAMASP sobre FCU</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>07/07</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1º/15º GAV</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Realizando inspeções ID 0A / 500FH</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Realizando inspeções 4300 FH/HSI.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5º ETA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pane no sistema de flape</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>07/07</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Motor recolhido para reparo na geradora de gases</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2741</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>07/07</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Itens entregues. Agd AT de hélice para definição de recolhimento ou translado da aeronave para o Parque</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>DACTA II</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>75 APE</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ANV acidentada.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>91 AIFP. Serão atendidas pela Vee One e FAB</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Aguardando avaliação de sinistro</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>06/07</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 44 IPLR</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 13 IPLR</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 57 IPLR</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>46209</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,6 +762,81 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>Disponibilidade_06_07_2026.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>21</v>
+      </c>
+      <c r="M5" t="n">
+        <v>19</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2702, 2709, 2719, 2721, 2733, 2736, 2741, 2743</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2721, 2723</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>10070:00</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4374:25</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>24</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Disponibilidade_07_07_2026.txt</t>
         </is>
       </c>
     </row>
@@ -776,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3411,6 +3486,888 @@
         <v>46209</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Agd parecer do AT do PAMASP sobre FCU</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>07/07</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1º/15º GAV</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Realizando inspeções ID 0A / 500FH</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Realizando inspeções 4300 FH/HSI.</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5º ETA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Pane no sistema de flape</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Motor recolhido para reparo na geradora de gases</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2741</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>MOTOR NÃO COMPLETANDO O CICLO DE PARTIDA, ESTABILIZANDO COM 40% DE NG</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Itens entregues. Agd AT de hélice para definição de recolhimento ou translado da aeronave para o Parque</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DACTA II</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>75 APE</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ANV acidentada.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>91 AIFP. Serão atendidas pela Vee One e FAB</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Aguardando avaliação de sinistro</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>06/07</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 44 IPLR</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 13 IPLR</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 57 IPLR</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>46210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,6 +837,81 @@
       <c r="U5" t="inlineStr">
         <is>
           <t>Disponibilidade_07_07_2026.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L6" t="n">
+        <v>19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2709, 2719, 2736, 2741, 2743</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>22</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2709, 2721, 2723</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>10070:00</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4406:50</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="T6" t="n">
+        <v>24</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Disponibilidade_08_07_2026.txt</t>
         </is>
       </c>
     </row>
@@ -851,7 +926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4368,6 +4443,868 @@
         <v>46210</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1º/15º GAV</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Realizando inspeções 4300 FH/HSI.</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5º ETA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Pane no sistema de flape</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Motor recolhido para reparo na geradora de gases</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2741</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Itens entregues. Agd AT de hélice para definição de recolhimento ou translado da aeronave para o Parque</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>DACTA II</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>75 APE</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ANV acidentada.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>91 AIFP. Serão atendidas pela Vee One e FAB</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Aguardando avaliação de sinistro</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>06/07</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 44 IPLR</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 13 IPLR</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 57 IPLR</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>46211</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,81 @@
       <c r="U6" t="inlineStr">
         <is>
           <t>Disponibilidade_08_07_2026.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>13</v>
+      </c>
+      <c r="L7" t="n">
+        <v>18</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2709, 2719, 2721, 2733, 2736, 2741, 2743</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>21</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2709, 2721, 2723</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>10070:00</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4463:45</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="T7" t="n">
+        <v>24</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Disponibilidade_09_07_2026.txt</t>
         </is>
       </c>
     </row>
@@ -926,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5305,6 +5380,878 @@
         <v>46211</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1º/15º GAV</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Realizando inspeções 4300 FH/HSI.</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5º ETA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Pane no sistema de flape</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>EM PESQUISA DE PANE DE FCU</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>09/07</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Motor recolhido para reparo na geradora de gases</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2741</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Itens entregues. Agd AT de hélice para definição de recolhimento ou translado da aeronave para o Parque</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>DACTA II</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>75 APE</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ANV acidentada.</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>91 AIFP. Serão atendidas pela Vee One e FAB</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Aguardando avaliação de sinistro</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>06/07</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 44 IPLR</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 13 IPLR</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 57 IPLR</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>46212</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -21,16 +21,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -434,114 +422,114 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>disponiveis_hoje</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>montadas_hoje</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>di</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>do_</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ii</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>in_</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>itr</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>previsao_fim_dia_disponiveis</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>previsao_fim_dia_montadas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>previsao_semana_disponiveis_qtd</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>previsao_semana_disponiveis_novas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>previsao_semana_montadas_qtd</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>previsao_semana_montadas_novas</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>esforco_anual_previsto</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>esforco_anual_realizado</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>esforco_percentual</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>motores_disponiveis</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>arquivo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B2" t="n">
@@ -616,7 +604,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="B3" t="n">
@@ -691,7 +679,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="B4" t="n">
@@ -766,7 +754,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="B5" t="n">
@@ -841,7 +829,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46211</v>
       </c>
       <c r="B6" t="n">
@@ -916,7 +904,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="B7" t="n">
@@ -1005,42 +993,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>matricula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unidade</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>situacao</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ocorrencia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>dpe_data</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>dpe_condicao</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>dpe_texto_original</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
@@ -1066,7 +1054,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1090,7 +1078,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1126,7 +1114,7 @@
           <t>01 DIA após chegada do item.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1150,7 +1138,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1174,7 +1162,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1199,7 +1187,7 @@
           <t>Realizando inspeções ID 0A,20,21,22 / 4100FH</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1208,7 +1196,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1233,7 +1221,7 @@
           <t>Pesquisa no sistema de indicação de flape.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1242,7 +1230,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1267,7 +1255,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1276,7 +1264,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1301,7 +1289,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1310,7 +1298,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1334,7 +1322,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1358,7 +1346,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1383,7 +1371,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1392,7 +1380,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1416,7 +1404,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1441,7 +1429,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1450,7 +1438,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1474,7 +1462,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1498,7 +1486,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1523,7 +1511,7 @@
           <t>Realizando inspeções programadas.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1532,7 +1520,7 @@
           <t>01/07</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1556,7 +1544,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1581,7 +1569,7 @@
           <t>Pesquisa de pane de vazamento de óleo do motor.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1590,7 +1578,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1626,7 +1614,7 @@
           <t>02 DIAS após chegada do item.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1650,7 +1638,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1674,7 +1662,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1710,7 +1698,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1738,7 +1726,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1774,7 +1762,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1799,7 +1787,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1808,7 +1796,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1844,7 +1832,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1880,7 +1868,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1916,7 +1904,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1940,7 +1928,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" s="2" t="n">
+      <c r="H31" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -1964,7 +1952,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2000,7 +1988,7 @@
           <t>01 DIA após resposta do AT.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2024,7 +2012,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2048,7 +2036,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2073,7 +2061,7 @@
           <t>Realizando inspeções ID 0A,20,21,22 / 4100FH</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2082,7 +2070,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2107,7 +2095,7 @@
           <t>Pesquisa no sistema de indicação de flape.</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -2116,7 +2104,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H37" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2141,7 +2129,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2150,7 +2138,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2175,7 +2163,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2184,7 +2172,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2208,7 +2196,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2232,7 +2220,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" s="2" t="n">
+      <c r="H41" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2257,7 +2245,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2266,7 +2254,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2290,7 +2278,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" s="2" t="n">
+      <c r="H43" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2315,7 +2303,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2324,7 +2312,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2348,7 +2336,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2372,7 +2360,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2396,7 +2384,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" s="2" t="n">
+      <c r="H47" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2420,7 +2408,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2445,7 +2433,7 @@
           <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -2454,7 +2442,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H49" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2490,7 +2478,7 @@
           <t>02 DIAS após chegada do item.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2514,7 +2502,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2538,7 +2526,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" s="2" t="n">
+      <c r="H52" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2574,7 +2562,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H53" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2602,7 +2590,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2638,7 +2626,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H55" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2663,7 +2651,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -2672,7 +2660,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2708,7 +2696,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H57" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2744,7 +2732,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2780,7 +2768,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H59" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2804,7 +2792,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" s="2" t="n">
+      <c r="H60" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2828,7 +2816,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="2" t="n">
+      <c r="H61" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2853,7 +2841,7 @@
           <t>Agd parecer do AT do PAMASP sobre FCU</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2862,7 +2850,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2886,7 +2874,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" s="2" t="n">
+      <c r="H63" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2911,7 +2899,7 @@
           <t>Realizando inspeções ID 0A / 500FH</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2920,7 +2908,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2944,7 +2932,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="2" t="n">
+      <c r="H65" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2968,7 +2956,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2993,7 +2981,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3002,7 +2990,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H67" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3027,7 +3015,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3036,7 +3024,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H68" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3060,7 +3048,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" s="2" t="n">
+      <c r="H69" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3084,7 +3072,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3109,7 +3097,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3118,7 +3106,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H71" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3142,7 +3130,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" s="2" t="n">
+      <c r="H72" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3167,7 +3155,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3176,7 +3164,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H73" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3200,7 +3188,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3224,7 +3212,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" s="2" t="n">
+      <c r="H75" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3248,7 +3236,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3272,7 +3260,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" s="2" t="n">
+      <c r="H77" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3297,7 +3285,7 @@
           <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -3306,7 +3294,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3342,7 +3330,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H79" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3366,7 +3354,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3390,7 +3378,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" s="2" t="n">
+      <c r="H81" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3426,7 +3414,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3454,7 +3442,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" s="2" t="n">
+      <c r="H83" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3490,7 +3478,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H84" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3515,7 +3503,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E85" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3524,7 +3512,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="H85" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3560,7 +3548,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H86" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3596,7 +3584,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H87" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3632,7 +3620,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H88" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3656,7 +3644,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" s="2" t="n">
+      <c r="H89" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3681,7 +3669,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E90" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -3690,7 +3678,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3715,7 +3703,7 @@
           <t>Agd parecer do AT do PAMASP sobre FCU</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -3724,7 +3712,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H91" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3748,7 +3736,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" s="2" t="n">
+      <c r="H92" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3773,7 +3761,7 @@
           <t>Realizando inspeções ID 0A / 500FH</t>
         </is>
       </c>
-      <c r="E93" s="2" t="n">
+      <c r="E93" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -3782,7 +3770,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="H93" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3806,7 +3794,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" s="2" t="n">
+      <c r="H94" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3830,7 +3818,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" s="2" t="n">
+      <c r="H95" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3855,7 +3843,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E96" s="2" t="n">
+      <c r="E96" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -3864,7 +3852,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H96" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3889,7 +3877,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E97" s="2" t="n">
+      <c r="E97" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3898,7 +3886,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H97" s="2" t="n">
+      <c r="H97" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3922,7 +3910,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" s="2" t="n">
+      <c r="H98" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3947,7 +3935,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n">
+      <c r="E99" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -3956,7 +3944,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="H99" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3981,7 +3969,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n">
+      <c r="E100" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -3990,7 +3978,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="H100" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4014,7 +4002,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" s="2" t="n">
+      <c r="H101" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4039,7 +4027,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="E102" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -4048,7 +4036,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H102" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4073,7 +4061,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -4082,7 +4070,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H103" s="2" t="n">
+      <c r="H103" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4106,7 +4094,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" s="2" t="n">
+      <c r="H104" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4130,7 +4118,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" s="2" t="n">
+      <c r="H105" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4154,7 +4142,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" s="2" t="n">
+      <c r="H106" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4179,7 +4167,7 @@
           <t>MOTOR NÃO COMPLETANDO O CICLO DE PARTIDA, ESTABILIZANDO COM 40% DE NG</t>
         </is>
       </c>
-      <c r="E107" s="2" t="n">
+      <c r="E107" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -4188,7 +4176,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H107" s="2" t="n">
+      <c r="H107" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4224,7 +4212,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="n">
+      <c r="H108" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4248,7 +4236,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" s="2" t="n">
+      <c r="H109" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4272,7 +4260,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" s="2" t="n">
+      <c r="H110" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4308,7 +4296,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="n">
+      <c r="H111" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4336,7 +4324,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" s="2" t="n">
+      <c r="H112" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4372,7 +4360,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H113" s="2" t="n">
+      <c r="H113" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4397,7 +4385,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E114" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -4406,7 +4394,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H114" s="2" t="n">
+      <c r="H114" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4442,7 +4430,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="n">
+      <c r="H115" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4478,7 +4466,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="n">
+      <c r="H116" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4514,7 +4502,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="n">
+      <c r="H117" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4538,7 +4526,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" s="2" t="n">
+      <c r="H118" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4563,7 +4551,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E119" s="2" t="n">
+      <c r="E119" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -4572,7 +4560,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H119" s="2" t="n">
+      <c r="H119" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4596,7 +4584,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" s="2" t="n">
+      <c r="H120" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4620,7 +4608,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" s="2" t="n">
+      <c r="H121" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4644,7 +4632,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" s="2" t="n">
+      <c r="H122" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4668,7 +4656,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" s="2" t="n">
+      <c r="H123" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4692,7 +4680,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" s="2" t="n">
+      <c r="H124" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4717,7 +4705,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E125" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -4726,7 +4714,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H125" s="2" t="n">
+      <c r="H125" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4751,7 +4739,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E126" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4760,7 +4748,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H126" s="2" t="n">
+      <c r="H126" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4784,7 +4772,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" s="2" t="n">
+      <c r="H127" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4809,7 +4797,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E128" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -4818,7 +4806,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H128" s="2" t="n">
+      <c r="H128" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4843,7 +4831,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n">
+      <c r="E129" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -4852,7 +4840,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H129" s="2" t="n">
+      <c r="H129" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4876,7 +4864,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" s="2" t="n">
+      <c r="H130" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4901,7 +4889,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E131" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -4910,7 +4898,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H131" s="2" t="n">
+      <c r="H131" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4935,7 +4923,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E132" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -4944,7 +4932,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H132" s="2" t="n">
+      <c r="H132" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4968,7 +4956,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" s="2" t="n">
+      <c r="H133" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4992,7 +4980,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" s="2" t="n">
+      <c r="H134" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5016,7 +5004,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" s="2" t="n">
+      <c r="H135" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5041,7 +5029,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="E136" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -5050,7 +5038,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H136" s="2" t="n">
+      <c r="H136" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5086,7 +5074,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="n">
+      <c r="H137" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5110,7 +5098,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" s="2" t="n">
+      <c r="H138" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5134,7 +5122,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" s="2" t="n">
+      <c r="H139" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5170,7 +5158,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="n">
+      <c r="H140" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5198,7 +5186,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" s="2" t="n">
+      <c r="H141" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5234,7 +5222,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H142" s="2" t="n">
+      <c r="H142" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5259,7 +5247,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E143" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -5268,7 +5256,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H143" s="2" t="n">
+      <c r="H143" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5304,7 +5292,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="n">
+      <c r="H144" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5340,7 +5328,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="n">
+      <c r="H145" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5376,7 +5364,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="n">
+      <c r="H146" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5400,7 +5388,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" s="2" t="n">
+      <c r="H147" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5425,7 +5413,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="E148" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -5434,7 +5422,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H148" s="2" t="n">
+      <c r="H148" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5458,7 +5446,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" s="2" t="n">
+      <c r="H149" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5482,7 +5470,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" s="2" t="n">
+      <c r="H150" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5506,7 +5494,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" s="2" t="n">
+      <c r="H151" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5530,7 +5518,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" s="2" t="n">
+      <c r="H152" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5554,7 +5542,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" s="2" t="n">
+      <c r="H153" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5579,7 +5567,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E154" s="2" t="n">
+      <c r="E154" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -5588,7 +5576,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H154" s="2" t="n">
+      <c r="H154" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5613,7 +5601,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E155" s="2" t="n">
+      <c r="E155" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -5622,7 +5610,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H155" s="2" t="n">
+      <c r="H155" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5646,7 +5634,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" s="2" t="n">
+      <c r="H156" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5671,7 +5659,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E157" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -5680,7 +5668,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H157" s="2" t="n">
+      <c r="H157" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5705,7 +5693,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E158" s="2" t="n">
+      <c r="E158" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -5714,7 +5702,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H158" s="2" t="n">
+      <c r="H158" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5739,7 +5727,7 @@
           <t>EM PESQUISA DE PANE DE FCU</t>
         </is>
       </c>
-      <c r="E159" s="2" t="n">
+      <c r="E159" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5748,7 +5736,7 @@
           <t>09/07</t>
         </is>
       </c>
-      <c r="H159" s="2" t="n">
+      <c r="H159" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5773,7 +5761,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="E160" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -5782,7 +5770,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H160" s="2" t="n">
+      <c r="H160" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5807,7 +5795,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E161" s="2" t="n">
+      <c r="E161" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -5816,7 +5804,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H161" s="2" t="n">
+      <c r="H161" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5840,7 +5828,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" s="2" t="n">
+      <c r="H162" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5864,7 +5852,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" s="2" t="n">
+      <c r="H163" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5888,7 +5876,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" s="2" t="n">
+      <c r="H164" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5913,7 +5901,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="E165" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -5922,7 +5910,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H165" s="2" t="n">
+      <c r="H165" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5958,7 +5946,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="n">
+      <c r="H166" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5982,7 +5970,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" s="2" t="n">
+      <c r="H167" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6006,7 +5994,7 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" s="2" t="n">
+      <c r="H168" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6042,7 +6030,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="n">
+      <c r="H169" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6070,7 +6058,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
-      <c r="H170" s="2" t="n">
+      <c r="H170" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6106,7 +6094,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H171" s="2" t="n">
+      <c r="H171" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6131,7 +6119,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n">
+      <c r="E172" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -6140,7 +6128,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H172" s="2" t="n">
+      <c r="H172" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6176,7 +6164,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H173" s="2" t="n">
+      <c r="H173" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6212,7 +6200,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H174" s="2" t="n">
+      <c r="H174" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6248,7 +6236,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H175" s="2" t="n">
+      <c r="H175" s="1" t="n">
         <v>46212</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -418,118 +430,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>disponiveis_hoje</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>montadas_hoje</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>di</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>do_</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ii</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>in_</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>itr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>is_</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>previsao_fim_dia_disponiveis</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>previsao_fim_dia_montadas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>previsao_semana_disponiveis_qtd</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>previsao_semana_disponiveis_novas</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>previsao_semana_montadas_qtd</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>previsao_semana_montadas_novas</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>esforco_anual_previsto</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>esforco_anual_realizado</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>esforco_percentual</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>motores_disponiveis</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>arquivo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B2" t="n">
@@ -604,7 +616,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="B3" t="n">
@@ -679,7 +691,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="B4" t="n">
@@ -754,7 +766,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="B5" t="n">
@@ -829,7 +841,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46211</v>
       </c>
       <c r="B6" t="n">
@@ -904,7 +916,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="B7" t="n">
@@ -975,6 +987,81 @@
       <c r="U7" t="inlineStr">
         <is>
           <t>Disponibilidade_09_07_2026.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>16</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2709, 2719, 2720, 2727, 2736, 2741, 2743</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2709, 2721, 2723</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>10070:00</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4481:45</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="T8" t="n">
+        <v>24</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Disponibilidade_10_07_2026.txt</t>
         </is>
       </c>
     </row>
@@ -989,46 +1076,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>matricula</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>unidade</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>situacao</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ocorrencia</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>dpe_data</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dpe_condicao</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dpe_texto_original</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
@@ -1054,7 +1141,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1078,7 +1165,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1114,7 +1201,7 @@
           <t>01 DIA após chegada do item.</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1138,7 +1225,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1162,7 +1249,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1187,7 +1274,7 @@
           <t>Realizando inspeções ID 0A,20,21,22 / 4100FH</t>
         </is>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1196,7 +1283,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1221,7 +1308,7 @@
           <t>Pesquisa no sistema de indicação de flape.</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1230,7 +1317,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1255,7 +1342,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1264,7 +1351,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1289,7 +1376,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1298,7 +1385,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1322,7 +1409,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1346,7 +1433,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1371,7 +1458,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1380,7 +1467,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1404,7 +1491,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1429,7 +1516,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1438,7 +1525,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1462,7 +1549,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1486,7 +1573,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1511,7 +1598,7 @@
           <t>Realizando inspeções programadas.</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1520,7 +1607,7 @@
           <t>01/07</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1544,7 +1631,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1569,7 +1656,7 @@
           <t>Pesquisa de pane de vazamento de óleo do motor.</t>
         </is>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1578,7 +1665,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1614,7 +1701,7 @@
           <t>02 DIAS após chegada do item.</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1638,7 +1725,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1662,7 +1749,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1698,7 +1785,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H24" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1726,7 +1813,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" s="1" t="n">
+      <c r="H25" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1762,7 +1849,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1787,7 +1874,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1796,7 +1883,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1832,7 +1919,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1868,7 +1955,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="H29" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1904,7 +1991,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1928,7 +2015,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -1952,7 +2039,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" s="1" t="n">
+      <c r="H32" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -1988,7 +2075,7 @@
           <t>01 DIA após resposta do AT.</t>
         </is>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="H33" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2012,7 +2099,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" s="1" t="n">
+      <c r="H34" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2036,7 +2123,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" s="1" t="n">
+      <c r="H35" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2061,7 +2148,7 @@
           <t>Realizando inspeções ID 0A,20,21,22 / 4100FH</t>
         </is>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2070,7 +2157,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="H36" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2095,7 +2182,7 @@
           <t>Pesquisa no sistema de indicação de flape.</t>
         </is>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -2104,7 +2191,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2129,7 +2216,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2138,7 +2225,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H38" s="1" t="n">
+      <c r="H38" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2163,7 +2250,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2172,7 +2259,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="H39" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2196,7 +2283,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="1" t="n">
+      <c r="H40" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2220,7 +2307,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" s="1" t="n">
+      <c r="H41" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2245,7 +2332,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2254,7 +2341,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="H42" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2278,7 +2365,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" s="1" t="n">
+      <c r="H43" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2303,7 +2390,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2312,7 +2399,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H44" s="1" t="n">
+      <c r="H44" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2336,7 +2423,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="1" t="n">
+      <c r="H45" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2360,7 +2447,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" s="1" t="n">
+      <c r="H46" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2384,7 +2471,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" s="1" t="n">
+      <c r="H47" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2408,7 +2495,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" s="1" t="n">
+      <c r="H48" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2433,7 +2520,7 @@
           <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
         </is>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -2442,7 +2529,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H49" s="1" t="n">
+      <c r="H49" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2478,7 +2565,7 @@
           <t>02 DIAS após chegada do item.</t>
         </is>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="H50" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2502,7 +2589,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" s="1" t="n">
+      <c r="H51" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2526,7 +2613,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" s="1" t="n">
+      <c r="H52" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2562,7 +2649,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H53" s="1" t="n">
+      <c r="H53" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2590,7 +2677,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="1" t="n">
+      <c r="H54" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2626,7 +2713,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H55" s="1" t="n">
+      <c r="H55" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2651,7 +2738,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -2660,7 +2747,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="H56" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2696,7 +2783,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="H57" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2732,7 +2819,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="H58" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2768,7 +2855,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="H59" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2792,7 +2879,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" s="1" t="n">
+      <c r="H60" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2816,7 +2903,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="1" t="n">
+      <c r="H61" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2841,7 +2928,7 @@
           <t>Agd parecer do AT do PAMASP sobre FCU</t>
         </is>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2850,7 +2937,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="H62" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2874,7 +2961,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" s="1" t="n">
+      <c r="H63" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2899,7 +2986,7 @@
           <t>Realizando inspeções ID 0A / 500FH</t>
         </is>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2908,7 +2995,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="H64" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2932,7 +3019,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="1" t="n">
+      <c r="H65" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2956,7 +3043,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" s="1" t="n">
+      <c r="H66" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2981,7 +3068,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2990,7 +3077,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H67" s="1" t="n">
+      <c r="H67" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3015,7 +3102,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3024,7 +3111,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H68" s="1" t="n">
+      <c r="H68" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3048,7 +3135,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" s="1" t="n">
+      <c r="H69" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3072,7 +3159,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" s="1" t="n">
+      <c r="H70" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3097,7 +3184,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3106,7 +3193,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H71" s="1" t="n">
+      <c r="H71" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3130,7 +3217,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" s="1" t="n">
+      <c r="H72" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3155,7 +3242,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3164,7 +3251,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="H73" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3188,7 +3275,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" s="1" t="n">
+      <c r="H74" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3212,7 +3299,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" s="1" t="n">
+      <c r="H75" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3236,7 +3323,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" s="1" t="n">
+      <c r="H76" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3260,7 +3347,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" s="1" t="n">
+      <c r="H77" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3285,7 +3372,7 @@
           <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
         </is>
       </c>
-      <c r="E78" s="1" t="n">
+      <c r="E78" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -3294,7 +3381,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="H78" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3330,7 +3417,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H79" s="1" t="n">
+      <c r="H79" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3354,7 +3441,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" s="1" t="n">
+      <c r="H80" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3378,7 +3465,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" s="1" t="n">
+      <c r="H81" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3414,7 +3501,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="H82" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3442,7 +3529,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" s="1" t="n">
+      <c r="H83" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3478,7 +3565,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H84" s="1" t="n">
+      <c r="H84" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3503,7 +3590,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E85" s="1" t="n">
+      <c r="E85" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3512,7 +3599,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H85" s="1" t="n">
+      <c r="H85" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3548,7 +3635,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H86" s="1" t="n">
+      <c r="H86" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3584,7 +3671,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H87" s="1" t="n">
+      <c r="H87" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3620,7 +3707,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H88" s="1" t="n">
+      <c r="H88" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3644,7 +3731,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" s="1" t="n">
+      <c r="H89" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3669,7 +3756,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E90" s="1" t="n">
+      <c r="E90" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -3678,7 +3765,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H90" s="1" t="n">
+      <c r="H90" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3703,7 +3790,7 @@
           <t>Agd parecer do AT do PAMASP sobre FCU</t>
         </is>
       </c>
-      <c r="E91" s="1" t="n">
+      <c r="E91" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -3712,7 +3799,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H91" s="1" t="n">
+      <c r="H91" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3736,7 +3823,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" s="1" t="n">
+      <c r="H92" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3761,7 +3848,7 @@
           <t>Realizando inspeções ID 0A / 500FH</t>
         </is>
       </c>
-      <c r="E93" s="1" t="n">
+      <c r="E93" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -3770,7 +3857,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H93" s="1" t="n">
+      <c r="H93" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3794,7 +3881,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" s="1" t="n">
+      <c r="H94" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3818,7 +3905,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" s="1" t="n">
+      <c r="H95" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3843,7 +3930,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E96" s="1" t="n">
+      <c r="E96" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -3852,7 +3939,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H96" s="1" t="n">
+      <c r="H96" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3877,7 +3964,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E97" s="1" t="n">
+      <c r="E97" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3886,7 +3973,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="H97" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3910,7 +3997,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" s="1" t="n">
+      <c r="H98" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3935,7 +4022,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E99" s="1" t="n">
+      <c r="E99" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -3944,7 +4031,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H99" s="1" t="n">
+      <c r="H99" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3969,7 +4056,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E100" s="1" t="n">
+      <c r="E100" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -3978,7 +4065,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H100" s="1" t="n">
+      <c r="H100" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4002,7 +4089,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" s="1" t="n">
+      <c r="H101" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4027,7 +4114,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E102" s="1" t="n">
+      <c r="E102" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -4036,7 +4123,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H102" s="1" t="n">
+      <c r="H102" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4061,7 +4148,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E103" s="1" t="n">
+      <c r="E103" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -4070,7 +4157,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H103" s="1" t="n">
+      <c r="H103" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4094,7 +4181,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" s="1" t="n">
+      <c r="H104" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4118,7 +4205,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" s="1" t="n">
+      <c r="H105" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4142,7 +4229,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" s="1" t="n">
+      <c r="H106" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4167,7 +4254,7 @@
           <t>MOTOR NÃO COMPLETANDO O CICLO DE PARTIDA, ESTABILIZANDO COM 40% DE NG</t>
         </is>
       </c>
-      <c r="E107" s="1" t="n">
+      <c r="E107" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -4176,7 +4263,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H107" s="1" t="n">
+      <c r="H107" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4212,7 +4299,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H108" s="1" t="n">
+      <c r="H108" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4236,7 +4323,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" s="1" t="n">
+      <c r="H109" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4260,7 +4347,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" s="1" t="n">
+      <c r="H110" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4296,7 +4383,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H111" s="1" t="n">
+      <c r="H111" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4324,7 +4411,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" s="1" t="n">
+      <c r="H112" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4360,7 +4447,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H113" s="1" t="n">
+      <c r="H113" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4385,7 +4472,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E114" s="1" t="n">
+      <c r="E114" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -4394,7 +4481,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H114" s="1" t="n">
+      <c r="H114" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4430,7 +4517,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H115" s="1" t="n">
+      <c r="H115" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4466,7 +4553,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H116" s="1" t="n">
+      <c r="H116" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4502,7 +4589,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H117" s="1" t="n">
+      <c r="H117" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4526,7 +4613,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" s="1" t="n">
+      <c r="H118" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4551,7 +4638,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E119" s="1" t="n">
+      <c r="E119" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -4560,7 +4647,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H119" s="1" t="n">
+      <c r="H119" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4584,7 +4671,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" s="1" t="n">
+      <c r="H120" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4608,7 +4695,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" s="1" t="n">
+      <c r="H121" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4632,7 +4719,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" s="1" t="n">
+      <c r="H122" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4656,7 +4743,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" s="1" t="n">
+      <c r="H123" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4680,7 +4767,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" s="1" t="n">
+      <c r="H124" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4705,7 +4792,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E125" s="1" t="n">
+      <c r="E125" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -4714,7 +4801,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H125" s="1" t="n">
+      <c r="H125" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4739,7 +4826,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E126" s="1" t="n">
+      <c r="E126" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4748,7 +4835,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H126" s="1" t="n">
+      <c r="H126" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4772,7 +4859,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" s="1" t="n">
+      <c r="H127" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4797,7 +4884,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E128" s="1" t="n">
+      <c r="E128" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -4806,7 +4893,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H128" s="1" t="n">
+      <c r="H128" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4831,7 +4918,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E129" s="1" t="n">
+      <c r="E129" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -4840,7 +4927,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H129" s="1" t="n">
+      <c r="H129" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4864,7 +4951,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" s="1" t="n">
+      <c r="H130" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4889,7 +4976,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E131" s="1" t="n">
+      <c r="E131" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -4898,7 +4985,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H131" s="1" t="n">
+      <c r="H131" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4923,7 +5010,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E132" s="1" t="n">
+      <c r="E132" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -4932,7 +5019,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H132" s="1" t="n">
+      <c r="H132" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4956,7 +5043,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" s="1" t="n">
+      <c r="H133" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4980,7 +5067,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" s="1" t="n">
+      <c r="H134" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5004,7 +5091,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" s="1" t="n">
+      <c r="H135" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5029,7 +5116,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E136" s="1" t="n">
+      <c r="E136" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -5038,7 +5125,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H136" s="1" t="n">
+      <c r="H136" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5074,7 +5161,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H137" s="1" t="n">
+      <c r="H137" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5098,7 +5185,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" s="1" t="n">
+      <c r="H138" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5122,7 +5209,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" s="1" t="n">
+      <c r="H139" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5158,7 +5245,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H140" s="1" t="n">
+      <c r="H140" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5186,7 +5273,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" s="1" t="n">
+      <c r="H141" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5222,7 +5309,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H142" s="1" t="n">
+      <c r="H142" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5247,7 +5334,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E143" s="1" t="n">
+      <c r="E143" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -5256,7 +5343,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H143" s="1" t="n">
+      <c r="H143" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5292,7 +5379,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H144" s="1" t="n">
+      <c r="H144" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5328,7 +5415,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H145" s="1" t="n">
+      <c r="H145" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5364,7 +5451,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H146" s="1" t="n">
+      <c r="H146" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5388,7 +5475,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" s="1" t="n">
+      <c r="H147" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5413,7 +5500,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E148" s="1" t="n">
+      <c r="E148" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -5422,7 +5509,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H148" s="1" t="n">
+      <c r="H148" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5446,7 +5533,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" s="1" t="n">
+      <c r="H149" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5470,7 +5557,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" s="1" t="n">
+      <c r="H150" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5494,7 +5581,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" s="1" t="n">
+      <c r="H151" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5518,7 +5605,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" s="1" t="n">
+      <c r="H152" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5542,7 +5629,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" s="1" t="n">
+      <c r="H153" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5567,7 +5654,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E154" s="1" t="n">
+      <c r="E154" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -5576,7 +5663,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H154" s="1" t="n">
+      <c r="H154" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5601,7 +5688,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E155" s="1" t="n">
+      <c r="E155" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -5610,7 +5697,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H155" s="1" t="n">
+      <c r="H155" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5634,7 +5721,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" s="1" t="n">
+      <c r="H156" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5659,7 +5746,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E157" s="1" t="n">
+      <c r="E157" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -5668,7 +5755,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H157" s="1" t="n">
+      <c r="H157" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5693,7 +5780,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E158" s="1" t="n">
+      <c r="E158" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -5702,7 +5789,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H158" s="1" t="n">
+      <c r="H158" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5727,7 +5814,7 @@
           <t>EM PESQUISA DE PANE DE FCU</t>
         </is>
       </c>
-      <c r="E159" s="1" t="n">
+      <c r="E159" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5736,7 +5823,7 @@
           <t>09/07</t>
         </is>
       </c>
-      <c r="H159" s="1" t="n">
+      <c r="H159" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5761,7 +5848,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E160" s="1" t="n">
+      <c r="E160" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -5770,7 +5857,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H160" s="1" t="n">
+      <c r="H160" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5795,7 +5882,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E161" s="1" t="n">
+      <c r="E161" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -5804,7 +5891,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H161" s="1" t="n">
+      <c r="H161" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5828,7 +5915,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" s="1" t="n">
+      <c r="H162" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5852,7 +5939,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" s="1" t="n">
+      <c r="H163" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5876,7 +5963,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" s="1" t="n">
+      <c r="H164" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5901,7 +5988,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E165" s="1" t="n">
+      <c r="E165" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -5910,7 +5997,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H165" s="1" t="n">
+      <c r="H165" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5946,7 +6033,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H166" s="1" t="n">
+      <c r="H166" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5970,7 +6057,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" s="1" t="n">
+      <c r="H167" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5994,7 +6081,7 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" s="1" t="n">
+      <c r="H168" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6030,7 +6117,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H169" s="1" t="n">
+      <c r="H169" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6058,7 +6145,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
-      <c r="H170" s="1" t="n">
+      <c r="H170" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6094,7 +6181,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H171" s="1" t="n">
+      <c r="H171" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6119,7 +6206,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E172" s="1" t="n">
+      <c r="E172" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -6128,7 +6215,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H172" s="1" t="n">
+      <c r="H172" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6164,7 +6251,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H173" s="1" t="n">
+      <c r="H173" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6200,7 +6287,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H174" s="1" t="n">
+      <c r="H174" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6236,8 +6323,890 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H175" s="1" t="n">
+      <c r="H175" s="2" t="n">
         <v>46212</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M, 01 IPLR de FCU</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1º ETA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1º/15º GAV</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Pesquisa de pane no painel de alarmes.</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1º/5º GAV</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Realizando inspeções 4300 FH/HSI.</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2º ETA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5º ETA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ITR</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Agd transmissão do atuador do flape</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Pesquisa de pane de FCU</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>6º ETA</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Motor recolhido para reparo na geradora de gases</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2741</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>7º ETA</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>15/07</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Itens entregues. Agd AT de hélice para definição de recolhimento ou translado da aeronave para o Parque</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>DACTA II</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>75 APE</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>A ser definido.</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ANV acidentada.</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>91 AIFP. Serão atendidas pela Vee One e FAB</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>A DET</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Aguardando avaliação de sinistro</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>06/07</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 44 IPLR</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 13 IPLR</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP.</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>PAMA-LS</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SEM MOTOR - 57 IPLR</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Aguarda DPE do PAMASP e PAMALS.</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>46213</v>
       </c>
     </row>
   </sheetData>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -21,16 +21,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -434,114 +422,114 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>disponiveis_hoje</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>montadas_hoje</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>di</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>do_</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ii</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>in_</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>itr</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>previsao_fim_dia_disponiveis</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>previsao_fim_dia_montadas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>previsao_semana_disponiveis_qtd</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>previsao_semana_disponiveis_novas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>previsao_semana_montadas_qtd</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>previsao_semana_montadas_novas</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>esforco_anual_previsto</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>esforco_anual_realizado</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>esforco_percentual</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>motores_disponiveis</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>arquivo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B2" t="n">
@@ -616,7 +604,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="B3" t="n">
@@ -691,7 +679,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="B4" t="n">
@@ -766,7 +754,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="B5" t="n">
@@ -841,7 +829,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46211</v>
       </c>
       <c r="B6" t="n">
@@ -916,7 +904,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="B7" t="n">
@@ -991,7 +979,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B8" t="n">
@@ -1080,42 +1068,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>matricula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unidade</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>situacao</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ocorrencia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>dpe_data</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>dpe_condicao</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>dpe_texto_original</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
@@ -1141,7 +1129,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1165,7 +1153,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1201,7 +1189,7 @@
           <t>01 DIA após chegada do item.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1225,7 +1213,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1249,7 +1237,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1274,7 +1262,7 @@
           <t>Realizando inspeções ID 0A,20,21,22 / 4100FH</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1283,7 +1271,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1308,7 +1296,7 @@
           <t>Pesquisa no sistema de indicação de flape.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1317,7 +1305,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1342,7 +1330,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1351,7 +1339,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1376,7 +1364,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1385,7 +1373,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1409,7 +1397,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1433,7 +1421,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1458,7 +1446,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1467,7 +1455,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1491,7 +1479,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1516,7 +1504,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1525,7 +1513,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1549,7 +1537,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1573,7 +1561,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1598,7 +1586,7 @@
           <t>Realizando inspeções programadas.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1607,7 +1595,7 @@
           <t>01/07</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1631,7 +1619,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1656,7 +1644,7 @@
           <t>Pesquisa de pane de vazamento de óleo do motor.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1665,7 +1653,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1701,7 +1689,7 @@
           <t>02 DIAS após chegada do item.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1725,7 +1713,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1749,7 +1737,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1785,7 +1773,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1813,7 +1801,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1849,7 +1837,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1874,7 +1862,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1883,7 +1871,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1919,7 +1907,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1955,7 +1943,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1991,7 +1979,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -2015,7 +2003,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" s="2" t="n">
+      <c r="H31" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2039,7 +2027,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2075,7 +2063,7 @@
           <t>01 DIA após resposta do AT.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2099,7 +2087,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2123,7 +2111,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2148,7 +2136,7 @@
           <t>Realizando inspeções ID 0A,20,21,22 / 4100FH</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2157,7 +2145,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2182,7 +2170,7 @@
           <t>Pesquisa no sistema de indicação de flape.</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -2191,7 +2179,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H37" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2216,7 +2204,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2225,7 +2213,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2250,7 +2238,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2259,7 +2247,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2283,7 +2271,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2307,7 +2295,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" s="2" t="n">
+      <c r="H41" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2332,7 +2320,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2341,7 +2329,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2365,7 +2353,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" s="2" t="n">
+      <c r="H43" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2390,7 +2378,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2399,7 +2387,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2423,7 +2411,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2447,7 +2435,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2471,7 +2459,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" s="2" t="n">
+      <c r="H47" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2495,7 +2483,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2520,7 +2508,7 @@
           <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -2529,7 +2517,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H49" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2565,7 +2553,7 @@
           <t>02 DIAS após chegada do item.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2589,7 +2577,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2613,7 +2601,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" s="2" t="n">
+      <c r="H52" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2649,7 +2637,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H53" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2677,7 +2665,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2713,7 +2701,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H55" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2738,7 +2726,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -2747,7 +2735,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2783,7 +2771,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H57" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2819,7 +2807,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2855,7 +2843,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H59" s="1" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2879,7 +2867,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" s="2" t="n">
+      <c r="H60" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2903,7 +2891,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="2" t="n">
+      <c r="H61" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2928,7 +2916,7 @@
           <t>Agd parecer do AT do PAMASP sobre FCU</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2937,7 +2925,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2961,7 +2949,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" s="2" t="n">
+      <c r="H63" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2986,7 +2974,7 @@
           <t>Realizando inspeções ID 0A / 500FH</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2995,7 +2983,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3019,7 +3007,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="2" t="n">
+      <c r="H65" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3043,7 +3031,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3068,7 +3056,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3077,7 +3065,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H67" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3102,7 +3090,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3111,7 +3099,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H68" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3135,7 +3123,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" s="2" t="n">
+      <c r="H69" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3159,7 +3147,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3184,7 +3172,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3193,7 +3181,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H71" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3217,7 +3205,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" s="2" t="n">
+      <c r="H72" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3242,7 +3230,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3251,7 +3239,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H73" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3275,7 +3263,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3299,7 +3287,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" s="2" t="n">
+      <c r="H75" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3323,7 +3311,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3347,7 +3335,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" s="2" t="n">
+      <c r="H77" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3372,7 +3360,7 @@
           <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -3381,7 +3369,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3417,7 +3405,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H79" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3441,7 +3429,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3465,7 +3453,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" s="2" t="n">
+      <c r="H81" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3501,7 +3489,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3529,7 +3517,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" s="2" t="n">
+      <c r="H83" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3565,7 +3553,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H84" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3590,7 +3578,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E85" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3599,7 +3587,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="H85" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3635,7 +3623,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H86" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3671,7 +3659,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H87" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3707,7 +3695,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H88" s="1" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3731,7 +3719,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" s="2" t="n">
+      <c r="H89" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3756,7 +3744,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E90" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -3765,7 +3753,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3790,7 +3778,7 @@
           <t>Agd parecer do AT do PAMASP sobre FCU</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -3799,7 +3787,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H91" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3823,7 +3811,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" s="2" t="n">
+      <c r="H92" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3848,7 +3836,7 @@
           <t>Realizando inspeções ID 0A / 500FH</t>
         </is>
       </c>
-      <c r="E93" s="2" t="n">
+      <c r="E93" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -3857,7 +3845,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="H93" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3881,7 +3869,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" s="2" t="n">
+      <c r="H94" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3905,7 +3893,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" s="2" t="n">
+      <c r="H95" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3930,7 +3918,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E96" s="2" t="n">
+      <c r="E96" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -3939,7 +3927,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H96" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3964,7 +3952,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E97" s="2" t="n">
+      <c r="E97" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3973,7 +3961,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H97" s="2" t="n">
+      <c r="H97" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3997,7 +3985,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" s="2" t="n">
+      <c r="H98" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4022,7 +4010,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n">
+      <c r="E99" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -4031,7 +4019,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="H99" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4056,7 +4044,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n">
+      <c r="E100" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -4065,7 +4053,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="H100" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4089,7 +4077,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" s="2" t="n">
+      <c r="H101" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4114,7 +4102,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="E102" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -4123,7 +4111,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H102" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4148,7 +4136,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -4157,7 +4145,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H103" s="2" t="n">
+      <c r="H103" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4181,7 +4169,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" s="2" t="n">
+      <c r="H104" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4205,7 +4193,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" s="2" t="n">
+      <c r="H105" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4229,7 +4217,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" s="2" t="n">
+      <c r="H106" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4254,7 +4242,7 @@
           <t>MOTOR NÃO COMPLETANDO O CICLO DE PARTIDA, ESTABILIZANDO COM 40% DE NG</t>
         </is>
       </c>
-      <c r="E107" s="2" t="n">
+      <c r="E107" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -4263,7 +4251,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H107" s="2" t="n">
+      <c r="H107" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4299,7 +4287,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="n">
+      <c r="H108" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4323,7 +4311,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" s="2" t="n">
+      <c r="H109" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4347,7 +4335,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" s="2" t="n">
+      <c r="H110" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4383,7 +4371,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="n">
+      <c r="H111" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4411,7 +4399,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" s="2" t="n">
+      <c r="H112" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4447,7 +4435,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H113" s="2" t="n">
+      <c r="H113" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4472,7 +4460,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E114" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -4481,7 +4469,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H114" s="2" t="n">
+      <c r="H114" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4517,7 +4505,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="n">
+      <c r="H115" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4553,7 +4541,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="n">
+      <c r="H116" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4589,7 +4577,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="n">
+      <c r="H117" s="1" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4613,7 +4601,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" s="2" t="n">
+      <c r="H118" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4638,7 +4626,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E119" s="2" t="n">
+      <c r="E119" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -4647,7 +4635,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H119" s="2" t="n">
+      <c r="H119" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4671,7 +4659,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" s="2" t="n">
+      <c r="H120" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4695,7 +4683,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" s="2" t="n">
+      <c r="H121" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4719,7 +4707,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" s="2" t="n">
+      <c r="H122" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4743,7 +4731,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" s="2" t="n">
+      <c r="H123" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4767,7 +4755,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" s="2" t="n">
+      <c r="H124" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4792,7 +4780,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E125" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -4801,7 +4789,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H125" s="2" t="n">
+      <c r="H125" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4826,7 +4814,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E126" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4835,7 +4823,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H126" s="2" t="n">
+      <c r="H126" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4859,7 +4847,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" s="2" t="n">
+      <c r="H127" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4884,7 +4872,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E128" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -4893,7 +4881,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H128" s="2" t="n">
+      <c r="H128" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4918,7 +4906,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n">
+      <c r="E129" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -4927,7 +4915,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H129" s="2" t="n">
+      <c r="H129" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4951,7 +4939,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" s="2" t="n">
+      <c r="H130" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4976,7 +4964,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E131" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -4985,7 +4973,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H131" s="2" t="n">
+      <c r="H131" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5010,7 +4998,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E132" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -5019,7 +5007,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H132" s="2" t="n">
+      <c r="H132" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5043,7 +5031,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" s="2" t="n">
+      <c r="H133" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5067,7 +5055,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" s="2" t="n">
+      <c r="H134" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5091,7 +5079,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" s="2" t="n">
+      <c r="H135" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5116,7 +5104,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="E136" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -5125,7 +5113,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H136" s="2" t="n">
+      <c r="H136" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5161,7 +5149,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="n">
+      <c r="H137" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5185,7 +5173,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" s="2" t="n">
+      <c r="H138" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5209,7 +5197,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" s="2" t="n">
+      <c r="H139" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5245,7 +5233,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="n">
+      <c r="H140" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5273,7 +5261,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" s="2" t="n">
+      <c r="H141" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5309,7 +5297,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H142" s="2" t="n">
+      <c r="H142" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5334,7 +5322,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E143" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -5343,7 +5331,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H143" s="2" t="n">
+      <c r="H143" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5379,7 +5367,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="n">
+      <c r="H144" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5415,7 +5403,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="n">
+      <c r="H145" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5451,7 +5439,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="n">
+      <c r="H146" s="1" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5475,7 +5463,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" s="2" t="n">
+      <c r="H147" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5500,7 +5488,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="E148" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -5509,7 +5497,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H148" s="2" t="n">
+      <c r="H148" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5533,7 +5521,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" s="2" t="n">
+      <c r="H149" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5557,7 +5545,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" s="2" t="n">
+      <c r="H150" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5581,7 +5569,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" s="2" t="n">
+      <c r="H151" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5605,7 +5593,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" s="2" t="n">
+      <c r="H152" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5629,7 +5617,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" s="2" t="n">
+      <c r="H153" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5654,7 +5642,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E154" s="2" t="n">
+      <c r="E154" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -5663,7 +5651,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H154" s="2" t="n">
+      <c r="H154" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5688,7 +5676,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E155" s="2" t="n">
+      <c r="E155" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -5697,7 +5685,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H155" s="2" t="n">
+      <c r="H155" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5721,7 +5709,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" s="2" t="n">
+      <c r="H156" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5746,7 +5734,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E157" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -5755,7 +5743,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H157" s="2" t="n">
+      <c r="H157" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5780,7 +5768,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E158" s="2" t="n">
+      <c r="E158" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -5789,7 +5777,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H158" s="2" t="n">
+      <c r="H158" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5814,7 +5802,7 @@
           <t>EM PESQUISA DE PANE DE FCU</t>
         </is>
       </c>
-      <c r="E159" s="2" t="n">
+      <c r="E159" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5823,7 +5811,7 @@
           <t>09/07</t>
         </is>
       </c>
-      <c r="H159" s="2" t="n">
+      <c r="H159" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5848,7 +5836,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="E160" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -5857,7 +5845,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H160" s="2" t="n">
+      <c r="H160" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5882,7 +5870,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E161" s="2" t="n">
+      <c r="E161" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -5891,7 +5879,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H161" s="2" t="n">
+      <c r="H161" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5915,7 +5903,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" s="2" t="n">
+      <c r="H162" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5939,7 +5927,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" s="2" t="n">
+      <c r="H163" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5963,7 +5951,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" s="2" t="n">
+      <c r="H164" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5988,7 +5976,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="E165" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -5997,7 +5985,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H165" s="2" t="n">
+      <c r="H165" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6033,7 +6021,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="n">
+      <c r="H166" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6057,7 +6045,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" s="2" t="n">
+      <c r="H167" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6081,7 +6069,7 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" s="2" t="n">
+      <c r="H168" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6117,7 +6105,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="n">
+      <c r="H169" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6145,7 +6133,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
-      <c r="H170" s="2" t="n">
+      <c r="H170" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6181,7 +6169,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H171" s="2" t="n">
+      <c r="H171" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6206,7 +6194,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n">
+      <c r="E172" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -6215,7 +6203,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H172" s="2" t="n">
+      <c r="H172" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6251,7 +6239,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H173" s="2" t="n">
+      <c r="H173" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6287,7 +6275,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H174" s="2" t="n">
+      <c r="H174" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6323,7 +6311,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H175" s="2" t="n">
+      <c r="H175" s="1" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6347,7 +6335,7 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
-      <c r="H176" s="2" t="n">
+      <c r="H176" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6372,7 +6360,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M, 01 IPLR de FCU</t>
         </is>
       </c>
-      <c r="E177" s="2" t="n">
+      <c r="E177" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -6381,7 +6369,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H177" s="2" t="n">
+      <c r="H177" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6405,7 +6393,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
-      <c r="H178" s="2" t="n">
+      <c r="H178" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6430,7 +6418,7 @@
           <t>Pesquisa de pane no painel de alarmes.</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n">
+      <c r="E179" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -6439,7 +6427,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H179" s="2" t="n">
+      <c r="H179" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6463,7 +6451,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
-      <c r="H180" s="2" t="n">
+      <c r="H180" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6487,7 +6475,7 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
-      <c r="H181" s="2" t="n">
+      <c r="H181" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6511,7 +6499,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
-      <c r="H182" s="2" t="n">
+      <c r="H182" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6536,7 +6524,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E183" s="2" t="n">
+      <c r="E183" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -6545,7 +6533,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H183" s="2" t="n">
+      <c r="H183" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6570,7 +6558,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E184" s="2" t="n">
+      <c r="E184" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -6579,7 +6567,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H184" s="2" t="n">
+      <c r="H184" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6603,7 +6591,7 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
-      <c r="H185" s="2" t="n">
+      <c r="H185" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6628,7 +6616,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E186" s="2" t="n">
+      <c r="E186" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -6637,7 +6625,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H186" s="2" t="n">
+      <c r="H186" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6662,7 +6650,7 @@
           <t>Agd transmissão do atuador do flape</t>
         </is>
       </c>
-      <c r="E187" s="2" t="n">
+      <c r="E187" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -6671,7 +6659,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H187" s="2" t="n">
+      <c r="H187" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6696,7 +6684,7 @@
           <t>Pesquisa de pane de FCU</t>
         </is>
       </c>
-      <c r="E188" s="2" t="n">
+      <c r="E188" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -6705,7 +6693,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H188" s="2" t="n">
+      <c r="H188" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6730,7 +6718,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E189" s="2" t="n">
+      <c r="E189" s="1" t="n">
         <v>46216</v>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -6739,7 +6727,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H189" s="2" t="n">
+      <c r="H189" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6764,7 +6752,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E190" s="2" t="n">
+      <c r="E190" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -6773,7 +6761,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H190" s="2" t="n">
+      <c r="H190" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6797,7 +6785,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
-      <c r="H191" s="2" t="n">
+      <c r="H191" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6821,7 +6809,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
-      <c r="H192" s="2" t="n">
+      <c r="H192" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6845,7 +6833,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
-      <c r="H193" s="2" t="n">
+      <c r="H193" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6870,7 +6858,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E194" s="2" t="n">
+      <c r="E194" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -6879,7 +6867,7 @@
           <t>15/07</t>
         </is>
       </c>
-      <c r="H194" s="2" t="n">
+      <c r="H194" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6915,7 +6903,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H195" s="2" t="n">
+      <c r="H195" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6939,7 +6927,7 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
-      <c r="H196" s="2" t="n">
+      <c r="H196" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6963,7 +6951,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" s="2" t="n">
+      <c r="H197" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6999,7 +6987,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H198" s="2" t="n">
+      <c r="H198" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7027,7 +7015,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" s="2" t="n">
+      <c r="H199" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7063,7 +7051,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H200" s="2" t="n">
+      <c r="H200" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7088,7 +7076,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E201" s="2" t="n">
+      <c r="E201" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -7097,7 +7085,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H201" s="2" t="n">
+      <c r="H201" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7133,7 +7121,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H202" s="2" t="n">
+      <c r="H202" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7169,7 +7157,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H203" s="2" t="n">
+      <c r="H203" s="1" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7205,7 +7193,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H204" s="2" t="n">
+      <c r="H204" s="1" t="n">
         <v>46213</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -422,114 +434,114 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>disponiveis_hoje</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>montadas_hoje</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>di</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>do_</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ii</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>in_</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>itr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>is_</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>previsao_fim_dia_disponiveis</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>previsao_fim_dia_montadas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>previsao_semana_disponiveis_qtd</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>previsao_semana_disponiveis_novas</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>previsao_semana_montadas_qtd</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>previsao_semana_montadas_novas</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>esforco_anual_previsto</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>esforco_anual_realizado</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>esforco_percentual</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>motores_disponiveis</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>arquivo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B2" t="n">
@@ -604,7 +616,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46205</v>
       </c>
       <c r="B3" t="n">
@@ -679,7 +691,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="B4" t="n">
@@ -754,7 +766,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="B5" t="n">
@@ -829,7 +841,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46211</v>
       </c>
       <c r="B6" t="n">
@@ -904,7 +916,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="B7" t="n">
@@ -979,7 +991,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B8" t="n">
@@ -1068,42 +1080,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>matricula</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>unidade</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>situacao</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ocorrencia</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>dpe_data</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dpe_condicao</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dpe_texto_original</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
@@ -1129,7 +1141,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1153,7 +1165,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1189,7 +1201,7 @@
           <t>01 DIA após chegada do item.</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1213,7 +1225,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1237,7 +1249,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1262,7 +1274,7 @@
           <t>Realizando inspeções ID 0A,20,21,22 / 4100FH</t>
         </is>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -1271,7 +1283,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1296,7 +1308,7 @@
           <t>Pesquisa no sistema de indicação de flape.</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -1305,7 +1317,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1330,7 +1342,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1339,7 +1351,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1364,7 +1376,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1373,7 +1385,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1397,7 +1409,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1421,7 +1433,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1446,7 +1458,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1455,7 +1467,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1479,7 +1491,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1504,7 +1516,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1513,7 +1525,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1537,7 +1549,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1561,7 +1573,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1586,7 +1598,7 @@
           <t>Realizando inspeções programadas.</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1595,7 +1607,7 @@
           <t>01/07</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1619,7 +1631,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1644,7 +1656,7 @@
           <t>Pesquisa de pane de vazamento de óleo do motor.</t>
         </is>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1653,7 +1665,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1689,7 +1701,7 @@
           <t>02 DIAS após chegada do item.</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1713,7 +1725,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1737,7 +1749,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1773,7 +1785,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H24" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1801,7 +1813,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" s="1" t="n">
+      <c r="H25" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1837,7 +1849,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1862,7 +1874,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1871,7 +1883,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1907,7 +1919,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1943,7 +1955,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="H29" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1979,7 +1991,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="2" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -2003,7 +2015,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2027,7 +2039,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" s="1" t="n">
+      <c r="H32" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2063,7 +2075,7 @@
           <t>01 DIA após resposta do AT.</t>
         </is>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="H33" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2087,7 +2099,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" s="1" t="n">
+      <c r="H34" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2111,7 +2123,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" s="1" t="n">
+      <c r="H35" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2136,7 +2148,7 @@
           <t>Realizando inspeções ID 0A,20,21,22 / 4100FH</t>
         </is>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -2145,7 +2157,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="H36" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2170,7 +2182,7 @@
           <t>Pesquisa no sistema de indicação de flape.</t>
         </is>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -2179,7 +2191,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2204,7 +2216,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2213,7 +2225,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H38" s="1" t="n">
+      <c r="H38" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2238,7 +2250,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2247,7 +2259,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="H39" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2271,7 +2283,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="1" t="n">
+      <c r="H40" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2295,7 +2307,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" s="1" t="n">
+      <c r="H41" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2320,7 +2332,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2329,7 +2341,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="H42" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2353,7 +2365,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" s="1" t="n">
+      <c r="H43" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2378,7 +2390,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2387,7 +2399,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H44" s="1" t="n">
+      <c r="H44" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2411,7 +2423,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="1" t="n">
+      <c r="H45" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2435,7 +2447,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" s="1" t="n">
+      <c r="H46" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2459,7 +2471,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" s="1" t="n">
+      <c r="H47" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2483,7 +2495,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" s="1" t="n">
+      <c r="H48" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2508,7 +2520,7 @@
           <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
         </is>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -2517,7 +2529,7 @@
           <t>03/07</t>
         </is>
       </c>
-      <c r="H49" s="1" t="n">
+      <c r="H49" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2553,7 +2565,7 @@
           <t>02 DIAS após chegada do item.</t>
         </is>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="H50" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2577,7 +2589,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" s="1" t="n">
+      <c r="H51" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2601,7 +2613,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" s="1" t="n">
+      <c r="H52" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2637,7 +2649,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H53" s="1" t="n">
+      <c r="H53" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2665,7 +2677,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="1" t="n">
+      <c r="H54" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2701,7 +2713,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H55" s="1" t="n">
+      <c r="H55" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2726,7 +2738,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -2735,7 +2747,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="H56" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2771,7 +2783,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="H57" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2807,7 +2819,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="H58" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2843,7 +2855,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="H59" s="2" t="n">
         <v>46205</v>
       </c>
     </row>
@@ -2867,7 +2879,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" s="1" t="n">
+      <c r="H60" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2891,7 +2903,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="1" t="n">
+      <c r="H61" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2916,7 +2928,7 @@
           <t>Agd parecer do AT do PAMASP sobre FCU</t>
         </is>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2925,7 +2937,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="H62" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2949,7 +2961,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" s="1" t="n">
+      <c r="H63" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -2974,7 +2986,7 @@
           <t>Realizando inspeções ID 0A / 500FH</t>
         </is>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2983,7 +2995,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="H64" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3007,7 +3019,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="1" t="n">
+      <c r="H65" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3031,7 +3043,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" s="1" t="n">
+      <c r="H66" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3056,7 +3068,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3065,7 +3077,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H67" s="1" t="n">
+      <c r="H67" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3090,7 +3102,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3099,7 +3111,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H68" s="1" t="n">
+      <c r="H68" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3123,7 +3135,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" s="1" t="n">
+      <c r="H69" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3147,7 +3159,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" s="1" t="n">
+      <c r="H70" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3172,7 +3184,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3181,7 +3193,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H71" s="1" t="n">
+      <c r="H71" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3205,7 +3217,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" s="1" t="n">
+      <c r="H72" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3230,7 +3242,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3239,7 +3251,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="H73" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3263,7 +3275,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" s="1" t="n">
+      <c r="H74" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3287,7 +3299,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" s="1" t="n">
+      <c r="H75" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3311,7 +3323,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" s="1" t="n">
+      <c r="H76" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3335,7 +3347,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" s="1" t="n">
+      <c r="H77" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3360,7 +3372,7 @@
           <t>Motor apresentando T5 limítrofe, em pesquisa de pane e substituição do terminal T5</t>
         </is>
       </c>
-      <c r="E78" s="1" t="n">
+      <c r="E78" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -3369,7 +3381,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="H78" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3405,7 +3417,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H79" s="1" t="n">
+      <c r="H79" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3429,7 +3441,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" s="1" t="n">
+      <c r="H80" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3453,7 +3465,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" s="1" t="n">
+      <c r="H81" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3489,7 +3501,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="H82" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3517,7 +3529,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" s="1" t="n">
+      <c r="H83" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3553,7 +3565,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H84" s="1" t="n">
+      <c r="H84" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3578,7 +3590,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E85" s="1" t="n">
+      <c r="E85" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3587,7 +3599,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H85" s="1" t="n">
+      <c r="H85" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3623,7 +3635,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H86" s="1" t="n">
+      <c r="H86" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3659,7 +3671,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H87" s="1" t="n">
+      <c r="H87" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3695,7 +3707,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H88" s="1" t="n">
+      <c r="H88" s="2" t="n">
         <v>46209</v>
       </c>
     </row>
@@ -3719,7 +3731,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" s="1" t="n">
+      <c r="H89" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3744,7 +3756,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E90" s="1" t="n">
+      <c r="E90" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -3753,7 +3765,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H90" s="1" t="n">
+      <c r="H90" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3778,7 +3790,7 @@
           <t>Agd parecer do AT do PAMASP sobre FCU</t>
         </is>
       </c>
-      <c r="E91" s="1" t="n">
+      <c r="E91" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -3787,7 +3799,7 @@
           <t>07/07</t>
         </is>
       </c>
-      <c r="H91" s="1" t="n">
+      <c r="H91" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3811,7 +3823,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" s="1" t="n">
+      <c r="H92" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3836,7 +3848,7 @@
           <t>Realizando inspeções ID 0A / 500FH</t>
         </is>
       </c>
-      <c r="E93" s="1" t="n">
+      <c r="E93" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -3845,7 +3857,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H93" s="1" t="n">
+      <c r="H93" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3869,7 +3881,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" s="1" t="n">
+      <c r="H94" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3893,7 +3905,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" s="1" t="n">
+      <c r="H95" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3918,7 +3930,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E96" s="1" t="n">
+      <c r="E96" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -3927,7 +3939,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H96" s="1" t="n">
+      <c r="H96" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3952,7 +3964,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E97" s="1" t="n">
+      <c r="E97" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3961,7 +3973,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="H97" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -3985,7 +3997,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" s="1" t="n">
+      <c r="H98" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4010,7 +4022,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E99" s="1" t="n">
+      <c r="E99" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -4019,7 +4031,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H99" s="1" t="n">
+      <c r="H99" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4044,7 +4056,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E100" s="1" t="n">
+      <c r="E100" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -4053,7 +4065,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H100" s="1" t="n">
+      <c r="H100" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4077,7 +4089,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" s="1" t="n">
+      <c r="H101" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4102,7 +4114,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E102" s="1" t="n">
+      <c r="E102" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -4111,7 +4123,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H102" s="1" t="n">
+      <c r="H102" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4136,7 +4148,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E103" s="1" t="n">
+      <c r="E103" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -4145,7 +4157,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H103" s="1" t="n">
+      <c r="H103" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4169,7 +4181,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" s="1" t="n">
+      <c r="H104" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4193,7 +4205,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" s="1" t="n">
+      <c r="H105" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4217,7 +4229,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" s="1" t="n">
+      <c r="H106" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4242,7 +4254,7 @@
           <t>MOTOR NÃO COMPLETANDO O CICLO DE PARTIDA, ESTABILIZANDO COM 40% DE NG</t>
         </is>
       </c>
-      <c r="E107" s="1" t="n">
+      <c r="E107" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -4251,7 +4263,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H107" s="1" t="n">
+      <c r="H107" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4287,7 +4299,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H108" s="1" t="n">
+      <c r="H108" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4311,7 +4323,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" s="1" t="n">
+      <c r="H109" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4335,7 +4347,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" s="1" t="n">
+      <c r="H110" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4371,7 +4383,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H111" s="1" t="n">
+      <c r="H111" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4399,7 +4411,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" s="1" t="n">
+      <c r="H112" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4435,7 +4447,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H113" s="1" t="n">
+      <c r="H113" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4460,7 +4472,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E114" s="1" t="n">
+      <c r="E114" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -4469,7 +4481,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H114" s="1" t="n">
+      <c r="H114" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4505,7 +4517,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H115" s="1" t="n">
+      <c r="H115" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4541,7 +4553,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H116" s="1" t="n">
+      <c r="H116" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4577,7 +4589,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H117" s="1" t="n">
+      <c r="H117" s="2" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -4601,7 +4613,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" s="1" t="n">
+      <c r="H118" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4626,7 +4638,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E119" s="1" t="n">
+      <c r="E119" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -4635,7 +4647,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H119" s="1" t="n">
+      <c r="H119" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4659,7 +4671,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" s="1" t="n">
+      <c r="H120" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4683,7 +4695,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" s="1" t="n">
+      <c r="H121" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4707,7 +4719,7 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" s="1" t="n">
+      <c r="H122" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4731,7 +4743,7 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" s="1" t="n">
+      <c r="H123" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4755,7 +4767,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" s="1" t="n">
+      <c r="H124" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4780,7 +4792,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E125" s="1" t="n">
+      <c r="E125" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -4789,7 +4801,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H125" s="1" t="n">
+      <c r="H125" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4814,7 +4826,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E126" s="1" t="n">
+      <c r="E126" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4823,7 +4835,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H126" s="1" t="n">
+      <c r="H126" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4847,7 +4859,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" s="1" t="n">
+      <c r="H127" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4872,7 +4884,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E128" s="1" t="n">
+      <c r="E128" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -4881,7 +4893,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H128" s="1" t="n">
+      <c r="H128" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4906,7 +4918,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E129" s="1" t="n">
+      <c r="E129" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -4915,7 +4927,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H129" s="1" t="n">
+      <c r="H129" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4939,7 +4951,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" s="1" t="n">
+      <c r="H130" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4964,7 +4976,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E131" s="1" t="n">
+      <c r="E131" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -4973,7 +4985,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H131" s="1" t="n">
+      <c r="H131" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -4998,7 +5010,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E132" s="1" t="n">
+      <c r="E132" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -5007,7 +5019,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H132" s="1" t="n">
+      <c r="H132" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5031,7 +5043,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" s="1" t="n">
+      <c r="H133" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5055,7 +5067,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" s="1" t="n">
+      <c r="H134" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5079,7 +5091,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" s="1" t="n">
+      <c r="H135" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5104,7 +5116,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E136" s="1" t="n">
+      <c r="E136" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -5113,7 +5125,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H136" s="1" t="n">
+      <c r="H136" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5149,7 +5161,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H137" s="1" t="n">
+      <c r="H137" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5173,7 +5185,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" s="1" t="n">
+      <c r="H138" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5197,7 +5209,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" s="1" t="n">
+      <c r="H139" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5233,7 +5245,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H140" s="1" t="n">
+      <c r="H140" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5261,7 +5273,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" s="1" t="n">
+      <c r="H141" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5297,7 +5309,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H142" s="1" t="n">
+      <c r="H142" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5322,7 +5334,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E143" s="1" t="n">
+      <c r="E143" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -5331,7 +5343,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H143" s="1" t="n">
+      <c r="H143" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5367,7 +5379,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H144" s="1" t="n">
+      <c r="H144" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5403,7 +5415,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H145" s="1" t="n">
+      <c r="H145" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5439,7 +5451,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H146" s="1" t="n">
+      <c r="H146" s="2" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -5463,7 +5475,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" s="1" t="n">
+      <c r="H147" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5488,7 +5500,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M</t>
         </is>
       </c>
-      <c r="E148" s="1" t="n">
+      <c r="E148" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -5497,7 +5509,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H148" s="1" t="n">
+      <c r="H148" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5521,7 +5533,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" s="1" t="n">
+      <c r="H149" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5545,7 +5557,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" s="1" t="n">
+      <c r="H150" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5569,7 +5581,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" s="1" t="n">
+      <c r="H151" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5593,7 +5605,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" s="1" t="n">
+      <c r="H152" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5617,7 +5629,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" s="1" t="n">
+      <c r="H153" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5642,7 +5654,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E154" s="1" t="n">
+      <c r="E154" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -5651,7 +5663,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H154" s="1" t="n">
+      <c r="H154" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5676,7 +5688,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E155" s="1" t="n">
+      <c r="E155" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -5685,7 +5697,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H155" s="1" t="n">
+      <c r="H155" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5709,7 +5721,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" s="1" t="n">
+      <c r="H156" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5734,7 +5746,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E157" s="1" t="n">
+      <c r="E157" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -5743,7 +5755,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H157" s="1" t="n">
+      <c r="H157" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5768,7 +5780,7 @@
           <t>Pane no sistema de flape</t>
         </is>
       </c>
-      <c r="E158" s="1" t="n">
+      <c r="E158" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -5777,7 +5789,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H158" s="1" t="n">
+      <c r="H158" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5802,7 +5814,7 @@
           <t>EM PESQUISA DE PANE DE FCU</t>
         </is>
       </c>
-      <c r="E159" s="1" t="n">
+      <c r="E159" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5811,7 +5823,7 @@
           <t>09/07</t>
         </is>
       </c>
-      <c r="H159" s="1" t="n">
+      <c r="H159" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5836,7 +5848,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E160" s="1" t="n">
+      <c r="E160" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -5845,7 +5857,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H160" s="1" t="n">
+      <c r="H160" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5870,7 +5882,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E161" s="1" t="n">
+      <c r="E161" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -5879,7 +5891,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H161" s="1" t="n">
+      <c r="H161" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5903,7 +5915,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" s="1" t="n">
+      <c r="H162" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5927,7 +5939,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" s="1" t="n">
+      <c r="H163" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5951,7 +5963,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" s="1" t="n">
+      <c r="H164" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -5976,7 +5988,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E165" s="1" t="n">
+      <c r="E165" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -5985,7 +5997,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H165" s="1" t="n">
+      <c r="H165" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6021,7 +6033,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H166" s="1" t="n">
+      <c r="H166" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6045,7 +6057,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" s="1" t="n">
+      <c r="H167" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6069,7 +6081,7 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" s="1" t="n">
+      <c r="H168" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6105,7 +6117,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H169" s="1" t="n">
+      <c r="H169" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6133,7 +6145,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
-      <c r="H170" s="1" t="n">
+      <c r="H170" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6169,7 +6181,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H171" s="1" t="n">
+      <c r="H171" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6194,7 +6206,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E172" s="1" t="n">
+      <c r="E172" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -6203,7 +6215,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H172" s="1" t="n">
+      <c r="H172" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6239,7 +6251,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H173" s="1" t="n">
+      <c r="H173" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6275,7 +6287,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H174" s="1" t="n">
+      <c r="H174" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6311,7 +6323,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H175" s="1" t="n">
+      <c r="H175" s="2" t="n">
         <v>46212</v>
       </c>
     </row>
@@ -6335,7 +6347,7 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
-      <c r="H176" s="1" t="n">
+      <c r="H176" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6360,7 +6372,7 @@
           <t>ANV REALIZANDO INSPEÇÃO PROGRAMADA ID5-15-06/+4200FH DO MOTOR/48M, 01 IPLR de FCU</t>
         </is>
       </c>
-      <c r="E177" s="1" t="n">
+      <c r="E177" s="2" t="n">
         <v>46217</v>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -6369,7 +6381,7 @@
           <t>14/07</t>
         </is>
       </c>
-      <c r="H177" s="1" t="n">
+      <c r="H177" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6393,7 +6405,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
-      <c r="H178" s="1" t="n">
+      <c r="H178" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6418,7 +6430,7 @@
           <t>Pesquisa de pane no painel de alarmes.</t>
         </is>
       </c>
-      <c r="E179" s="1" t="n">
+      <c r="E179" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -6427,7 +6439,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H179" s="1" t="n">
+      <c r="H179" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6451,7 +6463,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
-      <c r="H180" s="1" t="n">
+      <c r="H180" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6475,7 +6487,7 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
-      <c r="H181" s="1" t="n">
+      <c r="H181" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6499,7 +6511,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
-      <c r="H182" s="1" t="n">
+      <c r="H182" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6524,7 +6536,7 @@
           <t>Realizando inspeções ID 0A,02,07,10,11,12,21,22 / 2900FH/HSI</t>
         </is>
       </c>
-      <c r="E183" s="1" t="n">
+      <c r="E183" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -6533,7 +6545,7 @@
           <t>31/07</t>
         </is>
       </c>
-      <c r="H183" s="1" t="n">
+      <c r="H183" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6558,7 +6570,7 @@
           <t>Realizando inspeções 4300 FH/HSI.</t>
         </is>
       </c>
-      <c r="E184" s="1" t="n">
+      <c r="E184" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -6567,7 +6579,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H184" s="1" t="n">
+      <c r="H184" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6591,7 +6603,7 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
-      <c r="H185" s="1" t="n">
+      <c r="H185" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6616,7 +6628,7 @@
           <t>ANV REALIZANDO INSPEÇÕES ID5-15-0A/07 E 4400FH</t>
         </is>
       </c>
-      <c r="E186" s="1" t="n">
+      <c r="E186" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -6625,7 +6637,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H186" s="1" t="n">
+      <c r="H186" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6650,7 +6662,7 @@
           <t>Agd transmissão do atuador do flape</t>
         </is>
       </c>
-      <c r="E187" s="1" t="n">
+      <c r="E187" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -6659,7 +6671,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H187" s="1" t="n">
+      <c r="H187" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6684,7 +6696,7 @@
           <t>Pesquisa de pane de FCU</t>
         </is>
       </c>
-      <c r="E188" s="1" t="n">
+      <c r="E188" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -6693,7 +6705,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H188" s="1" t="n">
+      <c r="H188" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6718,7 +6730,7 @@
           <t>Motor recolhido para reparo na geradora de gases</t>
         </is>
       </c>
-      <c r="E189" s="1" t="n">
+      <c r="E189" s="2" t="n">
         <v>46216</v>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -6727,7 +6739,7 @@
           <t>13/07</t>
         </is>
       </c>
-      <c r="H189" s="1" t="n">
+      <c r="H189" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6752,7 +6764,7 @@
           <t>REALIZANDO INSPEÇÃO ID5-15-0A (3130021644), 3900H (MOT) (3130021645) ,MOT2M6 (MOT)( 3130021646)</t>
         </is>
       </c>
-      <c r="E190" s="1" t="n">
+      <c r="E190" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -6761,7 +6773,7 @@
           <t>10/07</t>
         </is>
       </c>
-      <c r="H190" s="1" t="n">
+      <c r="H190" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6785,7 +6797,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
-      <c r="H191" s="1" t="n">
+      <c r="H191" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6809,7 +6821,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
-      <c r="H192" s="1" t="n">
+      <c r="H192" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6833,7 +6845,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
-      <c r="H193" s="1" t="n">
+      <c r="H193" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6858,7 +6870,7 @@
           <t>Motor não completando ciclo de partida, estabilizando com 40% de NG</t>
         </is>
       </c>
-      <c r="E194" s="1" t="n">
+      <c r="E194" s="2" t="n">
         <v>46218</v>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -6867,7 +6879,7 @@
           <t>15/07</t>
         </is>
       </c>
-      <c r="H194" s="1" t="n">
+      <c r="H194" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6903,7 +6915,7 @@
           <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
         </is>
       </c>
-      <c r="H195" s="1" t="n">
+      <c r="H195" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6927,7 +6939,7 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
-      <c r="H196" s="1" t="n">
+      <c r="H196" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6951,7 +6963,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" s="1" t="n">
+      <c r="H197" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -6987,7 +6999,7 @@
           <t>A ser definido.</t>
         </is>
       </c>
-      <c r="H198" s="1" t="n">
+      <c r="H198" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7015,7 +7027,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" s="1" t="n">
+      <c r="H199" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7051,7 +7063,7 @@
           <t>A DET</t>
         </is>
       </c>
-      <c r="H200" s="1" t="n">
+      <c r="H200" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7076,7 +7088,7 @@
           <t>Aguardando avaliação de sinistro</t>
         </is>
       </c>
-      <c r="E201" s="1" t="n">
+      <c r="E201" s="2" t="n">
         <v>46209</v>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -7085,7 +7097,7 @@
           <t>06/07</t>
         </is>
       </c>
-      <c r="H201" s="1" t="n">
+      <c r="H201" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7121,7 +7133,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H202" s="1" t="n">
+      <c r="H202" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7157,7 +7169,7 @@
           <t>Aguarda DPE do PAMASP.</t>
         </is>
       </c>
-      <c r="H203" s="1" t="n">
+      <c r="H203" s="2" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -7193,7 +7205,7 @@
           <t>Aguarda DPE do PAMASP e PAMALS.</t>
         </is>
       </c>
-      <c r="H204" s="1" t="n">
+      <c r="H204" s="2" t="n">
         <v>46213</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="172">
   <si>
     <t>data_referencia</t>
   </si>
@@ -116,6 +116,9 @@
     <t>2721</t>
   </si>
   <si>
+    <t>2721, 2743</t>
+  </si>
+  <si>
     <t>10070:00</t>
   </si>
   <si>
@@ -146,6 +149,9 @@
     <t>4621:10</t>
   </si>
   <si>
+    <t>4658:25</t>
+  </si>
+  <si>
     <t>Disponibilidade_01_07_2026.txt</t>
   </si>
   <si>
@@ -173,6 +179,9 @@
     <t>Disponibilidade_14_07_2026.txt</t>
   </si>
   <si>
+    <t>Disponibilidade_15_07_2026.txt</t>
+  </si>
+  <si>
     <t>matricula</t>
   </si>
   <si>
@@ -443,6 +452,12 @@
     <t>Motor em recolhimento ao PAMASP. OS 3130021786.</t>
   </si>
   <si>
+    <t>Realizando inspeções ID5-15-0A(CEL), CORR60M E 300H(MOT)</t>
+  </si>
+  <si>
+    <t>Motor em recolhimento ao PAMASP. OS 3130021786. Será usado motor do 2732</t>
+  </si>
+  <si>
     <t>01 DIA após chegada do item.</t>
   </si>
   <si>
@@ -510,6 +525,12 @@
   </si>
   <si>
     <t>03/08</t>
+  </si>
+  <si>
+    <t>16/07</t>
+  </si>
+  <si>
+    <t>24/07</t>
   </si>
 </sst>
 </file>
@@ -519,8 +540,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -536,7 +565,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -544,12 +573,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -845,76 +892,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -963,10 +1010,10 @@
         <v>29</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S2">
         <v>41.81</v>
@@ -975,11 +1022,11 @@
         <v>24</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1028,10 +1075,10 @@
         <v>30</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S3">
         <v>42.15</v>
@@ -1040,11 +1087,11 @@
         <v>24</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1093,10 +1140,10 @@
         <v>30</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S4">
         <v>42.88</v>
@@ -1105,11 +1152,11 @@
         <v>24</v>
       </c>
       <c r="U4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1158,10 +1205,10 @@
         <v>30</v>
       </c>
       <c r="Q5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S5">
         <v>43.44</v>
@@ -1170,11 +1217,11 @@
         <v>24</v>
       </c>
       <c r="U5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1223,10 +1270,10 @@
         <v>31</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S6">
         <v>43.76</v>
@@ -1235,11 +1282,11 @@
         <v>24</v>
       </c>
       <c r="U6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1288,10 +1335,10 @@
         <v>31</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S7">
         <v>44.33</v>
@@ -1300,11 +1347,11 @@
         <v>24</v>
       </c>
       <c r="U7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1353,10 +1400,10 @@
         <v>31</v>
       </c>
       <c r="Q8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S8">
         <v>44.51</v>
@@ -1365,11 +1412,11 @@
         <v>24</v>
       </c>
       <c r="U8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1418,10 +1465,10 @@
         <v>31</v>
       </c>
       <c r="Q9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S9">
         <v>45.03</v>
@@ -1430,11 +1477,11 @@
         <v>24</v>
       </c>
       <c r="U9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1483,10 +1530,10 @@
         <v>32</v>
       </c>
       <c r="Q10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S10">
         <v>45.89</v>
@@ -1495,7 +1542,72 @@
         <v>24</v>
       </c>
       <c r="U10" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>13</v>
+      </c>
+      <c r="L11">
+        <v>18</v>
+      </c>
+      <c r="M11">
+        <v>16</v>
+      </c>
+      <c r="N11" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11">
+        <v>20</v>
+      </c>
+      <c r="P11" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R11" t="s">
+        <v>44</v>
+      </c>
+      <c r="S11">
+        <v>46.26</v>
+      </c>
+      <c r="T11">
+        <v>24</v>
+      </c>
+      <c r="U11" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1505,268 +1617,268 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H262"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H4" s="1">
+        <v>147</v>
+      </c>
+      <c r="H4" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="1">
+        <v>108</v>
+      </c>
+      <c r="E7" s="2">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H7" s="1">
+        <v>155</v>
+      </c>
+      <c r="H7" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="1">
+        <v>109</v>
+      </c>
+      <c r="E8" s="2">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="1">
+        <v>155</v>
+      </c>
+      <c r="H8" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="1">
+        <v>110</v>
+      </c>
+      <c r="E9" s="2">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
-        <v>151</v>
-      </c>
-      <c r="H9" s="1">
+        <v>156</v>
+      </c>
+      <c r="H9" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="1">
+        <v>111</v>
+      </c>
+      <c r="E10" s="2">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
-        <v>152</v>
-      </c>
-      <c r="H10" s="1">
+        <v>157</v>
+      </c>
+      <c r="H10" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="H11" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="H12" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="1">
+        <v>112</v>
+      </c>
+      <c r="E13" s="2">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="1">
+        <v>155</v>
+      </c>
+      <c r="H13" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="1">
+        <v>104</v>
+      </c>
+      <c r="H14" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -1775,551 +1887,551 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="1">
+        <v>113</v>
+      </c>
+      <c r="E15" s="2">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H15" s="1">
+        <v>158</v>
+      </c>
+      <c r="H15" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="H16" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" s="1">
+        <v>114</v>
+      </c>
+      <c r="E18" s="2">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
-        <v>154</v>
-      </c>
-      <c r="H18" s="1">
+        <v>159</v>
+      </c>
+      <c r="H18" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="1">
+        <v>115</v>
+      </c>
+      <c r="E20" s="2">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
-        <v>150</v>
-      </c>
-      <c r="H20" s="1">
+        <v>155</v>
+      </c>
+      <c r="H20" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F21" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G21" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" s="1">
+        <v>148</v>
+      </c>
+      <c r="H21" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" s="1">
+        <v>104</v>
+      </c>
+      <c r="H22" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="H23" s="1">
+        <v>100</v>
+      </c>
+      <c r="H23" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F24" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G24" t="s">
-        <v>144</v>
-      </c>
-      <c r="H24" s="1">
+        <v>149</v>
+      </c>
+      <c r="H24" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
-      </c>
-      <c r="H25" s="1">
+        <v>117</v>
+      </c>
+      <c r="H25" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G26" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="1">
+        <v>150</v>
+      </c>
+      <c r="H26" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="1">
+        <v>119</v>
+      </c>
+      <c r="E27" s="2">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
-        <v>155</v>
-      </c>
-      <c r="H27" s="1">
+        <v>160</v>
+      </c>
+      <c r="H27" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G28" t="s">
-        <v>146</v>
-      </c>
-      <c r="H28" s="1">
+        <v>151</v>
+      </c>
+      <c r="H28" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G29" t="s">
-        <v>146</v>
-      </c>
-      <c r="H29" s="1">
+        <v>151</v>
+      </c>
+      <c r="H29" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G30" t="s">
-        <v>147</v>
-      </c>
-      <c r="H30" s="1">
+        <v>152</v>
+      </c>
+      <c r="H30" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="H31" s="1">
+        <v>100</v>
+      </c>
+      <c r="H31" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
-      </c>
-      <c r="H32" s="1">
+        <v>100</v>
+      </c>
+      <c r="H32" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F33" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G33" t="s">
-        <v>148</v>
-      </c>
-      <c r="H33" s="1">
+        <v>153</v>
+      </c>
+      <c r="H33" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
-      </c>
-      <c r="H34" s="1">
+        <v>100</v>
+      </c>
+      <c r="H34" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
-      </c>
-      <c r="H35" s="1">
+        <v>100</v>
+      </c>
+      <c r="H35" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" s="1">
+        <v>108</v>
+      </c>
+      <c r="E36" s="2">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" s="1">
+        <v>155</v>
+      </c>
+      <c r="H36" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D37" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="1">
+        <v>109</v>
+      </c>
+      <c r="E37" s="2">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
-        <v>150</v>
-      </c>
-      <c r="H37" s="1">
+        <v>155</v>
+      </c>
+      <c r="H37" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
-      </c>
-      <c r="E38" s="1">
+        <v>110</v>
+      </c>
+      <c r="E38" s="2">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
-        <v>151</v>
-      </c>
-      <c r="H38" s="1">
+        <v>156</v>
+      </c>
+      <c r="H38" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
-      </c>
-      <c r="E39" s="1">
+        <v>111</v>
+      </c>
+      <c r="E39" s="2">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
-        <v>152</v>
-      </c>
-      <c r="H39" s="1">
+        <v>157</v>
+      </c>
+      <c r="H39" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
-      </c>
-      <c r="H40" s="1">
+        <v>100</v>
+      </c>
+      <c r="H40" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
-      </c>
-      <c r="H41" s="1">
+        <v>100</v>
+      </c>
+      <c r="H41" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>109</v>
-      </c>
-      <c r="E42" s="1">
+        <v>112</v>
+      </c>
+      <c r="E42" s="2">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
-      </c>
-      <c r="H42" s="1">
+        <v>155</v>
+      </c>
+      <c r="H42" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
-      </c>
-      <c r="H43" s="1">
+        <v>100</v>
+      </c>
+      <c r="H43" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2328,533 +2440,533 @@
         <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
-      </c>
-      <c r="E44" s="1">
+        <v>113</v>
+      </c>
+      <c r="E44" s="2">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
-        <v>153</v>
-      </c>
-      <c r="H44" s="1">
+        <v>158</v>
+      </c>
+      <c r="H44" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
-      </c>
-      <c r="H45" s="1">
+        <v>100</v>
+      </c>
+      <c r="H45" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
-      </c>
-      <c r="H46" s="1">
+        <v>100</v>
+      </c>
+      <c r="H46" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
-      </c>
-      <c r="H47" s="1">
+        <v>104</v>
+      </c>
+      <c r="H47" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
-      </c>
-      <c r="H48" s="1">
+        <v>100</v>
+      </c>
+      <c r="H48" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D49" t="s">
-        <v>121</v>
-      </c>
-      <c r="E49" s="1">
+        <v>124</v>
+      </c>
+      <c r="E49" s="2">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
-        <v>150</v>
-      </c>
-      <c r="H49" s="1">
+        <v>155</v>
+      </c>
+      <c r="H49" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F50" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G50" t="s">
-        <v>143</v>
-      </c>
-      <c r="H50" s="1">
+        <v>148</v>
+      </c>
+      <c r="H50" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>101</v>
-      </c>
-      <c r="H51" s="1">
+        <v>104</v>
+      </c>
+      <c r="H51" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>97</v>
-      </c>
-      <c r="H52" s="1">
+        <v>100</v>
+      </c>
+      <c r="H52" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F53" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G53" t="s">
-        <v>144</v>
-      </c>
-      <c r="H53" s="1">
+        <v>149</v>
+      </c>
+      <c r="H53" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
-      </c>
-      <c r="H54" s="1">
+        <v>117</v>
+      </c>
+      <c r="H54" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F55" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G55" t="s">
-        <v>145</v>
-      </c>
-      <c r="H55" s="1">
+        <v>150</v>
+      </c>
+      <c r="H55" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C56" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56" s="1">
+        <v>119</v>
+      </c>
+      <c r="E56" s="2">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
-        <v>155</v>
-      </c>
-      <c r="H56" s="1">
+        <v>160</v>
+      </c>
+      <c r="H56" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B57" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D57" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F57" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G57" t="s">
-        <v>146</v>
-      </c>
-      <c r="H57" s="1">
+        <v>151</v>
+      </c>
+      <c r="H57" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B58" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C58" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F58" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H58" s="1">
+        <v>151</v>
+      </c>
+      <c r="H58" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C59" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D59" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F59" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G59" t="s">
-        <v>147</v>
-      </c>
-      <c r="H59" s="1">
+        <v>152</v>
+      </c>
+      <c r="H59" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C60" t="s">
-        <v>97</v>
-      </c>
-      <c r="H60" s="1">
+        <v>100</v>
+      </c>
+      <c r="H60" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C61" t="s">
-        <v>97</v>
-      </c>
-      <c r="H61" s="1">
+        <v>100</v>
+      </c>
+      <c r="H61" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>120</v>
-      </c>
-      <c r="E62" s="1">
+        <v>123</v>
+      </c>
+      <c r="E62" s="2">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
-        <v>156</v>
-      </c>
-      <c r="H62" s="1">
+        <v>161</v>
+      </c>
+      <c r="H62" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
-      </c>
-      <c r="H63" s="1">
+        <v>100</v>
+      </c>
+      <c r="H63" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D64" t="s">
-        <v>122</v>
-      </c>
-      <c r="E64" s="1">
+        <v>125</v>
+      </c>
+      <c r="E64" s="2">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
-        <v>157</v>
-      </c>
-      <c r="H64" s="1">
+        <v>162</v>
+      </c>
+      <c r="H64" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
-        <v>97</v>
-      </c>
-      <c r="H65" s="1">
+        <v>100</v>
+      </c>
+      <c r="H65" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C66" t="s">
-        <v>101</v>
-      </c>
-      <c r="H66" s="1">
+        <v>104</v>
+      </c>
+      <c r="H66" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
-      </c>
-      <c r="E67" s="1">
+        <v>110</v>
+      </c>
+      <c r="E67" s="2">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
-        <v>151</v>
-      </c>
-      <c r="H67" s="1">
+        <v>156</v>
+      </c>
+      <c r="H67" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D68" t="s">
-        <v>108</v>
-      </c>
-      <c r="E68" s="1">
+        <v>111</v>
+      </c>
+      <c r="E68" s="2">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
-        <v>152</v>
-      </c>
-      <c r="H68" s="1">
+        <v>157</v>
+      </c>
+      <c r="H68" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C69" t="s">
-        <v>97</v>
-      </c>
-      <c r="H69" s="1">
+        <v>100</v>
+      </c>
+      <c r="H69" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B70" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>97</v>
-      </c>
-      <c r="H70" s="1">
+        <v>100</v>
+      </c>
+      <c r="H70" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D71" t="s">
-        <v>109</v>
-      </c>
-      <c r="E71" s="1">
+        <v>112</v>
+      </c>
+      <c r="E71" s="2">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
-        <v>156</v>
-      </c>
-      <c r="H71" s="1">
+        <v>161</v>
+      </c>
+      <c r="H71" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>97</v>
-      </c>
-      <c r="H72" s="1">
+        <v>100</v>
+      </c>
+      <c r="H72" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -2863,551 +2975,551 @@
         <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
-      </c>
-      <c r="E73" s="1">
+        <v>113</v>
+      </c>
+      <c r="E73" s="2">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
-        <v>153</v>
-      </c>
-      <c r="H73" s="1">
+        <v>158</v>
+      </c>
+      <c r="H73" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
-      </c>
-      <c r="H74" s="1">
+        <v>100</v>
+      </c>
+      <c r="H74" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C75" t="s">
-        <v>97</v>
-      </c>
-      <c r="H75" s="1">
+        <v>100</v>
+      </c>
+      <c r="H75" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C76" t="s">
-        <v>97</v>
-      </c>
-      <c r="H76" s="1">
+        <v>100</v>
+      </c>
+      <c r="H76" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
-      </c>
-      <c r="H77" s="1">
+        <v>100</v>
+      </c>
+      <c r="H77" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C78" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
-      </c>
-      <c r="E78" s="1">
+        <v>124</v>
+      </c>
+      <c r="E78" s="2">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
-        <v>156</v>
-      </c>
-      <c r="H78" s="1">
+        <v>161</v>
+      </c>
+      <c r="H78" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D79" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F79" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G79" t="s">
-        <v>149</v>
-      </c>
-      <c r="H79" s="1">
+        <v>154</v>
+      </c>
+      <c r="H79" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C80" t="s">
-        <v>101</v>
-      </c>
-      <c r="H80" s="1">
+        <v>104</v>
+      </c>
+      <c r="H80" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C81" t="s">
-        <v>97</v>
-      </c>
-      <c r="H81" s="1">
+        <v>100</v>
+      </c>
+      <c r="H81" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C82" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F82" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G82" t="s">
-        <v>144</v>
-      </c>
-      <c r="H82" s="1">
+        <v>149</v>
+      </c>
+      <c r="H82" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C83" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D83" t="s">
-        <v>114</v>
-      </c>
-      <c r="H83" s="1">
+        <v>117</v>
+      </c>
+      <c r="H83" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C84" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D84" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F84" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G84" t="s">
-        <v>145</v>
-      </c>
-      <c r="H84" s="1">
+        <v>150</v>
+      </c>
+      <c r="H84" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D85" t="s">
-        <v>116</v>
-      </c>
-      <c r="E85" s="1">
+        <v>119</v>
+      </c>
+      <c r="E85" s="2">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
-        <v>155</v>
-      </c>
-      <c r="H85" s="1">
+        <v>160</v>
+      </c>
+      <c r="H85" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D86" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F86" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G86" t="s">
-        <v>146</v>
-      </c>
-      <c r="H86" s="1">
+        <v>151</v>
+      </c>
+      <c r="H86" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C87" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D87" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F87" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G87" t="s">
-        <v>146</v>
-      </c>
-      <c r="H87" s="1">
+        <v>151</v>
+      </c>
+      <c r="H87" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C88" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D88" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F88" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G88" t="s">
-        <v>147</v>
-      </c>
-      <c r="H88" s="1">
+        <v>152</v>
+      </c>
+      <c r="H88" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C89" t="s">
-        <v>97</v>
-      </c>
-      <c r="H89" s="1">
+        <v>100</v>
+      </c>
+      <c r="H89" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C90" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
-      </c>
-      <c r="E90" s="1">
+        <v>127</v>
+      </c>
+      <c r="E90" s="2">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
-        <v>157</v>
-      </c>
-      <c r="H90" s="1">
+        <v>162</v>
+      </c>
+      <c r="H90" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B91" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C91" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D91" t="s">
-        <v>120</v>
-      </c>
-      <c r="E91" s="1">
+        <v>123</v>
+      </c>
+      <c r="E91" s="2">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
-        <v>156</v>
-      </c>
-      <c r="H91" s="1">
+        <v>161</v>
+      </c>
+      <c r="H91" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B92" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C92" t="s">
-        <v>97</v>
-      </c>
-      <c r="H92" s="1">
+        <v>100</v>
+      </c>
+      <c r="H92" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B93" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D93" t="s">
-        <v>122</v>
-      </c>
-      <c r="E93" s="1">
+        <v>125</v>
+      </c>
+      <c r="E93" s="2">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
-        <v>157</v>
-      </c>
-      <c r="H93" s="1">
+        <v>162</v>
+      </c>
+      <c r="H93" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B94" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>97</v>
-      </c>
-      <c r="H94" s="1">
+        <v>100</v>
+      </c>
+      <c r="H94" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C95" t="s">
-        <v>101</v>
-      </c>
-      <c r="H95" s="1">
+        <v>104</v>
+      </c>
+      <c r="H95" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C96" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D96" t="s">
-        <v>107</v>
-      </c>
-      <c r="E96" s="1">
+        <v>110</v>
+      </c>
+      <c r="E96" s="2">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
-        <v>151</v>
-      </c>
-      <c r="H96" s="1">
+        <v>156</v>
+      </c>
+      <c r="H96" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B97" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C97" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D97" t="s">
-        <v>108</v>
-      </c>
-      <c r="E97" s="1">
+        <v>111</v>
+      </c>
+      <c r="E97" s="2">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
-        <v>152</v>
-      </c>
-      <c r="H97" s="1">
+        <v>157</v>
+      </c>
+      <c r="H97" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B98" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C98" t="s">
-        <v>97</v>
-      </c>
-      <c r="H98" s="1">
+        <v>100</v>
+      </c>
+      <c r="H98" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B99" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C99" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D99" t="s">
-        <v>125</v>
-      </c>
-      <c r="E99" s="1">
+        <v>128</v>
+      </c>
+      <c r="E99" s="2">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
-        <v>152</v>
-      </c>
-      <c r="H99" s="1">
+        <v>157</v>
+      </c>
+      <c r="H99" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C100" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
-      </c>
-      <c r="E100" s="1">
+        <v>112</v>
+      </c>
+      <c r="E100" s="2">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
-        <v>152</v>
-      </c>
-      <c r="H100" s="1">
+        <v>157</v>
+      </c>
+      <c r="H100" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>97</v>
-      </c>
-      <c r="H101" s="1">
+        <v>100</v>
+      </c>
+      <c r="H101" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3416,542 +3528,542 @@
         <v>32</v>
       </c>
       <c r="B102" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C102" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D102" t="s">
-        <v>110</v>
-      </c>
-      <c r="E102" s="1">
+        <v>113</v>
+      </c>
+      <c r="E102" s="2">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
-        <v>153</v>
-      </c>
-      <c r="H102" s="1">
+        <v>158</v>
+      </c>
+      <c r="H102" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C103" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D103" t="s">
-        <v>126</v>
-      </c>
-      <c r="E103" s="1">
+        <v>129</v>
+      </c>
+      <c r="E103" s="2">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
-        <v>152</v>
-      </c>
-      <c r="H103" s="1">
+        <v>157</v>
+      </c>
+      <c r="H103" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C104" t="s">
-        <v>97</v>
-      </c>
-      <c r="H104" s="1">
+        <v>100</v>
+      </c>
+      <c r="H104" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C105" t="s">
-        <v>97</v>
-      </c>
-      <c r="H105" s="1">
+        <v>100</v>
+      </c>
+      <c r="H105" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C106" t="s">
-        <v>97</v>
-      </c>
-      <c r="H106" s="1">
+        <v>100</v>
+      </c>
+      <c r="H106" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C107" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D107" t="s">
-        <v>127</v>
-      </c>
-      <c r="E107" s="1">
+        <v>130</v>
+      </c>
+      <c r="E107" s="2">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
-        <v>152</v>
-      </c>
-      <c r="H107" s="1">
+        <v>157</v>
+      </c>
+      <c r="H107" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B108" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C108" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D108" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F108" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G108" t="s">
-        <v>149</v>
-      </c>
-      <c r="H108" s="1">
+        <v>154</v>
+      </c>
+      <c r="H108" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B109" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C109" t="s">
-        <v>101</v>
-      </c>
-      <c r="H109" s="1">
+        <v>104</v>
+      </c>
+      <c r="H109" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B110" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C110" t="s">
-        <v>97</v>
-      </c>
-      <c r="H110" s="1">
+        <v>100</v>
+      </c>
+      <c r="H110" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B111" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C111" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D111" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F111" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G111" t="s">
-        <v>144</v>
-      </c>
-      <c r="H111" s="1">
+        <v>149</v>
+      </c>
+      <c r="H111" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B112" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C112" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D112" t="s">
-        <v>114</v>
-      </c>
-      <c r="H112" s="1">
+        <v>117</v>
+      </c>
+      <c r="H112" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B113" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C113" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D113" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F113" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G113" t="s">
-        <v>145</v>
-      </c>
-      <c r="H113" s="1">
+        <v>150</v>
+      </c>
+      <c r="H113" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B114" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C114" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D114" t="s">
-        <v>116</v>
-      </c>
-      <c r="E114" s="1">
+        <v>119</v>
+      </c>
+      <c r="E114" s="2">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
-        <v>155</v>
-      </c>
-      <c r="H114" s="1">
+        <v>160</v>
+      </c>
+      <c r="H114" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B115" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C115" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D115" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F115" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G115" t="s">
-        <v>146</v>
-      </c>
-      <c r="H115" s="1">
+        <v>151</v>
+      </c>
+      <c r="H115" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B116" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C116" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D116" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F116" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G116" t="s">
-        <v>146</v>
-      </c>
-      <c r="H116" s="1">
+        <v>151</v>
+      </c>
+      <c r="H116" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B117" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C117" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D117" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F117" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G117" t="s">
-        <v>147</v>
-      </c>
-      <c r="H117" s="1">
+        <v>152</v>
+      </c>
+      <c r="H117" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C118" t="s">
-        <v>97</v>
-      </c>
-      <c r="H118" s="1">
+        <v>100</v>
+      </c>
+      <c r="H118" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B119" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C119" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D119" t="s">
-        <v>124</v>
-      </c>
-      <c r="E119" s="1">
+        <v>127</v>
+      </c>
+      <c r="E119" s="2">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
-        <v>157</v>
-      </c>
-      <c r="H119" s="1">
+        <v>162</v>
+      </c>
+      <c r="H119" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B120" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C120" t="s">
-        <v>101</v>
-      </c>
-      <c r="H120" s="1">
+        <v>104</v>
+      </c>
+      <c r="H120" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B121" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C121" t="s">
-        <v>97</v>
-      </c>
-      <c r="H121" s="1">
+        <v>100</v>
+      </c>
+      <c r="H121" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B122" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C122" t="s">
-        <v>101</v>
-      </c>
-      <c r="H122" s="1">
+        <v>104</v>
+      </c>
+      <c r="H122" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B123" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C123" t="s">
-        <v>101</v>
-      </c>
-      <c r="H123" s="1">
+        <v>104</v>
+      </c>
+      <c r="H123" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B124" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C124" t="s">
-        <v>101</v>
-      </c>
-      <c r="H124" s="1">
+        <v>104</v>
+      </c>
+      <c r="H124" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B125" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C125" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D125" t="s">
-        <v>107</v>
-      </c>
-      <c r="E125" s="1">
+        <v>110</v>
+      </c>
+      <c r="E125" s="2">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
-        <v>151</v>
-      </c>
-      <c r="H125" s="1">
+        <v>156</v>
+      </c>
+      <c r="H125" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C126" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D126" t="s">
-        <v>108</v>
-      </c>
-      <c r="E126" s="1">
+        <v>111</v>
+      </c>
+      <c r="E126" s="2">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
-        <v>152</v>
-      </c>
-      <c r="H126" s="1">
+        <v>157</v>
+      </c>
+      <c r="H126" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B127" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C127" t="s">
-        <v>97</v>
-      </c>
-      <c r="H127" s="1">
+        <v>100</v>
+      </c>
+      <c r="H127" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B128" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C128" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D128" t="s">
-        <v>125</v>
-      </c>
-      <c r="E128" s="1">
+        <v>128</v>
+      </c>
+      <c r="E128" s="2">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
-        <v>152</v>
-      </c>
-      <c r="H128" s="1">
+        <v>157</v>
+      </c>
+      <c r="H128" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B129" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C129" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D129" t="s">
-        <v>109</v>
-      </c>
-      <c r="E129" s="1">
+        <v>112</v>
+      </c>
+      <c r="E129" s="2">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
-        <v>152</v>
-      </c>
-      <c r="H129" s="1">
+        <v>157</v>
+      </c>
+      <c r="H129" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B130" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C130" t="s">
-        <v>97</v>
-      </c>
-      <c r="H130" s="1">
+        <v>100</v>
+      </c>
+      <c r="H130" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -3960,551 +4072,551 @@
         <v>32</v>
       </c>
       <c r="B131" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C131" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D131" t="s">
-        <v>110</v>
-      </c>
-      <c r="E131" s="1">
+        <v>113</v>
+      </c>
+      <c r="E131" s="2">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
-        <v>153</v>
-      </c>
-      <c r="H131" s="1">
+        <v>158</v>
+      </c>
+      <c r="H131" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B132" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C132" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D132" t="s">
-        <v>126</v>
-      </c>
-      <c r="E132" s="1">
+        <v>129</v>
+      </c>
+      <c r="E132" s="2">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
-        <v>152</v>
-      </c>
-      <c r="H132" s="1">
+        <v>157</v>
+      </c>
+      <c r="H132" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B133" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C133" t="s">
-        <v>97</v>
-      </c>
-      <c r="H133" s="1">
+        <v>100</v>
+      </c>
+      <c r="H133" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B134" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C134" t="s">
-        <v>97</v>
-      </c>
-      <c r="H134" s="1">
+        <v>100</v>
+      </c>
+      <c r="H134" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B135" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C135" t="s">
-        <v>97</v>
-      </c>
-      <c r="H135" s="1">
+        <v>100</v>
+      </c>
+      <c r="H135" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B136" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C136" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D136" t="s">
-        <v>128</v>
-      </c>
-      <c r="E136" s="1">
+        <v>131</v>
+      </c>
+      <c r="E136" s="2">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
-        <v>152</v>
-      </c>
-      <c r="H136" s="1">
+        <v>157</v>
+      </c>
+      <c r="H136" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B137" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C137" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D137" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F137" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G137" t="s">
-        <v>149</v>
-      </c>
-      <c r="H137" s="1">
+        <v>154</v>
+      </c>
+      <c r="H137" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B138" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C138" t="s">
-        <v>101</v>
-      </c>
-      <c r="H138" s="1">
+        <v>104</v>
+      </c>
+      <c r="H138" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B139" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C139" t="s">
-        <v>97</v>
-      </c>
-      <c r="H139" s="1">
+        <v>100</v>
+      </c>
+      <c r="H139" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B140" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C140" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D140" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F140" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G140" t="s">
-        <v>144</v>
-      </c>
-      <c r="H140" s="1">
+        <v>149</v>
+      </c>
+      <c r="H140" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B141" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C141" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D141" t="s">
-        <v>114</v>
-      </c>
-      <c r="H141" s="1">
+        <v>117</v>
+      </c>
+      <c r="H141" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B142" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C142" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D142" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F142" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G142" t="s">
-        <v>145</v>
-      </c>
-      <c r="H142" s="1">
+        <v>150</v>
+      </c>
+      <c r="H142" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B143" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C143" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D143" t="s">
-        <v>116</v>
-      </c>
-      <c r="E143" s="1">
+        <v>119</v>
+      </c>
+      <c r="E143" s="2">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
-        <v>155</v>
-      </c>
-      <c r="H143" s="1">
+        <v>160</v>
+      </c>
+      <c r="H143" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B144" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C144" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D144" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F144" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G144" t="s">
-        <v>146</v>
-      </c>
-      <c r="H144" s="1">
+        <v>151</v>
+      </c>
+      <c r="H144" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B145" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C145" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D145" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F145" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G145" t="s">
-        <v>146</v>
-      </c>
-      <c r="H145" s="1">
+        <v>151</v>
+      </c>
+      <c r="H145" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B146" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C146" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D146" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F146" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G146" t="s">
-        <v>147</v>
-      </c>
-      <c r="H146" s="1">
+        <v>152</v>
+      </c>
+      <c r="H146" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B147" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C147" t="s">
-        <v>97</v>
-      </c>
-      <c r="H147" s="1">
+        <v>100</v>
+      </c>
+      <c r="H147" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B148" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C148" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D148" t="s">
-        <v>124</v>
-      </c>
-      <c r="E148" s="1">
+        <v>127</v>
+      </c>
+      <c r="E148" s="2">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
-        <v>157</v>
-      </c>
-      <c r="H148" s="1">
+        <v>162</v>
+      </c>
+      <c r="H148" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B149" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C149" t="s">
-        <v>101</v>
-      </c>
-      <c r="H149" s="1">
+        <v>104</v>
+      </c>
+      <c r="H149" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B150" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C150" t="s">
-        <v>97</v>
-      </c>
-      <c r="H150" s="1">
+        <v>100</v>
+      </c>
+      <c r="H150" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B151" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C151" t="s">
-        <v>97</v>
-      </c>
-      <c r="H151" s="1">
+        <v>100</v>
+      </c>
+      <c r="H151" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B152" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C152" t="s">
-        <v>101</v>
-      </c>
-      <c r="H152" s="1">
+        <v>104</v>
+      </c>
+      <c r="H152" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B153" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C153" t="s">
-        <v>101</v>
-      </c>
-      <c r="H153" s="1">
+        <v>104</v>
+      </c>
+      <c r="H153" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C154" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D154" t="s">
-        <v>107</v>
-      </c>
-      <c r="E154" s="1">
+        <v>110</v>
+      </c>
+      <c r="E154" s="2">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
-        <v>151</v>
-      </c>
-      <c r="H154" s="1">
+        <v>156</v>
+      </c>
+      <c r="H154" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B155" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D155" t="s">
-        <v>108</v>
-      </c>
-      <c r="E155" s="1">
+        <v>111</v>
+      </c>
+      <c r="E155" s="2">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
-        <v>152</v>
-      </c>
-      <c r="H155" s="1">
+        <v>157</v>
+      </c>
+      <c r="H155" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B156" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>97</v>
-      </c>
-      <c r="H156" s="1">
+        <v>100</v>
+      </c>
+      <c r="H156" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B157" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C157" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D157" t="s">
-        <v>125</v>
-      </c>
-      <c r="E157" s="1">
+        <v>128</v>
+      </c>
+      <c r="E157" s="2">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
-        <v>152</v>
-      </c>
-      <c r="H157" s="1">
+        <v>157</v>
+      </c>
+      <c r="H157" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B158" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D158" t="s">
-        <v>109</v>
-      </c>
-      <c r="E158" s="1">
+        <v>112</v>
+      </c>
+      <c r="E158" s="2">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
-        <v>152</v>
-      </c>
-      <c r="H158" s="1">
+        <v>157</v>
+      </c>
+      <c r="H158" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B159" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C159" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D159" t="s">
-        <v>129</v>
-      </c>
-      <c r="E159" s="1">
+        <v>132</v>
+      </c>
+      <c r="E159" s="2">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
-        <v>158</v>
-      </c>
-      <c r="H159" s="1">
+        <v>163</v>
+      </c>
+      <c r="H159" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4513,560 +4625,560 @@
         <v>32</v>
       </c>
       <c r="B160" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D160" t="s">
-        <v>110</v>
-      </c>
-      <c r="E160" s="1">
+        <v>113</v>
+      </c>
+      <c r="E160" s="2">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
-        <v>153</v>
-      </c>
-      <c r="H160" s="1">
+        <v>158</v>
+      </c>
+      <c r="H160" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B161" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C161" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D161" t="s">
-        <v>126</v>
-      </c>
-      <c r="E161" s="1">
+        <v>129</v>
+      </c>
+      <c r="E161" s="2">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
-        <v>152</v>
-      </c>
-      <c r="H161" s="1">
+        <v>157</v>
+      </c>
+      <c r="H161" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B162" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C162" t="s">
-        <v>97</v>
-      </c>
-      <c r="H162" s="1">
+        <v>100</v>
+      </c>
+      <c r="H162" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B163" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C163" t="s">
-        <v>97</v>
-      </c>
-      <c r="H163" s="1">
+        <v>100</v>
+      </c>
+      <c r="H163" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B164" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C164" t="s">
-        <v>97</v>
-      </c>
-      <c r="H164" s="1">
+        <v>100</v>
+      </c>
+      <c r="H164" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B165" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C165" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D165" t="s">
-        <v>128</v>
-      </c>
-      <c r="E165" s="1">
+        <v>131</v>
+      </c>
+      <c r="E165" s="2">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
-        <v>152</v>
-      </c>
-      <c r="H165" s="1">
+        <v>157</v>
+      </c>
+      <c r="H165" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B166" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C166" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D166" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F166" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G166" t="s">
-        <v>149</v>
-      </c>
-      <c r="H166" s="1">
+        <v>154</v>
+      </c>
+      <c r="H166" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B167" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C167" t="s">
-        <v>101</v>
-      </c>
-      <c r="H167" s="1">
+        <v>104</v>
+      </c>
+      <c r="H167" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B168" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C168" t="s">
-        <v>97</v>
-      </c>
-      <c r="H168" s="1">
+        <v>100</v>
+      </c>
+      <c r="H168" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B169" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C169" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D169" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F169" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G169" t="s">
-        <v>144</v>
-      </c>
-      <c r="H169" s="1">
+        <v>149</v>
+      </c>
+      <c r="H169" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B170" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C170" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D170" t="s">
-        <v>114</v>
-      </c>
-      <c r="H170" s="1">
+        <v>117</v>
+      </c>
+      <c r="H170" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B171" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C171" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D171" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F171" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G171" t="s">
-        <v>145</v>
-      </c>
-      <c r="H171" s="1">
+        <v>150</v>
+      </c>
+      <c r="H171" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B172" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C172" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D172" t="s">
-        <v>116</v>
-      </c>
-      <c r="E172" s="1">
+        <v>119</v>
+      </c>
+      <c r="E172" s="2">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
-        <v>155</v>
-      </c>
-      <c r="H172" s="1">
+        <v>160</v>
+      </c>
+      <c r="H172" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B173" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C173" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D173" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F173" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G173" t="s">
-        <v>146</v>
-      </c>
-      <c r="H173" s="1">
+        <v>151</v>
+      </c>
+      <c r="H173" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B174" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C174" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D174" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F174" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G174" t="s">
-        <v>146</v>
-      </c>
-      <c r="H174" s="1">
+        <v>151</v>
+      </c>
+      <c r="H174" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B175" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C175" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D175" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F175" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G175" t="s">
-        <v>147</v>
-      </c>
-      <c r="H175" s="1">
+        <v>152</v>
+      </c>
+      <c r="H175" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B176" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C176" t="s">
-        <v>97</v>
-      </c>
-      <c r="H176" s="1">
+        <v>100</v>
+      </c>
+      <c r="H176" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B177" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C177" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D177" t="s">
-        <v>130</v>
-      </c>
-      <c r="E177" s="1">
+        <v>133</v>
+      </c>
+      <c r="E177" s="2">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
-        <v>157</v>
-      </c>
-      <c r="H177" s="1">
+        <v>162</v>
+      </c>
+      <c r="H177" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B178" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C178" t="s">
-        <v>97</v>
-      </c>
-      <c r="H178" s="1">
+        <v>100</v>
+      </c>
+      <c r="H178" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B179" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C179" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D179" t="s">
-        <v>131</v>
-      </c>
-      <c r="E179" s="1">
+        <v>134</v>
+      </c>
+      <c r="E179" s="2">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
-        <v>153</v>
-      </c>
-      <c r="H179" s="1">
+        <v>158</v>
+      </c>
+      <c r="H179" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B180" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C180" t="s">
-        <v>97</v>
-      </c>
-      <c r="H180" s="1">
+        <v>100</v>
+      </c>
+      <c r="H180" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B181" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C181" t="s">
-        <v>101</v>
-      </c>
-      <c r="H181" s="1">
+        <v>104</v>
+      </c>
+      <c r="H181" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B182" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C182" t="s">
-        <v>101</v>
-      </c>
-      <c r="H182" s="1">
+        <v>104</v>
+      </c>
+      <c r="H182" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B183" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C183" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D183" t="s">
-        <v>107</v>
-      </c>
-      <c r="E183" s="1">
+        <v>110</v>
+      </c>
+      <c r="E183" s="2">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
-        <v>151</v>
-      </c>
-      <c r="H183" s="1">
+        <v>156</v>
+      </c>
+      <c r="H183" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B184" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D184" t="s">
-        <v>108</v>
-      </c>
-      <c r="E184" s="1">
+        <v>111</v>
+      </c>
+      <c r="E184" s="2">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
-        <v>152</v>
-      </c>
-      <c r="H184" s="1">
+        <v>157</v>
+      </c>
+      <c r="H184" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B185" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>97</v>
-      </c>
-      <c r="H185" s="1">
+        <v>100</v>
+      </c>
+      <c r="H185" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B186" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C186" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D186" t="s">
-        <v>125</v>
-      </c>
-      <c r="E186" s="1">
+        <v>128</v>
+      </c>
+      <c r="E186" s="2">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
-        <v>152</v>
-      </c>
-      <c r="H186" s="1">
+        <v>157</v>
+      </c>
+      <c r="H186" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B187" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C187" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D187" t="s">
-        <v>132</v>
-      </c>
-      <c r="E187" s="1">
+        <v>135</v>
+      </c>
+      <c r="E187" s="2">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
-        <v>152</v>
-      </c>
-      <c r="H187" s="1">
+        <v>157</v>
+      </c>
+      <c r="H187" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B188" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C188" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D188" t="s">
-        <v>133</v>
-      </c>
-      <c r="E188" s="1">
+        <v>136</v>
+      </c>
+      <c r="E188" s="2">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
-        <v>152</v>
-      </c>
-      <c r="H188" s="1">
+        <v>157</v>
+      </c>
+      <c r="H188" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5075,533 +5187,533 @@
         <v>32</v>
       </c>
       <c r="B189" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C189" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D189" t="s">
-        <v>110</v>
-      </c>
-      <c r="E189" s="1">
+        <v>113</v>
+      </c>
+      <c r="E189" s="2">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
-        <v>153</v>
-      </c>
-      <c r="H189" s="1">
+        <v>158</v>
+      </c>
+      <c r="H189" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B190" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C190" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D190" t="s">
-        <v>126</v>
-      </c>
-      <c r="E190" s="1">
+        <v>129</v>
+      </c>
+      <c r="E190" s="2">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
-        <v>152</v>
-      </c>
-      <c r="H190" s="1">
+        <v>157</v>
+      </c>
+      <c r="H190" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B191" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C191" t="s">
-        <v>97</v>
-      </c>
-      <c r="H191" s="1">
+        <v>100</v>
+      </c>
+      <c r="H191" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B192" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C192" t="s">
-        <v>97</v>
-      </c>
-      <c r="H192" s="1">
+        <v>100</v>
+      </c>
+      <c r="H192" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B193" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C193" t="s">
-        <v>97</v>
-      </c>
-      <c r="H193" s="1">
+        <v>100</v>
+      </c>
+      <c r="H193" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B194" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C194" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D194" t="s">
-        <v>128</v>
-      </c>
-      <c r="E194" s="1">
+        <v>131</v>
+      </c>
+      <c r="E194" s="2">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
-        <v>159</v>
-      </c>
-      <c r="H194" s="1">
+        <v>164</v>
+      </c>
+      <c r="H194" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B195" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C195" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D195" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F195" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G195" t="s">
-        <v>149</v>
-      </c>
-      <c r="H195" s="1">
+        <v>154</v>
+      </c>
+      <c r="H195" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B196" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C196" t="s">
-        <v>101</v>
-      </c>
-      <c r="H196" s="1">
+        <v>104</v>
+      </c>
+      <c r="H196" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B197" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C197" t="s">
-        <v>97</v>
-      </c>
-      <c r="H197" s="1">
+        <v>100</v>
+      </c>
+      <c r="H197" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B198" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C198" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D198" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F198" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G198" t="s">
-        <v>144</v>
-      </c>
-      <c r="H198" s="1">
+        <v>149</v>
+      </c>
+      <c r="H198" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B199" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C199" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D199" t="s">
-        <v>114</v>
-      </c>
-      <c r="H199" s="1">
+        <v>117</v>
+      </c>
+      <c r="H199" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B200" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C200" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D200" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F200" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G200" t="s">
-        <v>145</v>
-      </c>
-      <c r="H200" s="1">
+        <v>150</v>
+      </c>
+      <c r="H200" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B201" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C201" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D201" t="s">
-        <v>116</v>
-      </c>
-      <c r="E201" s="1">
+        <v>119</v>
+      </c>
+      <c r="E201" s="2">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
-        <v>155</v>
-      </c>
-      <c r="H201" s="1">
+        <v>160</v>
+      </c>
+      <c r="H201" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B202" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C202" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D202" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F202" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G202" t="s">
-        <v>146</v>
-      </c>
-      <c r="H202" s="1">
+        <v>151</v>
+      </c>
+      <c r="H202" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B203" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C203" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D203" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F203" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G203" t="s">
-        <v>146</v>
-      </c>
-      <c r="H203" s="1">
+        <v>151</v>
+      </c>
+      <c r="H203" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B204" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C204" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D204" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F204" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G204" t="s">
-        <v>147</v>
-      </c>
-      <c r="H204" s="1">
+        <v>152</v>
+      </c>
+      <c r="H204" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B205" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C205" t="s">
-        <v>97</v>
-      </c>
-      <c r="H205" s="1">
+        <v>100</v>
+      </c>
+      <c r="H205" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B206" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C206" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D206" t="s">
-        <v>130</v>
-      </c>
-      <c r="E206" s="1">
+        <v>133</v>
+      </c>
+      <c r="E206" s="2">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
-        <v>157</v>
-      </c>
-      <c r="H206" s="1">
+        <v>162</v>
+      </c>
+      <c r="H206" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B207" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C207" t="s">
-        <v>97</v>
-      </c>
-      <c r="H207" s="1">
+        <v>100</v>
+      </c>
+      <c r="H207" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B208" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C208" t="s">
-        <v>101</v>
-      </c>
-      <c r="H208" s="1">
+        <v>104</v>
+      </c>
+      <c r="H208" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B209" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C209" t="s">
-        <v>97</v>
-      </c>
-      <c r="H209" s="1">
+        <v>100</v>
+      </c>
+      <c r="H209" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B210" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C210" t="s">
-        <v>101</v>
-      </c>
-      <c r="H210" s="1">
+        <v>104</v>
+      </c>
+      <c r="H210" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B211" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C211" t="s">
-        <v>101</v>
-      </c>
-      <c r="H211" s="1">
+        <v>104</v>
+      </c>
+      <c r="H211" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B212" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C212" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D212" t="s">
-        <v>107</v>
-      </c>
-      <c r="E212" s="1">
+        <v>110</v>
+      </c>
+      <c r="E212" s="2">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
-        <v>151</v>
-      </c>
-      <c r="H212" s="1">
+        <v>156</v>
+      </c>
+      <c r="H212" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B213" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C213" t="s">
-        <v>101</v>
-      </c>
-      <c r="H213" s="1">
+        <v>104</v>
+      </c>
+      <c r="H213" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B214" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C214" t="s">
-        <v>97</v>
-      </c>
-      <c r="H214" s="1">
+        <v>100</v>
+      </c>
+      <c r="H214" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B215" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C215" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D215" t="s">
-        <v>125</v>
-      </c>
-      <c r="E215" s="1">
+        <v>128</v>
+      </c>
+      <c r="E215" s="2">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
-        <v>160</v>
-      </c>
-      <c r="H215" s="1">
+        <v>165</v>
+      </c>
+      <c r="H215" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B216" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C216" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D216" t="s">
-        <v>132</v>
-      </c>
-      <c r="E216" s="1">
+        <v>135</v>
+      </c>
+      <c r="E216" s="2">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
-        <v>153</v>
-      </c>
-      <c r="H216" s="1">
+        <v>158</v>
+      </c>
+      <c r="H216" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B217" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C217" t="s">
-        <v>97</v>
-      </c>
-      <c r="H217" s="1">
+        <v>100</v>
+      </c>
+      <c r="H217" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5610,533 +5722,533 @@
         <v>32</v>
       </c>
       <c r="B218" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C218" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D218" t="s">
-        <v>110</v>
-      </c>
-      <c r="E218" s="1">
+        <v>113</v>
+      </c>
+      <c r="E218" s="2">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
-        <v>153</v>
-      </c>
-      <c r="H218" s="1">
+        <v>158</v>
+      </c>
+      <c r="H218" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B219" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C219" t="s">
-        <v>97</v>
-      </c>
-      <c r="H219" s="1">
+        <v>100</v>
+      </c>
+      <c r="H219" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B220" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C220" t="s">
-        <v>97</v>
-      </c>
-      <c r="H220" s="1">
+        <v>100</v>
+      </c>
+      <c r="H220" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B221" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C221" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D221" t="s">
-        <v>134</v>
-      </c>
-      <c r="E221" s="1">
+        <v>137</v>
+      </c>
+      <c r="E221" s="2">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
-        <v>157</v>
-      </c>
-      <c r="H221" s="1">
+        <v>162</v>
+      </c>
+      <c r="H221" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B222" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C222" t="s">
-        <v>97</v>
-      </c>
-      <c r="H222" s="1">
+        <v>100</v>
+      </c>
+      <c r="H222" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B223" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C223" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D223" t="s">
-        <v>135</v>
-      </c>
-      <c r="E223" s="1">
+        <v>138</v>
+      </c>
+      <c r="E223" s="2">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
-        <v>161</v>
-      </c>
-      <c r="H223" s="1">
+        <v>166</v>
+      </c>
+      <c r="H223" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B224" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C224" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D224" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F224" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G224" t="s">
-        <v>149</v>
-      </c>
-      <c r="H224" s="1">
+        <v>154</v>
+      </c>
+      <c r="H224" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B225" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C225" t="s">
-        <v>101</v>
-      </c>
-      <c r="H225" s="1">
+        <v>104</v>
+      </c>
+      <c r="H225" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B226" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C226" t="s">
-        <v>97</v>
-      </c>
-      <c r="H226" s="1">
+        <v>100</v>
+      </c>
+      <c r="H226" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B227" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C227" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D227" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F227" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G227" t="s">
-        <v>144</v>
-      </c>
-      <c r="H227" s="1">
+        <v>149</v>
+      </c>
+      <c r="H227" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B228" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C228" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D228" t="s">
-        <v>114</v>
-      </c>
-      <c r="H228" s="1">
+        <v>117</v>
+      </c>
+      <c r="H228" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B229" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C229" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D229" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F229" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G229" t="s">
-        <v>145</v>
-      </c>
-      <c r="H229" s="1">
+        <v>150</v>
+      </c>
+      <c r="H229" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B230" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C230" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D230" t="s">
-        <v>136</v>
-      </c>
-      <c r="E230" s="1">
+        <v>139</v>
+      </c>
+      <c r="E230" s="2">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
-        <v>162</v>
-      </c>
-      <c r="H230" s="1">
+        <v>167</v>
+      </c>
+      <c r="H230" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B231" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C231" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D231" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F231" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G231" t="s">
-        <v>146</v>
-      </c>
-      <c r="H231" s="1">
+        <v>151</v>
+      </c>
+      <c r="H231" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B232" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C232" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D232" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F232" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G232" t="s">
-        <v>146</v>
-      </c>
-      <c r="H232" s="1">
+        <v>151</v>
+      </c>
+      <c r="H232" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B233" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C233" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D233" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F233" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G233" t="s">
-        <v>147</v>
-      </c>
-      <c r="H233" s="1">
+        <v>152</v>
+      </c>
+      <c r="H233" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B234" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C234" t="s">
-        <v>97</v>
-      </c>
-      <c r="H234" s="1">
+        <v>100</v>
+      </c>
+      <c r="H234" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B235" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C235" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D235" t="s">
-        <v>137</v>
-      </c>
-      <c r="E235" s="1">
+        <v>140</v>
+      </c>
+      <c r="E235" s="2">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
-        <v>157</v>
-      </c>
-      <c r="H235" s="1">
+        <v>162</v>
+      </c>
+      <c r="H235" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B236" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C236" t="s">
-        <v>97</v>
-      </c>
-      <c r="H236" s="1">
+        <v>100</v>
+      </c>
+      <c r="H236" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B237" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C237" t="s">
-        <v>101</v>
-      </c>
-      <c r="H237" s="1">
+        <v>104</v>
+      </c>
+      <c r="H237" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B238" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C238" t="s">
-        <v>97</v>
-      </c>
-      <c r="H238" s="1">
+        <v>100</v>
+      </c>
+      <c r="H238" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B239" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C239" t="s">
-        <v>101</v>
-      </c>
-      <c r="H239" s="1">
+        <v>104</v>
+      </c>
+      <c r="H239" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B240" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C240" t="s">
-        <v>101</v>
-      </c>
-      <c r="H240" s="1">
+        <v>104</v>
+      </c>
+      <c r="H240" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B241" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C241" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D241" t="s">
-        <v>107</v>
-      </c>
-      <c r="E241" s="1">
+        <v>110</v>
+      </c>
+      <c r="E241" s="2">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
-        <v>151</v>
-      </c>
-      <c r="H241" s="1">
+        <v>156</v>
+      </c>
+      <c r="H241" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B242" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C242" t="s">
-        <v>101</v>
-      </c>
-      <c r="H242" s="1">
+        <v>104</v>
+      </c>
+      <c r="H242" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B243" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C243" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D243" t="s">
-        <v>138</v>
-      </c>
-      <c r="E243" s="1">
+        <v>141</v>
+      </c>
+      <c r="E243" s="2">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
-        <v>163</v>
-      </c>
-      <c r="H243" s="1">
+        <v>168</v>
+      </c>
+      <c r="H243" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B244" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C244" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D244" t="s">
-        <v>139</v>
-      </c>
-      <c r="E244" s="1">
+        <v>142</v>
+      </c>
+      <c r="E244" s="2">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
-        <v>160</v>
-      </c>
-      <c r="H244" s="1">
+        <v>165</v>
+      </c>
+      <c r="H244" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B245" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C245" t="s">
-        <v>101</v>
-      </c>
-      <c r="H245" s="1">
+        <v>104</v>
+      </c>
+      <c r="H245" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B246" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C246" t="s">
-        <v>97</v>
-      </c>
-      <c r="H246" s="1">
+        <v>100</v>
+      </c>
+      <c r="H246" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6145,316 +6257,860 @@
         <v>32</v>
       </c>
       <c r="B247" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C247" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D247" t="s">
-        <v>110</v>
-      </c>
-      <c r="E247" s="1">
+        <v>113</v>
+      </c>
+      <c r="E247" s="2">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
-        <v>164</v>
-      </c>
-      <c r="H247" s="1">
+        <v>169</v>
+      </c>
+      <c r="H247" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B248" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C248" t="s">
-        <v>97</v>
-      </c>
-      <c r="H248" s="1">
+        <v>100</v>
+      </c>
+      <c r="H248" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B249" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C249" t="s">
-        <v>97</v>
-      </c>
-      <c r="H249" s="1">
+        <v>100</v>
+      </c>
+      <c r="H249" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B250" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C250" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D250" t="s">
-        <v>140</v>
-      </c>
-      <c r="E250" s="1">
+        <v>143</v>
+      </c>
+      <c r="E250" s="2">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
-        <v>159</v>
-      </c>
-      <c r="H250" s="1">
+        <v>164</v>
+      </c>
+      <c r="H250" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B251" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C251" t="s">
-        <v>97</v>
-      </c>
-      <c r="H251" s="1">
+        <v>100</v>
+      </c>
+      <c r="H251" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B252" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C252" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D252" t="s">
-        <v>141</v>
-      </c>
-      <c r="E252" s="1">
+        <v>144</v>
+      </c>
+      <c r="E252" s="2">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
-        <v>161</v>
-      </c>
-      <c r="H252" s="1">
+        <v>166</v>
+      </c>
+      <c r="H252" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B253" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C253" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D253" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F253" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G253" t="s">
-        <v>149</v>
-      </c>
-      <c r="H253" s="1">
+        <v>154</v>
+      </c>
+      <c r="H253" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B254" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C254" t="s">
-        <v>101</v>
-      </c>
-      <c r="H254" s="1">
+        <v>104</v>
+      </c>
+      <c r="H254" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B255" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C255" t="s">
-        <v>97</v>
-      </c>
-      <c r="H255" s="1">
+        <v>100</v>
+      </c>
+      <c r="H255" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B256" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C256" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D256" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F256" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G256" t="s">
-        <v>144</v>
-      </c>
-      <c r="H256" s="1">
+        <v>149</v>
+      </c>
+      <c r="H256" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B257" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C257" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D257" t="s">
-        <v>114</v>
-      </c>
-      <c r="H257" s="1">
+        <v>117</v>
+      </c>
+      <c r="H257" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B258" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C258" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D258" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F258" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G258" t="s">
-        <v>145</v>
-      </c>
-      <c r="H258" s="1">
+        <v>150</v>
+      </c>
+      <c r="H258" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="A259" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B259" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C259" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D259" t="s">
-        <v>136</v>
-      </c>
-      <c r="E259" s="1">
+        <v>139</v>
+      </c>
+      <c r="E259" s="2">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
-        <v>162</v>
-      </c>
-      <c r="H259" s="1">
+        <v>167</v>
+      </c>
+      <c r="H259" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B260" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C260" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D260" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F260" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G260" t="s">
-        <v>146</v>
-      </c>
-      <c r="H260" s="1">
+        <v>151</v>
+      </c>
+      <c r="H260" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B261" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C261" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D261" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F261" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G261" t="s">
-        <v>146</v>
-      </c>
-      <c r="H261" s="1">
+        <v>151</v>
+      </c>
+      <c r="H261" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" t="s">
+        <v>89</v>
+      </c>
+      <c r="B262" t="s">
+        <v>99</v>
+      </c>
+      <c r="C262" t="s">
+        <v>101</v>
+      </c>
+      <c r="D262" t="s">
+        <v>122</v>
+      </c>
+      <c r="F262" t="s">
+        <v>152</v>
+      </c>
+      <c r="G262" t="s">
+        <v>152</v>
+      </c>
+      <c r="H262" s="2">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" t="s">
+        <v>62</v>
+      </c>
+      <c r="B263" t="s">
+        <v>90</v>
+      </c>
+      <c r="C263" t="s">
+        <v>100</v>
+      </c>
+      <c r="H263" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" t="s">
+        <v>63</v>
+      </c>
+      <c r="B264" t="s">
+        <v>90</v>
+      </c>
+      <c r="C264" t="s">
+        <v>102</v>
+      </c>
+      <c r="D264" t="s">
+        <v>140</v>
+      </c>
+      <c r="E264" s="2">
+        <v>46217</v>
+      </c>
+      <c r="G264" t="s">
+        <v>162</v>
+      </c>
+      <c r="H264" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" t="s">
+        <v>64</v>
+      </c>
+      <c r="B265" t="s">
+        <v>90</v>
+      </c>
+      <c r="C265" t="s">
+        <v>100</v>
+      </c>
+      <c r="H265" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" t="s">
+        <v>65</v>
+      </c>
+      <c r="B266" t="s">
+        <v>91</v>
+      </c>
+      <c r="C266" t="s">
+        <v>104</v>
+      </c>
+      <c r="H266" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" t="s">
+        <v>66</v>
+      </c>
+      <c r="B267" t="s">
+        <v>92</v>
+      </c>
+      <c r="C267" t="s">
+        <v>100</v>
+      </c>
+      <c r="H267" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" t="s">
+        <v>67</v>
+      </c>
+      <c r="B268" t="s">
+        <v>92</v>
+      </c>
+      <c r="C268" t="s">
+        <v>104</v>
+      </c>
+      <c r="H268" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269" t="s">
+        <v>68</v>
+      </c>
+      <c r="B269" t="s">
+        <v>92</v>
+      </c>
+      <c r="C269" t="s">
+        <v>104</v>
+      </c>
+      <c r="H269" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270" t="s">
+        <v>69</v>
+      </c>
+      <c r="B270" t="s">
+        <v>92</v>
+      </c>
+      <c r="C270" t="s">
+        <v>102</v>
+      </c>
+      <c r="D270" t="s">
+        <v>110</v>
+      </c>
+      <c r="E270" s="2">
+        <v>46234</v>
+      </c>
+      <c r="G270" t="s">
+        <v>156</v>
+      </c>
+      <c r="H270" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
+      <c r="A271" t="s">
+        <v>70</v>
+      </c>
+      <c r="B271" t="s">
+        <v>93</v>
+      </c>
+      <c r="C271" t="s">
+        <v>104</v>
+      </c>
+      <c r="H271" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272" t="s">
+        <v>71</v>
+      </c>
+      <c r="B272" t="s">
+        <v>93</v>
+      </c>
+      <c r="C272" t="s">
+        <v>102</v>
+      </c>
+      <c r="D272" t="s">
+        <v>141</v>
+      </c>
+      <c r="E272" s="2">
+        <v>46224</v>
+      </c>
+      <c r="G272" t="s">
+        <v>168</v>
+      </c>
+      <c r="H272" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273" t="s">
+        <v>72</v>
+      </c>
+      <c r="B273" t="s">
+        <v>94</v>
+      </c>
+      <c r="C273" t="s">
+        <v>102</v>
+      </c>
+      <c r="D273" t="s">
+        <v>142</v>
+      </c>
+      <c r="E273" s="2">
+        <v>46219</v>
+      </c>
+      <c r="G273" t="s">
+        <v>170</v>
+      </c>
+      <c r="H273" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274" t="s">
+        <v>73</v>
+      </c>
+      <c r="B274" t="s">
+        <v>95</v>
+      </c>
+      <c r="C274" t="s">
+        <v>100</v>
+      </c>
+      <c r="H274" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
+      <c r="A275" t="s">
+        <v>74</v>
+      </c>
+      <c r="B275" t="s">
+        <v>95</v>
+      </c>
+      <c r="C275" t="s">
+        <v>100</v>
+      </c>
+      <c r="H275" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
+      <c r="A276" t="s">
+        <v>32</v>
+      </c>
+      <c r="B276" t="s">
+        <v>95</v>
+      </c>
+      <c r="C276" t="s">
+        <v>101</v>
+      </c>
+      <c r="D276" t="s">
+        <v>113</v>
+      </c>
+      <c r="E276" s="2">
+        <v>46237</v>
+      </c>
+      <c r="G276" t="s">
+        <v>169</v>
+      </c>
+      <c r="H276" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277" t="s">
+        <v>75</v>
+      </c>
+      <c r="B277" t="s">
+        <v>96</v>
+      </c>
+      <c r="C277" t="s">
+        <v>100</v>
+      </c>
+      <c r="H277" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8">
+      <c r="A278" t="s">
+        <v>76</v>
+      </c>
+      <c r="B278" t="s">
+        <v>96</v>
+      </c>
+      <c r="C278" t="s">
+        <v>102</v>
+      </c>
+      <c r="D278" t="s">
+        <v>145</v>
+      </c>
+      <c r="E278" s="2">
+        <v>46227</v>
+      </c>
+      <c r="G278" t="s">
+        <v>171</v>
+      </c>
+      <c r="H278" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8">
+      <c r="A279" t="s">
+        <v>77</v>
+      </c>
+      <c r="B279" t="s">
+        <v>96</v>
+      </c>
+      <c r="C279" t="s">
+        <v>103</v>
+      </c>
+      <c r="D279" t="s">
+        <v>143</v>
+      </c>
+      <c r="E279" s="2">
+        <v>46219</v>
+      </c>
+      <c r="G279" t="s">
+        <v>170</v>
+      </c>
+      <c r="H279" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280" t="s">
+        <v>78</v>
+      </c>
+      <c r="B280" t="s">
+        <v>96</v>
+      </c>
+      <c r="C280" t="s">
+        <v>100</v>
+      </c>
+      <c r="H280" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" t="s">
+        <v>79</v>
+      </c>
+      <c r="B281" t="s">
+        <v>96</v>
+      </c>
+      <c r="C281" t="s">
+        <v>101</v>
+      </c>
+      <c r="D281" t="s">
+        <v>146</v>
+      </c>
+      <c r="E281" s="2">
+        <v>46241</v>
+      </c>
+      <c r="G281" t="s">
+        <v>166</v>
+      </c>
+      <c r="H281" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8">
+      <c r="A282" t="s">
+        <v>80</v>
+      </c>
+      <c r="B282" t="s">
+        <v>97</v>
+      </c>
+      <c r="C282" t="s">
+        <v>101</v>
+      </c>
+      <c r="D282" t="s">
+        <v>126</v>
+      </c>
+      <c r="F282" t="s">
+        <v>154</v>
+      </c>
+      <c r="G282" t="s">
+        <v>154</v>
+      </c>
+      <c r="H282" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8">
+      <c r="A283" t="s">
+        <v>81</v>
+      </c>
+      <c r="B283" t="s">
+        <v>98</v>
+      </c>
+      <c r="C283" t="s">
+        <v>104</v>
+      </c>
+      <c r="H283" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284" t="s">
+        <v>82</v>
+      </c>
+      <c r="B284" t="s">
+        <v>99</v>
+      </c>
+      <c r="C284" t="s">
+        <v>100</v>
+      </c>
+      <c r="H284" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285" t="s">
+        <v>83</v>
+      </c>
+      <c r="B285" t="s">
+        <v>99</v>
+      </c>
+      <c r="C285" t="s">
+        <v>105</v>
+      </c>
+      <c r="D285" t="s">
+        <v>116</v>
+      </c>
+      <c r="F285" t="s">
+        <v>149</v>
+      </c>
+      <c r="G285" t="s">
+        <v>149</v>
+      </c>
+      <c r="H285" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
+      <c r="A286" t="s">
+        <v>84</v>
+      </c>
+      <c r="B286" t="s">
+        <v>99</v>
+      </c>
+      <c r="C286" t="s">
+        <v>105</v>
+      </c>
+      <c r="D286" t="s">
+        <v>117</v>
+      </c>
+      <c r="H286" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8">
+      <c r="A287" t="s">
+        <v>85</v>
+      </c>
+      <c r="B287" t="s">
+        <v>99</v>
+      </c>
+      <c r="C287" t="s">
+        <v>101</v>
+      </c>
+      <c r="D287" t="s">
+        <v>118</v>
+      </c>
+      <c r="F287" t="s">
+        <v>150</v>
+      </c>
+      <c r="G287" t="s">
+        <v>150</v>
+      </c>
+      <c r="H287" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
+      <c r="A288" t="s">
         <v>86</v>
       </c>
-      <c r="B262" t="s">
-        <v>96</v>
-      </c>
-      <c r="C262" t="s">
-        <v>98</v>
-      </c>
-      <c r="D262" t="s">
-        <v>119</v>
-      </c>
-      <c r="F262" t="s">
-        <v>147</v>
-      </c>
-      <c r="G262" t="s">
-        <v>147</v>
-      </c>
-      <c r="H262" s="1">
-        <v>46217</v>
+      <c r="B288" t="s">
+        <v>99</v>
+      </c>
+      <c r="C288" t="s">
+        <v>103</v>
+      </c>
+      <c r="D288" t="s">
+        <v>139</v>
+      </c>
+      <c r="E288" s="2">
+        <v>46295</v>
+      </c>
+      <c r="G288" t="s">
+        <v>167</v>
+      </c>
+      <c r="H288" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
+      <c r="A289" t="s">
+        <v>87</v>
+      </c>
+      <c r="B289" t="s">
+        <v>99</v>
+      </c>
+      <c r="C289" t="s">
+        <v>101</v>
+      </c>
+      <c r="D289" t="s">
+        <v>120</v>
+      </c>
+      <c r="F289" t="s">
+        <v>151</v>
+      </c>
+      <c r="G289" t="s">
+        <v>151</v>
+      </c>
+      <c r="H289" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290" t="s">
+        <v>88</v>
+      </c>
+      <c r="B290" t="s">
+        <v>99</v>
+      </c>
+      <c r="C290" t="s">
+        <v>101</v>
+      </c>
+      <c r="D290" t="s">
+        <v>121</v>
+      </c>
+      <c r="F290" t="s">
+        <v>151</v>
+      </c>
+      <c r="G290" t="s">
+        <v>151</v>
+      </c>
+      <c r="H290" s="2">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291" t="s">
+        <v>89</v>
+      </c>
+      <c r="B291" t="s">
+        <v>99</v>
+      </c>
+      <c r="C291" t="s">
+        <v>101</v>
+      </c>
+      <c r="D291" t="s">
+        <v>122</v>
+      </c>
+      <c r="F291" t="s">
+        <v>152</v>
+      </c>
+      <c r="G291" t="s">
+        <v>152</v>
+      </c>
+      <c r="H291" s="2">
+        <v>46218</v>
       </c>
     </row>
   </sheetData>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -540,16 +540,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -565,7 +557,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -573,30 +565,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -896,72 +870,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1026,7 +1000,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1091,7 +1065,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1156,7 +1130,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1221,7 +1195,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1286,7 +1260,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1351,7 +1325,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1416,7 +1390,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1481,7 +1455,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1546,7 +1520,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1621,28 +1595,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1656,7 +1630,7 @@
       <c r="C2" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1670,7 +1644,7 @@
       <c r="C3" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1693,7 +1667,7 @@
       <c r="G4" t="s">
         <v>147</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1707,7 +1681,7 @@
       <c r="C5" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1721,7 +1695,7 @@
       <c r="C6" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1738,13 +1712,13 @@
       <c r="D7" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1761,13 +1735,13 @@
       <c r="D8" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>155</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1784,13 +1758,13 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>156</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1807,13 +1781,13 @@
       <c r="D10" t="s">
         <v>111</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>157</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1827,7 +1801,7 @@
       <c r="C11" t="s">
         <v>100</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1841,7 +1815,7 @@
       <c r="C12" t="s">
         <v>100</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1858,13 +1832,13 @@
       <c r="D13" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>155</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1878,7 +1852,7 @@
       <c r="C14" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1895,13 +1869,13 @@
       <c r="D15" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>158</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1915,7 +1889,7 @@
       <c r="C16" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1929,7 +1903,7 @@
       <c r="C17" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1946,13 +1920,13 @@
       <c r="D18" t="s">
         <v>114</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>159</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1966,7 +1940,7 @@
       <c r="C19" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1983,13 +1957,13 @@
       <c r="D20" t="s">
         <v>115</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2012,7 +1986,7 @@
       <c r="G21" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2026,7 +2000,7 @@
       <c r="C22" t="s">
         <v>104</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2040,7 +2014,7 @@
       <c r="C23" t="s">
         <v>100</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2063,7 +2037,7 @@
       <c r="G24" t="s">
         <v>149</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2080,7 +2054,7 @@
       <c r="D25" t="s">
         <v>117</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2103,7 +2077,7 @@
       <c r="G26" t="s">
         <v>150</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2120,13 +2094,13 @@
       <c r="D27" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>160</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2149,7 +2123,7 @@
       <c r="G28" t="s">
         <v>151</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2172,7 +2146,7 @@
       <c r="G29" t="s">
         <v>151</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2195,7 +2169,7 @@
       <c r="G30" t="s">
         <v>152</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2209,7 +2183,7 @@
       <c r="C31" t="s">
         <v>100</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2223,7 +2197,7 @@
       <c r="C32" t="s">
         <v>100</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2246,7 +2220,7 @@
       <c r="G33" t="s">
         <v>153</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2260,7 +2234,7 @@
       <c r="C34" t="s">
         <v>100</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2274,7 +2248,7 @@
       <c r="C35" t="s">
         <v>100</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2291,13 +2265,13 @@
       <c r="D36" t="s">
         <v>108</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>155</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2314,13 +2288,13 @@
       <c r="D37" t="s">
         <v>109</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>155</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2337,13 +2311,13 @@
       <c r="D38" t="s">
         <v>110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>156</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2360,13 +2334,13 @@
       <c r="D39" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>157</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2380,7 +2354,7 @@
       <c r="C40" t="s">
         <v>100</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2394,7 +2368,7 @@
       <c r="C41" t="s">
         <v>100</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2411,13 +2385,13 @@
       <c r="D42" t="s">
         <v>112</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>155</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2431,7 +2405,7 @@
       <c r="C43" t="s">
         <v>100</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2448,13 +2422,13 @@
       <c r="D44" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>158</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2468,7 +2442,7 @@
       <c r="C45" t="s">
         <v>100</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2482,7 +2456,7 @@
       <c r="C46" t="s">
         <v>100</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2496,7 +2470,7 @@
       <c r="C47" t="s">
         <v>104</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2510,7 +2484,7 @@
       <c r="C48" t="s">
         <v>100</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2527,13 +2501,13 @@
       <c r="D49" t="s">
         <v>124</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>155</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2556,7 +2530,7 @@
       <c r="G50" t="s">
         <v>148</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2570,7 +2544,7 @@
       <c r="C51" t="s">
         <v>104</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2584,7 +2558,7 @@
       <c r="C52" t="s">
         <v>100</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2607,7 +2581,7 @@
       <c r="G53" t="s">
         <v>149</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2624,7 +2598,7 @@
       <c r="D54" t="s">
         <v>117</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2647,7 +2621,7 @@
       <c r="G55" t="s">
         <v>150</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2664,13 +2638,13 @@
       <c r="D56" t="s">
         <v>119</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>160</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2693,7 +2667,7 @@
       <c r="G57" t="s">
         <v>151</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2716,7 +2690,7 @@
       <c r="G58" t="s">
         <v>151</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2739,7 +2713,7 @@
       <c r="G59" t="s">
         <v>152</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2753,7 +2727,7 @@
       <c r="C60" t="s">
         <v>100</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2767,7 +2741,7 @@
       <c r="C61" t="s">
         <v>100</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2784,13 +2758,13 @@
       <c r="D62" t="s">
         <v>123</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>161</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2804,7 +2778,7 @@
       <c r="C63" t="s">
         <v>100</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2821,13 +2795,13 @@
       <c r="D64" t="s">
         <v>125</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>162</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2841,7 +2815,7 @@
       <c r="C65" t="s">
         <v>100</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2855,7 +2829,7 @@
       <c r="C66" t="s">
         <v>104</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2872,13 +2846,13 @@
       <c r="D67" t="s">
         <v>110</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>156</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2895,13 +2869,13 @@
       <c r="D68" t="s">
         <v>111</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>157</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2915,7 +2889,7 @@
       <c r="C69" t="s">
         <v>100</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2929,7 +2903,7 @@
       <c r="C70" t="s">
         <v>100</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2946,13 +2920,13 @@
       <c r="D71" t="s">
         <v>112</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>161</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2966,7 +2940,7 @@
       <c r="C72" t="s">
         <v>100</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2983,13 +2957,13 @@
       <c r="D73" t="s">
         <v>113</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>158</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3003,7 +2977,7 @@
       <c r="C74" t="s">
         <v>100</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3017,7 +2991,7 @@
       <c r="C75" t="s">
         <v>100</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3031,7 +3005,7 @@
       <c r="C76" t="s">
         <v>100</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3045,7 +3019,7 @@
       <c r="C77" t="s">
         <v>100</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3062,13 +3036,13 @@
       <c r="D78" t="s">
         <v>124</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>161</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3091,7 +3065,7 @@
       <c r="G79" t="s">
         <v>154</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3105,7 +3079,7 @@
       <c r="C80" t="s">
         <v>104</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3119,7 +3093,7 @@
       <c r="C81" t="s">
         <v>100</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3142,7 +3116,7 @@
       <c r="G82" t="s">
         <v>149</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3159,7 +3133,7 @@
       <c r="D83" t="s">
         <v>117</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3182,7 +3156,7 @@
       <c r="G84" t="s">
         <v>150</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3199,13 +3173,13 @@
       <c r="D85" t="s">
         <v>119</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>160</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3228,7 +3202,7 @@
       <c r="G86" t="s">
         <v>151</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3251,7 +3225,7 @@
       <c r="G87" t="s">
         <v>151</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3274,7 +3248,7 @@
       <c r="G88" t="s">
         <v>152</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3288,7 +3262,7 @@
       <c r="C89" t="s">
         <v>100</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3305,13 +3279,13 @@
       <c r="D90" t="s">
         <v>127</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>162</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3328,13 +3302,13 @@
       <c r="D91" t="s">
         <v>123</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>161</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3348,7 +3322,7 @@
       <c r="C92" t="s">
         <v>100</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3365,13 +3339,13 @@
       <c r="D93" t="s">
         <v>125</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>162</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3385,7 +3359,7 @@
       <c r="C94" t="s">
         <v>100</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3399,7 +3373,7 @@
       <c r="C95" t="s">
         <v>104</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3416,13 +3390,13 @@
       <c r="D96" t="s">
         <v>110</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>156</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3439,13 +3413,13 @@
       <c r="D97" t="s">
         <v>111</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>157</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3459,7 +3433,7 @@
       <c r="C98" t="s">
         <v>100</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3476,13 +3450,13 @@
       <c r="D99" t="s">
         <v>128</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>157</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3499,13 +3473,13 @@
       <c r="D100" t="s">
         <v>112</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>157</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3519,7 +3493,7 @@
       <c r="C101" t="s">
         <v>100</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3536,13 +3510,13 @@
       <c r="D102" t="s">
         <v>113</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>158</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3559,13 +3533,13 @@
       <c r="D103" t="s">
         <v>129</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>157</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3579,7 +3553,7 @@
       <c r="C104" t="s">
         <v>100</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3593,7 +3567,7 @@
       <c r="C105" t="s">
         <v>100</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3607,7 +3581,7 @@
       <c r="C106" t="s">
         <v>100</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3624,13 +3598,13 @@
       <c r="D107" t="s">
         <v>130</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>157</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3653,7 +3627,7 @@
       <c r="G108" t="s">
         <v>154</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3667,7 +3641,7 @@
       <c r="C109" t="s">
         <v>104</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3681,7 +3655,7 @@
       <c r="C110" t="s">
         <v>100</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3704,7 +3678,7 @@
       <c r="G111" t="s">
         <v>149</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3721,7 +3695,7 @@
       <c r="D112" t="s">
         <v>117</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3744,7 +3718,7 @@
       <c r="G113" t="s">
         <v>150</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3761,13 +3735,13 @@
       <c r="D114" t="s">
         <v>119</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>160</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3790,7 +3764,7 @@
       <c r="G115" t="s">
         <v>151</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3813,7 +3787,7 @@
       <c r="G116" t="s">
         <v>151</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3836,7 +3810,7 @@
       <c r="G117" t="s">
         <v>152</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3850,7 +3824,7 @@
       <c r="C118" t="s">
         <v>100</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -3867,13 +3841,13 @@
       <c r="D119" t="s">
         <v>127</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>162</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -3887,7 +3861,7 @@
       <c r="C120" t="s">
         <v>104</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -3901,7 +3875,7 @@
       <c r="C121" t="s">
         <v>100</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -3915,7 +3889,7 @@
       <c r="C122" t="s">
         <v>104</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -3929,7 +3903,7 @@
       <c r="C123" t="s">
         <v>104</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -3943,7 +3917,7 @@
       <c r="C124" t="s">
         <v>104</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -3960,13 +3934,13 @@
       <c r="D125" t="s">
         <v>110</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>156</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -3983,13 +3957,13 @@
       <c r="D126" t="s">
         <v>111</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>157</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4003,7 +3977,7 @@
       <c r="C127" t="s">
         <v>100</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4020,13 +3994,13 @@
       <c r="D128" t="s">
         <v>128</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>157</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4043,13 +4017,13 @@
       <c r="D129" t="s">
         <v>112</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>157</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4063,7 +4037,7 @@
       <c r="C130" t="s">
         <v>100</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4080,13 +4054,13 @@
       <c r="D131" t="s">
         <v>113</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>158</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4103,13 +4077,13 @@
       <c r="D132" t="s">
         <v>129</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>157</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4123,7 +4097,7 @@
       <c r="C133" t="s">
         <v>100</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4137,7 +4111,7 @@
       <c r="C134" t="s">
         <v>100</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4151,7 +4125,7 @@
       <c r="C135" t="s">
         <v>100</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4168,13 +4142,13 @@
       <c r="D136" t="s">
         <v>131</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>157</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4197,7 +4171,7 @@
       <c r="G137" t="s">
         <v>154</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4211,7 +4185,7 @@
       <c r="C138" t="s">
         <v>104</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4225,7 +4199,7 @@
       <c r="C139" t="s">
         <v>100</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4248,7 +4222,7 @@
       <c r="G140" t="s">
         <v>149</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4265,7 +4239,7 @@
       <c r="D141" t="s">
         <v>117</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4288,7 +4262,7 @@
       <c r="G142" t="s">
         <v>150</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4305,13 +4279,13 @@
       <c r="D143" t="s">
         <v>119</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>160</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4334,7 +4308,7 @@
       <c r="G144" t="s">
         <v>151</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4357,7 +4331,7 @@
       <c r="G145" t="s">
         <v>151</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4380,7 +4354,7 @@
       <c r="G146" t="s">
         <v>152</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4394,7 +4368,7 @@
       <c r="C147" t="s">
         <v>100</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4411,13 +4385,13 @@
       <c r="D148" t="s">
         <v>127</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>162</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4431,7 +4405,7 @@
       <c r="C149" t="s">
         <v>104</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4445,7 +4419,7 @@
       <c r="C150" t="s">
         <v>100</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4459,7 +4433,7 @@
       <c r="C151" t="s">
         <v>100</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4473,7 +4447,7 @@
       <c r="C152" t="s">
         <v>104</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4487,7 +4461,7 @@
       <c r="C153" t="s">
         <v>104</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4504,13 +4478,13 @@
       <c r="D154" t="s">
         <v>110</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>156</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4527,13 +4501,13 @@
       <c r="D155" t="s">
         <v>111</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>157</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4547,7 +4521,7 @@
       <c r="C156" t="s">
         <v>100</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4564,13 +4538,13 @@
       <c r="D157" t="s">
         <v>128</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>157</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4587,13 +4561,13 @@
       <c r="D158" t="s">
         <v>112</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>157</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4610,13 +4584,13 @@
       <c r="D159" t="s">
         <v>132</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>163</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4633,13 +4607,13 @@
       <c r="D160" t="s">
         <v>113</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>158</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4656,13 +4630,13 @@
       <c r="D161" t="s">
         <v>129</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>157</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4676,7 +4650,7 @@
       <c r="C162" t="s">
         <v>100</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4690,7 +4664,7 @@
       <c r="C163" t="s">
         <v>100</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4704,7 +4678,7 @@
       <c r="C164" t="s">
         <v>100</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4721,13 +4695,13 @@
       <c r="D165" t="s">
         <v>131</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>157</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4750,7 +4724,7 @@
       <c r="G166" t="s">
         <v>154</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4764,7 +4738,7 @@
       <c r="C167" t="s">
         <v>104</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4778,7 +4752,7 @@
       <c r="C168" t="s">
         <v>100</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4801,7 +4775,7 @@
       <c r="G169" t="s">
         <v>149</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4818,7 +4792,7 @@
       <c r="D170" t="s">
         <v>117</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4841,7 +4815,7 @@
       <c r="G171" t="s">
         <v>150</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4858,13 +4832,13 @@
       <c r="D172" t="s">
         <v>119</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>160</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4887,7 +4861,7 @@
       <c r="G173" t="s">
         <v>151</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4910,7 +4884,7 @@
       <c r="G174" t="s">
         <v>151</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4933,7 +4907,7 @@
       <c r="G175" t="s">
         <v>152</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4947,7 +4921,7 @@
       <c r="C176" t="s">
         <v>100</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -4964,13 +4938,13 @@
       <c r="D177" t="s">
         <v>133</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>162</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -4984,7 +4958,7 @@
       <c r="C178" t="s">
         <v>100</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5001,13 +4975,13 @@
       <c r="D179" t="s">
         <v>134</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>158</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5021,7 +4995,7 @@
       <c r="C180" t="s">
         <v>100</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5035,7 +5009,7 @@
       <c r="C181" t="s">
         <v>104</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5049,7 +5023,7 @@
       <c r="C182" t="s">
         <v>104</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5066,13 +5040,13 @@
       <c r="D183" t="s">
         <v>110</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>156</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5089,13 +5063,13 @@
       <c r="D184" t="s">
         <v>111</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>157</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5109,7 +5083,7 @@
       <c r="C185" t="s">
         <v>100</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5126,13 +5100,13 @@
       <c r="D186" t="s">
         <v>128</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>157</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5149,13 +5123,13 @@
       <c r="D187" t="s">
         <v>135</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>157</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5172,13 +5146,13 @@
       <c r="D188" t="s">
         <v>136</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>157</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5195,13 +5169,13 @@
       <c r="D189" t="s">
         <v>113</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>158</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5218,13 +5192,13 @@
       <c r="D190" t="s">
         <v>129</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>157</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5238,7 +5212,7 @@
       <c r="C191" t="s">
         <v>100</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5252,7 +5226,7 @@
       <c r="C192" t="s">
         <v>100</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5266,7 +5240,7 @@
       <c r="C193" t="s">
         <v>100</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5283,13 +5257,13 @@
       <c r="D194" t="s">
         <v>131</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>164</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5312,7 +5286,7 @@
       <c r="G195" t="s">
         <v>154</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5326,7 +5300,7 @@
       <c r="C196" t="s">
         <v>104</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5340,7 +5314,7 @@
       <c r="C197" t="s">
         <v>100</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5363,7 +5337,7 @@
       <c r="G198" t="s">
         <v>149</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5380,7 +5354,7 @@
       <c r="D199" t="s">
         <v>117</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5403,7 +5377,7 @@
       <c r="G200" t="s">
         <v>150</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5420,13 +5394,13 @@
       <c r="D201" t="s">
         <v>119</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>160</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5449,7 +5423,7 @@
       <c r="G202" t="s">
         <v>151</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5472,7 +5446,7 @@
       <c r="G203" t="s">
         <v>151</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5495,7 +5469,7 @@
       <c r="G204" t="s">
         <v>152</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5509,7 +5483,7 @@
       <c r="C205" t="s">
         <v>100</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5526,13 +5500,13 @@
       <c r="D206" t="s">
         <v>133</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>162</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5546,7 +5520,7 @@
       <c r="C207" t="s">
         <v>100</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5560,7 +5534,7 @@
       <c r="C208" t="s">
         <v>104</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5574,7 +5548,7 @@
       <c r="C209" t="s">
         <v>100</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5588,7 +5562,7 @@
       <c r="C210" t="s">
         <v>104</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5602,7 +5576,7 @@
       <c r="C211" t="s">
         <v>104</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5619,13 +5593,13 @@
       <c r="D212" t="s">
         <v>110</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>156</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5639,7 +5613,7 @@
       <c r="C213" t="s">
         <v>104</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5653,7 +5627,7 @@
       <c r="C214" t="s">
         <v>100</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5670,13 +5644,13 @@
       <c r="D215" t="s">
         <v>128</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>165</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5693,13 +5667,13 @@
       <c r="D216" t="s">
         <v>135</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>158</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5713,7 +5687,7 @@
       <c r="C217" t="s">
         <v>100</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5730,13 +5704,13 @@
       <c r="D218" t="s">
         <v>113</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>158</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5750,7 +5724,7 @@
       <c r="C219" t="s">
         <v>100</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5764,7 +5738,7 @@
       <c r="C220" t="s">
         <v>100</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5781,13 +5755,13 @@
       <c r="D221" t="s">
         <v>137</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>162</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5801,7 +5775,7 @@
       <c r="C222" t="s">
         <v>100</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5818,13 +5792,13 @@
       <c r="D223" t="s">
         <v>138</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>166</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5847,7 +5821,7 @@
       <c r="G224" t="s">
         <v>154</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5861,7 +5835,7 @@
       <c r="C225" t="s">
         <v>104</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5875,7 +5849,7 @@
       <c r="C226" t="s">
         <v>100</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5898,7 +5872,7 @@
       <c r="G227" t="s">
         <v>149</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5915,7 +5889,7 @@
       <c r="D228" t="s">
         <v>117</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5938,7 +5912,7 @@
       <c r="G229" t="s">
         <v>150</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5955,13 +5929,13 @@
       <c r="D230" t="s">
         <v>139</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>167</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5984,7 +5958,7 @@
       <c r="G231" t="s">
         <v>151</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6007,7 +5981,7 @@
       <c r="G232" t="s">
         <v>151</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6030,7 +6004,7 @@
       <c r="G233" t="s">
         <v>152</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6044,7 +6018,7 @@
       <c r="C234" t="s">
         <v>100</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6061,13 +6035,13 @@
       <c r="D235" t="s">
         <v>140</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>162</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6081,7 +6055,7 @@
       <c r="C236" t="s">
         <v>100</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6095,7 +6069,7 @@
       <c r="C237" t="s">
         <v>104</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6109,7 +6083,7 @@
       <c r="C238" t="s">
         <v>100</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6123,7 +6097,7 @@
       <c r="C239" t="s">
         <v>104</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6137,7 +6111,7 @@
       <c r="C240" t="s">
         <v>104</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6154,13 +6128,13 @@
       <c r="D241" t="s">
         <v>110</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>156</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6174,7 +6148,7 @@
       <c r="C242" t="s">
         <v>104</v>
       </c>
-      <c r="H242" s="2">
+      <c r="H242" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6191,13 +6165,13 @@
       <c r="D243" t="s">
         <v>141</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>168</v>
       </c>
-      <c r="H243" s="2">
+      <c r="H243" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6214,13 +6188,13 @@
       <c r="D244" t="s">
         <v>142</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>165</v>
       </c>
-      <c r="H244" s="2">
+      <c r="H244" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6234,7 +6208,7 @@
       <c r="C245" t="s">
         <v>104</v>
       </c>
-      <c r="H245" s="2">
+      <c r="H245" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6248,7 +6222,7 @@
       <c r="C246" t="s">
         <v>100</v>
       </c>
-      <c r="H246" s="2">
+      <c r="H246" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6265,13 +6239,13 @@
       <c r="D247" t="s">
         <v>113</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>169</v>
       </c>
-      <c r="H247" s="2">
+      <c r="H247" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6285,7 +6259,7 @@
       <c r="C248" t="s">
         <v>100</v>
       </c>
-      <c r="H248" s="2">
+      <c r="H248" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6299,7 +6273,7 @@
       <c r="C249" t="s">
         <v>100</v>
       </c>
-      <c r="H249" s="2">
+      <c r="H249" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6316,13 +6290,13 @@
       <c r="D250" t="s">
         <v>143</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>164</v>
       </c>
-      <c r="H250" s="2">
+      <c r="H250" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6336,7 +6310,7 @@
       <c r="C251" t="s">
         <v>100</v>
       </c>
-      <c r="H251" s="2">
+      <c r="H251" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6353,13 +6327,13 @@
       <c r="D252" t="s">
         <v>144</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>166</v>
       </c>
-      <c r="H252" s="2">
+      <c r="H252" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6382,7 +6356,7 @@
       <c r="G253" t="s">
         <v>154</v>
       </c>
-      <c r="H253" s="2">
+      <c r="H253" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6396,7 +6370,7 @@
       <c r="C254" t="s">
         <v>104</v>
       </c>
-      <c r="H254" s="2">
+      <c r="H254" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6410,7 +6384,7 @@
       <c r="C255" t="s">
         <v>100</v>
       </c>
-      <c r="H255" s="2">
+      <c r="H255" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6433,7 +6407,7 @@
       <c r="G256" t="s">
         <v>149</v>
       </c>
-      <c r="H256" s="2">
+      <c r="H256" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6450,7 +6424,7 @@
       <c r="D257" t="s">
         <v>117</v>
       </c>
-      <c r="H257" s="2">
+      <c r="H257" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6473,7 +6447,7 @@
       <c r="G258" t="s">
         <v>150</v>
       </c>
-      <c r="H258" s="2">
+      <c r="H258" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6490,13 +6464,13 @@
       <c r="D259" t="s">
         <v>139</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>167</v>
       </c>
-      <c r="H259" s="2">
+      <c r="H259" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6519,7 +6493,7 @@
       <c r="G260" t="s">
         <v>151</v>
       </c>
-      <c r="H260" s="2">
+      <c r="H260" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6542,7 +6516,7 @@
       <c r="G261" t="s">
         <v>151</v>
       </c>
-      <c r="H261" s="2">
+      <c r="H261" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6565,7 +6539,7 @@
       <c r="G262" t="s">
         <v>152</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6579,7 +6553,7 @@
       <c r="C263" t="s">
         <v>100</v>
       </c>
-      <c r="H263" s="2">
+      <c r="H263" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6596,13 +6570,13 @@
       <c r="D264" t="s">
         <v>140</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>162</v>
       </c>
-      <c r="H264" s="2">
+      <c r="H264" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6616,7 +6590,7 @@
       <c r="C265" t="s">
         <v>100</v>
       </c>
-      <c r="H265" s="2">
+      <c r="H265" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6630,7 +6604,7 @@
       <c r="C266" t="s">
         <v>104</v>
       </c>
-      <c r="H266" s="2">
+      <c r="H266" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6644,7 +6618,7 @@
       <c r="C267" t="s">
         <v>100</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H267" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6658,7 +6632,7 @@
       <c r="C268" t="s">
         <v>104</v>
       </c>
-      <c r="H268" s="2">
+      <c r="H268" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6672,7 +6646,7 @@
       <c r="C269" t="s">
         <v>104</v>
       </c>
-      <c r="H269" s="2">
+      <c r="H269" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6689,13 +6663,13 @@
       <c r="D270" t="s">
         <v>110</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>156</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H270" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6709,7 +6683,7 @@
       <c r="C271" t="s">
         <v>104</v>
       </c>
-      <c r="H271" s="2">
+      <c r="H271" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6726,13 +6700,13 @@
       <c r="D272" t="s">
         <v>141</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>168</v>
       </c>
-      <c r="H272" s="2">
+      <c r="H272" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6749,13 +6723,13 @@
       <c r="D273" t="s">
         <v>142</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>170</v>
       </c>
-      <c r="H273" s="2">
+      <c r="H273" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6769,7 +6743,7 @@
       <c r="C274" t="s">
         <v>100</v>
       </c>
-      <c r="H274" s="2">
+      <c r="H274" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6783,7 +6757,7 @@
       <c r="C275" t="s">
         <v>100</v>
       </c>
-      <c r="H275" s="2">
+      <c r="H275" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6800,13 +6774,13 @@
       <c r="D276" t="s">
         <v>113</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>169</v>
       </c>
-      <c r="H276" s="2">
+      <c r="H276" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6820,7 +6794,7 @@
       <c r="C277" t="s">
         <v>100</v>
       </c>
-      <c r="H277" s="2">
+      <c r="H277" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6837,13 +6811,13 @@
       <c r="D278" t="s">
         <v>145</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>171</v>
       </c>
-      <c r="H278" s="2">
+      <c r="H278" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6860,13 +6834,13 @@
       <c r="D279" t="s">
         <v>143</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>170</v>
       </c>
-      <c r="H279" s="2">
+      <c r="H279" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6880,7 +6854,7 @@
       <c r="C280" t="s">
         <v>100</v>
       </c>
-      <c r="H280" s="2">
+      <c r="H280" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6897,13 +6871,13 @@
       <c r="D281" t="s">
         <v>146</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>166</v>
       </c>
-      <c r="H281" s="2">
+      <c r="H281" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6926,7 +6900,7 @@
       <c r="G282" t="s">
         <v>154</v>
       </c>
-      <c r="H282" s="2">
+      <c r="H282" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6940,7 +6914,7 @@
       <c r="C283" t="s">
         <v>104</v>
       </c>
-      <c r="H283" s="2">
+      <c r="H283" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6954,7 +6928,7 @@
       <c r="C284" t="s">
         <v>100</v>
       </c>
-      <c r="H284" s="2">
+      <c r="H284" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6977,7 +6951,7 @@
       <c r="G285" t="s">
         <v>149</v>
       </c>
-      <c r="H285" s="2">
+      <c r="H285" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6994,7 +6968,7 @@
       <c r="D286" t="s">
         <v>117</v>
       </c>
-      <c r="H286" s="2">
+      <c r="H286" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7017,7 +6991,7 @@
       <c r="G287" t="s">
         <v>150</v>
       </c>
-      <c r="H287" s="2">
+      <c r="H287" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7034,13 +7008,13 @@
       <c r="D288" t="s">
         <v>139</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>167</v>
       </c>
-      <c r="H288" s="2">
+      <c r="H288" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7063,7 +7037,7 @@
       <c r="G289" t="s">
         <v>151</v>
       </c>
-      <c r="H289" s="2">
+      <c r="H289" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7086,7 +7060,7 @@
       <c r="G290" t="s">
         <v>151</v>
       </c>
-      <c r="H290" s="2">
+      <c r="H290" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7109,7 +7083,7 @@
       <c r="G291" t="s">
         <v>152</v>
       </c>
-      <c r="H291" s="2">
+      <c r="H291" s="1">
         <v>46218</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="185">
   <si>
     <t>data_referencia</t>
   </si>
@@ -104,6 +104,9 @@
     <t>2722, 2738, 2743</t>
   </si>
   <si>
+    <t>2722, 2743</t>
+  </si>
+  <si>
     <t>2721, 2738, 2739</t>
   </si>
   <si>
@@ -152,6 +155,9 @@
     <t>4658:25</t>
   </si>
   <si>
+    <t>4749:20</t>
+  </si>
+  <si>
     <t>Disponibilidade_01_07_2026.txt</t>
   </si>
   <si>
@@ -182,6 +188,9 @@
     <t>Disponibilidade_15_07_2026.txt</t>
   </si>
   <si>
+    <t>Disponibilidade_17_07_2026.txt</t>
+  </si>
+  <si>
     <t>matricula</t>
   </si>
   <si>
@@ -458,6 +467,21 @@
     <t>Motor em recolhimento ao PAMASP. OS 3130021786. Será usado motor do 2732</t>
   </si>
   <si>
+    <t>NÚMERO DO PEDIDO DO PNEU - 17914796</t>
+  </si>
+  <si>
+    <t>GERADOR SEM INDICAÇÃO DE AMPERAGEM</t>
+  </si>
+  <si>
+    <t>AERONAVE AGUARDANDO TROCA DO ALTERNADOR E PULLING DRIVE OS: 3130021786</t>
+  </si>
+  <si>
+    <t>REALIZANDO INSTALAÇÃO DO MOTOR O.S. 3130021786</t>
+  </si>
+  <si>
+    <t>FCU será enviada hoje ao operador. DPE: 02 DIAS após chegada do item.</t>
+  </si>
+  <si>
     <t>01 DIA após chegada do item.</t>
   </si>
   <si>
@@ -480,6 +504,21 @@
   </si>
   <si>
     <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
+  </si>
+  <si>
+    <t>17/07.</t>
+  </si>
+  <si>
+    <t>01 DIA APÓS CHEGADA DO MATERIAL.</t>
+  </si>
+  <si>
+    <t>20/07.</t>
+  </si>
+  <si>
+    <t>31/08.</t>
+  </si>
+  <si>
+    <t>30/09.</t>
   </si>
   <si>
     <t>03/07</t>
@@ -866,7 +905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -981,13 +1020,13 @@
         <v>19</v>
       </c>
       <c r="P2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S2">
         <v>41.81</v>
@@ -996,7 +1035,7 @@
         <v>24</v>
       </c>
       <c r="U2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -1046,13 +1085,13 @@
         <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S3">
         <v>42.15</v>
@@ -1061,7 +1100,7 @@
         <v>24</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -1111,13 +1150,13 @@
         <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S4">
         <v>42.88</v>
@@ -1126,7 +1165,7 @@
         <v>24</v>
       </c>
       <c r="U4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -1176,13 +1215,13 @@
         <v>22</v>
       </c>
       <c r="P5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S5">
         <v>43.44</v>
@@ -1191,7 +1230,7 @@
         <v>24</v>
       </c>
       <c r="U5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -1241,13 +1280,13 @@
         <v>22</v>
       </c>
       <c r="P6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S6">
         <v>43.76</v>
@@ -1256,7 +1295,7 @@
         <v>24</v>
       </c>
       <c r="U6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -1306,13 +1345,13 @@
         <v>21</v>
       </c>
       <c r="P7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S7">
         <v>44.33</v>
@@ -1321,7 +1360,7 @@
         <v>24</v>
       </c>
       <c r="U7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -1371,13 +1410,13 @@
         <v>21</v>
       </c>
       <c r="P8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S8">
         <v>44.51</v>
@@ -1386,7 +1425,7 @@
         <v>24</v>
       </c>
       <c r="U8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1436,13 +1475,13 @@
         <v>21</v>
       </c>
       <c r="P9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S9">
         <v>45.03</v>
@@ -1451,7 +1490,7 @@
         <v>24</v>
       </c>
       <c r="U9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1501,13 +1540,13 @@
         <v>19</v>
       </c>
       <c r="P10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S10">
         <v>45.89</v>
@@ -1516,7 +1555,7 @@
         <v>24</v>
       </c>
       <c r="U10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1566,13 +1605,13 @@
         <v>20</v>
       </c>
       <c r="P11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S11">
         <v>46.26</v>
@@ -1581,7 +1620,72 @@
         <v>24</v>
       </c>
       <c r="U11" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>14</v>
+      </c>
+      <c r="L12">
+        <v>18</v>
+      </c>
+      <c r="M12">
+        <v>16</v>
+      </c>
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12">
+        <v>17</v>
+      </c>
+      <c r="P12" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" t="s">
+        <v>46</v>
+      </c>
+      <c r="S12">
+        <v>47.16</v>
+      </c>
+      <c r="T12">
+        <v>22</v>
+      </c>
+      <c r="U12" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1591,30 +1695,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H1" t="s">
         <v>0</v>
@@ -1622,13 +1726,13 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H2" s="1">
         <v>46204</v>
@@ -1636,13 +1740,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H3" s="1">
         <v>46204</v>
@@ -1650,22 +1754,22 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H4" s="1">
         <v>46204</v>
@@ -1673,13 +1777,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H5" s="1">
         <v>46204</v>
@@ -1687,13 +1791,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H6" s="1">
         <v>46204</v>
@@ -1701,22 +1805,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H7" s="1">
         <v>46204</v>
@@ -1724,22 +1828,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H8" s="1">
         <v>46204</v>
@@ -1747,22 +1851,22 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H9" s="1">
         <v>46204</v>
@@ -1770,22 +1874,22 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H10" s="1">
         <v>46204</v>
@@ -1793,13 +1897,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H11" s="1">
         <v>46204</v>
@@ -1807,13 +1911,13 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H12" s="1">
         <v>46204</v>
@@ -1821,22 +1925,22 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H13" s="1">
         <v>46204</v>
@@ -1844,13 +1948,13 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H14" s="1">
         <v>46204</v>
@@ -1858,22 +1962,22 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H15" s="1">
         <v>46204</v>
@@ -1881,13 +1985,13 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H16" s="1">
         <v>46204</v>
@@ -1895,13 +1999,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H17" s="1">
         <v>46204</v>
@@ -1909,22 +2013,22 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H18" s="1">
         <v>46204</v>
@@ -1932,13 +2036,13 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H19" s="1">
         <v>46204</v>
@@ -1946,22 +2050,22 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H20" s="1">
         <v>46204</v>
@@ -1969,22 +2073,22 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F21" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G21" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H21" s="1">
         <v>46204</v>
@@ -1992,13 +2096,13 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H22" s="1">
         <v>46204</v>
@@ -2006,13 +2110,13 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H23" s="1">
         <v>46204</v>
@@ -2020,22 +2124,22 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G24" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H24" s="1">
         <v>46204</v>
@@ -2043,16 +2147,16 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H25" s="1">
         <v>46204</v>
@@ -2060,22 +2164,22 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F26" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G26" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H26" s="1">
         <v>46204</v>
@@ -2083,22 +2187,22 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H27" s="1">
         <v>46204</v>
@@ -2106,22 +2210,22 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G28" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H28" s="1">
         <v>46204</v>
@@ -2129,22 +2233,22 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G29" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H29" s="1">
         <v>46204</v>
@@ -2152,22 +2256,22 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F30" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G30" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H30" s="1">
         <v>46204</v>
@@ -2175,13 +2279,13 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H31" s="1">
         <v>46205</v>
@@ -2189,13 +2293,13 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H32" s="1">
         <v>46205</v>
@@ -2203,22 +2307,22 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G33" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H33" s="1">
         <v>46205</v>
@@ -2226,13 +2330,13 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H34" s="1">
         <v>46205</v>
@@ -2240,13 +2344,13 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H35" s="1">
         <v>46205</v>
@@ -2254,22 +2358,22 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H36" s="1">
         <v>46205</v>
@@ -2277,22 +2381,22 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H37" s="1">
         <v>46205</v>
@@ -2300,22 +2404,22 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H38" s="1">
         <v>46205</v>
@@ -2323,22 +2427,22 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H39" s="1">
         <v>46205</v>
@@ -2346,13 +2450,13 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H40" s="1">
         <v>46205</v>
@@ -2360,13 +2464,13 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H41" s="1">
         <v>46205</v>
@@ -2374,22 +2478,22 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H42" s="1">
         <v>46205</v>
@@ -2397,13 +2501,13 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H43" s="1">
         <v>46205</v>
@@ -2411,22 +2515,22 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H44" s="1">
         <v>46205</v>
@@ -2434,13 +2538,13 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H45" s="1">
         <v>46205</v>
@@ -2448,13 +2552,13 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H46" s="1">
         <v>46205</v>
@@ -2462,13 +2566,13 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H47" s="1">
         <v>46205</v>
@@ -2476,13 +2580,13 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H48" s="1">
         <v>46205</v>
@@ -2490,22 +2594,22 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H49" s="1">
         <v>46205</v>
@@ -2513,22 +2617,22 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F50" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G50" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H50" s="1">
         <v>46205</v>
@@ -2536,13 +2640,13 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H51" s="1">
         <v>46205</v>
@@ -2550,13 +2654,13 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H52" s="1">
         <v>46205</v>
@@ -2564,22 +2668,22 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C53" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D53" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F53" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G53" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H53" s="1">
         <v>46205</v>
@@ -2587,16 +2691,16 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D54" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H54" s="1">
         <v>46205</v>
@@ -2604,22 +2708,22 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F55" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G55" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H55" s="1">
         <v>46205</v>
@@ -2627,22 +2731,22 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D56" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H56" s="1">
         <v>46205</v>
@@ -2650,22 +2754,22 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F57" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G57" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H57" s="1">
         <v>46205</v>
@@ -2673,22 +2777,22 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F58" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G58" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H58" s="1">
         <v>46205</v>
@@ -2696,22 +2800,22 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C59" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F59" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G59" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H59" s="1">
         <v>46205</v>
@@ -2719,13 +2823,13 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H60" s="1">
         <v>46209</v>
@@ -2733,13 +2837,13 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H61" s="1">
         <v>46209</v>
@@ -2747,22 +2851,22 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D62" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="H62" s="1">
         <v>46209</v>
@@ -2770,13 +2874,13 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H63" s="1">
         <v>46209</v>
@@ -2784,22 +2888,22 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D64" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H64" s="1">
         <v>46209</v>
@@ -2807,13 +2911,13 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H65" s="1">
         <v>46209</v>
@@ -2821,13 +2925,13 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H66" s="1">
         <v>46209</v>
@@ -2835,22 +2939,22 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D67" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H67" s="1">
         <v>46209</v>
@@ -2858,22 +2962,22 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H68" s="1">
         <v>46209</v>
@@ -2881,13 +2985,13 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H69" s="1">
         <v>46209</v>
@@ -2895,13 +2999,13 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H70" s="1">
         <v>46209</v>
@@ -2909,22 +3013,22 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="H71" s="1">
         <v>46209</v>
@@ -2932,13 +3036,13 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H72" s="1">
         <v>46209</v>
@@ -2946,22 +3050,22 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H73" s="1">
         <v>46209</v>
@@ -2969,13 +3073,13 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H74" s="1">
         <v>46209</v>
@@ -2983,13 +3087,13 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H75" s="1">
         <v>46209</v>
@@ -2997,13 +3101,13 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H76" s="1">
         <v>46209</v>
@@ -3011,13 +3115,13 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C77" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H77" s="1">
         <v>46209</v>
@@ -3025,22 +3129,22 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C78" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D78" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="H78" s="1">
         <v>46209</v>
@@ -3048,22 +3152,22 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F79" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G79" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H79" s="1">
         <v>46209</v>
@@ -3071,13 +3175,13 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C80" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H80" s="1">
         <v>46209</v>
@@ -3085,13 +3189,13 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C81" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H81" s="1">
         <v>46209</v>
@@ -3099,22 +3203,22 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C82" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D82" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F82" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G82" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H82" s="1">
         <v>46209</v>
@@ -3122,16 +3226,16 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C83" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D83" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H83" s="1">
         <v>46209</v>
@@ -3139,22 +3243,22 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C84" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D84" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F84" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G84" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H84" s="1">
         <v>46209</v>
@@ -3162,22 +3266,22 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D85" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H85" s="1">
         <v>46209</v>
@@ -3185,22 +3289,22 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D86" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F86" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G86" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H86" s="1">
         <v>46209</v>
@@ -3208,22 +3312,22 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C87" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D87" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F87" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G87" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H87" s="1">
         <v>46209</v>
@@ -3231,22 +3335,22 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C88" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F88" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G88" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H88" s="1">
         <v>46209</v>
@@ -3254,13 +3358,13 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H89" s="1">
         <v>46210</v>
@@ -3268,22 +3372,22 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H90" s="1">
         <v>46210</v>
@@ -3291,22 +3395,22 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C91" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="H91" s="1">
         <v>46210</v>
@@ -3314,13 +3418,13 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C92" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H92" s="1">
         <v>46210</v>
@@ -3328,22 +3432,22 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D93" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H93" s="1">
         <v>46210</v>
@@ -3351,13 +3455,13 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C94" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H94" s="1">
         <v>46210</v>
@@ -3365,13 +3469,13 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C95" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H95" s="1">
         <v>46210</v>
@@ -3379,22 +3483,22 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C96" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D96" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H96" s="1">
         <v>46210</v>
@@ -3402,22 +3506,22 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C97" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D97" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H97" s="1">
         <v>46210</v>
@@ -3425,13 +3529,13 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H98" s="1">
         <v>46210</v>
@@ -3439,22 +3543,22 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D99" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H99" s="1">
         <v>46210</v>
@@ -3462,22 +3566,22 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D100" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H100" s="1">
         <v>46210</v>
@@ -3485,13 +3589,13 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H101" s="1">
         <v>46210</v>
@@ -3499,22 +3603,22 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C102" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D102" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H102" s="1">
         <v>46210</v>
@@ -3522,22 +3626,22 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B103" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C103" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D103" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H103" s="1">
         <v>46210</v>
@@ -3545,13 +3649,13 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B104" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C104" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H104" s="1">
         <v>46210</v>
@@ -3559,13 +3663,13 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B105" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H105" s="1">
         <v>46210</v>
@@ -3573,13 +3677,13 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B106" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C106" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H106" s="1">
         <v>46210</v>
@@ -3587,22 +3691,22 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B107" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C107" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H107" s="1">
         <v>46210</v>
@@ -3610,22 +3714,22 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B108" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C108" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F108" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G108" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H108" s="1">
         <v>46210</v>
@@ -3633,13 +3737,13 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B109" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C109" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H109" s="1">
         <v>46210</v>
@@ -3647,13 +3751,13 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B110" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C110" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H110" s="1">
         <v>46210</v>
@@ -3661,22 +3765,22 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B111" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C111" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D111" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F111" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G111" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H111" s="1">
         <v>46210</v>
@@ -3684,16 +3788,16 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B112" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C112" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D112" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H112" s="1">
         <v>46210</v>
@@ -3701,22 +3805,22 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B113" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C113" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D113" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F113" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G113" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H113" s="1">
         <v>46210</v>
@@ -3724,22 +3828,22 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B114" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D114" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H114" s="1">
         <v>46210</v>
@@ -3747,22 +3851,22 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C115" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D115" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F115" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G115" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H115" s="1">
         <v>46210</v>
@@ -3770,22 +3874,22 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C116" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D116" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F116" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G116" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H116" s="1">
         <v>46210</v>
@@ -3793,22 +3897,22 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B117" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C117" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D117" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F117" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G117" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H117" s="1">
         <v>46210</v>
@@ -3816,13 +3920,13 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C118" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H118" s="1">
         <v>46211</v>
@@ -3830,22 +3934,22 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B119" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C119" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D119" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H119" s="1">
         <v>46211</v>
@@ -3853,13 +3957,13 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B120" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C120" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H120" s="1">
         <v>46211</v>
@@ -3867,13 +3971,13 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B121" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C121" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H121" s="1">
         <v>46211</v>
@@ -3881,13 +3985,13 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B122" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C122" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H122" s="1">
         <v>46211</v>
@@ -3895,13 +3999,13 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B123" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C123" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H123" s="1">
         <v>46211</v>
@@ -3909,13 +4013,13 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B124" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C124" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H124" s="1">
         <v>46211</v>
@@ -3923,22 +4027,22 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B125" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C125" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D125" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H125" s="1">
         <v>46211</v>
@@ -3946,22 +4050,22 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B126" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C126" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D126" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H126" s="1">
         <v>46211</v>
@@ -3969,13 +4073,13 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B127" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C127" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H127" s="1">
         <v>46211</v>
@@ -3983,22 +4087,22 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B128" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C128" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D128" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H128" s="1">
         <v>46211</v>
@@ -4006,22 +4110,22 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B129" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C129" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D129" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H129" s="1">
         <v>46211</v>
@@ -4029,13 +4133,13 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B130" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C130" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H130" s="1">
         <v>46211</v>
@@ -4043,22 +4147,22 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B131" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D131" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H131" s="1">
         <v>46211</v>
@@ -4066,22 +4170,22 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B132" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C132" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D132" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H132" s="1">
         <v>46211</v>
@@ -4089,13 +4193,13 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B133" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C133" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H133" s="1">
         <v>46211</v>
@@ -4103,13 +4207,13 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B134" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C134" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H134" s="1">
         <v>46211</v>
@@ -4117,13 +4221,13 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B135" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C135" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H135" s="1">
         <v>46211</v>
@@ -4131,22 +4235,22 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B136" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C136" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D136" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H136" s="1">
         <v>46211</v>
@@ -4154,22 +4258,22 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B137" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C137" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D137" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F137" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G137" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H137" s="1">
         <v>46211</v>
@@ -4177,13 +4281,13 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B138" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C138" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H138" s="1">
         <v>46211</v>
@@ -4191,13 +4295,13 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B139" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C139" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H139" s="1">
         <v>46211</v>
@@ -4205,22 +4309,22 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B140" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C140" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D140" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F140" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G140" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H140" s="1">
         <v>46211</v>
@@ -4228,16 +4332,16 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B141" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C141" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D141" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H141" s="1">
         <v>46211</v>
@@ -4245,22 +4349,22 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B142" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C142" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D142" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F142" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G142" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H142" s="1">
         <v>46211</v>
@@ -4268,22 +4372,22 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B143" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C143" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D143" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H143" s="1">
         <v>46211</v>
@@ -4291,22 +4395,22 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B144" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C144" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D144" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F144" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G144" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H144" s="1">
         <v>46211</v>
@@ -4314,22 +4418,22 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B145" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C145" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D145" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F145" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G145" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H145" s="1">
         <v>46211</v>
@@ -4337,22 +4441,22 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B146" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D146" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F146" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G146" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H146" s="1">
         <v>46211</v>
@@ -4360,13 +4464,13 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B147" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H147" s="1">
         <v>46212</v>
@@ -4374,22 +4478,22 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D148" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H148" s="1">
         <v>46212</v>
@@ -4397,13 +4501,13 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B149" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C149" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H149" s="1">
         <v>46212</v>
@@ -4411,13 +4515,13 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B150" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C150" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H150" s="1">
         <v>46212</v>
@@ -4425,13 +4529,13 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B151" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H151" s="1">
         <v>46212</v>
@@ -4439,13 +4543,13 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B152" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C152" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H152" s="1">
         <v>46212</v>
@@ -4453,13 +4557,13 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B153" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C153" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H153" s="1">
         <v>46212</v>
@@ -4467,22 +4571,22 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B154" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C154" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D154" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H154" s="1">
         <v>46212</v>
@@ -4490,22 +4594,22 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B155" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C155" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D155" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H155" s="1">
         <v>46212</v>
@@ -4513,13 +4617,13 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B156" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C156" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H156" s="1">
         <v>46212</v>
@@ -4527,22 +4631,22 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B157" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C157" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D157" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H157" s="1">
         <v>46212</v>
@@ -4550,22 +4654,22 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B158" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D158" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H158" s="1">
         <v>46212</v>
@@ -4573,22 +4677,22 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B159" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C159" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D159" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="H159" s="1">
         <v>46212</v>
@@ -4596,22 +4700,22 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B160" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C160" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D160" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H160" s="1">
         <v>46212</v>
@@ -4619,22 +4723,22 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B161" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C161" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D161" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H161" s="1">
         <v>46212</v>
@@ -4642,13 +4746,13 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B162" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C162" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H162" s="1">
         <v>46212</v>
@@ -4656,13 +4760,13 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B163" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C163" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H163" s="1">
         <v>46212</v>
@@ -4670,13 +4774,13 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B164" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C164" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H164" s="1">
         <v>46212</v>
@@ -4684,22 +4788,22 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B165" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C165" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D165" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H165" s="1">
         <v>46212</v>
@@ -4707,22 +4811,22 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B166" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C166" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D166" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F166" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G166" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H166" s="1">
         <v>46212</v>
@@ -4730,13 +4834,13 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B167" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C167" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H167" s="1">
         <v>46212</v>
@@ -4744,13 +4848,13 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B168" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C168" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H168" s="1">
         <v>46212</v>
@@ -4758,22 +4862,22 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B169" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C169" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D169" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F169" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G169" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H169" s="1">
         <v>46212</v>
@@ -4781,16 +4885,16 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B170" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C170" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D170" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H170" s="1">
         <v>46212</v>
@@ -4798,22 +4902,22 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B171" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C171" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D171" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F171" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G171" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H171" s="1">
         <v>46212</v>
@@ -4821,22 +4925,22 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B172" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C172" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D172" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H172" s="1">
         <v>46212</v>
@@ -4844,22 +4948,22 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B173" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C173" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D173" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F173" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G173" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H173" s="1">
         <v>46212</v>
@@ -4867,22 +4971,22 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B174" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C174" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D174" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F174" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G174" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H174" s="1">
         <v>46212</v>
@@ -4890,22 +4994,22 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B175" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C175" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D175" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F175" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G175" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H175" s="1">
         <v>46212</v>
@@ -4913,13 +5017,13 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B176" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C176" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H176" s="1">
         <v>46213</v>
@@ -4927,22 +5031,22 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B177" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C177" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D177" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H177" s="1">
         <v>46213</v>
@@ -4950,13 +5054,13 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B178" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C178" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H178" s="1">
         <v>46213</v>
@@ -4964,22 +5068,22 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B179" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C179" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D179" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H179" s="1">
         <v>46213</v>
@@ -4987,13 +5091,13 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B180" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C180" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H180" s="1">
         <v>46213</v>
@@ -5001,13 +5105,13 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B181" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C181" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H181" s="1">
         <v>46213</v>
@@ -5015,13 +5119,13 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B182" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C182" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H182" s="1">
         <v>46213</v>
@@ -5029,22 +5133,22 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B183" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C183" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D183" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H183" s="1">
         <v>46213</v>
@@ -5052,22 +5156,22 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B184" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C184" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D184" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H184" s="1">
         <v>46213</v>
@@ -5075,13 +5179,13 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B185" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C185" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H185" s="1">
         <v>46213</v>
@@ -5089,22 +5193,22 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B186" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D186" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H186" s="1">
         <v>46213</v>
@@ -5112,22 +5216,22 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B187" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C187" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D187" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H187" s="1">
         <v>46213</v>
@@ -5135,22 +5239,22 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B188" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C188" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D188" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H188" s="1">
         <v>46213</v>
@@ -5158,22 +5262,22 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B189" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D189" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H189" s="1">
         <v>46213</v>
@@ -5181,22 +5285,22 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B190" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C190" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D190" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H190" s="1">
         <v>46213</v>
@@ -5204,13 +5308,13 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B191" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C191" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H191" s="1">
         <v>46213</v>
@@ -5218,13 +5322,13 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B192" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C192" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H192" s="1">
         <v>46213</v>
@@ -5232,13 +5336,13 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B193" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C193" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H193" s="1">
         <v>46213</v>
@@ -5246,22 +5350,22 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B194" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C194" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D194" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H194" s="1">
         <v>46213</v>
@@ -5269,22 +5373,22 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B195" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D195" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F195" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G195" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H195" s="1">
         <v>46213</v>
@@ -5292,13 +5396,13 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B196" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C196" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H196" s="1">
         <v>46213</v>
@@ -5306,13 +5410,13 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B197" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C197" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H197" s="1">
         <v>46213</v>
@@ -5320,22 +5424,22 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B198" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C198" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D198" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F198" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G198" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H198" s="1">
         <v>46213</v>
@@ -5343,16 +5447,16 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B199" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C199" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D199" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H199" s="1">
         <v>46213</v>
@@ -5360,22 +5464,22 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B200" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C200" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D200" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F200" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G200" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H200" s="1">
         <v>46213</v>
@@ -5383,22 +5487,22 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C201" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D201" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H201" s="1">
         <v>46213</v>
@@ -5406,22 +5510,22 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B202" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C202" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D202" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F202" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G202" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H202" s="1">
         <v>46213</v>
@@ -5429,22 +5533,22 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B203" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C203" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D203" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F203" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G203" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H203" s="1">
         <v>46213</v>
@@ -5452,22 +5556,22 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B204" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C204" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D204" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F204" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G204" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H204" s="1">
         <v>46213</v>
@@ -5475,13 +5579,13 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B205" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C205" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H205" s="1">
         <v>46216</v>
@@ -5489,22 +5593,22 @@
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B206" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C206" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D206" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H206" s="1">
         <v>46216</v>
@@ -5512,13 +5616,13 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B207" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C207" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H207" s="1">
         <v>46216</v>
@@ -5526,13 +5630,13 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B208" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C208" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H208" s="1">
         <v>46216</v>
@@ -5540,13 +5644,13 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B209" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C209" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H209" s="1">
         <v>46216</v>
@@ -5554,13 +5658,13 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B210" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C210" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H210" s="1">
         <v>46216</v>
@@ -5568,13 +5672,13 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B211" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C211" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H211" s="1">
         <v>46216</v>
@@ -5582,22 +5686,22 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B212" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C212" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D212" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H212" s="1">
         <v>46216</v>
@@ -5605,13 +5709,13 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B213" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C213" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H213" s="1">
         <v>46216</v>
@@ -5619,13 +5723,13 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B214" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C214" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H214" s="1">
         <v>46216</v>
@@ -5633,22 +5737,22 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B215" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C215" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D215" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H215" s="1">
         <v>46216</v>
@@ -5656,22 +5760,22 @@
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B216" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C216" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D216" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H216" s="1">
         <v>46216</v>
@@ -5679,13 +5783,13 @@
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B217" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C217" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H217" s="1">
         <v>46216</v>
@@ -5693,22 +5797,22 @@
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B218" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C218" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D218" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="H218" s="1">
         <v>46216</v>
@@ -5716,13 +5820,13 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B219" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C219" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H219" s="1">
         <v>46216</v>
@@ -5730,13 +5834,13 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B220" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C220" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H220" s="1">
         <v>46216</v>
@@ -5744,22 +5848,22 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B221" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C221" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D221" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H221" s="1">
         <v>46216</v>
@@ -5767,13 +5871,13 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B222" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C222" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H222" s="1">
         <v>46216</v>
@@ -5781,22 +5885,22 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B223" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C223" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D223" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H223" s="1">
         <v>46216</v>
@@ -5804,22 +5908,22 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B224" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C224" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D224" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F224" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G224" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H224" s="1">
         <v>46216</v>
@@ -5827,13 +5931,13 @@
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B225" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C225" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H225" s="1">
         <v>46216</v>
@@ -5841,13 +5945,13 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B226" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C226" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H226" s="1">
         <v>46216</v>
@@ -5855,22 +5959,22 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B227" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C227" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D227" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F227" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G227" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H227" s="1">
         <v>46216</v>
@@ -5878,16 +5982,16 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B228" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C228" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D228" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H228" s="1">
         <v>46216</v>
@@ -5895,22 +5999,22 @@
     </row>
     <row r="229" spans="1:8">
       <c r="A229" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B229" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C229" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D229" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F229" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G229" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H229" s="1">
         <v>46216</v>
@@ -5918,22 +6022,22 @@
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B230" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C230" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D230" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="H230" s="1">
         <v>46216</v>
@@ -5941,22 +6045,22 @@
     </row>
     <row r="231" spans="1:8">
       <c r="A231" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B231" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C231" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D231" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F231" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G231" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H231" s="1">
         <v>46216</v>
@@ -5964,22 +6068,22 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B232" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C232" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D232" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F232" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G232" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H232" s="1">
         <v>46216</v>
@@ -5987,22 +6091,22 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B233" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C233" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D233" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F233" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G233" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H233" s="1">
         <v>46216</v>
@@ -6010,13 +6114,13 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B234" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C234" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H234" s="1">
         <v>46217</v>
@@ -6024,22 +6128,22 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B235" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C235" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D235" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H235" s="1">
         <v>46217</v>
@@ -6047,13 +6151,13 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B236" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C236" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H236" s="1">
         <v>46217</v>
@@ -6061,13 +6165,13 @@
     </row>
     <row r="237" spans="1:8">
       <c r="A237" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B237" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C237" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H237" s="1">
         <v>46217</v>
@@ -6075,13 +6179,13 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B238" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C238" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H238" s="1">
         <v>46217</v>
@@ -6089,13 +6193,13 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B239" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C239" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H239" s="1">
         <v>46217</v>
@@ -6103,13 +6207,13 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B240" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C240" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H240" s="1">
         <v>46217</v>
@@ -6117,22 +6221,22 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B241" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C241" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D241" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H241" s="1">
         <v>46217</v>
@@ -6140,13 +6244,13 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B242" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C242" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H242" s="1">
         <v>46217</v>
@@ -6154,22 +6258,22 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B243" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C243" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D243" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H243" s="1">
         <v>46217</v>
@@ -6177,22 +6281,22 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B244" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C244" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D244" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H244" s="1">
         <v>46217</v>
@@ -6200,13 +6304,13 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B245" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C245" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H245" s="1">
         <v>46217</v>
@@ -6214,13 +6318,13 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B246" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C246" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H246" s="1">
         <v>46217</v>
@@ -6228,22 +6332,22 @@
     </row>
     <row r="247" spans="1:8">
       <c r="A247" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B247" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C247" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D247" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H247" s="1">
         <v>46217</v>
@@ -6251,13 +6355,13 @@
     </row>
     <row r="248" spans="1:8">
       <c r="A248" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B248" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C248" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H248" s="1">
         <v>46217</v>
@@ -6265,13 +6369,13 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B249" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C249" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H249" s="1">
         <v>46217</v>
@@ -6279,22 +6383,22 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B250" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C250" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D250" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H250" s="1">
         <v>46217</v>
@@ -6302,13 +6406,13 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B251" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C251" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H251" s="1">
         <v>46217</v>
@@ -6316,22 +6420,22 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B252" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C252" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D252" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H252" s="1">
         <v>46217</v>
@@ -6339,22 +6443,22 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B253" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C253" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D253" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F253" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G253" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H253" s="1">
         <v>46217</v>
@@ -6362,13 +6466,13 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B254" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C254" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H254" s="1">
         <v>46217</v>
@@ -6376,13 +6480,13 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B255" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C255" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H255" s="1">
         <v>46217</v>
@@ -6390,22 +6494,22 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B256" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C256" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D256" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F256" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G256" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H256" s="1">
         <v>46217</v>
@@ -6413,16 +6517,16 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B257" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C257" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D257" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H257" s="1">
         <v>46217</v>
@@ -6430,22 +6534,22 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B258" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C258" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D258" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F258" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G258" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H258" s="1">
         <v>46217</v>
@@ -6453,22 +6557,22 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B259" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C259" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D259" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="H259" s="1">
         <v>46217</v>
@@ -6476,22 +6580,22 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B260" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C260" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D260" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F260" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G260" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H260" s="1">
         <v>46217</v>
@@ -6499,22 +6603,22 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B261" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C261" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D261" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F261" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G261" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H261" s="1">
         <v>46217</v>
@@ -6522,22 +6626,22 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B262" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C262" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D262" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F262" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G262" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H262" s="1">
         <v>46217</v>
@@ -6545,13 +6649,13 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B263" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C263" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H263" s="1">
         <v>46218</v>
@@ -6559,22 +6663,22 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B264" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C264" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D264" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H264" s="1">
         <v>46218</v>
@@ -6582,13 +6686,13 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B265" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C265" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H265" s="1">
         <v>46218</v>
@@ -6596,13 +6700,13 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B266" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C266" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H266" s="1">
         <v>46218</v>
@@ -6610,13 +6714,13 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B267" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C267" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H267" s="1">
         <v>46218</v>
@@ -6624,13 +6728,13 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B268" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C268" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H268" s="1">
         <v>46218</v>
@@ -6638,13 +6742,13 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B269" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C269" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H269" s="1">
         <v>46218</v>
@@ -6652,22 +6756,22 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B270" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C270" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D270" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H270" s="1">
         <v>46218</v>
@@ -6675,13 +6779,13 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B271" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C271" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H271" s="1">
         <v>46218</v>
@@ -6689,22 +6793,22 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B272" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C272" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D272" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H272" s="1">
         <v>46218</v>
@@ -6712,22 +6816,22 @@
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B273" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C273" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D273" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="H273" s="1">
         <v>46218</v>
@@ -6735,13 +6839,13 @@
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B274" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C274" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H274" s="1">
         <v>46218</v>
@@ -6749,13 +6853,13 @@
     </row>
     <row r="275" spans="1:8">
       <c r="A275" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B275" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C275" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H275" s="1">
         <v>46218</v>
@@ -6763,22 +6867,22 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B276" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C276" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D276" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H276" s="1">
         <v>46218</v>
@@ -6786,13 +6890,13 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B277" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C277" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H277" s="1">
         <v>46218</v>
@@ -6800,22 +6904,22 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B278" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C278" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D278" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H278" s="1">
         <v>46218</v>
@@ -6823,22 +6927,22 @@
     </row>
     <row r="279" spans="1:8">
       <c r="A279" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B279" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C279" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D279" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="H279" s="1">
         <v>46218</v>
@@ -6846,13 +6950,13 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B280" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C280" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H280" s="1">
         <v>46218</v>
@@ -6860,22 +6964,22 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B281" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C281" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D281" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H281" s="1">
         <v>46218</v>
@@ -6883,22 +6987,22 @@
     </row>
     <row r="282" spans="1:8">
       <c r="A282" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B282" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C282" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D282" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F282" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G282" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H282" s="1">
         <v>46218</v>
@@ -6906,13 +7010,13 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B283" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C283" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H283" s="1">
         <v>46218</v>
@@ -6920,13 +7024,13 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B284" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C284" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H284" s="1">
         <v>46218</v>
@@ -6934,22 +7038,22 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B285" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C285" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D285" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F285" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G285" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H285" s="1">
         <v>46218</v>
@@ -6957,16 +7061,16 @@
     </row>
     <row r="286" spans="1:8">
       <c r="A286" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B286" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C286" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D286" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H286" s="1">
         <v>46218</v>
@@ -6974,22 +7078,22 @@
     </row>
     <row r="287" spans="1:8">
       <c r="A287" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B287" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C287" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D287" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F287" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G287" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H287" s="1">
         <v>46218</v>
@@ -6997,22 +7101,22 @@
     </row>
     <row r="288" spans="1:8">
       <c r="A288" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B288" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C288" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D288" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="H288" s="1">
         <v>46218</v>
@@ -7020,22 +7124,22 @@
     </row>
     <row r="289" spans="1:8">
       <c r="A289" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B289" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C289" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D289" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F289" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G289" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H289" s="1">
         <v>46218</v>
@@ -7043,22 +7147,22 @@
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B290" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C290" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D290" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F290" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G290" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H290" s="1">
         <v>46218</v>
@@ -7066,25 +7170,581 @@
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B291" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C291" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D291" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F291" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G291" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H291" s="1">
         <v>46218</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8">
+      <c r="A292" t="s">
+        <v>65</v>
+      </c>
+      <c r="B292" t="s">
+        <v>93</v>
+      </c>
+      <c r="C292" t="s">
+        <v>103</v>
+      </c>
+      <c r="H292" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293" t="s">
+        <v>66</v>
+      </c>
+      <c r="B293" t="s">
+        <v>93</v>
+      </c>
+      <c r="C293" t="s">
+        <v>105</v>
+      </c>
+      <c r="D293" t="s">
+        <v>143</v>
+      </c>
+      <c r="F293" t="s">
+        <v>163</v>
+      </c>
+      <c r="G293" t="s">
+        <v>163</v>
+      </c>
+      <c r="H293" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="A294" t="s">
+        <v>67</v>
+      </c>
+      <c r="B294" t="s">
+        <v>93</v>
+      </c>
+      <c r="C294" t="s">
+        <v>103</v>
+      </c>
+      <c r="H294" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295" t="s">
+        <v>68</v>
+      </c>
+      <c r="B295" t="s">
+        <v>94</v>
+      </c>
+      <c r="C295" t="s">
+        <v>104</v>
+      </c>
+      <c r="D295" t="s">
+        <v>150</v>
+      </c>
+      <c r="F295" t="s">
+        <v>164</v>
+      </c>
+      <c r="G295" t="s">
+        <v>164</v>
+      </c>
+      <c r="H295" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296" t="s">
+        <v>69</v>
+      </c>
+      <c r="B296" t="s">
+        <v>95</v>
+      </c>
+      <c r="C296" t="s">
+        <v>103</v>
+      </c>
+      <c r="H296" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297" t="s">
+        <v>70</v>
+      </c>
+      <c r="B297" t="s">
+        <v>95</v>
+      </c>
+      <c r="C297" t="s">
+        <v>107</v>
+      </c>
+      <c r="H297" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" t="s">
+        <v>71</v>
+      </c>
+      <c r="B298" t="s">
+        <v>95</v>
+      </c>
+      <c r="C298" t="s">
+        <v>106</v>
+      </c>
+      <c r="D298" t="s">
+        <v>151</v>
+      </c>
+      <c r="F298" t="s">
+        <v>165</v>
+      </c>
+      <c r="G298" t="s">
+        <v>165</v>
+      </c>
+      <c r="H298" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299" t="s">
+        <v>72</v>
+      </c>
+      <c r="B299" t="s">
+        <v>95</v>
+      </c>
+      <c r="C299" t="s">
+        <v>105</v>
+      </c>
+      <c r="D299" t="s">
+        <v>113</v>
+      </c>
+      <c r="E299" s="1">
+        <v>46234</v>
+      </c>
+      <c r="G299" t="s">
+        <v>169</v>
+      </c>
+      <c r="H299" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300" t="s">
+        <v>73</v>
+      </c>
+      <c r="B300" t="s">
+        <v>96</v>
+      </c>
+      <c r="C300" t="s">
+        <v>103</v>
+      </c>
+      <c r="H300" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301" t="s">
+        <v>74</v>
+      </c>
+      <c r="B301" t="s">
+        <v>96</v>
+      </c>
+      <c r="C301" t="s">
+        <v>105</v>
+      </c>
+      <c r="D301" t="s">
+        <v>144</v>
+      </c>
+      <c r="E301" s="1">
+        <v>46224</v>
+      </c>
+      <c r="G301" t="s">
+        <v>181</v>
+      </c>
+      <c r="H301" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" t="s">
+        <v>75</v>
+      </c>
+      <c r="B302" t="s">
+        <v>97</v>
+      </c>
+      <c r="C302" t="s">
+        <v>105</v>
+      </c>
+      <c r="D302" t="s">
+        <v>145</v>
+      </c>
+      <c r="E302" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G302" t="s">
+        <v>178</v>
+      </c>
+      <c r="H302" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303" t="s">
+        <v>76</v>
+      </c>
+      <c r="B303" t="s">
+        <v>98</v>
+      </c>
+      <c r="C303" t="s">
+        <v>103</v>
+      </c>
+      <c r="H303" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304" t="s">
+        <v>77</v>
+      </c>
+      <c r="B304" t="s">
+        <v>98</v>
+      </c>
+      <c r="C304" t="s">
+        <v>103</v>
+      </c>
+      <c r="H304" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305" t="s">
+        <v>33</v>
+      </c>
+      <c r="B305" t="s">
+        <v>98</v>
+      </c>
+      <c r="C305" t="s">
+        <v>104</v>
+      </c>
+      <c r="D305" t="s">
+        <v>116</v>
+      </c>
+      <c r="E305" s="1">
+        <v>46237</v>
+      </c>
+      <c r="G305" t="s">
+        <v>182</v>
+      </c>
+      <c r="H305" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306" t="s">
+        <v>78</v>
+      </c>
+      <c r="B306" t="s">
+        <v>99</v>
+      </c>
+      <c r="C306" t="s">
+        <v>103</v>
+      </c>
+      <c r="H306" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8">
+      <c r="A307" t="s">
+        <v>79</v>
+      </c>
+      <c r="B307" t="s">
+        <v>99</v>
+      </c>
+      <c r="C307" t="s">
+        <v>105</v>
+      </c>
+      <c r="D307" t="s">
+        <v>148</v>
+      </c>
+      <c r="E307" s="1">
+        <v>46227</v>
+      </c>
+      <c r="G307" t="s">
+        <v>184</v>
+      </c>
+      <c r="H307" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="A308" t="s">
+        <v>80</v>
+      </c>
+      <c r="B308" t="s">
+        <v>99</v>
+      </c>
+      <c r="C308" t="s">
+        <v>107</v>
+      </c>
+      <c r="H308" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
+      <c r="A309" t="s">
+        <v>81</v>
+      </c>
+      <c r="B309" t="s">
+        <v>99</v>
+      </c>
+      <c r="C309" t="s">
+        <v>106</v>
+      </c>
+      <c r="D309" t="s">
+        <v>152</v>
+      </c>
+      <c r="F309" t="s">
+        <v>163</v>
+      </c>
+      <c r="G309" t="s">
+        <v>163</v>
+      </c>
+      <c r="H309" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8">
+      <c r="A310" t="s">
+        <v>82</v>
+      </c>
+      <c r="B310" t="s">
+        <v>99</v>
+      </c>
+      <c r="C310" t="s">
+        <v>106</v>
+      </c>
+      <c r="D310" t="s">
+        <v>153</v>
+      </c>
+      <c r="F310" t="s">
+        <v>166</v>
+      </c>
+      <c r="G310" t="s">
+        <v>166</v>
+      </c>
+      <c r="H310" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311" t="s">
+        <v>83</v>
+      </c>
+      <c r="B311" t="s">
+        <v>100</v>
+      </c>
+      <c r="C311" t="s">
+        <v>104</v>
+      </c>
+      <c r="D311" t="s">
+        <v>154</v>
+      </c>
+      <c r="H311" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="A312" t="s">
+        <v>84</v>
+      </c>
+      <c r="B312" t="s">
+        <v>101</v>
+      </c>
+      <c r="C312" t="s">
+        <v>107</v>
+      </c>
+      <c r="H312" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8">
+      <c r="A313" t="s">
+        <v>85</v>
+      </c>
+      <c r="B313" t="s">
+        <v>102</v>
+      </c>
+      <c r="C313" t="s">
+        <v>103</v>
+      </c>
+      <c r="H313" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8">
+      <c r="A314" t="s">
+        <v>86</v>
+      </c>
+      <c r="B314" t="s">
+        <v>102</v>
+      </c>
+      <c r="C314" t="s">
+        <v>108</v>
+      </c>
+      <c r="D314" t="s">
+        <v>119</v>
+      </c>
+      <c r="F314" t="s">
+        <v>157</v>
+      </c>
+      <c r="G314" t="s">
+        <v>157</v>
+      </c>
+      <c r="H314" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
+      <c r="A315" t="s">
+        <v>87</v>
+      </c>
+      <c r="B315" t="s">
+        <v>102</v>
+      </c>
+      <c r="C315" t="s">
+        <v>108</v>
+      </c>
+      <c r="D315" t="s">
+        <v>120</v>
+      </c>
+      <c r="H315" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8">
+      <c r="A316" t="s">
+        <v>88</v>
+      </c>
+      <c r="B316" t="s">
+        <v>102</v>
+      </c>
+      <c r="C316" t="s">
+        <v>104</v>
+      </c>
+      <c r="D316" t="s">
+        <v>121</v>
+      </c>
+      <c r="F316" t="s">
+        <v>158</v>
+      </c>
+      <c r="G316" t="s">
+        <v>158</v>
+      </c>
+      <c r="H316" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8">
+      <c r="A317" t="s">
+        <v>89</v>
+      </c>
+      <c r="B317" t="s">
+        <v>102</v>
+      </c>
+      <c r="C317" t="s">
+        <v>106</v>
+      </c>
+      <c r="D317" t="s">
+        <v>142</v>
+      </c>
+      <c r="F317" t="s">
+        <v>167</v>
+      </c>
+      <c r="G317" t="s">
+        <v>167</v>
+      </c>
+      <c r="H317" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="A318" t="s">
+        <v>90</v>
+      </c>
+      <c r="B318" t="s">
+        <v>102</v>
+      </c>
+      <c r="C318" t="s">
+        <v>104</v>
+      </c>
+      <c r="D318" t="s">
+        <v>123</v>
+      </c>
+      <c r="F318" t="s">
+        <v>159</v>
+      </c>
+      <c r="G318" t="s">
+        <v>159</v>
+      </c>
+      <c r="H318" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8">
+      <c r="A319" t="s">
+        <v>91</v>
+      </c>
+      <c r="B319" t="s">
+        <v>102</v>
+      </c>
+      <c r="C319" t="s">
+        <v>104</v>
+      </c>
+      <c r="D319" t="s">
+        <v>124</v>
+      </c>
+      <c r="F319" t="s">
+        <v>159</v>
+      </c>
+      <c r="G319" t="s">
+        <v>159</v>
+      </c>
+      <c r="H319" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
+      <c r="A320" t="s">
+        <v>92</v>
+      </c>
+      <c r="B320" t="s">
+        <v>102</v>
+      </c>
+      <c r="C320" t="s">
+        <v>104</v>
+      </c>
+      <c r="D320" t="s">
+        <v>125</v>
+      </c>
+      <c r="F320" t="s">
+        <v>160</v>
+      </c>
+      <c r="G320" t="s">
+        <v>160</v>
+      </c>
+      <c r="H320" s="1">
+        <v>46220</v>
       </c>
     </row>
   </sheetData>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="196">
   <si>
     <t>data_referencia</t>
   </si>
@@ -107,6 +107,9 @@
     <t>2722, 2743</t>
   </si>
   <si>
+    <t>2709, 2719, 2720, 2722, 2127, 2733, 2737</t>
+  </si>
+  <si>
     <t>2721, 2738, 2739</t>
   </si>
   <si>
@@ -122,6 +125,9 @@
     <t>2721, 2743</t>
   </si>
   <si>
+    <t>2720, 2737</t>
+  </si>
+  <si>
     <t>10070:00</t>
   </si>
   <si>
@@ -158,6 +164,9 @@
     <t>4749:20</t>
   </si>
   <si>
+    <t>4850:26</t>
+  </si>
+  <si>
     <t>Disponibilidade_01_07_2026.txt</t>
   </si>
   <si>
@@ -191,6 +200,9 @@
     <t>Disponibilidade_17_07_2026.txt</t>
   </si>
   <si>
+    <t>Disponibilidade_21_07_2026.txt</t>
+  </si>
+  <si>
     <t>matricula</t>
   </si>
   <si>
@@ -482,6 +494,21 @@
     <t>FCU será enviada hoje ao operador. DPE: 02 DIAS após chegada do item.</t>
   </si>
   <si>
+    <t>SUBSTITUIÇÃO DO PNEU</t>
+  </si>
+  <si>
+    <t>ANV PESQ PANE ALTÍMETRO E TRANSPONDER</t>
+  </si>
+  <si>
+    <t>PANE DE STBY PWR ON</t>
+  </si>
+  <si>
+    <t>PESQUISA DE PANE DE FLAPE</t>
+  </si>
+  <si>
+    <t>Aguardando o envio de uma FCU pela Vee One. DPE: 02 DIAS após chegada do item.</t>
+  </si>
+  <si>
     <t>01 DIA após chegada do item.</t>
   </si>
   <si>
@@ -519,6 +546,12 @@
   </si>
   <si>
     <t>30/09.</t>
+  </si>
+  <si>
+    <t>22/07.</t>
+  </si>
+  <si>
+    <t>21/07.</t>
   </si>
   <si>
     <t>03/07</t>
@@ -579,8 +612,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -596,7 +637,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -604,12 +645,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -905,76 +964,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1020,13 +1079,13 @@
         <v>19</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S2">
         <v>41.81</v>
@@ -1035,11 +1094,11 @@
         <v>24</v>
       </c>
       <c r="U2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1085,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S3">
         <v>42.15</v>
@@ -1100,11 +1159,11 @@
         <v>24</v>
       </c>
       <c r="U3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1150,13 +1209,13 @@
         <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S4">
         <v>42.88</v>
@@ -1165,11 +1224,11 @@
         <v>24</v>
       </c>
       <c r="U4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1215,13 +1274,13 @@
         <v>22</v>
       </c>
       <c r="P5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S5">
         <v>43.44</v>
@@ -1230,11 +1289,11 @@
         <v>24</v>
       </c>
       <c r="U5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1280,13 +1339,13 @@
         <v>22</v>
       </c>
       <c r="P6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S6">
         <v>43.76</v>
@@ -1295,11 +1354,11 @@
         <v>24</v>
       </c>
       <c r="U6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1345,13 +1404,13 @@
         <v>21</v>
       </c>
       <c r="P7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S7">
         <v>44.33</v>
@@ -1360,11 +1419,11 @@
         <v>24</v>
       </c>
       <c r="U7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1410,13 +1469,13 @@
         <v>21</v>
       </c>
       <c r="P8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S8">
         <v>44.51</v>
@@ -1425,11 +1484,11 @@
         <v>24</v>
       </c>
       <c r="U8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1475,13 +1534,13 @@
         <v>21</v>
       </c>
       <c r="P9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S9">
         <v>45.03</v>
@@ -1490,11 +1549,11 @@
         <v>24</v>
       </c>
       <c r="U9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1540,13 +1599,13 @@
         <v>19</v>
       </c>
       <c r="P10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="S10">
         <v>45.89</v>
@@ -1555,11 +1614,11 @@
         <v>24</v>
       </c>
       <c r="U10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1605,13 +1664,13 @@
         <v>20</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S11">
         <v>46.26</v>
@@ -1620,11 +1679,11 @@
         <v>24</v>
       </c>
       <c r="U11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1670,13 +1729,13 @@
         <v>17</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S12">
         <v>47.16</v>
@@ -1685,7 +1744,72 @@
         <v>22</v>
       </c>
       <c r="U12" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="2">
+        <v>46224</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>6</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>15</v>
+      </c>
+      <c r="L13">
+        <v>19</v>
+      </c>
+      <c r="M13">
+        <v>18</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13">
+        <v>17</v>
+      </c>
+      <c r="P13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>37</v>
+      </c>
+      <c r="R13" t="s">
+        <v>49</v>
+      </c>
+      <c r="S13">
+        <v>48.17</v>
+      </c>
+      <c r="T13">
+        <v>22</v>
+      </c>
+      <c r="U13" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1695,6056 +1819,6612 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H349"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H2" s="1">
+        <v>107</v>
+      </c>
+      <c r="H2" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H3" s="1">
+        <v>107</v>
+      </c>
+      <c r="H3" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F4" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="1">
+        <v>164</v>
+      </c>
+      <c r="H4" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="1">
+        <v>107</v>
+      </c>
+      <c r="H5" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" s="1">
+        <v>107</v>
+      </c>
+      <c r="H6" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" s="1">
+        <v>115</v>
+      </c>
+      <c r="E7" s="2">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
-        <v>168</v>
-      </c>
-      <c r="H7" s="1">
+        <v>179</v>
+      </c>
+      <c r="H7" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="1">
+        <v>116</v>
+      </c>
+      <c r="E8" s="2">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H8" s="1">
+        <v>179</v>
+      </c>
+      <c r="H8" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="1">
+        <v>117</v>
+      </c>
+      <c r="E9" s="2">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H9" s="1">
+        <v>180</v>
+      </c>
+      <c r="H9" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="1">
+        <v>118</v>
+      </c>
+      <c r="E10" s="2">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
-        <v>170</v>
-      </c>
-      <c r="H10" s="1">
+        <v>181</v>
+      </c>
+      <c r="H10" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" s="1">
+        <v>107</v>
+      </c>
+      <c r="H11" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" s="1">
+        <v>107</v>
+      </c>
+      <c r="H12" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="1">
+        <v>119</v>
+      </c>
+      <c r="E13" s="2">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
-      </c>
-      <c r="H13" s="1">
+        <v>179</v>
+      </c>
+      <c r="H13" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="1">
+        <v>111</v>
+      </c>
+      <c r="H14" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" s="1">
+        <v>120</v>
+      </c>
+      <c r="E15" s="2">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
-        <v>171</v>
-      </c>
-      <c r="H15" s="1">
+        <v>182</v>
+      </c>
+      <c r="H15" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="1">
+        <v>107</v>
+      </c>
+      <c r="H16" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="1">
+        <v>107</v>
+      </c>
+      <c r="H17" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" s="1">
+        <v>121</v>
+      </c>
+      <c r="E18" s="2">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
-        <v>172</v>
-      </c>
-      <c r="H18" s="1">
+        <v>183</v>
+      </c>
+      <c r="H18" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="H19" s="1">
+        <v>107</v>
+      </c>
+      <c r="H19" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="1">
+        <v>122</v>
+      </c>
+      <c r="E20" s="2">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
-        <v>168</v>
-      </c>
-      <c r="H20" s="1">
+        <v>179</v>
+      </c>
+      <c r="H20" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F21" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
-      </c>
-      <c r="H21" s="1">
+        <v>165</v>
+      </c>
+      <c r="H21" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="1">
+        <v>111</v>
+      </c>
+      <c r="H22" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="1">
+        <v>107</v>
+      </c>
+      <c r="H23" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G24" t="s">
-        <v>157</v>
-      </c>
-      <c r="H24" s="1">
+        <v>166</v>
+      </c>
+      <c r="H24" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="1">
+        <v>124</v>
+      </c>
+      <c r="H25" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G26" t="s">
-        <v>158</v>
-      </c>
-      <c r="H26" s="1">
+        <v>167</v>
+      </c>
+      <c r="H26" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="1">
+        <v>126</v>
+      </c>
+      <c r="E27" s="2">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
-        <v>173</v>
-      </c>
-      <c r="H27" s="1">
+        <v>184</v>
+      </c>
+      <c r="H27" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F28" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G28" t="s">
-        <v>159</v>
-      </c>
-      <c r="H28" s="1">
+        <v>168</v>
+      </c>
+      <c r="H28" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G29" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="1">
+        <v>168</v>
+      </c>
+      <c r="H29" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F30" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G30" t="s">
-        <v>160</v>
-      </c>
-      <c r="H30" s="1">
+        <v>169</v>
+      </c>
+      <c r="H30" s="2">
         <v>46204</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
-      </c>
-      <c r="H31" s="1">
+        <v>107</v>
+      </c>
+      <c r="H31" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
-      </c>
-      <c r="H32" s="1">
+        <v>107</v>
+      </c>
+      <c r="H32" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F33" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G33" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" s="1">
+        <v>170</v>
+      </c>
+      <c r="H33" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
-      </c>
-      <c r="H34" s="1">
+        <v>107</v>
+      </c>
+      <c r="H34" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
-      </c>
-      <c r="H35" s="1">
+        <v>107</v>
+      </c>
+      <c r="H35" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
-      </c>
-      <c r="E36" s="1">
+        <v>115</v>
+      </c>
+      <c r="E36" s="2">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
-        <v>168</v>
-      </c>
-      <c r="H36" s="1">
+        <v>179</v>
+      </c>
+      <c r="H36" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="1">
+        <v>116</v>
+      </c>
+      <c r="E37" s="2">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
-        <v>168</v>
-      </c>
-      <c r="H37" s="1">
+        <v>179</v>
+      </c>
+      <c r="H37" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
-      </c>
-      <c r="E38" s="1">
+        <v>117</v>
+      </c>
+      <c r="E38" s="2">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
-        <v>169</v>
-      </c>
-      <c r="H38" s="1">
+        <v>180</v>
+      </c>
+      <c r="H38" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="1">
+        <v>118</v>
+      </c>
+      <c r="E39" s="2">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
-        <v>170</v>
-      </c>
-      <c r="H39" s="1">
+        <v>181</v>
+      </c>
+      <c r="H39" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
-      </c>
-      <c r="H40" s="1">
+        <v>107</v>
+      </c>
+      <c r="H40" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
-      </c>
-      <c r="H41" s="1">
+        <v>107</v>
+      </c>
+      <c r="H41" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="1">
+        <v>119</v>
+      </c>
+      <c r="E42" s="2">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
-        <v>168</v>
-      </c>
-      <c r="H42" s="1">
+        <v>179</v>
+      </c>
+      <c r="H42" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
-      </c>
-      <c r="H43" s="1">
+        <v>107</v>
+      </c>
+      <c r="H43" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C44" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
-        <v>116</v>
-      </c>
-      <c r="E44" s="1">
+        <v>120</v>
+      </c>
+      <c r="E44" s="2">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
-        <v>171</v>
-      </c>
-      <c r="H44" s="1">
+        <v>182</v>
+      </c>
+      <c r="H44" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
-      </c>
-      <c r="H45" s="1">
+        <v>107</v>
+      </c>
+      <c r="H45" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
-      </c>
-      <c r="H46" s="1">
+        <v>107</v>
+      </c>
+      <c r="H46" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
-      </c>
-      <c r="H47" s="1">
+        <v>111</v>
+      </c>
+      <c r="H47" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
-      </c>
-      <c r="H48" s="1">
+        <v>107</v>
+      </c>
+      <c r="H48" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" s="1">
+        <v>131</v>
+      </c>
+      <c r="E49" s="2">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
-      </c>
-      <c r="H49" s="1">
+        <v>179</v>
+      </c>
+      <c r="H49" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G50" t="s">
-        <v>156</v>
-      </c>
-      <c r="H50" s="1">
+        <v>165</v>
+      </c>
+      <c r="H50" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="H51" s="1">
+        <v>111</v>
+      </c>
+      <c r="H51" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
-      </c>
-      <c r="H52" s="1">
+        <v>107</v>
+      </c>
+      <c r="H52" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C53" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F53" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G53" t="s">
-        <v>157</v>
-      </c>
-      <c r="H53" s="1">
+        <v>166</v>
+      </c>
+      <c r="H53" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
-      </c>
-      <c r="H54" s="1">
+        <v>124</v>
+      </c>
+      <c r="H54" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F55" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G55" t="s">
-        <v>158</v>
-      </c>
-      <c r="H55" s="1">
+        <v>167</v>
+      </c>
+      <c r="H55" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D56" t="s">
-        <v>122</v>
-      </c>
-      <c r="E56" s="1">
+        <v>126</v>
+      </c>
+      <c r="E56" s="2">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
-        <v>173</v>
-      </c>
-      <c r="H56" s="1">
+        <v>184</v>
+      </c>
+      <c r="H56" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D57" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F57" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G57" t="s">
-        <v>159</v>
-      </c>
-      <c r="H57" s="1">
+        <v>168</v>
+      </c>
+      <c r="H57" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D58" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F58" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G58" t="s">
-        <v>159</v>
-      </c>
-      <c r="H58" s="1">
+        <v>168</v>
+      </c>
+      <c r="H58" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B59" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D59" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F59" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G59" t="s">
-        <v>160</v>
-      </c>
-      <c r="H59" s="1">
+        <v>169</v>
+      </c>
+      <c r="H59" s="2">
         <v>46205</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
-      </c>
-      <c r="H60" s="1">
+        <v>107</v>
+      </c>
+      <c r="H60" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
-      </c>
-      <c r="H61" s="1">
+        <v>107</v>
+      </c>
+      <c r="H61" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C62" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
-      </c>
-      <c r="E62" s="1">
+        <v>130</v>
+      </c>
+      <c r="E62" s="2">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
-        <v>174</v>
-      </c>
-      <c r="H62" s="1">
+        <v>185</v>
+      </c>
+      <c r="H62" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
-      </c>
-      <c r="H63" s="1">
+        <v>107</v>
+      </c>
+      <c r="H63" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C64" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D64" t="s">
-        <v>128</v>
-      </c>
-      <c r="E64" s="1">
+        <v>132</v>
+      </c>
+      <c r="E64" s="2">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
-        <v>175</v>
-      </c>
-      <c r="H64" s="1">
+        <v>186</v>
+      </c>
+      <c r="H64" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
-      </c>
-      <c r="H65" s="1">
+        <v>107</v>
+      </c>
+      <c r="H65" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C66" t="s">
-        <v>107</v>
-      </c>
-      <c r="H66" s="1">
+        <v>111</v>
+      </c>
+      <c r="H66" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C67" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
-      </c>
-      <c r="E67" s="1">
+        <v>117</v>
+      </c>
+      <c r="E67" s="2">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
-        <v>169</v>
-      </c>
-      <c r="H67" s="1">
+        <v>180</v>
+      </c>
+      <c r="H67" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D68" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68" s="1">
+        <v>118</v>
+      </c>
+      <c r="E68" s="2">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
-        <v>170</v>
-      </c>
-      <c r="H68" s="1">
+        <v>181</v>
+      </c>
+      <c r="H68" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
-      </c>
-      <c r="H69" s="1">
+        <v>107</v>
+      </c>
+      <c r="H69" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
-      </c>
-      <c r="H70" s="1">
+        <v>107</v>
+      </c>
+      <c r="H70" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D71" t="s">
-        <v>115</v>
-      </c>
-      <c r="E71" s="1">
+        <v>119</v>
+      </c>
+      <c r="E71" s="2">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
-      </c>
-      <c r="H71" s="1">
+        <v>185</v>
+      </c>
+      <c r="H71" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
-      </c>
-      <c r="H72" s="1">
+        <v>107</v>
+      </c>
+      <c r="H72" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C73" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D73" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73" s="1">
+        <v>120</v>
+      </c>
+      <c r="E73" s="2">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
-        <v>171</v>
-      </c>
-      <c r="H73" s="1">
+        <v>182</v>
+      </c>
+      <c r="H73" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B74" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
-      </c>
-      <c r="H74" s="1">
+        <v>107</v>
+      </c>
+      <c r="H74" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
-      </c>
-      <c r="H75" s="1">
+        <v>107</v>
+      </c>
+      <c r="H75" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C76" t="s">
-        <v>103</v>
-      </c>
-      <c r="H76" s="1">
+        <v>107</v>
+      </c>
+      <c r="H76" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
-      </c>
-      <c r="H77" s="1">
+        <v>107</v>
+      </c>
+      <c r="H77" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
-        <v>127</v>
-      </c>
-      <c r="E78" s="1">
+        <v>131</v>
+      </c>
+      <c r="E78" s="2">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
-      </c>
-      <c r="H78" s="1">
+        <v>185</v>
+      </c>
+      <c r="H78" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D79" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F79" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G79" t="s">
-        <v>162</v>
-      </c>
-      <c r="H79" s="1">
+        <v>171</v>
+      </c>
+      <c r="H79" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
-      </c>
-      <c r="H80" s="1">
+        <v>111</v>
+      </c>
+      <c r="H80" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
-      </c>
-      <c r="H81" s="1">
+        <v>107</v>
+      </c>
+      <c r="H81" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C82" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F82" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G82" t="s">
-        <v>157</v>
-      </c>
-      <c r="H82" s="1">
+        <v>166</v>
+      </c>
+      <c r="H82" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B83" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>120</v>
-      </c>
-      <c r="H83" s="1">
+        <v>124</v>
+      </c>
+      <c r="H83" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B84" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C84" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D84" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F84" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G84" t="s">
-        <v>158</v>
-      </c>
-      <c r="H84" s="1">
+        <v>167</v>
+      </c>
+      <c r="H84" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B85" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C85" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D85" t="s">
-        <v>122</v>
-      </c>
-      <c r="E85" s="1">
+        <v>126</v>
+      </c>
+      <c r="E85" s="2">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
-        <v>173</v>
-      </c>
-      <c r="H85" s="1">
+        <v>184</v>
+      </c>
+      <c r="H85" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B86" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C86" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D86" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F86" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G86" t="s">
-        <v>159</v>
-      </c>
-      <c r="H86" s="1">
+        <v>168</v>
+      </c>
+      <c r="H86" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B87" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C87" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D87" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F87" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G87" t="s">
-        <v>159</v>
-      </c>
-      <c r="H87" s="1">
+        <v>168</v>
+      </c>
+      <c r="H87" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C88" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F88" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G88" t="s">
-        <v>160</v>
-      </c>
-      <c r="H88" s="1">
+        <v>169</v>
+      </c>
+      <c r="H88" s="2">
         <v>46209</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
-      </c>
-      <c r="H89" s="1">
+        <v>107</v>
+      </c>
+      <c r="H89" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C90" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D90" t="s">
-        <v>130</v>
-      </c>
-      <c r="E90" s="1">
+        <v>134</v>
+      </c>
+      <c r="E90" s="2">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
-        <v>175</v>
-      </c>
-      <c r="H90" s="1">
+        <v>186</v>
+      </c>
+      <c r="H90" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C91" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D91" t="s">
-        <v>126</v>
-      </c>
-      <c r="E91" s="1">
+        <v>130</v>
+      </c>
+      <c r="E91" s="2">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
-        <v>174</v>
-      </c>
-      <c r="H91" s="1">
+        <v>185</v>
+      </c>
+      <c r="H91" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B92" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>103</v>
-      </c>
-      <c r="H92" s="1">
+        <v>107</v>
+      </c>
+      <c r="H92" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B93" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C93" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D93" t="s">
-        <v>128</v>
-      </c>
-      <c r="E93" s="1">
+        <v>132</v>
+      </c>
+      <c r="E93" s="2">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
-        <v>175</v>
-      </c>
-      <c r="H93" s="1">
+        <v>186</v>
+      </c>
+      <c r="H93" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
-      </c>
-      <c r="H94" s="1">
+        <v>107</v>
+      </c>
+      <c r="H94" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
-      </c>
-      <c r="H95" s="1">
+        <v>111</v>
+      </c>
+      <c r="H95" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C96" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
-      </c>
-      <c r="E96" s="1">
+        <v>117</v>
+      </c>
+      <c r="E96" s="2">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
-        <v>169</v>
-      </c>
-      <c r="H96" s="1">
+        <v>180</v>
+      </c>
+      <c r="H96" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C97" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D97" t="s">
-        <v>114</v>
-      </c>
-      <c r="E97" s="1">
+        <v>118</v>
+      </c>
+      <c r="E97" s="2">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
-        <v>170</v>
-      </c>
-      <c r="H97" s="1">
+        <v>181</v>
+      </c>
+      <c r="H97" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C98" t="s">
-        <v>103</v>
-      </c>
-      <c r="H98" s="1">
+        <v>107</v>
+      </c>
+      <c r="H98" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C99" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D99" t="s">
-        <v>131</v>
-      </c>
-      <c r="E99" s="1">
+        <v>135</v>
+      </c>
+      <c r="E99" s="2">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
-        <v>170</v>
-      </c>
-      <c r="H99" s="1">
+        <v>181</v>
+      </c>
+      <c r="H99" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D100" t="s">
-        <v>115</v>
-      </c>
-      <c r="E100" s="1">
+        <v>119</v>
+      </c>
+      <c r="E100" s="2">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
-        <v>170</v>
-      </c>
-      <c r="H100" s="1">
+        <v>181</v>
+      </c>
+      <c r="H100" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>103</v>
-      </c>
-      <c r="H101" s="1">
+        <v>107</v>
+      </c>
+      <c r="H101" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C102" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D102" t="s">
-        <v>116</v>
-      </c>
-      <c r="E102" s="1">
+        <v>120</v>
+      </c>
+      <c r="E102" s="2">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
-        <v>171</v>
-      </c>
-      <c r="H102" s="1">
+        <v>182</v>
+      </c>
+      <c r="H102" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C103" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D103" t="s">
-        <v>132</v>
-      </c>
-      <c r="E103" s="1">
+        <v>136</v>
+      </c>
+      <c r="E103" s="2">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
-        <v>170</v>
-      </c>
-      <c r="H103" s="1">
+        <v>181</v>
+      </c>
+      <c r="H103" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B104" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C104" t="s">
-        <v>103</v>
-      </c>
-      <c r="H104" s="1">
+        <v>107</v>
+      </c>
+      <c r="H104" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
-      </c>
-      <c r="H105" s="1">
+        <v>107</v>
+      </c>
+      <c r="H105" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B106" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C106" t="s">
-        <v>103</v>
-      </c>
-      <c r="H106" s="1">
+        <v>107</v>
+      </c>
+      <c r="H106" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B107" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D107" t="s">
-        <v>133</v>
-      </c>
-      <c r="E107" s="1">
+        <v>137</v>
+      </c>
+      <c r="E107" s="2">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
-        <v>170</v>
-      </c>
-      <c r="H107" s="1">
+        <v>181</v>
+      </c>
+      <c r="H107" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B108" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C108" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D108" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F108" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G108" t="s">
-        <v>162</v>
-      </c>
-      <c r="H108" s="1">
+        <v>171</v>
+      </c>
+      <c r="H108" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B109" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C109" t="s">
-        <v>107</v>
-      </c>
-      <c r="H109" s="1">
+        <v>111</v>
+      </c>
+      <c r="H109" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B110" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C110" t="s">
-        <v>103</v>
-      </c>
-      <c r="H110" s="1">
+        <v>107</v>
+      </c>
+      <c r="H110" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B111" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C111" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D111" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F111" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G111" t="s">
-        <v>157</v>
-      </c>
-      <c r="H111" s="1">
+        <v>166</v>
+      </c>
+      <c r="H111" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B112" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C112" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D112" t="s">
-        <v>120</v>
-      </c>
-      <c r="H112" s="1">
+        <v>124</v>
+      </c>
+      <c r="H112" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C113" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D113" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F113" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G113" t="s">
-        <v>158</v>
-      </c>
-      <c r="H113" s="1">
+        <v>167</v>
+      </c>
+      <c r="H113" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D114" t="s">
-        <v>122</v>
-      </c>
-      <c r="E114" s="1">
+        <v>126</v>
+      </c>
+      <c r="E114" s="2">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
-        <v>173</v>
-      </c>
-      <c r="H114" s="1">
+        <v>184</v>
+      </c>
+      <c r="H114" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B115" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C115" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D115" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F115" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G115" t="s">
-        <v>159</v>
-      </c>
-      <c r="H115" s="1">
+        <v>168</v>
+      </c>
+      <c r="H115" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B116" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D116" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F116" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G116" t="s">
-        <v>159</v>
-      </c>
-      <c r="H116" s="1">
+        <v>168</v>
+      </c>
+      <c r="H116" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B117" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C117" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D117" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F117" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G117" t="s">
-        <v>160</v>
-      </c>
-      <c r="H117" s="1">
+        <v>169</v>
+      </c>
+      <c r="H117" s="2">
         <v>46210</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B118" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
-      </c>
-      <c r="H118" s="1">
+        <v>107</v>
+      </c>
+      <c r="H118" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B119" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C119" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D119" t="s">
-        <v>130</v>
-      </c>
-      <c r="E119" s="1">
+        <v>134</v>
+      </c>
+      <c r="E119" s="2">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
-        <v>175</v>
-      </c>
-      <c r="H119" s="1">
+        <v>186</v>
+      </c>
+      <c r="H119" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B120" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C120" t="s">
-        <v>107</v>
-      </c>
-      <c r="H120" s="1">
+        <v>111</v>
+      </c>
+      <c r="H120" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B121" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
-        <v>103</v>
-      </c>
-      <c r="H121" s="1">
+        <v>107</v>
+      </c>
+      <c r="H121" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B122" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C122" t="s">
-        <v>107</v>
-      </c>
-      <c r="H122" s="1">
+        <v>111</v>
+      </c>
+      <c r="H122" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B123" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C123" t="s">
-        <v>107</v>
-      </c>
-      <c r="H123" s="1">
+        <v>111</v>
+      </c>
+      <c r="H123" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B124" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C124" t="s">
-        <v>107</v>
-      </c>
-      <c r="H124" s="1">
+        <v>111</v>
+      </c>
+      <c r="H124" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B125" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C125" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D125" t="s">
-        <v>113</v>
-      </c>
-      <c r="E125" s="1">
+        <v>117</v>
+      </c>
+      <c r="E125" s="2">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
-        <v>169</v>
-      </c>
-      <c r="H125" s="1">
+        <v>180</v>
+      </c>
+      <c r="H125" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B126" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C126" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D126" t="s">
-        <v>114</v>
-      </c>
-      <c r="E126" s="1">
+        <v>118</v>
+      </c>
+      <c r="E126" s="2">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
-        <v>170</v>
-      </c>
-      <c r="H126" s="1">
+        <v>181</v>
+      </c>
+      <c r="H126" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B127" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
-      </c>
-      <c r="H127" s="1">
+        <v>107</v>
+      </c>
+      <c r="H127" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B128" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C128" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D128" t="s">
-        <v>131</v>
-      </c>
-      <c r="E128" s="1">
+        <v>135</v>
+      </c>
+      <c r="E128" s="2">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
-        <v>170</v>
-      </c>
-      <c r="H128" s="1">
+        <v>181</v>
+      </c>
+      <c r="H128" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B129" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C129" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D129" t="s">
-        <v>115</v>
-      </c>
-      <c r="E129" s="1">
+        <v>119</v>
+      </c>
+      <c r="E129" s="2">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
-        <v>170</v>
-      </c>
-      <c r="H129" s="1">
+        <v>181</v>
+      </c>
+      <c r="H129" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B130" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
-      </c>
-      <c r="H130" s="1">
+        <v>107</v>
+      </c>
+      <c r="H130" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B131" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C131" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D131" t="s">
-        <v>116</v>
-      </c>
-      <c r="E131" s="1">
+        <v>120</v>
+      </c>
+      <c r="E131" s="2">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
-        <v>171</v>
-      </c>
-      <c r="H131" s="1">
+        <v>182</v>
+      </c>
+      <c r="H131" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B132" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C132" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D132" t="s">
-        <v>132</v>
-      </c>
-      <c r="E132" s="1">
+        <v>136</v>
+      </c>
+      <c r="E132" s="2">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
-        <v>170</v>
-      </c>
-      <c r="H132" s="1">
+        <v>181</v>
+      </c>
+      <c r="H132" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B133" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
-      </c>
-      <c r="H133" s="1">
+        <v>107</v>
+      </c>
+      <c r="H133" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B134" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C134" t="s">
-        <v>103</v>
-      </c>
-      <c r="H134" s="1">
+        <v>107</v>
+      </c>
+      <c r="H134" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B135" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C135" t="s">
-        <v>103</v>
-      </c>
-      <c r="H135" s="1">
+        <v>107</v>
+      </c>
+      <c r="H135" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B136" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C136" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D136" t="s">
-        <v>134</v>
-      </c>
-      <c r="E136" s="1">
+        <v>138</v>
+      </c>
+      <c r="E136" s="2">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
-        <v>170</v>
-      </c>
-      <c r="H136" s="1">
+        <v>181</v>
+      </c>
+      <c r="H136" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B137" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C137" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D137" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F137" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G137" t="s">
-        <v>162</v>
-      </c>
-      <c r="H137" s="1">
+        <v>171</v>
+      </c>
+      <c r="H137" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B138" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C138" t="s">
-        <v>107</v>
-      </c>
-      <c r="H138" s="1">
+        <v>111</v>
+      </c>
+      <c r="H138" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B139" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
-      </c>
-      <c r="H139" s="1">
+        <v>107</v>
+      </c>
+      <c r="H139" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B140" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C140" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D140" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F140" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G140" t="s">
-        <v>157</v>
-      </c>
-      <c r="H140" s="1">
+        <v>166</v>
+      </c>
+      <c r="H140" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B141" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C141" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D141" t="s">
-        <v>120</v>
-      </c>
-      <c r="H141" s="1">
+        <v>124</v>
+      </c>
+      <c r="H141" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B142" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C142" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D142" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F142" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G142" t="s">
-        <v>158</v>
-      </c>
-      <c r="H142" s="1">
+        <v>167</v>
+      </c>
+      <c r="H142" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B143" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C143" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D143" t="s">
-        <v>122</v>
-      </c>
-      <c r="E143" s="1">
+        <v>126</v>
+      </c>
+      <c r="E143" s="2">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
-        <v>173</v>
-      </c>
-      <c r="H143" s="1">
+        <v>184</v>
+      </c>
+      <c r="H143" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B144" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C144" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D144" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F144" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G144" t="s">
-        <v>159</v>
-      </c>
-      <c r="H144" s="1">
+        <v>168</v>
+      </c>
+      <c r="H144" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B145" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C145" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D145" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F145" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G145" t="s">
-        <v>159</v>
-      </c>
-      <c r="H145" s="1">
+        <v>168</v>
+      </c>
+      <c r="H145" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B146" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C146" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D146" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F146" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G146" t="s">
-        <v>160</v>
-      </c>
-      <c r="H146" s="1">
+        <v>169</v>
+      </c>
+      <c r="H146" s="2">
         <v>46211</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B147" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C147" t="s">
-        <v>103</v>
-      </c>
-      <c r="H147" s="1">
+        <v>107</v>
+      </c>
+      <c r="H147" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B148" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C148" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D148" t="s">
-        <v>130</v>
-      </c>
-      <c r="E148" s="1">
+        <v>134</v>
+      </c>
+      <c r="E148" s="2">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
-        <v>175</v>
-      </c>
-      <c r="H148" s="1">
+        <v>186</v>
+      </c>
+      <c r="H148" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B149" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C149" t="s">
-        <v>107</v>
-      </c>
-      <c r="H149" s="1">
+        <v>111</v>
+      </c>
+      <c r="H149" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B150" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C150" t="s">
-        <v>103</v>
-      </c>
-      <c r="H150" s="1">
+        <v>107</v>
+      </c>
+      <c r="H150" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B151" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C151" t="s">
-        <v>103</v>
-      </c>
-      <c r="H151" s="1">
+        <v>107</v>
+      </c>
+      <c r="H151" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B152" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C152" t="s">
-        <v>107</v>
-      </c>
-      <c r="H152" s="1">
+        <v>111</v>
+      </c>
+      <c r="H152" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B153" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C153" t="s">
-        <v>107</v>
-      </c>
-      <c r="H153" s="1">
+        <v>111</v>
+      </c>
+      <c r="H153" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B154" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C154" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D154" t="s">
-        <v>113</v>
-      </c>
-      <c r="E154" s="1">
+        <v>117</v>
+      </c>
+      <c r="E154" s="2">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
-        <v>169</v>
-      </c>
-      <c r="H154" s="1">
+        <v>180</v>
+      </c>
+      <c r="H154" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B155" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C155" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D155" t="s">
-        <v>114</v>
-      </c>
-      <c r="E155" s="1">
+        <v>118</v>
+      </c>
+      <c r="E155" s="2">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
-        <v>170</v>
-      </c>
-      <c r="H155" s="1">
+        <v>181</v>
+      </c>
+      <c r="H155" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B156" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C156" t="s">
-        <v>103</v>
-      </c>
-      <c r="H156" s="1">
+        <v>107</v>
+      </c>
+      <c r="H156" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B157" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C157" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D157" t="s">
-        <v>131</v>
-      </c>
-      <c r="E157" s="1">
+        <v>135</v>
+      </c>
+      <c r="E157" s="2">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
-        <v>170</v>
-      </c>
-      <c r="H157" s="1">
+        <v>181</v>
+      </c>
+      <c r="H157" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B158" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C158" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D158" t="s">
-        <v>115</v>
-      </c>
-      <c r="E158" s="1">
+        <v>119</v>
+      </c>
+      <c r="E158" s="2">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
-        <v>170</v>
-      </c>
-      <c r="H158" s="1">
+        <v>181</v>
+      </c>
+      <c r="H158" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B159" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D159" t="s">
-        <v>135</v>
-      </c>
-      <c r="E159" s="1">
+        <v>139</v>
+      </c>
+      <c r="E159" s="2">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
-        <v>176</v>
-      </c>
-      <c r="H159" s="1">
+        <v>187</v>
+      </c>
+      <c r="H159" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B160" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C160" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D160" t="s">
-        <v>116</v>
-      </c>
-      <c r="E160" s="1">
+        <v>120</v>
+      </c>
+      <c r="E160" s="2">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
-        <v>171</v>
-      </c>
-      <c r="H160" s="1">
+        <v>182</v>
+      </c>
+      <c r="H160" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B161" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C161" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D161" t="s">
-        <v>132</v>
-      </c>
-      <c r="E161" s="1">
+        <v>136</v>
+      </c>
+      <c r="E161" s="2">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
-        <v>170</v>
-      </c>
-      <c r="H161" s="1">
+        <v>181</v>
+      </c>
+      <c r="H161" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B162" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C162" t="s">
-        <v>103</v>
-      </c>
-      <c r="H162" s="1">
+        <v>107</v>
+      </c>
+      <c r="H162" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B163" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C163" t="s">
-        <v>103</v>
-      </c>
-      <c r="H163" s="1">
+        <v>107</v>
+      </c>
+      <c r="H163" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B164" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C164" t="s">
-        <v>103</v>
-      </c>
-      <c r="H164" s="1">
+        <v>107</v>
+      </c>
+      <c r="H164" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B165" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C165" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D165" t="s">
-        <v>134</v>
-      </c>
-      <c r="E165" s="1">
+        <v>138</v>
+      </c>
+      <c r="E165" s="2">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
-        <v>170</v>
-      </c>
-      <c r="H165" s="1">
+        <v>181</v>
+      </c>
+      <c r="H165" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B166" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C166" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D166" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F166" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G166" t="s">
-        <v>162</v>
-      </c>
-      <c r="H166" s="1">
+        <v>171</v>
+      </c>
+      <c r="H166" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B167" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C167" t="s">
-        <v>107</v>
-      </c>
-      <c r="H167" s="1">
+        <v>111</v>
+      </c>
+      <c r="H167" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B168" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C168" t="s">
-        <v>103</v>
-      </c>
-      <c r="H168" s="1">
+        <v>107</v>
+      </c>
+      <c r="H168" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B169" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C169" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D169" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F169" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G169" t="s">
-        <v>157</v>
-      </c>
-      <c r="H169" s="1">
+        <v>166</v>
+      </c>
+      <c r="H169" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B170" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C170" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D170" t="s">
-        <v>120</v>
-      </c>
-      <c r="H170" s="1">
+        <v>124</v>
+      </c>
+      <c r="H170" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B171" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C171" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D171" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F171" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G171" t="s">
-        <v>158</v>
-      </c>
-      <c r="H171" s="1">
+        <v>167</v>
+      </c>
+      <c r="H171" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B172" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C172" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D172" t="s">
-        <v>122</v>
-      </c>
-      <c r="E172" s="1">
+        <v>126</v>
+      </c>
+      <c r="E172" s="2">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
-        <v>173</v>
-      </c>
-      <c r="H172" s="1">
+        <v>184</v>
+      </c>
+      <c r="H172" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B173" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C173" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D173" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F173" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G173" t="s">
-        <v>159</v>
-      </c>
-      <c r="H173" s="1">
+        <v>168</v>
+      </c>
+      <c r="H173" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B174" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C174" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D174" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F174" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G174" t="s">
-        <v>159</v>
-      </c>
-      <c r="H174" s="1">
+        <v>168</v>
+      </c>
+      <c r="H174" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B175" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C175" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D175" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F175" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G175" t="s">
-        <v>160</v>
-      </c>
-      <c r="H175" s="1">
+        <v>169</v>
+      </c>
+      <c r="H175" s="2">
         <v>46212</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B176" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C176" t="s">
-        <v>103</v>
-      </c>
-      <c r="H176" s="1">
+        <v>107</v>
+      </c>
+      <c r="H176" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B177" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C177" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D177" t="s">
-        <v>136</v>
-      </c>
-      <c r="E177" s="1">
+        <v>140</v>
+      </c>
+      <c r="E177" s="2">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
-        <v>175</v>
-      </c>
-      <c r="H177" s="1">
+        <v>186</v>
+      </c>
+      <c r="H177" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B178" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C178" t="s">
-        <v>103</v>
-      </c>
-      <c r="H178" s="1">
+        <v>107</v>
+      </c>
+      <c r="H178" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B179" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C179" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D179" t="s">
-        <v>137</v>
-      </c>
-      <c r="E179" s="1">
+        <v>141</v>
+      </c>
+      <c r="E179" s="2">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
-        <v>171</v>
-      </c>
-      <c r="H179" s="1">
+        <v>182</v>
+      </c>
+      <c r="H179" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B180" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C180" t="s">
-        <v>103</v>
-      </c>
-      <c r="H180" s="1">
+        <v>107</v>
+      </c>
+      <c r="H180" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B181" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C181" t="s">
-        <v>107</v>
-      </c>
-      <c r="H181" s="1">
+        <v>111</v>
+      </c>
+      <c r="H181" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B182" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C182" t="s">
-        <v>107</v>
-      </c>
-      <c r="H182" s="1">
+        <v>111</v>
+      </c>
+      <c r="H182" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B183" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C183" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D183" t="s">
-        <v>113</v>
-      </c>
-      <c r="E183" s="1">
+        <v>117</v>
+      </c>
+      <c r="E183" s="2">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
-        <v>169</v>
-      </c>
-      <c r="H183" s="1">
+        <v>180</v>
+      </c>
+      <c r="H183" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B184" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C184" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D184" t="s">
-        <v>114</v>
-      </c>
-      <c r="E184" s="1">
+        <v>118</v>
+      </c>
+      <c r="E184" s="2">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
-        <v>170</v>
-      </c>
-      <c r="H184" s="1">
+        <v>181</v>
+      </c>
+      <c r="H184" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B185" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C185" t="s">
-        <v>103</v>
-      </c>
-      <c r="H185" s="1">
+        <v>107</v>
+      </c>
+      <c r="H185" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B186" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C186" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D186" t="s">
-        <v>131</v>
-      </c>
-      <c r="E186" s="1">
+        <v>135</v>
+      </c>
+      <c r="E186" s="2">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
-        <v>170</v>
-      </c>
-      <c r="H186" s="1">
+        <v>181</v>
+      </c>
+      <c r="H186" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B187" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C187" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D187" t="s">
-        <v>138</v>
-      </c>
-      <c r="E187" s="1">
+        <v>142</v>
+      </c>
+      <c r="E187" s="2">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
-        <v>170</v>
-      </c>
-      <c r="H187" s="1">
+        <v>181</v>
+      </c>
+      <c r="H187" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B188" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C188" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D188" t="s">
-        <v>139</v>
-      </c>
-      <c r="E188" s="1">
+        <v>143</v>
+      </c>
+      <c r="E188" s="2">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
-        <v>170</v>
-      </c>
-      <c r="H188" s="1">
+        <v>181</v>
+      </c>
+      <c r="H188" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B189" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C189" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D189" t="s">
-        <v>116</v>
-      </c>
-      <c r="E189" s="1">
+        <v>120</v>
+      </c>
+      <c r="E189" s="2">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
-        <v>171</v>
-      </c>
-      <c r="H189" s="1">
+        <v>182</v>
+      </c>
+      <c r="H189" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B190" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C190" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D190" t="s">
-        <v>132</v>
-      </c>
-      <c r="E190" s="1">
+        <v>136</v>
+      </c>
+      <c r="E190" s="2">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
-        <v>170</v>
-      </c>
-      <c r="H190" s="1">
+        <v>181</v>
+      </c>
+      <c r="H190" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B191" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C191" t="s">
-        <v>103</v>
-      </c>
-      <c r="H191" s="1">
+        <v>107</v>
+      </c>
+      <c r="H191" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B192" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C192" t="s">
-        <v>103</v>
-      </c>
-      <c r="H192" s="1">
+        <v>107</v>
+      </c>
+      <c r="H192" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C193" t="s">
-        <v>103</v>
-      </c>
-      <c r="H193" s="1">
+        <v>107</v>
+      </c>
+      <c r="H193" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C194" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D194" t="s">
-        <v>134</v>
-      </c>
-      <c r="E194" s="1">
+        <v>138</v>
+      </c>
+      <c r="E194" s="2">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
-        <v>177</v>
-      </c>
-      <c r="H194" s="1">
+        <v>188</v>
+      </c>
+      <c r="H194" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C195" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D195" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F195" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G195" t="s">
-        <v>162</v>
-      </c>
-      <c r="H195" s="1">
+        <v>171</v>
+      </c>
+      <c r="H195" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B196" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C196" t="s">
-        <v>107</v>
-      </c>
-      <c r="H196" s="1">
+        <v>111</v>
+      </c>
+      <c r="H196" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B197" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C197" t="s">
-        <v>103</v>
-      </c>
-      <c r="H197" s="1">
+        <v>107</v>
+      </c>
+      <c r="H197" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B198" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C198" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D198" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F198" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G198" t="s">
-        <v>157</v>
-      </c>
-      <c r="H198" s="1">
+        <v>166</v>
+      </c>
+      <c r="H198" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B199" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C199" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D199" t="s">
-        <v>120</v>
-      </c>
-      <c r="H199" s="1">
+        <v>124</v>
+      </c>
+      <c r="H199" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B200" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C200" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D200" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F200" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G200" t="s">
-        <v>158</v>
-      </c>
-      <c r="H200" s="1">
+        <v>167</v>
+      </c>
+      <c r="H200" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B201" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C201" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D201" t="s">
-        <v>122</v>
-      </c>
-      <c r="E201" s="1">
+        <v>126</v>
+      </c>
+      <c r="E201" s="2">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
-        <v>173</v>
-      </c>
-      <c r="H201" s="1">
+        <v>184</v>
+      </c>
+      <c r="H201" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B202" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C202" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D202" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F202" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G202" t="s">
-        <v>159</v>
-      </c>
-      <c r="H202" s="1">
+        <v>168</v>
+      </c>
+      <c r="H202" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B203" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C203" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D203" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F203" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G203" t="s">
-        <v>159</v>
-      </c>
-      <c r="H203" s="1">
+        <v>168</v>
+      </c>
+      <c r="H203" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B204" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C204" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D204" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F204" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G204" t="s">
-        <v>160</v>
-      </c>
-      <c r="H204" s="1">
+        <v>169</v>
+      </c>
+      <c r="H204" s="2">
         <v>46213</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B205" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C205" t="s">
-        <v>103</v>
-      </c>
-      <c r="H205" s="1">
+        <v>107</v>
+      </c>
+      <c r="H205" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B206" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C206" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D206" t="s">
-        <v>136</v>
-      </c>
-      <c r="E206" s="1">
+        <v>140</v>
+      </c>
+      <c r="E206" s="2">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
-        <v>175</v>
-      </c>
-      <c r="H206" s="1">
+        <v>186</v>
+      </c>
+      <c r="H206" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B207" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C207" t="s">
-        <v>103</v>
-      </c>
-      <c r="H207" s="1">
+        <v>107</v>
+      </c>
+      <c r="H207" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B208" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C208" t="s">
-        <v>107</v>
-      </c>
-      <c r="H208" s="1">
+        <v>111</v>
+      </c>
+      <c r="H208" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B209" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C209" t="s">
-        <v>103</v>
-      </c>
-      <c r="H209" s="1">
+        <v>107</v>
+      </c>
+      <c r="H209" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B210" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C210" t="s">
-        <v>107</v>
-      </c>
-      <c r="H210" s="1">
+        <v>111</v>
+      </c>
+      <c r="H210" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B211" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C211" t="s">
-        <v>107</v>
-      </c>
-      <c r="H211" s="1">
+        <v>111</v>
+      </c>
+      <c r="H211" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B212" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C212" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D212" t="s">
-        <v>113</v>
-      </c>
-      <c r="E212" s="1">
+        <v>117</v>
+      </c>
+      <c r="E212" s="2">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
-        <v>169</v>
-      </c>
-      <c r="H212" s="1">
+        <v>180</v>
+      </c>
+      <c r="H212" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B213" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C213" t="s">
-        <v>107</v>
-      </c>
-      <c r="H213" s="1">
+        <v>111</v>
+      </c>
+      <c r="H213" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B214" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C214" t="s">
-        <v>103</v>
-      </c>
-      <c r="H214" s="1">
+        <v>107</v>
+      </c>
+      <c r="H214" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B215" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C215" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D215" t="s">
-        <v>131</v>
-      </c>
-      <c r="E215" s="1">
+        <v>135</v>
+      </c>
+      <c r="E215" s="2">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
-        <v>178</v>
-      </c>
-      <c r="H215" s="1">
+        <v>189</v>
+      </c>
+      <c r="H215" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B216" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C216" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D216" t="s">
-        <v>138</v>
-      </c>
-      <c r="E216" s="1">
+        <v>142</v>
+      </c>
+      <c r="E216" s="2">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
-        <v>171</v>
-      </c>
-      <c r="H216" s="1">
+        <v>182</v>
+      </c>
+      <c r="H216" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B217" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C217" t="s">
-        <v>103</v>
-      </c>
-      <c r="H217" s="1">
+        <v>107</v>
+      </c>
+      <c r="H217" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B218" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C218" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D218" t="s">
-        <v>116</v>
-      </c>
-      <c r="E218" s="1">
+        <v>120</v>
+      </c>
+      <c r="E218" s="2">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
-        <v>171</v>
-      </c>
-      <c r="H218" s="1">
+        <v>182</v>
+      </c>
+      <c r="H218" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B219" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C219" t="s">
-        <v>103</v>
-      </c>
-      <c r="H219" s="1">
+        <v>107</v>
+      </c>
+      <c r="H219" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B220" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C220" t="s">
-        <v>103</v>
-      </c>
-      <c r="H220" s="1">
+        <v>107</v>
+      </c>
+      <c r="H220" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B221" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C221" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D221" t="s">
-        <v>140</v>
-      </c>
-      <c r="E221" s="1">
+        <v>144</v>
+      </c>
+      <c r="E221" s="2">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
-        <v>175</v>
-      </c>
-      <c r="H221" s="1">
+        <v>186</v>
+      </c>
+      <c r="H221" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B222" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C222" t="s">
-        <v>103</v>
-      </c>
-      <c r="H222" s="1">
+        <v>107</v>
+      </c>
+      <c r="H222" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B223" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C223" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D223" t="s">
-        <v>141</v>
-      </c>
-      <c r="E223" s="1">
+        <v>145</v>
+      </c>
+      <c r="E223" s="2">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
-        <v>179</v>
-      </c>
-      <c r="H223" s="1">
+        <v>190</v>
+      </c>
+      <c r="H223" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B224" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C224" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D224" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F224" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G224" t="s">
-        <v>162</v>
-      </c>
-      <c r="H224" s="1">
+        <v>171</v>
+      </c>
+      <c r="H224" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B225" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C225" t="s">
-        <v>107</v>
-      </c>
-      <c r="H225" s="1">
+        <v>111</v>
+      </c>
+      <c r="H225" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B226" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C226" t="s">
-        <v>103</v>
-      </c>
-      <c r="H226" s="1">
+        <v>107</v>
+      </c>
+      <c r="H226" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B227" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C227" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D227" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F227" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G227" t="s">
-        <v>157</v>
-      </c>
-      <c r="H227" s="1">
+        <v>166</v>
+      </c>
+      <c r="H227" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B228" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C228" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D228" t="s">
-        <v>120</v>
-      </c>
-      <c r="H228" s="1">
+        <v>124</v>
+      </c>
+      <c r="H228" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B229" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C229" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D229" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F229" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G229" t="s">
-        <v>158</v>
-      </c>
-      <c r="H229" s="1">
+        <v>167</v>
+      </c>
+      <c r="H229" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B230" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C230" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D230" t="s">
-        <v>142</v>
-      </c>
-      <c r="E230" s="1">
+        <v>146</v>
+      </c>
+      <c r="E230" s="2">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
-        <v>180</v>
-      </c>
-      <c r="H230" s="1">
+        <v>191</v>
+      </c>
+      <c r="H230" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B231" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C231" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D231" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F231" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G231" t="s">
-        <v>159</v>
-      </c>
-      <c r="H231" s="1">
+        <v>168</v>
+      </c>
+      <c r="H231" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B232" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C232" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D232" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F232" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G232" t="s">
-        <v>159</v>
-      </c>
-      <c r="H232" s="1">
+        <v>168</v>
+      </c>
+      <c r="H232" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B233" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C233" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D233" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F233" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G233" t="s">
-        <v>160</v>
-      </c>
-      <c r="H233" s="1">
+        <v>169</v>
+      </c>
+      <c r="H233" s="2">
         <v>46216</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B234" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C234" t="s">
-        <v>103</v>
-      </c>
-      <c r="H234" s="1">
+        <v>107</v>
+      </c>
+      <c r="H234" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B235" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C235" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D235" t="s">
-        <v>143</v>
-      </c>
-      <c r="E235" s="1">
+        <v>147</v>
+      </c>
+      <c r="E235" s="2">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
-        <v>175</v>
-      </c>
-      <c r="H235" s="1">
+        <v>186</v>
+      </c>
+      <c r="H235" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B236" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C236" t="s">
-        <v>103</v>
-      </c>
-      <c r="H236" s="1">
+        <v>107</v>
+      </c>
+      <c r="H236" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B237" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C237" t="s">
-        <v>107</v>
-      </c>
-      <c r="H237" s="1">
+        <v>111</v>
+      </c>
+      <c r="H237" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B238" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C238" t="s">
-        <v>103</v>
-      </c>
-      <c r="H238" s="1">
+        <v>107</v>
+      </c>
+      <c r="H238" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B239" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C239" t="s">
-        <v>107</v>
-      </c>
-      <c r="H239" s="1">
+        <v>111</v>
+      </c>
+      <c r="H239" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B240" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C240" t="s">
-        <v>107</v>
-      </c>
-      <c r="H240" s="1">
+        <v>111</v>
+      </c>
+      <c r="H240" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B241" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C241" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D241" t="s">
-        <v>113</v>
-      </c>
-      <c r="E241" s="1">
+        <v>117</v>
+      </c>
+      <c r="E241" s="2">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
-        <v>169</v>
-      </c>
-      <c r="H241" s="1">
+        <v>180</v>
+      </c>
+      <c r="H241" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B242" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C242" t="s">
-        <v>107</v>
-      </c>
-      <c r="H242" s="1">
+        <v>111</v>
+      </c>
+      <c r="H242" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B243" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C243" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D243" t="s">
-        <v>144</v>
-      </c>
-      <c r="E243" s="1">
+        <v>148</v>
+      </c>
+      <c r="E243" s="2">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
-        <v>181</v>
-      </c>
-      <c r="H243" s="1">
+        <v>192</v>
+      </c>
+      <c r="H243" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B244" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C244" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D244" t="s">
-        <v>145</v>
-      </c>
-      <c r="E244" s="1">
+        <v>149</v>
+      </c>
+      <c r="E244" s="2">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
-        <v>178</v>
-      </c>
-      <c r="H244" s="1">
+        <v>189</v>
+      </c>
+      <c r="H244" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B245" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C245" t="s">
-        <v>107</v>
-      </c>
-      <c r="H245" s="1">
+        <v>111</v>
+      </c>
+      <c r="H245" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B246" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C246" t="s">
-        <v>103</v>
-      </c>
-      <c r="H246" s="1">
+        <v>107</v>
+      </c>
+      <c r="H246" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B247" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C247" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D247" t="s">
-        <v>116</v>
-      </c>
-      <c r="E247" s="1">
+        <v>120</v>
+      </c>
+      <c r="E247" s="2">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
-        <v>182</v>
-      </c>
-      <c r="H247" s="1">
+        <v>193</v>
+      </c>
+      <c r="H247" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B248" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C248" t="s">
-        <v>103</v>
-      </c>
-      <c r="H248" s="1">
+        <v>107</v>
+      </c>
+      <c r="H248" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B249" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C249" t="s">
-        <v>103</v>
-      </c>
-      <c r="H249" s="1">
+        <v>107</v>
+      </c>
+      <c r="H249" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B250" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C250" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D250" t="s">
-        <v>146</v>
-      </c>
-      <c r="E250" s="1">
+        <v>150</v>
+      </c>
+      <c r="E250" s="2">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
-        <v>177</v>
-      </c>
-      <c r="H250" s="1">
+        <v>188</v>
+      </c>
+      <c r="H250" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B251" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C251" t="s">
-        <v>103</v>
-      </c>
-      <c r="H251" s="1">
+        <v>107</v>
+      </c>
+      <c r="H251" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B252" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C252" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D252" t="s">
-        <v>147</v>
-      </c>
-      <c r="E252" s="1">
+        <v>151</v>
+      </c>
+      <c r="E252" s="2">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
-        <v>179</v>
-      </c>
-      <c r="H252" s="1">
+        <v>190</v>
+      </c>
+      <c r="H252" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B253" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C253" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D253" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F253" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G253" t="s">
-        <v>162</v>
-      </c>
-      <c r="H253" s="1">
+        <v>171</v>
+      </c>
+      <c r="H253" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B254" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C254" t="s">
-        <v>107</v>
-      </c>
-      <c r="H254" s="1">
+        <v>111</v>
+      </c>
+      <c r="H254" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B255" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C255" t="s">
-        <v>103</v>
-      </c>
-      <c r="H255" s="1">
+        <v>107</v>
+      </c>
+      <c r="H255" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B256" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C256" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D256" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F256" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G256" t="s">
-        <v>157</v>
-      </c>
-      <c r="H256" s="1">
+        <v>166</v>
+      </c>
+      <c r="H256" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B257" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C257" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D257" t="s">
-        <v>120</v>
-      </c>
-      <c r="H257" s="1">
+        <v>124</v>
+      </c>
+      <c r="H257" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B258" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C258" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D258" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F258" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G258" t="s">
-        <v>158</v>
-      </c>
-      <c r="H258" s="1">
+        <v>167</v>
+      </c>
+      <c r="H258" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="A259" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B259" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C259" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D259" t="s">
-        <v>142</v>
-      </c>
-      <c r="E259" s="1">
+        <v>146</v>
+      </c>
+      <c r="E259" s="2">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
-        <v>180</v>
-      </c>
-      <c r="H259" s="1">
+        <v>191</v>
+      </c>
+      <c r="H259" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B260" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C260" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D260" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F260" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G260" t="s">
-        <v>159</v>
-      </c>
-      <c r="H260" s="1">
+        <v>168</v>
+      </c>
+      <c r="H260" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B261" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C261" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D261" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F261" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G261" t="s">
-        <v>159</v>
-      </c>
-      <c r="H261" s="1">
+        <v>168</v>
+      </c>
+      <c r="H261" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B262" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C262" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D262" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F262" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G262" t="s">
-        <v>160</v>
-      </c>
-      <c r="H262" s="1">
+        <v>169</v>
+      </c>
+      <c r="H262" s="2">
         <v>46217</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B263" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C263" t="s">
-        <v>103</v>
-      </c>
-      <c r="H263" s="1">
+        <v>107</v>
+      </c>
+      <c r="H263" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B264" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C264" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D264" t="s">
-        <v>143</v>
-      </c>
-      <c r="E264" s="1">
+        <v>147</v>
+      </c>
+      <c r="E264" s="2">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
-        <v>175</v>
-      </c>
-      <c r="H264" s="1">
+        <v>186</v>
+      </c>
+      <c r="H264" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B265" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C265" t="s">
-        <v>103</v>
-      </c>
-      <c r="H265" s="1">
+        <v>107</v>
+      </c>
+      <c r="H265" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B266" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C266" t="s">
-        <v>107</v>
-      </c>
-      <c r="H266" s="1">
+        <v>111</v>
+      </c>
+      <c r="H266" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B267" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C267" t="s">
-        <v>103</v>
-      </c>
-      <c r="H267" s="1">
+        <v>107</v>
+      </c>
+      <c r="H267" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B268" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C268" t="s">
-        <v>107</v>
-      </c>
-      <c r="H268" s="1">
+        <v>111</v>
+      </c>
+      <c r="H268" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B269" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C269" t="s">
-        <v>107</v>
-      </c>
-      <c r="H269" s="1">
+        <v>111</v>
+      </c>
+      <c r="H269" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B270" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C270" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D270" t="s">
-        <v>113</v>
-      </c>
-      <c r="E270" s="1">
+        <v>117</v>
+      </c>
+      <c r="E270" s="2">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
-        <v>169</v>
-      </c>
-      <c r="H270" s="1">
+        <v>180</v>
+      </c>
+      <c r="H270" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B271" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C271" t="s">
-        <v>107</v>
-      </c>
-      <c r="H271" s="1">
+        <v>111</v>
+      </c>
+      <c r="H271" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B272" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C272" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D272" t="s">
-        <v>144</v>
-      </c>
-      <c r="E272" s="1">
+        <v>148</v>
+      </c>
+      <c r="E272" s="2">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
-        <v>181</v>
-      </c>
-      <c r="H272" s="1">
+        <v>192</v>
+      </c>
+      <c r="H272" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B273" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C273" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D273" t="s">
-        <v>145</v>
-      </c>
-      <c r="E273" s="1">
+        <v>149</v>
+      </c>
+      <c r="E273" s="2">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
-        <v>183</v>
-      </c>
-      <c r="H273" s="1">
+        <v>194</v>
+      </c>
+      <c r="H273" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B274" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C274" t="s">
-        <v>103</v>
-      </c>
-      <c r="H274" s="1">
+        <v>107</v>
+      </c>
+      <c r="H274" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B275" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C275" t="s">
-        <v>103</v>
-      </c>
-      <c r="H275" s="1">
+        <v>107</v>
+      </c>
+      <c r="H275" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B276" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C276" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D276" t="s">
-        <v>116</v>
-      </c>
-      <c r="E276" s="1">
+        <v>120</v>
+      </c>
+      <c r="E276" s="2">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
-        <v>182</v>
-      </c>
-      <c r="H276" s="1">
+        <v>193</v>
+      </c>
+      <c r="H276" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B277" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C277" t="s">
-        <v>103</v>
-      </c>
-      <c r="H277" s="1">
+        <v>107</v>
+      </c>
+      <c r="H277" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B278" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C278" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D278" t="s">
-        <v>148</v>
-      </c>
-      <c r="E278" s="1">
+        <v>152</v>
+      </c>
+      <c r="E278" s="2">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
-        <v>184</v>
-      </c>
-      <c r="H278" s="1">
+        <v>195</v>
+      </c>
+      <c r="H278" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="279" spans="1:8">
       <c r="A279" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B279" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C279" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D279" t="s">
-        <v>146</v>
-      </c>
-      <c r="E279" s="1">
+        <v>150</v>
+      </c>
+      <c r="E279" s="2">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
-        <v>183</v>
-      </c>
-      <c r="H279" s="1">
+        <v>194</v>
+      </c>
+      <c r="H279" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="280" spans="1:8">
       <c r="A280" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B280" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C280" t="s">
-        <v>103</v>
-      </c>
-      <c r="H280" s="1">
+        <v>107</v>
+      </c>
+      <c r="H280" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B281" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C281" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D281" t="s">
-        <v>149</v>
-      </c>
-      <c r="E281" s="1">
+        <v>153</v>
+      </c>
+      <c r="E281" s="2">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
-        <v>179</v>
-      </c>
-      <c r="H281" s="1">
+        <v>190</v>
+      </c>
+      <c r="H281" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B282" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C282" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D282" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F282" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G282" t="s">
-        <v>162</v>
-      </c>
-      <c r="H282" s="1">
+        <v>171</v>
+      </c>
+      <c r="H282" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B283" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C283" t="s">
-        <v>107</v>
-      </c>
-      <c r="H283" s="1">
+        <v>111</v>
+      </c>
+      <c r="H283" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B284" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C284" t="s">
-        <v>103</v>
-      </c>
-      <c r="H284" s="1">
+        <v>107</v>
+      </c>
+      <c r="H284" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B285" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C285" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D285" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F285" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G285" t="s">
-        <v>157</v>
-      </c>
-      <c r="H285" s="1">
+        <v>166</v>
+      </c>
+      <c r="H285" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B286" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C286" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D286" t="s">
-        <v>120</v>
-      </c>
-      <c r="H286" s="1">
+        <v>124</v>
+      </c>
+      <c r="H286" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B287" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C287" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D287" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F287" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G287" t="s">
-        <v>158</v>
-      </c>
-      <c r="H287" s="1">
+        <v>167</v>
+      </c>
+      <c r="H287" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B288" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C288" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D288" t="s">
-        <v>142</v>
-      </c>
-      <c r="E288" s="1">
+        <v>146</v>
+      </c>
+      <c r="E288" s="2">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
-        <v>180</v>
-      </c>
-      <c r="H288" s="1">
+        <v>191</v>
+      </c>
+      <c r="H288" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B289" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C289" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D289" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F289" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G289" t="s">
-        <v>159</v>
-      </c>
-      <c r="H289" s="1">
+        <v>168</v>
+      </c>
+      <c r="H289" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B290" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C290" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D290" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F290" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G290" t="s">
-        <v>159</v>
-      </c>
-      <c r="H290" s="1">
+        <v>168</v>
+      </c>
+      <c r="H290" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B291" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C291" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D291" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F291" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G291" t="s">
-        <v>160</v>
-      </c>
-      <c r="H291" s="1">
+        <v>169</v>
+      </c>
+      <c r="H291" s="2">
         <v>46218</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B292" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C292" t="s">
-        <v>103</v>
-      </c>
-      <c r="H292" s="1">
+        <v>107</v>
+      </c>
+      <c r="H292" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B293" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C293" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D293" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F293" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="G293" t="s">
-        <v>163</v>
-      </c>
-      <c r="H293" s="1">
+        <v>172</v>
+      </c>
+      <c r="H293" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B294" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C294" t="s">
-        <v>103</v>
-      </c>
-      <c r="H294" s="1">
+        <v>107</v>
+      </c>
+      <c r="H294" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="295" spans="1:8">
       <c r="A295" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B295" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C295" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D295" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F295" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G295" t="s">
-        <v>164</v>
-      </c>
-      <c r="H295" s="1">
+        <v>173</v>
+      </c>
+      <c r="H295" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B296" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C296" t="s">
-        <v>103</v>
-      </c>
-      <c r="H296" s="1">
+        <v>107</v>
+      </c>
+      <c r="H296" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B297" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C297" t="s">
-        <v>107</v>
-      </c>
-      <c r="H297" s="1">
+        <v>111</v>
+      </c>
+      <c r="H297" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B298" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C298" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D298" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F298" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G298" t="s">
-        <v>165</v>
-      </c>
-      <c r="H298" s="1">
+        <v>174</v>
+      </c>
+      <c r="H298" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B299" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C299" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D299" t="s">
-        <v>113</v>
-      </c>
-      <c r="E299" s="1">
+        <v>117</v>
+      </c>
+      <c r="E299" s="2">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
-        <v>169</v>
-      </c>
-      <c r="H299" s="1">
+        <v>180</v>
+      </c>
+      <c r="H299" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B300" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C300" t="s">
-        <v>103</v>
-      </c>
-      <c r="H300" s="1">
+        <v>107</v>
+      </c>
+      <c r="H300" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B301" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C301" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D301" t="s">
-        <v>144</v>
-      </c>
-      <c r="E301" s="1">
+        <v>148</v>
+      </c>
+      <c r="E301" s="2">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
-        <v>181</v>
-      </c>
-      <c r="H301" s="1">
+        <v>192</v>
+      </c>
+      <c r="H301" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="302" spans="1:8">
       <c r="A302" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B302" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C302" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D302" t="s">
-        <v>145</v>
-      </c>
-      <c r="E302" s="1">
+        <v>149</v>
+      </c>
+      <c r="E302" s="2">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
-        <v>178</v>
-      </c>
-      <c r="H302" s="1">
+        <v>189</v>
+      </c>
+      <c r="H302" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B303" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C303" t="s">
-        <v>103</v>
-      </c>
-      <c r="H303" s="1">
+        <v>107</v>
+      </c>
+      <c r="H303" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B304" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C304" t="s">
-        <v>103</v>
-      </c>
-      <c r="H304" s="1">
+        <v>107</v>
+      </c>
+      <c r="H304" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B305" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C305" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D305" t="s">
-        <v>116</v>
-      </c>
-      <c r="E305" s="1">
+        <v>120</v>
+      </c>
+      <c r="E305" s="2">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
-        <v>182</v>
-      </c>
-      <c r="H305" s="1">
+        <v>193</v>
+      </c>
+      <c r="H305" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B306" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C306" t="s">
-        <v>103</v>
-      </c>
-      <c r="H306" s="1">
+        <v>107</v>
+      </c>
+      <c r="H306" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B307" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C307" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D307" t="s">
-        <v>148</v>
-      </c>
-      <c r="E307" s="1">
+        <v>152</v>
+      </c>
+      <c r="E307" s="2">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
-        <v>184</v>
-      </c>
-      <c r="H307" s="1">
+        <v>195</v>
+      </c>
+      <c r="H307" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B308" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C308" t="s">
-        <v>107</v>
-      </c>
-      <c r="H308" s="1">
+        <v>111</v>
+      </c>
+      <c r="H308" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B309" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C309" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D309" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F309" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="G309" t="s">
-        <v>163</v>
-      </c>
-      <c r="H309" s="1">
+        <v>172</v>
+      </c>
+      <c r="H309" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="310" spans="1:8">
       <c r="A310" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B310" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C310" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D310" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F310" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G310" t="s">
-        <v>166</v>
-      </c>
-      <c r="H310" s="1">
+        <v>175</v>
+      </c>
+      <c r="H310" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="311" spans="1:8">
       <c r="A311" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B311" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C311" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D311" t="s">
-        <v>154</v>
-      </c>
-      <c r="H311" s="1">
+        <v>158</v>
+      </c>
+      <c r="H311" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B312" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C312" t="s">
-        <v>107</v>
-      </c>
-      <c r="H312" s="1">
+        <v>111</v>
+      </c>
+      <c r="H312" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B313" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C313" t="s">
-        <v>103</v>
-      </c>
-      <c r="H313" s="1">
+        <v>107</v>
+      </c>
+      <c r="H313" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B314" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C314" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D314" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F314" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G314" t="s">
-        <v>157</v>
-      </c>
-      <c r="H314" s="1">
+        <v>166</v>
+      </c>
+      <c r="H314" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B315" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C315" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D315" t="s">
-        <v>120</v>
-      </c>
-      <c r="H315" s="1">
+        <v>124</v>
+      </c>
+      <c r="H315" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B316" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C316" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D316" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F316" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G316" t="s">
-        <v>158</v>
-      </c>
-      <c r="H316" s="1">
+        <v>167</v>
+      </c>
+      <c r="H316" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B317" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C317" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D317" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F317" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G317" t="s">
-        <v>167</v>
-      </c>
-      <c r="H317" s="1">
+        <v>176</v>
+      </c>
+      <c r="H317" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B318" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C318" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D318" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F318" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G318" t="s">
-        <v>159</v>
-      </c>
-      <c r="H318" s="1">
+        <v>168</v>
+      </c>
+      <c r="H318" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="319" spans="1:8">
       <c r="A319" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B319" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C319" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D319" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F319" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G319" t="s">
-        <v>159</v>
-      </c>
-      <c r="H319" s="1">
+        <v>168</v>
+      </c>
+      <c r="H319" s="2">
         <v>46220</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" t="s">
+        <v>96</v>
+      </c>
+      <c r="B320" t="s">
+        <v>106</v>
+      </c>
+      <c r="C320" t="s">
+        <v>108</v>
+      </c>
+      <c r="D320" t="s">
+        <v>129</v>
+      </c>
+      <c r="F320" t="s">
+        <v>169</v>
+      </c>
+      <c r="G320" t="s">
+        <v>169</v>
+      </c>
+      <c r="H320" s="2">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" t="s">
+        <v>69</v>
+      </c>
+      <c r="B321" t="s">
+        <v>97</v>
+      </c>
+      <c r="C321" t="s">
+        <v>107</v>
+      </c>
+      <c r="H321" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322" t="s">
+        <v>70</v>
+      </c>
+      <c r="B322" t="s">
+        <v>97</v>
+      </c>
+      <c r="C322" t="s">
+        <v>109</v>
+      </c>
+      <c r="D322" t="s">
+        <v>147</v>
+      </c>
+      <c r="F322" t="s">
+        <v>177</v>
+      </c>
+      <c r="G322" t="s">
+        <v>177</v>
+      </c>
+      <c r="H322" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323" t="s">
+        <v>71</v>
+      </c>
+      <c r="B323" t="s">
+        <v>97</v>
+      </c>
+      <c r="C323" t="s">
+        <v>107</v>
+      </c>
+      <c r="H323" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="A324" t="s">
+        <v>72</v>
+      </c>
+      <c r="B324" t="s">
+        <v>98</v>
+      </c>
+      <c r="C324" t="s">
+        <v>110</v>
+      </c>
+      <c r="D324" t="s">
+        <v>159</v>
+      </c>
+      <c r="F324" t="s">
+        <v>178</v>
+      </c>
+      <c r="G324" t="s">
+        <v>178</v>
+      </c>
+      <c r="H324" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" t="s">
+        <v>73</v>
+      </c>
+      <c r="B325" t="s">
+        <v>99</v>
+      </c>
+      <c r="C325" t="s">
+        <v>107</v>
+      </c>
+      <c r="H325" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326" t="s">
+        <v>74</v>
+      </c>
+      <c r="B326" t="s">
+        <v>99</v>
+      </c>
+      <c r="C326" t="s">
+        <v>111</v>
+      </c>
+      <c r="H326" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327" t="s">
+        <v>75</v>
+      </c>
+      <c r="B327" t="s">
+        <v>99</v>
+      </c>
+      <c r="C327" t="s">
+        <v>111</v>
+      </c>
+      <c r="H327" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" t="s">
+        <v>76</v>
+      </c>
+      <c r="B328" t="s">
+        <v>99</v>
+      </c>
+      <c r="C328" t="s">
+        <v>109</v>
+      </c>
+      <c r="D328" t="s">
+        <v>117</v>
+      </c>
+      <c r="E328" s="2">
+        <v>46234</v>
+      </c>
+      <c r="G328" t="s">
+        <v>180</v>
+      </c>
+      <c r="H328" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" t="s">
+        <v>77</v>
+      </c>
+      <c r="B329" t="s">
+        <v>100</v>
+      </c>
+      <c r="C329" t="s">
+        <v>110</v>
+      </c>
+      <c r="D329" t="s">
+        <v>160</v>
+      </c>
+      <c r="F329" t="s">
+        <v>178</v>
+      </c>
+      <c r="G329" t="s">
+        <v>178</v>
+      </c>
+      <c r="H329" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" t="s">
+        <v>78</v>
+      </c>
+      <c r="B330" t="s">
+        <v>100</v>
+      </c>
+      <c r="C330" t="s">
+        <v>109</v>
+      </c>
+      <c r="D330" t="s">
+        <v>148</v>
+      </c>
+      <c r="F330" t="s">
+        <v>178</v>
+      </c>
+      <c r="G330" t="s">
+        <v>178</v>
+      </c>
+      <c r="H330" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" t="s">
+        <v>79</v>
+      </c>
+      <c r="B331" t="s">
+        <v>101</v>
+      </c>
+      <c r="C331" t="s">
+        <v>107</v>
+      </c>
+      <c r="H331" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8">
+      <c r="A332" t="s">
+        <v>80</v>
+      </c>
+      <c r="B332" t="s">
+        <v>102</v>
+      </c>
+      <c r="C332" t="s">
+        <v>110</v>
+      </c>
+      <c r="D332" t="s">
+        <v>161</v>
+      </c>
+      <c r="F332" t="s">
+        <v>178</v>
+      </c>
+      <c r="G332" t="s">
+        <v>178</v>
+      </c>
+      <c r="H332" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8">
+      <c r="A333" t="s">
+        <v>81</v>
+      </c>
+      <c r="B333" t="s">
+        <v>102</v>
+      </c>
+      <c r="C333" t="s">
+        <v>110</v>
+      </c>
+      <c r="D333" t="s">
+        <v>162</v>
+      </c>
+      <c r="F333" t="s">
+        <v>177</v>
+      </c>
+      <c r="G333" t="s">
+        <v>177</v>
+      </c>
+      <c r="H333" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334" t="s">
+        <v>34</v>
+      </c>
+      <c r="B334" t="s">
+        <v>102</v>
+      </c>
+      <c r="C334" t="s">
+        <v>108</v>
+      </c>
+      <c r="D334" t="s">
+        <v>120</v>
+      </c>
+      <c r="E334" s="2">
+        <v>46237</v>
+      </c>
+      <c r="G334" t="s">
+        <v>193</v>
+      </c>
+      <c r="H334" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" t="s">
+        <v>82</v>
+      </c>
+      <c r="B335" t="s">
+        <v>103</v>
+      </c>
+      <c r="C335" t="s">
+        <v>107</v>
+      </c>
+      <c r="H335" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336" t="s">
+        <v>83</v>
+      </c>
+      <c r="B336" t="s">
+        <v>103</v>
+      </c>
+      <c r="C336" t="s">
+        <v>109</v>
+      </c>
+      <c r="D336" t="s">
+        <v>152</v>
+      </c>
+      <c r="E336" s="2">
+        <v>46227</v>
+      </c>
+      <c r="G336" t="s">
+        <v>195</v>
+      </c>
+      <c r="H336" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337" t="s">
+        <v>84</v>
+      </c>
+      <c r="B337" t="s">
+        <v>103</v>
+      </c>
+      <c r="C337" t="s">
+        <v>107</v>
+      </c>
+      <c r="H337" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
+      <c r="A338" t="s">
+        <v>85</v>
+      </c>
+      <c r="B338" t="s">
+        <v>103</v>
+      </c>
+      <c r="C338" t="s">
+        <v>107</v>
+      </c>
+      <c r="H338" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8">
+      <c r="A339" t="s">
+        <v>86</v>
+      </c>
+      <c r="B339" t="s">
+        <v>103</v>
+      </c>
+      <c r="C339" t="s">
+        <v>110</v>
+      </c>
+      <c r="D339" t="s">
+        <v>157</v>
+      </c>
+      <c r="F339" t="s">
+        <v>175</v>
+      </c>
+      <c r="G339" t="s">
+        <v>175</v>
+      </c>
+      <c r="H339" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8">
+      <c r="A340" t="s">
+        <v>87</v>
+      </c>
+      <c r="B340" t="s">
+        <v>104</v>
+      </c>
+      <c r="C340" t="s">
+        <v>108</v>
+      </c>
+      <c r="D340" t="s">
+        <v>163</v>
+      </c>
+      <c r="H340" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8">
+      <c r="A341" t="s">
+        <v>88</v>
+      </c>
+      <c r="B341" t="s">
+        <v>105</v>
+      </c>
+      <c r="C341" t="s">
+        <v>111</v>
+      </c>
+      <c r="H341" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8">
+      <c r="A342" t="s">
+        <v>89</v>
+      </c>
+      <c r="B342" t="s">
+        <v>106</v>
+      </c>
+      <c r="C342" t="s">
+        <v>107</v>
+      </c>
+      <c r="H342" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8">
+      <c r="A343" t="s">
+        <v>90</v>
+      </c>
+      <c r="B343" t="s">
+        <v>106</v>
+      </c>
+      <c r="C343" t="s">
+        <v>112</v>
+      </c>
+      <c r="D343" t="s">
+        <v>123</v>
+      </c>
+      <c r="F343" t="s">
+        <v>166</v>
+      </c>
+      <c r="G343" t="s">
+        <v>166</v>
+      </c>
+      <c r="H343" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" t="s">
+        <v>91</v>
+      </c>
+      <c r="B344" t="s">
+        <v>106</v>
+      </c>
+      <c r="C344" t="s">
+        <v>112</v>
+      </c>
+      <c r="D344" t="s">
+        <v>124</v>
+      </c>
+      <c r="H344" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" t="s">
         <v>92</v>
       </c>
-      <c r="B320" t="s">
-        <v>102</v>
-      </c>
-      <c r="C320" t="s">
-        <v>104</v>
-      </c>
-      <c r="D320" t="s">
+      <c r="B345" t="s">
+        <v>106</v>
+      </c>
+      <c r="C345" t="s">
+        <v>108</v>
+      </c>
+      <c r="D345" t="s">
         <v>125</v>
       </c>
-      <c r="F320" t="s">
-        <v>160</v>
-      </c>
-      <c r="G320" t="s">
-        <v>160</v>
-      </c>
-      <c r="H320" s="1">
-        <v>46220</v>
+      <c r="F345" t="s">
+        <v>167</v>
+      </c>
+      <c r="G345" t="s">
+        <v>167</v>
+      </c>
+      <c r="H345" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" t="s">
+        <v>93</v>
+      </c>
+      <c r="B346" t="s">
+        <v>106</v>
+      </c>
+      <c r="C346" t="s">
+        <v>110</v>
+      </c>
+      <c r="D346" t="s">
+        <v>146</v>
+      </c>
+      <c r="F346" t="s">
+        <v>176</v>
+      </c>
+      <c r="G346" t="s">
+        <v>176</v>
+      </c>
+      <c r="H346" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347" t="s">
+        <v>94</v>
+      </c>
+      <c r="B347" t="s">
+        <v>106</v>
+      </c>
+      <c r="C347" t="s">
+        <v>108</v>
+      </c>
+      <c r="D347" t="s">
+        <v>127</v>
+      </c>
+      <c r="F347" t="s">
+        <v>168</v>
+      </c>
+      <c r="G347" t="s">
+        <v>168</v>
+      </c>
+      <c r="H347" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348" t="s">
+        <v>95</v>
+      </c>
+      <c r="B348" t="s">
+        <v>106</v>
+      </c>
+      <c r="C348" t="s">
+        <v>108</v>
+      </c>
+      <c r="D348" t="s">
+        <v>128</v>
+      </c>
+      <c r="F348" t="s">
+        <v>168</v>
+      </c>
+      <c r="G348" t="s">
+        <v>168</v>
+      </c>
+      <c r="H348" s="2">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349" t="s">
+        <v>96</v>
+      </c>
+      <c r="B349" t="s">
+        <v>106</v>
+      </c>
+      <c r="C349" t="s">
+        <v>108</v>
+      </c>
+      <c r="D349" t="s">
+        <v>129</v>
+      </c>
+      <c r="F349" t="s">
+        <v>169</v>
+      </c>
+      <c r="G349" t="s">
+        <v>169</v>
+      </c>
+      <c r="H349" s="2">
+        <v>46224</v>
       </c>
     </row>
   </sheetData>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -612,16 +612,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -637,7 +629,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -645,30 +637,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -968,72 +942,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1098,7 +1072,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1163,7 +1137,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1228,7 +1202,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1293,7 +1267,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1358,7 +1332,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1423,7 +1397,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1488,7 +1462,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1553,7 +1527,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1618,7 +1592,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1683,7 +1657,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1748,7 +1722,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -1823,28 +1797,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1858,7 +1832,7 @@
       <c r="C2" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1872,7 +1846,7 @@
       <c r="C3" t="s">
         <v>107</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1895,7 +1869,7 @@
       <c r="G4" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1909,7 +1883,7 @@
       <c r="C5" t="s">
         <v>107</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1923,7 +1897,7 @@
       <c r="C6" t="s">
         <v>107</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1940,13 +1914,13 @@
       <c r="D7" t="s">
         <v>115</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>179</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1963,13 +1937,13 @@
       <c r="D8" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>179</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1986,13 +1960,13 @@
       <c r="D9" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>180</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2009,13 +1983,13 @@
       <c r="D10" t="s">
         <v>118</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>181</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2029,7 +2003,7 @@
       <c r="C11" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2043,7 +2017,7 @@
       <c r="C12" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2060,13 +2034,13 @@
       <c r="D13" t="s">
         <v>119</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>179</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2080,7 +2054,7 @@
       <c r="C14" t="s">
         <v>111</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2097,13 +2071,13 @@
       <c r="D15" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>182</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2117,7 +2091,7 @@
       <c r="C16" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2131,7 +2105,7 @@
       <c r="C17" t="s">
         <v>107</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2148,13 +2122,13 @@
       <c r="D18" t="s">
         <v>121</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>183</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2168,7 +2142,7 @@
       <c r="C19" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2185,13 +2159,13 @@
       <c r="D20" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>179</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2214,7 +2188,7 @@
       <c r="G21" t="s">
         <v>165</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2228,7 +2202,7 @@
       <c r="C22" t="s">
         <v>111</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2242,7 +2216,7 @@
       <c r="C23" t="s">
         <v>107</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2265,7 +2239,7 @@
       <c r="G24" t="s">
         <v>166</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2282,7 +2256,7 @@
       <c r="D25" t="s">
         <v>124</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2305,7 +2279,7 @@
       <c r="G26" t="s">
         <v>167</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2322,13 +2296,13 @@
       <c r="D27" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>184</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2351,7 +2325,7 @@
       <c r="G28" t="s">
         <v>168</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2374,7 +2348,7 @@
       <c r="G29" t="s">
         <v>168</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2397,7 +2371,7 @@
       <c r="G30" t="s">
         <v>169</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2411,7 +2385,7 @@
       <c r="C31" t="s">
         <v>107</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2425,7 +2399,7 @@
       <c r="C32" t="s">
         <v>107</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2448,7 +2422,7 @@
       <c r="G33" t="s">
         <v>170</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2462,7 +2436,7 @@
       <c r="C34" t="s">
         <v>107</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2476,7 +2450,7 @@
       <c r="C35" t="s">
         <v>107</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2493,13 +2467,13 @@
       <c r="D36" t="s">
         <v>115</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>179</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2516,13 +2490,13 @@
       <c r="D37" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>179</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2539,13 +2513,13 @@
       <c r="D38" t="s">
         <v>117</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>180</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2562,13 +2536,13 @@
       <c r="D39" t="s">
         <v>118</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>181</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2582,7 +2556,7 @@
       <c r="C40" t="s">
         <v>107</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2596,7 +2570,7 @@
       <c r="C41" t="s">
         <v>107</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2613,13 +2587,13 @@
       <c r="D42" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>179</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2633,7 +2607,7 @@
       <c r="C43" t="s">
         <v>107</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2650,13 +2624,13 @@
       <c r="D44" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>182</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2670,7 +2644,7 @@
       <c r="C45" t="s">
         <v>107</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2684,7 +2658,7 @@
       <c r="C46" t="s">
         <v>107</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2698,7 +2672,7 @@
       <c r="C47" t="s">
         <v>111</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2712,7 +2686,7 @@
       <c r="C48" t="s">
         <v>107</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2729,13 +2703,13 @@
       <c r="D49" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>179</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2758,7 +2732,7 @@
       <c r="G50" t="s">
         <v>165</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2772,7 +2746,7 @@
       <c r="C51" t="s">
         <v>111</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2786,7 +2760,7 @@
       <c r="C52" t="s">
         <v>107</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2809,7 +2783,7 @@
       <c r="G53" t="s">
         <v>166</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2826,7 +2800,7 @@
       <c r="D54" t="s">
         <v>124</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2849,7 +2823,7 @@
       <c r="G55" t="s">
         <v>167</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2866,13 +2840,13 @@
       <c r="D56" t="s">
         <v>126</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>184</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2895,7 +2869,7 @@
       <c r="G57" t="s">
         <v>168</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2918,7 +2892,7 @@
       <c r="G58" t="s">
         <v>168</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2941,7 +2915,7 @@
       <c r="G59" t="s">
         <v>169</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2955,7 +2929,7 @@
       <c r="C60" t="s">
         <v>107</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2969,7 +2943,7 @@
       <c r="C61" t="s">
         <v>107</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2986,13 +2960,13 @@
       <c r="D62" t="s">
         <v>130</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>185</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3006,7 +2980,7 @@
       <c r="C63" t="s">
         <v>107</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3023,13 +2997,13 @@
       <c r="D64" t="s">
         <v>132</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>186</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3043,7 +3017,7 @@
       <c r="C65" t="s">
         <v>107</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3057,7 +3031,7 @@
       <c r="C66" t="s">
         <v>111</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3074,13 +3048,13 @@
       <c r="D67" t="s">
         <v>117</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>180</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3097,13 +3071,13 @@
       <c r="D68" t="s">
         <v>118</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>181</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3117,7 +3091,7 @@
       <c r="C69" t="s">
         <v>107</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3131,7 +3105,7 @@
       <c r="C70" t="s">
         <v>107</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3148,13 +3122,13 @@
       <c r="D71" t="s">
         <v>119</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>185</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3168,7 +3142,7 @@
       <c r="C72" t="s">
         <v>107</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3185,13 +3159,13 @@
       <c r="D73" t="s">
         <v>120</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>182</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3205,7 +3179,7 @@
       <c r="C74" t="s">
         <v>107</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3219,7 +3193,7 @@
       <c r="C75" t="s">
         <v>107</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3233,7 +3207,7 @@
       <c r="C76" t="s">
         <v>107</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3247,7 +3221,7 @@
       <c r="C77" t="s">
         <v>107</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3264,13 +3238,13 @@
       <c r="D78" t="s">
         <v>131</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>185</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3293,7 +3267,7 @@
       <c r="G79" t="s">
         <v>171</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3307,7 +3281,7 @@
       <c r="C80" t="s">
         <v>111</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3321,7 +3295,7 @@
       <c r="C81" t="s">
         <v>107</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3344,7 +3318,7 @@
       <c r="G82" t="s">
         <v>166</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3361,7 +3335,7 @@
       <c r="D83" t="s">
         <v>124</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3384,7 +3358,7 @@
       <c r="G84" t="s">
         <v>167</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3401,13 +3375,13 @@
       <c r="D85" t="s">
         <v>126</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>184</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3430,7 +3404,7 @@
       <c r="G86" t="s">
         <v>168</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3453,7 +3427,7 @@
       <c r="G87" t="s">
         <v>168</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3476,7 +3450,7 @@
       <c r="G88" t="s">
         <v>169</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3490,7 +3464,7 @@
       <c r="C89" t="s">
         <v>107</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3507,13 +3481,13 @@
       <c r="D90" t="s">
         <v>134</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>186</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3530,13 +3504,13 @@
       <c r="D91" t="s">
         <v>130</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>185</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3550,7 +3524,7 @@
       <c r="C92" t="s">
         <v>107</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3567,13 +3541,13 @@
       <c r="D93" t="s">
         <v>132</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>186</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3587,7 +3561,7 @@
       <c r="C94" t="s">
         <v>107</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3601,7 +3575,7 @@
       <c r="C95" t="s">
         <v>111</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3618,13 +3592,13 @@
       <c r="D96" t="s">
         <v>117</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>180</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3641,13 +3615,13 @@
       <c r="D97" t="s">
         <v>118</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>181</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3661,7 +3635,7 @@
       <c r="C98" t="s">
         <v>107</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3678,13 +3652,13 @@
       <c r="D99" t="s">
         <v>135</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>181</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3701,13 +3675,13 @@
       <c r="D100" t="s">
         <v>119</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>181</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3721,7 +3695,7 @@
       <c r="C101" t="s">
         <v>107</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3738,13 +3712,13 @@
       <c r="D102" t="s">
         <v>120</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>182</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3761,13 +3735,13 @@
       <c r="D103" t="s">
         <v>136</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>181</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3781,7 +3755,7 @@
       <c r="C104" t="s">
         <v>107</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3795,7 +3769,7 @@
       <c r="C105" t="s">
         <v>107</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3809,7 +3783,7 @@
       <c r="C106" t="s">
         <v>107</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3826,13 +3800,13 @@
       <c r="D107" t="s">
         <v>137</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>181</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3855,7 +3829,7 @@
       <c r="G108" t="s">
         <v>171</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3869,7 +3843,7 @@
       <c r="C109" t="s">
         <v>111</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3883,7 +3857,7 @@
       <c r="C110" t="s">
         <v>107</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3906,7 +3880,7 @@
       <c r="G111" t="s">
         <v>166</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3923,7 +3897,7 @@
       <c r="D112" t="s">
         <v>124</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3946,7 +3920,7 @@
       <c r="G113" t="s">
         <v>167</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3963,13 +3937,13 @@
       <c r="D114" t="s">
         <v>126</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>184</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3992,7 +3966,7 @@
       <c r="G115" t="s">
         <v>168</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4015,7 +3989,7 @@
       <c r="G116" t="s">
         <v>168</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4038,7 +4012,7 @@
       <c r="G117" t="s">
         <v>169</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4052,7 +4026,7 @@
       <c r="C118" t="s">
         <v>107</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4069,13 +4043,13 @@
       <c r="D119" t="s">
         <v>134</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>186</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4089,7 +4063,7 @@
       <c r="C120" t="s">
         <v>111</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4103,7 +4077,7 @@
       <c r="C121" t="s">
         <v>107</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4117,7 +4091,7 @@
       <c r="C122" t="s">
         <v>111</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4131,7 +4105,7 @@
       <c r="C123" t="s">
         <v>111</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4145,7 +4119,7 @@
       <c r="C124" t="s">
         <v>111</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4162,13 +4136,13 @@
       <c r="D125" t="s">
         <v>117</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>180</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4185,13 +4159,13 @@
       <c r="D126" t="s">
         <v>118</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>181</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4205,7 +4179,7 @@
       <c r="C127" t="s">
         <v>107</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4222,13 +4196,13 @@
       <c r="D128" t="s">
         <v>135</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>181</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4245,13 +4219,13 @@
       <c r="D129" t="s">
         <v>119</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>181</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4265,7 +4239,7 @@
       <c r="C130" t="s">
         <v>107</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4282,13 +4256,13 @@
       <c r="D131" t="s">
         <v>120</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>182</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4305,13 +4279,13 @@
       <c r="D132" t="s">
         <v>136</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>181</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4325,7 +4299,7 @@
       <c r="C133" t="s">
         <v>107</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4339,7 +4313,7 @@
       <c r="C134" t="s">
         <v>107</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4353,7 +4327,7 @@
       <c r="C135" t="s">
         <v>107</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4370,13 +4344,13 @@
       <c r="D136" t="s">
         <v>138</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>181</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4399,7 +4373,7 @@
       <c r="G137" t="s">
         <v>171</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4413,7 +4387,7 @@
       <c r="C138" t="s">
         <v>111</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4427,7 +4401,7 @@
       <c r="C139" t="s">
         <v>107</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4450,7 +4424,7 @@
       <c r="G140" t="s">
         <v>166</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4467,7 +4441,7 @@
       <c r="D141" t="s">
         <v>124</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4490,7 +4464,7 @@
       <c r="G142" t="s">
         <v>167</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4507,13 +4481,13 @@
       <c r="D143" t="s">
         <v>126</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>184</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4536,7 +4510,7 @@
       <c r="G144" t="s">
         <v>168</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4559,7 +4533,7 @@
       <c r="G145" t="s">
         <v>168</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4582,7 +4556,7 @@
       <c r="G146" t="s">
         <v>169</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4596,7 +4570,7 @@
       <c r="C147" t="s">
         <v>107</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4613,13 +4587,13 @@
       <c r="D148" t="s">
         <v>134</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>186</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4633,7 +4607,7 @@
       <c r="C149" t="s">
         <v>111</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4647,7 +4621,7 @@
       <c r="C150" t="s">
         <v>107</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4661,7 +4635,7 @@
       <c r="C151" t="s">
         <v>107</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4675,7 +4649,7 @@
       <c r="C152" t="s">
         <v>111</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4689,7 +4663,7 @@
       <c r="C153" t="s">
         <v>111</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4706,13 +4680,13 @@
       <c r="D154" t="s">
         <v>117</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>180</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4729,13 +4703,13 @@
       <c r="D155" t="s">
         <v>118</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>181</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4749,7 +4723,7 @@
       <c r="C156" t="s">
         <v>107</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4766,13 +4740,13 @@
       <c r="D157" t="s">
         <v>135</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>181</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4789,13 +4763,13 @@
       <c r="D158" t="s">
         <v>119</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>181</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4812,13 +4786,13 @@
       <c r="D159" t="s">
         <v>139</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>187</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4835,13 +4809,13 @@
       <c r="D160" t="s">
         <v>120</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>182</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4858,13 +4832,13 @@
       <c r="D161" t="s">
         <v>136</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>181</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4878,7 +4852,7 @@
       <c r="C162" t="s">
         <v>107</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4892,7 +4866,7 @@
       <c r="C163" t="s">
         <v>107</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4906,7 +4880,7 @@
       <c r="C164" t="s">
         <v>107</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4923,13 +4897,13 @@
       <c r="D165" t="s">
         <v>138</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>181</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4952,7 +4926,7 @@
       <c r="G166" t="s">
         <v>171</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4966,7 +4940,7 @@
       <c r="C167" t="s">
         <v>111</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4980,7 +4954,7 @@
       <c r="C168" t="s">
         <v>107</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5003,7 +4977,7 @@
       <c r="G169" t="s">
         <v>166</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5020,7 +4994,7 @@
       <c r="D170" t="s">
         <v>124</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5043,7 +5017,7 @@
       <c r="G171" t="s">
         <v>167</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5060,13 +5034,13 @@
       <c r="D172" t="s">
         <v>126</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>184</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5089,7 +5063,7 @@
       <c r="G173" t="s">
         <v>168</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5112,7 +5086,7 @@
       <c r="G174" t="s">
         <v>168</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5135,7 +5109,7 @@
       <c r="G175" t="s">
         <v>169</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5149,7 +5123,7 @@
       <c r="C176" t="s">
         <v>107</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5166,13 +5140,13 @@
       <c r="D177" t="s">
         <v>140</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>186</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5186,7 +5160,7 @@
       <c r="C178" t="s">
         <v>107</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5203,13 +5177,13 @@
       <c r="D179" t="s">
         <v>141</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>182</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5223,7 +5197,7 @@
       <c r="C180" t="s">
         <v>107</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5237,7 +5211,7 @@
       <c r="C181" t="s">
         <v>111</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5251,7 +5225,7 @@
       <c r="C182" t="s">
         <v>111</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5268,13 +5242,13 @@
       <c r="D183" t="s">
         <v>117</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>180</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5291,13 +5265,13 @@
       <c r="D184" t="s">
         <v>118</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>181</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5311,7 +5285,7 @@
       <c r="C185" t="s">
         <v>107</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5328,13 +5302,13 @@
       <c r="D186" t="s">
         <v>135</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>181</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5351,13 +5325,13 @@
       <c r="D187" t="s">
         <v>142</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>181</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5374,13 +5348,13 @@
       <c r="D188" t="s">
         <v>143</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>181</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5397,13 +5371,13 @@
       <c r="D189" t="s">
         <v>120</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>182</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5420,13 +5394,13 @@
       <c r="D190" t="s">
         <v>136</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>181</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5440,7 +5414,7 @@
       <c r="C191" t="s">
         <v>107</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5454,7 +5428,7 @@
       <c r="C192" t="s">
         <v>107</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5468,7 +5442,7 @@
       <c r="C193" t="s">
         <v>107</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5485,13 +5459,13 @@
       <c r="D194" t="s">
         <v>138</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>188</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5514,7 +5488,7 @@
       <c r="G195" t="s">
         <v>171</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5528,7 +5502,7 @@
       <c r="C196" t="s">
         <v>111</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5542,7 +5516,7 @@
       <c r="C197" t="s">
         <v>107</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5565,7 +5539,7 @@
       <c r="G198" t="s">
         <v>166</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5582,7 +5556,7 @@
       <c r="D199" t="s">
         <v>124</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5605,7 +5579,7 @@
       <c r="G200" t="s">
         <v>167</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5622,13 +5596,13 @@
       <c r="D201" t="s">
         <v>126</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>184</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5651,7 +5625,7 @@
       <c r="G202" t="s">
         <v>168</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5674,7 +5648,7 @@
       <c r="G203" t="s">
         <v>168</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5697,7 +5671,7 @@
       <c r="G204" t="s">
         <v>169</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5711,7 +5685,7 @@
       <c r="C205" t="s">
         <v>107</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5728,13 +5702,13 @@
       <c r="D206" t="s">
         <v>140</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>186</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5748,7 +5722,7 @@
       <c r="C207" t="s">
         <v>107</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5762,7 +5736,7 @@
       <c r="C208" t="s">
         <v>111</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5776,7 +5750,7 @@
       <c r="C209" t="s">
         <v>107</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5790,7 +5764,7 @@
       <c r="C210" t="s">
         <v>111</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5804,7 +5778,7 @@
       <c r="C211" t="s">
         <v>111</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5821,13 +5795,13 @@
       <c r="D212" t="s">
         <v>117</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>180</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5841,7 +5815,7 @@
       <c r="C213" t="s">
         <v>111</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5855,7 +5829,7 @@
       <c r="C214" t="s">
         <v>107</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5872,13 +5846,13 @@
       <c r="D215" t="s">
         <v>135</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>189</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5895,13 +5869,13 @@
       <c r="D216" t="s">
         <v>142</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>182</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5915,7 +5889,7 @@
       <c r="C217" t="s">
         <v>107</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5932,13 +5906,13 @@
       <c r="D218" t="s">
         <v>120</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>182</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5952,7 +5926,7 @@
       <c r="C219" t="s">
         <v>107</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5966,7 +5940,7 @@
       <c r="C220" t="s">
         <v>107</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5983,13 +5957,13 @@
       <c r="D221" t="s">
         <v>144</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>186</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6003,7 +5977,7 @@
       <c r="C222" t="s">
         <v>107</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6020,13 +5994,13 @@
       <c r="D223" t="s">
         <v>145</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>190</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6049,7 +6023,7 @@
       <c r="G224" t="s">
         <v>171</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6063,7 +6037,7 @@
       <c r="C225" t="s">
         <v>111</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6077,7 +6051,7 @@
       <c r="C226" t="s">
         <v>107</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6100,7 +6074,7 @@
       <c r="G227" t="s">
         <v>166</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6117,7 +6091,7 @@
       <c r="D228" t="s">
         <v>124</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6140,7 +6114,7 @@
       <c r="G229" t="s">
         <v>167</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6157,13 +6131,13 @@
       <c r="D230" t="s">
         <v>146</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>191</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6186,7 +6160,7 @@
       <c r="G231" t="s">
         <v>168</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6209,7 +6183,7 @@
       <c r="G232" t="s">
         <v>168</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6232,7 +6206,7 @@
       <c r="G233" t="s">
         <v>169</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6246,7 +6220,7 @@
       <c r="C234" t="s">
         <v>107</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6263,13 +6237,13 @@
       <c r="D235" t="s">
         <v>147</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>186</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6283,7 +6257,7 @@
       <c r="C236" t="s">
         <v>107</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6297,7 +6271,7 @@
       <c r="C237" t="s">
         <v>111</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6311,7 +6285,7 @@
       <c r="C238" t="s">
         <v>107</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6325,7 +6299,7 @@
       <c r="C239" t="s">
         <v>111</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6339,7 +6313,7 @@
       <c r="C240" t="s">
         <v>111</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6356,13 +6330,13 @@
       <c r="D241" t="s">
         <v>117</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>180</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6376,7 +6350,7 @@
       <c r="C242" t="s">
         <v>111</v>
       </c>
-      <c r="H242" s="2">
+      <c r="H242" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6393,13 +6367,13 @@
       <c r="D243" t="s">
         <v>148</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>192</v>
       </c>
-      <c r="H243" s="2">
+      <c r="H243" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6416,13 +6390,13 @@
       <c r="D244" t="s">
         <v>149</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>189</v>
       </c>
-      <c r="H244" s="2">
+      <c r="H244" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6436,7 +6410,7 @@
       <c r="C245" t="s">
         <v>111</v>
       </c>
-      <c r="H245" s="2">
+      <c r="H245" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6450,7 +6424,7 @@
       <c r="C246" t="s">
         <v>107</v>
       </c>
-      <c r="H246" s="2">
+      <c r="H246" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6467,13 +6441,13 @@
       <c r="D247" t="s">
         <v>120</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>193</v>
       </c>
-      <c r="H247" s="2">
+      <c r="H247" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6487,7 +6461,7 @@
       <c r="C248" t="s">
         <v>107</v>
       </c>
-      <c r="H248" s="2">
+      <c r="H248" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6501,7 +6475,7 @@
       <c r="C249" t="s">
         <v>107</v>
       </c>
-      <c r="H249" s="2">
+      <c r="H249" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6518,13 +6492,13 @@
       <c r="D250" t="s">
         <v>150</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>188</v>
       </c>
-      <c r="H250" s="2">
+      <c r="H250" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6538,7 +6512,7 @@
       <c r="C251" t="s">
         <v>107</v>
       </c>
-      <c r="H251" s="2">
+      <c r="H251" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6555,13 +6529,13 @@
       <c r="D252" t="s">
         <v>151</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>190</v>
       </c>
-      <c r="H252" s="2">
+      <c r="H252" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6584,7 +6558,7 @@
       <c r="G253" t="s">
         <v>171</v>
       </c>
-      <c r="H253" s="2">
+      <c r="H253" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6598,7 +6572,7 @@
       <c r="C254" t="s">
         <v>111</v>
       </c>
-      <c r="H254" s="2">
+      <c r="H254" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6612,7 +6586,7 @@
       <c r="C255" t="s">
         <v>107</v>
       </c>
-      <c r="H255" s="2">
+      <c r="H255" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6635,7 +6609,7 @@
       <c r="G256" t="s">
         <v>166</v>
       </c>
-      <c r="H256" s="2">
+      <c r="H256" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6652,7 +6626,7 @@
       <c r="D257" t="s">
         <v>124</v>
       </c>
-      <c r="H257" s="2">
+      <c r="H257" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6675,7 +6649,7 @@
       <c r="G258" t="s">
         <v>167</v>
       </c>
-      <c r="H258" s="2">
+      <c r="H258" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6692,13 +6666,13 @@
       <c r="D259" t="s">
         <v>146</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>191</v>
       </c>
-      <c r="H259" s="2">
+      <c r="H259" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6721,7 +6695,7 @@
       <c r="G260" t="s">
         <v>168</v>
       </c>
-      <c r="H260" s="2">
+      <c r="H260" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6744,7 +6718,7 @@
       <c r="G261" t="s">
         <v>168</v>
       </c>
-      <c r="H261" s="2">
+      <c r="H261" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6767,7 +6741,7 @@
       <c r="G262" t="s">
         <v>169</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6781,7 +6755,7 @@
       <c r="C263" t="s">
         <v>107</v>
       </c>
-      <c r="H263" s="2">
+      <c r="H263" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6798,13 +6772,13 @@
       <c r="D264" t="s">
         <v>147</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>186</v>
       </c>
-      <c r="H264" s="2">
+      <c r="H264" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6818,7 +6792,7 @@
       <c r="C265" t="s">
         <v>107</v>
       </c>
-      <c r="H265" s="2">
+      <c r="H265" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6832,7 +6806,7 @@
       <c r="C266" t="s">
         <v>111</v>
       </c>
-      <c r="H266" s="2">
+      <c r="H266" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6846,7 +6820,7 @@
       <c r="C267" t="s">
         <v>107</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H267" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6860,7 +6834,7 @@
       <c r="C268" t="s">
         <v>111</v>
       </c>
-      <c r="H268" s="2">
+      <c r="H268" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6874,7 +6848,7 @@
       <c r="C269" t="s">
         <v>111</v>
       </c>
-      <c r="H269" s="2">
+      <c r="H269" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6891,13 +6865,13 @@
       <c r="D270" t="s">
         <v>117</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>180</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H270" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6911,7 +6885,7 @@
       <c r="C271" t="s">
         <v>111</v>
       </c>
-      <c r="H271" s="2">
+      <c r="H271" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6928,13 +6902,13 @@
       <c r="D272" t="s">
         <v>148</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>192</v>
       </c>
-      <c r="H272" s="2">
+      <c r="H272" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6951,13 +6925,13 @@
       <c r="D273" t="s">
         <v>149</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>194</v>
       </c>
-      <c r="H273" s="2">
+      <c r="H273" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6971,7 +6945,7 @@
       <c r="C274" t="s">
         <v>107</v>
       </c>
-      <c r="H274" s="2">
+      <c r="H274" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6985,7 +6959,7 @@
       <c r="C275" t="s">
         <v>107</v>
       </c>
-      <c r="H275" s="2">
+      <c r="H275" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7002,13 +6976,13 @@
       <c r="D276" t="s">
         <v>120</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>193</v>
       </c>
-      <c r="H276" s="2">
+      <c r="H276" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7022,7 +6996,7 @@
       <c r="C277" t="s">
         <v>107</v>
       </c>
-      <c r="H277" s="2">
+      <c r="H277" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7039,13 +7013,13 @@
       <c r="D278" t="s">
         <v>152</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>195</v>
       </c>
-      <c r="H278" s="2">
+      <c r="H278" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7062,13 +7036,13 @@
       <c r="D279" t="s">
         <v>150</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>194</v>
       </c>
-      <c r="H279" s="2">
+      <c r="H279" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7082,7 +7056,7 @@
       <c r="C280" t="s">
         <v>107</v>
       </c>
-      <c r="H280" s="2">
+      <c r="H280" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7099,13 +7073,13 @@
       <c r="D281" t="s">
         <v>153</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>190</v>
       </c>
-      <c r="H281" s="2">
+      <c r="H281" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7128,7 +7102,7 @@
       <c r="G282" t="s">
         <v>171</v>
       </c>
-      <c r="H282" s="2">
+      <c r="H282" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7142,7 +7116,7 @@
       <c r="C283" t="s">
         <v>111</v>
       </c>
-      <c r="H283" s="2">
+      <c r="H283" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7156,7 +7130,7 @@
       <c r="C284" t="s">
         <v>107</v>
       </c>
-      <c r="H284" s="2">
+      <c r="H284" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7179,7 +7153,7 @@
       <c r="G285" t="s">
         <v>166</v>
       </c>
-      <c r="H285" s="2">
+      <c r="H285" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7196,7 +7170,7 @@
       <c r="D286" t="s">
         <v>124</v>
       </c>
-      <c r="H286" s="2">
+      <c r="H286" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7219,7 +7193,7 @@
       <c r="G287" t="s">
         <v>167</v>
       </c>
-      <c r="H287" s="2">
+      <c r="H287" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7236,13 +7210,13 @@
       <c r="D288" t="s">
         <v>146</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>191</v>
       </c>
-      <c r="H288" s="2">
+      <c r="H288" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7265,7 +7239,7 @@
       <c r="G289" t="s">
         <v>168</v>
       </c>
-      <c r="H289" s="2">
+      <c r="H289" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7288,7 +7262,7 @@
       <c r="G290" t="s">
         <v>168</v>
       </c>
-      <c r="H290" s="2">
+      <c r="H290" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7311,7 +7285,7 @@
       <c r="G291" t="s">
         <v>169</v>
       </c>
-      <c r="H291" s="2">
+      <c r="H291" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7325,7 +7299,7 @@
       <c r="C292" t="s">
         <v>107</v>
       </c>
-      <c r="H292" s="2">
+      <c r="H292" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7348,7 +7322,7 @@
       <c r="G293" t="s">
         <v>172</v>
       </c>
-      <c r="H293" s="2">
+      <c r="H293" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7362,7 +7336,7 @@
       <c r="C294" t="s">
         <v>107</v>
       </c>
-      <c r="H294" s="2">
+      <c r="H294" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7385,7 +7359,7 @@
       <c r="G295" t="s">
         <v>173</v>
       </c>
-      <c r="H295" s="2">
+      <c r="H295" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7399,7 +7373,7 @@
       <c r="C296" t="s">
         <v>107</v>
       </c>
-      <c r="H296" s="2">
+      <c r="H296" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7413,7 +7387,7 @@
       <c r="C297" t="s">
         <v>111</v>
       </c>
-      <c r="H297" s="2">
+      <c r="H297" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7436,7 +7410,7 @@
       <c r="G298" t="s">
         <v>174</v>
       </c>
-      <c r="H298" s="2">
+      <c r="H298" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7453,13 +7427,13 @@
       <c r="D299" t="s">
         <v>117</v>
       </c>
-      <c r="E299" s="2">
+      <c r="E299" s="1">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>180</v>
       </c>
-      <c r="H299" s="2">
+      <c r="H299" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7473,7 +7447,7 @@
       <c r="C300" t="s">
         <v>107</v>
       </c>
-      <c r="H300" s="2">
+      <c r="H300" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7490,13 +7464,13 @@
       <c r="D301" t="s">
         <v>148</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301" s="1">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>192</v>
       </c>
-      <c r="H301" s="2">
+      <c r="H301" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7513,13 +7487,13 @@
       <c r="D302" t="s">
         <v>149</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302" s="1">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>189</v>
       </c>
-      <c r="H302" s="2">
+      <c r="H302" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7533,7 +7507,7 @@
       <c r="C303" t="s">
         <v>107</v>
       </c>
-      <c r="H303" s="2">
+      <c r="H303" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7547,7 +7521,7 @@
       <c r="C304" t="s">
         <v>107</v>
       </c>
-      <c r="H304" s="2">
+      <c r="H304" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7564,13 +7538,13 @@
       <c r="D305" t="s">
         <v>120</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305" s="1">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>193</v>
       </c>
-      <c r="H305" s="2">
+      <c r="H305" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7584,7 +7558,7 @@
       <c r="C306" t="s">
         <v>107</v>
       </c>
-      <c r="H306" s="2">
+      <c r="H306" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7601,13 +7575,13 @@
       <c r="D307" t="s">
         <v>152</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307" s="1">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>195</v>
       </c>
-      <c r="H307" s="2">
+      <c r="H307" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7621,7 +7595,7 @@
       <c r="C308" t="s">
         <v>111</v>
       </c>
-      <c r="H308" s="2">
+      <c r="H308" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7644,7 +7618,7 @@
       <c r="G309" t="s">
         <v>172</v>
       </c>
-      <c r="H309" s="2">
+      <c r="H309" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7667,7 +7641,7 @@
       <c r="G310" t="s">
         <v>175</v>
       </c>
-      <c r="H310" s="2">
+      <c r="H310" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7684,7 +7658,7 @@
       <c r="D311" t="s">
         <v>158</v>
       </c>
-      <c r="H311" s="2">
+      <c r="H311" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7698,7 +7672,7 @@
       <c r="C312" t="s">
         <v>111</v>
       </c>
-      <c r="H312" s="2">
+      <c r="H312" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7712,7 +7686,7 @@
       <c r="C313" t="s">
         <v>107</v>
       </c>
-      <c r="H313" s="2">
+      <c r="H313" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7735,7 +7709,7 @@
       <c r="G314" t="s">
         <v>166</v>
       </c>
-      <c r="H314" s="2">
+      <c r="H314" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7752,7 +7726,7 @@
       <c r="D315" t="s">
         <v>124</v>
       </c>
-      <c r="H315" s="2">
+      <c r="H315" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7775,7 +7749,7 @@
       <c r="G316" t="s">
         <v>167</v>
       </c>
-      <c r="H316" s="2">
+      <c r="H316" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7798,7 +7772,7 @@
       <c r="G317" t="s">
         <v>176</v>
       </c>
-      <c r="H317" s="2">
+      <c r="H317" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7821,7 +7795,7 @@
       <c r="G318" t="s">
         <v>168</v>
       </c>
-      <c r="H318" s="2">
+      <c r="H318" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7844,7 +7818,7 @@
       <c r="G319" t="s">
         <v>168</v>
       </c>
-      <c r="H319" s="2">
+      <c r="H319" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7867,7 +7841,7 @@
       <c r="G320" t="s">
         <v>169</v>
       </c>
-      <c r="H320" s="2">
+      <c r="H320" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7881,7 +7855,7 @@
       <c r="C321" t="s">
         <v>107</v>
       </c>
-      <c r="H321" s="2">
+      <c r="H321" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -7904,7 +7878,7 @@
       <c r="G322" t="s">
         <v>177</v>
       </c>
-      <c r="H322" s="2">
+      <c r="H322" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -7918,7 +7892,7 @@
       <c r="C323" t="s">
         <v>107</v>
       </c>
-      <c r="H323" s="2">
+      <c r="H323" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -7941,7 +7915,7 @@
       <c r="G324" t="s">
         <v>178</v>
       </c>
-      <c r="H324" s="2">
+      <c r="H324" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -7955,7 +7929,7 @@
       <c r="C325" t="s">
         <v>107</v>
       </c>
-      <c r="H325" s="2">
+      <c r="H325" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -7969,7 +7943,7 @@
       <c r="C326" t="s">
         <v>111</v>
       </c>
-      <c r="H326" s="2">
+      <c r="H326" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -7983,7 +7957,7 @@
       <c r="C327" t="s">
         <v>111</v>
       </c>
-      <c r="H327" s="2">
+      <c r="H327" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8000,13 +7974,13 @@
       <c r="D328" t="s">
         <v>117</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328" s="1">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>180</v>
       </c>
-      <c r="H328" s="2">
+      <c r="H328" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8029,7 +8003,7 @@
       <c r="G329" t="s">
         <v>178</v>
       </c>
-      <c r="H329" s="2">
+      <c r="H329" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8052,7 +8026,7 @@
       <c r="G330" t="s">
         <v>178</v>
       </c>
-      <c r="H330" s="2">
+      <c r="H330" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8066,7 +8040,7 @@
       <c r="C331" t="s">
         <v>107</v>
       </c>
-      <c r="H331" s="2">
+      <c r="H331" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8089,7 +8063,7 @@
       <c r="G332" t="s">
         <v>178</v>
       </c>
-      <c r="H332" s="2">
+      <c r="H332" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8112,7 +8086,7 @@
       <c r="G333" t="s">
         <v>177</v>
       </c>
-      <c r="H333" s="2">
+      <c r="H333" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8129,13 +8103,13 @@
       <c r="D334" t="s">
         <v>120</v>
       </c>
-      <c r="E334" s="2">
+      <c r="E334" s="1">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>193</v>
       </c>
-      <c r="H334" s="2">
+      <c r="H334" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8149,7 +8123,7 @@
       <c r="C335" t="s">
         <v>107</v>
       </c>
-      <c r="H335" s="2">
+      <c r="H335" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8166,13 +8140,13 @@
       <c r="D336" t="s">
         <v>152</v>
       </c>
-      <c r="E336" s="2">
+      <c r="E336" s="1">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>195</v>
       </c>
-      <c r="H336" s="2">
+      <c r="H336" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8186,7 +8160,7 @@
       <c r="C337" t="s">
         <v>107</v>
       </c>
-      <c r="H337" s="2">
+      <c r="H337" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8200,7 +8174,7 @@
       <c r="C338" t="s">
         <v>107</v>
       </c>
-      <c r="H338" s="2">
+      <c r="H338" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8223,7 +8197,7 @@
       <c r="G339" t="s">
         <v>175</v>
       </c>
-      <c r="H339" s="2">
+      <c r="H339" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8240,7 +8214,7 @@
       <c r="D340" t="s">
         <v>163</v>
       </c>
-      <c r="H340" s="2">
+      <c r="H340" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8254,7 +8228,7 @@
       <c r="C341" t="s">
         <v>111</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8268,7 +8242,7 @@
       <c r="C342" t="s">
         <v>107</v>
       </c>
-      <c r="H342" s="2">
+      <c r="H342" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8291,7 +8265,7 @@
       <c r="G343" t="s">
         <v>166</v>
       </c>
-      <c r="H343" s="2">
+      <c r="H343" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8308,7 +8282,7 @@
       <c r="D344" t="s">
         <v>124</v>
       </c>
-      <c r="H344" s="2">
+      <c r="H344" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8331,7 +8305,7 @@
       <c r="G345" t="s">
         <v>167</v>
       </c>
-      <c r="H345" s="2">
+      <c r="H345" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8354,7 +8328,7 @@
       <c r="G346" t="s">
         <v>176</v>
       </c>
-      <c r="H346" s="2">
+      <c r="H346" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8377,7 +8351,7 @@
       <c r="G347" t="s">
         <v>168</v>
       </c>
-      <c r="H347" s="2">
+      <c r="H347" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8400,7 +8374,7 @@
       <c r="G348" t="s">
         <v>168</v>
       </c>
-      <c r="H348" s="2">
+      <c r="H348" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8423,7 +8397,7 @@
       <c r="G349" t="s">
         <v>169</v>
       </c>
-      <c r="H349" s="2">
+      <c r="H349" s="1">
         <v>46224</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -639,16 +639,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -664,7 +656,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -672,30 +664,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -995,72 +969,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1125,7 +1099,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1190,7 +1164,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1255,7 +1229,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1320,7 +1294,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1385,7 +1359,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1450,7 +1424,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1515,7 +1489,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1580,7 +1554,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1645,7 +1619,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1710,7 +1684,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1775,7 +1749,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -1840,7 +1814,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -1915,28 +1889,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1950,7 +1924,7 @@
       <c r="C2" t="s">
         <v>112</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1964,7 +1938,7 @@
       <c r="C3" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -1987,7 +1961,7 @@
       <c r="G4" t="s">
         <v>170</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2001,7 +1975,7 @@
       <c r="C5" t="s">
         <v>112</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2015,7 +1989,7 @@
       <c r="C6" t="s">
         <v>112</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2032,13 +2006,13 @@
       <c r="D7" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2055,13 +2029,13 @@
       <c r="D8" t="s">
         <v>121</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>188</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2078,13 +2052,13 @@
       <c r="D9" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>189</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2101,13 +2075,13 @@
       <c r="D10" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>190</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2121,7 +2095,7 @@
       <c r="C11" t="s">
         <v>112</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2135,7 +2109,7 @@
       <c r="C12" t="s">
         <v>112</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2152,13 +2126,13 @@
       <c r="D13" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>188</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2172,7 +2146,7 @@
       <c r="C14" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2189,13 +2163,13 @@
       <c r="D15" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>191</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2209,7 +2183,7 @@
       <c r="C16" t="s">
         <v>112</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2223,7 +2197,7 @@
       <c r="C17" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2240,13 +2214,13 @@
       <c r="D18" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>192</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2260,7 +2234,7 @@
       <c r="C19" t="s">
         <v>112</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2277,13 +2251,13 @@
       <c r="D20" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>188</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2306,7 +2280,7 @@
       <c r="G21" t="s">
         <v>171</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2320,7 +2294,7 @@
       <c r="C22" t="s">
         <v>116</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2334,7 +2308,7 @@
       <c r="C23" t="s">
         <v>112</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2357,7 +2331,7 @@
       <c r="G24" t="s">
         <v>172</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2374,7 +2348,7 @@
       <c r="D25" t="s">
         <v>129</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2397,7 +2371,7 @@
       <c r="G26" t="s">
         <v>173</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2414,13 +2388,13 @@
       <c r="D27" t="s">
         <v>131</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>193</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2443,7 +2417,7 @@
       <c r="G28" t="s">
         <v>174</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2466,7 +2440,7 @@
       <c r="G29" t="s">
         <v>174</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2489,7 +2463,7 @@
       <c r="G30" t="s">
         <v>175</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2503,7 +2477,7 @@
       <c r="C31" t="s">
         <v>112</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2517,7 +2491,7 @@
       <c r="C32" t="s">
         <v>112</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2540,7 +2514,7 @@
       <c r="G33" t="s">
         <v>176</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2554,7 +2528,7 @@
       <c r="C34" t="s">
         <v>112</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2568,7 +2542,7 @@
       <c r="C35" t="s">
         <v>112</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2585,13 +2559,13 @@
       <c r="D36" t="s">
         <v>120</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>188</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2608,13 +2582,13 @@
       <c r="D37" t="s">
         <v>121</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>188</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2631,13 +2605,13 @@
       <c r="D38" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>189</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2654,13 +2628,13 @@
       <c r="D39" t="s">
         <v>123</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>190</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2674,7 +2648,7 @@
       <c r="C40" t="s">
         <v>112</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2688,7 +2662,7 @@
       <c r="C41" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2705,13 +2679,13 @@
       <c r="D42" t="s">
         <v>124</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>188</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2725,7 +2699,7 @@
       <c r="C43" t="s">
         <v>112</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2742,13 +2716,13 @@
       <c r="D44" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>191</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2762,7 +2736,7 @@
       <c r="C45" t="s">
         <v>112</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2776,7 +2750,7 @@
       <c r="C46" t="s">
         <v>112</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2790,7 +2764,7 @@
       <c r="C47" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2804,7 +2778,7 @@
       <c r="C48" t="s">
         <v>112</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2821,13 +2795,13 @@
       <c r="D49" t="s">
         <v>136</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>188</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2850,7 +2824,7 @@
       <c r="G50" t="s">
         <v>171</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2864,7 +2838,7 @@
       <c r="C51" t="s">
         <v>116</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2878,7 +2852,7 @@
       <c r="C52" t="s">
         <v>112</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2901,7 +2875,7 @@
       <c r="G53" t="s">
         <v>172</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2918,7 +2892,7 @@
       <c r="D54" t="s">
         <v>129</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2941,7 +2915,7 @@
       <c r="G55" t="s">
         <v>173</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2958,13 +2932,13 @@
       <c r="D56" t="s">
         <v>131</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>193</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2987,7 +2961,7 @@
       <c r="G57" t="s">
         <v>174</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3010,7 +2984,7 @@
       <c r="G58" t="s">
         <v>174</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3033,7 +3007,7 @@
       <c r="G59" t="s">
         <v>175</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3047,7 +3021,7 @@
       <c r="C60" t="s">
         <v>112</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3061,7 +3035,7 @@
       <c r="C61" t="s">
         <v>112</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3078,13 +3052,13 @@
       <c r="D62" t="s">
         <v>135</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>194</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3098,7 +3072,7 @@
       <c r="C63" t="s">
         <v>112</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3115,13 +3089,13 @@
       <c r="D64" t="s">
         <v>137</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>195</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3135,7 +3109,7 @@
       <c r="C65" t="s">
         <v>112</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3149,7 +3123,7 @@
       <c r="C66" t="s">
         <v>116</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3166,13 +3140,13 @@
       <c r="D67" t="s">
         <v>122</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>189</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3189,13 +3163,13 @@
       <c r="D68" t="s">
         <v>123</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>190</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3209,7 +3183,7 @@
       <c r="C69" t="s">
         <v>112</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3223,7 +3197,7 @@
       <c r="C70" t="s">
         <v>112</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3240,13 +3214,13 @@
       <c r="D71" t="s">
         <v>124</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>194</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3260,7 +3234,7 @@
       <c r="C72" t="s">
         <v>112</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3277,13 +3251,13 @@
       <c r="D73" t="s">
         <v>125</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>191</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3297,7 +3271,7 @@
       <c r="C74" t="s">
         <v>112</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3311,7 +3285,7 @@
       <c r="C75" t="s">
         <v>112</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3325,7 +3299,7 @@
       <c r="C76" t="s">
         <v>112</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3339,7 +3313,7 @@
       <c r="C77" t="s">
         <v>112</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3356,13 +3330,13 @@
       <c r="D78" t="s">
         <v>136</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>194</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3385,7 +3359,7 @@
       <c r="G79" t="s">
         <v>177</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3399,7 +3373,7 @@
       <c r="C80" t="s">
         <v>116</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3413,7 +3387,7 @@
       <c r="C81" t="s">
         <v>112</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3436,7 +3410,7 @@
       <c r="G82" t="s">
         <v>172</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3453,7 +3427,7 @@
       <c r="D83" t="s">
         <v>129</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3476,7 +3450,7 @@
       <c r="G84" t="s">
         <v>173</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3493,13 +3467,13 @@
       <c r="D85" t="s">
         <v>131</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>193</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3522,7 +3496,7 @@
       <c r="G86" t="s">
         <v>174</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3545,7 +3519,7 @@
       <c r="G87" t="s">
         <v>174</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3568,7 +3542,7 @@
       <c r="G88" t="s">
         <v>175</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3582,7 +3556,7 @@
       <c r="C89" t="s">
         <v>112</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3599,13 +3573,13 @@
       <c r="D90" t="s">
         <v>139</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>195</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3622,13 +3596,13 @@
       <c r="D91" t="s">
         <v>135</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>194</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3642,7 +3616,7 @@
       <c r="C92" t="s">
         <v>112</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3659,13 +3633,13 @@
       <c r="D93" t="s">
         <v>137</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>195</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3679,7 +3653,7 @@
       <c r="C94" t="s">
         <v>112</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3693,7 +3667,7 @@
       <c r="C95" t="s">
         <v>116</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3710,13 +3684,13 @@
       <c r="D96" t="s">
         <v>122</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>189</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3733,13 +3707,13 @@
       <c r="D97" t="s">
         <v>123</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>190</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3753,7 +3727,7 @@
       <c r="C98" t="s">
         <v>112</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3770,13 +3744,13 @@
       <c r="D99" t="s">
         <v>140</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>190</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3793,13 +3767,13 @@
       <c r="D100" t="s">
         <v>124</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>190</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3813,7 +3787,7 @@
       <c r="C101" t="s">
         <v>112</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3830,13 +3804,13 @@
       <c r="D102" t="s">
         <v>125</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>191</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3853,13 +3827,13 @@
       <c r="D103" t="s">
         <v>141</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>190</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3873,7 +3847,7 @@
       <c r="C104" t="s">
         <v>112</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3887,7 +3861,7 @@
       <c r="C105" t="s">
         <v>112</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3901,7 +3875,7 @@
       <c r="C106" t="s">
         <v>112</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3918,13 +3892,13 @@
       <c r="D107" t="s">
         <v>142</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>190</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3947,7 +3921,7 @@
       <c r="G108" t="s">
         <v>177</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3961,7 +3935,7 @@
       <c r="C109" t="s">
         <v>116</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3975,7 +3949,7 @@
       <c r="C110" t="s">
         <v>112</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3998,7 +3972,7 @@
       <c r="G111" t="s">
         <v>172</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4015,7 +3989,7 @@
       <c r="D112" t="s">
         <v>129</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4038,7 +4012,7 @@
       <c r="G113" t="s">
         <v>173</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4055,13 +4029,13 @@
       <c r="D114" t="s">
         <v>131</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>193</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4084,7 +4058,7 @@
       <c r="G115" t="s">
         <v>174</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4107,7 +4081,7 @@
       <c r="G116" t="s">
         <v>174</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4130,7 +4104,7 @@
       <c r="G117" t="s">
         <v>175</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4144,7 +4118,7 @@
       <c r="C118" t="s">
         <v>112</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4161,13 +4135,13 @@
       <c r="D119" t="s">
         <v>139</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>195</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4181,7 +4155,7 @@
       <c r="C120" t="s">
         <v>116</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4195,7 +4169,7 @@
       <c r="C121" t="s">
         <v>112</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4209,7 +4183,7 @@
       <c r="C122" t="s">
         <v>116</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4223,7 +4197,7 @@
       <c r="C123" t="s">
         <v>116</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4237,7 +4211,7 @@
       <c r="C124" t="s">
         <v>116</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4254,13 +4228,13 @@
       <c r="D125" t="s">
         <v>122</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>189</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4277,13 +4251,13 @@
       <c r="D126" t="s">
         <v>123</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>190</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4297,7 +4271,7 @@
       <c r="C127" t="s">
         <v>112</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4314,13 +4288,13 @@
       <c r="D128" t="s">
         <v>140</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>190</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4337,13 +4311,13 @@
       <c r="D129" t="s">
         <v>124</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>190</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4357,7 +4331,7 @@
       <c r="C130" t="s">
         <v>112</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4374,13 +4348,13 @@
       <c r="D131" t="s">
         <v>125</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>191</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4397,13 +4371,13 @@
       <c r="D132" t="s">
         <v>141</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>190</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4417,7 +4391,7 @@
       <c r="C133" t="s">
         <v>112</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4431,7 +4405,7 @@
       <c r="C134" t="s">
         <v>112</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4445,7 +4419,7 @@
       <c r="C135" t="s">
         <v>112</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4462,13 +4436,13 @@
       <c r="D136" t="s">
         <v>143</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>190</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4491,7 +4465,7 @@
       <c r="G137" t="s">
         <v>177</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4505,7 +4479,7 @@
       <c r="C138" t="s">
         <v>116</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4519,7 +4493,7 @@
       <c r="C139" t="s">
         <v>112</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4542,7 +4516,7 @@
       <c r="G140" t="s">
         <v>172</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4559,7 +4533,7 @@
       <c r="D141" t="s">
         <v>129</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4582,7 +4556,7 @@
       <c r="G142" t="s">
         <v>173</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4599,13 +4573,13 @@
       <c r="D143" t="s">
         <v>131</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>193</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4628,7 +4602,7 @@
       <c r="G144" t="s">
         <v>174</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4651,7 +4625,7 @@
       <c r="G145" t="s">
         <v>174</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4674,7 +4648,7 @@
       <c r="G146" t="s">
         <v>175</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4688,7 +4662,7 @@
       <c r="C147" t="s">
         <v>112</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4705,13 +4679,13 @@
       <c r="D148" t="s">
         <v>139</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>195</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4725,7 +4699,7 @@
       <c r="C149" t="s">
         <v>116</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4739,7 +4713,7 @@
       <c r="C150" t="s">
         <v>112</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4753,7 +4727,7 @@
       <c r="C151" t="s">
         <v>112</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4767,7 +4741,7 @@
       <c r="C152" t="s">
         <v>116</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4781,7 +4755,7 @@
       <c r="C153" t="s">
         <v>116</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4798,13 +4772,13 @@
       <c r="D154" t="s">
         <v>122</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>189</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4821,13 +4795,13 @@
       <c r="D155" t="s">
         <v>123</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>190</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4841,7 +4815,7 @@
       <c r="C156" t="s">
         <v>112</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4858,13 +4832,13 @@
       <c r="D157" t="s">
         <v>140</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>190</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4881,13 +4855,13 @@
       <c r="D158" t="s">
         <v>124</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>190</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4904,13 +4878,13 @@
       <c r="D159" t="s">
         <v>144</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>196</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4927,13 +4901,13 @@
       <c r="D160" t="s">
         <v>125</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>191</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4950,13 +4924,13 @@
       <c r="D161" t="s">
         <v>141</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>190</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4970,7 +4944,7 @@
       <c r="C162" t="s">
         <v>112</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4984,7 +4958,7 @@
       <c r="C163" t="s">
         <v>112</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4998,7 +4972,7 @@
       <c r="C164" t="s">
         <v>112</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5015,13 +4989,13 @@
       <c r="D165" t="s">
         <v>143</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>190</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5044,7 +5018,7 @@
       <c r="G166" t="s">
         <v>177</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5058,7 +5032,7 @@
       <c r="C167" t="s">
         <v>116</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5072,7 +5046,7 @@
       <c r="C168" t="s">
         <v>112</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5095,7 +5069,7 @@
       <c r="G169" t="s">
         <v>172</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5112,7 +5086,7 @@
       <c r="D170" t="s">
         <v>129</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5135,7 +5109,7 @@
       <c r="G171" t="s">
         <v>173</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5152,13 +5126,13 @@
       <c r="D172" t="s">
         <v>131</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>193</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5181,7 +5155,7 @@
       <c r="G173" t="s">
         <v>174</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5204,7 +5178,7 @@
       <c r="G174" t="s">
         <v>174</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5227,7 +5201,7 @@
       <c r="G175" t="s">
         <v>175</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5241,7 +5215,7 @@
       <c r="C176" t="s">
         <v>112</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5258,13 +5232,13 @@
       <c r="D177" t="s">
         <v>145</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>195</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5278,7 +5252,7 @@
       <c r="C178" t="s">
         <v>112</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5295,13 +5269,13 @@
       <c r="D179" t="s">
         <v>146</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>191</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5315,7 +5289,7 @@
       <c r="C180" t="s">
         <v>112</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5329,7 +5303,7 @@
       <c r="C181" t="s">
         <v>116</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5343,7 +5317,7 @@
       <c r="C182" t="s">
         <v>116</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5360,13 +5334,13 @@
       <c r="D183" t="s">
         <v>122</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>189</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5383,13 +5357,13 @@
       <c r="D184" t="s">
         <v>123</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>190</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5403,7 +5377,7 @@
       <c r="C185" t="s">
         <v>112</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5420,13 +5394,13 @@
       <c r="D186" t="s">
         <v>140</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>190</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5443,13 +5417,13 @@
       <c r="D187" t="s">
         <v>147</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>190</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5466,13 +5440,13 @@
       <c r="D188" t="s">
         <v>148</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>190</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5489,13 +5463,13 @@
       <c r="D189" t="s">
         <v>125</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>191</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5512,13 +5486,13 @@
       <c r="D190" t="s">
         <v>141</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>190</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5532,7 +5506,7 @@
       <c r="C191" t="s">
         <v>112</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5546,7 +5520,7 @@
       <c r="C192" t="s">
         <v>112</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5560,7 +5534,7 @@
       <c r="C193" t="s">
         <v>112</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5577,13 +5551,13 @@
       <c r="D194" t="s">
         <v>143</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>197</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5606,7 +5580,7 @@
       <c r="G195" t="s">
         <v>177</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5620,7 +5594,7 @@
       <c r="C196" t="s">
         <v>116</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5634,7 +5608,7 @@
       <c r="C197" t="s">
         <v>112</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5657,7 +5631,7 @@
       <c r="G198" t="s">
         <v>172</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5674,7 +5648,7 @@
       <c r="D199" t="s">
         <v>129</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5697,7 +5671,7 @@
       <c r="G200" t="s">
         <v>173</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5714,13 +5688,13 @@
       <c r="D201" t="s">
         <v>131</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>193</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5743,7 +5717,7 @@
       <c r="G202" t="s">
         <v>174</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5766,7 +5740,7 @@
       <c r="G203" t="s">
         <v>174</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5789,7 +5763,7 @@
       <c r="G204" t="s">
         <v>175</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5803,7 +5777,7 @@
       <c r="C205" t="s">
         <v>112</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5820,13 +5794,13 @@
       <c r="D206" t="s">
         <v>145</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>195</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5840,7 +5814,7 @@
       <c r="C207" t="s">
         <v>112</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5854,7 +5828,7 @@
       <c r="C208" t="s">
         <v>116</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5868,7 +5842,7 @@
       <c r="C209" t="s">
         <v>112</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5882,7 +5856,7 @@
       <c r="C210" t="s">
         <v>116</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5896,7 +5870,7 @@
       <c r="C211" t="s">
         <v>116</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5913,13 +5887,13 @@
       <c r="D212" t="s">
         <v>122</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>189</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5933,7 +5907,7 @@
       <c r="C213" t="s">
         <v>116</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5947,7 +5921,7 @@
       <c r="C214" t="s">
         <v>112</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5964,13 +5938,13 @@
       <c r="D215" t="s">
         <v>140</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>198</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5987,13 +5961,13 @@
       <c r="D216" t="s">
         <v>147</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>191</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6007,7 +5981,7 @@
       <c r="C217" t="s">
         <v>112</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6024,13 +5998,13 @@
       <c r="D218" t="s">
         <v>125</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>191</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6044,7 +6018,7 @@
       <c r="C219" t="s">
         <v>112</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6058,7 +6032,7 @@
       <c r="C220" t="s">
         <v>112</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6075,13 +6049,13 @@
       <c r="D221" t="s">
         <v>149</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>195</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6095,7 +6069,7 @@
       <c r="C222" t="s">
         <v>112</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6112,13 +6086,13 @@
       <c r="D223" t="s">
         <v>150</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>199</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6141,7 +6115,7 @@
       <c r="G224" t="s">
         <v>177</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6155,7 +6129,7 @@
       <c r="C225" t="s">
         <v>116</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6169,7 +6143,7 @@
       <c r="C226" t="s">
         <v>112</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6192,7 +6166,7 @@
       <c r="G227" t="s">
         <v>172</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6209,7 +6183,7 @@
       <c r="D228" t="s">
         <v>129</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6232,7 +6206,7 @@
       <c r="G229" t="s">
         <v>173</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6249,13 +6223,13 @@
       <c r="D230" t="s">
         <v>151</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>200</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6278,7 +6252,7 @@
       <c r="G231" t="s">
         <v>174</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6301,7 +6275,7 @@
       <c r="G232" t="s">
         <v>174</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6324,7 +6298,7 @@
       <c r="G233" t="s">
         <v>175</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6338,7 +6312,7 @@
       <c r="C234" t="s">
         <v>112</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6355,13 +6329,13 @@
       <c r="D235" t="s">
         <v>152</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>195</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6375,7 +6349,7 @@
       <c r="C236" t="s">
         <v>112</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6389,7 +6363,7 @@
       <c r="C237" t="s">
         <v>116</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6403,7 +6377,7 @@
       <c r="C238" t="s">
         <v>112</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6417,7 +6391,7 @@
       <c r="C239" t="s">
         <v>116</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6431,7 +6405,7 @@
       <c r="C240" t="s">
         <v>116</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6448,13 +6422,13 @@
       <c r="D241" t="s">
         <v>122</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>189</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6468,7 +6442,7 @@
       <c r="C242" t="s">
         <v>116</v>
       </c>
-      <c r="H242" s="2">
+      <c r="H242" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6485,13 +6459,13 @@
       <c r="D243" t="s">
         <v>153</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>201</v>
       </c>
-      <c r="H243" s="2">
+      <c r="H243" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6508,13 +6482,13 @@
       <c r="D244" t="s">
         <v>154</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>198</v>
       </c>
-      <c r="H244" s="2">
+      <c r="H244" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6528,7 +6502,7 @@
       <c r="C245" t="s">
         <v>116</v>
       </c>
-      <c r="H245" s="2">
+      <c r="H245" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6542,7 +6516,7 @@
       <c r="C246" t="s">
         <v>112</v>
       </c>
-      <c r="H246" s="2">
+      <c r="H246" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6559,13 +6533,13 @@
       <c r="D247" t="s">
         <v>125</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>202</v>
       </c>
-      <c r="H247" s="2">
+      <c r="H247" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6579,7 +6553,7 @@
       <c r="C248" t="s">
         <v>112</v>
       </c>
-      <c r="H248" s="2">
+      <c r="H248" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6593,7 +6567,7 @@
       <c r="C249" t="s">
         <v>112</v>
       </c>
-      <c r="H249" s="2">
+      <c r="H249" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6610,13 +6584,13 @@
       <c r="D250" t="s">
         <v>155</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>197</v>
       </c>
-      <c r="H250" s="2">
+      <c r="H250" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6630,7 +6604,7 @@
       <c r="C251" t="s">
         <v>112</v>
       </c>
-      <c r="H251" s="2">
+      <c r="H251" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6647,13 +6621,13 @@
       <c r="D252" t="s">
         <v>156</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>199</v>
       </c>
-      <c r="H252" s="2">
+      <c r="H252" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6676,7 +6650,7 @@
       <c r="G253" t="s">
         <v>177</v>
       </c>
-      <c r="H253" s="2">
+      <c r="H253" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6690,7 +6664,7 @@
       <c r="C254" t="s">
         <v>116</v>
       </c>
-      <c r="H254" s="2">
+      <c r="H254" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6704,7 +6678,7 @@
       <c r="C255" t="s">
         <v>112</v>
       </c>
-      <c r="H255" s="2">
+      <c r="H255" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6727,7 +6701,7 @@
       <c r="G256" t="s">
         <v>172</v>
       </c>
-      <c r="H256" s="2">
+      <c r="H256" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6744,7 +6718,7 @@
       <c r="D257" t="s">
         <v>129</v>
       </c>
-      <c r="H257" s="2">
+      <c r="H257" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6767,7 +6741,7 @@
       <c r="G258" t="s">
         <v>173</v>
       </c>
-      <c r="H258" s="2">
+      <c r="H258" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6784,13 +6758,13 @@
       <c r="D259" t="s">
         <v>151</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>200</v>
       </c>
-      <c r="H259" s="2">
+      <c r="H259" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6813,7 +6787,7 @@
       <c r="G260" t="s">
         <v>174</v>
       </c>
-      <c r="H260" s="2">
+      <c r="H260" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6836,7 +6810,7 @@
       <c r="G261" t="s">
         <v>174</v>
       </c>
-      <c r="H261" s="2">
+      <c r="H261" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6859,7 +6833,7 @@
       <c r="G262" t="s">
         <v>175</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6873,7 +6847,7 @@
       <c r="C263" t="s">
         <v>112</v>
       </c>
-      <c r="H263" s="2">
+      <c r="H263" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6890,13 +6864,13 @@
       <c r="D264" t="s">
         <v>152</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>195</v>
       </c>
-      <c r="H264" s="2">
+      <c r="H264" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6910,7 +6884,7 @@
       <c r="C265" t="s">
         <v>112</v>
       </c>
-      <c r="H265" s="2">
+      <c r="H265" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6924,7 +6898,7 @@
       <c r="C266" t="s">
         <v>116</v>
       </c>
-      <c r="H266" s="2">
+      <c r="H266" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6938,7 +6912,7 @@
       <c r="C267" t="s">
         <v>112</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H267" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6952,7 +6926,7 @@
       <c r="C268" t="s">
         <v>116</v>
       </c>
-      <c r="H268" s="2">
+      <c r="H268" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6966,7 +6940,7 @@
       <c r="C269" t="s">
         <v>116</v>
       </c>
-      <c r="H269" s="2">
+      <c r="H269" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6983,13 +6957,13 @@
       <c r="D270" t="s">
         <v>122</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>189</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H270" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7003,7 +6977,7 @@
       <c r="C271" t="s">
         <v>116</v>
       </c>
-      <c r="H271" s="2">
+      <c r="H271" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7020,13 +6994,13 @@
       <c r="D272" t="s">
         <v>153</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>201</v>
       </c>
-      <c r="H272" s="2">
+      <c r="H272" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7043,13 +7017,13 @@
       <c r="D273" t="s">
         <v>154</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>203</v>
       </c>
-      <c r="H273" s="2">
+      <c r="H273" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7063,7 +7037,7 @@
       <c r="C274" t="s">
         <v>112</v>
       </c>
-      <c r="H274" s="2">
+      <c r="H274" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7077,7 +7051,7 @@
       <c r="C275" t="s">
         <v>112</v>
       </c>
-      <c r="H275" s="2">
+      <c r="H275" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7094,13 +7068,13 @@
       <c r="D276" t="s">
         <v>125</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>202</v>
       </c>
-      <c r="H276" s="2">
+      <c r="H276" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7114,7 +7088,7 @@
       <c r="C277" t="s">
         <v>112</v>
       </c>
-      <c r="H277" s="2">
+      <c r="H277" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7131,13 +7105,13 @@
       <c r="D278" t="s">
         <v>157</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>204</v>
       </c>
-      <c r="H278" s="2">
+      <c r="H278" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7154,13 +7128,13 @@
       <c r="D279" t="s">
         <v>155</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>203</v>
       </c>
-      <c r="H279" s="2">
+      <c r="H279" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7174,7 +7148,7 @@
       <c r="C280" t="s">
         <v>112</v>
       </c>
-      <c r="H280" s="2">
+      <c r="H280" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7191,13 +7165,13 @@
       <c r="D281" t="s">
         <v>158</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>199</v>
       </c>
-      <c r="H281" s="2">
+      <c r="H281" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7220,7 +7194,7 @@
       <c r="G282" t="s">
         <v>177</v>
       </c>
-      <c r="H282" s="2">
+      <c r="H282" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7234,7 +7208,7 @@
       <c r="C283" t="s">
         <v>116</v>
       </c>
-      <c r="H283" s="2">
+      <c r="H283" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7248,7 +7222,7 @@
       <c r="C284" t="s">
         <v>112</v>
       </c>
-      <c r="H284" s="2">
+      <c r="H284" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7271,7 +7245,7 @@
       <c r="G285" t="s">
         <v>172</v>
       </c>
-      <c r="H285" s="2">
+      <c r="H285" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7288,7 +7262,7 @@
       <c r="D286" t="s">
         <v>129</v>
       </c>
-      <c r="H286" s="2">
+      <c r="H286" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7311,7 +7285,7 @@
       <c r="G287" t="s">
         <v>173</v>
       </c>
-      <c r="H287" s="2">
+      <c r="H287" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7328,13 +7302,13 @@
       <c r="D288" t="s">
         <v>151</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>200</v>
       </c>
-      <c r="H288" s="2">
+      <c r="H288" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7357,7 +7331,7 @@
       <c r="G289" t="s">
         <v>174</v>
       </c>
-      <c r="H289" s="2">
+      <c r="H289" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7380,7 +7354,7 @@
       <c r="G290" t="s">
         <v>174</v>
       </c>
-      <c r="H290" s="2">
+      <c r="H290" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7403,7 +7377,7 @@
       <c r="G291" t="s">
         <v>175</v>
       </c>
-      <c r="H291" s="2">
+      <c r="H291" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7417,7 +7391,7 @@
       <c r="C292" t="s">
         <v>112</v>
       </c>
-      <c r="H292" s="2">
+      <c r="H292" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7440,7 +7414,7 @@
       <c r="G293" t="s">
         <v>178</v>
       </c>
-      <c r="H293" s="2">
+      <c r="H293" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7454,7 +7428,7 @@
       <c r="C294" t="s">
         <v>112</v>
       </c>
-      <c r="H294" s="2">
+      <c r="H294" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7477,7 +7451,7 @@
       <c r="G295" t="s">
         <v>179</v>
       </c>
-      <c r="H295" s="2">
+      <c r="H295" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7491,7 +7465,7 @@
       <c r="C296" t="s">
         <v>112</v>
       </c>
-      <c r="H296" s="2">
+      <c r="H296" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7505,7 +7479,7 @@
       <c r="C297" t="s">
         <v>116</v>
       </c>
-      <c r="H297" s="2">
+      <c r="H297" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7528,7 +7502,7 @@
       <c r="G298" t="s">
         <v>180</v>
       </c>
-      <c r="H298" s="2">
+      <c r="H298" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7545,13 +7519,13 @@
       <c r="D299" t="s">
         <v>122</v>
       </c>
-      <c r="E299" s="2">
+      <c r="E299" s="1">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>189</v>
       </c>
-      <c r="H299" s="2">
+      <c r="H299" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7565,7 +7539,7 @@
       <c r="C300" t="s">
         <v>112</v>
       </c>
-      <c r="H300" s="2">
+      <c r="H300" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7582,13 +7556,13 @@
       <c r="D301" t="s">
         <v>153</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301" s="1">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>201</v>
       </c>
-      <c r="H301" s="2">
+      <c r="H301" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7605,13 +7579,13 @@
       <c r="D302" t="s">
         <v>154</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302" s="1">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>198</v>
       </c>
-      <c r="H302" s="2">
+      <c r="H302" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7625,7 +7599,7 @@
       <c r="C303" t="s">
         <v>112</v>
       </c>
-      <c r="H303" s="2">
+      <c r="H303" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7639,7 +7613,7 @@
       <c r="C304" t="s">
         <v>112</v>
       </c>
-      <c r="H304" s="2">
+      <c r="H304" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7656,13 +7630,13 @@
       <c r="D305" t="s">
         <v>125</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305" s="1">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>202</v>
       </c>
-      <c r="H305" s="2">
+      <c r="H305" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7676,7 +7650,7 @@
       <c r="C306" t="s">
         <v>112</v>
       </c>
-      <c r="H306" s="2">
+      <c r="H306" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7693,13 +7667,13 @@
       <c r="D307" t="s">
         <v>157</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307" s="1">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>204</v>
       </c>
-      <c r="H307" s="2">
+      <c r="H307" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7713,7 +7687,7 @@
       <c r="C308" t="s">
         <v>116</v>
       </c>
-      <c r="H308" s="2">
+      <c r="H308" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7736,7 +7710,7 @@
       <c r="G309" t="s">
         <v>178</v>
       </c>
-      <c r="H309" s="2">
+      <c r="H309" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7759,7 +7733,7 @@
       <c r="G310" t="s">
         <v>181</v>
       </c>
-      <c r="H310" s="2">
+      <c r="H310" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7776,7 +7750,7 @@
       <c r="D311" t="s">
         <v>163</v>
       </c>
-      <c r="H311" s="2">
+      <c r="H311" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7790,7 +7764,7 @@
       <c r="C312" t="s">
         <v>116</v>
       </c>
-      <c r="H312" s="2">
+      <c r="H312" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7804,7 +7778,7 @@
       <c r="C313" t="s">
         <v>112</v>
       </c>
-      <c r="H313" s="2">
+      <c r="H313" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7827,7 +7801,7 @@
       <c r="G314" t="s">
         <v>172</v>
       </c>
-      <c r="H314" s="2">
+      <c r="H314" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7844,7 +7818,7 @@
       <c r="D315" t="s">
         <v>129</v>
       </c>
-      <c r="H315" s="2">
+      <c r="H315" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7867,7 +7841,7 @@
       <c r="G316" t="s">
         <v>173</v>
       </c>
-      <c r="H316" s="2">
+      <c r="H316" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7890,7 +7864,7 @@
       <c r="G317" t="s">
         <v>182</v>
       </c>
-      <c r="H317" s="2">
+      <c r="H317" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7913,7 +7887,7 @@
       <c r="G318" t="s">
         <v>174</v>
       </c>
-      <c r="H318" s="2">
+      <c r="H318" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7936,7 +7910,7 @@
       <c r="G319" t="s">
         <v>174</v>
       </c>
-      <c r="H319" s="2">
+      <c r="H319" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7959,7 +7933,7 @@
       <c r="G320" t="s">
         <v>175</v>
       </c>
-      <c r="H320" s="2">
+      <c r="H320" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7973,7 +7947,7 @@
       <c r="C321" t="s">
         <v>112</v>
       </c>
-      <c r="H321" s="2">
+      <c r="H321" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -7996,7 +7970,7 @@
       <c r="G322" t="s">
         <v>183</v>
       </c>
-      <c r="H322" s="2">
+      <c r="H322" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8010,7 +7984,7 @@
       <c r="C323" t="s">
         <v>112</v>
       </c>
-      <c r="H323" s="2">
+      <c r="H323" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8033,7 +8007,7 @@
       <c r="G324" t="s">
         <v>184</v>
       </c>
-      <c r="H324" s="2">
+      <c r="H324" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8047,7 +8021,7 @@
       <c r="C325" t="s">
         <v>112</v>
       </c>
-      <c r="H325" s="2">
+      <c r="H325" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8061,7 +8035,7 @@
       <c r="C326" t="s">
         <v>116</v>
       </c>
-      <c r="H326" s="2">
+      <c r="H326" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8075,7 +8049,7 @@
       <c r="C327" t="s">
         <v>116</v>
       </c>
-      <c r="H327" s="2">
+      <c r="H327" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8092,13 +8066,13 @@
       <c r="D328" t="s">
         <v>122</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328" s="1">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>189</v>
       </c>
-      <c r="H328" s="2">
+      <c r="H328" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8121,7 +8095,7 @@
       <c r="G329" t="s">
         <v>184</v>
       </c>
-      <c r="H329" s="2">
+      <c r="H329" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8144,7 +8118,7 @@
       <c r="G330" t="s">
         <v>184</v>
       </c>
-      <c r="H330" s="2">
+      <c r="H330" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8158,7 +8132,7 @@
       <c r="C331" t="s">
         <v>112</v>
       </c>
-      <c r="H331" s="2">
+      <c r="H331" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8181,7 +8155,7 @@
       <c r="G332" t="s">
         <v>184</v>
       </c>
-      <c r="H332" s="2">
+      <c r="H332" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8204,7 +8178,7 @@
       <c r="G333" t="s">
         <v>183</v>
       </c>
-      <c r="H333" s="2">
+      <c r="H333" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8221,13 +8195,13 @@
       <c r="D334" t="s">
         <v>125</v>
       </c>
-      <c r="E334" s="2">
+      <c r="E334" s="1">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>202</v>
       </c>
-      <c r="H334" s="2">
+      <c r="H334" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8241,7 +8215,7 @@
       <c r="C335" t="s">
         <v>112</v>
       </c>
-      <c r="H335" s="2">
+      <c r="H335" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8258,13 +8232,13 @@
       <c r="D336" t="s">
         <v>157</v>
       </c>
-      <c r="E336" s="2">
+      <c r="E336" s="1">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>204</v>
       </c>
-      <c r="H336" s="2">
+      <c r="H336" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8278,7 +8252,7 @@
       <c r="C337" t="s">
         <v>112</v>
       </c>
-      <c r="H337" s="2">
+      <c r="H337" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8292,7 +8266,7 @@
       <c r="C338" t="s">
         <v>112</v>
       </c>
-      <c r="H338" s="2">
+      <c r="H338" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8315,7 +8289,7 @@
       <c r="G339" t="s">
         <v>181</v>
       </c>
-      <c r="H339" s="2">
+      <c r="H339" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8332,7 +8306,7 @@
       <c r="D340" t="s">
         <v>168</v>
       </c>
-      <c r="H340" s="2">
+      <c r="H340" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8346,7 +8320,7 @@
       <c r="C341" t="s">
         <v>116</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8360,7 +8334,7 @@
       <c r="C342" t="s">
         <v>112</v>
       </c>
-      <c r="H342" s="2">
+      <c r="H342" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8383,7 +8357,7 @@
       <c r="G343" t="s">
         <v>172</v>
       </c>
-      <c r="H343" s="2">
+      <c r="H343" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8400,7 +8374,7 @@
       <c r="D344" t="s">
         <v>129</v>
       </c>
-      <c r="H344" s="2">
+      <c r="H344" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8423,7 +8397,7 @@
       <c r="G345" t="s">
         <v>173</v>
       </c>
-      <c r="H345" s="2">
+      <c r="H345" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8446,7 +8420,7 @@
       <c r="G346" t="s">
         <v>182</v>
       </c>
-      <c r="H346" s="2">
+      <c r="H346" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8469,7 +8443,7 @@
       <c r="G347" t="s">
         <v>174</v>
       </c>
-      <c r="H347" s="2">
+      <c r="H347" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8492,7 +8466,7 @@
       <c r="G348" t="s">
         <v>174</v>
       </c>
-      <c r="H348" s="2">
+      <c r="H348" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8515,7 +8489,7 @@
       <c r="G349" t="s">
         <v>175</v>
       </c>
-      <c r="H349" s="2">
+      <c r="H349" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8529,7 +8503,7 @@
       <c r="C350" t="s">
         <v>112</v>
       </c>
-      <c r="H350" s="2">
+      <c r="H350" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8552,7 +8526,7 @@
       <c r="G351" t="s">
         <v>183</v>
       </c>
-      <c r="H351" s="2">
+      <c r="H351" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8566,7 +8540,7 @@
       <c r="C352" t="s">
         <v>112</v>
       </c>
-      <c r="H352" s="2">
+      <c r="H352" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8580,7 +8554,7 @@
       <c r="C353" t="s">
         <v>112</v>
       </c>
-      <c r="H353" s="2">
+      <c r="H353" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8594,7 +8568,7 @@
       <c r="C354" t="s">
         <v>112</v>
       </c>
-      <c r="H354" s="2">
+      <c r="H354" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8608,7 +8582,7 @@
       <c r="C355" t="s">
         <v>116</v>
       </c>
-      <c r="H355" s="2">
+      <c r="H355" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8622,7 +8596,7 @@
       <c r="C356" t="s">
         <v>116</v>
       </c>
-      <c r="H356" s="2">
+      <c r="H356" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8645,7 +8619,7 @@
       <c r="G357" t="s">
         <v>185</v>
       </c>
-      <c r="H357" s="2">
+      <c r="H357" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8659,7 +8633,7 @@
       <c r="C358" t="s">
         <v>112</v>
       </c>
-      <c r="H358" s="2">
+      <c r="H358" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8682,7 +8656,7 @@
       <c r="G359" t="s">
         <v>186</v>
       </c>
-      <c r="H359" s="2">
+      <c r="H359" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8696,7 +8670,7 @@
       <c r="C360" t="s">
         <v>112</v>
       </c>
-      <c r="H360" s="2">
+      <c r="H360" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8710,7 +8684,7 @@
       <c r="C361" t="s">
         <v>112</v>
       </c>
-      <c r="H361" s="2">
+      <c r="H361" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8733,7 +8707,7 @@
       <c r="G362" t="s">
         <v>183</v>
       </c>
-      <c r="H362" s="2">
+      <c r="H362" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8756,7 +8730,7 @@
       <c r="G363" t="s">
         <v>187</v>
       </c>
-      <c r="H363" s="2">
+      <c r="H363" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8770,7 +8744,7 @@
       <c r="C364" t="s">
         <v>112</v>
       </c>
-      <c r="H364" s="2">
+      <c r="H364" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8793,7 +8767,7 @@
       <c r="G365" t="s">
         <v>186</v>
       </c>
-      <c r="H365" s="2">
+      <c r="H365" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8807,7 +8781,7 @@
       <c r="C366" t="s">
         <v>112</v>
       </c>
-      <c r="H366" s="2">
+      <c r="H366" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8821,7 +8795,7 @@
       <c r="C367" t="s">
         <v>112</v>
       </c>
-      <c r="H367" s="2">
+      <c r="H367" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8844,7 +8818,7 @@
       <c r="G368" t="s">
         <v>185</v>
       </c>
-      <c r="H368" s="2">
+      <c r="H368" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8867,7 +8841,7 @@
       <c r="G369" t="s">
         <v>186</v>
       </c>
-      <c r="H369" s="2">
+      <c r="H369" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8884,7 +8858,7 @@
       <c r="D370" t="s">
         <v>168</v>
       </c>
-      <c r="H370" s="2">
+      <c r="H370" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8898,7 +8872,7 @@
       <c r="C371" t="s">
         <v>112</v>
       </c>
-      <c r="H371" s="2">
+      <c r="H371" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8921,7 +8895,7 @@
       <c r="G372" t="s">
         <v>172</v>
       </c>
-      <c r="H372" s="2">
+      <c r="H372" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8938,7 +8912,7 @@
       <c r="D373" t="s">
         <v>129</v>
       </c>
-      <c r="H373" s="2">
+      <c r="H373" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8961,7 +8935,7 @@
       <c r="G374" t="s">
         <v>173</v>
       </c>
-      <c r="H374" s="2">
+      <c r="H374" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8984,7 +8958,7 @@
       <c r="G375" t="s">
         <v>182</v>
       </c>
-      <c r="H375" s="2">
+      <c r="H375" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9007,7 +8981,7 @@
       <c r="G376" t="s">
         <v>174</v>
       </c>
-      <c r="H376" s="2">
+      <c r="H376" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9030,7 +9004,7 @@
       <c r="G377" t="s">
         <v>174</v>
       </c>
-      <c r="H377" s="2">
+      <c r="H377" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9053,7 +9027,7 @@
       <c r="G378" t="s">
         <v>175</v>
       </c>
-      <c r="H378" s="2">
+      <c r="H378" s="1">
         <v>46225</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -651,16 +651,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -676,7 +668,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -684,30 +676,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1007,72 +981,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1137,7 +1111,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1202,7 +1176,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1267,7 +1241,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1332,7 +1306,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1397,7 +1371,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1462,7 +1436,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1527,7 +1501,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1592,7 +1566,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1657,7 +1631,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1722,7 +1696,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1787,7 +1761,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -1852,7 +1826,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -1917,7 +1891,7 @@
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>46226</v>
       </c>
       <c r="B15">
@@ -1992,28 +1966,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2027,7 +2001,7 @@
       <c r="C2" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2041,7 +2015,7 @@
       <c r="C3" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2064,7 +2038,7 @@
       <c r="G4" t="s">
         <v>174</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2078,7 +2052,7 @@
       <c r="C5" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2092,7 +2066,7 @@
       <c r="C6" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2109,13 +2083,13 @@
       <c r="D7" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2132,13 +2106,13 @@
       <c r="D8" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>192</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2155,13 +2129,13 @@
       <c r="D9" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>193</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2178,13 +2152,13 @@
       <c r="D10" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2198,7 +2172,7 @@
       <c r="C11" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2212,7 +2186,7 @@
       <c r="C12" t="s">
         <v>115</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2229,13 +2203,13 @@
       <c r="D13" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>192</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2249,7 +2223,7 @@
       <c r="C14" t="s">
         <v>119</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2266,13 +2240,13 @@
       <c r="D15" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>195</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2286,7 +2260,7 @@
       <c r="C16" t="s">
         <v>115</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2300,7 +2274,7 @@
       <c r="C17" t="s">
         <v>115</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2317,13 +2291,13 @@
       <c r="D18" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>196</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2337,7 +2311,7 @@
       <c r="C19" t="s">
         <v>115</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2354,13 +2328,13 @@
       <c r="D20" t="s">
         <v>130</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>192</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2383,7 +2357,7 @@
       <c r="G21" t="s">
         <v>175</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2397,7 +2371,7 @@
       <c r="C22" t="s">
         <v>119</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2411,7 +2385,7 @@
       <c r="C23" t="s">
         <v>115</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2434,7 +2408,7 @@
       <c r="G24" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2451,7 +2425,7 @@
       <c r="D25" t="s">
         <v>132</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2474,7 +2448,7 @@
       <c r="G26" t="s">
         <v>177</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2491,13 +2465,13 @@
       <c r="D27" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>197</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2520,7 +2494,7 @@
       <c r="G28" t="s">
         <v>178</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2543,7 +2517,7 @@
       <c r="G29" t="s">
         <v>178</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2566,7 +2540,7 @@
       <c r="G30" t="s">
         <v>179</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2580,7 +2554,7 @@
       <c r="C31" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2594,7 +2568,7 @@
       <c r="C32" t="s">
         <v>115</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2617,7 +2591,7 @@
       <c r="G33" t="s">
         <v>180</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2631,7 +2605,7 @@
       <c r="C34" t="s">
         <v>115</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2645,7 +2619,7 @@
       <c r="C35" t="s">
         <v>115</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2662,13 +2636,13 @@
       <c r="D36" t="s">
         <v>123</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>192</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2685,13 +2659,13 @@
       <c r="D37" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>192</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2708,13 +2682,13 @@
       <c r="D38" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>193</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2731,13 +2705,13 @@
       <c r="D39" t="s">
         <v>126</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>194</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2751,7 +2725,7 @@
       <c r="C40" t="s">
         <v>115</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2765,7 +2739,7 @@
       <c r="C41" t="s">
         <v>115</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2782,13 +2756,13 @@
       <c r="D42" t="s">
         <v>127</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>192</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2802,7 +2776,7 @@
       <c r="C43" t="s">
         <v>115</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2819,13 +2793,13 @@
       <c r="D44" t="s">
         <v>128</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>195</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2839,7 +2813,7 @@
       <c r="C45" t="s">
         <v>115</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2853,7 +2827,7 @@
       <c r="C46" t="s">
         <v>115</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2867,7 +2841,7 @@
       <c r="C47" t="s">
         <v>119</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2881,7 +2855,7 @@
       <c r="C48" t="s">
         <v>115</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2898,13 +2872,13 @@
       <c r="D49" t="s">
         <v>139</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>192</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2927,7 +2901,7 @@
       <c r="G50" t="s">
         <v>175</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2941,7 +2915,7 @@
       <c r="C51" t="s">
         <v>119</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2955,7 +2929,7 @@
       <c r="C52" t="s">
         <v>115</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2978,7 +2952,7 @@
       <c r="G53" t="s">
         <v>176</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2995,7 +2969,7 @@
       <c r="D54" t="s">
         <v>132</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3018,7 +2992,7 @@
       <c r="G55" t="s">
         <v>177</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3035,13 +3009,13 @@
       <c r="D56" t="s">
         <v>134</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>197</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3064,7 +3038,7 @@
       <c r="G57" t="s">
         <v>178</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3087,7 +3061,7 @@
       <c r="G58" t="s">
         <v>178</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3110,7 +3084,7 @@
       <c r="G59" t="s">
         <v>179</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3124,7 +3098,7 @@
       <c r="C60" t="s">
         <v>115</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3138,7 +3112,7 @@
       <c r="C61" t="s">
         <v>115</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3155,13 +3129,13 @@
       <c r="D62" t="s">
         <v>138</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>198</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3175,7 +3149,7 @@
       <c r="C63" t="s">
         <v>115</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3192,13 +3166,13 @@
       <c r="D64" t="s">
         <v>140</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>199</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3212,7 +3186,7 @@
       <c r="C65" t="s">
         <v>115</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3226,7 +3200,7 @@
       <c r="C66" t="s">
         <v>119</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3243,13 +3217,13 @@
       <c r="D67" t="s">
         <v>125</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>193</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3266,13 +3240,13 @@
       <c r="D68" t="s">
         <v>126</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>194</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3286,7 +3260,7 @@
       <c r="C69" t="s">
         <v>115</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3300,7 +3274,7 @@
       <c r="C70" t="s">
         <v>115</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3317,13 +3291,13 @@
       <c r="D71" t="s">
         <v>127</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>198</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3337,7 +3311,7 @@
       <c r="C72" t="s">
         <v>115</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3354,13 +3328,13 @@
       <c r="D73" t="s">
         <v>128</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>195</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3374,7 +3348,7 @@
       <c r="C74" t="s">
         <v>115</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3388,7 +3362,7 @@
       <c r="C75" t="s">
         <v>115</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3402,7 +3376,7 @@
       <c r="C76" t="s">
         <v>115</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3416,7 +3390,7 @@
       <c r="C77" t="s">
         <v>115</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3433,13 +3407,13 @@
       <c r="D78" t="s">
         <v>139</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>198</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3462,7 +3436,7 @@
       <c r="G79" t="s">
         <v>181</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3476,7 +3450,7 @@
       <c r="C80" t="s">
         <v>119</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3490,7 +3464,7 @@
       <c r="C81" t="s">
         <v>115</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3513,7 +3487,7 @@
       <c r="G82" t="s">
         <v>176</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3530,7 +3504,7 @@
       <c r="D83" t="s">
         <v>132</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3553,7 +3527,7 @@
       <c r="G84" t="s">
         <v>177</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3570,13 +3544,13 @@
       <c r="D85" t="s">
         <v>134</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>197</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3599,7 +3573,7 @@
       <c r="G86" t="s">
         <v>178</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3622,7 +3596,7 @@
       <c r="G87" t="s">
         <v>178</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3645,7 +3619,7 @@
       <c r="G88" t="s">
         <v>179</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3659,7 +3633,7 @@
       <c r="C89" t="s">
         <v>115</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3676,13 +3650,13 @@
       <c r="D90" t="s">
         <v>142</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>199</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3699,13 +3673,13 @@
       <c r="D91" t="s">
         <v>138</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>198</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3719,7 +3693,7 @@
       <c r="C92" t="s">
         <v>115</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3736,13 +3710,13 @@
       <c r="D93" t="s">
         <v>140</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>199</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3756,7 +3730,7 @@
       <c r="C94" t="s">
         <v>115</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3770,7 +3744,7 @@
       <c r="C95" t="s">
         <v>119</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3787,13 +3761,13 @@
       <c r="D96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>193</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3810,13 +3784,13 @@
       <c r="D97" t="s">
         <v>126</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>194</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3830,7 +3804,7 @@
       <c r="C98" t="s">
         <v>115</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3847,13 +3821,13 @@
       <c r="D99" t="s">
         <v>143</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>194</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3870,13 +3844,13 @@
       <c r="D100" t="s">
         <v>127</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>194</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3890,7 +3864,7 @@
       <c r="C101" t="s">
         <v>115</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3907,13 +3881,13 @@
       <c r="D102" t="s">
         <v>128</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>195</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3930,13 +3904,13 @@
       <c r="D103" t="s">
         <v>144</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>194</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3950,7 +3924,7 @@
       <c r="C104" t="s">
         <v>115</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3964,7 +3938,7 @@
       <c r="C105" t="s">
         <v>115</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3978,7 +3952,7 @@
       <c r="C106" t="s">
         <v>115</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3995,13 +3969,13 @@
       <c r="D107" t="s">
         <v>145</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>194</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4024,7 +3998,7 @@
       <c r="G108" t="s">
         <v>181</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4038,7 +4012,7 @@
       <c r="C109" t="s">
         <v>119</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4052,7 +4026,7 @@
       <c r="C110" t="s">
         <v>115</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4075,7 +4049,7 @@
       <c r="G111" t="s">
         <v>176</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4092,7 +4066,7 @@
       <c r="D112" t="s">
         <v>132</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4115,7 +4089,7 @@
       <c r="G113" t="s">
         <v>177</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4132,13 +4106,13 @@
       <c r="D114" t="s">
         <v>134</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>197</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4161,7 +4135,7 @@
       <c r="G115" t="s">
         <v>178</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4184,7 +4158,7 @@
       <c r="G116" t="s">
         <v>178</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4207,7 +4181,7 @@
       <c r="G117" t="s">
         <v>179</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4221,7 +4195,7 @@
       <c r="C118" t="s">
         <v>115</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4238,13 +4212,13 @@
       <c r="D119" t="s">
         <v>142</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>199</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4258,7 +4232,7 @@
       <c r="C120" t="s">
         <v>119</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4272,7 +4246,7 @@
       <c r="C121" t="s">
         <v>115</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4286,7 +4260,7 @@
       <c r="C122" t="s">
         <v>119</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4300,7 +4274,7 @@
       <c r="C123" t="s">
         <v>119</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4314,7 +4288,7 @@
       <c r="C124" t="s">
         <v>119</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4331,13 +4305,13 @@
       <c r="D125" t="s">
         <v>125</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>193</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4354,13 +4328,13 @@
       <c r="D126" t="s">
         <v>126</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>194</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4374,7 +4348,7 @@
       <c r="C127" t="s">
         <v>115</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4391,13 +4365,13 @@
       <c r="D128" t="s">
         <v>143</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>194</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4414,13 +4388,13 @@
       <c r="D129" t="s">
         <v>127</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>194</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4434,7 +4408,7 @@
       <c r="C130" t="s">
         <v>115</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4451,13 +4425,13 @@
       <c r="D131" t="s">
         <v>128</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>195</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4474,13 +4448,13 @@
       <c r="D132" t="s">
         <v>144</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>194</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4494,7 +4468,7 @@
       <c r="C133" t="s">
         <v>115</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4508,7 +4482,7 @@
       <c r="C134" t="s">
         <v>115</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4522,7 +4496,7 @@
       <c r="C135" t="s">
         <v>115</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4539,13 +4513,13 @@
       <c r="D136" t="s">
         <v>146</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>194</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4568,7 +4542,7 @@
       <c r="G137" t="s">
         <v>181</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4582,7 +4556,7 @@
       <c r="C138" t="s">
         <v>119</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4596,7 +4570,7 @@
       <c r="C139" t="s">
         <v>115</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4619,7 +4593,7 @@
       <c r="G140" t="s">
         <v>176</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4636,7 +4610,7 @@
       <c r="D141" t="s">
         <v>132</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4659,7 +4633,7 @@
       <c r="G142" t="s">
         <v>177</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4676,13 +4650,13 @@
       <c r="D143" t="s">
         <v>134</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>197</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4705,7 +4679,7 @@
       <c r="G144" t="s">
         <v>178</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4728,7 +4702,7 @@
       <c r="G145" t="s">
         <v>178</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4751,7 +4725,7 @@
       <c r="G146" t="s">
         <v>179</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4765,7 +4739,7 @@
       <c r="C147" t="s">
         <v>115</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4782,13 +4756,13 @@
       <c r="D148" t="s">
         <v>142</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>199</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4802,7 +4776,7 @@
       <c r="C149" t="s">
         <v>119</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4816,7 +4790,7 @@
       <c r="C150" t="s">
         <v>115</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4830,7 +4804,7 @@
       <c r="C151" t="s">
         <v>115</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4844,7 +4818,7 @@
       <c r="C152" t="s">
         <v>119</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4858,7 +4832,7 @@
       <c r="C153" t="s">
         <v>119</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4875,13 +4849,13 @@
       <c r="D154" t="s">
         <v>125</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>193</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4898,13 +4872,13 @@
       <c r="D155" t="s">
         <v>126</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>194</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4918,7 +4892,7 @@
       <c r="C156" t="s">
         <v>115</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4935,13 +4909,13 @@
       <c r="D157" t="s">
         <v>143</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>194</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4958,13 +4932,13 @@
       <c r="D158" t="s">
         <v>127</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>194</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4981,13 +4955,13 @@
       <c r="D159" t="s">
         <v>147</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>200</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5004,13 +4978,13 @@
       <c r="D160" t="s">
         <v>128</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>195</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5027,13 +5001,13 @@
       <c r="D161" t="s">
         <v>144</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>194</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5047,7 +5021,7 @@
       <c r="C162" t="s">
         <v>115</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5061,7 +5035,7 @@
       <c r="C163" t="s">
         <v>115</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5075,7 +5049,7 @@
       <c r="C164" t="s">
         <v>115</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5092,13 +5066,13 @@
       <c r="D165" t="s">
         <v>146</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>194</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5121,7 +5095,7 @@
       <c r="G166" t="s">
         <v>181</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5135,7 +5109,7 @@
       <c r="C167" t="s">
         <v>119</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5149,7 +5123,7 @@
       <c r="C168" t="s">
         <v>115</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5172,7 +5146,7 @@
       <c r="G169" t="s">
         <v>176</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5189,7 +5163,7 @@
       <c r="D170" t="s">
         <v>132</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5212,7 +5186,7 @@
       <c r="G171" t="s">
         <v>177</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5229,13 +5203,13 @@
       <c r="D172" t="s">
         <v>134</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>197</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5258,7 +5232,7 @@
       <c r="G173" t="s">
         <v>178</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5281,7 +5255,7 @@
       <c r="G174" t="s">
         <v>178</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5304,7 +5278,7 @@
       <c r="G175" t="s">
         <v>179</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5318,7 +5292,7 @@
       <c r="C176" t="s">
         <v>115</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5335,13 +5309,13 @@
       <c r="D177" t="s">
         <v>148</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>199</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5355,7 +5329,7 @@
       <c r="C178" t="s">
         <v>115</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5372,13 +5346,13 @@
       <c r="D179" t="s">
         <v>149</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>195</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5392,7 +5366,7 @@
       <c r="C180" t="s">
         <v>115</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5406,7 +5380,7 @@
       <c r="C181" t="s">
         <v>119</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5420,7 +5394,7 @@
       <c r="C182" t="s">
         <v>119</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5437,13 +5411,13 @@
       <c r="D183" t="s">
         <v>125</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>193</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5460,13 +5434,13 @@
       <c r="D184" t="s">
         <v>126</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>194</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5480,7 +5454,7 @@
       <c r="C185" t="s">
         <v>115</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5497,13 +5471,13 @@
       <c r="D186" t="s">
         <v>143</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>194</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5520,13 +5494,13 @@
       <c r="D187" t="s">
         <v>150</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>194</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5543,13 +5517,13 @@
       <c r="D188" t="s">
         <v>151</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>194</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5566,13 +5540,13 @@
       <c r="D189" t="s">
         <v>128</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>195</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5589,13 +5563,13 @@
       <c r="D190" t="s">
         <v>144</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>194</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5609,7 +5583,7 @@
       <c r="C191" t="s">
         <v>115</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5623,7 +5597,7 @@
       <c r="C192" t="s">
         <v>115</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5637,7 +5611,7 @@
       <c r="C193" t="s">
         <v>115</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5654,13 +5628,13 @@
       <c r="D194" t="s">
         <v>146</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>201</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5683,7 +5657,7 @@
       <c r="G195" t="s">
         <v>181</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5697,7 +5671,7 @@
       <c r="C196" t="s">
         <v>119</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5711,7 +5685,7 @@
       <c r="C197" t="s">
         <v>115</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5734,7 +5708,7 @@
       <c r="G198" t="s">
         <v>176</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5751,7 +5725,7 @@
       <c r="D199" t="s">
         <v>132</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5774,7 +5748,7 @@
       <c r="G200" t="s">
         <v>177</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5791,13 +5765,13 @@
       <c r="D201" t="s">
         <v>134</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>197</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5820,7 +5794,7 @@
       <c r="G202" t="s">
         <v>178</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5843,7 +5817,7 @@
       <c r="G203" t="s">
         <v>178</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5866,7 +5840,7 @@
       <c r="G204" t="s">
         <v>179</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5880,7 +5854,7 @@
       <c r="C205" t="s">
         <v>115</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5897,13 +5871,13 @@
       <c r="D206" t="s">
         <v>148</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>199</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5917,7 +5891,7 @@
       <c r="C207" t="s">
         <v>115</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5931,7 +5905,7 @@
       <c r="C208" t="s">
         <v>119</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5945,7 +5919,7 @@
       <c r="C209" t="s">
         <v>115</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5959,7 +5933,7 @@
       <c r="C210" t="s">
         <v>119</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5973,7 +5947,7 @@
       <c r="C211" t="s">
         <v>119</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -5990,13 +5964,13 @@
       <c r="D212" t="s">
         <v>125</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>193</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6010,7 +5984,7 @@
       <c r="C213" t="s">
         <v>119</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6024,7 +5998,7 @@
       <c r="C214" t="s">
         <v>115</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6041,13 +6015,13 @@
       <c r="D215" t="s">
         <v>143</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>202</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6064,13 +6038,13 @@
       <c r="D216" t="s">
         <v>150</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>195</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6084,7 +6058,7 @@
       <c r="C217" t="s">
         <v>115</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6101,13 +6075,13 @@
       <c r="D218" t="s">
         <v>128</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>195</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6121,7 +6095,7 @@
       <c r="C219" t="s">
         <v>115</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6135,7 +6109,7 @@
       <c r="C220" t="s">
         <v>115</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6152,13 +6126,13 @@
       <c r="D221" t="s">
         <v>152</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>199</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6172,7 +6146,7 @@
       <c r="C222" t="s">
         <v>115</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6189,13 +6163,13 @@
       <c r="D223" t="s">
         <v>153</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>203</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6218,7 +6192,7 @@
       <c r="G224" t="s">
         <v>181</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6232,7 +6206,7 @@
       <c r="C225" t="s">
         <v>119</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6246,7 +6220,7 @@
       <c r="C226" t="s">
         <v>115</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6269,7 +6243,7 @@
       <c r="G227" t="s">
         <v>176</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6286,7 +6260,7 @@
       <c r="D228" t="s">
         <v>132</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6309,7 +6283,7 @@
       <c r="G229" t="s">
         <v>177</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6326,13 +6300,13 @@
       <c r="D230" t="s">
         <v>154</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>204</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6355,7 +6329,7 @@
       <c r="G231" t="s">
         <v>178</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6378,7 +6352,7 @@
       <c r="G232" t="s">
         <v>178</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6401,7 +6375,7 @@
       <c r="G233" t="s">
         <v>179</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6415,7 +6389,7 @@
       <c r="C234" t="s">
         <v>115</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6432,13 +6406,13 @@
       <c r="D235" t="s">
         <v>155</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>199</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6452,7 +6426,7 @@
       <c r="C236" t="s">
         <v>115</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6466,7 +6440,7 @@
       <c r="C237" t="s">
         <v>119</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6480,7 +6454,7 @@
       <c r="C238" t="s">
         <v>115</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6494,7 +6468,7 @@
       <c r="C239" t="s">
         <v>119</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6508,7 +6482,7 @@
       <c r="C240" t="s">
         <v>119</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6525,13 +6499,13 @@
       <c r="D241" t="s">
         <v>125</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>193</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6545,7 +6519,7 @@
       <c r="C242" t="s">
         <v>119</v>
       </c>
-      <c r="H242" s="2">
+      <c r="H242" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6562,13 +6536,13 @@
       <c r="D243" t="s">
         <v>156</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>205</v>
       </c>
-      <c r="H243" s="2">
+      <c r="H243" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6585,13 +6559,13 @@
       <c r="D244" t="s">
         <v>157</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>202</v>
       </c>
-      <c r="H244" s="2">
+      <c r="H244" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6605,7 +6579,7 @@
       <c r="C245" t="s">
         <v>119</v>
       </c>
-      <c r="H245" s="2">
+      <c r="H245" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6619,7 +6593,7 @@
       <c r="C246" t="s">
         <v>115</v>
       </c>
-      <c r="H246" s="2">
+      <c r="H246" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6636,13 +6610,13 @@
       <c r="D247" t="s">
         <v>128</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>206</v>
       </c>
-      <c r="H247" s="2">
+      <c r="H247" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6656,7 +6630,7 @@
       <c r="C248" t="s">
         <v>115</v>
       </c>
-      <c r="H248" s="2">
+      <c r="H248" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6670,7 +6644,7 @@
       <c r="C249" t="s">
         <v>115</v>
       </c>
-      <c r="H249" s="2">
+      <c r="H249" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6687,13 +6661,13 @@
       <c r="D250" t="s">
         <v>158</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>201</v>
       </c>
-      <c r="H250" s="2">
+      <c r="H250" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6707,7 +6681,7 @@
       <c r="C251" t="s">
         <v>115</v>
       </c>
-      <c r="H251" s="2">
+      <c r="H251" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6724,13 +6698,13 @@
       <c r="D252" t="s">
         <v>159</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>203</v>
       </c>
-      <c r="H252" s="2">
+      <c r="H252" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6753,7 +6727,7 @@
       <c r="G253" t="s">
         <v>181</v>
       </c>
-      <c r="H253" s="2">
+      <c r="H253" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6767,7 +6741,7 @@
       <c r="C254" t="s">
         <v>119</v>
       </c>
-      <c r="H254" s="2">
+      <c r="H254" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6781,7 +6755,7 @@
       <c r="C255" t="s">
         <v>115</v>
       </c>
-      <c r="H255" s="2">
+      <c r="H255" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6804,7 +6778,7 @@
       <c r="G256" t="s">
         <v>176</v>
       </c>
-      <c r="H256" s="2">
+      <c r="H256" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6821,7 +6795,7 @@
       <c r="D257" t="s">
         <v>132</v>
       </c>
-      <c r="H257" s="2">
+      <c r="H257" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6844,7 +6818,7 @@
       <c r="G258" t="s">
         <v>177</v>
       </c>
-      <c r="H258" s="2">
+      <c r="H258" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6861,13 +6835,13 @@
       <c r="D259" t="s">
         <v>154</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>204</v>
       </c>
-      <c r="H259" s="2">
+      <c r="H259" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6890,7 +6864,7 @@
       <c r="G260" t="s">
         <v>178</v>
       </c>
-      <c r="H260" s="2">
+      <c r="H260" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6913,7 +6887,7 @@
       <c r="G261" t="s">
         <v>178</v>
       </c>
-      <c r="H261" s="2">
+      <c r="H261" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6936,7 +6910,7 @@
       <c r="G262" t="s">
         <v>179</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6950,7 +6924,7 @@
       <c r="C263" t="s">
         <v>115</v>
       </c>
-      <c r="H263" s="2">
+      <c r="H263" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6967,13 +6941,13 @@
       <c r="D264" t="s">
         <v>155</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>199</v>
       </c>
-      <c r="H264" s="2">
+      <c r="H264" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -6987,7 +6961,7 @@
       <c r="C265" t="s">
         <v>115</v>
       </c>
-      <c r="H265" s="2">
+      <c r="H265" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7001,7 +6975,7 @@
       <c r="C266" t="s">
         <v>119</v>
       </c>
-      <c r="H266" s="2">
+      <c r="H266" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7015,7 +6989,7 @@
       <c r="C267" t="s">
         <v>115</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H267" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7029,7 +7003,7 @@
       <c r="C268" t="s">
         <v>119</v>
       </c>
-      <c r="H268" s="2">
+      <c r="H268" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7043,7 +7017,7 @@
       <c r="C269" t="s">
         <v>119</v>
       </c>
-      <c r="H269" s="2">
+      <c r="H269" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7060,13 +7034,13 @@
       <c r="D270" t="s">
         <v>125</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>193</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H270" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7080,7 +7054,7 @@
       <c r="C271" t="s">
         <v>119</v>
       </c>
-      <c r="H271" s="2">
+      <c r="H271" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7097,13 +7071,13 @@
       <c r="D272" t="s">
         <v>156</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>205</v>
       </c>
-      <c r="H272" s="2">
+      <c r="H272" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7120,13 +7094,13 @@
       <c r="D273" t="s">
         <v>157</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>207</v>
       </c>
-      <c r="H273" s="2">
+      <c r="H273" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7140,7 +7114,7 @@
       <c r="C274" t="s">
         <v>115</v>
       </c>
-      <c r="H274" s="2">
+      <c r="H274" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7154,7 +7128,7 @@
       <c r="C275" t="s">
         <v>115</v>
       </c>
-      <c r="H275" s="2">
+      <c r="H275" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7171,13 +7145,13 @@
       <c r="D276" t="s">
         <v>128</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>206</v>
       </c>
-      <c r="H276" s="2">
+      <c r="H276" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7191,7 +7165,7 @@
       <c r="C277" t="s">
         <v>115</v>
       </c>
-      <c r="H277" s="2">
+      <c r="H277" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7208,13 +7182,13 @@
       <c r="D278" t="s">
         <v>160</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>208</v>
       </c>
-      <c r="H278" s="2">
+      <c r="H278" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7231,13 +7205,13 @@
       <c r="D279" t="s">
         <v>158</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>207</v>
       </c>
-      <c r="H279" s="2">
+      <c r="H279" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7251,7 +7225,7 @@
       <c r="C280" t="s">
         <v>115</v>
       </c>
-      <c r="H280" s="2">
+      <c r="H280" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7268,13 +7242,13 @@
       <c r="D281" t="s">
         <v>161</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>203</v>
       </c>
-      <c r="H281" s="2">
+      <c r="H281" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7297,7 +7271,7 @@
       <c r="G282" t="s">
         <v>181</v>
       </c>
-      <c r="H282" s="2">
+      <c r="H282" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7311,7 +7285,7 @@
       <c r="C283" t="s">
         <v>119</v>
       </c>
-      <c r="H283" s="2">
+      <c r="H283" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7325,7 +7299,7 @@
       <c r="C284" t="s">
         <v>115</v>
       </c>
-      <c r="H284" s="2">
+      <c r="H284" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7348,7 +7322,7 @@
       <c r="G285" t="s">
         <v>176</v>
       </c>
-      <c r="H285" s="2">
+      <c r="H285" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7365,7 +7339,7 @@
       <c r="D286" t="s">
         <v>132</v>
       </c>
-      <c r="H286" s="2">
+      <c r="H286" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7388,7 +7362,7 @@
       <c r="G287" t="s">
         <v>177</v>
       </c>
-      <c r="H287" s="2">
+      <c r="H287" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7405,13 +7379,13 @@
       <c r="D288" t="s">
         <v>154</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>204</v>
       </c>
-      <c r="H288" s="2">
+      <c r="H288" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7434,7 +7408,7 @@
       <c r="G289" t="s">
         <v>178</v>
       </c>
-      <c r="H289" s="2">
+      <c r="H289" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7457,7 +7431,7 @@
       <c r="G290" t="s">
         <v>178</v>
       </c>
-      <c r="H290" s="2">
+      <c r="H290" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7480,7 +7454,7 @@
       <c r="G291" t="s">
         <v>179</v>
       </c>
-      <c r="H291" s="2">
+      <c r="H291" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7494,7 +7468,7 @@
       <c r="C292" t="s">
         <v>115</v>
       </c>
-      <c r="H292" s="2">
+      <c r="H292" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7517,7 +7491,7 @@
       <c r="G293" t="s">
         <v>182</v>
       </c>
-      <c r="H293" s="2">
+      <c r="H293" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7531,7 +7505,7 @@
       <c r="C294" t="s">
         <v>115</v>
       </c>
-      <c r="H294" s="2">
+      <c r="H294" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7554,7 +7528,7 @@
       <c r="G295" t="s">
         <v>183</v>
       </c>
-      <c r="H295" s="2">
+      <c r="H295" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7568,7 +7542,7 @@
       <c r="C296" t="s">
         <v>115</v>
       </c>
-      <c r="H296" s="2">
+      <c r="H296" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7582,7 +7556,7 @@
       <c r="C297" t="s">
         <v>119</v>
       </c>
-      <c r="H297" s="2">
+      <c r="H297" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7605,7 +7579,7 @@
       <c r="G298" t="s">
         <v>184</v>
       </c>
-      <c r="H298" s="2">
+      <c r="H298" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7622,13 +7596,13 @@
       <c r="D299" t="s">
         <v>125</v>
       </c>
-      <c r="E299" s="2">
+      <c r="E299" s="1">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>193</v>
       </c>
-      <c r="H299" s="2">
+      <c r="H299" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7642,7 +7616,7 @@
       <c r="C300" t="s">
         <v>115</v>
       </c>
-      <c r="H300" s="2">
+      <c r="H300" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7659,13 +7633,13 @@
       <c r="D301" t="s">
         <v>156</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301" s="1">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>205</v>
       </c>
-      <c r="H301" s="2">
+      <c r="H301" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7682,13 +7656,13 @@
       <c r="D302" t="s">
         <v>157</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302" s="1">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>202</v>
       </c>
-      <c r="H302" s="2">
+      <c r="H302" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7702,7 +7676,7 @@
       <c r="C303" t="s">
         <v>115</v>
       </c>
-      <c r="H303" s="2">
+      <c r="H303" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7716,7 +7690,7 @@
       <c r="C304" t="s">
         <v>115</v>
       </c>
-      <c r="H304" s="2">
+      <c r="H304" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7733,13 +7707,13 @@
       <c r="D305" t="s">
         <v>128</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305" s="1">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>206</v>
       </c>
-      <c r="H305" s="2">
+      <c r="H305" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7753,7 +7727,7 @@
       <c r="C306" t="s">
         <v>115</v>
       </c>
-      <c r="H306" s="2">
+      <c r="H306" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7770,13 +7744,13 @@
       <c r="D307" t="s">
         <v>160</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307" s="1">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>208</v>
       </c>
-      <c r="H307" s="2">
+      <c r="H307" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7790,7 +7764,7 @@
       <c r="C308" t="s">
         <v>119</v>
       </c>
-      <c r="H308" s="2">
+      <c r="H308" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7813,7 +7787,7 @@
       <c r="G309" t="s">
         <v>182</v>
       </c>
-      <c r="H309" s="2">
+      <c r="H309" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7836,7 +7810,7 @@
       <c r="G310" t="s">
         <v>185</v>
       </c>
-      <c r="H310" s="2">
+      <c r="H310" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7853,7 +7827,7 @@
       <c r="D311" t="s">
         <v>166</v>
       </c>
-      <c r="H311" s="2">
+      <c r="H311" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7867,7 +7841,7 @@
       <c r="C312" t="s">
         <v>119</v>
       </c>
-      <c r="H312" s="2">
+      <c r="H312" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7881,7 +7855,7 @@
       <c r="C313" t="s">
         <v>115</v>
       </c>
-      <c r="H313" s="2">
+      <c r="H313" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7904,7 +7878,7 @@
       <c r="G314" t="s">
         <v>176</v>
       </c>
-      <c r="H314" s="2">
+      <c r="H314" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7921,7 +7895,7 @@
       <c r="D315" t="s">
         <v>132</v>
       </c>
-      <c r="H315" s="2">
+      <c r="H315" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7944,7 +7918,7 @@
       <c r="G316" t="s">
         <v>177</v>
       </c>
-      <c r="H316" s="2">
+      <c r="H316" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7967,7 +7941,7 @@
       <c r="G317" t="s">
         <v>186</v>
       </c>
-      <c r="H317" s="2">
+      <c r="H317" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7990,7 +7964,7 @@
       <c r="G318" t="s">
         <v>178</v>
       </c>
-      <c r="H318" s="2">
+      <c r="H318" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8013,7 +7987,7 @@
       <c r="G319" t="s">
         <v>178</v>
       </c>
-      <c r="H319" s="2">
+      <c r="H319" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8036,7 +8010,7 @@
       <c r="G320" t="s">
         <v>179</v>
       </c>
-      <c r="H320" s="2">
+      <c r="H320" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8050,7 +8024,7 @@
       <c r="C321" t="s">
         <v>115</v>
       </c>
-      <c r="H321" s="2">
+      <c r="H321" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8073,7 +8047,7 @@
       <c r="G322" t="s">
         <v>187</v>
       </c>
-      <c r="H322" s="2">
+      <c r="H322" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8087,7 +8061,7 @@
       <c r="C323" t="s">
         <v>115</v>
       </c>
-      <c r="H323" s="2">
+      <c r="H323" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8110,7 +8084,7 @@
       <c r="G324" t="s">
         <v>188</v>
       </c>
-      <c r="H324" s="2">
+      <c r="H324" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8124,7 +8098,7 @@
       <c r="C325" t="s">
         <v>115</v>
       </c>
-      <c r="H325" s="2">
+      <c r="H325" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8138,7 +8112,7 @@
       <c r="C326" t="s">
         <v>119</v>
       </c>
-      <c r="H326" s="2">
+      <c r="H326" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8152,7 +8126,7 @@
       <c r="C327" t="s">
         <v>119</v>
       </c>
-      <c r="H327" s="2">
+      <c r="H327" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8169,13 +8143,13 @@
       <c r="D328" t="s">
         <v>125</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328" s="1">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>193</v>
       </c>
-      <c r="H328" s="2">
+      <c r="H328" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8198,7 +8172,7 @@
       <c r="G329" t="s">
         <v>188</v>
       </c>
-      <c r="H329" s="2">
+      <c r="H329" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8221,7 +8195,7 @@
       <c r="G330" t="s">
         <v>188</v>
       </c>
-      <c r="H330" s="2">
+      <c r="H330" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8235,7 +8209,7 @@
       <c r="C331" t="s">
         <v>115</v>
       </c>
-      <c r="H331" s="2">
+      <c r="H331" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8258,7 +8232,7 @@
       <c r="G332" t="s">
         <v>188</v>
       </c>
-      <c r="H332" s="2">
+      <c r="H332" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8281,7 +8255,7 @@
       <c r="G333" t="s">
         <v>187</v>
       </c>
-      <c r="H333" s="2">
+      <c r="H333" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8298,13 +8272,13 @@
       <c r="D334" t="s">
         <v>128</v>
       </c>
-      <c r="E334" s="2">
+      <c r="E334" s="1">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>206</v>
       </c>
-      <c r="H334" s="2">
+      <c r="H334" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8318,7 +8292,7 @@
       <c r="C335" t="s">
         <v>115</v>
       </c>
-      <c r="H335" s="2">
+      <c r="H335" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8335,13 +8309,13 @@
       <c r="D336" t="s">
         <v>160</v>
       </c>
-      <c r="E336" s="2">
+      <c r="E336" s="1">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>208</v>
       </c>
-      <c r="H336" s="2">
+      <c r="H336" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8355,7 +8329,7 @@
       <c r="C337" t="s">
         <v>115</v>
       </c>
-      <c r="H337" s="2">
+      <c r="H337" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8369,7 +8343,7 @@
       <c r="C338" t="s">
         <v>115</v>
       </c>
-      <c r="H338" s="2">
+      <c r="H338" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8392,7 +8366,7 @@
       <c r="G339" t="s">
         <v>185</v>
       </c>
-      <c r="H339" s="2">
+      <c r="H339" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8409,7 +8383,7 @@
       <c r="D340" t="s">
         <v>171</v>
       </c>
-      <c r="H340" s="2">
+      <c r="H340" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8423,7 +8397,7 @@
       <c r="C341" t="s">
         <v>119</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8437,7 +8411,7 @@
       <c r="C342" t="s">
         <v>115</v>
       </c>
-      <c r="H342" s="2">
+      <c r="H342" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8460,7 +8434,7 @@
       <c r="G343" t="s">
         <v>176</v>
       </c>
-      <c r="H343" s="2">
+      <c r="H343" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8477,7 +8451,7 @@
       <c r="D344" t="s">
         <v>132</v>
       </c>
-      <c r="H344" s="2">
+      <c r="H344" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8500,7 +8474,7 @@
       <c r="G345" t="s">
         <v>177</v>
       </c>
-      <c r="H345" s="2">
+      <c r="H345" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8523,7 +8497,7 @@
       <c r="G346" t="s">
         <v>186</v>
       </c>
-      <c r="H346" s="2">
+      <c r="H346" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8546,7 +8520,7 @@
       <c r="G347" t="s">
         <v>178</v>
       </c>
-      <c r="H347" s="2">
+      <c r="H347" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8569,7 +8543,7 @@
       <c r="G348" t="s">
         <v>178</v>
       </c>
-      <c r="H348" s="2">
+      <c r="H348" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8592,7 +8566,7 @@
       <c r="G349" t="s">
         <v>179</v>
       </c>
-      <c r="H349" s="2">
+      <c r="H349" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8606,7 +8580,7 @@
       <c r="C350" t="s">
         <v>115</v>
       </c>
-      <c r="H350" s="2">
+      <c r="H350" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8629,7 +8603,7 @@
       <c r="G351" t="s">
         <v>187</v>
       </c>
-      <c r="H351" s="2">
+      <c r="H351" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8643,7 +8617,7 @@
       <c r="C352" t="s">
         <v>115</v>
       </c>
-      <c r="H352" s="2">
+      <c r="H352" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8657,7 +8631,7 @@
       <c r="C353" t="s">
         <v>115</v>
       </c>
-      <c r="H353" s="2">
+      <c r="H353" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8671,7 +8645,7 @@
       <c r="C354" t="s">
         <v>115</v>
       </c>
-      <c r="H354" s="2">
+      <c r="H354" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8685,7 +8659,7 @@
       <c r="C355" t="s">
         <v>119</v>
       </c>
-      <c r="H355" s="2">
+      <c r="H355" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8699,7 +8673,7 @@
       <c r="C356" t="s">
         <v>119</v>
       </c>
-      <c r="H356" s="2">
+      <c r="H356" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8722,7 +8696,7 @@
       <c r="G357" t="s">
         <v>189</v>
       </c>
-      <c r="H357" s="2">
+      <c r="H357" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8736,7 +8710,7 @@
       <c r="C358" t="s">
         <v>115</v>
       </c>
-      <c r="H358" s="2">
+      <c r="H358" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8759,7 +8733,7 @@
       <c r="G359" t="s">
         <v>190</v>
       </c>
-      <c r="H359" s="2">
+      <c r="H359" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8773,7 +8747,7 @@
       <c r="C360" t="s">
         <v>115</v>
       </c>
-      <c r="H360" s="2">
+      <c r="H360" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8787,7 +8761,7 @@
       <c r="C361" t="s">
         <v>115</v>
       </c>
-      <c r="H361" s="2">
+      <c r="H361" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8810,7 +8784,7 @@
       <c r="G362" t="s">
         <v>187</v>
       </c>
-      <c r="H362" s="2">
+      <c r="H362" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8833,7 +8807,7 @@
       <c r="G363" t="s">
         <v>191</v>
       </c>
-      <c r="H363" s="2">
+      <c r="H363" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8847,7 +8821,7 @@
       <c r="C364" t="s">
         <v>115</v>
       </c>
-      <c r="H364" s="2">
+      <c r="H364" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8870,7 +8844,7 @@
       <c r="G365" t="s">
         <v>190</v>
       </c>
-      <c r="H365" s="2">
+      <c r="H365" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8884,7 +8858,7 @@
       <c r="C366" t="s">
         <v>115</v>
       </c>
-      <c r="H366" s="2">
+      <c r="H366" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8898,7 +8872,7 @@
       <c r="C367" t="s">
         <v>115</v>
       </c>
-      <c r="H367" s="2">
+      <c r="H367" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8921,7 +8895,7 @@
       <c r="G368" t="s">
         <v>189</v>
       </c>
-      <c r="H368" s="2">
+      <c r="H368" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8944,7 +8918,7 @@
       <c r="G369" t="s">
         <v>190</v>
       </c>
-      <c r="H369" s="2">
+      <c r="H369" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8961,7 +8935,7 @@
       <c r="D370" t="s">
         <v>171</v>
       </c>
-      <c r="H370" s="2">
+      <c r="H370" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8975,7 +8949,7 @@
       <c r="C371" t="s">
         <v>115</v>
       </c>
-      <c r="H371" s="2">
+      <c r="H371" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8998,7 +8972,7 @@
       <c r="G372" t="s">
         <v>176</v>
       </c>
-      <c r="H372" s="2">
+      <c r="H372" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9015,7 +8989,7 @@
       <c r="D373" t="s">
         <v>132</v>
       </c>
-      <c r="H373" s="2">
+      <c r="H373" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9038,7 +9012,7 @@
       <c r="G374" t="s">
         <v>177</v>
       </c>
-      <c r="H374" s="2">
+      <c r="H374" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9061,7 +9035,7 @@
       <c r="G375" t="s">
         <v>186</v>
       </c>
-      <c r="H375" s="2">
+      <c r="H375" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9084,7 +9058,7 @@
       <c r="G376" t="s">
         <v>178</v>
       </c>
-      <c r="H376" s="2">
+      <c r="H376" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9107,7 +9081,7 @@
       <c r="G377" t="s">
         <v>178</v>
       </c>
-      <c r="H377" s="2">
+      <c r="H377" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9130,7 +9104,7 @@
       <c r="G378" t="s">
         <v>179</v>
       </c>
-      <c r="H378" s="2">
+      <c r="H378" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9144,7 +9118,7 @@
       <c r="C379" t="s">
         <v>115</v>
       </c>
-      <c r="H379" s="2">
+      <c r="H379" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9167,7 +9141,7 @@
       <c r="G380" t="s">
         <v>190</v>
       </c>
-      <c r="H380" s="2">
+      <c r="H380" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9181,7 +9155,7 @@
       <c r="C381" t="s">
         <v>115</v>
       </c>
-      <c r="H381" s="2">
+      <c r="H381" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9195,7 +9169,7 @@
       <c r="C382" t="s">
         <v>115</v>
       </c>
-      <c r="H382" s="2">
+      <c r="H382" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9209,7 +9183,7 @@
       <c r="C383" t="s">
         <v>115</v>
       </c>
-      <c r="H383" s="2">
+      <c r="H383" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9223,7 +9197,7 @@
       <c r="C384" t="s">
         <v>119</v>
       </c>
-      <c r="H384" s="2">
+      <c r="H384" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9237,7 +9211,7 @@
       <c r="C385" t="s">
         <v>119</v>
       </c>
-      <c r="H385" s="2">
+      <c r="H385" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9260,7 +9234,7 @@
       <c r="G386" t="s">
         <v>189</v>
       </c>
-      <c r="H386" s="2">
+      <c r="H386" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9274,7 +9248,7 @@
       <c r="C387" t="s">
         <v>115</v>
       </c>
-      <c r="H387" s="2">
+      <c r="H387" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9288,7 +9262,7 @@
       <c r="C388" t="s">
         <v>119</v>
       </c>
-      <c r="H388" s="2">
+      <c r="H388" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9302,7 +9276,7 @@
       <c r="C389" t="s">
         <v>115</v>
       </c>
-      <c r="H389" s="2">
+      <c r="H389" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9316,7 +9290,7 @@
       <c r="C390" t="s">
         <v>115</v>
       </c>
-      <c r="H390" s="2">
+      <c r="H390" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9339,7 +9313,7 @@
       <c r="G391" t="s">
         <v>190</v>
       </c>
-      <c r="H391" s="2">
+      <c r="H391" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9362,7 +9336,7 @@
       <c r="G392" t="s">
         <v>191</v>
       </c>
-      <c r="H392" s="2">
+      <c r="H392" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9376,7 +9350,7 @@
       <c r="C393" t="s">
         <v>115</v>
       </c>
-      <c r="H393" s="2">
+      <c r="H393" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9399,7 +9373,7 @@
       <c r="G394" t="s">
         <v>190</v>
       </c>
-      <c r="H394" s="2">
+      <c r="H394" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9413,7 +9387,7 @@
       <c r="C395" t="s">
         <v>115</v>
       </c>
-      <c r="H395" s="2">
+      <c r="H395" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9427,7 +9401,7 @@
       <c r="C396" t="s">
         <v>115</v>
       </c>
-      <c r="H396" s="2">
+      <c r="H396" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9450,7 +9424,7 @@
       <c r="G397" t="s">
         <v>189</v>
       </c>
-      <c r="H397" s="2">
+      <c r="H397" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9473,7 +9447,7 @@
       <c r="G398" t="s">
         <v>190</v>
       </c>
-      <c r="H398" s="2">
+      <c r="H398" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9490,7 +9464,7 @@
       <c r="D399" t="s">
         <v>171</v>
       </c>
-      <c r="H399" s="2">
+      <c r="H399" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9504,7 +9478,7 @@
       <c r="C400" t="s">
         <v>115</v>
       </c>
-      <c r="H400" s="2">
+      <c r="H400" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9527,7 +9501,7 @@
       <c r="G401" t="s">
         <v>176</v>
       </c>
-      <c r="H401" s="2">
+      <c r="H401" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9544,7 +9518,7 @@
       <c r="D402" t="s">
         <v>132</v>
       </c>
-      <c r="H402" s="2">
+      <c r="H402" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9567,7 +9541,7 @@
       <c r="G403" t="s">
         <v>177</v>
       </c>
-      <c r="H403" s="2">
+      <c r="H403" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9590,7 +9564,7 @@
       <c r="G404" t="s">
         <v>186</v>
       </c>
-      <c r="H404" s="2">
+      <c r="H404" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9613,7 +9587,7 @@
       <c r="G405" t="s">
         <v>178</v>
       </c>
-      <c r="H405" s="2">
+      <c r="H405" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9636,7 +9610,7 @@
       <c r="G406" t="s">
         <v>178</v>
       </c>
-      <c r="H406" s="2">
+      <c r="H406" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9659,7 +9633,7 @@
       <c r="G407" t="s">
         <v>179</v>
       </c>
-      <c r="H407" s="2">
+      <c r="H407" s="1">
         <v>46226</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -651,8 +651,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -668,7 +676,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -676,12 +684,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -981,72 +1007,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1111,7 +1137,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1176,7 +1202,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1241,7 +1267,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1306,7 +1332,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1371,7 +1397,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1436,7 +1462,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1501,7 +1527,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1566,7 +1592,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1631,7 +1657,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1696,7 +1722,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1761,7 +1787,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -1826,7 +1852,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -1891,7 +1917,7 @@
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>46226</v>
       </c>
       <c r="B15">
@@ -1966,28 +1992,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2001,7 +2027,7 @@
       <c r="C2" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2015,7 +2041,7 @@
       <c r="C3" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2038,7 +2064,7 @@
       <c r="G4" t="s">
         <v>174</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2052,7 +2078,7 @@
       <c r="C5" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2066,7 +2092,7 @@
       <c r="C6" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2083,13 +2109,13 @@
       <c r="D7" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2106,13 +2132,13 @@
       <c r="D8" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>192</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2129,13 +2155,13 @@
       <c r="D9" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>193</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2152,13 +2178,13 @@
       <c r="D10" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2172,7 +2198,7 @@
       <c r="C11" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2186,7 +2212,7 @@
       <c r="C12" t="s">
         <v>115</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2203,13 +2229,13 @@
       <c r="D13" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>192</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2223,7 +2249,7 @@
       <c r="C14" t="s">
         <v>119</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2240,13 +2266,13 @@
       <c r="D15" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>195</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2260,7 +2286,7 @@
       <c r="C16" t="s">
         <v>115</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2274,7 +2300,7 @@
       <c r="C17" t="s">
         <v>115</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2291,13 +2317,13 @@
       <c r="D18" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>196</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2311,7 +2337,7 @@
       <c r="C19" t="s">
         <v>115</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2328,13 +2354,13 @@
       <c r="D20" t="s">
         <v>130</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>192</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2357,7 +2383,7 @@
       <c r="G21" t="s">
         <v>175</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2371,7 +2397,7 @@
       <c r="C22" t="s">
         <v>119</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2385,7 +2411,7 @@
       <c r="C23" t="s">
         <v>115</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2408,7 +2434,7 @@
       <c r="G24" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2425,7 +2451,7 @@
       <c r="D25" t="s">
         <v>132</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2448,7 +2474,7 @@
       <c r="G26" t="s">
         <v>177</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2465,13 +2491,13 @@
       <c r="D27" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="2">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>197</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2494,7 +2520,7 @@
       <c r="G28" t="s">
         <v>178</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2517,7 +2543,7 @@
       <c r="G29" t="s">
         <v>178</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2540,7 +2566,7 @@
       <c r="G30" t="s">
         <v>179</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2554,7 +2580,7 @@
       <c r="C31" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2568,7 +2594,7 @@
       <c r="C32" t="s">
         <v>115</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2591,7 +2617,7 @@
       <c r="G33" t="s">
         <v>180</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2605,7 +2631,7 @@
       <c r="C34" t="s">
         <v>115</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2619,7 +2645,7 @@
       <c r="C35" t="s">
         <v>115</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2636,13 +2662,13 @@
       <c r="D36" t="s">
         <v>123</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>192</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2659,13 +2685,13 @@
       <c r="D37" t="s">
         <v>124</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="2">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>192</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2682,13 +2708,13 @@
       <c r="D38" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="2">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>193</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2705,13 +2731,13 @@
       <c r="D39" t="s">
         <v>126</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="2">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>194</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2725,7 +2751,7 @@
       <c r="C40" t="s">
         <v>115</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2739,7 +2765,7 @@
       <c r="C41" t="s">
         <v>115</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2756,13 +2782,13 @@
       <c r="D42" t="s">
         <v>127</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>192</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2776,7 +2802,7 @@
       <c r="C43" t="s">
         <v>115</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2793,13 +2819,13 @@
       <c r="D44" t="s">
         <v>128</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>195</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H44" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2813,7 +2839,7 @@
       <c r="C45" t="s">
         <v>115</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H45" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2827,7 +2853,7 @@
       <c r="C46" t="s">
         <v>115</v>
       </c>
-      <c r="H46" s="1">
+      <c r="H46" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2841,7 +2867,7 @@
       <c r="C47" t="s">
         <v>119</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H47" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2855,7 +2881,7 @@
       <c r="C48" t="s">
         <v>115</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H48" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2872,13 +2898,13 @@
       <c r="D49" t="s">
         <v>139</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>192</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H49" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2901,7 +2927,7 @@
       <c r="G50" t="s">
         <v>175</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H50" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2915,7 +2941,7 @@
       <c r="C51" t="s">
         <v>119</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2929,7 +2955,7 @@
       <c r="C52" t="s">
         <v>115</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H52" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2952,7 +2978,7 @@
       <c r="G53" t="s">
         <v>176</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H53" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2969,7 +2995,7 @@
       <c r="D54" t="s">
         <v>132</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H54" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2992,7 +3018,7 @@
       <c r="G55" t="s">
         <v>177</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H55" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3009,13 +3035,13 @@
       <c r="D56" t="s">
         <v>134</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>197</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H56" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3038,7 +3064,7 @@
       <c r="G57" t="s">
         <v>178</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H57" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3061,7 +3087,7 @@
       <c r="G58" t="s">
         <v>178</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3084,7 +3110,7 @@
       <c r="G59" t="s">
         <v>179</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3098,7 +3124,7 @@
       <c r="C60" t="s">
         <v>115</v>
       </c>
-      <c r="H60" s="1">
+      <c r="H60" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3112,7 +3138,7 @@
       <c r="C61" t="s">
         <v>115</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H61" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3129,13 +3155,13 @@
       <c r="D62" t="s">
         <v>138</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="2">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>198</v>
       </c>
-      <c r="H62" s="1">
+      <c r="H62" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3149,7 +3175,7 @@
       <c r="C63" t="s">
         <v>115</v>
       </c>
-      <c r="H63" s="1">
+      <c r="H63" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3166,13 +3192,13 @@
       <c r="D64" t="s">
         <v>140</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="2">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>199</v>
       </c>
-      <c r="H64" s="1">
+      <c r="H64" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3186,7 +3212,7 @@
       <c r="C65" t="s">
         <v>115</v>
       </c>
-      <c r="H65" s="1">
+      <c r="H65" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3200,7 +3226,7 @@
       <c r="C66" t="s">
         <v>119</v>
       </c>
-      <c r="H66" s="1">
+      <c r="H66" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3217,13 +3243,13 @@
       <c r="D67" t="s">
         <v>125</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="2">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>193</v>
       </c>
-      <c r="H67" s="1">
+      <c r="H67" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3240,13 +3266,13 @@
       <c r="D68" t="s">
         <v>126</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="2">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>194</v>
       </c>
-      <c r="H68" s="1">
+      <c r="H68" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3260,7 +3286,7 @@
       <c r="C69" t="s">
         <v>115</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H69" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3274,7 +3300,7 @@
       <c r="C70" t="s">
         <v>115</v>
       </c>
-      <c r="H70" s="1">
+      <c r="H70" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3291,13 +3317,13 @@
       <c r="D71" t="s">
         <v>127</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="2">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>198</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H71" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3311,7 +3337,7 @@
       <c r="C72" t="s">
         <v>115</v>
       </c>
-      <c r="H72" s="1">
+      <c r="H72" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3328,13 +3354,13 @@
       <c r="D73" t="s">
         <v>128</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="2">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>195</v>
       </c>
-      <c r="H73" s="1">
+      <c r="H73" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3348,7 +3374,7 @@
       <c r="C74" t="s">
         <v>115</v>
       </c>
-      <c r="H74" s="1">
+      <c r="H74" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3362,7 +3388,7 @@
       <c r="C75" t="s">
         <v>115</v>
       </c>
-      <c r="H75" s="1">
+      <c r="H75" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3376,7 +3402,7 @@
       <c r="C76" t="s">
         <v>115</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H76" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3390,7 +3416,7 @@
       <c r="C77" t="s">
         <v>115</v>
       </c>
-      <c r="H77" s="1">
+      <c r="H77" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3407,13 +3433,13 @@
       <c r="D78" t="s">
         <v>139</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E78" s="2">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>198</v>
       </c>
-      <c r="H78" s="1">
+      <c r="H78" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3436,7 +3462,7 @@
       <c r="G79" t="s">
         <v>181</v>
       </c>
-      <c r="H79" s="1">
+      <c r="H79" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3450,7 +3476,7 @@
       <c r="C80" t="s">
         <v>119</v>
       </c>
-      <c r="H80" s="1">
+      <c r="H80" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3464,7 +3490,7 @@
       <c r="C81" t="s">
         <v>115</v>
       </c>
-      <c r="H81" s="1">
+      <c r="H81" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3487,7 +3513,7 @@
       <c r="G82" t="s">
         <v>176</v>
       </c>
-      <c r="H82" s="1">
+      <c r="H82" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3504,7 +3530,7 @@
       <c r="D83" t="s">
         <v>132</v>
       </c>
-      <c r="H83" s="1">
+      <c r="H83" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3527,7 +3553,7 @@
       <c r="G84" t="s">
         <v>177</v>
       </c>
-      <c r="H84" s="1">
+      <c r="H84" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3544,13 +3570,13 @@
       <c r="D85" t="s">
         <v>134</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85" s="2">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>197</v>
       </c>
-      <c r="H85" s="1">
+      <c r="H85" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3573,7 +3599,7 @@
       <c r="G86" t="s">
         <v>178</v>
       </c>
-      <c r="H86" s="1">
+      <c r="H86" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3596,7 +3622,7 @@
       <c r="G87" t="s">
         <v>178</v>
       </c>
-      <c r="H87" s="1">
+      <c r="H87" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3619,7 +3645,7 @@
       <c r="G88" t="s">
         <v>179</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H88" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3633,7 +3659,7 @@
       <c r="C89" t="s">
         <v>115</v>
       </c>
-      <c r="H89" s="1">
+      <c r="H89" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3650,13 +3676,13 @@
       <c r="D90" t="s">
         <v>142</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90" s="2">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>199</v>
       </c>
-      <c r="H90" s="1">
+      <c r="H90" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3673,13 +3699,13 @@
       <c r="D91" t="s">
         <v>138</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E91" s="2">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>198</v>
       </c>
-      <c r="H91" s="1">
+      <c r="H91" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3693,7 +3719,7 @@
       <c r="C92" t="s">
         <v>115</v>
       </c>
-      <c r="H92" s="1">
+      <c r="H92" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3710,13 +3736,13 @@
       <c r="D93" t="s">
         <v>140</v>
       </c>
-      <c r="E93" s="1">
+      <c r="E93" s="2">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>199</v>
       </c>
-      <c r="H93" s="1">
+      <c r="H93" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3730,7 +3756,7 @@
       <c r="C94" t="s">
         <v>115</v>
       </c>
-      <c r="H94" s="1">
+      <c r="H94" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3744,7 +3770,7 @@
       <c r="C95" t="s">
         <v>119</v>
       </c>
-      <c r="H95" s="1">
+      <c r="H95" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3761,13 +3787,13 @@
       <c r="D96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E96" s="2">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>193</v>
       </c>
-      <c r="H96" s="1">
+      <c r="H96" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3784,13 +3810,13 @@
       <c r="D97" t="s">
         <v>126</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E97" s="2">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>194</v>
       </c>
-      <c r="H97" s="1">
+      <c r="H97" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3804,7 +3830,7 @@
       <c r="C98" t="s">
         <v>115</v>
       </c>
-      <c r="H98" s="1">
+      <c r="H98" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3821,13 +3847,13 @@
       <c r="D99" t="s">
         <v>143</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99" s="2">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>194</v>
       </c>
-      <c r="H99" s="1">
+      <c r="H99" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3844,13 +3870,13 @@
       <c r="D100" t="s">
         <v>127</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="2">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>194</v>
       </c>
-      <c r="H100" s="1">
+      <c r="H100" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3864,7 +3890,7 @@
       <c r="C101" t="s">
         <v>115</v>
       </c>
-      <c r="H101" s="1">
+      <c r="H101" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3881,13 +3907,13 @@
       <c r="D102" t="s">
         <v>128</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102" s="2">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>195</v>
       </c>
-      <c r="H102" s="1">
+      <c r="H102" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3904,13 +3930,13 @@
       <c r="D103" t="s">
         <v>144</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103" s="2">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>194</v>
       </c>
-      <c r="H103" s="1">
+      <c r="H103" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3924,7 +3950,7 @@
       <c r="C104" t="s">
         <v>115</v>
       </c>
-      <c r="H104" s="1">
+      <c r="H104" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3938,7 +3964,7 @@
       <c r="C105" t="s">
         <v>115</v>
       </c>
-      <c r="H105" s="1">
+      <c r="H105" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3952,7 +3978,7 @@
       <c r="C106" t="s">
         <v>115</v>
       </c>
-      <c r="H106" s="1">
+      <c r="H106" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3969,13 +3995,13 @@
       <c r="D107" t="s">
         <v>145</v>
       </c>
-      <c r="E107" s="1">
+      <c r="E107" s="2">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>194</v>
       </c>
-      <c r="H107" s="1">
+      <c r="H107" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3998,7 +4024,7 @@
       <c r="G108" t="s">
         <v>181</v>
       </c>
-      <c r="H108" s="1">
+      <c r="H108" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4012,7 +4038,7 @@
       <c r="C109" t="s">
         <v>119</v>
       </c>
-      <c r="H109" s="1">
+      <c r="H109" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4026,7 +4052,7 @@
       <c r="C110" t="s">
         <v>115</v>
       </c>
-      <c r="H110" s="1">
+      <c r="H110" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4049,7 +4075,7 @@
       <c r="G111" t="s">
         <v>176</v>
       </c>
-      <c r="H111" s="1">
+      <c r="H111" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4066,7 +4092,7 @@
       <c r="D112" t="s">
         <v>132</v>
       </c>
-      <c r="H112" s="1">
+      <c r="H112" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4089,7 +4115,7 @@
       <c r="G113" t="s">
         <v>177</v>
       </c>
-      <c r="H113" s="1">
+      <c r="H113" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4106,13 +4132,13 @@
       <c r="D114" t="s">
         <v>134</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114" s="2">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>197</v>
       </c>
-      <c r="H114" s="1">
+      <c r="H114" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4135,7 +4161,7 @@
       <c r="G115" t="s">
         <v>178</v>
       </c>
-      <c r="H115" s="1">
+      <c r="H115" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4158,7 +4184,7 @@
       <c r="G116" t="s">
         <v>178</v>
       </c>
-      <c r="H116" s="1">
+      <c r="H116" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4181,7 +4207,7 @@
       <c r="G117" t="s">
         <v>179</v>
       </c>
-      <c r="H117" s="1">
+      <c r="H117" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4195,7 +4221,7 @@
       <c r="C118" t="s">
         <v>115</v>
       </c>
-      <c r="H118" s="1">
+      <c r="H118" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4212,13 +4238,13 @@
       <c r="D119" t="s">
         <v>142</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119" s="2">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>199</v>
       </c>
-      <c r="H119" s="1">
+      <c r="H119" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4232,7 +4258,7 @@
       <c r="C120" t="s">
         <v>119</v>
       </c>
-      <c r="H120" s="1">
+      <c r="H120" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4246,7 +4272,7 @@
       <c r="C121" t="s">
         <v>115</v>
       </c>
-      <c r="H121" s="1">
+      <c r="H121" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4260,7 +4286,7 @@
       <c r="C122" t="s">
         <v>119</v>
       </c>
-      <c r="H122" s="1">
+      <c r="H122" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4274,7 +4300,7 @@
       <c r="C123" t="s">
         <v>119</v>
       </c>
-      <c r="H123" s="1">
+      <c r="H123" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4288,7 +4314,7 @@
       <c r="C124" t="s">
         <v>119</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H124" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4305,13 +4331,13 @@
       <c r="D125" t="s">
         <v>125</v>
       </c>
-      <c r="E125" s="1">
+      <c r="E125" s="2">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>193</v>
       </c>
-      <c r="H125" s="1">
+      <c r="H125" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4328,13 +4354,13 @@
       <c r="D126" t="s">
         <v>126</v>
       </c>
-      <c r="E126" s="1">
+      <c r="E126" s="2">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>194</v>
       </c>
-      <c r="H126" s="1">
+      <c r="H126" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4348,7 +4374,7 @@
       <c r="C127" t="s">
         <v>115</v>
       </c>
-      <c r="H127" s="1">
+      <c r="H127" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4365,13 +4391,13 @@
       <c r="D128" t="s">
         <v>143</v>
       </c>
-      <c r="E128" s="1">
+      <c r="E128" s="2">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>194</v>
       </c>
-      <c r="H128" s="1">
+      <c r="H128" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4388,13 +4414,13 @@
       <c r="D129" t="s">
         <v>127</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E129" s="2">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>194</v>
       </c>
-      <c r="H129" s="1">
+      <c r="H129" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4408,7 +4434,7 @@
       <c r="C130" t="s">
         <v>115</v>
       </c>
-      <c r="H130" s="1">
+      <c r="H130" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4425,13 +4451,13 @@
       <c r="D131" t="s">
         <v>128</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E131" s="2">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>195</v>
       </c>
-      <c r="H131" s="1">
+      <c r="H131" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4448,13 +4474,13 @@
       <c r="D132" t="s">
         <v>144</v>
       </c>
-      <c r="E132" s="1">
+      <c r="E132" s="2">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>194</v>
       </c>
-      <c r="H132" s="1">
+      <c r="H132" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4468,7 +4494,7 @@
       <c r="C133" t="s">
         <v>115</v>
       </c>
-      <c r="H133" s="1">
+      <c r="H133" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4482,7 +4508,7 @@
       <c r="C134" t="s">
         <v>115</v>
       </c>
-      <c r="H134" s="1">
+      <c r="H134" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4496,7 +4522,7 @@
       <c r="C135" t="s">
         <v>115</v>
       </c>
-      <c r="H135" s="1">
+      <c r="H135" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4513,13 +4539,13 @@
       <c r="D136" t="s">
         <v>146</v>
       </c>
-      <c r="E136" s="1">
+      <c r="E136" s="2">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>194</v>
       </c>
-      <c r="H136" s="1">
+      <c r="H136" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4542,7 +4568,7 @@
       <c r="G137" t="s">
         <v>181</v>
       </c>
-      <c r="H137" s="1">
+      <c r="H137" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4556,7 +4582,7 @@
       <c r="C138" t="s">
         <v>119</v>
       </c>
-      <c r="H138" s="1">
+      <c r="H138" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4570,7 +4596,7 @@
       <c r="C139" t="s">
         <v>115</v>
       </c>
-      <c r="H139" s="1">
+      <c r="H139" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4593,7 +4619,7 @@
       <c r="G140" t="s">
         <v>176</v>
       </c>
-      <c r="H140" s="1">
+      <c r="H140" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4610,7 +4636,7 @@
       <c r="D141" t="s">
         <v>132</v>
       </c>
-      <c r="H141" s="1">
+      <c r="H141" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4633,7 +4659,7 @@
       <c r="G142" t="s">
         <v>177</v>
       </c>
-      <c r="H142" s="1">
+      <c r="H142" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4650,13 +4676,13 @@
       <c r="D143" t="s">
         <v>134</v>
       </c>
-      <c r="E143" s="1">
+      <c r="E143" s="2">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>197</v>
       </c>
-      <c r="H143" s="1">
+      <c r="H143" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4679,7 +4705,7 @@
       <c r="G144" t="s">
         <v>178</v>
       </c>
-      <c r="H144" s="1">
+      <c r="H144" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4702,7 +4728,7 @@
       <c r="G145" t="s">
         <v>178</v>
       </c>
-      <c r="H145" s="1">
+      <c r="H145" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4725,7 +4751,7 @@
       <c r="G146" t="s">
         <v>179</v>
       </c>
-      <c r="H146" s="1">
+      <c r="H146" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4739,7 +4765,7 @@
       <c r="C147" t="s">
         <v>115</v>
       </c>
-      <c r="H147" s="1">
+      <c r="H147" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4756,13 +4782,13 @@
       <c r="D148" t="s">
         <v>142</v>
       </c>
-      <c r="E148" s="1">
+      <c r="E148" s="2">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>199</v>
       </c>
-      <c r="H148" s="1">
+      <c r="H148" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4776,7 +4802,7 @@
       <c r="C149" t="s">
         <v>119</v>
       </c>
-      <c r="H149" s="1">
+      <c r="H149" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4790,7 +4816,7 @@
       <c r="C150" t="s">
         <v>115</v>
       </c>
-      <c r="H150" s="1">
+      <c r="H150" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4804,7 +4830,7 @@
       <c r="C151" t="s">
         <v>115</v>
       </c>
-      <c r="H151" s="1">
+      <c r="H151" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4818,7 +4844,7 @@
       <c r="C152" t="s">
         <v>119</v>
       </c>
-      <c r="H152" s="1">
+      <c r="H152" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4832,7 +4858,7 @@
       <c r="C153" t="s">
         <v>119</v>
       </c>
-      <c r="H153" s="1">
+      <c r="H153" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4849,13 +4875,13 @@
       <c r="D154" t="s">
         <v>125</v>
       </c>
-      <c r="E154" s="1">
+      <c r="E154" s="2">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>193</v>
       </c>
-      <c r="H154" s="1">
+      <c r="H154" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4872,13 +4898,13 @@
       <c r="D155" t="s">
         <v>126</v>
       </c>
-      <c r="E155" s="1">
+      <c r="E155" s="2">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>194</v>
       </c>
-      <c r="H155" s="1">
+      <c r="H155" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4892,7 +4918,7 @@
       <c r="C156" t="s">
         <v>115</v>
       </c>
-      <c r="H156" s="1">
+      <c r="H156" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4909,13 +4935,13 @@
       <c r="D157" t="s">
         <v>143</v>
       </c>
-      <c r="E157" s="1">
+      <c r="E157" s="2">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>194</v>
       </c>
-      <c r="H157" s="1">
+      <c r="H157" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4932,13 +4958,13 @@
       <c r="D158" t="s">
         <v>127</v>
       </c>
-      <c r="E158" s="1">
+      <c r="E158" s="2">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>194</v>
       </c>
-      <c r="H158" s="1">
+      <c r="H158" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4955,13 +4981,13 @@
       <c r="D159" t="s">
         <v>147</v>
       </c>
-      <c r="E159" s="1">
+      <c r="E159" s="2">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>200</v>
       </c>
-      <c r="H159" s="1">
+      <c r="H159" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4978,13 +5004,13 @@
       <c r="D160" t="s">
         <v>128</v>
       </c>
-      <c r="E160" s="1">
+      <c r="E160" s="2">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>195</v>
       </c>
-      <c r="H160" s="1">
+      <c r="H160" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5001,13 +5027,13 @@
       <c r="D161" t="s">
         <v>144</v>
       </c>
-      <c r="E161" s="1">
+      <c r="E161" s="2">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>194</v>
       </c>
-      <c r="H161" s="1">
+      <c r="H161" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5021,7 +5047,7 @@
       <c r="C162" t="s">
         <v>115</v>
       </c>
-      <c r="H162" s="1">
+      <c r="H162" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5035,7 +5061,7 @@
       <c r="C163" t="s">
         <v>115</v>
       </c>
-      <c r="H163" s="1">
+      <c r="H163" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5049,7 +5075,7 @@
       <c r="C164" t="s">
         <v>115</v>
       </c>
-      <c r="H164" s="1">
+      <c r="H164" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5066,13 +5092,13 @@
       <c r="D165" t="s">
         <v>146</v>
       </c>
-      <c r="E165" s="1">
+      <c r="E165" s="2">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>194</v>
       </c>
-      <c r="H165" s="1">
+      <c r="H165" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5095,7 +5121,7 @@
       <c r="G166" t="s">
         <v>181</v>
       </c>
-      <c r="H166" s="1">
+      <c r="H166" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5109,7 +5135,7 @@
       <c r="C167" t="s">
         <v>119</v>
       </c>
-      <c r="H167" s="1">
+      <c r="H167" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5123,7 +5149,7 @@
       <c r="C168" t="s">
         <v>115</v>
       </c>
-      <c r="H168" s="1">
+      <c r="H168" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5146,7 +5172,7 @@
       <c r="G169" t="s">
         <v>176</v>
       </c>
-      <c r="H169" s="1">
+      <c r="H169" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5163,7 +5189,7 @@
       <c r="D170" t="s">
         <v>132</v>
       </c>
-      <c r="H170" s="1">
+      <c r="H170" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5186,7 +5212,7 @@
       <c r="G171" t="s">
         <v>177</v>
       </c>
-      <c r="H171" s="1">
+      <c r="H171" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5203,13 +5229,13 @@
       <c r="D172" t="s">
         <v>134</v>
       </c>
-      <c r="E172" s="1">
+      <c r="E172" s="2">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>197</v>
       </c>
-      <c r="H172" s="1">
+      <c r="H172" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5232,7 +5258,7 @@
       <c r="G173" t="s">
         <v>178</v>
       </c>
-      <c r="H173" s="1">
+      <c r="H173" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5255,7 +5281,7 @@
       <c r="G174" t="s">
         <v>178</v>
       </c>
-      <c r="H174" s="1">
+      <c r="H174" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5278,7 +5304,7 @@
       <c r="G175" t="s">
         <v>179</v>
       </c>
-      <c r="H175" s="1">
+      <c r="H175" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5292,7 +5318,7 @@
       <c r="C176" t="s">
         <v>115</v>
       </c>
-      <c r="H176" s="1">
+      <c r="H176" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5309,13 +5335,13 @@
       <c r="D177" t="s">
         <v>148</v>
       </c>
-      <c r="E177" s="1">
+      <c r="E177" s="2">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>199</v>
       </c>
-      <c r="H177" s="1">
+      <c r="H177" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5329,7 +5355,7 @@
       <c r="C178" t="s">
         <v>115</v>
       </c>
-      <c r="H178" s="1">
+      <c r="H178" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5346,13 +5372,13 @@
       <c r="D179" t="s">
         <v>149</v>
       </c>
-      <c r="E179" s="1">
+      <c r="E179" s="2">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>195</v>
       </c>
-      <c r="H179" s="1">
+      <c r="H179" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5366,7 +5392,7 @@
       <c r="C180" t="s">
         <v>115</v>
       </c>
-      <c r="H180" s="1">
+      <c r="H180" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5380,7 +5406,7 @@
       <c r="C181" t="s">
         <v>119</v>
       </c>
-      <c r="H181" s="1">
+      <c r="H181" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5394,7 +5420,7 @@
       <c r="C182" t="s">
         <v>119</v>
       </c>
-      <c r="H182" s="1">
+      <c r="H182" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5411,13 +5437,13 @@
       <c r="D183" t="s">
         <v>125</v>
       </c>
-      <c r="E183" s="1">
+      <c r="E183" s="2">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>193</v>
       </c>
-      <c r="H183" s="1">
+      <c r="H183" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5434,13 +5460,13 @@
       <c r="D184" t="s">
         <v>126</v>
       </c>
-      <c r="E184" s="1">
+      <c r="E184" s="2">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>194</v>
       </c>
-      <c r="H184" s="1">
+      <c r="H184" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5454,7 +5480,7 @@
       <c r="C185" t="s">
         <v>115</v>
       </c>
-      <c r="H185" s="1">
+      <c r="H185" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5471,13 +5497,13 @@
       <c r="D186" t="s">
         <v>143</v>
       </c>
-      <c r="E186" s="1">
+      <c r="E186" s="2">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>194</v>
       </c>
-      <c r="H186" s="1">
+      <c r="H186" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5494,13 +5520,13 @@
       <c r="D187" t="s">
         <v>150</v>
       </c>
-      <c r="E187" s="1">
+      <c r="E187" s="2">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>194</v>
       </c>
-      <c r="H187" s="1">
+      <c r="H187" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5517,13 +5543,13 @@
       <c r="D188" t="s">
         <v>151</v>
       </c>
-      <c r="E188" s="1">
+      <c r="E188" s="2">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>194</v>
       </c>
-      <c r="H188" s="1">
+      <c r="H188" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5540,13 +5566,13 @@
       <c r="D189" t="s">
         <v>128</v>
       </c>
-      <c r="E189" s="1">
+      <c r="E189" s="2">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>195</v>
       </c>
-      <c r="H189" s="1">
+      <c r="H189" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5563,13 +5589,13 @@
       <c r="D190" t="s">
         <v>144</v>
       </c>
-      <c r="E190" s="1">
+      <c r="E190" s="2">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>194</v>
       </c>
-      <c r="H190" s="1">
+      <c r="H190" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5583,7 +5609,7 @@
       <c r="C191" t="s">
         <v>115</v>
       </c>
-      <c r="H191" s="1">
+      <c r="H191" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5597,7 +5623,7 @@
       <c r="C192" t="s">
         <v>115</v>
       </c>
-      <c r="H192" s="1">
+      <c r="H192" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5611,7 +5637,7 @@
       <c r="C193" t="s">
         <v>115</v>
       </c>
-      <c r="H193" s="1">
+      <c r="H193" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5628,13 +5654,13 @@
       <c r="D194" t="s">
         <v>146</v>
       </c>
-      <c r="E194" s="1">
+      <c r="E194" s="2">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>201</v>
       </c>
-      <c r="H194" s="1">
+      <c r="H194" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5657,7 +5683,7 @@
       <c r="G195" t="s">
         <v>181</v>
       </c>
-      <c r="H195" s="1">
+      <c r="H195" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5671,7 +5697,7 @@
       <c r="C196" t="s">
         <v>119</v>
       </c>
-      <c r="H196" s="1">
+      <c r="H196" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5685,7 +5711,7 @@
       <c r="C197" t="s">
         <v>115</v>
       </c>
-      <c r="H197" s="1">
+      <c r="H197" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5708,7 +5734,7 @@
       <c r="G198" t="s">
         <v>176</v>
       </c>
-      <c r="H198" s="1">
+      <c r="H198" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5725,7 +5751,7 @@
       <c r="D199" t="s">
         <v>132</v>
       </c>
-      <c r="H199" s="1">
+      <c r="H199" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5748,7 +5774,7 @@
       <c r="G200" t="s">
         <v>177</v>
       </c>
-      <c r="H200" s="1">
+      <c r="H200" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5765,13 +5791,13 @@
       <c r="D201" t="s">
         <v>134</v>
       </c>
-      <c r="E201" s="1">
+      <c r="E201" s="2">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>197</v>
       </c>
-      <c r="H201" s="1">
+      <c r="H201" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5794,7 +5820,7 @@
       <c r="G202" t="s">
         <v>178</v>
       </c>
-      <c r="H202" s="1">
+      <c r="H202" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5817,7 +5843,7 @@
       <c r="G203" t="s">
         <v>178</v>
       </c>
-      <c r="H203" s="1">
+      <c r="H203" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5840,7 +5866,7 @@
       <c r="G204" t="s">
         <v>179</v>
       </c>
-      <c r="H204" s="1">
+      <c r="H204" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5854,7 +5880,7 @@
       <c r="C205" t="s">
         <v>115</v>
       </c>
-      <c r="H205" s="1">
+      <c r="H205" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5871,13 +5897,13 @@
       <c r="D206" t="s">
         <v>148</v>
       </c>
-      <c r="E206" s="1">
+      <c r="E206" s="2">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>199</v>
       </c>
-      <c r="H206" s="1">
+      <c r="H206" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5891,7 +5917,7 @@
       <c r="C207" t="s">
         <v>115</v>
       </c>
-      <c r="H207" s="1">
+      <c r="H207" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5905,7 +5931,7 @@
       <c r="C208" t="s">
         <v>119</v>
       </c>
-      <c r="H208" s="1">
+      <c r="H208" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5919,7 +5945,7 @@
       <c r="C209" t="s">
         <v>115</v>
       </c>
-      <c r="H209" s="1">
+      <c r="H209" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5933,7 +5959,7 @@
       <c r="C210" t="s">
         <v>119</v>
       </c>
-      <c r="H210" s="1">
+      <c r="H210" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5947,7 +5973,7 @@
       <c r="C211" t="s">
         <v>119</v>
       </c>
-      <c r="H211" s="1">
+      <c r="H211" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5964,13 +5990,13 @@
       <c r="D212" t="s">
         <v>125</v>
       </c>
-      <c r="E212" s="1">
+      <c r="E212" s="2">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>193</v>
       </c>
-      <c r="H212" s="1">
+      <c r="H212" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5984,7 +6010,7 @@
       <c r="C213" t="s">
         <v>119</v>
       </c>
-      <c r="H213" s="1">
+      <c r="H213" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -5998,7 +6024,7 @@
       <c r="C214" t="s">
         <v>115</v>
       </c>
-      <c r="H214" s="1">
+      <c r="H214" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6015,13 +6041,13 @@
       <c r="D215" t="s">
         <v>143</v>
       </c>
-      <c r="E215" s="1">
+      <c r="E215" s="2">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>202</v>
       </c>
-      <c r="H215" s="1">
+      <c r="H215" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6038,13 +6064,13 @@
       <c r="D216" t="s">
         <v>150</v>
       </c>
-      <c r="E216" s="1">
+      <c r="E216" s="2">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>195</v>
       </c>
-      <c r="H216" s="1">
+      <c r="H216" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6058,7 +6084,7 @@
       <c r="C217" t="s">
         <v>115</v>
       </c>
-      <c r="H217" s="1">
+      <c r="H217" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6075,13 +6101,13 @@
       <c r="D218" t="s">
         <v>128</v>
       </c>
-      <c r="E218" s="1">
+      <c r="E218" s="2">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>195</v>
       </c>
-      <c r="H218" s="1">
+      <c r="H218" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6095,7 +6121,7 @@
       <c r="C219" t="s">
         <v>115</v>
       </c>
-      <c r="H219" s="1">
+      <c r="H219" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6109,7 +6135,7 @@
       <c r="C220" t="s">
         <v>115</v>
       </c>
-      <c r="H220" s="1">
+      <c r="H220" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6126,13 +6152,13 @@
       <c r="D221" t="s">
         <v>152</v>
       </c>
-      <c r="E221" s="1">
+      <c r="E221" s="2">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>199</v>
       </c>
-      <c r="H221" s="1">
+      <c r="H221" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6146,7 +6172,7 @@
       <c r="C222" t="s">
         <v>115</v>
       </c>
-      <c r="H222" s="1">
+      <c r="H222" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6163,13 +6189,13 @@
       <c r="D223" t="s">
         <v>153</v>
       </c>
-      <c r="E223" s="1">
+      <c r="E223" s="2">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>203</v>
       </c>
-      <c r="H223" s="1">
+      <c r="H223" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6192,7 +6218,7 @@
       <c r="G224" t="s">
         <v>181</v>
       </c>
-      <c r="H224" s="1">
+      <c r="H224" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6206,7 +6232,7 @@
       <c r="C225" t="s">
         <v>119</v>
       </c>
-      <c r="H225" s="1">
+      <c r="H225" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6220,7 +6246,7 @@
       <c r="C226" t="s">
         <v>115</v>
       </c>
-      <c r="H226" s="1">
+      <c r="H226" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6243,7 +6269,7 @@
       <c r="G227" t="s">
         <v>176</v>
       </c>
-      <c r="H227" s="1">
+      <c r="H227" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6260,7 +6286,7 @@
       <c r="D228" t="s">
         <v>132</v>
       </c>
-      <c r="H228" s="1">
+      <c r="H228" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6283,7 +6309,7 @@
       <c r="G229" t="s">
         <v>177</v>
       </c>
-      <c r="H229" s="1">
+      <c r="H229" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6300,13 +6326,13 @@
       <c r="D230" t="s">
         <v>154</v>
       </c>
-      <c r="E230" s="1">
+      <c r="E230" s="2">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>204</v>
       </c>
-      <c r="H230" s="1">
+      <c r="H230" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6329,7 +6355,7 @@
       <c r="G231" t="s">
         <v>178</v>
       </c>
-      <c r="H231" s="1">
+      <c r="H231" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6352,7 +6378,7 @@
       <c r="G232" t="s">
         <v>178</v>
       </c>
-      <c r="H232" s="1">
+      <c r="H232" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6375,7 +6401,7 @@
       <c r="G233" t="s">
         <v>179</v>
       </c>
-      <c r="H233" s="1">
+      <c r="H233" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6389,7 +6415,7 @@
       <c r="C234" t="s">
         <v>115</v>
       </c>
-      <c r="H234" s="1">
+      <c r="H234" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6406,13 +6432,13 @@
       <c r="D235" t="s">
         <v>155</v>
       </c>
-      <c r="E235" s="1">
+      <c r="E235" s="2">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>199</v>
       </c>
-      <c r="H235" s="1">
+      <c r="H235" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6426,7 +6452,7 @@
       <c r="C236" t="s">
         <v>115</v>
       </c>
-      <c r="H236" s="1">
+      <c r="H236" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6440,7 +6466,7 @@
       <c r="C237" t="s">
         <v>119</v>
       </c>
-      <c r="H237" s="1">
+      <c r="H237" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6454,7 +6480,7 @@
       <c r="C238" t="s">
         <v>115</v>
       </c>
-      <c r="H238" s="1">
+      <c r="H238" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6468,7 +6494,7 @@
       <c r="C239" t="s">
         <v>119</v>
       </c>
-      <c r="H239" s="1">
+      <c r="H239" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6482,7 +6508,7 @@
       <c r="C240" t="s">
         <v>119</v>
       </c>
-      <c r="H240" s="1">
+      <c r="H240" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6499,13 +6525,13 @@
       <c r="D241" t="s">
         <v>125</v>
       </c>
-      <c r="E241" s="1">
+      <c r="E241" s="2">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>193</v>
       </c>
-      <c r="H241" s="1">
+      <c r="H241" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6519,7 +6545,7 @@
       <c r="C242" t="s">
         <v>119</v>
       </c>
-      <c r="H242" s="1">
+      <c r="H242" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6536,13 +6562,13 @@
       <c r="D243" t="s">
         <v>156</v>
       </c>
-      <c r="E243" s="1">
+      <c r="E243" s="2">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>205</v>
       </c>
-      <c r="H243" s="1">
+      <c r="H243" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6559,13 +6585,13 @@
       <c r="D244" t="s">
         <v>157</v>
       </c>
-      <c r="E244" s="1">
+      <c r="E244" s="2">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>202</v>
       </c>
-      <c r="H244" s="1">
+      <c r="H244" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6579,7 +6605,7 @@
       <c r="C245" t="s">
         <v>119</v>
       </c>
-      <c r="H245" s="1">
+      <c r="H245" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6593,7 +6619,7 @@
       <c r="C246" t="s">
         <v>115</v>
       </c>
-      <c r="H246" s="1">
+      <c r="H246" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6610,13 +6636,13 @@
       <c r="D247" t="s">
         <v>128</v>
       </c>
-      <c r="E247" s="1">
+      <c r="E247" s="2">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>206</v>
       </c>
-      <c r="H247" s="1">
+      <c r="H247" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6630,7 +6656,7 @@
       <c r="C248" t="s">
         <v>115</v>
       </c>
-      <c r="H248" s="1">
+      <c r="H248" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6644,7 +6670,7 @@
       <c r="C249" t="s">
         <v>115</v>
       </c>
-      <c r="H249" s="1">
+      <c r="H249" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6661,13 +6687,13 @@
       <c r="D250" t="s">
         <v>158</v>
       </c>
-      <c r="E250" s="1">
+      <c r="E250" s="2">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>201</v>
       </c>
-      <c r="H250" s="1">
+      <c r="H250" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6681,7 +6707,7 @@
       <c r="C251" t="s">
         <v>115</v>
       </c>
-      <c r="H251" s="1">
+      <c r="H251" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6698,13 +6724,13 @@
       <c r="D252" t="s">
         <v>159</v>
       </c>
-      <c r="E252" s="1">
+      <c r="E252" s="2">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>203</v>
       </c>
-      <c r="H252" s="1">
+      <c r="H252" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6727,7 +6753,7 @@
       <c r="G253" t="s">
         <v>181</v>
       </c>
-      <c r="H253" s="1">
+      <c r="H253" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6741,7 +6767,7 @@
       <c r="C254" t="s">
         <v>119</v>
       </c>
-      <c r="H254" s="1">
+      <c r="H254" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6755,7 +6781,7 @@
       <c r="C255" t="s">
         <v>115</v>
       </c>
-      <c r="H255" s="1">
+      <c r="H255" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6778,7 +6804,7 @@
       <c r="G256" t="s">
         <v>176</v>
       </c>
-      <c r="H256" s="1">
+      <c r="H256" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6795,7 +6821,7 @@
       <c r="D257" t="s">
         <v>132</v>
       </c>
-      <c r="H257" s="1">
+      <c r="H257" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6818,7 +6844,7 @@
       <c r="G258" t="s">
         <v>177</v>
       </c>
-      <c r="H258" s="1">
+      <c r="H258" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6835,13 +6861,13 @@
       <c r="D259" t="s">
         <v>154</v>
       </c>
-      <c r="E259" s="1">
+      <c r="E259" s="2">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>204</v>
       </c>
-      <c r="H259" s="1">
+      <c r="H259" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6864,7 +6890,7 @@
       <c r="G260" t="s">
         <v>178</v>
       </c>
-      <c r="H260" s="1">
+      <c r="H260" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6887,7 +6913,7 @@
       <c r="G261" t="s">
         <v>178</v>
       </c>
-      <c r="H261" s="1">
+      <c r="H261" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6910,7 +6936,7 @@
       <c r="G262" t="s">
         <v>179</v>
       </c>
-      <c r="H262" s="1">
+      <c r="H262" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6924,7 +6950,7 @@
       <c r="C263" t="s">
         <v>115</v>
       </c>
-      <c r="H263" s="1">
+      <c r="H263" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -6941,13 +6967,13 @@
       <c r="D264" t="s">
         <v>155</v>
       </c>
-      <c r="E264" s="1">
+      <c r="E264" s="2">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>199</v>
       </c>
-      <c r="H264" s="1">
+      <c r="H264" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -6961,7 +6987,7 @@
       <c r="C265" t="s">
         <v>115</v>
       </c>
-      <c r="H265" s="1">
+      <c r="H265" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -6975,7 +7001,7 @@
       <c r="C266" t="s">
         <v>119</v>
       </c>
-      <c r="H266" s="1">
+      <c r="H266" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -6989,7 +7015,7 @@
       <c r="C267" t="s">
         <v>115</v>
       </c>
-      <c r="H267" s="1">
+      <c r="H267" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7003,7 +7029,7 @@
       <c r="C268" t="s">
         <v>119</v>
       </c>
-      <c r="H268" s="1">
+      <c r="H268" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7017,7 +7043,7 @@
       <c r="C269" t="s">
         <v>119</v>
       </c>
-      <c r="H269" s="1">
+      <c r="H269" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7034,13 +7060,13 @@
       <c r="D270" t="s">
         <v>125</v>
       </c>
-      <c r="E270" s="1">
+      <c r="E270" s="2">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>193</v>
       </c>
-      <c r="H270" s="1">
+      <c r="H270" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7054,7 +7080,7 @@
       <c r="C271" t="s">
         <v>119</v>
       </c>
-      <c r="H271" s="1">
+      <c r="H271" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7071,13 +7097,13 @@
       <c r="D272" t="s">
         <v>156</v>
       </c>
-      <c r="E272" s="1">
+      <c r="E272" s="2">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>205</v>
       </c>
-      <c r="H272" s="1">
+      <c r="H272" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7094,13 +7120,13 @@
       <c r="D273" t="s">
         <v>157</v>
       </c>
-      <c r="E273" s="1">
+      <c r="E273" s="2">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>207</v>
       </c>
-      <c r="H273" s="1">
+      <c r="H273" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7114,7 +7140,7 @@
       <c r="C274" t="s">
         <v>115</v>
       </c>
-      <c r="H274" s="1">
+      <c r="H274" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7128,7 +7154,7 @@
       <c r="C275" t="s">
         <v>115</v>
       </c>
-      <c r="H275" s="1">
+      <c r="H275" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7145,13 +7171,13 @@
       <c r="D276" t="s">
         <v>128</v>
       </c>
-      <c r="E276" s="1">
+      <c r="E276" s="2">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>206</v>
       </c>
-      <c r="H276" s="1">
+      <c r="H276" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7165,7 +7191,7 @@
       <c r="C277" t="s">
         <v>115</v>
       </c>
-      <c r="H277" s="1">
+      <c r="H277" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7182,13 +7208,13 @@
       <c r="D278" t="s">
         <v>160</v>
       </c>
-      <c r="E278" s="1">
+      <c r="E278" s="2">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>208</v>
       </c>
-      <c r="H278" s="1">
+      <c r="H278" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7205,13 +7231,13 @@
       <c r="D279" t="s">
         <v>158</v>
       </c>
-      <c r="E279" s="1">
+      <c r="E279" s="2">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>207</v>
       </c>
-      <c r="H279" s="1">
+      <c r="H279" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7225,7 +7251,7 @@
       <c r="C280" t="s">
         <v>115</v>
       </c>
-      <c r="H280" s="1">
+      <c r="H280" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7242,13 +7268,13 @@
       <c r="D281" t="s">
         <v>161</v>
       </c>
-      <c r="E281" s="1">
+      <c r="E281" s="2">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>203</v>
       </c>
-      <c r="H281" s="1">
+      <c r="H281" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7271,7 +7297,7 @@
       <c r="G282" t="s">
         <v>181</v>
       </c>
-      <c r="H282" s="1">
+      <c r="H282" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7285,7 +7311,7 @@
       <c r="C283" t="s">
         <v>119</v>
       </c>
-      <c r="H283" s="1">
+      <c r="H283" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7299,7 +7325,7 @@
       <c r="C284" t="s">
         <v>115</v>
       </c>
-      <c r="H284" s="1">
+      <c r="H284" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7322,7 +7348,7 @@
       <c r="G285" t="s">
         <v>176</v>
       </c>
-      <c r="H285" s="1">
+      <c r="H285" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7339,7 +7365,7 @@
       <c r="D286" t="s">
         <v>132</v>
       </c>
-      <c r="H286" s="1">
+      <c r="H286" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7362,7 +7388,7 @@
       <c r="G287" t="s">
         <v>177</v>
       </c>
-      <c r="H287" s="1">
+      <c r="H287" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7379,13 +7405,13 @@
       <c r="D288" t="s">
         <v>154</v>
       </c>
-      <c r="E288" s="1">
+      <c r="E288" s="2">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>204</v>
       </c>
-      <c r="H288" s="1">
+      <c r="H288" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7408,7 +7434,7 @@
       <c r="G289" t="s">
         <v>178</v>
       </c>
-      <c r="H289" s="1">
+      <c r="H289" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7431,7 +7457,7 @@
       <c r="G290" t="s">
         <v>178</v>
       </c>
-      <c r="H290" s="1">
+      <c r="H290" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7454,7 +7480,7 @@
       <c r="G291" t="s">
         <v>179</v>
       </c>
-      <c r="H291" s="1">
+      <c r="H291" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7468,7 +7494,7 @@
       <c r="C292" t="s">
         <v>115</v>
       </c>
-      <c r="H292" s="1">
+      <c r="H292" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7491,7 +7517,7 @@
       <c r="G293" t="s">
         <v>182</v>
       </c>
-      <c r="H293" s="1">
+      <c r="H293" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7505,7 +7531,7 @@
       <c r="C294" t="s">
         <v>115</v>
       </c>
-      <c r="H294" s="1">
+      <c r="H294" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7528,7 +7554,7 @@
       <c r="G295" t="s">
         <v>183</v>
       </c>
-      <c r="H295" s="1">
+      <c r="H295" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7542,7 +7568,7 @@
       <c r="C296" t="s">
         <v>115</v>
       </c>
-      <c r="H296" s="1">
+      <c r="H296" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7556,7 +7582,7 @@
       <c r="C297" t="s">
         <v>119</v>
       </c>
-      <c r="H297" s="1">
+      <c r="H297" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7579,7 +7605,7 @@
       <c r="G298" t="s">
         <v>184</v>
       </c>
-      <c r="H298" s="1">
+      <c r="H298" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7596,13 +7622,13 @@
       <c r="D299" t="s">
         <v>125</v>
       </c>
-      <c r="E299" s="1">
+      <c r="E299" s="2">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>193</v>
       </c>
-      <c r="H299" s="1">
+      <c r="H299" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7616,7 +7642,7 @@
       <c r="C300" t="s">
         <v>115</v>
       </c>
-      <c r="H300" s="1">
+      <c r="H300" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7633,13 +7659,13 @@
       <c r="D301" t="s">
         <v>156</v>
       </c>
-      <c r="E301" s="1">
+      <c r="E301" s="2">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>205</v>
       </c>
-      <c r="H301" s="1">
+      <c r="H301" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7656,13 +7682,13 @@
       <c r="D302" t="s">
         <v>157</v>
       </c>
-      <c r="E302" s="1">
+      <c r="E302" s="2">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>202</v>
       </c>
-      <c r="H302" s="1">
+      <c r="H302" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7676,7 +7702,7 @@
       <c r="C303" t="s">
         <v>115</v>
       </c>
-      <c r="H303" s="1">
+      <c r="H303" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7690,7 +7716,7 @@
       <c r="C304" t="s">
         <v>115</v>
       </c>
-      <c r="H304" s="1">
+      <c r="H304" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7707,13 +7733,13 @@
       <c r="D305" t="s">
         <v>128</v>
       </c>
-      <c r="E305" s="1">
+      <c r="E305" s="2">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>206</v>
       </c>
-      <c r="H305" s="1">
+      <c r="H305" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7727,7 +7753,7 @@
       <c r="C306" t="s">
         <v>115</v>
       </c>
-      <c r="H306" s="1">
+      <c r="H306" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7744,13 +7770,13 @@
       <c r="D307" t="s">
         <v>160</v>
       </c>
-      <c r="E307" s="1">
+      <c r="E307" s="2">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>208</v>
       </c>
-      <c r="H307" s="1">
+      <c r="H307" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7764,7 +7790,7 @@
       <c r="C308" t="s">
         <v>119</v>
       </c>
-      <c r="H308" s="1">
+      <c r="H308" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7787,7 +7813,7 @@
       <c r="G309" t="s">
         <v>182</v>
       </c>
-      <c r="H309" s="1">
+      <c r="H309" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7810,7 +7836,7 @@
       <c r="G310" t="s">
         <v>185</v>
       </c>
-      <c r="H310" s="1">
+      <c r="H310" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7827,7 +7853,7 @@
       <c r="D311" t="s">
         <v>166</v>
       </c>
-      <c r="H311" s="1">
+      <c r="H311" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7841,7 +7867,7 @@
       <c r="C312" t="s">
         <v>119</v>
       </c>
-      <c r="H312" s="1">
+      <c r="H312" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7855,7 +7881,7 @@
       <c r="C313" t="s">
         <v>115</v>
       </c>
-      <c r="H313" s="1">
+      <c r="H313" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7878,7 +7904,7 @@
       <c r="G314" t="s">
         <v>176</v>
       </c>
-      <c r="H314" s="1">
+      <c r="H314" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7895,7 +7921,7 @@
       <c r="D315" t="s">
         <v>132</v>
       </c>
-      <c r="H315" s="1">
+      <c r="H315" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7918,7 +7944,7 @@
       <c r="G316" t="s">
         <v>177</v>
       </c>
-      <c r="H316" s="1">
+      <c r="H316" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7941,7 +7967,7 @@
       <c r="G317" t="s">
         <v>186</v>
       </c>
-      <c r="H317" s="1">
+      <c r="H317" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7964,7 +7990,7 @@
       <c r="G318" t="s">
         <v>178</v>
       </c>
-      <c r="H318" s="1">
+      <c r="H318" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7987,7 +8013,7 @@
       <c r="G319" t="s">
         <v>178</v>
       </c>
-      <c r="H319" s="1">
+      <c r="H319" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8010,7 +8036,7 @@
       <c r="G320" t="s">
         <v>179</v>
       </c>
-      <c r="H320" s="1">
+      <c r="H320" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8024,7 +8050,7 @@
       <c r="C321" t="s">
         <v>115</v>
       </c>
-      <c r="H321" s="1">
+      <c r="H321" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8047,7 +8073,7 @@
       <c r="G322" t="s">
         <v>187</v>
       </c>
-      <c r="H322" s="1">
+      <c r="H322" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8061,7 +8087,7 @@
       <c r="C323" t="s">
         <v>115</v>
       </c>
-      <c r="H323" s="1">
+      <c r="H323" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8084,7 +8110,7 @@
       <c r="G324" t="s">
         <v>188</v>
       </c>
-      <c r="H324" s="1">
+      <c r="H324" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8098,7 +8124,7 @@
       <c r="C325" t="s">
         <v>115</v>
       </c>
-      <c r="H325" s="1">
+      <c r="H325" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8112,7 +8138,7 @@
       <c r="C326" t="s">
         <v>119</v>
       </c>
-      <c r="H326" s="1">
+      <c r="H326" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8126,7 +8152,7 @@
       <c r="C327" t="s">
         <v>119</v>
       </c>
-      <c r="H327" s="1">
+      <c r="H327" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8143,13 +8169,13 @@
       <c r="D328" t="s">
         <v>125</v>
       </c>
-      <c r="E328" s="1">
+      <c r="E328" s="2">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>193</v>
       </c>
-      <c r="H328" s="1">
+      <c r="H328" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8172,7 +8198,7 @@
       <c r="G329" t="s">
         <v>188</v>
       </c>
-      <c r="H329" s="1">
+      <c r="H329" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8195,7 +8221,7 @@
       <c r="G330" t="s">
         <v>188</v>
       </c>
-      <c r="H330" s="1">
+      <c r="H330" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8209,7 +8235,7 @@
       <c r="C331" t="s">
         <v>115</v>
       </c>
-      <c r="H331" s="1">
+      <c r="H331" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8232,7 +8258,7 @@
       <c r="G332" t="s">
         <v>188</v>
       </c>
-      <c r="H332" s="1">
+      <c r="H332" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8255,7 +8281,7 @@
       <c r="G333" t="s">
         <v>187</v>
       </c>
-      <c r="H333" s="1">
+      <c r="H333" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8272,13 +8298,13 @@
       <c r="D334" t="s">
         <v>128</v>
       </c>
-      <c r="E334" s="1">
+      <c r="E334" s="2">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>206</v>
       </c>
-      <c r="H334" s="1">
+      <c r="H334" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8292,7 +8318,7 @@
       <c r="C335" t="s">
         <v>115</v>
       </c>
-      <c r="H335" s="1">
+      <c r="H335" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8309,13 +8335,13 @@
       <c r="D336" t="s">
         <v>160</v>
       </c>
-      <c r="E336" s="1">
+      <c r="E336" s="2">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>208</v>
       </c>
-      <c r="H336" s="1">
+      <c r="H336" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8329,7 +8355,7 @@
       <c r="C337" t="s">
         <v>115</v>
       </c>
-      <c r="H337" s="1">
+      <c r="H337" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8343,7 +8369,7 @@
       <c r="C338" t="s">
         <v>115</v>
       </c>
-      <c r="H338" s="1">
+      <c r="H338" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8366,7 +8392,7 @@
       <c r="G339" t="s">
         <v>185</v>
       </c>
-      <c r="H339" s="1">
+      <c r="H339" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8383,7 +8409,7 @@
       <c r="D340" t="s">
         <v>171</v>
       </c>
-      <c r="H340" s="1">
+      <c r="H340" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8397,7 +8423,7 @@
       <c r="C341" t="s">
         <v>119</v>
       </c>
-      <c r="H341" s="1">
+      <c r="H341" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8411,7 +8437,7 @@
       <c r="C342" t="s">
         <v>115</v>
       </c>
-      <c r="H342" s="1">
+      <c r="H342" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8434,7 +8460,7 @@
       <c r="G343" t="s">
         <v>176</v>
       </c>
-      <c r="H343" s="1">
+      <c r="H343" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8451,7 +8477,7 @@
       <c r="D344" t="s">
         <v>132</v>
       </c>
-      <c r="H344" s="1">
+      <c r="H344" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8474,7 +8500,7 @@
       <c r="G345" t="s">
         <v>177</v>
       </c>
-      <c r="H345" s="1">
+      <c r="H345" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8497,7 +8523,7 @@
       <c r="G346" t="s">
         <v>186</v>
       </c>
-      <c r="H346" s="1">
+      <c r="H346" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8520,7 +8546,7 @@
       <c r="G347" t="s">
         <v>178</v>
       </c>
-      <c r="H347" s="1">
+      <c r="H347" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8543,7 +8569,7 @@
       <c r="G348" t="s">
         <v>178</v>
       </c>
-      <c r="H348" s="1">
+      <c r="H348" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8566,7 +8592,7 @@
       <c r="G349" t="s">
         <v>179</v>
       </c>
-      <c r="H349" s="1">
+      <c r="H349" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8580,7 +8606,7 @@
       <c r="C350" t="s">
         <v>115</v>
       </c>
-      <c r="H350" s="1">
+      <c r="H350" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8603,7 +8629,7 @@
       <c r="G351" t="s">
         <v>187</v>
       </c>
-      <c r="H351" s="1">
+      <c r="H351" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8617,7 +8643,7 @@
       <c r="C352" t="s">
         <v>115</v>
       </c>
-      <c r="H352" s="1">
+      <c r="H352" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8631,7 +8657,7 @@
       <c r="C353" t="s">
         <v>115</v>
       </c>
-      <c r="H353" s="1">
+      <c r="H353" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8645,7 +8671,7 @@
       <c r="C354" t="s">
         <v>115</v>
       </c>
-      <c r="H354" s="1">
+      <c r="H354" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8659,7 +8685,7 @@
       <c r="C355" t="s">
         <v>119</v>
       </c>
-      <c r="H355" s="1">
+      <c r="H355" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8673,7 +8699,7 @@
       <c r="C356" t="s">
         <v>119</v>
       </c>
-      <c r="H356" s="1">
+      <c r="H356" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8696,7 +8722,7 @@
       <c r="G357" t="s">
         <v>189</v>
       </c>
-      <c r="H357" s="1">
+      <c r="H357" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8710,7 +8736,7 @@
       <c r="C358" t="s">
         <v>115</v>
       </c>
-      <c r="H358" s="1">
+      <c r="H358" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8733,7 +8759,7 @@
       <c r="G359" t="s">
         <v>190</v>
       </c>
-      <c r="H359" s="1">
+      <c r="H359" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8747,7 +8773,7 @@
       <c r="C360" t="s">
         <v>115</v>
       </c>
-      <c r="H360" s="1">
+      <c r="H360" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8761,7 +8787,7 @@
       <c r="C361" t="s">
         <v>115</v>
       </c>
-      <c r="H361" s="1">
+      <c r="H361" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8784,7 +8810,7 @@
       <c r="G362" t="s">
         <v>187</v>
       </c>
-      <c r="H362" s="1">
+      <c r="H362" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8807,7 +8833,7 @@
       <c r="G363" t="s">
         <v>191</v>
       </c>
-      <c r="H363" s="1">
+      <c r="H363" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8821,7 +8847,7 @@
       <c r="C364" t="s">
         <v>115</v>
       </c>
-      <c r="H364" s="1">
+      <c r="H364" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8844,7 +8870,7 @@
       <c r="G365" t="s">
         <v>190</v>
       </c>
-      <c r="H365" s="1">
+      <c r="H365" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8858,7 +8884,7 @@
       <c r="C366" t="s">
         <v>115</v>
       </c>
-      <c r="H366" s="1">
+      <c r="H366" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8872,7 +8898,7 @@
       <c r="C367" t="s">
         <v>115</v>
       </c>
-      <c r="H367" s="1">
+      <c r="H367" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8895,7 +8921,7 @@
       <c r="G368" t="s">
         <v>189</v>
       </c>
-      <c r="H368" s="1">
+      <c r="H368" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8918,7 +8944,7 @@
       <c r="G369" t="s">
         <v>190</v>
       </c>
-      <c r="H369" s="1">
+      <c r="H369" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8935,7 +8961,7 @@
       <c r="D370" t="s">
         <v>171</v>
       </c>
-      <c r="H370" s="1">
+      <c r="H370" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8949,7 +8975,7 @@
       <c r="C371" t="s">
         <v>115</v>
       </c>
-      <c r="H371" s="1">
+      <c r="H371" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8972,7 +8998,7 @@
       <c r="G372" t="s">
         <v>176</v>
       </c>
-      <c r="H372" s="1">
+      <c r="H372" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8989,7 +9015,7 @@
       <c r="D373" t="s">
         <v>132</v>
       </c>
-      <c r="H373" s="1">
+      <c r="H373" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9012,7 +9038,7 @@
       <c r="G374" t="s">
         <v>177</v>
       </c>
-      <c r="H374" s="1">
+      <c r="H374" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9035,7 +9061,7 @@
       <c r="G375" t="s">
         <v>186</v>
       </c>
-      <c r="H375" s="1">
+      <c r="H375" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9058,7 +9084,7 @@
       <c r="G376" t="s">
         <v>178</v>
       </c>
-      <c r="H376" s="1">
+      <c r="H376" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9081,7 +9107,7 @@
       <c r="G377" t="s">
         <v>178</v>
       </c>
-      <c r="H377" s="1">
+      <c r="H377" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9104,7 +9130,7 @@
       <c r="G378" t="s">
         <v>179</v>
       </c>
-      <c r="H378" s="1">
+      <c r="H378" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9118,7 +9144,7 @@
       <c r="C379" t="s">
         <v>115</v>
       </c>
-      <c r="H379" s="1">
+      <c r="H379" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9141,7 +9167,7 @@
       <c r="G380" t="s">
         <v>190</v>
       </c>
-      <c r="H380" s="1">
+      <c r="H380" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9155,7 +9181,7 @@
       <c r="C381" t="s">
         <v>115</v>
       </c>
-      <c r="H381" s="1">
+      <c r="H381" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9169,7 +9195,7 @@
       <c r="C382" t="s">
         <v>115</v>
       </c>
-      <c r="H382" s="1">
+      <c r="H382" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9183,7 +9209,7 @@
       <c r="C383" t="s">
         <v>115</v>
       </c>
-      <c r="H383" s="1">
+      <c r="H383" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9197,7 +9223,7 @@
       <c r="C384" t="s">
         <v>119</v>
       </c>
-      <c r="H384" s="1">
+      <c r="H384" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9211,7 +9237,7 @@
       <c r="C385" t="s">
         <v>119</v>
       </c>
-      <c r="H385" s="1">
+      <c r="H385" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9234,7 +9260,7 @@
       <c r="G386" t="s">
         <v>189</v>
       </c>
-      <c r="H386" s="1">
+      <c r="H386" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9248,7 +9274,7 @@
       <c r="C387" t="s">
         <v>115</v>
       </c>
-      <c r="H387" s="1">
+      <c r="H387" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9262,7 +9288,7 @@
       <c r="C388" t="s">
         <v>119</v>
       </c>
-      <c r="H388" s="1">
+      <c r="H388" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9276,7 +9302,7 @@
       <c r="C389" t="s">
         <v>115</v>
       </c>
-      <c r="H389" s="1">
+      <c r="H389" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9290,7 +9316,7 @@
       <c r="C390" t="s">
         <v>115</v>
       </c>
-      <c r="H390" s="1">
+      <c r="H390" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9313,7 +9339,7 @@
       <c r="G391" t="s">
         <v>190</v>
       </c>
-      <c r="H391" s="1">
+      <c r="H391" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9336,7 +9362,7 @@
       <c r="G392" t="s">
         <v>191</v>
       </c>
-      <c r="H392" s="1">
+      <c r="H392" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9350,7 +9376,7 @@
       <c r="C393" t="s">
         <v>115</v>
       </c>
-      <c r="H393" s="1">
+      <c r="H393" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9373,7 +9399,7 @@
       <c r="G394" t="s">
         <v>190</v>
       </c>
-      <c r="H394" s="1">
+      <c r="H394" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9387,7 +9413,7 @@
       <c r="C395" t="s">
         <v>115</v>
       </c>
-      <c r="H395" s="1">
+      <c r="H395" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9401,7 +9427,7 @@
       <c r="C396" t="s">
         <v>115</v>
       </c>
-      <c r="H396" s="1">
+      <c r="H396" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9424,7 +9450,7 @@
       <c r="G397" t="s">
         <v>189</v>
       </c>
-      <c r="H397" s="1">
+      <c r="H397" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9447,7 +9473,7 @@
       <c r="G398" t="s">
         <v>190</v>
       </c>
-      <c r="H398" s="1">
+      <c r="H398" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9464,7 +9490,7 @@
       <c r="D399" t="s">
         <v>171</v>
       </c>
-      <c r="H399" s="1">
+      <c r="H399" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9478,7 +9504,7 @@
       <c r="C400" t="s">
         <v>115</v>
       </c>
-      <c r="H400" s="1">
+      <c r="H400" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9501,7 +9527,7 @@
       <c r="G401" t="s">
         <v>176</v>
       </c>
-      <c r="H401" s="1">
+      <c r="H401" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9518,7 +9544,7 @@
       <c r="D402" t="s">
         <v>132</v>
       </c>
-      <c r="H402" s="1">
+      <c r="H402" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9541,7 +9567,7 @@
       <c r="G403" t="s">
         <v>177</v>
       </c>
-      <c r="H403" s="1">
+      <c r="H403" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9564,7 +9590,7 @@
       <c r="G404" t="s">
         <v>186</v>
       </c>
-      <c r="H404" s="1">
+      <c r="H404" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9587,7 +9613,7 @@
       <c r="G405" t="s">
         <v>178</v>
       </c>
-      <c r="H405" s="1">
+      <c r="H405" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9610,7 +9636,7 @@
       <c r="G406" t="s">
         <v>178</v>
       </c>
-      <c r="H406" s="1">
+      <c r="H406" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9633,7 +9659,7 @@
       <c r="G407" t="s">
         <v>179</v>
       </c>
-      <c r="H407" s="1">
+      <c r="H407" s="2">
         <v>46226</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="222">
   <si>
     <t>data_referencia</t>
   </si>
@@ -596,12 +596,63 @@
     <t>02 DIAS após chegada do item - Solicitado alteração de DPE e situação no SILOMS.</t>
   </si>
   <si>
+    <t>01 DIA APÓS CHEGADA DO MATERIAL.</t>
+  </si>
+  <si>
+    <t>03/07</t>
+  </si>
+  <si>
+    <t>31/07</t>
+  </si>
+  <si>
+    <t>10/07</t>
+  </si>
+  <si>
+    <t>13/07</t>
+  </si>
+  <si>
+    <t>01/07</t>
+  </si>
+  <si>
+    <t>06/07</t>
+  </si>
+  <si>
+    <t>07/07</t>
+  </si>
+  <si>
+    <t>14/07</t>
+  </si>
+  <si>
+    <t>09/07</t>
+  </si>
+  <si>
+    <t>15/07</t>
+  </si>
+  <si>
+    <t>17/07</t>
+  </si>
+  <si>
+    <t>07/08</t>
+  </si>
+  <si>
+    <t>30/09</t>
+  </si>
+  <si>
+    <t>21/07</t>
+  </si>
+  <si>
+    <t>03/08</t>
+  </si>
+  <si>
+    <t>16/07</t>
+  </si>
+  <si>
+    <t>24/07</t>
+  </si>
+  <si>
     <t>17/07.</t>
   </si>
   <si>
-    <t>01 DIA APÓS CHEGADA DO MATERIAL.</t>
-  </si>
-  <si>
     <t>20/07.</t>
   </si>
   <si>
@@ -630,57 +681,6 @@
   </si>
   <si>
     <t>27/07.</t>
-  </si>
-  <si>
-    <t>03/07</t>
-  </si>
-  <si>
-    <t>31/07</t>
-  </si>
-  <si>
-    <t>10/07</t>
-  </si>
-  <si>
-    <t>13/07</t>
-  </si>
-  <si>
-    <t>01/07</t>
-  </si>
-  <si>
-    <t>06/07</t>
-  </si>
-  <si>
-    <t>07/07</t>
-  </si>
-  <si>
-    <t>14/07</t>
-  </si>
-  <si>
-    <t>09/07</t>
-  </si>
-  <si>
-    <t>15/07</t>
-  </si>
-  <si>
-    <t>17/07</t>
-  </si>
-  <si>
-    <t>07/08</t>
-  </si>
-  <si>
-    <t>30/09</t>
-  </si>
-  <si>
-    <t>21/07</t>
-  </si>
-  <si>
-    <t>03/08</t>
-  </si>
-  <si>
-    <t>16/07</t>
-  </si>
-  <si>
-    <t>24/07</t>
   </si>
 </sst>
 </file>
@@ -2282,7 +2282,7 @@
         <v>46206</v>
       </c>
       <c r="G7" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H7" s="2">
         <v>46204</v>
@@ -2305,7 +2305,7 @@
         <v>46206</v>
       </c>
       <c r="G8" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H8" s="2">
         <v>46204</v>
@@ -2328,7 +2328,7 @@
         <v>46234</v>
       </c>
       <c r="G9" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H9" s="2">
         <v>46204</v>
@@ -2351,7 +2351,7 @@
         <v>46213</v>
       </c>
       <c r="G10" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H10" s="2">
         <v>46204</v>
@@ -2402,7 +2402,7 @@
         <v>46206</v>
       </c>
       <c r="G13" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H13" s="2">
         <v>46204</v>
@@ -2439,7 +2439,7 @@
         <v>46216</v>
       </c>
       <c r="G15" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H15" s="2">
         <v>46204</v>
@@ -2490,7 +2490,7 @@
         <v>46204</v>
       </c>
       <c r="G18" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="H18" s="2">
         <v>46204</v>
@@ -2527,7 +2527,7 @@
         <v>46206</v>
       </c>
       <c r="G20" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H20" s="2">
         <v>46204</v>
@@ -2664,7 +2664,7 @@
         <v>46209</v>
       </c>
       <c r="G27" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H27" s="2">
         <v>46204</v>
@@ -2835,7 +2835,7 @@
         <v>46206</v>
       </c>
       <c r="G36" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H36" s="2">
         <v>46205</v>
@@ -2858,7 +2858,7 @@
         <v>46206</v>
       </c>
       <c r="G37" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H37" s="2">
         <v>46205</v>
@@ -2881,7 +2881,7 @@
         <v>46234</v>
       </c>
       <c r="G38" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H38" s="2">
         <v>46205</v>
@@ -2904,7 +2904,7 @@
         <v>46213</v>
       </c>
       <c r="G39" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H39" s="2">
         <v>46205</v>
@@ -2955,7 +2955,7 @@
         <v>46206</v>
       </c>
       <c r="G42" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H42" s="2">
         <v>46205</v>
@@ -2992,7 +2992,7 @@
         <v>46216</v>
       </c>
       <c r="G44" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H44" s="2">
         <v>46205</v>
@@ -3071,7 +3071,7 @@
         <v>46206</v>
       </c>
       <c r="G49" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H49" s="2">
         <v>46205</v>
@@ -3208,7 +3208,7 @@
         <v>46209</v>
       </c>
       <c r="G56" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H56" s="2">
         <v>46205</v>
@@ -3328,7 +3328,7 @@
         <v>46210</v>
       </c>
       <c r="G62" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H62" s="2">
         <v>46209</v>
@@ -3365,7 +3365,7 @@
         <v>46217</v>
       </c>
       <c r="G64" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H64" s="2">
         <v>46209</v>
@@ -3416,7 +3416,7 @@
         <v>46234</v>
       </c>
       <c r="G67" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H67" s="2">
         <v>46209</v>
@@ -3439,7 +3439,7 @@
         <v>46213</v>
       </c>
       <c r="G68" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H68" s="2">
         <v>46209</v>
@@ -3490,7 +3490,7 @@
         <v>46210</v>
       </c>
       <c r="G71" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H71" s="2">
         <v>46209</v>
@@ -3527,7 +3527,7 @@
         <v>46216</v>
       </c>
       <c r="G73" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H73" s="2">
         <v>46209</v>
@@ -3606,7 +3606,7 @@
         <v>46210</v>
       </c>
       <c r="G78" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H78" s="2">
         <v>46209</v>
@@ -3743,7 +3743,7 @@
         <v>46209</v>
       </c>
       <c r="G85" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H85" s="2">
         <v>46209</v>
@@ -3849,7 +3849,7 @@
         <v>46217</v>
       </c>
       <c r="G90" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H90" s="2">
         <v>46210</v>
@@ -3872,7 +3872,7 @@
         <v>46210</v>
       </c>
       <c r="G91" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H91" s="2">
         <v>46210</v>
@@ -3909,7 +3909,7 @@
         <v>46217</v>
       </c>
       <c r="G93" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H93" s="2">
         <v>46210</v>
@@ -3960,7 +3960,7 @@
         <v>46234</v>
       </c>
       <c r="G96" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H96" s="2">
         <v>46210</v>
@@ -3983,7 +3983,7 @@
         <v>46213</v>
       </c>
       <c r="G97" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H97" s="2">
         <v>46210</v>
@@ -4020,7 +4020,7 @@
         <v>46213</v>
       </c>
       <c r="G99" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H99" s="2">
         <v>46210</v>
@@ -4043,7 +4043,7 @@
         <v>46213</v>
       </c>
       <c r="G100" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H100" s="2">
         <v>46210</v>
@@ -4080,7 +4080,7 @@
         <v>46216</v>
       </c>
       <c r="G102" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H102" s="2">
         <v>46210</v>
@@ -4103,7 +4103,7 @@
         <v>46213</v>
       </c>
       <c r="G103" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H103" s="2">
         <v>46210</v>
@@ -4168,7 +4168,7 @@
         <v>46213</v>
       </c>
       <c r="G107" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H107" s="2">
         <v>46210</v>
@@ -4305,7 +4305,7 @@
         <v>46209</v>
       </c>
       <c r="G114" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H114" s="2">
         <v>46210</v>
@@ -4411,7 +4411,7 @@
         <v>46217</v>
       </c>
       <c r="G119" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H119" s="2">
         <v>46211</v>
@@ -4504,7 +4504,7 @@
         <v>46234</v>
       </c>
       <c r="G125" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H125" s="2">
         <v>46211</v>
@@ -4527,7 +4527,7 @@
         <v>46213</v>
       </c>
       <c r="G126" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H126" s="2">
         <v>46211</v>
@@ -4564,7 +4564,7 @@
         <v>46213</v>
       </c>
       <c r="G128" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H128" s="2">
         <v>46211</v>
@@ -4587,7 +4587,7 @@
         <v>46213</v>
       </c>
       <c r="G129" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H129" s="2">
         <v>46211</v>
@@ -4624,7 +4624,7 @@
         <v>46216</v>
       </c>
       <c r="G131" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H131" s="2">
         <v>46211</v>
@@ -4647,7 +4647,7 @@
         <v>46213</v>
       </c>
       <c r="G132" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H132" s="2">
         <v>46211</v>
@@ -4712,7 +4712,7 @@
         <v>46213</v>
       </c>
       <c r="G136" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H136" s="2">
         <v>46211</v>
@@ -4849,7 +4849,7 @@
         <v>46209</v>
       </c>
       <c r="G143" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H143" s="2">
         <v>46211</v>
@@ -4955,7 +4955,7 @@
         <v>46217</v>
       </c>
       <c r="G148" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H148" s="2">
         <v>46212</v>
@@ -5048,7 +5048,7 @@
         <v>46234</v>
       </c>
       <c r="G154" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H154" s="2">
         <v>46212</v>
@@ -5071,7 +5071,7 @@
         <v>46213</v>
       </c>
       <c r="G155" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H155" s="2">
         <v>46212</v>
@@ -5108,7 +5108,7 @@
         <v>46213</v>
       </c>
       <c r="G157" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H157" s="2">
         <v>46212</v>
@@ -5131,7 +5131,7 @@
         <v>46213</v>
       </c>
       <c r="G158" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H158" s="2">
         <v>46212</v>
@@ -5154,7 +5154,7 @@
         <v>46212</v>
       </c>
       <c r="G159" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="H159" s="2">
         <v>46212</v>
@@ -5177,7 +5177,7 @@
         <v>46216</v>
       </c>
       <c r="G160" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H160" s="2">
         <v>46212</v>
@@ -5200,7 +5200,7 @@
         <v>46213</v>
       </c>
       <c r="G161" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H161" s="2">
         <v>46212</v>
@@ -5265,7 +5265,7 @@
         <v>46213</v>
       </c>
       <c r="G165" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H165" s="2">
         <v>46212</v>
@@ -5402,7 +5402,7 @@
         <v>46209</v>
       </c>
       <c r="G172" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H172" s="2">
         <v>46212</v>
@@ -5508,7 +5508,7 @@
         <v>46217</v>
       </c>
       <c r="G177" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H177" s="2">
         <v>46213</v>
@@ -5545,7 +5545,7 @@
         <v>46216</v>
       </c>
       <c r="G179" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H179" s="2">
         <v>46213</v>
@@ -5610,7 +5610,7 @@
         <v>46234</v>
       </c>
       <c r="G183" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H183" s="2">
         <v>46213</v>
@@ -5633,7 +5633,7 @@
         <v>46213</v>
       </c>
       <c r="G184" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H184" s="2">
         <v>46213</v>
@@ -5670,7 +5670,7 @@
         <v>46213</v>
       </c>
       <c r="G186" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H186" s="2">
         <v>46213</v>
@@ -5693,7 +5693,7 @@
         <v>46213</v>
       </c>
       <c r="G187" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H187" s="2">
         <v>46213</v>
@@ -5716,7 +5716,7 @@
         <v>46213</v>
       </c>
       <c r="G188" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H188" s="2">
         <v>46213</v>
@@ -5739,7 +5739,7 @@
         <v>46216</v>
       </c>
       <c r="G189" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H189" s="2">
         <v>46213</v>
@@ -5762,7 +5762,7 @@
         <v>46213</v>
       </c>
       <c r="G190" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H190" s="2">
         <v>46213</v>
@@ -5827,7 +5827,7 @@
         <v>46218</v>
       </c>
       <c r="G194" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="H194" s="2">
         <v>46213</v>
@@ -5964,7 +5964,7 @@
         <v>46209</v>
       </c>
       <c r="G201" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H201" s="2">
         <v>46213</v>
@@ -6070,7 +6070,7 @@
         <v>46217</v>
       </c>
       <c r="G206" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H206" s="2">
         <v>46216</v>
@@ -6163,7 +6163,7 @@
         <v>46234</v>
       </c>
       <c r="G212" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H212" s="2">
         <v>46216</v>
@@ -6214,7 +6214,7 @@
         <v>46220</v>
       </c>
       <c r="G215" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="H215" s="2">
         <v>46216</v>
@@ -6237,7 +6237,7 @@
         <v>46216</v>
       </c>
       <c r="G216" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H216" s="2">
         <v>46216</v>
@@ -6274,7 +6274,7 @@
         <v>46216</v>
       </c>
       <c r="G218" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H218" s="2">
         <v>46216</v>
@@ -6325,7 +6325,7 @@
         <v>46217</v>
       </c>
       <c r="G221" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H221" s="2">
         <v>46216</v>
@@ -6362,7 +6362,7 @@
         <v>46241</v>
       </c>
       <c r="G223" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H223" s="2">
         <v>46216</v>
@@ -6499,7 +6499,7 @@
         <v>46295</v>
       </c>
       <c r="G230" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="H230" s="2">
         <v>46216</v>
@@ -6605,7 +6605,7 @@
         <v>46217</v>
       </c>
       <c r="G235" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H235" s="2">
         <v>46217</v>
@@ -6698,7 +6698,7 @@
         <v>46234</v>
       </c>
       <c r="G241" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H241" s="2">
         <v>46217</v>
@@ -6735,7 +6735,7 @@
         <v>46224</v>
       </c>
       <c r="G243" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="H243" s="2">
         <v>46217</v>
@@ -6758,7 +6758,7 @@
         <v>46220</v>
       </c>
       <c r="G244" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="H244" s="2">
         <v>46217</v>
@@ -6809,7 +6809,7 @@
         <v>46237</v>
       </c>
       <c r="G247" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="H247" s="2">
         <v>46217</v>
@@ -6860,7 +6860,7 @@
         <v>46218</v>
       </c>
       <c r="G250" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="H250" s="2">
         <v>46217</v>
@@ -6897,7 +6897,7 @@
         <v>46241</v>
       </c>
       <c r="G252" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H252" s="2">
         <v>46217</v>
@@ -7034,7 +7034,7 @@
         <v>46295</v>
       </c>
       <c r="G259" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="H259" s="2">
         <v>46217</v>
@@ -7140,7 +7140,7 @@
         <v>46217</v>
       </c>
       <c r="G264" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="H264" s="2">
         <v>46218</v>
@@ -7233,7 +7233,7 @@
         <v>46234</v>
       </c>
       <c r="G270" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H270" s="2">
         <v>46218</v>
@@ -7270,7 +7270,7 @@
         <v>46224</v>
       </c>
       <c r="G272" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="H272" s="2">
         <v>46218</v>
@@ -7293,7 +7293,7 @@
         <v>46219</v>
       </c>
       <c r="G273" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H273" s="2">
         <v>46218</v>
@@ -7344,7 +7344,7 @@
         <v>46237</v>
       </c>
       <c r="G276" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="H276" s="2">
         <v>46218</v>
@@ -7381,7 +7381,7 @@
         <v>46227</v>
       </c>
       <c r="G278" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="H278" s="2">
         <v>46218</v>
@@ -7404,7 +7404,7 @@
         <v>46219</v>
       </c>
       <c r="G279" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H279" s="2">
         <v>46218</v>
@@ -7441,7 +7441,7 @@
         <v>46241</v>
       </c>
       <c r="G281" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H281" s="2">
         <v>46218</v>
@@ -7578,7 +7578,7 @@
         <v>46295</v>
       </c>
       <c r="G288" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="H288" s="2">
         <v>46218</v>
@@ -7680,11 +7680,11 @@
       <c r="D293" t="s">
         <v>163</v>
       </c>
-      <c r="F293" t="s">
-        <v>193</v>
+      <c r="E293" s="2">
+        <v>46220</v>
       </c>
       <c r="G293" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="H293" s="2">
         <v>46220</v>
@@ -7718,10 +7718,10 @@
         <v>170</v>
       </c>
       <c r="F295" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G295" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H295" s="2">
         <v>46220</v>
@@ -7768,11 +7768,11 @@
       <c r="D298" t="s">
         <v>171</v>
       </c>
-      <c r="F298" t="s">
-        <v>195</v>
+      <c r="E298" s="2">
+        <v>46223</v>
       </c>
       <c r="G298" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H298" s="2">
         <v>46220</v>
@@ -7795,7 +7795,7 @@
         <v>46234</v>
       </c>
       <c r="G299" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H299" s="2">
         <v>46220</v>
@@ -7832,7 +7832,7 @@
         <v>46224</v>
       </c>
       <c r="G301" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="H301" s="2">
         <v>46220</v>
@@ -7855,7 +7855,7 @@
         <v>46220</v>
       </c>
       <c r="G302" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="H302" s="2">
         <v>46220</v>
@@ -7906,7 +7906,7 @@
         <v>46237</v>
       </c>
       <c r="G305" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="H305" s="2">
         <v>46220</v>
@@ -7943,7 +7943,7 @@
         <v>46227</v>
       </c>
       <c r="G307" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="H307" s="2">
         <v>46220</v>
@@ -7976,11 +7976,11 @@
       <c r="D309" t="s">
         <v>172</v>
       </c>
-      <c r="F309" t="s">
-        <v>193</v>
+      <c r="E309" s="2">
+        <v>46220</v>
       </c>
       <c r="G309" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="H309" s="2">
         <v>46220</v>
@@ -7999,11 +7999,11 @@
       <c r="D310" t="s">
         <v>173</v>
       </c>
-      <c r="F310" t="s">
-        <v>196</v>
+      <c r="E310" s="2">
+        <v>46265</v>
       </c>
       <c r="G310" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="H310" s="2">
         <v>46220</v>
@@ -8130,11 +8130,11 @@
       <c r="D317" t="s">
         <v>162</v>
       </c>
-      <c r="F317" t="s">
-        <v>197</v>
+      <c r="E317" s="2">
+        <v>46295</v>
       </c>
       <c r="G317" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H317" s="2">
         <v>46220</v>
@@ -8236,11 +8236,11 @@
       <c r="D322" t="s">
         <v>163</v>
       </c>
-      <c r="F322" t="s">
-        <v>198</v>
+      <c r="E322" s="2">
+        <v>46225</v>
       </c>
       <c r="G322" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="H322" s="2">
         <v>46224</v>
@@ -8273,11 +8273,11 @@
       <c r="D324" t="s">
         <v>175</v>
       </c>
-      <c r="F324" t="s">
-        <v>199</v>
+      <c r="E324" s="2">
+        <v>46224</v>
       </c>
       <c r="G324" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="H324" s="2">
         <v>46224</v>
@@ -8342,7 +8342,7 @@
         <v>46234</v>
       </c>
       <c r="G328" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H328" s="2">
         <v>46224</v>
@@ -8361,11 +8361,11 @@
       <c r="D329" t="s">
         <v>176</v>
       </c>
-      <c r="F329" t="s">
-        <v>199</v>
+      <c r="E329" s="2">
+        <v>46224</v>
       </c>
       <c r="G329" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="H329" s="2">
         <v>46224</v>
@@ -8384,11 +8384,11 @@
       <c r="D330" t="s">
         <v>164</v>
       </c>
-      <c r="F330" t="s">
-        <v>199</v>
+      <c r="E330" s="2">
+        <v>46224</v>
       </c>
       <c r="G330" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="H330" s="2">
         <v>46224</v>
@@ -8421,11 +8421,11 @@
       <c r="D332" t="s">
         <v>177</v>
       </c>
-      <c r="F332" t="s">
-        <v>199</v>
+      <c r="E332" s="2">
+        <v>46224</v>
       </c>
       <c r="G332" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="H332" s="2">
         <v>46224</v>
@@ -8444,11 +8444,11 @@
       <c r="D333" t="s">
         <v>178</v>
       </c>
-      <c r="F333" t="s">
-        <v>198</v>
+      <c r="E333" s="2">
+        <v>46225</v>
       </c>
       <c r="G333" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="H333" s="2">
         <v>46224</v>
@@ -8471,7 +8471,7 @@
         <v>46237</v>
       </c>
       <c r="G334" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="H334" s="2">
         <v>46224</v>
@@ -8508,7 +8508,7 @@
         <v>46227</v>
       </c>
       <c r="G336" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="H336" s="2">
         <v>46224</v>
@@ -8555,11 +8555,11 @@
       <c r="D339" t="s">
         <v>173</v>
       </c>
-      <c r="F339" t="s">
-        <v>196</v>
+      <c r="E339" s="2">
+        <v>46265</v>
       </c>
       <c r="G339" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="H339" s="2">
         <v>46224</v>
@@ -8686,11 +8686,11 @@
       <c r="D346" t="s">
         <v>162</v>
       </c>
-      <c r="F346" t="s">
-        <v>197</v>
+      <c r="E346" s="2">
+        <v>46295</v>
       </c>
       <c r="G346" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H346" s="2">
         <v>46224</v>
@@ -8792,11 +8792,11 @@
       <c r="D351" t="s">
         <v>163</v>
       </c>
-      <c r="F351" t="s">
-        <v>198</v>
+      <c r="E351" s="2">
+        <v>46225</v>
       </c>
       <c r="G351" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="H351" s="2">
         <v>46225</v>
@@ -8885,11 +8885,11 @@
       <c r="D357" t="s">
         <v>133</v>
       </c>
-      <c r="F357" t="s">
-        <v>200</v>
+      <c r="E357" s="2">
+        <v>46234</v>
       </c>
       <c r="G357" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H357" s="2">
         <v>46225</v>
@@ -8922,11 +8922,11 @@
       <c r="D359" t="s">
         <v>164</v>
       </c>
-      <c r="F359" t="s">
-        <v>201</v>
+      <c r="E359" s="2">
+        <v>46227</v>
       </c>
       <c r="G359" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H359" s="2">
         <v>46225</v>
@@ -8973,11 +8973,11 @@
       <c r="D362" t="s">
         <v>178</v>
       </c>
-      <c r="F362" t="s">
-        <v>198</v>
+      <c r="E362" s="2">
+        <v>46225</v>
       </c>
       <c r="G362" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="H362" s="2">
         <v>46225</v>
@@ -8996,11 +8996,11 @@
       <c r="D363" t="s">
         <v>136</v>
       </c>
-      <c r="F363" t="s">
-        <v>202</v>
+      <c r="E363" s="2">
+        <v>46237</v>
       </c>
       <c r="G363" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="H363" s="2">
         <v>46225</v>
@@ -9033,11 +9033,11 @@
       <c r="D365" t="s">
         <v>168</v>
       </c>
-      <c r="F365" t="s">
-        <v>201</v>
+      <c r="E365" s="2">
+        <v>46227</v>
       </c>
       <c r="G365" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H365" s="2">
         <v>46225</v>
@@ -9084,11 +9084,11 @@
       <c r="D368" t="s">
         <v>173</v>
       </c>
-      <c r="F368" t="s">
-        <v>200</v>
+      <c r="E368" s="2">
+        <v>46234</v>
       </c>
       <c r="G368" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H368" s="2">
         <v>46225</v>
@@ -9107,11 +9107,11 @@
       <c r="D369" t="s">
         <v>180</v>
       </c>
-      <c r="F369" t="s">
-        <v>201</v>
+      <c r="E369" s="2">
+        <v>46227</v>
       </c>
       <c r="G369" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H369" s="2">
         <v>46225</v>
@@ -9224,11 +9224,11 @@
       <c r="D375" t="s">
         <v>162</v>
       </c>
-      <c r="F375" t="s">
-        <v>197</v>
+      <c r="E375" s="2">
+        <v>46295</v>
       </c>
       <c r="G375" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H375" s="2">
         <v>46225</v>
@@ -9330,11 +9330,11 @@
       <c r="D380" t="s">
         <v>163</v>
       </c>
-      <c r="F380" t="s">
-        <v>201</v>
+      <c r="E380" s="2">
+        <v>46227</v>
       </c>
       <c r="G380" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H380" s="2">
         <v>46226</v>
@@ -9423,11 +9423,11 @@
       <c r="D386" t="s">
         <v>133</v>
       </c>
-      <c r="F386" t="s">
-        <v>200</v>
+      <c r="E386" s="2">
+        <v>46234</v>
       </c>
       <c r="G386" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H386" s="2">
         <v>46226</v>
@@ -9502,11 +9502,11 @@
       <c r="D391" t="s">
         <v>181</v>
       </c>
-      <c r="F391" t="s">
-        <v>201</v>
+      <c r="E391" s="2">
+        <v>46227</v>
       </c>
       <c r="G391" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H391" s="2">
         <v>46226</v>
@@ -9525,11 +9525,11 @@
       <c r="D392" t="s">
         <v>136</v>
       </c>
-      <c r="F392" t="s">
-        <v>202</v>
+      <c r="E392" s="2">
+        <v>46237</v>
       </c>
       <c r="G392" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="H392" s="2">
         <v>46226</v>
@@ -9562,11 +9562,11 @@
       <c r="D394" t="s">
         <v>168</v>
       </c>
-      <c r="F394" t="s">
-        <v>201</v>
+      <c r="E394" s="2">
+        <v>46227</v>
       </c>
       <c r="G394" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H394" s="2">
         <v>46226</v>
@@ -9613,11 +9613,11 @@
       <c r="D397" t="s">
         <v>173</v>
       </c>
-      <c r="F397" t="s">
-        <v>200</v>
+      <c r="E397" s="2">
+        <v>46234</v>
       </c>
       <c r="G397" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H397" s="2">
         <v>46226</v>
@@ -9636,11 +9636,11 @@
       <c r="D398" t="s">
         <v>180</v>
       </c>
-      <c r="F398" t="s">
-        <v>201</v>
+      <c r="E398" s="2">
+        <v>46227</v>
       </c>
       <c r="G398" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H398" s="2">
         <v>46226</v>
@@ -9753,11 +9753,11 @@
       <c r="D404" t="s">
         <v>162</v>
       </c>
-      <c r="F404" t="s">
-        <v>197</v>
+      <c r="E404" s="2">
+        <v>46295</v>
       </c>
       <c r="G404" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H404" s="2">
         <v>46226</v>
@@ -9859,11 +9859,11 @@
       <c r="D409" t="s">
         <v>150</v>
       </c>
-      <c r="F409" t="s">
-        <v>203</v>
+      <c r="E409" s="2">
+        <v>46231</v>
       </c>
       <c r="G409" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="H409" s="2">
         <v>46227</v>
@@ -9952,11 +9952,11 @@
       <c r="D415" t="s">
         <v>182</v>
       </c>
-      <c r="F415" t="s">
-        <v>200</v>
+      <c r="E415" s="2">
+        <v>46234</v>
       </c>
       <c r="G415" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H415" s="2">
         <v>46227</v>
@@ -10031,11 +10031,11 @@
       <c r="D420" t="s">
         <v>136</v>
       </c>
-      <c r="F420" t="s">
-        <v>202</v>
+      <c r="E420" s="2">
+        <v>46237</v>
       </c>
       <c r="G420" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="H420" s="2">
         <v>46227</v>
@@ -10068,11 +10068,11 @@
       <c r="D422" t="s">
         <v>168</v>
       </c>
-      <c r="F422" t="s">
-        <v>201</v>
+      <c r="E422" s="2">
+        <v>46227</v>
       </c>
       <c r="G422" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H422" s="2">
         <v>46227</v>
@@ -10119,11 +10119,11 @@
       <c r="D425" t="s">
         <v>173</v>
       </c>
-      <c r="F425" t="s">
-        <v>200</v>
+      <c r="E425" s="2">
+        <v>46234</v>
       </c>
       <c r="G425" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H425" s="2">
         <v>46227</v>
@@ -10142,11 +10142,11 @@
       <c r="D426" t="s">
         <v>180</v>
       </c>
-      <c r="F426" t="s">
-        <v>201</v>
+      <c r="E426" s="2">
+        <v>46227</v>
       </c>
       <c r="G426" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="H426" s="2">
         <v>46227</v>
@@ -10259,11 +10259,11 @@
       <c r="D432" t="s">
         <v>162</v>
       </c>
-      <c r="F432" t="s">
-        <v>197</v>
+      <c r="E432" s="2">
+        <v>46295</v>
       </c>
       <c r="G432" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H432" s="2">
         <v>46227</v>
@@ -10351,11 +10351,11 @@
       <c r="D436" t="s">
         <v>183</v>
       </c>
-      <c r="F436" t="s">
-        <v>204</v>
+      <c r="E436" s="2">
+        <v>46230</v>
       </c>
       <c r="G436" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="H436" s="2">
         <v>46227</v>
@@ -10388,11 +10388,11 @@
       <c r="D438" t="s">
         <v>150</v>
       </c>
-      <c r="F438" t="s">
-        <v>203</v>
+      <c r="E438" s="2">
+        <v>46231</v>
       </c>
       <c r="G438" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="H438" s="2">
         <v>46230</v>
@@ -10481,11 +10481,11 @@
       <c r="D444" t="s">
         <v>182</v>
       </c>
-      <c r="F444" t="s">
-        <v>200</v>
+      <c r="E444" s="2">
+        <v>46234</v>
       </c>
       <c r="G444" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H444" s="2">
         <v>46230</v>
@@ -10518,11 +10518,11 @@
       <c r="D446" t="s">
         <v>184</v>
       </c>
-      <c r="F446" t="s">
-        <v>204</v>
+      <c r="E446" s="2">
+        <v>46230</v>
       </c>
       <c r="G446" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="H446" s="2">
         <v>46230</v>
@@ -10569,11 +10569,11 @@
       <c r="D449" t="s">
         <v>136</v>
       </c>
-      <c r="F449" t="s">
-        <v>202</v>
+      <c r="E449" s="2">
+        <v>46237</v>
       </c>
       <c r="G449" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="H449" s="2">
         <v>46230</v>
@@ -10648,11 +10648,11 @@
       <c r="D454" t="s">
         <v>173</v>
       </c>
-      <c r="F454" t="s">
-        <v>200</v>
+      <c r="E454" s="2">
+        <v>46234</v>
       </c>
       <c r="G454" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="H454" s="2">
         <v>46230</v>
@@ -10779,11 +10779,11 @@
       <c r="D461" t="s">
         <v>162</v>
       </c>
-      <c r="F461" t="s">
-        <v>197</v>
+      <c r="E461" s="2">
+        <v>46295</v>
       </c>
       <c r="G461" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H461" s="2">
         <v>46230</v>
@@ -10871,11 +10871,11 @@
       <c r="D465" t="s">
         <v>183</v>
       </c>
-      <c r="F465" t="s">
-        <v>204</v>
+      <c r="E465" s="2">
+        <v>46230</v>
       </c>
       <c r="G465" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="H465" s="2">
         <v>46230</v>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -690,16 +690,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -715,7 +707,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -723,30 +715,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1046,72 +1020,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1176,7 +1150,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1241,7 +1215,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1306,7 +1280,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1371,7 +1345,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1436,7 +1410,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1501,7 +1475,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1566,7 +1540,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1631,7 +1605,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1696,7 +1670,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1761,7 +1735,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1826,7 +1800,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -1891,7 +1865,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -1956,7 +1930,7 @@
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>46226</v>
       </c>
       <c r="B15">
@@ -2021,7 +1995,7 @@
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>46227</v>
       </c>
       <c r="B16">
@@ -2086,7 +2060,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>46230</v>
       </c>
       <c r="B17">
@@ -2161,28 +2135,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2196,7 +2170,7 @@
       <c r="C2" t="s">
         <v>123</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2210,7 +2184,7 @@
       <c r="C3" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2233,7 +2207,7 @@
       <c r="G4" t="s">
         <v>185</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2247,7 +2221,7 @@
       <c r="C5" t="s">
         <v>123</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2261,7 +2235,7 @@
       <c r="C6" t="s">
         <v>123</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2278,13 +2252,13 @@
       <c r="D7" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>194</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2301,13 +2275,13 @@
       <c r="D8" t="s">
         <v>132</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>194</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2324,13 +2298,13 @@
       <c r="D9" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>195</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2347,13 +2321,13 @@
       <c r="D10" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>196</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2367,7 +2341,7 @@
       <c r="C11" t="s">
         <v>123</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2381,7 +2355,7 @@
       <c r="C12" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2398,13 +2372,13 @@
       <c r="D13" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>194</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2418,7 +2392,7 @@
       <c r="C14" t="s">
         <v>127</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2435,13 +2409,13 @@
       <c r="D15" t="s">
         <v>136</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2455,7 +2429,7 @@
       <c r="C16" t="s">
         <v>123</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2469,7 +2443,7 @@
       <c r="C17" t="s">
         <v>123</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2486,13 +2460,13 @@
       <c r="D18" t="s">
         <v>137</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>198</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2506,7 +2480,7 @@
       <c r="C19" t="s">
         <v>123</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2523,13 +2497,13 @@
       <c r="D20" t="s">
         <v>138</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>194</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2552,7 +2526,7 @@
       <c r="G21" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2566,7 +2540,7 @@
       <c r="C22" t="s">
         <v>127</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2580,7 +2554,7 @@
       <c r="C23" t="s">
         <v>123</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2603,7 +2577,7 @@
       <c r="G24" t="s">
         <v>187</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2620,7 +2594,7 @@
       <c r="D25" t="s">
         <v>140</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2643,7 +2617,7 @@
       <c r="G26" t="s">
         <v>188</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2660,13 +2634,13 @@
       <c r="D27" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>199</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2689,7 +2663,7 @@
       <c r="G28" t="s">
         <v>189</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2712,7 +2686,7 @@
       <c r="G29" t="s">
         <v>189</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2735,7 +2709,7 @@
       <c r="G30" t="s">
         <v>190</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2749,7 +2723,7 @@
       <c r="C31" t="s">
         <v>123</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2763,7 +2737,7 @@
       <c r="C32" t="s">
         <v>123</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2786,7 +2760,7 @@
       <c r="G33" t="s">
         <v>191</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2800,7 +2774,7 @@
       <c r="C34" t="s">
         <v>123</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2814,7 +2788,7 @@
       <c r="C35" t="s">
         <v>123</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2831,13 +2805,13 @@
       <c r="D36" t="s">
         <v>131</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>194</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2854,13 +2828,13 @@
       <c r="D37" t="s">
         <v>132</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2877,13 +2851,13 @@
       <c r="D38" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>195</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2900,13 +2874,13 @@
       <c r="D39" t="s">
         <v>134</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>196</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2920,7 +2894,7 @@
       <c r="C40" t="s">
         <v>123</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2934,7 +2908,7 @@
       <c r="C41" t="s">
         <v>123</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2951,13 +2925,13 @@
       <c r="D42" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>194</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2971,7 +2945,7 @@
       <c r="C43" t="s">
         <v>123</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2988,13 +2962,13 @@
       <c r="D44" t="s">
         <v>136</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>197</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3008,7 +2982,7 @@
       <c r="C45" t="s">
         <v>123</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3022,7 +2996,7 @@
       <c r="C46" t="s">
         <v>123</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3036,7 +3010,7 @@
       <c r="C47" t="s">
         <v>127</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3050,7 +3024,7 @@
       <c r="C48" t="s">
         <v>123</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3067,13 +3041,13 @@
       <c r="D49" t="s">
         <v>147</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>194</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3096,7 +3070,7 @@
       <c r="G50" t="s">
         <v>186</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3110,7 +3084,7 @@
       <c r="C51" t="s">
         <v>127</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3124,7 +3098,7 @@
       <c r="C52" t="s">
         <v>123</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3147,7 +3121,7 @@
       <c r="G53" t="s">
         <v>187</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3164,7 +3138,7 @@
       <c r="D54" t="s">
         <v>140</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3187,7 +3161,7 @@
       <c r="G55" t="s">
         <v>188</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3204,13 +3178,13 @@
       <c r="D56" t="s">
         <v>142</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>199</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3233,7 +3207,7 @@
       <c r="G57" t="s">
         <v>189</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3256,7 +3230,7 @@
       <c r="G58" t="s">
         <v>189</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3279,7 +3253,7 @@
       <c r="G59" t="s">
         <v>190</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3293,7 +3267,7 @@
       <c r="C60" t="s">
         <v>123</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3307,7 +3281,7 @@
       <c r="C61" t="s">
         <v>123</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3324,13 +3298,13 @@
       <c r="D62" t="s">
         <v>146</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>200</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3344,7 +3318,7 @@
       <c r="C63" t="s">
         <v>123</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3361,13 +3335,13 @@
       <c r="D64" t="s">
         <v>148</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>201</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3381,7 +3355,7 @@
       <c r="C65" t="s">
         <v>123</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3395,7 +3369,7 @@
       <c r="C66" t="s">
         <v>127</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3412,13 +3386,13 @@
       <c r="D67" t="s">
         <v>133</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>195</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3435,13 +3409,13 @@
       <c r="D68" t="s">
         <v>134</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>196</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3455,7 +3429,7 @@
       <c r="C69" t="s">
         <v>123</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3469,7 +3443,7 @@
       <c r="C70" t="s">
         <v>123</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3486,13 +3460,13 @@
       <c r="D71" t="s">
         <v>135</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>200</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3506,7 +3480,7 @@
       <c r="C72" t="s">
         <v>123</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3523,13 +3497,13 @@
       <c r="D73" t="s">
         <v>136</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>197</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3543,7 +3517,7 @@
       <c r="C74" t="s">
         <v>123</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3557,7 +3531,7 @@
       <c r="C75" t="s">
         <v>123</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3571,7 +3545,7 @@
       <c r="C76" t="s">
         <v>123</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3585,7 +3559,7 @@
       <c r="C77" t="s">
         <v>123</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3602,13 +3576,13 @@
       <c r="D78" t="s">
         <v>147</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>200</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3631,7 +3605,7 @@
       <c r="G79" t="s">
         <v>192</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3645,7 +3619,7 @@
       <c r="C80" t="s">
         <v>127</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3659,7 +3633,7 @@
       <c r="C81" t="s">
         <v>123</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3682,7 +3656,7 @@
       <c r="G82" t="s">
         <v>187</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3699,7 +3673,7 @@
       <c r="D83" t="s">
         <v>140</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3722,7 +3696,7 @@
       <c r="G84" t="s">
         <v>188</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3739,13 +3713,13 @@
       <c r="D85" t="s">
         <v>142</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3768,7 +3742,7 @@
       <c r="G86" t="s">
         <v>189</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3791,7 +3765,7 @@
       <c r="G87" t="s">
         <v>189</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3814,7 +3788,7 @@
       <c r="G88" t="s">
         <v>190</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3828,7 +3802,7 @@
       <c r="C89" t="s">
         <v>123</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3845,13 +3819,13 @@
       <c r="D90" t="s">
         <v>150</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>201</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3868,13 +3842,13 @@
       <c r="D91" t="s">
         <v>146</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>200</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3888,7 +3862,7 @@
       <c r="C92" t="s">
         <v>123</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3905,13 +3879,13 @@
       <c r="D93" t="s">
         <v>148</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>201</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3925,7 +3899,7 @@
       <c r="C94" t="s">
         <v>123</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3939,7 +3913,7 @@
       <c r="C95" t="s">
         <v>127</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3956,13 +3930,13 @@
       <c r="D96" t="s">
         <v>133</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>195</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3979,13 +3953,13 @@
       <c r="D97" t="s">
         <v>134</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>196</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3999,7 +3973,7 @@
       <c r="C98" t="s">
         <v>123</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4016,13 +3990,13 @@
       <c r="D99" t="s">
         <v>151</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>196</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4039,13 +4013,13 @@
       <c r="D100" t="s">
         <v>135</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>196</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4059,7 +4033,7 @@
       <c r="C101" t="s">
         <v>123</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4076,13 +4050,13 @@
       <c r="D102" t="s">
         <v>136</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>197</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4099,13 +4073,13 @@
       <c r="D103" t="s">
         <v>152</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>196</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4119,7 +4093,7 @@
       <c r="C104" t="s">
         <v>123</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4133,7 +4107,7 @@
       <c r="C105" t="s">
         <v>123</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4147,7 +4121,7 @@
       <c r="C106" t="s">
         <v>123</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4164,13 +4138,13 @@
       <c r="D107" t="s">
         <v>153</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>196</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4193,7 +4167,7 @@
       <c r="G108" t="s">
         <v>192</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4207,7 +4181,7 @@
       <c r="C109" t="s">
         <v>127</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4221,7 +4195,7 @@
       <c r="C110" t="s">
         <v>123</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4244,7 +4218,7 @@
       <c r="G111" t="s">
         <v>187</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4261,7 +4235,7 @@
       <c r="D112" t="s">
         <v>140</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4284,7 +4258,7 @@
       <c r="G113" t="s">
         <v>188</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4301,13 +4275,13 @@
       <c r="D114" t="s">
         <v>142</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>199</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4330,7 +4304,7 @@
       <c r="G115" t="s">
         <v>189</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4353,7 +4327,7 @@
       <c r="G116" t="s">
         <v>189</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4376,7 +4350,7 @@
       <c r="G117" t="s">
         <v>190</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4390,7 +4364,7 @@
       <c r="C118" t="s">
         <v>123</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4407,13 +4381,13 @@
       <c r="D119" t="s">
         <v>150</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>201</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4427,7 +4401,7 @@
       <c r="C120" t="s">
         <v>127</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4441,7 +4415,7 @@
       <c r="C121" t="s">
         <v>123</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4455,7 +4429,7 @@
       <c r="C122" t="s">
         <v>127</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4469,7 +4443,7 @@
       <c r="C123" t="s">
         <v>127</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4483,7 +4457,7 @@
       <c r="C124" t="s">
         <v>127</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4500,13 +4474,13 @@
       <c r="D125" t="s">
         <v>133</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>195</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4523,13 +4497,13 @@
       <c r="D126" t="s">
         <v>134</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>196</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4543,7 +4517,7 @@
       <c r="C127" t="s">
         <v>123</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4560,13 +4534,13 @@
       <c r="D128" t="s">
         <v>151</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>196</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4583,13 +4557,13 @@
       <c r="D129" t="s">
         <v>135</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>196</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4603,7 +4577,7 @@
       <c r="C130" t="s">
         <v>123</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4620,13 +4594,13 @@
       <c r="D131" t="s">
         <v>136</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>197</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4643,13 +4617,13 @@
       <c r="D132" t="s">
         <v>152</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>196</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4663,7 +4637,7 @@
       <c r="C133" t="s">
         <v>123</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4677,7 +4651,7 @@
       <c r="C134" t="s">
         <v>123</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4691,7 +4665,7 @@
       <c r="C135" t="s">
         <v>123</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4708,13 +4682,13 @@
       <c r="D136" t="s">
         <v>154</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>196</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4737,7 +4711,7 @@
       <c r="G137" t="s">
         <v>192</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4751,7 +4725,7 @@
       <c r="C138" t="s">
         <v>127</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4765,7 +4739,7 @@
       <c r="C139" t="s">
         <v>123</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4788,7 +4762,7 @@
       <c r="G140" t="s">
         <v>187</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4805,7 +4779,7 @@
       <c r="D141" t="s">
         <v>140</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4828,7 +4802,7 @@
       <c r="G142" t="s">
         <v>188</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4845,13 +4819,13 @@
       <c r="D143" t="s">
         <v>142</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>199</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4874,7 +4848,7 @@
       <c r="G144" t="s">
         <v>189</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4897,7 +4871,7 @@
       <c r="G145" t="s">
         <v>189</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4920,7 +4894,7 @@
       <c r="G146" t="s">
         <v>190</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4934,7 +4908,7 @@
       <c r="C147" t="s">
         <v>123</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4951,13 +4925,13 @@
       <c r="D148" t="s">
         <v>150</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>201</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4971,7 +4945,7 @@
       <c r="C149" t="s">
         <v>127</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4985,7 +4959,7 @@
       <c r="C150" t="s">
         <v>123</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -4999,7 +4973,7 @@
       <c r="C151" t="s">
         <v>123</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5013,7 +4987,7 @@
       <c r="C152" t="s">
         <v>127</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5027,7 +5001,7 @@
       <c r="C153" t="s">
         <v>127</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5044,13 +5018,13 @@
       <c r="D154" t="s">
         <v>133</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>195</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5067,13 +5041,13 @@
       <c r="D155" t="s">
         <v>134</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>196</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5087,7 +5061,7 @@
       <c r="C156" t="s">
         <v>123</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5104,13 +5078,13 @@
       <c r="D157" t="s">
         <v>151</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>196</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5127,13 +5101,13 @@
       <c r="D158" t="s">
         <v>135</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>196</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5150,13 +5124,13 @@
       <c r="D159" t="s">
         <v>155</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>202</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5173,13 +5147,13 @@
       <c r="D160" t="s">
         <v>136</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>197</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5196,13 +5170,13 @@
       <c r="D161" t="s">
         <v>152</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>196</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5216,7 +5190,7 @@
       <c r="C162" t="s">
         <v>123</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5230,7 +5204,7 @@
       <c r="C163" t="s">
         <v>123</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5244,7 +5218,7 @@
       <c r="C164" t="s">
         <v>123</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5261,13 +5235,13 @@
       <c r="D165" t="s">
         <v>154</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>196</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5290,7 +5264,7 @@
       <c r="G166" t="s">
         <v>192</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5304,7 +5278,7 @@
       <c r="C167" t="s">
         <v>127</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5318,7 +5292,7 @@
       <c r="C168" t="s">
         <v>123</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5341,7 +5315,7 @@
       <c r="G169" t="s">
         <v>187</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5358,7 +5332,7 @@
       <c r="D170" t="s">
         <v>140</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5381,7 +5355,7 @@
       <c r="G171" t="s">
         <v>188</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5398,13 +5372,13 @@
       <c r="D172" t="s">
         <v>142</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>199</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5427,7 +5401,7 @@
       <c r="G173" t="s">
         <v>189</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5450,7 +5424,7 @@
       <c r="G174" t="s">
         <v>189</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5473,7 +5447,7 @@
       <c r="G175" t="s">
         <v>190</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5487,7 +5461,7 @@
       <c r="C176" t="s">
         <v>123</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5504,13 +5478,13 @@
       <c r="D177" t="s">
         <v>156</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>201</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5524,7 +5498,7 @@
       <c r="C178" t="s">
         <v>123</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5541,13 +5515,13 @@
       <c r="D179" t="s">
         <v>157</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>197</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5561,7 +5535,7 @@
       <c r="C180" t="s">
         <v>123</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5575,7 +5549,7 @@
       <c r="C181" t="s">
         <v>127</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5589,7 +5563,7 @@
       <c r="C182" t="s">
         <v>127</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5606,13 +5580,13 @@
       <c r="D183" t="s">
         <v>133</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>195</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5629,13 +5603,13 @@
       <c r="D184" t="s">
         <v>134</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>196</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5649,7 +5623,7 @@
       <c r="C185" t="s">
         <v>123</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5666,13 +5640,13 @@
       <c r="D186" t="s">
         <v>151</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>196</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5689,13 +5663,13 @@
       <c r="D187" t="s">
         <v>158</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>196</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5712,13 +5686,13 @@
       <c r="D188" t="s">
         <v>159</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>196</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5735,13 +5709,13 @@
       <c r="D189" t="s">
         <v>136</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>197</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5758,13 +5732,13 @@
       <c r="D190" t="s">
         <v>152</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>196</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5778,7 +5752,7 @@
       <c r="C191" t="s">
         <v>123</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5792,7 +5766,7 @@
       <c r="C192" t="s">
         <v>123</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5806,7 +5780,7 @@
       <c r="C193" t="s">
         <v>123</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5823,13 +5797,13 @@
       <c r="D194" t="s">
         <v>154</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>203</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5852,7 +5826,7 @@
       <c r="G195" t="s">
         <v>192</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5866,7 +5840,7 @@
       <c r="C196" t="s">
         <v>127</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5880,7 +5854,7 @@
       <c r="C197" t="s">
         <v>123</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5903,7 +5877,7 @@
       <c r="G198" t="s">
         <v>187</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5920,7 +5894,7 @@
       <c r="D199" t="s">
         <v>140</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5943,7 +5917,7 @@
       <c r="G200" t="s">
         <v>188</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5960,13 +5934,13 @@
       <c r="D201" t="s">
         <v>142</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>199</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5989,7 +5963,7 @@
       <c r="G202" t="s">
         <v>189</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6012,7 +5986,7 @@
       <c r="G203" t="s">
         <v>189</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6035,7 +6009,7 @@
       <c r="G204" t="s">
         <v>190</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6049,7 +6023,7 @@
       <c r="C205" t="s">
         <v>123</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6066,13 +6040,13 @@
       <c r="D206" t="s">
         <v>156</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>201</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6086,7 +6060,7 @@
       <c r="C207" t="s">
         <v>123</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6100,7 +6074,7 @@
       <c r="C208" t="s">
         <v>127</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6114,7 +6088,7 @@
       <c r="C209" t="s">
         <v>123</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6128,7 +6102,7 @@
       <c r="C210" t="s">
         <v>127</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6142,7 +6116,7 @@
       <c r="C211" t="s">
         <v>127</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6159,13 +6133,13 @@
       <c r="D212" t="s">
         <v>133</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>195</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6179,7 +6153,7 @@
       <c r="C213" t="s">
         <v>127</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6193,7 +6167,7 @@
       <c r="C214" t="s">
         <v>123</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6210,13 +6184,13 @@
       <c r="D215" t="s">
         <v>151</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>204</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6233,13 +6207,13 @@
       <c r="D216" t="s">
         <v>158</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>197</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6253,7 +6227,7 @@
       <c r="C217" t="s">
         <v>123</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6270,13 +6244,13 @@
       <c r="D218" t="s">
         <v>136</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>197</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6290,7 +6264,7 @@
       <c r="C219" t="s">
         <v>123</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6304,7 +6278,7 @@
       <c r="C220" t="s">
         <v>123</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6321,13 +6295,13 @@
       <c r="D221" t="s">
         <v>160</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>201</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6341,7 +6315,7 @@
       <c r="C222" t="s">
         <v>123</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6358,13 +6332,13 @@
       <c r="D223" t="s">
         <v>161</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>205</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6387,7 +6361,7 @@
       <c r="G224" t="s">
         <v>192</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6401,7 +6375,7 @@
       <c r="C225" t="s">
         <v>127</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6415,7 +6389,7 @@
       <c r="C226" t="s">
         <v>123</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6438,7 +6412,7 @@
       <c r="G227" t="s">
         <v>187</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6455,7 +6429,7 @@
       <c r="D228" t="s">
         <v>140</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6478,7 +6452,7 @@
       <c r="G229" t="s">
         <v>188</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6495,13 +6469,13 @@
       <c r="D230" t="s">
         <v>162</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>206</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6524,7 +6498,7 @@
       <c r="G231" t="s">
         <v>189</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6547,7 +6521,7 @@
       <c r="G232" t="s">
         <v>189</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6570,7 +6544,7 @@
       <c r="G233" t="s">
         <v>190</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6584,7 +6558,7 @@
       <c r="C234" t="s">
         <v>123</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6601,13 +6575,13 @@
       <c r="D235" t="s">
         <v>163</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>201</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6621,7 +6595,7 @@
       <c r="C236" t="s">
         <v>123</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6635,7 +6609,7 @@
       <c r="C237" t="s">
         <v>127</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6649,7 +6623,7 @@
       <c r="C238" t="s">
         <v>123</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6663,7 +6637,7 @@
       <c r="C239" t="s">
         <v>127</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6677,7 +6651,7 @@
       <c r="C240" t="s">
         <v>127</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6694,13 +6668,13 @@
       <c r="D241" t="s">
         <v>133</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>195</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6714,7 +6688,7 @@
       <c r="C242" t="s">
         <v>127</v>
       </c>
-      <c r="H242" s="2">
+      <c r="H242" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6731,13 +6705,13 @@
       <c r="D243" t="s">
         <v>164</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>207</v>
       </c>
-      <c r="H243" s="2">
+      <c r="H243" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6754,13 +6728,13 @@
       <c r="D244" t="s">
         <v>165</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>204</v>
       </c>
-      <c r="H244" s="2">
+      <c r="H244" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6774,7 +6748,7 @@
       <c r="C245" t="s">
         <v>127</v>
       </c>
-      <c r="H245" s="2">
+      <c r="H245" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6788,7 +6762,7 @@
       <c r="C246" t="s">
         <v>123</v>
       </c>
-      <c r="H246" s="2">
+      <c r="H246" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6805,13 +6779,13 @@
       <c r="D247" t="s">
         <v>136</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>208</v>
       </c>
-      <c r="H247" s="2">
+      <c r="H247" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6825,7 +6799,7 @@
       <c r="C248" t="s">
         <v>123</v>
       </c>
-      <c r="H248" s="2">
+      <c r="H248" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6839,7 +6813,7 @@
       <c r="C249" t="s">
         <v>123</v>
       </c>
-      <c r="H249" s="2">
+      <c r="H249" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6856,13 +6830,13 @@
       <c r="D250" t="s">
         <v>166</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>203</v>
       </c>
-      <c r="H250" s="2">
+      <c r="H250" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6876,7 +6850,7 @@
       <c r="C251" t="s">
         <v>123</v>
       </c>
-      <c r="H251" s="2">
+      <c r="H251" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6893,13 +6867,13 @@
       <c r="D252" t="s">
         <v>167</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>205</v>
       </c>
-      <c r="H252" s="2">
+      <c r="H252" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6922,7 +6896,7 @@
       <c r="G253" t="s">
         <v>192</v>
       </c>
-      <c r="H253" s="2">
+      <c r="H253" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6936,7 +6910,7 @@
       <c r="C254" t="s">
         <v>127</v>
       </c>
-      <c r="H254" s="2">
+      <c r="H254" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6950,7 +6924,7 @@
       <c r="C255" t="s">
         <v>123</v>
       </c>
-      <c r="H255" s="2">
+      <c r="H255" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6973,7 +6947,7 @@
       <c r="G256" t="s">
         <v>187</v>
       </c>
-      <c r="H256" s="2">
+      <c r="H256" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6990,7 +6964,7 @@
       <c r="D257" t="s">
         <v>140</v>
       </c>
-      <c r="H257" s="2">
+      <c r="H257" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7013,7 +6987,7 @@
       <c r="G258" t="s">
         <v>188</v>
       </c>
-      <c r="H258" s="2">
+      <c r="H258" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7030,13 +7004,13 @@
       <c r="D259" t="s">
         <v>162</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>206</v>
       </c>
-      <c r="H259" s="2">
+      <c r="H259" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7059,7 +7033,7 @@
       <c r="G260" t="s">
         <v>189</v>
       </c>
-      <c r="H260" s="2">
+      <c r="H260" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7082,7 +7056,7 @@
       <c r="G261" t="s">
         <v>189</v>
       </c>
-      <c r="H261" s="2">
+      <c r="H261" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7105,7 +7079,7 @@
       <c r="G262" t="s">
         <v>190</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7119,7 +7093,7 @@
       <c r="C263" t="s">
         <v>123</v>
       </c>
-      <c r="H263" s="2">
+      <c r="H263" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7136,13 +7110,13 @@
       <c r="D264" t="s">
         <v>163</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>201</v>
       </c>
-      <c r="H264" s="2">
+      <c r="H264" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7156,7 +7130,7 @@
       <c r="C265" t="s">
         <v>123</v>
       </c>
-      <c r="H265" s="2">
+      <c r="H265" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7170,7 +7144,7 @@
       <c r="C266" t="s">
         <v>127</v>
       </c>
-      <c r="H266" s="2">
+      <c r="H266" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7184,7 +7158,7 @@
       <c r="C267" t="s">
         <v>123</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H267" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7198,7 +7172,7 @@
       <c r="C268" t="s">
         <v>127</v>
       </c>
-      <c r="H268" s="2">
+      <c r="H268" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7212,7 +7186,7 @@
       <c r="C269" t="s">
         <v>127</v>
       </c>
-      <c r="H269" s="2">
+      <c r="H269" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7229,13 +7203,13 @@
       <c r="D270" t="s">
         <v>133</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>195</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H270" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7249,7 +7223,7 @@
       <c r="C271" t="s">
         <v>127</v>
       </c>
-      <c r="H271" s="2">
+      <c r="H271" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7266,13 +7240,13 @@
       <c r="D272" t="s">
         <v>164</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>207</v>
       </c>
-      <c r="H272" s="2">
+      <c r="H272" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7289,13 +7263,13 @@
       <c r="D273" t="s">
         <v>165</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>209</v>
       </c>
-      <c r="H273" s="2">
+      <c r="H273" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7309,7 +7283,7 @@
       <c r="C274" t="s">
         <v>123</v>
       </c>
-      <c r="H274" s="2">
+      <c r="H274" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7323,7 +7297,7 @@
       <c r="C275" t="s">
         <v>123</v>
       </c>
-      <c r="H275" s="2">
+      <c r="H275" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7340,13 +7314,13 @@
       <c r="D276" t="s">
         <v>136</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>208</v>
       </c>
-      <c r="H276" s="2">
+      <c r="H276" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7360,7 +7334,7 @@
       <c r="C277" t="s">
         <v>123</v>
       </c>
-      <c r="H277" s="2">
+      <c r="H277" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7377,13 +7351,13 @@
       <c r="D278" t="s">
         <v>168</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>210</v>
       </c>
-      <c r="H278" s="2">
+      <c r="H278" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7400,13 +7374,13 @@
       <c r="D279" t="s">
         <v>166</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>209</v>
       </c>
-      <c r="H279" s="2">
+      <c r="H279" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7420,7 +7394,7 @@
       <c r="C280" t="s">
         <v>123</v>
       </c>
-      <c r="H280" s="2">
+      <c r="H280" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7437,13 +7411,13 @@
       <c r="D281" t="s">
         <v>169</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>205</v>
       </c>
-      <c r="H281" s="2">
+      <c r="H281" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7466,7 +7440,7 @@
       <c r="G282" t="s">
         <v>192</v>
       </c>
-      <c r="H282" s="2">
+      <c r="H282" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7480,7 +7454,7 @@
       <c r="C283" t="s">
         <v>127</v>
       </c>
-      <c r="H283" s="2">
+      <c r="H283" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7494,7 +7468,7 @@
       <c r="C284" t="s">
         <v>123</v>
       </c>
-      <c r="H284" s="2">
+      <c r="H284" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7517,7 +7491,7 @@
       <c r="G285" t="s">
         <v>187</v>
       </c>
-      <c r="H285" s="2">
+      <c r="H285" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7534,7 +7508,7 @@
       <c r="D286" t="s">
         <v>140</v>
       </c>
-      <c r="H286" s="2">
+      <c r="H286" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7557,7 +7531,7 @@
       <c r="G287" t="s">
         <v>188</v>
       </c>
-      <c r="H287" s="2">
+      <c r="H287" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7574,13 +7548,13 @@
       <c r="D288" t="s">
         <v>162</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>206</v>
       </c>
-      <c r="H288" s="2">
+      <c r="H288" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7603,7 +7577,7 @@
       <c r="G289" t="s">
         <v>189</v>
       </c>
-      <c r="H289" s="2">
+      <c r="H289" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7626,7 +7600,7 @@
       <c r="G290" t="s">
         <v>189</v>
       </c>
-      <c r="H290" s="2">
+      <c r="H290" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7649,7 +7623,7 @@
       <c r="G291" t="s">
         <v>190</v>
       </c>
-      <c r="H291" s="2">
+      <c r="H291" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7663,7 +7637,7 @@
       <c r="C292" t="s">
         <v>123</v>
       </c>
-      <c r="H292" s="2">
+      <c r="H292" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7680,13 +7654,13 @@
       <c r="D293" t="s">
         <v>163</v>
       </c>
-      <c r="E293" s="2">
+      <c r="E293" s="1">
         <v>46220</v>
       </c>
       <c r="G293" t="s">
         <v>211</v>
       </c>
-      <c r="H293" s="2">
+      <c r="H293" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7700,7 +7674,7 @@
       <c r="C294" t="s">
         <v>123</v>
       </c>
-      <c r="H294" s="2">
+      <c r="H294" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7723,7 +7697,7 @@
       <c r="G295" t="s">
         <v>193</v>
       </c>
-      <c r="H295" s="2">
+      <c r="H295" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7737,7 +7711,7 @@
       <c r="C296" t="s">
         <v>123</v>
       </c>
-      <c r="H296" s="2">
+      <c r="H296" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7751,7 +7725,7 @@
       <c r="C297" t="s">
         <v>127</v>
       </c>
-      <c r="H297" s="2">
+      <c r="H297" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7768,13 +7742,13 @@
       <c r="D298" t="s">
         <v>171</v>
       </c>
-      <c r="E298" s="2">
+      <c r="E298" s="1">
         <v>46223</v>
       </c>
       <c r="G298" t="s">
         <v>212</v>
       </c>
-      <c r="H298" s="2">
+      <c r="H298" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7791,13 +7765,13 @@
       <c r="D299" t="s">
         <v>133</v>
       </c>
-      <c r="E299" s="2">
+      <c r="E299" s="1">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>195</v>
       </c>
-      <c r="H299" s="2">
+      <c r="H299" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7811,7 +7785,7 @@
       <c r="C300" t="s">
         <v>123</v>
       </c>
-      <c r="H300" s="2">
+      <c r="H300" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7828,13 +7802,13 @@
       <c r="D301" t="s">
         <v>164</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301" s="1">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>207</v>
       </c>
-      <c r="H301" s="2">
+      <c r="H301" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7851,13 +7825,13 @@
       <c r="D302" t="s">
         <v>165</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302" s="1">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>204</v>
       </c>
-      <c r="H302" s="2">
+      <c r="H302" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7871,7 +7845,7 @@
       <c r="C303" t="s">
         <v>123</v>
       </c>
-      <c r="H303" s="2">
+      <c r="H303" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7885,7 +7859,7 @@
       <c r="C304" t="s">
         <v>123</v>
       </c>
-      <c r="H304" s="2">
+      <c r="H304" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7902,13 +7876,13 @@
       <c r="D305" t="s">
         <v>136</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305" s="1">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>208</v>
       </c>
-      <c r="H305" s="2">
+      <c r="H305" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7922,7 +7896,7 @@
       <c r="C306" t="s">
         <v>123</v>
       </c>
-      <c r="H306" s="2">
+      <c r="H306" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7939,13 +7913,13 @@
       <c r="D307" t="s">
         <v>168</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307" s="1">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>210</v>
       </c>
-      <c r="H307" s="2">
+      <c r="H307" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7959,7 +7933,7 @@
       <c r="C308" t="s">
         <v>127</v>
       </c>
-      <c r="H308" s="2">
+      <c r="H308" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7976,13 +7950,13 @@
       <c r="D309" t="s">
         <v>172</v>
       </c>
-      <c r="E309" s="2">
+      <c r="E309" s="1">
         <v>46220</v>
       </c>
       <c r="G309" t="s">
         <v>211</v>
       </c>
-      <c r="H309" s="2">
+      <c r="H309" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7999,13 +7973,13 @@
       <c r="D310" t="s">
         <v>173</v>
       </c>
-      <c r="E310" s="2">
+      <c r="E310" s="1">
         <v>46265</v>
       </c>
       <c r="G310" t="s">
         <v>213</v>
       </c>
-      <c r="H310" s="2">
+      <c r="H310" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8022,7 +7996,7 @@
       <c r="D311" t="s">
         <v>174</v>
       </c>
-      <c r="H311" s="2">
+      <c r="H311" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8036,7 +8010,7 @@
       <c r="C312" t="s">
         <v>127</v>
       </c>
-      <c r="H312" s="2">
+      <c r="H312" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8050,7 +8024,7 @@
       <c r="C313" t="s">
         <v>123</v>
       </c>
-      <c r="H313" s="2">
+      <c r="H313" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8073,7 +8047,7 @@
       <c r="G314" t="s">
         <v>187</v>
       </c>
-      <c r="H314" s="2">
+      <c r="H314" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8090,7 +8064,7 @@
       <c r="D315" t="s">
         <v>140</v>
       </c>
-      <c r="H315" s="2">
+      <c r="H315" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8113,7 +8087,7 @@
       <c r="G316" t="s">
         <v>188</v>
       </c>
-      <c r="H316" s="2">
+      <c r="H316" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8130,13 +8104,13 @@
       <c r="D317" t="s">
         <v>162</v>
       </c>
-      <c r="E317" s="2">
+      <c r="E317" s="1">
         <v>46295</v>
       </c>
       <c r="G317" t="s">
         <v>214</v>
       </c>
-      <c r="H317" s="2">
+      <c r="H317" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8159,7 +8133,7 @@
       <c r="G318" t="s">
         <v>189</v>
       </c>
-      <c r="H318" s="2">
+      <c r="H318" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8182,7 +8156,7 @@
       <c r="G319" t="s">
         <v>189</v>
       </c>
-      <c r="H319" s="2">
+      <c r="H319" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8205,7 +8179,7 @@
       <c r="G320" t="s">
         <v>190</v>
       </c>
-      <c r="H320" s="2">
+      <c r="H320" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8219,7 +8193,7 @@
       <c r="C321" t="s">
         <v>123</v>
       </c>
-      <c r="H321" s="2">
+      <c r="H321" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8236,13 +8210,13 @@
       <c r="D322" t="s">
         <v>163</v>
       </c>
-      <c r="E322" s="2">
+      <c r="E322" s="1">
         <v>46225</v>
       </c>
       <c r="G322" t="s">
         <v>215</v>
       </c>
-      <c r="H322" s="2">
+      <c r="H322" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8256,7 +8230,7 @@
       <c r="C323" t="s">
         <v>123</v>
       </c>
-      <c r="H323" s="2">
+      <c r="H323" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8273,13 +8247,13 @@
       <c r="D324" t="s">
         <v>175</v>
       </c>
-      <c r="E324" s="2">
+      <c r="E324" s="1">
         <v>46224</v>
       </c>
       <c r="G324" t="s">
         <v>216</v>
       </c>
-      <c r="H324" s="2">
+      <c r="H324" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8293,7 +8267,7 @@
       <c r="C325" t="s">
         <v>123</v>
       </c>
-      <c r="H325" s="2">
+      <c r="H325" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8307,7 +8281,7 @@
       <c r="C326" t="s">
         <v>127</v>
       </c>
-      <c r="H326" s="2">
+      <c r="H326" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8321,7 +8295,7 @@
       <c r="C327" t="s">
         <v>127</v>
       </c>
-      <c r="H327" s="2">
+      <c r="H327" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8338,13 +8312,13 @@
       <c r="D328" t="s">
         <v>133</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328" s="1">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>195</v>
       </c>
-      <c r="H328" s="2">
+      <c r="H328" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8361,13 +8335,13 @@
       <c r="D329" t="s">
         <v>176</v>
       </c>
-      <c r="E329" s="2">
+      <c r="E329" s="1">
         <v>46224</v>
       </c>
       <c r="G329" t="s">
         <v>216</v>
       </c>
-      <c r="H329" s="2">
+      <c r="H329" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8384,13 +8358,13 @@
       <c r="D330" t="s">
         <v>164</v>
       </c>
-      <c r="E330" s="2">
+      <c r="E330" s="1">
         <v>46224</v>
       </c>
       <c r="G330" t="s">
         <v>216</v>
       </c>
-      <c r="H330" s="2">
+      <c r="H330" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8404,7 +8378,7 @@
       <c r="C331" t="s">
         <v>123</v>
       </c>
-      <c r="H331" s="2">
+      <c r="H331" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8421,13 +8395,13 @@
       <c r="D332" t="s">
         <v>177</v>
       </c>
-      <c r="E332" s="2">
+      <c r="E332" s="1">
         <v>46224</v>
       </c>
       <c r="G332" t="s">
         <v>216</v>
       </c>
-      <c r="H332" s="2">
+      <c r="H332" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8444,13 +8418,13 @@
       <c r="D333" t="s">
         <v>178</v>
       </c>
-      <c r="E333" s="2">
+      <c r="E333" s="1">
         <v>46225</v>
       </c>
       <c r="G333" t="s">
         <v>215</v>
       </c>
-      <c r="H333" s="2">
+      <c r="H333" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8467,13 +8441,13 @@
       <c r="D334" t="s">
         <v>136</v>
       </c>
-      <c r="E334" s="2">
+      <c r="E334" s="1">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>208</v>
       </c>
-      <c r="H334" s="2">
+      <c r="H334" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8487,7 +8461,7 @@
       <c r="C335" t="s">
         <v>123</v>
       </c>
-      <c r="H335" s="2">
+      <c r="H335" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8504,13 +8478,13 @@
       <c r="D336" t="s">
         <v>168</v>
       </c>
-      <c r="E336" s="2">
+      <c r="E336" s="1">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>210</v>
       </c>
-      <c r="H336" s="2">
+      <c r="H336" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8524,7 +8498,7 @@
       <c r="C337" t="s">
         <v>123</v>
       </c>
-      <c r="H337" s="2">
+      <c r="H337" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8538,7 +8512,7 @@
       <c r="C338" t="s">
         <v>123</v>
       </c>
-      <c r="H338" s="2">
+      <c r="H338" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8555,13 +8529,13 @@
       <c r="D339" t="s">
         <v>173</v>
       </c>
-      <c r="E339" s="2">
+      <c r="E339" s="1">
         <v>46265</v>
       </c>
       <c r="G339" t="s">
         <v>213</v>
       </c>
-      <c r="H339" s="2">
+      <c r="H339" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8578,7 +8552,7 @@
       <c r="D340" t="s">
         <v>179</v>
       </c>
-      <c r="H340" s="2">
+      <c r="H340" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8592,7 +8566,7 @@
       <c r="C341" t="s">
         <v>127</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8606,7 +8580,7 @@
       <c r="C342" t="s">
         <v>123</v>
       </c>
-      <c r="H342" s="2">
+      <c r="H342" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8629,7 +8603,7 @@
       <c r="G343" t="s">
         <v>187</v>
       </c>
-      <c r="H343" s="2">
+      <c r="H343" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8646,7 +8620,7 @@
       <c r="D344" t="s">
         <v>140</v>
       </c>
-      <c r="H344" s="2">
+      <c r="H344" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8669,7 +8643,7 @@
       <c r="G345" t="s">
         <v>188</v>
       </c>
-      <c r="H345" s="2">
+      <c r="H345" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8686,13 +8660,13 @@
       <c r="D346" t="s">
         <v>162</v>
       </c>
-      <c r="E346" s="2">
+      <c r="E346" s="1">
         <v>46295</v>
       </c>
       <c r="G346" t="s">
         <v>214</v>
       </c>
-      <c r="H346" s="2">
+      <c r="H346" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8715,7 +8689,7 @@
       <c r="G347" t="s">
         <v>189</v>
       </c>
-      <c r="H347" s="2">
+      <c r="H347" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8738,7 +8712,7 @@
       <c r="G348" t="s">
         <v>189</v>
       </c>
-      <c r="H348" s="2">
+      <c r="H348" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8761,7 +8735,7 @@
       <c r="G349" t="s">
         <v>190</v>
       </c>
-      <c r="H349" s="2">
+      <c r="H349" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8775,7 +8749,7 @@
       <c r="C350" t="s">
         <v>123</v>
       </c>
-      <c r="H350" s="2">
+      <c r="H350" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8792,13 +8766,13 @@
       <c r="D351" t="s">
         <v>163</v>
       </c>
-      <c r="E351" s="2">
+      <c r="E351" s="1">
         <v>46225</v>
       </c>
       <c r="G351" t="s">
         <v>215</v>
       </c>
-      <c r="H351" s="2">
+      <c r="H351" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8812,7 +8786,7 @@
       <c r="C352" t="s">
         <v>123</v>
       </c>
-      <c r="H352" s="2">
+      <c r="H352" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8826,7 +8800,7 @@
       <c r="C353" t="s">
         <v>123</v>
       </c>
-      <c r="H353" s="2">
+      <c r="H353" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8840,7 +8814,7 @@
       <c r="C354" t="s">
         <v>123</v>
       </c>
-      <c r="H354" s="2">
+      <c r="H354" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8854,7 +8828,7 @@
       <c r="C355" t="s">
         <v>127</v>
       </c>
-      <c r="H355" s="2">
+      <c r="H355" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8868,7 +8842,7 @@
       <c r="C356" t="s">
         <v>127</v>
       </c>
-      <c r="H356" s="2">
+      <c r="H356" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8885,13 +8859,13 @@
       <c r="D357" t="s">
         <v>133</v>
       </c>
-      <c r="E357" s="2">
+      <c r="E357" s="1">
         <v>46234</v>
       </c>
       <c r="G357" t="s">
         <v>217</v>
       </c>
-      <c r="H357" s="2">
+      <c r="H357" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8905,7 +8879,7 @@
       <c r="C358" t="s">
         <v>123</v>
       </c>
-      <c r="H358" s="2">
+      <c r="H358" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8922,13 +8896,13 @@
       <c r="D359" t="s">
         <v>164</v>
       </c>
-      <c r="E359" s="2">
+      <c r="E359" s="1">
         <v>46227</v>
       </c>
       <c r="G359" t="s">
         <v>218</v>
       </c>
-      <c r="H359" s="2">
+      <c r="H359" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8942,7 +8916,7 @@
       <c r="C360" t="s">
         <v>123</v>
       </c>
-      <c r="H360" s="2">
+      <c r="H360" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8956,7 +8930,7 @@
       <c r="C361" t="s">
         <v>123</v>
       </c>
-      <c r="H361" s="2">
+      <c r="H361" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8973,13 +8947,13 @@
       <c r="D362" t="s">
         <v>178</v>
       </c>
-      <c r="E362" s="2">
+      <c r="E362" s="1">
         <v>46225</v>
       </c>
       <c r="G362" t="s">
         <v>215</v>
       </c>
-      <c r="H362" s="2">
+      <c r="H362" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8996,13 +8970,13 @@
       <c r="D363" t="s">
         <v>136</v>
       </c>
-      <c r="E363" s="2">
+      <c r="E363" s="1">
         <v>46237</v>
       </c>
       <c r="G363" t="s">
         <v>219</v>
       </c>
-      <c r="H363" s="2">
+      <c r="H363" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9016,7 +8990,7 @@
       <c r="C364" t="s">
         <v>123</v>
       </c>
-      <c r="H364" s="2">
+      <c r="H364" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9033,13 +9007,13 @@
       <c r="D365" t="s">
         <v>168</v>
       </c>
-      <c r="E365" s="2">
+      <c r="E365" s="1">
         <v>46227</v>
       </c>
       <c r="G365" t="s">
         <v>218</v>
       </c>
-      <c r="H365" s="2">
+      <c r="H365" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9053,7 +9027,7 @@
       <c r="C366" t="s">
         <v>123</v>
       </c>
-      <c r="H366" s="2">
+      <c r="H366" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9067,7 +9041,7 @@
       <c r="C367" t="s">
         <v>123</v>
       </c>
-      <c r="H367" s="2">
+      <c r="H367" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9084,13 +9058,13 @@
       <c r="D368" t="s">
         <v>173</v>
       </c>
-      <c r="E368" s="2">
+      <c r="E368" s="1">
         <v>46234</v>
       </c>
       <c r="G368" t="s">
         <v>217</v>
       </c>
-      <c r="H368" s="2">
+      <c r="H368" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9107,13 +9081,13 @@
       <c r="D369" t="s">
         <v>180</v>
       </c>
-      <c r="E369" s="2">
+      <c r="E369" s="1">
         <v>46227</v>
       </c>
       <c r="G369" t="s">
         <v>218</v>
       </c>
-      <c r="H369" s="2">
+      <c r="H369" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9130,7 +9104,7 @@
       <c r="D370" t="s">
         <v>179</v>
       </c>
-      <c r="H370" s="2">
+      <c r="H370" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9144,7 +9118,7 @@
       <c r="C371" t="s">
         <v>123</v>
       </c>
-      <c r="H371" s="2">
+      <c r="H371" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9167,7 +9141,7 @@
       <c r="G372" t="s">
         <v>187</v>
       </c>
-      <c r="H372" s="2">
+      <c r="H372" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9184,7 +9158,7 @@
       <c r="D373" t="s">
         <v>140</v>
       </c>
-      <c r="H373" s="2">
+      <c r="H373" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9207,7 +9181,7 @@
       <c r="G374" t="s">
         <v>188</v>
       </c>
-      <c r="H374" s="2">
+      <c r="H374" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9224,13 +9198,13 @@
       <c r="D375" t="s">
         <v>162</v>
       </c>
-      <c r="E375" s="2">
+      <c r="E375" s="1">
         <v>46295</v>
       </c>
       <c r="G375" t="s">
         <v>214</v>
       </c>
-      <c r="H375" s="2">
+      <c r="H375" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9253,7 +9227,7 @@
       <c r="G376" t="s">
         <v>189</v>
       </c>
-      <c r="H376" s="2">
+      <c r="H376" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9276,7 +9250,7 @@
       <c r="G377" t="s">
         <v>189</v>
       </c>
-      <c r="H377" s="2">
+      <c r="H377" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9299,7 +9273,7 @@
       <c r="G378" t="s">
         <v>190</v>
       </c>
-      <c r="H378" s="2">
+      <c r="H378" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9313,7 +9287,7 @@
       <c r="C379" t="s">
         <v>123</v>
       </c>
-      <c r="H379" s="2">
+      <c r="H379" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9330,13 +9304,13 @@
       <c r="D380" t="s">
         <v>163</v>
       </c>
-      <c r="E380" s="2">
+      <c r="E380" s="1">
         <v>46227</v>
       </c>
       <c r="G380" t="s">
         <v>218</v>
       </c>
-      <c r="H380" s="2">
+      <c r="H380" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9350,7 +9324,7 @@
       <c r="C381" t="s">
         <v>123</v>
       </c>
-      <c r="H381" s="2">
+      <c r="H381" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9364,7 +9338,7 @@
       <c r="C382" t="s">
         <v>123</v>
       </c>
-      <c r="H382" s="2">
+      <c r="H382" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9378,7 +9352,7 @@
       <c r="C383" t="s">
         <v>123</v>
       </c>
-      <c r="H383" s="2">
+      <c r="H383" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9392,7 +9366,7 @@
       <c r="C384" t="s">
         <v>127</v>
       </c>
-      <c r="H384" s="2">
+      <c r="H384" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9406,7 +9380,7 @@
       <c r="C385" t="s">
         <v>127</v>
       </c>
-      <c r="H385" s="2">
+      <c r="H385" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9423,13 +9397,13 @@
       <c r="D386" t="s">
         <v>133</v>
       </c>
-      <c r="E386" s="2">
+      <c r="E386" s="1">
         <v>46234</v>
       </c>
       <c r="G386" t="s">
         <v>217</v>
       </c>
-      <c r="H386" s="2">
+      <c r="H386" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9443,7 +9417,7 @@
       <c r="C387" t="s">
         <v>123</v>
       </c>
-      <c r="H387" s="2">
+      <c r="H387" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9457,7 +9431,7 @@
       <c r="C388" t="s">
         <v>127</v>
       </c>
-      <c r="H388" s="2">
+      <c r="H388" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9471,7 +9445,7 @@
       <c r="C389" t="s">
         <v>123</v>
       </c>
-      <c r="H389" s="2">
+      <c r="H389" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9485,7 +9459,7 @@
       <c r="C390" t="s">
         <v>123</v>
       </c>
-      <c r="H390" s="2">
+      <c r="H390" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9502,13 +9476,13 @@
       <c r="D391" t="s">
         <v>181</v>
       </c>
-      <c r="E391" s="2">
+      <c r="E391" s="1">
         <v>46227</v>
       </c>
       <c r="G391" t="s">
         <v>218</v>
       </c>
-      <c r="H391" s="2">
+      <c r="H391" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9525,13 +9499,13 @@
       <c r="D392" t="s">
         <v>136</v>
       </c>
-      <c r="E392" s="2">
+      <c r="E392" s="1">
         <v>46237</v>
       </c>
       <c r="G392" t="s">
         <v>219</v>
       </c>
-      <c r="H392" s="2">
+      <c r="H392" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9545,7 +9519,7 @@
       <c r="C393" t="s">
         <v>123</v>
       </c>
-      <c r="H393" s="2">
+      <c r="H393" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9562,13 +9536,13 @@
       <c r="D394" t="s">
         <v>168</v>
       </c>
-      <c r="E394" s="2">
+      <c r="E394" s="1">
         <v>46227</v>
       </c>
       <c r="G394" t="s">
         <v>218</v>
       </c>
-      <c r="H394" s="2">
+      <c r="H394" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9582,7 +9556,7 @@
       <c r="C395" t="s">
         <v>123</v>
       </c>
-      <c r="H395" s="2">
+      <c r="H395" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9596,7 +9570,7 @@
       <c r="C396" t="s">
         <v>123</v>
       </c>
-      <c r="H396" s="2">
+      <c r="H396" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9613,13 +9587,13 @@
       <c r="D397" t="s">
         <v>173</v>
       </c>
-      <c r="E397" s="2">
+      <c r="E397" s="1">
         <v>46234</v>
       </c>
       <c r="G397" t="s">
         <v>217</v>
       </c>
-      <c r="H397" s="2">
+      <c r="H397" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9636,13 +9610,13 @@
       <c r="D398" t="s">
         <v>180</v>
       </c>
-      <c r="E398" s="2">
+      <c r="E398" s="1">
         <v>46227</v>
       </c>
       <c r="G398" t="s">
         <v>218</v>
       </c>
-      <c r="H398" s="2">
+      <c r="H398" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9659,7 +9633,7 @@
       <c r="D399" t="s">
         <v>179</v>
       </c>
-      <c r="H399" s="2">
+      <c r="H399" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9673,7 +9647,7 @@
       <c r="C400" t="s">
         <v>123</v>
       </c>
-      <c r="H400" s="2">
+      <c r="H400" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9696,7 +9670,7 @@
       <c r="G401" t="s">
         <v>187</v>
       </c>
-      <c r="H401" s="2">
+      <c r="H401" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9713,7 +9687,7 @@
       <c r="D402" t="s">
         <v>140</v>
       </c>
-      <c r="H402" s="2">
+      <c r="H402" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9736,7 +9710,7 @@
       <c r="G403" t="s">
         <v>188</v>
       </c>
-      <c r="H403" s="2">
+      <c r="H403" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9753,13 +9727,13 @@
       <c r="D404" t="s">
         <v>162</v>
       </c>
-      <c r="E404" s="2">
+      <c r="E404" s="1">
         <v>46295</v>
       </c>
       <c r="G404" t="s">
         <v>214</v>
       </c>
-      <c r="H404" s="2">
+      <c r="H404" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9782,7 +9756,7 @@
       <c r="G405" t="s">
         <v>189</v>
       </c>
-      <c r="H405" s="2">
+      <c r="H405" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9805,7 +9779,7 @@
       <c r="G406" t="s">
         <v>189</v>
       </c>
-      <c r="H406" s="2">
+      <c r="H406" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9828,7 +9802,7 @@
       <c r="G407" t="s">
         <v>190</v>
       </c>
-      <c r="H407" s="2">
+      <c r="H407" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9842,7 +9816,7 @@
       <c r="C408" t="s">
         <v>123</v>
       </c>
-      <c r="H408" s="2">
+      <c r="H408" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9859,13 +9833,13 @@
       <c r="D409" t="s">
         <v>150</v>
       </c>
-      <c r="E409" s="2">
+      <c r="E409" s="1">
         <v>46231</v>
       </c>
       <c r="G409" t="s">
         <v>220</v>
       </c>
-      <c r="H409" s="2">
+      <c r="H409" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9879,7 +9853,7 @@
       <c r="C410" t="s">
         <v>123</v>
       </c>
-      <c r="H410" s="2">
+      <c r="H410" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9893,7 +9867,7 @@
       <c r="C411" t="s">
         <v>123</v>
       </c>
-      <c r="H411" s="2">
+      <c r="H411" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9907,7 +9881,7 @@
       <c r="C412" t="s">
         <v>123</v>
       </c>
-      <c r="H412" s="2">
+      <c r="H412" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9921,7 +9895,7 @@
       <c r="C413" t="s">
         <v>127</v>
       </c>
-      <c r="H413" s="2">
+      <c r="H413" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9935,7 +9909,7 @@
       <c r="C414" t="s">
         <v>127</v>
       </c>
-      <c r="H414" s="2">
+      <c r="H414" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9952,13 +9926,13 @@
       <c r="D415" t="s">
         <v>182</v>
       </c>
-      <c r="E415" s="2">
+      <c r="E415" s="1">
         <v>46234</v>
       </c>
       <c r="G415" t="s">
         <v>217</v>
       </c>
-      <c r="H415" s="2">
+      <c r="H415" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9972,7 +9946,7 @@
       <c r="C416" t="s">
         <v>123</v>
       </c>
-      <c r="H416" s="2">
+      <c r="H416" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9986,7 +9960,7 @@
       <c r="C417" t="s">
         <v>127</v>
       </c>
-      <c r="H417" s="2">
+      <c r="H417" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10000,7 +9974,7 @@
       <c r="C418" t="s">
         <v>123</v>
       </c>
-      <c r="H418" s="2">
+      <c r="H418" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10014,7 +9988,7 @@
       <c r="C419" t="s">
         <v>123</v>
       </c>
-      <c r="H419" s="2">
+      <c r="H419" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10031,13 +10005,13 @@
       <c r="D420" t="s">
         <v>136</v>
       </c>
-      <c r="E420" s="2">
+      <c r="E420" s="1">
         <v>46237</v>
       </c>
       <c r="G420" t="s">
         <v>219</v>
       </c>
-      <c r="H420" s="2">
+      <c r="H420" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10051,7 +10025,7 @@
       <c r="C421" t="s">
         <v>123</v>
       </c>
-      <c r="H421" s="2">
+      <c r="H421" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10068,13 +10042,13 @@
       <c r="D422" t="s">
         <v>168</v>
       </c>
-      <c r="E422" s="2">
+      <c r="E422" s="1">
         <v>46227</v>
       </c>
       <c r="G422" t="s">
         <v>218</v>
       </c>
-      <c r="H422" s="2">
+      <c r="H422" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10088,7 +10062,7 @@
       <c r="C423" t="s">
         <v>123</v>
       </c>
-      <c r="H423" s="2">
+      <c r="H423" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10102,7 +10076,7 @@
       <c r="C424" t="s">
         <v>123</v>
       </c>
-      <c r="H424" s="2">
+      <c r="H424" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10119,13 +10093,13 @@
       <c r="D425" t="s">
         <v>173</v>
       </c>
-      <c r="E425" s="2">
+      <c r="E425" s="1">
         <v>46234</v>
       </c>
       <c r="G425" t="s">
         <v>217</v>
       </c>
-      <c r="H425" s="2">
+      <c r="H425" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10142,13 +10116,13 @@
       <c r="D426" t="s">
         <v>180</v>
       </c>
-      <c r="E426" s="2">
+      <c r="E426" s="1">
         <v>46227</v>
       </c>
       <c r="G426" t="s">
         <v>218</v>
       </c>
-      <c r="H426" s="2">
+      <c r="H426" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10165,7 +10139,7 @@
       <c r="D427" t="s">
         <v>179</v>
       </c>
-      <c r="H427" s="2">
+      <c r="H427" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10179,7 +10153,7 @@
       <c r="C428" t="s">
         <v>123</v>
       </c>
-      <c r="H428" s="2">
+      <c r="H428" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10202,7 +10176,7 @@
       <c r="G429" t="s">
         <v>187</v>
       </c>
-      <c r="H429" s="2">
+      <c r="H429" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10219,7 +10193,7 @@
       <c r="D430" t="s">
         <v>140</v>
       </c>
-      <c r="H430" s="2">
+      <c r="H430" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10242,7 +10216,7 @@
       <c r="G431" t="s">
         <v>188</v>
       </c>
-      <c r="H431" s="2">
+      <c r="H431" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10259,13 +10233,13 @@
       <c r="D432" t="s">
         <v>162</v>
       </c>
-      <c r="E432" s="2">
+      <c r="E432" s="1">
         <v>46295</v>
       </c>
       <c r="G432" t="s">
         <v>214</v>
       </c>
-      <c r="H432" s="2">
+      <c r="H432" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10288,7 +10262,7 @@
       <c r="G433" t="s">
         <v>189</v>
       </c>
-      <c r="H433" s="2">
+      <c r="H433" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10311,7 +10285,7 @@
       <c r="G434" t="s">
         <v>189</v>
       </c>
-      <c r="H434" s="2">
+      <c r="H434" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10334,7 +10308,7 @@
       <c r="G435" t="s">
         <v>190</v>
       </c>
-      <c r="H435" s="2">
+      <c r="H435" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10351,13 +10325,13 @@
       <c r="D436" t="s">
         <v>183</v>
       </c>
-      <c r="E436" s="2">
+      <c r="E436" s="1">
         <v>46230</v>
       </c>
       <c r="G436" t="s">
         <v>221</v>
       </c>
-      <c r="H436" s="2">
+      <c r="H436" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10371,7 +10345,7 @@
       <c r="C437" t="s">
         <v>123</v>
       </c>
-      <c r="H437" s="2">
+      <c r="H437" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10388,13 +10362,13 @@
       <c r="D438" t="s">
         <v>150</v>
       </c>
-      <c r="E438" s="2">
+      <c r="E438" s="1">
         <v>46231</v>
       </c>
       <c r="G438" t="s">
         <v>220</v>
       </c>
-      <c r="H438" s="2">
+      <c r="H438" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10408,7 +10382,7 @@
       <c r="C439" t="s">
         <v>123</v>
       </c>
-      <c r="H439" s="2">
+      <c r="H439" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10422,7 +10396,7 @@
       <c r="C440" t="s">
         <v>123</v>
       </c>
-      <c r="H440" s="2">
+      <c r="H440" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10436,7 +10410,7 @@
       <c r="C441" t="s">
         <v>123</v>
       </c>
-      <c r="H441" s="2">
+      <c r="H441" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10450,7 +10424,7 @@
       <c r="C442" t="s">
         <v>127</v>
       </c>
-      <c r="H442" s="2">
+      <c r="H442" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10464,7 +10438,7 @@
       <c r="C443" t="s">
         <v>127</v>
       </c>
-      <c r="H443" s="2">
+      <c r="H443" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10481,13 +10455,13 @@
       <c r="D444" t="s">
         <v>182</v>
       </c>
-      <c r="E444" s="2">
+      <c r="E444" s="1">
         <v>46234</v>
       </c>
       <c r="G444" t="s">
         <v>217</v>
       </c>
-      <c r="H444" s="2">
+      <c r="H444" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10501,7 +10475,7 @@
       <c r="C445" t="s">
         <v>123</v>
       </c>
-      <c r="H445" s="2">
+      <c r="H445" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10518,13 +10492,13 @@
       <c r="D446" t="s">
         <v>184</v>
       </c>
-      <c r="E446" s="2">
+      <c r="E446" s="1">
         <v>46230</v>
       </c>
       <c r="G446" t="s">
         <v>221</v>
       </c>
-      <c r="H446" s="2">
+      <c r="H446" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10538,7 +10512,7 @@
       <c r="C447" t="s">
         <v>123</v>
       </c>
-      <c r="H447" s="2">
+      <c r="H447" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10552,7 +10526,7 @@
       <c r="C448" t="s">
         <v>123</v>
       </c>
-      <c r="H448" s="2">
+      <c r="H448" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10569,13 +10543,13 @@
       <c r="D449" t="s">
         <v>136</v>
       </c>
-      <c r="E449" s="2">
+      <c r="E449" s="1">
         <v>46237</v>
       </c>
       <c r="G449" t="s">
         <v>219</v>
       </c>
-      <c r="H449" s="2">
+      <c r="H449" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10589,7 +10563,7 @@
       <c r="C450" t="s">
         <v>123</v>
       </c>
-      <c r="H450" s="2">
+      <c r="H450" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10603,7 +10577,7 @@
       <c r="C451" t="s">
         <v>123</v>
       </c>
-      <c r="H451" s="2">
+      <c r="H451" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10617,7 +10591,7 @@
       <c r="C452" t="s">
         <v>123</v>
       </c>
-      <c r="H452" s="2">
+      <c r="H452" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10631,7 +10605,7 @@
       <c r="C453" t="s">
         <v>123</v>
       </c>
-      <c r="H453" s="2">
+      <c r="H453" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10648,13 +10622,13 @@
       <c r="D454" t="s">
         <v>173</v>
       </c>
-      <c r="E454" s="2">
+      <c r="E454" s="1">
         <v>46234</v>
       </c>
       <c r="G454" t="s">
         <v>217</v>
       </c>
-      <c r="H454" s="2">
+      <c r="H454" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10668,7 +10642,7 @@
       <c r="C455" t="s">
         <v>127</v>
       </c>
-      <c r="H455" s="2">
+      <c r="H455" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10685,7 +10659,7 @@
       <c r="D456" t="s">
         <v>179</v>
       </c>
-      <c r="H456" s="2">
+      <c r="H456" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10699,7 +10673,7 @@
       <c r="C457" t="s">
         <v>123</v>
       </c>
-      <c r="H457" s="2">
+      <c r="H457" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10722,7 +10696,7 @@
       <c r="G458" t="s">
         <v>187</v>
       </c>
-      <c r="H458" s="2">
+      <c r="H458" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10739,7 +10713,7 @@
       <c r="D459" t="s">
         <v>140</v>
       </c>
-      <c r="H459" s="2">
+      <c r="H459" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10762,7 +10736,7 @@
       <c r="G460" t="s">
         <v>188</v>
       </c>
-      <c r="H460" s="2">
+      <c r="H460" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10779,13 +10753,13 @@
       <c r="D461" t="s">
         <v>162</v>
       </c>
-      <c r="E461" s="2">
+      <c r="E461" s="1">
         <v>46295</v>
       </c>
       <c r="G461" t="s">
         <v>214</v>
       </c>
-      <c r="H461" s="2">
+      <c r="H461" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10808,7 +10782,7 @@
       <c r="G462" t="s">
         <v>189</v>
       </c>
-      <c r="H462" s="2">
+      <c r="H462" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10831,7 +10805,7 @@
       <c r="G463" t="s">
         <v>189</v>
       </c>
-      <c r="H463" s="2">
+      <c r="H463" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10854,7 +10828,7 @@
       <c r="G464" t="s">
         <v>190</v>
       </c>
-      <c r="H464" s="2">
+      <c r="H464" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10871,13 +10845,13 @@
       <c r="D465" t="s">
         <v>183</v>
       </c>
-      <c r="E465" s="2">
+      <c r="E465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
         <v>221</v>
       </c>
-      <c r="H465" s="2">
+      <c r="H465" s="1">
         <v>46230</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -690,8 +690,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -707,7 +715,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -715,12 +723,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1020,72 +1046,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1150,7 +1176,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1215,7 +1241,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1280,7 +1306,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1345,7 +1371,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1410,7 +1436,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1475,7 +1501,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1540,7 +1566,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1605,7 +1631,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1670,7 +1696,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1735,7 +1761,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1800,7 +1826,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -1865,7 +1891,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -1930,7 +1956,7 @@
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>46226</v>
       </c>
       <c r="B15">
@@ -1995,7 +2021,7 @@
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>46227</v>
       </c>
       <c r="B16">
@@ -2060,7 +2086,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>46230</v>
       </c>
       <c r="B17">
@@ -2135,28 +2161,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2170,7 +2196,7 @@
       <c r="C2" t="s">
         <v>123</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2184,7 +2210,7 @@
       <c r="C3" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2207,7 +2233,7 @@
       <c r="G4" t="s">
         <v>185</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2221,7 +2247,7 @@
       <c r="C5" t="s">
         <v>123</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2235,7 +2261,7 @@
       <c r="C6" t="s">
         <v>123</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2252,13 +2278,13 @@
       <c r="D7" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>194</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2275,13 +2301,13 @@
       <c r="D8" t="s">
         <v>132</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>194</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2298,13 +2324,13 @@
       <c r="D9" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>195</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2321,13 +2347,13 @@
       <c r="D10" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>196</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2341,7 +2367,7 @@
       <c r="C11" t="s">
         <v>123</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2355,7 +2381,7 @@
       <c r="C12" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2372,13 +2398,13 @@
       <c r="D13" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>194</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2392,7 +2418,7 @@
       <c r="C14" t="s">
         <v>127</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2409,13 +2435,13 @@
       <c r="D15" t="s">
         <v>136</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2429,7 +2455,7 @@
       <c r="C16" t="s">
         <v>123</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2443,7 +2469,7 @@
       <c r="C17" t="s">
         <v>123</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2460,13 +2486,13 @@
       <c r="D18" t="s">
         <v>137</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>198</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2480,7 +2506,7 @@
       <c r="C19" t="s">
         <v>123</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2497,13 +2523,13 @@
       <c r="D20" t="s">
         <v>138</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>194</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2526,7 +2552,7 @@
       <c r="G21" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2540,7 +2566,7 @@
       <c r="C22" t="s">
         <v>127</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2554,7 +2580,7 @@
       <c r="C23" t="s">
         <v>123</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2577,7 +2603,7 @@
       <c r="G24" t="s">
         <v>187</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2594,7 +2620,7 @@
       <c r="D25" t="s">
         <v>140</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2617,7 +2643,7 @@
       <c r="G26" t="s">
         <v>188</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2634,13 +2660,13 @@
       <c r="D27" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="2">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>199</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2663,7 +2689,7 @@
       <c r="G28" t="s">
         <v>189</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2686,7 +2712,7 @@
       <c r="G29" t="s">
         <v>189</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2709,7 +2735,7 @@
       <c r="G30" t="s">
         <v>190</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="2">
         <v>46204</v>
       </c>
     </row>
@@ -2723,7 +2749,7 @@
       <c r="C31" t="s">
         <v>123</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2737,7 +2763,7 @@
       <c r="C32" t="s">
         <v>123</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2760,7 +2786,7 @@
       <c r="G33" t="s">
         <v>191</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2774,7 +2800,7 @@
       <c r="C34" t="s">
         <v>123</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2788,7 +2814,7 @@
       <c r="C35" t="s">
         <v>123</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2805,13 +2831,13 @@
       <c r="D36" t="s">
         <v>131</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>194</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2828,13 +2854,13 @@
       <c r="D37" t="s">
         <v>132</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="2">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>194</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2851,13 +2877,13 @@
       <c r="D38" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="2">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>195</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2874,13 +2900,13 @@
       <c r="D39" t="s">
         <v>134</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="2">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>196</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2894,7 +2920,7 @@
       <c r="C40" t="s">
         <v>123</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2908,7 +2934,7 @@
       <c r="C41" t="s">
         <v>123</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2925,13 +2951,13 @@
       <c r="D42" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>194</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2945,7 +2971,7 @@
       <c r="C43" t="s">
         <v>123</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2962,13 +2988,13 @@
       <c r="D44" t="s">
         <v>136</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>197</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H44" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2982,7 +3008,7 @@
       <c r="C45" t="s">
         <v>123</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H45" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -2996,7 +3022,7 @@
       <c r="C46" t="s">
         <v>123</v>
       </c>
-      <c r="H46" s="1">
+      <c r="H46" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3010,7 +3036,7 @@
       <c r="C47" t="s">
         <v>127</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H47" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3024,7 +3050,7 @@
       <c r="C48" t="s">
         <v>123</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H48" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3041,13 +3067,13 @@
       <c r="D49" t="s">
         <v>147</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>194</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H49" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3070,7 +3096,7 @@
       <c r="G50" t="s">
         <v>186</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H50" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3084,7 +3110,7 @@
       <c r="C51" t="s">
         <v>127</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3098,7 +3124,7 @@
       <c r="C52" t="s">
         <v>123</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H52" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3121,7 +3147,7 @@
       <c r="G53" t="s">
         <v>187</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H53" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3138,7 +3164,7 @@
       <c r="D54" t="s">
         <v>140</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H54" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3161,7 +3187,7 @@
       <c r="G55" t="s">
         <v>188</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H55" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3178,13 +3204,13 @@
       <c r="D56" t="s">
         <v>142</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>199</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H56" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3207,7 +3233,7 @@
       <c r="G57" t="s">
         <v>189</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H57" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3230,7 +3256,7 @@
       <c r="G58" t="s">
         <v>189</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3253,7 +3279,7 @@
       <c r="G59" t="s">
         <v>190</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="2">
         <v>46205</v>
       </c>
     </row>
@@ -3267,7 +3293,7 @@
       <c r="C60" t="s">
         <v>123</v>
       </c>
-      <c r="H60" s="1">
+      <c r="H60" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3281,7 +3307,7 @@
       <c r="C61" t="s">
         <v>123</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H61" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3298,13 +3324,13 @@
       <c r="D62" t="s">
         <v>146</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="2">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>200</v>
       </c>
-      <c r="H62" s="1">
+      <c r="H62" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3318,7 +3344,7 @@
       <c r="C63" t="s">
         <v>123</v>
       </c>
-      <c r="H63" s="1">
+      <c r="H63" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3335,13 +3361,13 @@
       <c r="D64" t="s">
         <v>148</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="2">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>201</v>
       </c>
-      <c r="H64" s="1">
+      <c r="H64" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3355,7 +3381,7 @@
       <c r="C65" t="s">
         <v>123</v>
       </c>
-      <c r="H65" s="1">
+      <c r="H65" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3369,7 +3395,7 @@
       <c r="C66" t="s">
         <v>127</v>
       </c>
-      <c r="H66" s="1">
+      <c r="H66" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3386,13 +3412,13 @@
       <c r="D67" t="s">
         <v>133</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="2">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>195</v>
       </c>
-      <c r="H67" s="1">
+      <c r="H67" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3409,13 +3435,13 @@
       <c r="D68" t="s">
         <v>134</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="2">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>196</v>
       </c>
-      <c r="H68" s="1">
+      <c r="H68" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3429,7 +3455,7 @@
       <c r="C69" t="s">
         <v>123</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H69" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3443,7 +3469,7 @@
       <c r="C70" t="s">
         <v>123</v>
       </c>
-      <c r="H70" s="1">
+      <c r="H70" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3460,13 +3486,13 @@
       <c r="D71" t="s">
         <v>135</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="2">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>200</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H71" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3480,7 +3506,7 @@
       <c r="C72" t="s">
         <v>123</v>
       </c>
-      <c r="H72" s="1">
+      <c r="H72" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3497,13 +3523,13 @@
       <c r="D73" t="s">
         <v>136</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="2">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>197</v>
       </c>
-      <c r="H73" s="1">
+      <c r="H73" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3517,7 +3543,7 @@
       <c r="C74" t="s">
         <v>123</v>
       </c>
-      <c r="H74" s="1">
+      <c r="H74" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3531,7 +3557,7 @@
       <c r="C75" t="s">
         <v>123</v>
       </c>
-      <c r="H75" s="1">
+      <c r="H75" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3545,7 +3571,7 @@
       <c r="C76" t="s">
         <v>123</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H76" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3559,7 +3585,7 @@
       <c r="C77" t="s">
         <v>123</v>
       </c>
-      <c r="H77" s="1">
+      <c r="H77" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3576,13 +3602,13 @@
       <c r="D78" t="s">
         <v>147</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E78" s="2">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>200</v>
       </c>
-      <c r="H78" s="1">
+      <c r="H78" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3605,7 +3631,7 @@
       <c r="G79" t="s">
         <v>192</v>
       </c>
-      <c r="H79" s="1">
+      <c r="H79" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3619,7 +3645,7 @@
       <c r="C80" t="s">
         <v>127</v>
       </c>
-      <c r="H80" s="1">
+      <c r="H80" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3633,7 +3659,7 @@
       <c r="C81" t="s">
         <v>123</v>
       </c>
-      <c r="H81" s="1">
+      <c r="H81" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3656,7 +3682,7 @@
       <c r="G82" t="s">
         <v>187</v>
       </c>
-      <c r="H82" s="1">
+      <c r="H82" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3673,7 +3699,7 @@
       <c r="D83" t="s">
         <v>140</v>
       </c>
-      <c r="H83" s="1">
+      <c r="H83" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3696,7 +3722,7 @@
       <c r="G84" t="s">
         <v>188</v>
       </c>
-      <c r="H84" s="1">
+      <c r="H84" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3713,13 +3739,13 @@
       <c r="D85" t="s">
         <v>142</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85" s="2">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>199</v>
       </c>
-      <c r="H85" s="1">
+      <c r="H85" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3742,7 +3768,7 @@
       <c r="G86" t="s">
         <v>189</v>
       </c>
-      <c r="H86" s="1">
+      <c r="H86" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3765,7 +3791,7 @@
       <c r="G87" t="s">
         <v>189</v>
       </c>
-      <c r="H87" s="1">
+      <c r="H87" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3788,7 +3814,7 @@
       <c r="G88" t="s">
         <v>190</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H88" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -3802,7 +3828,7 @@
       <c r="C89" t="s">
         <v>123</v>
       </c>
-      <c r="H89" s="1">
+      <c r="H89" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3819,13 +3845,13 @@
       <c r="D90" t="s">
         <v>150</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90" s="2">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>201</v>
       </c>
-      <c r="H90" s="1">
+      <c r="H90" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3842,13 +3868,13 @@
       <c r="D91" t="s">
         <v>146</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E91" s="2">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>200</v>
       </c>
-      <c r="H91" s="1">
+      <c r="H91" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3862,7 +3888,7 @@
       <c r="C92" t="s">
         <v>123</v>
       </c>
-      <c r="H92" s="1">
+      <c r="H92" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3879,13 +3905,13 @@
       <c r="D93" t="s">
         <v>148</v>
       </c>
-      <c r="E93" s="1">
+      <c r="E93" s="2">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>201</v>
       </c>
-      <c r="H93" s="1">
+      <c r="H93" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3899,7 +3925,7 @@
       <c r="C94" t="s">
         <v>123</v>
       </c>
-      <c r="H94" s="1">
+      <c r="H94" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3913,7 +3939,7 @@
       <c r="C95" t="s">
         <v>127</v>
       </c>
-      <c r="H95" s="1">
+      <c r="H95" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3930,13 +3956,13 @@
       <c r="D96" t="s">
         <v>133</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E96" s="2">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>195</v>
       </c>
-      <c r="H96" s="1">
+      <c r="H96" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3953,13 +3979,13 @@
       <c r="D97" t="s">
         <v>134</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E97" s="2">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>196</v>
       </c>
-      <c r="H97" s="1">
+      <c r="H97" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3973,7 +3999,7 @@
       <c r="C98" t="s">
         <v>123</v>
       </c>
-      <c r="H98" s="1">
+      <c r="H98" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -3990,13 +4016,13 @@
       <c r="D99" t="s">
         <v>151</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99" s="2">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>196</v>
       </c>
-      <c r="H99" s="1">
+      <c r="H99" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4013,13 +4039,13 @@
       <c r="D100" t="s">
         <v>135</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="2">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>196</v>
       </c>
-      <c r="H100" s="1">
+      <c r="H100" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4033,7 +4059,7 @@
       <c r="C101" t="s">
         <v>123</v>
       </c>
-      <c r="H101" s="1">
+      <c r="H101" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4050,13 +4076,13 @@
       <c r="D102" t="s">
         <v>136</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102" s="2">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>197</v>
       </c>
-      <c r="H102" s="1">
+      <c r="H102" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4073,13 +4099,13 @@
       <c r="D103" t="s">
         <v>152</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103" s="2">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>196</v>
       </c>
-      <c r="H103" s="1">
+      <c r="H103" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4093,7 +4119,7 @@
       <c r="C104" t="s">
         <v>123</v>
       </c>
-      <c r="H104" s="1">
+      <c r="H104" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4107,7 +4133,7 @@
       <c r="C105" t="s">
         <v>123</v>
       </c>
-      <c r="H105" s="1">
+      <c r="H105" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4121,7 +4147,7 @@
       <c r="C106" t="s">
         <v>123</v>
       </c>
-      <c r="H106" s="1">
+      <c r="H106" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4138,13 +4164,13 @@
       <c r="D107" t="s">
         <v>153</v>
       </c>
-      <c r="E107" s="1">
+      <c r="E107" s="2">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>196</v>
       </c>
-      <c r="H107" s="1">
+      <c r="H107" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4167,7 +4193,7 @@
       <c r="G108" t="s">
         <v>192</v>
       </c>
-      <c r="H108" s="1">
+      <c r="H108" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4181,7 +4207,7 @@
       <c r="C109" t="s">
         <v>127</v>
       </c>
-      <c r="H109" s="1">
+      <c r="H109" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4195,7 +4221,7 @@
       <c r="C110" t="s">
         <v>123</v>
       </c>
-      <c r="H110" s="1">
+      <c r="H110" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4218,7 +4244,7 @@
       <c r="G111" t="s">
         <v>187</v>
       </c>
-      <c r="H111" s="1">
+      <c r="H111" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4235,7 +4261,7 @@
       <c r="D112" t="s">
         <v>140</v>
       </c>
-      <c r="H112" s="1">
+      <c r="H112" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4258,7 +4284,7 @@
       <c r="G113" t="s">
         <v>188</v>
       </c>
-      <c r="H113" s="1">
+      <c r="H113" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4275,13 +4301,13 @@
       <c r="D114" t="s">
         <v>142</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114" s="2">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>199</v>
       </c>
-      <c r="H114" s="1">
+      <c r="H114" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4304,7 +4330,7 @@
       <c r="G115" t="s">
         <v>189</v>
       </c>
-      <c r="H115" s="1">
+      <c r="H115" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4327,7 +4353,7 @@
       <c r="G116" t="s">
         <v>189</v>
       </c>
-      <c r="H116" s="1">
+      <c r="H116" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4350,7 +4376,7 @@
       <c r="G117" t="s">
         <v>190</v>
       </c>
-      <c r="H117" s="1">
+      <c r="H117" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -4364,7 +4390,7 @@
       <c r="C118" t="s">
         <v>123</v>
       </c>
-      <c r="H118" s="1">
+      <c r="H118" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4381,13 +4407,13 @@
       <c r="D119" t="s">
         <v>150</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119" s="2">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>201</v>
       </c>
-      <c r="H119" s="1">
+      <c r="H119" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4401,7 +4427,7 @@
       <c r="C120" t="s">
         <v>127</v>
       </c>
-      <c r="H120" s="1">
+      <c r="H120" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4415,7 +4441,7 @@
       <c r="C121" t="s">
         <v>123</v>
       </c>
-      <c r="H121" s="1">
+      <c r="H121" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4429,7 +4455,7 @@
       <c r="C122" t="s">
         <v>127</v>
       </c>
-      <c r="H122" s="1">
+      <c r="H122" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4443,7 +4469,7 @@
       <c r="C123" t="s">
         <v>127</v>
       </c>
-      <c r="H123" s="1">
+      <c r="H123" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4457,7 +4483,7 @@
       <c r="C124" t="s">
         <v>127</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H124" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4474,13 +4500,13 @@
       <c r="D125" t="s">
         <v>133</v>
       </c>
-      <c r="E125" s="1">
+      <c r="E125" s="2">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>195</v>
       </c>
-      <c r="H125" s="1">
+      <c r="H125" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4497,13 +4523,13 @@
       <c r="D126" t="s">
         <v>134</v>
       </c>
-      <c r="E126" s="1">
+      <c r="E126" s="2">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>196</v>
       </c>
-      <c r="H126" s="1">
+      <c r="H126" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4517,7 +4543,7 @@
       <c r="C127" t="s">
         <v>123</v>
       </c>
-      <c r="H127" s="1">
+      <c r="H127" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4534,13 +4560,13 @@
       <c r="D128" t="s">
         <v>151</v>
       </c>
-      <c r="E128" s="1">
+      <c r="E128" s="2">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>196</v>
       </c>
-      <c r="H128" s="1">
+      <c r="H128" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4557,13 +4583,13 @@
       <c r="D129" t="s">
         <v>135</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E129" s="2">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>196</v>
       </c>
-      <c r="H129" s="1">
+      <c r="H129" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4577,7 +4603,7 @@
       <c r="C130" t="s">
         <v>123</v>
       </c>
-      <c r="H130" s="1">
+      <c r="H130" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4594,13 +4620,13 @@
       <c r="D131" t="s">
         <v>136</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E131" s="2">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>197</v>
       </c>
-      <c r="H131" s="1">
+      <c r="H131" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4617,13 +4643,13 @@
       <c r="D132" t="s">
         <v>152</v>
       </c>
-      <c r="E132" s="1">
+      <c r="E132" s="2">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>196</v>
       </c>
-      <c r="H132" s="1">
+      <c r="H132" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4637,7 +4663,7 @@
       <c r="C133" t="s">
         <v>123</v>
       </c>
-      <c r="H133" s="1">
+      <c r="H133" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4651,7 +4677,7 @@
       <c r="C134" t="s">
         <v>123</v>
       </c>
-      <c r="H134" s="1">
+      <c r="H134" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4665,7 +4691,7 @@
       <c r="C135" t="s">
         <v>123</v>
       </c>
-      <c r="H135" s="1">
+      <c r="H135" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4682,13 +4708,13 @@
       <c r="D136" t="s">
         <v>154</v>
       </c>
-      <c r="E136" s="1">
+      <c r="E136" s="2">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>196</v>
       </c>
-      <c r="H136" s="1">
+      <c r="H136" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4711,7 +4737,7 @@
       <c r="G137" t="s">
         <v>192</v>
       </c>
-      <c r="H137" s="1">
+      <c r="H137" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4725,7 +4751,7 @@
       <c r="C138" t="s">
         <v>127</v>
       </c>
-      <c r="H138" s="1">
+      <c r="H138" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4739,7 +4765,7 @@
       <c r="C139" t="s">
         <v>123</v>
       </c>
-      <c r="H139" s="1">
+      <c r="H139" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4762,7 +4788,7 @@
       <c r="G140" t="s">
         <v>187</v>
       </c>
-      <c r="H140" s="1">
+      <c r="H140" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4779,7 +4805,7 @@
       <c r="D141" t="s">
         <v>140</v>
       </c>
-      <c r="H141" s="1">
+      <c r="H141" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4802,7 +4828,7 @@
       <c r="G142" t="s">
         <v>188</v>
       </c>
-      <c r="H142" s="1">
+      <c r="H142" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4819,13 +4845,13 @@
       <c r="D143" t="s">
         <v>142</v>
       </c>
-      <c r="E143" s="1">
+      <c r="E143" s="2">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>199</v>
       </c>
-      <c r="H143" s="1">
+      <c r="H143" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4848,7 +4874,7 @@
       <c r="G144" t="s">
         <v>189</v>
       </c>
-      <c r="H144" s="1">
+      <c r="H144" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4871,7 +4897,7 @@
       <c r="G145" t="s">
         <v>189</v>
       </c>
-      <c r="H145" s="1">
+      <c r="H145" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4894,7 +4920,7 @@
       <c r="G146" t="s">
         <v>190</v>
       </c>
-      <c r="H146" s="1">
+      <c r="H146" s="2">
         <v>46211</v>
       </c>
     </row>
@@ -4908,7 +4934,7 @@
       <c r="C147" t="s">
         <v>123</v>
       </c>
-      <c r="H147" s="1">
+      <c r="H147" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4925,13 +4951,13 @@
       <c r="D148" t="s">
         <v>150</v>
       </c>
-      <c r="E148" s="1">
+      <c r="E148" s="2">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>201</v>
       </c>
-      <c r="H148" s="1">
+      <c r="H148" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4945,7 +4971,7 @@
       <c r="C149" t="s">
         <v>127</v>
       </c>
-      <c r="H149" s="1">
+      <c r="H149" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4959,7 +4985,7 @@
       <c r="C150" t="s">
         <v>123</v>
       </c>
-      <c r="H150" s="1">
+      <c r="H150" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4973,7 +4999,7 @@
       <c r="C151" t="s">
         <v>123</v>
       </c>
-      <c r="H151" s="1">
+      <c r="H151" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -4987,7 +5013,7 @@
       <c r="C152" t="s">
         <v>127</v>
       </c>
-      <c r="H152" s="1">
+      <c r="H152" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5001,7 +5027,7 @@
       <c r="C153" t="s">
         <v>127</v>
       </c>
-      <c r="H153" s="1">
+      <c r="H153" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5018,13 +5044,13 @@
       <c r="D154" t="s">
         <v>133</v>
       </c>
-      <c r="E154" s="1">
+      <c r="E154" s="2">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>195</v>
       </c>
-      <c r="H154" s="1">
+      <c r="H154" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5041,13 +5067,13 @@
       <c r="D155" t="s">
         <v>134</v>
       </c>
-      <c r="E155" s="1">
+      <c r="E155" s="2">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>196</v>
       </c>
-      <c r="H155" s="1">
+      <c r="H155" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5061,7 +5087,7 @@
       <c r="C156" t="s">
         <v>123</v>
       </c>
-      <c r="H156" s="1">
+      <c r="H156" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5078,13 +5104,13 @@
       <c r="D157" t="s">
         <v>151</v>
       </c>
-      <c r="E157" s="1">
+      <c r="E157" s="2">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>196</v>
       </c>
-      <c r="H157" s="1">
+      <c r="H157" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5101,13 +5127,13 @@
       <c r="D158" t="s">
         <v>135</v>
       </c>
-      <c r="E158" s="1">
+      <c r="E158" s="2">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>196</v>
       </c>
-      <c r="H158" s="1">
+      <c r="H158" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5124,13 +5150,13 @@
       <c r="D159" t="s">
         <v>155</v>
       </c>
-      <c r="E159" s="1">
+      <c r="E159" s="2">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>202</v>
       </c>
-      <c r="H159" s="1">
+      <c r="H159" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5147,13 +5173,13 @@
       <c r="D160" t="s">
         <v>136</v>
       </c>
-      <c r="E160" s="1">
+      <c r="E160" s="2">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>197</v>
       </c>
-      <c r="H160" s="1">
+      <c r="H160" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5170,13 +5196,13 @@
       <c r="D161" t="s">
         <v>152</v>
       </c>
-      <c r="E161" s="1">
+      <c r="E161" s="2">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>196</v>
       </c>
-      <c r="H161" s="1">
+      <c r="H161" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5190,7 +5216,7 @@
       <c r="C162" t="s">
         <v>123</v>
       </c>
-      <c r="H162" s="1">
+      <c r="H162" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5204,7 +5230,7 @@
       <c r="C163" t="s">
         <v>123</v>
       </c>
-      <c r="H163" s="1">
+      <c r="H163" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5218,7 +5244,7 @@
       <c r="C164" t="s">
         <v>123</v>
       </c>
-      <c r="H164" s="1">
+      <c r="H164" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5235,13 +5261,13 @@
       <c r="D165" t="s">
         <v>154</v>
       </c>
-      <c r="E165" s="1">
+      <c r="E165" s="2">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>196</v>
       </c>
-      <c r="H165" s="1">
+      <c r="H165" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5264,7 +5290,7 @@
       <c r="G166" t="s">
         <v>192</v>
       </c>
-      <c r="H166" s="1">
+      <c r="H166" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5278,7 +5304,7 @@
       <c r="C167" t="s">
         <v>127</v>
       </c>
-      <c r="H167" s="1">
+      <c r="H167" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5292,7 +5318,7 @@
       <c r="C168" t="s">
         <v>123</v>
       </c>
-      <c r="H168" s="1">
+      <c r="H168" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5315,7 +5341,7 @@
       <c r="G169" t="s">
         <v>187</v>
       </c>
-      <c r="H169" s="1">
+      <c r="H169" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5332,7 +5358,7 @@
       <c r="D170" t="s">
         <v>140</v>
       </c>
-      <c r="H170" s="1">
+      <c r="H170" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5355,7 +5381,7 @@
       <c r="G171" t="s">
         <v>188</v>
       </c>
-      <c r="H171" s="1">
+      <c r="H171" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5372,13 +5398,13 @@
       <c r="D172" t="s">
         <v>142</v>
       </c>
-      <c r="E172" s="1">
+      <c r="E172" s="2">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>199</v>
       </c>
-      <c r="H172" s="1">
+      <c r="H172" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5401,7 +5427,7 @@
       <c r="G173" t="s">
         <v>189</v>
       </c>
-      <c r="H173" s="1">
+      <c r="H173" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5424,7 +5450,7 @@
       <c r="G174" t="s">
         <v>189</v>
       </c>
-      <c r="H174" s="1">
+      <c r="H174" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5447,7 +5473,7 @@
       <c r="G175" t="s">
         <v>190</v>
       </c>
-      <c r="H175" s="1">
+      <c r="H175" s="2">
         <v>46212</v>
       </c>
     </row>
@@ -5461,7 +5487,7 @@
       <c r="C176" t="s">
         <v>123</v>
       </c>
-      <c r="H176" s="1">
+      <c r="H176" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5478,13 +5504,13 @@
       <c r="D177" t="s">
         <v>156</v>
       </c>
-      <c r="E177" s="1">
+      <c r="E177" s="2">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>201</v>
       </c>
-      <c r="H177" s="1">
+      <c r="H177" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5498,7 +5524,7 @@
       <c r="C178" t="s">
         <v>123</v>
       </c>
-      <c r="H178" s="1">
+      <c r="H178" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5515,13 +5541,13 @@
       <c r="D179" t="s">
         <v>157</v>
       </c>
-      <c r="E179" s="1">
+      <c r="E179" s="2">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>197</v>
       </c>
-      <c r="H179" s="1">
+      <c r="H179" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5535,7 +5561,7 @@
       <c r="C180" t="s">
         <v>123</v>
       </c>
-      <c r="H180" s="1">
+      <c r="H180" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5549,7 +5575,7 @@
       <c r="C181" t="s">
         <v>127</v>
       </c>
-      <c r="H181" s="1">
+      <c r="H181" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5563,7 +5589,7 @@
       <c r="C182" t="s">
         <v>127</v>
       </c>
-      <c r="H182" s="1">
+      <c r="H182" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5580,13 +5606,13 @@
       <c r="D183" t="s">
         <v>133</v>
       </c>
-      <c r="E183" s="1">
+      <c r="E183" s="2">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>195</v>
       </c>
-      <c r="H183" s="1">
+      <c r="H183" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5603,13 +5629,13 @@
       <c r="D184" t="s">
         <v>134</v>
       </c>
-      <c r="E184" s="1">
+      <c r="E184" s="2">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>196</v>
       </c>
-      <c r="H184" s="1">
+      <c r="H184" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5623,7 +5649,7 @@
       <c r="C185" t="s">
         <v>123</v>
       </c>
-      <c r="H185" s="1">
+      <c r="H185" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5640,13 +5666,13 @@
       <c r="D186" t="s">
         <v>151</v>
       </c>
-      <c r="E186" s="1">
+      <c r="E186" s="2">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>196</v>
       </c>
-      <c r="H186" s="1">
+      <c r="H186" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5663,13 +5689,13 @@
       <c r="D187" t="s">
         <v>158</v>
       </c>
-      <c r="E187" s="1">
+      <c r="E187" s="2">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>196</v>
       </c>
-      <c r="H187" s="1">
+      <c r="H187" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5686,13 +5712,13 @@
       <c r="D188" t="s">
         <v>159</v>
       </c>
-      <c r="E188" s="1">
+      <c r="E188" s="2">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>196</v>
       </c>
-      <c r="H188" s="1">
+      <c r="H188" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5709,13 +5735,13 @@
       <c r="D189" t="s">
         <v>136</v>
       </c>
-      <c r="E189" s="1">
+      <c r="E189" s="2">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>197</v>
       </c>
-      <c r="H189" s="1">
+      <c r="H189" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5732,13 +5758,13 @@
       <c r="D190" t="s">
         <v>152</v>
       </c>
-      <c r="E190" s="1">
+      <c r="E190" s="2">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>196</v>
       </c>
-      <c r="H190" s="1">
+      <c r="H190" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5752,7 +5778,7 @@
       <c r="C191" t="s">
         <v>123</v>
       </c>
-      <c r="H191" s="1">
+      <c r="H191" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5766,7 +5792,7 @@
       <c r="C192" t="s">
         <v>123</v>
       </c>
-      <c r="H192" s="1">
+      <c r="H192" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5780,7 +5806,7 @@
       <c r="C193" t="s">
         <v>123</v>
       </c>
-      <c r="H193" s="1">
+      <c r="H193" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5797,13 +5823,13 @@
       <c r="D194" t="s">
         <v>154</v>
       </c>
-      <c r="E194" s="1">
+      <c r="E194" s="2">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>203</v>
       </c>
-      <c r="H194" s="1">
+      <c r="H194" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5826,7 +5852,7 @@
       <c r="G195" t="s">
         <v>192</v>
       </c>
-      <c r="H195" s="1">
+      <c r="H195" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5840,7 +5866,7 @@
       <c r="C196" t="s">
         <v>127</v>
       </c>
-      <c r="H196" s="1">
+      <c r="H196" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5854,7 +5880,7 @@
       <c r="C197" t="s">
         <v>123</v>
       </c>
-      <c r="H197" s="1">
+      <c r="H197" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5877,7 +5903,7 @@
       <c r="G198" t="s">
         <v>187</v>
       </c>
-      <c r="H198" s="1">
+      <c r="H198" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5894,7 +5920,7 @@
       <c r="D199" t="s">
         <v>140</v>
       </c>
-      <c r="H199" s="1">
+      <c r="H199" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5917,7 +5943,7 @@
       <c r="G200" t="s">
         <v>188</v>
       </c>
-      <c r="H200" s="1">
+      <c r="H200" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5934,13 +5960,13 @@
       <c r="D201" t="s">
         <v>142</v>
       </c>
-      <c r="E201" s="1">
+      <c r="E201" s="2">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>199</v>
       </c>
-      <c r="H201" s="1">
+      <c r="H201" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5963,7 +5989,7 @@
       <c r="G202" t="s">
         <v>189</v>
       </c>
-      <c r="H202" s="1">
+      <c r="H202" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -5986,7 +6012,7 @@
       <c r="G203" t="s">
         <v>189</v>
       </c>
-      <c r="H203" s="1">
+      <c r="H203" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -6009,7 +6035,7 @@
       <c r="G204" t="s">
         <v>190</v>
       </c>
-      <c r="H204" s="1">
+      <c r="H204" s="2">
         <v>46213</v>
       </c>
     </row>
@@ -6023,7 +6049,7 @@
       <c r="C205" t="s">
         <v>123</v>
       </c>
-      <c r="H205" s="1">
+      <c r="H205" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6040,13 +6066,13 @@
       <c r="D206" t="s">
         <v>156</v>
       </c>
-      <c r="E206" s="1">
+      <c r="E206" s="2">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>201</v>
       </c>
-      <c r="H206" s="1">
+      <c r="H206" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6060,7 +6086,7 @@
       <c r="C207" t="s">
         <v>123</v>
       </c>
-      <c r="H207" s="1">
+      <c r="H207" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6074,7 +6100,7 @@
       <c r="C208" t="s">
         <v>127</v>
       </c>
-      <c r="H208" s="1">
+      <c r="H208" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6088,7 +6114,7 @@
       <c r="C209" t="s">
         <v>123</v>
       </c>
-      <c r="H209" s="1">
+      <c r="H209" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6102,7 +6128,7 @@
       <c r="C210" t="s">
         <v>127</v>
       </c>
-      <c r="H210" s="1">
+      <c r="H210" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6116,7 +6142,7 @@
       <c r="C211" t="s">
         <v>127</v>
       </c>
-      <c r="H211" s="1">
+      <c r="H211" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6133,13 +6159,13 @@
       <c r="D212" t="s">
         <v>133</v>
       </c>
-      <c r="E212" s="1">
+      <c r="E212" s="2">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>195</v>
       </c>
-      <c r="H212" s="1">
+      <c r="H212" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6153,7 +6179,7 @@
       <c r="C213" t="s">
         <v>127</v>
       </c>
-      <c r="H213" s="1">
+      <c r="H213" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6167,7 +6193,7 @@
       <c r="C214" t="s">
         <v>123</v>
       </c>
-      <c r="H214" s="1">
+      <c r="H214" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6184,13 +6210,13 @@
       <c r="D215" t="s">
         <v>151</v>
       </c>
-      <c r="E215" s="1">
+      <c r="E215" s="2">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>204</v>
       </c>
-      <c r="H215" s="1">
+      <c r="H215" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6207,13 +6233,13 @@
       <c r="D216" t="s">
         <v>158</v>
       </c>
-      <c r="E216" s="1">
+      <c r="E216" s="2">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>197</v>
       </c>
-      <c r="H216" s="1">
+      <c r="H216" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6227,7 +6253,7 @@
       <c r="C217" t="s">
         <v>123</v>
       </c>
-      <c r="H217" s="1">
+      <c r="H217" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6244,13 +6270,13 @@
       <c r="D218" t="s">
         <v>136</v>
       </c>
-      <c r="E218" s="1">
+      <c r="E218" s="2">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>197</v>
       </c>
-      <c r="H218" s="1">
+      <c r="H218" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6264,7 +6290,7 @@
       <c r="C219" t="s">
         <v>123</v>
       </c>
-      <c r="H219" s="1">
+      <c r="H219" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6278,7 +6304,7 @@
       <c r="C220" t="s">
         <v>123</v>
       </c>
-      <c r="H220" s="1">
+      <c r="H220" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6295,13 +6321,13 @@
       <c r="D221" t="s">
         <v>160</v>
       </c>
-      <c r="E221" s="1">
+      <c r="E221" s="2">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>201</v>
       </c>
-      <c r="H221" s="1">
+      <c r="H221" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6315,7 +6341,7 @@
       <c r="C222" t="s">
         <v>123</v>
       </c>
-      <c r="H222" s="1">
+      <c r="H222" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6332,13 +6358,13 @@
       <c r="D223" t="s">
         <v>161</v>
       </c>
-      <c r="E223" s="1">
+      <c r="E223" s="2">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>205</v>
       </c>
-      <c r="H223" s="1">
+      <c r="H223" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6361,7 +6387,7 @@
       <c r="G224" t="s">
         <v>192</v>
       </c>
-      <c r="H224" s="1">
+      <c r="H224" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6375,7 +6401,7 @@
       <c r="C225" t="s">
         <v>127</v>
       </c>
-      <c r="H225" s="1">
+      <c r="H225" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6389,7 +6415,7 @@
       <c r="C226" t="s">
         <v>123</v>
       </c>
-      <c r="H226" s="1">
+      <c r="H226" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6412,7 +6438,7 @@
       <c r="G227" t="s">
         <v>187</v>
       </c>
-      <c r="H227" s="1">
+      <c r="H227" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6429,7 +6455,7 @@
       <c r="D228" t="s">
         <v>140</v>
       </c>
-      <c r="H228" s="1">
+      <c r="H228" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6452,7 +6478,7 @@
       <c r="G229" t="s">
         <v>188</v>
       </c>
-      <c r="H229" s="1">
+      <c r="H229" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6469,13 +6495,13 @@
       <c r="D230" t="s">
         <v>162</v>
       </c>
-      <c r="E230" s="1">
+      <c r="E230" s="2">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>206</v>
       </c>
-      <c r="H230" s="1">
+      <c r="H230" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6498,7 +6524,7 @@
       <c r="G231" t="s">
         <v>189</v>
       </c>
-      <c r="H231" s="1">
+      <c r="H231" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6521,7 +6547,7 @@
       <c r="G232" t="s">
         <v>189</v>
       </c>
-      <c r="H232" s="1">
+      <c r="H232" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6544,7 +6570,7 @@
       <c r="G233" t="s">
         <v>190</v>
       </c>
-      <c r="H233" s="1">
+      <c r="H233" s="2">
         <v>46216</v>
       </c>
     </row>
@@ -6558,7 +6584,7 @@
       <c r="C234" t="s">
         <v>123</v>
       </c>
-      <c r="H234" s="1">
+      <c r="H234" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6575,13 +6601,13 @@
       <c r="D235" t="s">
         <v>163</v>
       </c>
-      <c r="E235" s="1">
+      <c r="E235" s="2">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>201</v>
       </c>
-      <c r="H235" s="1">
+      <c r="H235" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6595,7 +6621,7 @@
       <c r="C236" t="s">
         <v>123</v>
       </c>
-      <c r="H236" s="1">
+      <c r="H236" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6609,7 +6635,7 @@
       <c r="C237" t="s">
         <v>127</v>
       </c>
-      <c r="H237" s="1">
+      <c r="H237" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6623,7 +6649,7 @@
       <c r="C238" t="s">
         <v>123</v>
       </c>
-      <c r="H238" s="1">
+      <c r="H238" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6637,7 +6663,7 @@
       <c r="C239" t="s">
         <v>127</v>
       </c>
-      <c r="H239" s="1">
+      <c r="H239" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6651,7 +6677,7 @@
       <c r="C240" t="s">
         <v>127</v>
       </c>
-      <c r="H240" s="1">
+      <c r="H240" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6668,13 +6694,13 @@
       <c r="D241" t="s">
         <v>133</v>
       </c>
-      <c r="E241" s="1">
+      <c r="E241" s="2">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>195</v>
       </c>
-      <c r="H241" s="1">
+      <c r="H241" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6688,7 +6714,7 @@
       <c r="C242" t="s">
         <v>127</v>
       </c>
-      <c r="H242" s="1">
+      <c r="H242" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6705,13 +6731,13 @@
       <c r="D243" t="s">
         <v>164</v>
       </c>
-      <c r="E243" s="1">
+      <c r="E243" s="2">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>207</v>
       </c>
-      <c r="H243" s="1">
+      <c r="H243" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6728,13 +6754,13 @@
       <c r="D244" t="s">
         <v>165</v>
       </c>
-      <c r="E244" s="1">
+      <c r="E244" s="2">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>204</v>
       </c>
-      <c r="H244" s="1">
+      <c r="H244" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6748,7 +6774,7 @@
       <c r="C245" t="s">
         <v>127</v>
       </c>
-      <c r="H245" s="1">
+      <c r="H245" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6762,7 +6788,7 @@
       <c r="C246" t="s">
         <v>123</v>
       </c>
-      <c r="H246" s="1">
+      <c r="H246" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6779,13 +6805,13 @@
       <c r="D247" t="s">
         <v>136</v>
       </c>
-      <c r="E247" s="1">
+      <c r="E247" s="2">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>208</v>
       </c>
-      <c r="H247" s="1">
+      <c r="H247" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6799,7 +6825,7 @@
       <c r="C248" t="s">
         <v>123</v>
       </c>
-      <c r="H248" s="1">
+      <c r="H248" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6813,7 +6839,7 @@
       <c r="C249" t="s">
         <v>123</v>
       </c>
-      <c r="H249" s="1">
+      <c r="H249" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6830,13 +6856,13 @@
       <c r="D250" t="s">
         <v>166</v>
       </c>
-      <c r="E250" s="1">
+      <c r="E250" s="2">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>203</v>
       </c>
-      <c r="H250" s="1">
+      <c r="H250" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6850,7 +6876,7 @@
       <c r="C251" t="s">
         <v>123</v>
       </c>
-      <c r="H251" s="1">
+      <c r="H251" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6867,13 +6893,13 @@
       <c r="D252" t="s">
         <v>167</v>
       </c>
-      <c r="E252" s="1">
+      <c r="E252" s="2">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>205</v>
       </c>
-      <c r="H252" s="1">
+      <c r="H252" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6896,7 +6922,7 @@
       <c r="G253" t="s">
         <v>192</v>
       </c>
-      <c r="H253" s="1">
+      <c r="H253" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6910,7 +6936,7 @@
       <c r="C254" t="s">
         <v>127</v>
       </c>
-      <c r="H254" s="1">
+      <c r="H254" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6924,7 +6950,7 @@
       <c r="C255" t="s">
         <v>123</v>
       </c>
-      <c r="H255" s="1">
+      <c r="H255" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6947,7 +6973,7 @@
       <c r="G256" t="s">
         <v>187</v>
       </c>
-      <c r="H256" s="1">
+      <c r="H256" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6964,7 +6990,7 @@
       <c r="D257" t="s">
         <v>140</v>
       </c>
-      <c r="H257" s="1">
+      <c r="H257" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -6987,7 +7013,7 @@
       <c r="G258" t="s">
         <v>188</v>
       </c>
-      <c r="H258" s="1">
+      <c r="H258" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -7004,13 +7030,13 @@
       <c r="D259" t="s">
         <v>162</v>
       </c>
-      <c r="E259" s="1">
+      <c r="E259" s="2">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>206</v>
       </c>
-      <c r="H259" s="1">
+      <c r="H259" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -7033,7 +7059,7 @@
       <c r="G260" t="s">
         <v>189</v>
       </c>
-      <c r="H260" s="1">
+      <c r="H260" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -7056,7 +7082,7 @@
       <c r="G261" t="s">
         <v>189</v>
       </c>
-      <c r="H261" s="1">
+      <c r="H261" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -7079,7 +7105,7 @@
       <c r="G262" t="s">
         <v>190</v>
       </c>
-      <c r="H262" s="1">
+      <c r="H262" s="2">
         <v>46217</v>
       </c>
     </row>
@@ -7093,7 +7119,7 @@
       <c r="C263" t="s">
         <v>123</v>
       </c>
-      <c r="H263" s="1">
+      <c r="H263" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7110,13 +7136,13 @@
       <c r="D264" t="s">
         <v>163</v>
       </c>
-      <c r="E264" s="1">
+      <c r="E264" s="2">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>201</v>
       </c>
-      <c r="H264" s="1">
+      <c r="H264" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7130,7 +7156,7 @@
       <c r="C265" t="s">
         <v>123</v>
       </c>
-      <c r="H265" s="1">
+      <c r="H265" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7144,7 +7170,7 @@
       <c r="C266" t="s">
         <v>127</v>
       </c>
-      <c r="H266" s="1">
+      <c r="H266" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7158,7 +7184,7 @@
       <c r="C267" t="s">
         <v>123</v>
       </c>
-      <c r="H267" s="1">
+      <c r="H267" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7172,7 +7198,7 @@
       <c r="C268" t="s">
         <v>127</v>
       </c>
-      <c r="H268" s="1">
+      <c r="H268" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7186,7 +7212,7 @@
       <c r="C269" t="s">
         <v>127</v>
       </c>
-      <c r="H269" s="1">
+      <c r="H269" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7203,13 +7229,13 @@
       <c r="D270" t="s">
         <v>133</v>
       </c>
-      <c r="E270" s="1">
+      <c r="E270" s="2">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>195</v>
       </c>
-      <c r="H270" s="1">
+      <c r="H270" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7223,7 +7249,7 @@
       <c r="C271" t="s">
         <v>127</v>
       </c>
-      <c r="H271" s="1">
+      <c r="H271" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7240,13 +7266,13 @@
       <c r="D272" t="s">
         <v>164</v>
       </c>
-      <c r="E272" s="1">
+      <c r="E272" s="2">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>207</v>
       </c>
-      <c r="H272" s="1">
+      <c r="H272" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7263,13 +7289,13 @@
       <c r="D273" t="s">
         <v>165</v>
       </c>
-      <c r="E273" s="1">
+      <c r="E273" s="2">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>209</v>
       </c>
-      <c r="H273" s="1">
+      <c r="H273" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7283,7 +7309,7 @@
       <c r="C274" t="s">
         <v>123</v>
       </c>
-      <c r="H274" s="1">
+      <c r="H274" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7297,7 +7323,7 @@
       <c r="C275" t="s">
         <v>123</v>
       </c>
-      <c r="H275" s="1">
+      <c r="H275" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7314,13 +7340,13 @@
       <c r="D276" t="s">
         <v>136</v>
       </c>
-      <c r="E276" s="1">
+      <c r="E276" s="2">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>208</v>
       </c>
-      <c r="H276" s="1">
+      <c r="H276" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7334,7 +7360,7 @@
       <c r="C277" t="s">
         <v>123</v>
       </c>
-      <c r="H277" s="1">
+      <c r="H277" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7351,13 +7377,13 @@
       <c r="D278" t="s">
         <v>168</v>
       </c>
-      <c r="E278" s="1">
+      <c r="E278" s="2">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>210</v>
       </c>
-      <c r="H278" s="1">
+      <c r="H278" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7374,13 +7400,13 @@
       <c r="D279" t="s">
         <v>166</v>
       </c>
-      <c r="E279" s="1">
+      <c r="E279" s="2">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>209</v>
       </c>
-      <c r="H279" s="1">
+      <c r="H279" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7394,7 +7420,7 @@
       <c r="C280" t="s">
         <v>123</v>
       </c>
-      <c r="H280" s="1">
+      <c r="H280" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7411,13 +7437,13 @@
       <c r="D281" t="s">
         <v>169</v>
       </c>
-      <c r="E281" s="1">
+      <c r="E281" s="2">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>205</v>
       </c>
-      <c r="H281" s="1">
+      <c r="H281" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7440,7 +7466,7 @@
       <c r="G282" t="s">
         <v>192</v>
       </c>
-      <c r="H282" s="1">
+      <c r="H282" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7454,7 +7480,7 @@
       <c r="C283" t="s">
         <v>127</v>
       </c>
-      <c r="H283" s="1">
+      <c r="H283" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7468,7 +7494,7 @@
       <c r="C284" t="s">
         <v>123</v>
       </c>
-      <c r="H284" s="1">
+      <c r="H284" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7491,7 +7517,7 @@
       <c r="G285" t="s">
         <v>187</v>
       </c>
-      <c r="H285" s="1">
+      <c r="H285" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7508,7 +7534,7 @@
       <c r="D286" t="s">
         <v>140</v>
       </c>
-      <c r="H286" s="1">
+      <c r="H286" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7531,7 +7557,7 @@
       <c r="G287" t="s">
         <v>188</v>
       </c>
-      <c r="H287" s="1">
+      <c r="H287" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7548,13 +7574,13 @@
       <c r="D288" t="s">
         <v>162</v>
       </c>
-      <c r="E288" s="1">
+      <c r="E288" s="2">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>206</v>
       </c>
-      <c r="H288" s="1">
+      <c r="H288" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7577,7 +7603,7 @@
       <c r="G289" t="s">
         <v>189</v>
       </c>
-      <c r="H289" s="1">
+      <c r="H289" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7600,7 +7626,7 @@
       <c r="G290" t="s">
         <v>189</v>
       </c>
-      <c r="H290" s="1">
+      <c r="H290" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7623,7 +7649,7 @@
       <c r="G291" t="s">
         <v>190</v>
       </c>
-      <c r="H291" s="1">
+      <c r="H291" s="2">
         <v>46218</v>
       </c>
     </row>
@@ -7637,7 +7663,7 @@
       <c r="C292" t="s">
         <v>123</v>
       </c>
-      <c r="H292" s="1">
+      <c r="H292" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7654,13 +7680,13 @@
       <c r="D293" t="s">
         <v>163</v>
       </c>
-      <c r="E293" s="1">
+      <c r="E293" s="2">
         <v>46220</v>
       </c>
       <c r="G293" t="s">
         <v>211</v>
       </c>
-      <c r="H293" s="1">
+      <c r="H293" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7674,7 +7700,7 @@
       <c r="C294" t="s">
         <v>123</v>
       </c>
-      <c r="H294" s="1">
+      <c r="H294" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7697,7 +7723,7 @@
       <c r="G295" t="s">
         <v>193</v>
       </c>
-      <c r="H295" s="1">
+      <c r="H295" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7711,7 +7737,7 @@
       <c r="C296" t="s">
         <v>123</v>
       </c>
-      <c r="H296" s="1">
+      <c r="H296" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7725,7 +7751,7 @@
       <c r="C297" t="s">
         <v>127</v>
       </c>
-      <c r="H297" s="1">
+      <c r="H297" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7742,13 +7768,13 @@
       <c r="D298" t="s">
         <v>171</v>
       </c>
-      <c r="E298" s="1">
+      <c r="E298" s="2">
         <v>46223</v>
       </c>
       <c r="G298" t="s">
         <v>212</v>
       </c>
-      <c r="H298" s="1">
+      <c r="H298" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7765,13 +7791,13 @@
       <c r="D299" t="s">
         <v>133</v>
       </c>
-      <c r="E299" s="1">
+      <c r="E299" s="2">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>195</v>
       </c>
-      <c r="H299" s="1">
+      <c r="H299" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7785,7 +7811,7 @@
       <c r="C300" t="s">
         <v>123</v>
       </c>
-      <c r="H300" s="1">
+      <c r="H300" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7802,13 +7828,13 @@
       <c r="D301" t="s">
         <v>164</v>
       </c>
-      <c r="E301" s="1">
+      <c r="E301" s="2">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>207</v>
       </c>
-      <c r="H301" s="1">
+      <c r="H301" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7825,13 +7851,13 @@
       <c r="D302" t="s">
         <v>165</v>
       </c>
-      <c r="E302" s="1">
+      <c r="E302" s="2">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>204</v>
       </c>
-      <c r="H302" s="1">
+      <c r="H302" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7845,7 +7871,7 @@
       <c r="C303" t="s">
         <v>123</v>
       </c>
-      <c r="H303" s="1">
+      <c r="H303" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7859,7 +7885,7 @@
       <c r="C304" t="s">
         <v>123</v>
       </c>
-      <c r="H304" s="1">
+      <c r="H304" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7876,13 +7902,13 @@
       <c r="D305" t="s">
         <v>136</v>
       </c>
-      <c r="E305" s="1">
+      <c r="E305" s="2">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>208</v>
       </c>
-      <c r="H305" s="1">
+      <c r="H305" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7896,7 +7922,7 @@
       <c r="C306" t="s">
         <v>123</v>
       </c>
-      <c r="H306" s="1">
+      <c r="H306" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7913,13 +7939,13 @@
       <c r="D307" t="s">
         <v>168</v>
       </c>
-      <c r="E307" s="1">
+      <c r="E307" s="2">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>210</v>
       </c>
-      <c r="H307" s="1">
+      <c r="H307" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7933,7 +7959,7 @@
       <c r="C308" t="s">
         <v>127</v>
       </c>
-      <c r="H308" s="1">
+      <c r="H308" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7950,13 +7976,13 @@
       <c r="D309" t="s">
         <v>172</v>
       </c>
-      <c r="E309" s="1">
+      <c r="E309" s="2">
         <v>46220</v>
       </c>
       <c r="G309" t="s">
         <v>211</v>
       </c>
-      <c r="H309" s="1">
+      <c r="H309" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7973,13 +7999,13 @@
       <c r="D310" t="s">
         <v>173</v>
       </c>
-      <c r="E310" s="1">
+      <c r="E310" s="2">
         <v>46265</v>
       </c>
       <c r="G310" t="s">
         <v>213</v>
       </c>
-      <c r="H310" s="1">
+      <c r="H310" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -7996,7 +8022,7 @@
       <c r="D311" t="s">
         <v>174</v>
       </c>
-      <c r="H311" s="1">
+      <c r="H311" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8010,7 +8036,7 @@
       <c r="C312" t="s">
         <v>127</v>
       </c>
-      <c r="H312" s="1">
+      <c r="H312" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8024,7 +8050,7 @@
       <c r="C313" t="s">
         <v>123</v>
       </c>
-      <c r="H313" s="1">
+      <c r="H313" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8047,7 +8073,7 @@
       <c r="G314" t="s">
         <v>187</v>
       </c>
-      <c r="H314" s="1">
+      <c r="H314" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8064,7 +8090,7 @@
       <c r="D315" t="s">
         <v>140</v>
       </c>
-      <c r="H315" s="1">
+      <c r="H315" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8087,7 +8113,7 @@
       <c r="G316" t="s">
         <v>188</v>
       </c>
-      <c r="H316" s="1">
+      <c r="H316" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8104,13 +8130,13 @@
       <c r="D317" t="s">
         <v>162</v>
       </c>
-      <c r="E317" s="1">
+      <c r="E317" s="2">
         <v>46295</v>
       </c>
       <c r="G317" t="s">
         <v>214</v>
       </c>
-      <c r="H317" s="1">
+      <c r="H317" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8133,7 +8159,7 @@
       <c r="G318" t="s">
         <v>189</v>
       </c>
-      <c r="H318" s="1">
+      <c r="H318" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8156,7 +8182,7 @@
       <c r="G319" t="s">
         <v>189</v>
       </c>
-      <c r="H319" s="1">
+      <c r="H319" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8179,7 +8205,7 @@
       <c r="G320" t="s">
         <v>190</v>
       </c>
-      <c r="H320" s="1">
+      <c r="H320" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -8193,7 +8219,7 @@
       <c r="C321" t="s">
         <v>123</v>
       </c>
-      <c r="H321" s="1">
+      <c r="H321" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8210,13 +8236,13 @@
       <c r="D322" t="s">
         <v>163</v>
       </c>
-      <c r="E322" s="1">
+      <c r="E322" s="2">
         <v>46225</v>
       </c>
       <c r="G322" t="s">
         <v>215</v>
       </c>
-      <c r="H322" s="1">
+      <c r="H322" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8230,7 +8256,7 @@
       <c r="C323" t="s">
         <v>123</v>
       </c>
-      <c r="H323" s="1">
+      <c r="H323" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8247,13 +8273,13 @@
       <c r="D324" t="s">
         <v>175</v>
       </c>
-      <c r="E324" s="1">
+      <c r="E324" s="2">
         <v>46224</v>
       </c>
       <c r="G324" t="s">
         <v>216</v>
       </c>
-      <c r="H324" s="1">
+      <c r="H324" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8267,7 +8293,7 @@
       <c r="C325" t="s">
         <v>123</v>
       </c>
-      <c r="H325" s="1">
+      <c r="H325" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8281,7 +8307,7 @@
       <c r="C326" t="s">
         <v>127</v>
       </c>
-      <c r="H326" s="1">
+      <c r="H326" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8295,7 +8321,7 @@
       <c r="C327" t="s">
         <v>127</v>
       </c>
-      <c r="H327" s="1">
+      <c r="H327" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8312,13 +8338,13 @@
       <c r="D328" t="s">
         <v>133</v>
       </c>
-      <c r="E328" s="1">
+      <c r="E328" s="2">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>195</v>
       </c>
-      <c r="H328" s="1">
+      <c r="H328" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8335,13 +8361,13 @@
       <c r="D329" t="s">
         <v>176</v>
       </c>
-      <c r="E329" s="1">
+      <c r="E329" s="2">
         <v>46224</v>
       </c>
       <c r="G329" t="s">
         <v>216</v>
       </c>
-      <c r="H329" s="1">
+      <c r="H329" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8358,13 +8384,13 @@
       <c r="D330" t="s">
         <v>164</v>
       </c>
-      <c r="E330" s="1">
+      <c r="E330" s="2">
         <v>46224</v>
       </c>
       <c r="G330" t="s">
         <v>216</v>
       </c>
-      <c r="H330" s="1">
+      <c r="H330" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8378,7 +8404,7 @@
       <c r="C331" t="s">
         <v>123</v>
       </c>
-      <c r="H331" s="1">
+      <c r="H331" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8395,13 +8421,13 @@
       <c r="D332" t="s">
         <v>177</v>
       </c>
-      <c r="E332" s="1">
+      <c r="E332" s="2">
         <v>46224</v>
       </c>
       <c r="G332" t="s">
         <v>216</v>
       </c>
-      <c r="H332" s="1">
+      <c r="H332" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8418,13 +8444,13 @@
       <c r="D333" t="s">
         <v>178</v>
       </c>
-      <c r="E333" s="1">
+      <c r="E333" s="2">
         <v>46225</v>
       </c>
       <c r="G333" t="s">
         <v>215</v>
       </c>
-      <c r="H333" s="1">
+      <c r="H333" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8441,13 +8467,13 @@
       <c r="D334" t="s">
         <v>136</v>
       </c>
-      <c r="E334" s="1">
+      <c r="E334" s="2">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>208</v>
       </c>
-      <c r="H334" s="1">
+      <c r="H334" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8461,7 +8487,7 @@
       <c r="C335" t="s">
         <v>123</v>
       </c>
-      <c r="H335" s="1">
+      <c r="H335" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8478,13 +8504,13 @@
       <c r="D336" t="s">
         <v>168</v>
       </c>
-      <c r="E336" s="1">
+      <c r="E336" s="2">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>210</v>
       </c>
-      <c r="H336" s="1">
+      <c r="H336" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8498,7 +8524,7 @@
       <c r="C337" t="s">
         <v>123</v>
       </c>
-      <c r="H337" s="1">
+      <c r="H337" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8512,7 +8538,7 @@
       <c r="C338" t="s">
         <v>123</v>
       </c>
-      <c r="H338" s="1">
+      <c r="H338" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8529,13 +8555,13 @@
       <c r="D339" t="s">
         <v>173</v>
       </c>
-      <c r="E339" s="1">
+      <c r="E339" s="2">
         <v>46265</v>
       </c>
       <c r="G339" t="s">
         <v>213</v>
       </c>
-      <c r="H339" s="1">
+      <c r="H339" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8552,7 +8578,7 @@
       <c r="D340" t="s">
         <v>179</v>
       </c>
-      <c r="H340" s="1">
+      <c r="H340" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8566,7 +8592,7 @@
       <c r="C341" t="s">
         <v>127</v>
       </c>
-      <c r="H341" s="1">
+      <c r="H341" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8580,7 +8606,7 @@
       <c r="C342" t="s">
         <v>123</v>
       </c>
-      <c r="H342" s="1">
+      <c r="H342" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8603,7 +8629,7 @@
       <c r="G343" t="s">
         <v>187</v>
       </c>
-      <c r="H343" s="1">
+      <c r="H343" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8620,7 +8646,7 @@
       <c r="D344" t="s">
         <v>140</v>
       </c>
-      <c r="H344" s="1">
+      <c r="H344" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8643,7 +8669,7 @@
       <c r="G345" t="s">
         <v>188</v>
       </c>
-      <c r="H345" s="1">
+      <c r="H345" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8660,13 +8686,13 @@
       <c r="D346" t="s">
         <v>162</v>
       </c>
-      <c r="E346" s="1">
+      <c r="E346" s="2">
         <v>46295</v>
       </c>
       <c r="G346" t="s">
         <v>214</v>
       </c>
-      <c r="H346" s="1">
+      <c r="H346" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8689,7 +8715,7 @@
       <c r="G347" t="s">
         <v>189</v>
       </c>
-      <c r="H347" s="1">
+      <c r="H347" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8712,7 +8738,7 @@
       <c r="G348" t="s">
         <v>189</v>
       </c>
-      <c r="H348" s="1">
+      <c r="H348" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8735,7 +8761,7 @@
       <c r="G349" t="s">
         <v>190</v>
       </c>
-      <c r="H349" s="1">
+      <c r="H349" s="2">
         <v>46224</v>
       </c>
     </row>
@@ -8749,7 +8775,7 @@
       <c r="C350" t="s">
         <v>123</v>
       </c>
-      <c r="H350" s="1">
+      <c r="H350" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8766,13 +8792,13 @@
       <c r="D351" t="s">
         <v>163</v>
       </c>
-      <c r="E351" s="1">
+      <c r="E351" s="2">
         <v>46225</v>
       </c>
       <c r="G351" t="s">
         <v>215</v>
       </c>
-      <c r="H351" s="1">
+      <c r="H351" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8786,7 +8812,7 @@
       <c r="C352" t="s">
         <v>123</v>
       </c>
-      <c r="H352" s="1">
+      <c r="H352" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8800,7 +8826,7 @@
       <c r="C353" t="s">
         <v>123</v>
       </c>
-      <c r="H353" s="1">
+      <c r="H353" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8814,7 +8840,7 @@
       <c r="C354" t="s">
         <v>123</v>
       </c>
-      <c r="H354" s="1">
+      <c r="H354" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8828,7 +8854,7 @@
       <c r="C355" t="s">
         <v>127</v>
       </c>
-      <c r="H355" s="1">
+      <c r="H355" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8842,7 +8868,7 @@
       <c r="C356" t="s">
         <v>127</v>
       </c>
-      <c r="H356" s="1">
+      <c r="H356" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8859,13 +8885,13 @@
       <c r="D357" t="s">
         <v>133</v>
       </c>
-      <c r="E357" s="1">
+      <c r="E357" s="2">
         <v>46234</v>
       </c>
       <c r="G357" t="s">
         <v>217</v>
       </c>
-      <c r="H357" s="1">
+      <c r="H357" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8879,7 +8905,7 @@
       <c r="C358" t="s">
         <v>123</v>
       </c>
-      <c r="H358" s="1">
+      <c r="H358" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8896,13 +8922,13 @@
       <c r="D359" t="s">
         <v>164</v>
       </c>
-      <c r="E359" s="1">
+      <c r="E359" s="2">
         <v>46227</v>
       </c>
       <c r="G359" t="s">
         <v>218</v>
       </c>
-      <c r="H359" s="1">
+      <c r="H359" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8916,7 +8942,7 @@
       <c r="C360" t="s">
         <v>123</v>
       </c>
-      <c r="H360" s="1">
+      <c r="H360" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8930,7 +8956,7 @@
       <c r="C361" t="s">
         <v>123</v>
       </c>
-      <c r="H361" s="1">
+      <c r="H361" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8947,13 +8973,13 @@
       <c r="D362" t="s">
         <v>178</v>
       </c>
-      <c r="E362" s="1">
+      <c r="E362" s="2">
         <v>46225</v>
       </c>
       <c r="G362" t="s">
         <v>215</v>
       </c>
-      <c r="H362" s="1">
+      <c r="H362" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8970,13 +8996,13 @@
       <c r="D363" t="s">
         <v>136</v>
       </c>
-      <c r="E363" s="1">
+      <c r="E363" s="2">
         <v>46237</v>
       </c>
       <c r="G363" t="s">
         <v>219</v>
       </c>
-      <c r="H363" s="1">
+      <c r="H363" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -8990,7 +9016,7 @@
       <c r="C364" t="s">
         <v>123</v>
       </c>
-      <c r="H364" s="1">
+      <c r="H364" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9007,13 +9033,13 @@
       <c r="D365" t="s">
         <v>168</v>
       </c>
-      <c r="E365" s="1">
+      <c r="E365" s="2">
         <v>46227</v>
       </c>
       <c r="G365" t="s">
         <v>218</v>
       </c>
-      <c r="H365" s="1">
+      <c r="H365" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9027,7 +9053,7 @@
       <c r="C366" t="s">
         <v>123</v>
       </c>
-      <c r="H366" s="1">
+      <c r="H366" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9041,7 +9067,7 @@
       <c r="C367" t="s">
         <v>123</v>
       </c>
-      <c r="H367" s="1">
+      <c r="H367" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9058,13 +9084,13 @@
       <c r="D368" t="s">
         <v>173</v>
       </c>
-      <c r="E368" s="1">
+      <c r="E368" s="2">
         <v>46234</v>
       </c>
       <c r="G368" t="s">
         <v>217</v>
       </c>
-      <c r="H368" s="1">
+      <c r="H368" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9081,13 +9107,13 @@
       <c r="D369" t="s">
         <v>180</v>
       </c>
-      <c r="E369" s="1">
+      <c r="E369" s="2">
         <v>46227</v>
       </c>
       <c r="G369" t="s">
         <v>218</v>
       </c>
-      <c r="H369" s="1">
+      <c r="H369" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9104,7 +9130,7 @@
       <c r="D370" t="s">
         <v>179</v>
       </c>
-      <c r="H370" s="1">
+      <c r="H370" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9118,7 +9144,7 @@
       <c r="C371" t="s">
         <v>123</v>
       </c>
-      <c r="H371" s="1">
+      <c r="H371" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9141,7 +9167,7 @@
       <c r="G372" t="s">
         <v>187</v>
       </c>
-      <c r="H372" s="1">
+      <c r="H372" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9158,7 +9184,7 @@
       <c r="D373" t="s">
         <v>140</v>
       </c>
-      <c r="H373" s="1">
+      <c r="H373" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9181,7 +9207,7 @@
       <c r="G374" t="s">
         <v>188</v>
       </c>
-      <c r="H374" s="1">
+      <c r="H374" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9198,13 +9224,13 @@
       <c r="D375" t="s">
         <v>162</v>
       </c>
-      <c r="E375" s="1">
+      <c r="E375" s="2">
         <v>46295</v>
       </c>
       <c r="G375" t="s">
         <v>214</v>
       </c>
-      <c r="H375" s="1">
+      <c r="H375" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9227,7 +9253,7 @@
       <c r="G376" t="s">
         <v>189</v>
       </c>
-      <c r="H376" s="1">
+      <c r="H376" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9250,7 +9276,7 @@
       <c r="G377" t="s">
         <v>189</v>
       </c>
-      <c r="H377" s="1">
+      <c r="H377" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9273,7 +9299,7 @@
       <c r="G378" t="s">
         <v>190</v>
       </c>
-      <c r="H378" s="1">
+      <c r="H378" s="2">
         <v>46225</v>
       </c>
     </row>
@@ -9287,7 +9313,7 @@
       <c r="C379" t="s">
         <v>123</v>
       </c>
-      <c r="H379" s="1">
+      <c r="H379" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9304,13 +9330,13 @@
       <c r="D380" t="s">
         <v>163</v>
       </c>
-      <c r="E380" s="1">
+      <c r="E380" s="2">
         <v>46227</v>
       </c>
       <c r="G380" t="s">
         <v>218</v>
       </c>
-      <c r="H380" s="1">
+      <c r="H380" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9324,7 +9350,7 @@
       <c r="C381" t="s">
         <v>123</v>
       </c>
-      <c r="H381" s="1">
+      <c r="H381" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9338,7 +9364,7 @@
       <c r="C382" t="s">
         <v>123</v>
       </c>
-      <c r="H382" s="1">
+      <c r="H382" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9352,7 +9378,7 @@
       <c r="C383" t="s">
         <v>123</v>
       </c>
-      <c r="H383" s="1">
+      <c r="H383" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9366,7 +9392,7 @@
       <c r="C384" t="s">
         <v>127</v>
       </c>
-      <c r="H384" s="1">
+      <c r="H384" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9380,7 +9406,7 @@
       <c r="C385" t="s">
         <v>127</v>
       </c>
-      <c r="H385" s="1">
+      <c r="H385" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9397,13 +9423,13 @@
       <c r="D386" t="s">
         <v>133</v>
       </c>
-      <c r="E386" s="1">
+      <c r="E386" s="2">
         <v>46234</v>
       </c>
       <c r="G386" t="s">
         <v>217</v>
       </c>
-      <c r="H386" s="1">
+      <c r="H386" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9417,7 +9443,7 @@
       <c r="C387" t="s">
         <v>123</v>
       </c>
-      <c r="H387" s="1">
+      <c r="H387" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9431,7 +9457,7 @@
       <c r="C388" t="s">
         <v>127</v>
       </c>
-      <c r="H388" s="1">
+      <c r="H388" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9445,7 +9471,7 @@
       <c r="C389" t="s">
         <v>123</v>
       </c>
-      <c r="H389" s="1">
+      <c r="H389" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9459,7 +9485,7 @@
       <c r="C390" t="s">
         <v>123</v>
       </c>
-      <c r="H390" s="1">
+      <c r="H390" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9476,13 +9502,13 @@
       <c r="D391" t="s">
         <v>181</v>
       </c>
-      <c r="E391" s="1">
+      <c r="E391" s="2">
         <v>46227</v>
       </c>
       <c r="G391" t="s">
         <v>218</v>
       </c>
-      <c r="H391" s="1">
+      <c r="H391" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9499,13 +9525,13 @@
       <c r="D392" t="s">
         <v>136</v>
       </c>
-      <c r="E392" s="1">
+      <c r="E392" s="2">
         <v>46237</v>
       </c>
       <c r="G392" t="s">
         <v>219</v>
       </c>
-      <c r="H392" s="1">
+      <c r="H392" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9519,7 +9545,7 @@
       <c r="C393" t="s">
         <v>123</v>
       </c>
-      <c r="H393" s="1">
+      <c r="H393" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9536,13 +9562,13 @@
       <c r="D394" t="s">
         <v>168</v>
       </c>
-      <c r="E394" s="1">
+      <c r="E394" s="2">
         <v>46227</v>
       </c>
       <c r="G394" t="s">
         <v>218</v>
       </c>
-      <c r="H394" s="1">
+      <c r="H394" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9556,7 +9582,7 @@
       <c r="C395" t="s">
         <v>123</v>
       </c>
-      <c r="H395" s="1">
+      <c r="H395" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9570,7 +9596,7 @@
       <c r="C396" t="s">
         <v>123</v>
       </c>
-      <c r="H396" s="1">
+      <c r="H396" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9587,13 +9613,13 @@
       <c r="D397" t="s">
         <v>173</v>
       </c>
-      <c r="E397" s="1">
+      <c r="E397" s="2">
         <v>46234</v>
       </c>
       <c r="G397" t="s">
         <v>217</v>
       </c>
-      <c r="H397" s="1">
+      <c r="H397" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9610,13 +9636,13 @@
       <c r="D398" t="s">
         <v>180</v>
       </c>
-      <c r="E398" s="1">
+      <c r="E398" s="2">
         <v>46227</v>
       </c>
       <c r="G398" t="s">
         <v>218</v>
       </c>
-      <c r="H398" s="1">
+      <c r="H398" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9633,7 +9659,7 @@
       <c r="D399" t="s">
         <v>179</v>
       </c>
-      <c r="H399" s="1">
+      <c r="H399" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9647,7 +9673,7 @@
       <c r="C400" t="s">
         <v>123</v>
       </c>
-      <c r="H400" s="1">
+      <c r="H400" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9670,7 +9696,7 @@
       <c r="G401" t="s">
         <v>187</v>
       </c>
-      <c r="H401" s="1">
+      <c r="H401" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9687,7 +9713,7 @@
       <c r="D402" t="s">
         <v>140</v>
       </c>
-      <c r="H402" s="1">
+      <c r="H402" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9710,7 +9736,7 @@
       <c r="G403" t="s">
         <v>188</v>
       </c>
-      <c r="H403" s="1">
+      <c r="H403" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9727,13 +9753,13 @@
       <c r="D404" t="s">
         <v>162</v>
       </c>
-      <c r="E404" s="1">
+      <c r="E404" s="2">
         <v>46295</v>
       </c>
       <c r="G404" t="s">
         <v>214</v>
       </c>
-      <c r="H404" s="1">
+      <c r="H404" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9756,7 +9782,7 @@
       <c r="G405" t="s">
         <v>189</v>
       </c>
-      <c r="H405" s="1">
+      <c r="H405" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9779,7 +9805,7 @@
       <c r="G406" t="s">
         <v>189</v>
       </c>
-      <c r="H406" s="1">
+      <c r="H406" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9802,7 +9828,7 @@
       <c r="G407" t="s">
         <v>190</v>
       </c>
-      <c r="H407" s="1">
+      <c r="H407" s="2">
         <v>46226</v>
       </c>
     </row>
@@ -9816,7 +9842,7 @@
       <c r="C408" t="s">
         <v>123</v>
       </c>
-      <c r="H408" s="1">
+      <c r="H408" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9833,13 +9859,13 @@
       <c r="D409" t="s">
         <v>150</v>
       </c>
-      <c r="E409" s="1">
+      <c r="E409" s="2">
         <v>46231</v>
       </c>
       <c r="G409" t="s">
         <v>220</v>
       </c>
-      <c r="H409" s="1">
+      <c r="H409" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9853,7 +9879,7 @@
       <c r="C410" t="s">
         <v>123</v>
       </c>
-      <c r="H410" s="1">
+      <c r="H410" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9867,7 +9893,7 @@
       <c r="C411" t="s">
         <v>123</v>
       </c>
-      <c r="H411" s="1">
+      <c r="H411" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9881,7 +9907,7 @@
       <c r="C412" t="s">
         <v>123</v>
       </c>
-      <c r="H412" s="1">
+      <c r="H412" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9895,7 +9921,7 @@
       <c r="C413" t="s">
         <v>127</v>
       </c>
-      <c r="H413" s="1">
+      <c r="H413" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9909,7 +9935,7 @@
       <c r="C414" t="s">
         <v>127</v>
       </c>
-      <c r="H414" s="1">
+      <c r="H414" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9926,13 +9952,13 @@
       <c r="D415" t="s">
         <v>182</v>
       </c>
-      <c r="E415" s="1">
+      <c r="E415" s="2">
         <v>46234</v>
       </c>
       <c r="G415" t="s">
         <v>217</v>
       </c>
-      <c r="H415" s="1">
+      <c r="H415" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9946,7 +9972,7 @@
       <c r="C416" t="s">
         <v>123</v>
       </c>
-      <c r="H416" s="1">
+      <c r="H416" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9960,7 +9986,7 @@
       <c r="C417" t="s">
         <v>127</v>
       </c>
-      <c r="H417" s="1">
+      <c r="H417" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9974,7 +10000,7 @@
       <c r="C418" t="s">
         <v>123</v>
       </c>
-      <c r="H418" s="1">
+      <c r="H418" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -9988,7 +10014,7 @@
       <c r="C419" t="s">
         <v>123</v>
       </c>
-      <c r="H419" s="1">
+      <c r="H419" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10005,13 +10031,13 @@
       <c r="D420" t="s">
         <v>136</v>
       </c>
-      <c r="E420" s="1">
+      <c r="E420" s="2">
         <v>46237</v>
       </c>
       <c r="G420" t="s">
         <v>219</v>
       </c>
-      <c r="H420" s="1">
+      <c r="H420" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10025,7 +10051,7 @@
       <c r="C421" t="s">
         <v>123</v>
       </c>
-      <c r="H421" s="1">
+      <c r="H421" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10042,13 +10068,13 @@
       <c r="D422" t="s">
         <v>168</v>
       </c>
-      <c r="E422" s="1">
+      <c r="E422" s="2">
         <v>46227</v>
       </c>
       <c r="G422" t="s">
         <v>218</v>
       </c>
-      <c r="H422" s="1">
+      <c r="H422" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10062,7 +10088,7 @@
       <c r="C423" t="s">
         <v>123</v>
       </c>
-      <c r="H423" s="1">
+      <c r="H423" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10076,7 +10102,7 @@
       <c r="C424" t="s">
         <v>123</v>
       </c>
-      <c r="H424" s="1">
+      <c r="H424" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10093,13 +10119,13 @@
       <c r="D425" t="s">
         <v>173</v>
       </c>
-      <c r="E425" s="1">
+      <c r="E425" s="2">
         <v>46234</v>
       </c>
       <c r="G425" t="s">
         <v>217</v>
       </c>
-      <c r="H425" s="1">
+      <c r="H425" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10116,13 +10142,13 @@
       <c r="D426" t="s">
         <v>180</v>
       </c>
-      <c r="E426" s="1">
+      <c r="E426" s="2">
         <v>46227</v>
       </c>
       <c r="G426" t="s">
         <v>218</v>
       </c>
-      <c r="H426" s="1">
+      <c r="H426" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10139,7 +10165,7 @@
       <c r="D427" t="s">
         <v>179</v>
       </c>
-      <c r="H427" s="1">
+      <c r="H427" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10153,7 +10179,7 @@
       <c r="C428" t="s">
         <v>123</v>
       </c>
-      <c r="H428" s="1">
+      <c r="H428" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10176,7 +10202,7 @@
       <c r="G429" t="s">
         <v>187</v>
       </c>
-      <c r="H429" s="1">
+      <c r="H429" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10193,7 +10219,7 @@
       <c r="D430" t="s">
         <v>140</v>
       </c>
-      <c r="H430" s="1">
+      <c r="H430" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10216,7 +10242,7 @@
       <c r="G431" t="s">
         <v>188</v>
       </c>
-      <c r="H431" s="1">
+      <c r="H431" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10233,13 +10259,13 @@
       <c r="D432" t="s">
         <v>162</v>
       </c>
-      <c r="E432" s="1">
+      <c r="E432" s="2">
         <v>46295</v>
       </c>
       <c r="G432" t="s">
         <v>214</v>
       </c>
-      <c r="H432" s="1">
+      <c r="H432" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10262,7 +10288,7 @@
       <c r="G433" t="s">
         <v>189</v>
       </c>
-      <c r="H433" s="1">
+      <c r="H433" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10285,7 +10311,7 @@
       <c r="G434" t="s">
         <v>189</v>
       </c>
-      <c r="H434" s="1">
+      <c r="H434" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10308,7 +10334,7 @@
       <c r="G435" t="s">
         <v>190</v>
       </c>
-      <c r="H435" s="1">
+      <c r="H435" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10325,13 +10351,13 @@
       <c r="D436" t="s">
         <v>183</v>
       </c>
-      <c r="E436" s="1">
+      <c r="E436" s="2">
         <v>46230</v>
       </c>
       <c r="G436" t="s">
         <v>221</v>
       </c>
-      <c r="H436" s="1">
+      <c r="H436" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -10345,7 +10371,7 @@
       <c r="C437" t="s">
         <v>123</v>
       </c>
-      <c r="H437" s="1">
+      <c r="H437" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10362,13 +10388,13 @@
       <c r="D438" t="s">
         <v>150</v>
       </c>
-      <c r="E438" s="1">
+      <c r="E438" s="2">
         <v>46231</v>
       </c>
       <c r="G438" t="s">
         <v>220</v>
       </c>
-      <c r="H438" s="1">
+      <c r="H438" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10382,7 +10408,7 @@
       <c r="C439" t="s">
         <v>123</v>
       </c>
-      <c r="H439" s="1">
+      <c r="H439" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10396,7 +10422,7 @@
       <c r="C440" t="s">
         <v>123</v>
       </c>
-      <c r="H440" s="1">
+      <c r="H440" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10410,7 +10436,7 @@
       <c r="C441" t="s">
         <v>123</v>
       </c>
-      <c r="H441" s="1">
+      <c r="H441" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10424,7 +10450,7 @@
       <c r="C442" t="s">
         <v>127</v>
       </c>
-      <c r="H442" s="1">
+      <c r="H442" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10438,7 +10464,7 @@
       <c r="C443" t="s">
         <v>127</v>
       </c>
-      <c r="H443" s="1">
+      <c r="H443" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10455,13 +10481,13 @@
       <c r="D444" t="s">
         <v>182</v>
       </c>
-      <c r="E444" s="1">
+      <c r="E444" s="2">
         <v>46234</v>
       </c>
       <c r="G444" t="s">
         <v>217</v>
       </c>
-      <c r="H444" s="1">
+      <c r="H444" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10475,7 +10501,7 @@
       <c r="C445" t="s">
         <v>123</v>
       </c>
-      <c r="H445" s="1">
+      <c r="H445" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10492,13 +10518,13 @@
       <c r="D446" t="s">
         <v>184</v>
       </c>
-      <c r="E446" s="1">
+      <c r="E446" s="2">
         <v>46230</v>
       </c>
       <c r="G446" t="s">
         <v>221</v>
       </c>
-      <c r="H446" s="1">
+      <c r="H446" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10512,7 +10538,7 @@
       <c r="C447" t="s">
         <v>123</v>
       </c>
-      <c r="H447" s="1">
+      <c r="H447" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10526,7 +10552,7 @@
       <c r="C448" t="s">
         <v>123</v>
       </c>
-      <c r="H448" s="1">
+      <c r="H448" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10543,13 +10569,13 @@
       <c r="D449" t="s">
         <v>136</v>
       </c>
-      <c r="E449" s="1">
+      <c r="E449" s="2">
         <v>46237</v>
       </c>
       <c r="G449" t="s">
         <v>219</v>
       </c>
-      <c r="H449" s="1">
+      <c r="H449" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10563,7 +10589,7 @@
       <c r="C450" t="s">
         <v>123</v>
       </c>
-      <c r="H450" s="1">
+      <c r="H450" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10577,7 +10603,7 @@
       <c r="C451" t="s">
         <v>123</v>
       </c>
-      <c r="H451" s="1">
+      <c r="H451" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10591,7 +10617,7 @@
       <c r="C452" t="s">
         <v>123</v>
       </c>
-      <c r="H452" s="1">
+      <c r="H452" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10605,7 +10631,7 @@
       <c r="C453" t="s">
         <v>123</v>
       </c>
-      <c r="H453" s="1">
+      <c r="H453" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10622,13 +10648,13 @@
       <c r="D454" t="s">
         <v>173</v>
       </c>
-      <c r="E454" s="1">
+      <c r="E454" s="2">
         <v>46234</v>
       </c>
       <c r="G454" t="s">
         <v>217</v>
       </c>
-      <c r="H454" s="1">
+      <c r="H454" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10642,7 +10668,7 @@
       <c r="C455" t="s">
         <v>127</v>
       </c>
-      <c r="H455" s="1">
+      <c r="H455" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10659,7 +10685,7 @@
       <c r="D456" t="s">
         <v>179</v>
       </c>
-      <c r="H456" s="1">
+      <c r="H456" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10673,7 +10699,7 @@
       <c r="C457" t="s">
         <v>123</v>
       </c>
-      <c r="H457" s="1">
+      <c r="H457" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10696,7 +10722,7 @@
       <c r="G458" t="s">
         <v>187</v>
       </c>
-      <c r="H458" s="1">
+      <c r="H458" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10713,7 +10739,7 @@
       <c r="D459" t="s">
         <v>140</v>
       </c>
-      <c r="H459" s="1">
+      <c r="H459" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10736,7 +10762,7 @@
       <c r="G460" t="s">
         <v>188</v>
       </c>
-      <c r="H460" s="1">
+      <c r="H460" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10753,13 +10779,13 @@
       <c r="D461" t="s">
         <v>162</v>
       </c>
-      <c r="E461" s="1">
+      <c r="E461" s="2">
         <v>46295</v>
       </c>
       <c r="G461" t="s">
         <v>214</v>
       </c>
-      <c r="H461" s="1">
+      <c r="H461" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10782,7 +10808,7 @@
       <c r="G462" t="s">
         <v>189</v>
       </c>
-      <c r="H462" s="1">
+      <c r="H462" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10805,7 +10831,7 @@
       <c r="G463" t="s">
         <v>189</v>
       </c>
-      <c r="H463" s="1">
+      <c r="H463" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10828,7 +10854,7 @@
       <c r="G464" t="s">
         <v>190</v>
       </c>
-      <c r="H464" s="1">
+      <c r="H464" s="2">
         <v>46230</v>
       </c>
     </row>
@@ -10845,13 +10871,13 @@
       <c r="D465" t="s">
         <v>183</v>
       </c>
-      <c r="E465" s="1">
+      <c r="E465" s="2">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
         <v>221</v>
       </c>
-      <c r="H465" s="1">
+      <c r="H465" s="2">
         <v>46230</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -708,16 +708,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -733,7 +725,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -741,30 +733,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1064,72 +1038,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1194,7 +1168,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1259,7 +1233,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1324,7 +1298,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1389,7 +1363,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1454,7 +1428,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1519,7 +1493,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1584,7 +1558,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1649,7 +1623,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1714,7 +1688,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1779,7 +1753,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1844,7 +1818,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -1909,7 +1883,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -1974,7 +1948,7 @@
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>46226</v>
       </c>
       <c r="B15">
@@ -2039,7 +2013,7 @@
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>46227</v>
       </c>
       <c r="B16">
@@ -2104,7 +2078,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>46230</v>
       </c>
       <c r="B17">
@@ -2169,7 +2143,7 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>46231</v>
       </c>
       <c r="B18">
@@ -2241,28 +2215,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2276,7 +2250,7 @@
       <c r="C2" t="s">
         <v>126</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2290,7 +2264,7 @@
       <c r="C3" t="s">
         <v>126</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2313,7 +2287,7 @@
       <c r="G4" t="s">
         <v>190</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2327,7 +2301,7 @@
       <c r="C5" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2341,7 +2315,7 @@
       <c r="C6" t="s">
         <v>126</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2358,13 +2332,13 @@
       <c r="D7" t="s">
         <v>134</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2381,13 +2355,13 @@
       <c r="D8" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>199</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2404,13 +2378,13 @@
       <c r="D9" t="s">
         <v>136</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2427,13 +2401,13 @@
       <c r="D10" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>201</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2447,7 +2421,7 @@
       <c r="C11" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2461,7 +2435,7 @@
       <c r="C12" t="s">
         <v>126</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2478,13 +2452,13 @@
       <c r="D13" t="s">
         <v>138</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>199</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2498,7 +2472,7 @@
       <c r="C14" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2515,13 +2489,13 @@
       <c r="D15" t="s">
         <v>139</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>202</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2535,7 +2509,7 @@
       <c r="C16" t="s">
         <v>126</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2549,7 +2523,7 @@
       <c r="C17" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2566,13 +2540,13 @@
       <c r="D18" t="s">
         <v>140</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>203</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2586,7 +2560,7 @@
       <c r="C19" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2603,13 +2577,13 @@
       <c r="D20" t="s">
         <v>141</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>199</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2632,7 +2606,7 @@
       <c r="G21" t="s">
         <v>191</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2646,7 +2620,7 @@
       <c r="C22" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2660,7 +2634,7 @@
       <c r="C23" t="s">
         <v>126</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2683,7 +2657,7 @@
       <c r="G24" t="s">
         <v>192</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2700,7 +2674,7 @@
       <c r="D25" t="s">
         <v>143</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2723,7 +2697,7 @@
       <c r="G26" t="s">
         <v>193</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2740,13 +2714,13 @@
       <c r="D27" t="s">
         <v>145</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>204</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2769,7 +2743,7 @@
       <c r="G28" t="s">
         <v>194</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2792,7 +2766,7 @@
       <c r="G29" t="s">
         <v>194</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2815,7 +2789,7 @@
       <c r="G30" t="s">
         <v>195</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2829,7 +2803,7 @@
       <c r="C31" t="s">
         <v>126</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2843,7 +2817,7 @@
       <c r="C32" t="s">
         <v>126</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2866,7 +2840,7 @@
       <c r="G33" t="s">
         <v>196</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2880,7 +2854,7 @@
       <c r="C34" t="s">
         <v>126</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2894,7 +2868,7 @@
       <c r="C35" t="s">
         <v>126</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2911,13 +2885,13 @@
       <c r="D36" t="s">
         <v>134</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>199</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2934,13 +2908,13 @@
       <c r="D37" t="s">
         <v>135</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>199</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2957,13 +2931,13 @@
       <c r="D38" t="s">
         <v>136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>200</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -2980,13 +2954,13 @@
       <c r="D39" t="s">
         <v>137</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>201</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3000,7 +2974,7 @@
       <c r="C40" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3014,7 +2988,7 @@
       <c r="C41" t="s">
         <v>126</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3031,13 +3005,13 @@
       <c r="D42" t="s">
         <v>138</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>199</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3051,7 +3025,7 @@
       <c r="C43" t="s">
         <v>126</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3068,13 +3042,13 @@
       <c r="D44" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>202</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3088,7 +3062,7 @@
       <c r="C45" t="s">
         <v>126</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3102,7 +3076,7 @@
       <c r="C46" t="s">
         <v>126</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3116,7 +3090,7 @@
       <c r="C47" t="s">
         <v>130</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3130,7 +3104,7 @@
       <c r="C48" t="s">
         <v>126</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3147,13 +3121,13 @@
       <c r="D49" t="s">
         <v>150</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>199</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3176,7 +3150,7 @@
       <c r="G50" t="s">
         <v>191</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3190,7 +3164,7 @@
       <c r="C51" t="s">
         <v>130</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3204,7 +3178,7 @@
       <c r="C52" t="s">
         <v>126</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3227,7 +3201,7 @@
       <c r="G53" t="s">
         <v>192</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3244,7 +3218,7 @@
       <c r="D54" t="s">
         <v>143</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3267,7 +3241,7 @@
       <c r="G55" t="s">
         <v>193</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3284,13 +3258,13 @@
       <c r="D56" t="s">
         <v>145</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>204</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3313,7 +3287,7 @@
       <c r="G57" t="s">
         <v>194</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3336,7 +3310,7 @@
       <c r="G58" t="s">
         <v>194</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3359,7 +3333,7 @@
       <c r="G59" t="s">
         <v>195</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3373,7 +3347,7 @@
       <c r="C60" t="s">
         <v>126</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3387,7 +3361,7 @@
       <c r="C61" t="s">
         <v>126</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3404,13 +3378,13 @@
       <c r="D62" t="s">
         <v>149</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>205</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3424,7 +3398,7 @@
       <c r="C63" t="s">
         <v>126</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3441,13 +3415,13 @@
       <c r="D64" t="s">
         <v>151</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>206</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3461,7 +3435,7 @@
       <c r="C65" t="s">
         <v>126</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3475,7 +3449,7 @@
       <c r="C66" t="s">
         <v>130</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3492,13 +3466,13 @@
       <c r="D67" t="s">
         <v>136</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>200</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3515,13 +3489,13 @@
       <c r="D68" t="s">
         <v>137</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>201</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3535,7 +3509,7 @@
       <c r="C69" t="s">
         <v>126</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3549,7 +3523,7 @@
       <c r="C70" t="s">
         <v>126</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3566,13 +3540,13 @@
       <c r="D71" t="s">
         <v>138</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>205</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3586,7 +3560,7 @@
       <c r="C72" t="s">
         <v>126</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3603,13 +3577,13 @@
       <c r="D73" t="s">
         <v>139</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>202</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3623,7 +3597,7 @@
       <c r="C74" t="s">
         <v>126</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3637,7 +3611,7 @@
       <c r="C75" t="s">
         <v>126</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3651,7 +3625,7 @@
       <c r="C76" t="s">
         <v>126</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3665,7 +3639,7 @@
       <c r="C77" t="s">
         <v>126</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3682,13 +3656,13 @@
       <c r="D78" t="s">
         <v>150</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>205</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3711,7 +3685,7 @@
       <c r="G79" t="s">
         <v>197</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3725,7 +3699,7 @@
       <c r="C80" t="s">
         <v>130</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3739,7 +3713,7 @@
       <c r="C81" t="s">
         <v>126</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3762,7 +3736,7 @@
       <c r="G82" t="s">
         <v>192</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3779,7 +3753,7 @@
       <c r="D83" t="s">
         <v>143</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3802,7 +3776,7 @@
       <c r="G84" t="s">
         <v>193</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3819,13 +3793,13 @@
       <c r="D85" t="s">
         <v>145</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>204</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3848,7 +3822,7 @@
       <c r="G86" t="s">
         <v>194</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3871,7 +3845,7 @@
       <c r="G87" t="s">
         <v>194</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3894,7 +3868,7 @@
       <c r="G88" t="s">
         <v>195</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3908,7 +3882,7 @@
       <c r="C89" t="s">
         <v>126</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3925,13 +3899,13 @@
       <c r="D90" t="s">
         <v>153</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>206</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3948,13 +3922,13 @@
       <c r="D91" t="s">
         <v>149</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>205</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3968,7 +3942,7 @@
       <c r="C92" t="s">
         <v>126</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -3985,13 +3959,13 @@
       <c r="D93" t="s">
         <v>151</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>206</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4005,7 +3979,7 @@
       <c r="C94" t="s">
         <v>126</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4019,7 +3993,7 @@
       <c r="C95" t="s">
         <v>130</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4036,13 +4010,13 @@
       <c r="D96" t="s">
         <v>136</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>200</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4059,13 +4033,13 @@
       <c r="D97" t="s">
         <v>137</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>201</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4079,7 +4053,7 @@
       <c r="C98" t="s">
         <v>126</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4096,13 +4070,13 @@
       <c r="D99" t="s">
         <v>154</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>201</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4119,13 +4093,13 @@
       <c r="D100" t="s">
         <v>138</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>201</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4139,7 +4113,7 @@
       <c r="C101" t="s">
         <v>126</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4156,13 +4130,13 @@
       <c r="D102" t="s">
         <v>139</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>202</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4179,13 +4153,13 @@
       <c r="D103" t="s">
         <v>155</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>201</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4199,7 +4173,7 @@
       <c r="C104" t="s">
         <v>126</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4213,7 +4187,7 @@
       <c r="C105" t="s">
         <v>126</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4227,7 +4201,7 @@
       <c r="C106" t="s">
         <v>126</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4244,13 +4218,13 @@
       <c r="D107" t="s">
         <v>156</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>201</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4273,7 +4247,7 @@
       <c r="G108" t="s">
         <v>197</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4287,7 +4261,7 @@
       <c r="C109" t="s">
         <v>130</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4301,7 +4275,7 @@
       <c r="C110" t="s">
         <v>126</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4324,7 +4298,7 @@
       <c r="G111" t="s">
         <v>192</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4341,7 +4315,7 @@
       <c r="D112" t="s">
         <v>143</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4364,7 +4338,7 @@
       <c r="G113" t="s">
         <v>193</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4381,13 +4355,13 @@
       <c r="D114" t="s">
         <v>145</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>204</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4410,7 +4384,7 @@
       <c r="G115" t="s">
         <v>194</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4433,7 +4407,7 @@
       <c r="G116" t="s">
         <v>194</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4456,7 +4430,7 @@
       <c r="G117" t="s">
         <v>195</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4470,7 +4444,7 @@
       <c r="C118" t="s">
         <v>126</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4487,13 +4461,13 @@
       <c r="D119" t="s">
         <v>153</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>206</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4507,7 +4481,7 @@
       <c r="C120" t="s">
         <v>130</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4521,7 +4495,7 @@
       <c r="C121" t="s">
         <v>126</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4535,7 +4509,7 @@
       <c r="C122" t="s">
         <v>130</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4549,7 +4523,7 @@
       <c r="C123" t="s">
         <v>130</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4563,7 +4537,7 @@
       <c r="C124" t="s">
         <v>130</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4580,13 +4554,13 @@
       <c r="D125" t="s">
         <v>136</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>200</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4603,13 +4577,13 @@
       <c r="D126" t="s">
         <v>137</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>201</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4623,7 +4597,7 @@
       <c r="C127" t="s">
         <v>126</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4640,13 +4614,13 @@
       <c r="D128" t="s">
         <v>154</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>201</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4663,13 +4637,13 @@
       <c r="D129" t="s">
         <v>138</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>201</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4683,7 +4657,7 @@
       <c r="C130" t="s">
         <v>126</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4700,13 +4674,13 @@
       <c r="D131" t="s">
         <v>139</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>202</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4723,13 +4697,13 @@
       <c r="D132" t="s">
         <v>155</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>201</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4743,7 +4717,7 @@
       <c r="C133" t="s">
         <v>126</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4757,7 +4731,7 @@
       <c r="C134" t="s">
         <v>126</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4771,7 +4745,7 @@
       <c r="C135" t="s">
         <v>126</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4788,13 +4762,13 @@
       <c r="D136" t="s">
         <v>157</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>201</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4817,7 +4791,7 @@
       <c r="G137" t="s">
         <v>197</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4831,7 +4805,7 @@
       <c r="C138" t="s">
         <v>130</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4845,7 +4819,7 @@
       <c r="C139" t="s">
         <v>126</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4868,7 +4842,7 @@
       <c r="G140" t="s">
         <v>192</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4885,7 +4859,7 @@
       <c r="D141" t="s">
         <v>143</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4908,7 +4882,7 @@
       <c r="G142" t="s">
         <v>193</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4925,13 +4899,13 @@
       <c r="D143" t="s">
         <v>145</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>204</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4954,7 +4928,7 @@
       <c r="G144" t="s">
         <v>194</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4977,7 +4951,7 @@
       <c r="G145" t="s">
         <v>194</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5000,7 +4974,7 @@
       <c r="G146" t="s">
         <v>195</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5014,7 +4988,7 @@
       <c r="C147" t="s">
         <v>126</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5031,13 +5005,13 @@
       <c r="D148" t="s">
         <v>153</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>206</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5051,7 +5025,7 @@
       <c r="C149" t="s">
         <v>130</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5065,7 +5039,7 @@
       <c r="C150" t="s">
         <v>126</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5079,7 +5053,7 @@
       <c r="C151" t="s">
         <v>126</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5093,7 +5067,7 @@
       <c r="C152" t="s">
         <v>130</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5107,7 +5081,7 @@
       <c r="C153" t="s">
         <v>130</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5124,13 +5098,13 @@
       <c r="D154" t="s">
         <v>136</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>200</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5147,13 +5121,13 @@
       <c r="D155" t="s">
         <v>137</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>201</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5167,7 +5141,7 @@
       <c r="C156" t="s">
         <v>126</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5184,13 +5158,13 @@
       <c r="D157" t="s">
         <v>154</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>201</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5207,13 +5181,13 @@
       <c r="D158" t="s">
         <v>138</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>201</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5230,13 +5204,13 @@
       <c r="D159" t="s">
         <v>158</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>207</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5253,13 +5227,13 @@
       <c r="D160" t="s">
         <v>139</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>202</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5276,13 +5250,13 @@
       <c r="D161" t="s">
         <v>155</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>201</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5296,7 +5270,7 @@
       <c r="C162" t="s">
         <v>126</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5310,7 +5284,7 @@
       <c r="C163" t="s">
         <v>126</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5324,7 +5298,7 @@
       <c r="C164" t="s">
         <v>126</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5341,13 +5315,13 @@
       <c r="D165" t="s">
         <v>157</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>201</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5370,7 +5344,7 @@
       <c r="G166" t="s">
         <v>197</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5384,7 +5358,7 @@
       <c r="C167" t="s">
         <v>130</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5398,7 +5372,7 @@
       <c r="C168" t="s">
         <v>126</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5421,7 +5395,7 @@
       <c r="G169" t="s">
         <v>192</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5438,7 +5412,7 @@
       <c r="D170" t="s">
         <v>143</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5461,7 +5435,7 @@
       <c r="G171" t="s">
         <v>193</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5478,13 +5452,13 @@
       <c r="D172" t="s">
         <v>145</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>204</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5507,7 +5481,7 @@
       <c r="G173" t="s">
         <v>194</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5530,7 +5504,7 @@
       <c r="G174" t="s">
         <v>194</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5553,7 +5527,7 @@
       <c r="G175" t="s">
         <v>195</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5567,7 +5541,7 @@
       <c r="C176" t="s">
         <v>126</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5584,13 +5558,13 @@
       <c r="D177" t="s">
         <v>159</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>206</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5604,7 +5578,7 @@
       <c r="C178" t="s">
         <v>126</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5621,13 +5595,13 @@
       <c r="D179" t="s">
         <v>160</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>202</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5641,7 +5615,7 @@
       <c r="C180" t="s">
         <v>126</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5655,7 +5629,7 @@
       <c r="C181" t="s">
         <v>130</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5669,7 +5643,7 @@
       <c r="C182" t="s">
         <v>130</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5686,13 +5660,13 @@
       <c r="D183" t="s">
         <v>136</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>200</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5709,13 +5683,13 @@
       <c r="D184" t="s">
         <v>137</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>201</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5729,7 +5703,7 @@
       <c r="C185" t="s">
         <v>126</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5746,13 +5720,13 @@
       <c r="D186" t="s">
         <v>154</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>201</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5769,13 +5743,13 @@
       <c r="D187" t="s">
         <v>161</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>201</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5792,13 +5766,13 @@
       <c r="D188" t="s">
         <v>162</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>201</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5815,13 +5789,13 @@
       <c r="D189" t="s">
         <v>139</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>202</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5838,13 +5812,13 @@
       <c r="D190" t="s">
         <v>155</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>201</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5858,7 +5832,7 @@
       <c r="C191" t="s">
         <v>126</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5872,7 +5846,7 @@
       <c r="C192" t="s">
         <v>126</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5886,7 +5860,7 @@
       <c r="C193" t="s">
         <v>126</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5903,13 +5877,13 @@
       <c r="D194" t="s">
         <v>157</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>208</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5932,7 +5906,7 @@
       <c r="G195" t="s">
         <v>197</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5946,7 +5920,7 @@
       <c r="C196" t="s">
         <v>130</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5960,7 +5934,7 @@
       <c r="C197" t="s">
         <v>126</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5983,7 +5957,7 @@
       <c r="G198" t="s">
         <v>192</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6000,7 +5974,7 @@
       <c r="D199" t="s">
         <v>143</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6023,7 +5997,7 @@
       <c r="G200" t="s">
         <v>193</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6040,13 +6014,13 @@
       <c r="D201" t="s">
         <v>145</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>204</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6069,7 +6043,7 @@
       <c r="G202" t="s">
         <v>194</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6092,7 +6066,7 @@
       <c r="G203" t="s">
         <v>194</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6115,7 +6089,7 @@
       <c r="G204" t="s">
         <v>195</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6129,7 +6103,7 @@
       <c r="C205" t="s">
         <v>126</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6146,13 +6120,13 @@
       <c r="D206" t="s">
         <v>159</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>206</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6166,7 +6140,7 @@
       <c r="C207" t="s">
         <v>126</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6180,7 +6154,7 @@
       <c r="C208" t="s">
         <v>130</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6194,7 +6168,7 @@
       <c r="C209" t="s">
         <v>126</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6208,7 +6182,7 @@
       <c r="C210" t="s">
         <v>130</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6222,7 +6196,7 @@
       <c r="C211" t="s">
         <v>130</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6239,13 +6213,13 @@
       <c r="D212" t="s">
         <v>136</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>200</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6259,7 +6233,7 @@
       <c r="C213" t="s">
         <v>130</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6273,7 +6247,7 @@
       <c r="C214" t="s">
         <v>126</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6290,13 +6264,13 @@
       <c r="D215" t="s">
         <v>154</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>209</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6313,13 +6287,13 @@
       <c r="D216" t="s">
         <v>161</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>202</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6333,7 +6307,7 @@
       <c r="C217" t="s">
         <v>126</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6350,13 +6324,13 @@
       <c r="D218" t="s">
         <v>139</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>202</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6370,7 +6344,7 @@
       <c r="C219" t="s">
         <v>126</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6384,7 +6358,7 @@
       <c r="C220" t="s">
         <v>126</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6401,13 +6375,13 @@
       <c r="D221" t="s">
         <v>163</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>206</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6421,7 +6395,7 @@
       <c r="C222" t="s">
         <v>126</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6438,13 +6412,13 @@
       <c r="D223" t="s">
         <v>164</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>210</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6467,7 +6441,7 @@
       <c r="G224" t="s">
         <v>197</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6481,7 +6455,7 @@
       <c r="C225" t="s">
         <v>130</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6495,7 +6469,7 @@
       <c r="C226" t="s">
         <v>126</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6518,7 +6492,7 @@
       <c r="G227" t="s">
         <v>192</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6535,7 +6509,7 @@
       <c r="D228" t="s">
         <v>143</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6558,7 +6532,7 @@
       <c r="G229" t="s">
         <v>193</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6575,13 +6549,13 @@
       <c r="D230" t="s">
         <v>165</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>211</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6604,7 +6578,7 @@
       <c r="G231" t="s">
         <v>194</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6627,7 +6601,7 @@
       <c r="G232" t="s">
         <v>194</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6650,7 +6624,7 @@
       <c r="G233" t="s">
         <v>195</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6664,7 +6638,7 @@
       <c r="C234" t="s">
         <v>126</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6681,13 +6655,13 @@
       <c r="D235" t="s">
         <v>166</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>206</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6701,7 +6675,7 @@
       <c r="C236" t="s">
         <v>126</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6715,7 +6689,7 @@
       <c r="C237" t="s">
         <v>130</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6729,7 +6703,7 @@
       <c r="C238" t="s">
         <v>126</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6743,7 +6717,7 @@
       <c r="C239" t="s">
         <v>130</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6757,7 +6731,7 @@
       <c r="C240" t="s">
         <v>130</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6774,13 +6748,13 @@
       <c r="D241" t="s">
         <v>136</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>200</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6794,7 +6768,7 @@
       <c r="C242" t="s">
         <v>130</v>
       </c>
-      <c r="H242" s="2">
+      <c r="H242" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6811,13 +6785,13 @@
       <c r="D243" t="s">
         <v>167</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>212</v>
       </c>
-      <c r="H243" s="2">
+      <c r="H243" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6834,13 +6808,13 @@
       <c r="D244" t="s">
         <v>168</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>209</v>
       </c>
-      <c r="H244" s="2">
+      <c r="H244" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6854,7 +6828,7 @@
       <c r="C245" t="s">
         <v>130</v>
       </c>
-      <c r="H245" s="2">
+      <c r="H245" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6868,7 +6842,7 @@
       <c r="C246" t="s">
         <v>126</v>
       </c>
-      <c r="H246" s="2">
+      <c r="H246" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6885,13 +6859,13 @@
       <c r="D247" t="s">
         <v>139</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>213</v>
       </c>
-      <c r="H247" s="2">
+      <c r="H247" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6905,7 +6879,7 @@
       <c r="C248" t="s">
         <v>126</v>
       </c>
-      <c r="H248" s="2">
+      <c r="H248" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6919,7 +6893,7 @@
       <c r="C249" t="s">
         <v>126</v>
       </c>
-      <c r="H249" s="2">
+      <c r="H249" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6936,13 +6910,13 @@
       <c r="D250" t="s">
         <v>169</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>208</v>
       </c>
-      <c r="H250" s="2">
+      <c r="H250" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6956,7 +6930,7 @@
       <c r="C251" t="s">
         <v>126</v>
       </c>
-      <c r="H251" s="2">
+      <c r="H251" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -6973,13 +6947,13 @@
       <c r="D252" t="s">
         <v>170</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>210</v>
       </c>
-      <c r="H252" s="2">
+      <c r="H252" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7002,7 +6976,7 @@
       <c r="G253" t="s">
         <v>197</v>
       </c>
-      <c r="H253" s="2">
+      <c r="H253" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7016,7 +6990,7 @@
       <c r="C254" t="s">
         <v>130</v>
       </c>
-      <c r="H254" s="2">
+      <c r="H254" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7030,7 +7004,7 @@
       <c r="C255" t="s">
         <v>126</v>
       </c>
-      <c r="H255" s="2">
+      <c r="H255" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7053,7 +7027,7 @@
       <c r="G256" t="s">
         <v>192</v>
       </c>
-      <c r="H256" s="2">
+      <c r="H256" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7070,7 +7044,7 @@
       <c r="D257" t="s">
         <v>143</v>
       </c>
-      <c r="H257" s="2">
+      <c r="H257" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7093,7 +7067,7 @@
       <c r="G258" t="s">
         <v>193</v>
       </c>
-      <c r="H258" s="2">
+      <c r="H258" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7110,13 +7084,13 @@
       <c r="D259" t="s">
         <v>165</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>211</v>
       </c>
-      <c r="H259" s="2">
+      <c r="H259" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7139,7 +7113,7 @@
       <c r="G260" t="s">
         <v>194</v>
       </c>
-      <c r="H260" s="2">
+      <c r="H260" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7162,7 +7136,7 @@
       <c r="G261" t="s">
         <v>194</v>
       </c>
-      <c r="H261" s="2">
+      <c r="H261" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7185,7 +7159,7 @@
       <c r="G262" t="s">
         <v>195</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7199,7 +7173,7 @@
       <c r="C263" t="s">
         <v>126</v>
       </c>
-      <c r="H263" s="2">
+      <c r="H263" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7216,13 +7190,13 @@
       <c r="D264" t="s">
         <v>166</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>206</v>
       </c>
-      <c r="H264" s="2">
+      <c r="H264" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7236,7 +7210,7 @@
       <c r="C265" t="s">
         <v>126</v>
       </c>
-      <c r="H265" s="2">
+      <c r="H265" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7250,7 +7224,7 @@
       <c r="C266" t="s">
         <v>130</v>
       </c>
-      <c r="H266" s="2">
+      <c r="H266" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7264,7 +7238,7 @@
       <c r="C267" t="s">
         <v>126</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H267" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7278,7 +7252,7 @@
       <c r="C268" t="s">
         <v>130</v>
       </c>
-      <c r="H268" s="2">
+      <c r="H268" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7292,7 +7266,7 @@
       <c r="C269" t="s">
         <v>130</v>
       </c>
-      <c r="H269" s="2">
+      <c r="H269" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7309,13 +7283,13 @@
       <c r="D270" t="s">
         <v>136</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>200</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H270" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7329,7 +7303,7 @@
       <c r="C271" t="s">
         <v>130</v>
       </c>
-      <c r="H271" s="2">
+      <c r="H271" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7346,13 +7320,13 @@
       <c r="D272" t="s">
         <v>167</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>212</v>
       </c>
-      <c r="H272" s="2">
+      <c r="H272" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7369,13 +7343,13 @@
       <c r="D273" t="s">
         <v>168</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>214</v>
       </c>
-      <c r="H273" s="2">
+      <c r="H273" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7389,7 +7363,7 @@
       <c r="C274" t="s">
         <v>126</v>
       </c>
-      <c r="H274" s="2">
+      <c r="H274" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7403,7 +7377,7 @@
       <c r="C275" t="s">
         <v>126</v>
       </c>
-      <c r="H275" s="2">
+      <c r="H275" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7420,13 +7394,13 @@
       <c r="D276" t="s">
         <v>139</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>213</v>
       </c>
-      <c r="H276" s="2">
+      <c r="H276" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7440,7 +7414,7 @@
       <c r="C277" t="s">
         <v>126</v>
       </c>
-      <c r="H277" s="2">
+      <c r="H277" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7457,13 +7431,13 @@
       <c r="D278" t="s">
         <v>171</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>215</v>
       </c>
-      <c r="H278" s="2">
+      <c r="H278" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7480,13 +7454,13 @@
       <c r="D279" t="s">
         <v>169</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>214</v>
       </c>
-      <c r="H279" s="2">
+      <c r="H279" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7500,7 +7474,7 @@
       <c r="C280" t="s">
         <v>126</v>
       </c>
-      <c r="H280" s="2">
+      <c r="H280" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7517,13 +7491,13 @@
       <c r="D281" t="s">
         <v>172</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>210</v>
       </c>
-      <c r="H281" s="2">
+      <c r="H281" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7546,7 +7520,7 @@
       <c r="G282" t="s">
         <v>197</v>
       </c>
-      <c r="H282" s="2">
+      <c r="H282" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7560,7 +7534,7 @@
       <c r="C283" t="s">
         <v>130</v>
       </c>
-      <c r="H283" s="2">
+      <c r="H283" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7574,7 +7548,7 @@
       <c r="C284" t="s">
         <v>126</v>
       </c>
-      <c r="H284" s="2">
+      <c r="H284" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7597,7 +7571,7 @@
       <c r="G285" t="s">
         <v>192</v>
       </c>
-      <c r="H285" s="2">
+      <c r="H285" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7614,7 +7588,7 @@
       <c r="D286" t="s">
         <v>143</v>
       </c>
-      <c r="H286" s="2">
+      <c r="H286" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7637,7 +7611,7 @@
       <c r="G287" t="s">
         <v>193</v>
       </c>
-      <c r="H287" s="2">
+      <c r="H287" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7654,13 +7628,13 @@
       <c r="D288" t="s">
         <v>165</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>211</v>
       </c>
-      <c r="H288" s="2">
+      <c r="H288" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7683,7 +7657,7 @@
       <c r="G289" t="s">
         <v>194</v>
       </c>
-      <c r="H289" s="2">
+      <c r="H289" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7706,7 +7680,7 @@
       <c r="G290" t="s">
         <v>194</v>
       </c>
-      <c r="H290" s="2">
+      <c r="H290" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7729,7 +7703,7 @@
       <c r="G291" t="s">
         <v>195</v>
       </c>
-      <c r="H291" s="2">
+      <c r="H291" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7743,7 +7717,7 @@
       <c r="C292" t="s">
         <v>126</v>
       </c>
-      <c r="H292" s="2">
+      <c r="H292" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7760,13 +7734,13 @@
       <c r="D293" t="s">
         <v>166</v>
       </c>
-      <c r="E293" s="2">
+      <c r="E293" s="1">
         <v>46220</v>
       </c>
       <c r="G293" t="s">
         <v>216</v>
       </c>
-      <c r="H293" s="2">
+      <c r="H293" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7780,7 +7754,7 @@
       <c r="C294" t="s">
         <v>126</v>
       </c>
-      <c r="H294" s="2">
+      <c r="H294" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7803,7 +7777,7 @@
       <c r="G295" t="s">
         <v>198</v>
       </c>
-      <c r="H295" s="2">
+      <c r="H295" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7817,7 +7791,7 @@
       <c r="C296" t="s">
         <v>126</v>
       </c>
-      <c r="H296" s="2">
+      <c r="H296" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7831,7 +7805,7 @@
       <c r="C297" t="s">
         <v>130</v>
       </c>
-      <c r="H297" s="2">
+      <c r="H297" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7848,13 +7822,13 @@
       <c r="D298" t="s">
         <v>174</v>
       </c>
-      <c r="E298" s="2">
+      <c r="E298" s="1">
         <v>46223</v>
       </c>
       <c r="G298" t="s">
         <v>217</v>
       </c>
-      <c r="H298" s="2">
+      <c r="H298" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7871,13 +7845,13 @@
       <c r="D299" t="s">
         <v>136</v>
       </c>
-      <c r="E299" s="2">
+      <c r="E299" s="1">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>200</v>
       </c>
-      <c r="H299" s="2">
+      <c r="H299" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7891,7 +7865,7 @@
       <c r="C300" t="s">
         <v>126</v>
       </c>
-      <c r="H300" s="2">
+      <c r="H300" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7908,13 +7882,13 @@
       <c r="D301" t="s">
         <v>167</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301" s="1">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>212</v>
       </c>
-      <c r="H301" s="2">
+      <c r="H301" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7931,13 +7905,13 @@
       <c r="D302" t="s">
         <v>168</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302" s="1">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>209</v>
       </c>
-      <c r="H302" s="2">
+      <c r="H302" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7951,7 +7925,7 @@
       <c r="C303" t="s">
         <v>126</v>
       </c>
-      <c r="H303" s="2">
+      <c r="H303" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7965,7 +7939,7 @@
       <c r="C304" t="s">
         <v>126</v>
       </c>
-      <c r="H304" s="2">
+      <c r="H304" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -7982,13 +7956,13 @@
       <c r="D305" t="s">
         <v>139</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305" s="1">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>213</v>
       </c>
-      <c r="H305" s="2">
+      <c r="H305" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8002,7 +7976,7 @@
       <c r="C306" t="s">
         <v>126</v>
       </c>
-      <c r="H306" s="2">
+      <c r="H306" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8019,13 +7993,13 @@
       <c r="D307" t="s">
         <v>171</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307" s="1">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>215</v>
       </c>
-      <c r="H307" s="2">
+      <c r="H307" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8039,7 +8013,7 @@
       <c r="C308" t="s">
         <v>130</v>
       </c>
-      <c r="H308" s="2">
+      <c r="H308" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8056,13 +8030,13 @@
       <c r="D309" t="s">
         <v>175</v>
       </c>
-      <c r="E309" s="2">
+      <c r="E309" s="1">
         <v>46220</v>
       </c>
       <c r="G309" t="s">
         <v>216</v>
       </c>
-      <c r="H309" s="2">
+      <c r="H309" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8079,13 +8053,13 @@
       <c r="D310" t="s">
         <v>176</v>
       </c>
-      <c r="E310" s="2">
+      <c r="E310" s="1">
         <v>46265</v>
       </c>
       <c r="G310" t="s">
         <v>218</v>
       </c>
-      <c r="H310" s="2">
+      <c r="H310" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8102,7 +8076,7 @@
       <c r="D311" t="s">
         <v>177</v>
       </c>
-      <c r="H311" s="2">
+      <c r="H311" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8116,7 +8090,7 @@
       <c r="C312" t="s">
         <v>130</v>
       </c>
-      <c r="H312" s="2">
+      <c r="H312" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8130,7 +8104,7 @@
       <c r="C313" t="s">
         <v>126</v>
       </c>
-      <c r="H313" s="2">
+      <c r="H313" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8153,7 +8127,7 @@
       <c r="G314" t="s">
         <v>192</v>
       </c>
-      <c r="H314" s="2">
+      <c r="H314" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8170,7 +8144,7 @@
       <c r="D315" t="s">
         <v>143</v>
       </c>
-      <c r="H315" s="2">
+      <c r="H315" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8193,7 +8167,7 @@
       <c r="G316" t="s">
         <v>193</v>
       </c>
-      <c r="H316" s="2">
+      <c r="H316" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8210,13 +8184,13 @@
       <c r="D317" t="s">
         <v>165</v>
       </c>
-      <c r="E317" s="2">
+      <c r="E317" s="1">
         <v>46295</v>
       </c>
       <c r="G317" t="s">
         <v>219</v>
       </c>
-      <c r="H317" s="2">
+      <c r="H317" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8239,7 +8213,7 @@
       <c r="G318" t="s">
         <v>194</v>
       </c>
-      <c r="H318" s="2">
+      <c r="H318" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8262,7 +8236,7 @@
       <c r="G319" t="s">
         <v>194</v>
       </c>
-      <c r="H319" s="2">
+      <c r="H319" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8285,7 +8259,7 @@
       <c r="G320" t="s">
         <v>195</v>
       </c>
-      <c r="H320" s="2">
+      <c r="H320" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8299,7 +8273,7 @@
       <c r="C321" t="s">
         <v>126</v>
       </c>
-      <c r="H321" s="2">
+      <c r="H321" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8316,13 +8290,13 @@
       <c r="D322" t="s">
         <v>166</v>
       </c>
-      <c r="E322" s="2">
+      <c r="E322" s="1">
         <v>46225</v>
       </c>
       <c r="G322" t="s">
         <v>220</v>
       </c>
-      <c r="H322" s="2">
+      <c r="H322" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8336,7 +8310,7 @@
       <c r="C323" t="s">
         <v>126</v>
       </c>
-      <c r="H323" s="2">
+      <c r="H323" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8353,13 +8327,13 @@
       <c r="D324" t="s">
         <v>178</v>
       </c>
-      <c r="E324" s="2">
+      <c r="E324" s="1">
         <v>46224</v>
       </c>
       <c r="G324" t="s">
         <v>221</v>
       </c>
-      <c r="H324" s="2">
+      <c r="H324" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8373,7 +8347,7 @@
       <c r="C325" t="s">
         <v>126</v>
       </c>
-      <c r="H325" s="2">
+      <c r="H325" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8387,7 +8361,7 @@
       <c r="C326" t="s">
         <v>130</v>
       </c>
-      <c r="H326" s="2">
+      <c r="H326" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8401,7 +8375,7 @@
       <c r="C327" t="s">
         <v>130</v>
       </c>
-      <c r="H327" s="2">
+      <c r="H327" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8418,13 +8392,13 @@
       <c r="D328" t="s">
         <v>136</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328" s="1">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>200</v>
       </c>
-      <c r="H328" s="2">
+      <c r="H328" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8441,13 +8415,13 @@
       <c r="D329" t="s">
         <v>179</v>
       </c>
-      <c r="E329" s="2">
+      <c r="E329" s="1">
         <v>46224</v>
       </c>
       <c r="G329" t="s">
         <v>221</v>
       </c>
-      <c r="H329" s="2">
+      <c r="H329" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8464,13 +8438,13 @@
       <c r="D330" t="s">
         <v>167</v>
       </c>
-      <c r="E330" s="2">
+      <c r="E330" s="1">
         <v>46224</v>
       </c>
       <c r="G330" t="s">
         <v>221</v>
       </c>
-      <c r="H330" s="2">
+      <c r="H330" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8484,7 +8458,7 @@
       <c r="C331" t="s">
         <v>126</v>
       </c>
-      <c r="H331" s="2">
+      <c r="H331" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8501,13 +8475,13 @@
       <c r="D332" t="s">
         <v>180</v>
       </c>
-      <c r="E332" s="2">
+      <c r="E332" s="1">
         <v>46224</v>
       </c>
       <c r="G332" t="s">
         <v>221</v>
       </c>
-      <c r="H332" s="2">
+      <c r="H332" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8524,13 +8498,13 @@
       <c r="D333" t="s">
         <v>181</v>
       </c>
-      <c r="E333" s="2">
+      <c r="E333" s="1">
         <v>46225</v>
       </c>
       <c r="G333" t="s">
         <v>220</v>
       </c>
-      <c r="H333" s="2">
+      <c r="H333" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8547,13 +8521,13 @@
       <c r="D334" t="s">
         <v>139</v>
       </c>
-      <c r="E334" s="2">
+      <c r="E334" s="1">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>213</v>
       </c>
-      <c r="H334" s="2">
+      <c r="H334" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8567,7 +8541,7 @@
       <c r="C335" t="s">
         <v>126</v>
       </c>
-      <c r="H335" s="2">
+      <c r="H335" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8584,13 +8558,13 @@
       <c r="D336" t="s">
         <v>171</v>
       </c>
-      <c r="E336" s="2">
+      <c r="E336" s="1">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>215</v>
       </c>
-      <c r="H336" s="2">
+      <c r="H336" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8604,7 +8578,7 @@
       <c r="C337" t="s">
         <v>126</v>
       </c>
-      <c r="H337" s="2">
+      <c r="H337" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8618,7 +8592,7 @@
       <c r="C338" t="s">
         <v>126</v>
       </c>
-      <c r="H338" s="2">
+      <c r="H338" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8635,13 +8609,13 @@
       <c r="D339" t="s">
         <v>176</v>
       </c>
-      <c r="E339" s="2">
+      <c r="E339" s="1">
         <v>46265</v>
       </c>
       <c r="G339" t="s">
         <v>218</v>
       </c>
-      <c r="H339" s="2">
+      <c r="H339" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8658,7 +8632,7 @@
       <c r="D340" t="s">
         <v>182</v>
       </c>
-      <c r="H340" s="2">
+      <c r="H340" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8672,7 +8646,7 @@
       <c r="C341" t="s">
         <v>130</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8686,7 +8660,7 @@
       <c r="C342" t="s">
         <v>126</v>
       </c>
-      <c r="H342" s="2">
+      <c r="H342" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8709,7 +8683,7 @@
       <c r="G343" t="s">
         <v>192</v>
       </c>
-      <c r="H343" s="2">
+      <c r="H343" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8726,7 +8700,7 @@
       <c r="D344" t="s">
         <v>143</v>
       </c>
-      <c r="H344" s="2">
+      <c r="H344" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8749,7 +8723,7 @@
       <c r="G345" t="s">
         <v>193</v>
       </c>
-      <c r="H345" s="2">
+      <c r="H345" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8766,13 +8740,13 @@
       <c r="D346" t="s">
         <v>165</v>
       </c>
-      <c r="E346" s="2">
+      <c r="E346" s="1">
         <v>46295</v>
       </c>
       <c r="G346" t="s">
         <v>219</v>
       </c>
-      <c r="H346" s="2">
+      <c r="H346" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8795,7 +8769,7 @@
       <c r="G347" t="s">
         <v>194</v>
       </c>
-      <c r="H347" s="2">
+      <c r="H347" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8818,7 +8792,7 @@
       <c r="G348" t="s">
         <v>194</v>
       </c>
-      <c r="H348" s="2">
+      <c r="H348" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8841,7 +8815,7 @@
       <c r="G349" t="s">
         <v>195</v>
       </c>
-      <c r="H349" s="2">
+      <c r="H349" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8855,7 +8829,7 @@
       <c r="C350" t="s">
         <v>126</v>
       </c>
-      <c r="H350" s="2">
+      <c r="H350" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8872,13 +8846,13 @@
       <c r="D351" t="s">
         <v>166</v>
       </c>
-      <c r="E351" s="2">
+      <c r="E351" s="1">
         <v>46225</v>
       </c>
       <c r="G351" t="s">
         <v>220</v>
       </c>
-      <c r="H351" s="2">
+      <c r="H351" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8892,7 +8866,7 @@
       <c r="C352" t="s">
         <v>126</v>
       </c>
-      <c r="H352" s="2">
+      <c r="H352" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8906,7 +8880,7 @@
       <c r="C353" t="s">
         <v>126</v>
       </c>
-      <c r="H353" s="2">
+      <c r="H353" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8920,7 +8894,7 @@
       <c r="C354" t="s">
         <v>126</v>
       </c>
-      <c r="H354" s="2">
+      <c r="H354" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8934,7 +8908,7 @@
       <c r="C355" t="s">
         <v>130</v>
       </c>
-      <c r="H355" s="2">
+      <c r="H355" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8948,7 +8922,7 @@
       <c r="C356" t="s">
         <v>130</v>
       </c>
-      <c r="H356" s="2">
+      <c r="H356" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8965,13 +8939,13 @@
       <c r="D357" t="s">
         <v>136</v>
       </c>
-      <c r="E357" s="2">
+      <c r="E357" s="1">
         <v>46234</v>
       </c>
       <c r="G357" t="s">
         <v>222</v>
       </c>
-      <c r="H357" s="2">
+      <c r="H357" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -8985,7 +8959,7 @@
       <c r="C358" t="s">
         <v>126</v>
       </c>
-      <c r="H358" s="2">
+      <c r="H358" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9002,13 +8976,13 @@
       <c r="D359" t="s">
         <v>167</v>
       </c>
-      <c r="E359" s="2">
+      <c r="E359" s="1">
         <v>46227</v>
       </c>
       <c r="G359" t="s">
         <v>223</v>
       </c>
-      <c r="H359" s="2">
+      <c r="H359" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9022,7 +8996,7 @@
       <c r="C360" t="s">
         <v>126</v>
       </c>
-      <c r="H360" s="2">
+      <c r="H360" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9036,7 +9010,7 @@
       <c r="C361" t="s">
         <v>126</v>
       </c>
-      <c r="H361" s="2">
+      <c r="H361" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9053,13 +9027,13 @@
       <c r="D362" t="s">
         <v>181</v>
       </c>
-      <c r="E362" s="2">
+      <c r="E362" s="1">
         <v>46225</v>
       </c>
       <c r="G362" t="s">
         <v>220</v>
       </c>
-      <c r="H362" s="2">
+      <c r="H362" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9076,13 +9050,13 @@
       <c r="D363" t="s">
         <v>139</v>
       </c>
-      <c r="E363" s="2">
+      <c r="E363" s="1">
         <v>46237</v>
       </c>
       <c r="G363" t="s">
         <v>224</v>
       </c>
-      <c r="H363" s="2">
+      <c r="H363" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9096,7 +9070,7 @@
       <c r="C364" t="s">
         <v>126</v>
       </c>
-      <c r="H364" s="2">
+      <c r="H364" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9113,13 +9087,13 @@
       <c r="D365" t="s">
         <v>171</v>
       </c>
-      <c r="E365" s="2">
+      <c r="E365" s="1">
         <v>46227</v>
       </c>
       <c r="G365" t="s">
         <v>223</v>
       </c>
-      <c r="H365" s="2">
+      <c r="H365" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9133,7 +9107,7 @@
       <c r="C366" t="s">
         <v>126</v>
       </c>
-      <c r="H366" s="2">
+      <c r="H366" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9147,7 +9121,7 @@
       <c r="C367" t="s">
         <v>126</v>
       </c>
-      <c r="H367" s="2">
+      <c r="H367" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9164,13 +9138,13 @@
       <c r="D368" t="s">
         <v>176</v>
       </c>
-      <c r="E368" s="2">
+      <c r="E368" s="1">
         <v>46234</v>
       </c>
       <c r="G368" t="s">
         <v>222</v>
       </c>
-      <c r="H368" s="2">
+      <c r="H368" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9187,13 +9161,13 @@
       <c r="D369" t="s">
         <v>183</v>
       </c>
-      <c r="E369" s="2">
+      <c r="E369" s="1">
         <v>46227</v>
       </c>
       <c r="G369" t="s">
         <v>223</v>
       </c>
-      <c r="H369" s="2">
+      <c r="H369" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9210,7 +9184,7 @@
       <c r="D370" t="s">
         <v>182</v>
       </c>
-      <c r="H370" s="2">
+      <c r="H370" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9224,7 +9198,7 @@
       <c r="C371" t="s">
         <v>126</v>
       </c>
-      <c r="H371" s="2">
+      <c r="H371" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9247,7 +9221,7 @@
       <c r="G372" t="s">
         <v>192</v>
       </c>
-      <c r="H372" s="2">
+      <c r="H372" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9264,7 +9238,7 @@
       <c r="D373" t="s">
         <v>143</v>
       </c>
-      <c r="H373" s="2">
+      <c r="H373" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9287,7 +9261,7 @@
       <c r="G374" t="s">
         <v>193</v>
       </c>
-      <c r="H374" s="2">
+      <c r="H374" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9304,13 +9278,13 @@
       <c r="D375" t="s">
         <v>165</v>
       </c>
-      <c r="E375" s="2">
+      <c r="E375" s="1">
         <v>46295</v>
       </c>
       <c r="G375" t="s">
         <v>219</v>
       </c>
-      <c r="H375" s="2">
+      <c r="H375" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9333,7 +9307,7 @@
       <c r="G376" t="s">
         <v>194</v>
       </c>
-      <c r="H376" s="2">
+      <c r="H376" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9356,7 +9330,7 @@
       <c r="G377" t="s">
         <v>194</v>
       </c>
-      <c r="H377" s="2">
+      <c r="H377" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9379,7 +9353,7 @@
       <c r="G378" t="s">
         <v>195</v>
       </c>
-      <c r="H378" s="2">
+      <c r="H378" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9393,7 +9367,7 @@
       <c r="C379" t="s">
         <v>126</v>
       </c>
-      <c r="H379" s="2">
+      <c r="H379" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9410,13 +9384,13 @@
       <c r="D380" t="s">
         <v>166</v>
       </c>
-      <c r="E380" s="2">
+      <c r="E380" s="1">
         <v>46227</v>
       </c>
       <c r="G380" t="s">
         <v>223</v>
       </c>
-      <c r="H380" s="2">
+      <c r="H380" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9430,7 +9404,7 @@
       <c r="C381" t="s">
         <v>126</v>
       </c>
-      <c r="H381" s="2">
+      <c r="H381" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9444,7 +9418,7 @@
       <c r="C382" t="s">
         <v>126</v>
       </c>
-      <c r="H382" s="2">
+      <c r="H382" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9458,7 +9432,7 @@
       <c r="C383" t="s">
         <v>126</v>
       </c>
-      <c r="H383" s="2">
+      <c r="H383" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9472,7 +9446,7 @@
       <c r="C384" t="s">
         <v>130</v>
       </c>
-      <c r="H384" s="2">
+      <c r="H384" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9486,7 +9460,7 @@
       <c r="C385" t="s">
         <v>130</v>
       </c>
-      <c r="H385" s="2">
+      <c r="H385" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9503,13 +9477,13 @@
       <c r="D386" t="s">
         <v>136</v>
       </c>
-      <c r="E386" s="2">
+      <c r="E386" s="1">
         <v>46234</v>
       </c>
       <c r="G386" t="s">
         <v>222</v>
       </c>
-      <c r="H386" s="2">
+      <c r="H386" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9523,7 +9497,7 @@
       <c r="C387" t="s">
         <v>126</v>
       </c>
-      <c r="H387" s="2">
+      <c r="H387" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9537,7 +9511,7 @@
       <c r="C388" t="s">
         <v>130</v>
       </c>
-      <c r="H388" s="2">
+      <c r="H388" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9551,7 +9525,7 @@
       <c r="C389" t="s">
         <v>126</v>
       </c>
-      <c r="H389" s="2">
+      <c r="H389" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9565,7 +9539,7 @@
       <c r="C390" t="s">
         <v>126</v>
       </c>
-      <c r="H390" s="2">
+      <c r="H390" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9582,13 +9556,13 @@
       <c r="D391" t="s">
         <v>184</v>
       </c>
-      <c r="E391" s="2">
+      <c r="E391" s="1">
         <v>46227</v>
       </c>
       <c r="G391" t="s">
         <v>223</v>
       </c>
-      <c r="H391" s="2">
+      <c r="H391" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9605,13 +9579,13 @@
       <c r="D392" t="s">
         <v>139</v>
       </c>
-      <c r="E392" s="2">
+      <c r="E392" s="1">
         <v>46237</v>
       </c>
       <c r="G392" t="s">
         <v>224</v>
       </c>
-      <c r="H392" s="2">
+      <c r="H392" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9625,7 +9599,7 @@
       <c r="C393" t="s">
         <v>126</v>
       </c>
-      <c r="H393" s="2">
+      <c r="H393" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9642,13 +9616,13 @@
       <c r="D394" t="s">
         <v>171</v>
       </c>
-      <c r="E394" s="2">
+      <c r="E394" s="1">
         <v>46227</v>
       </c>
       <c r="G394" t="s">
         <v>223</v>
       </c>
-      <c r="H394" s="2">
+      <c r="H394" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9662,7 +9636,7 @@
       <c r="C395" t="s">
         <v>126</v>
       </c>
-      <c r="H395" s="2">
+      <c r="H395" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9676,7 +9650,7 @@
       <c r="C396" t="s">
         <v>126</v>
       </c>
-      <c r="H396" s="2">
+      <c r="H396" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9693,13 +9667,13 @@
       <c r="D397" t="s">
         <v>176</v>
       </c>
-      <c r="E397" s="2">
+      <c r="E397" s="1">
         <v>46234</v>
       </c>
       <c r="G397" t="s">
         <v>222</v>
       </c>
-      <c r="H397" s="2">
+      <c r="H397" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9716,13 +9690,13 @@
       <c r="D398" t="s">
         <v>183</v>
       </c>
-      <c r="E398" s="2">
+      <c r="E398" s="1">
         <v>46227</v>
       </c>
       <c r="G398" t="s">
         <v>223</v>
       </c>
-      <c r="H398" s="2">
+      <c r="H398" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9739,7 +9713,7 @@
       <c r="D399" t="s">
         <v>182</v>
       </c>
-      <c r="H399" s="2">
+      <c r="H399" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9753,7 +9727,7 @@
       <c r="C400" t="s">
         <v>126</v>
       </c>
-      <c r="H400" s="2">
+      <c r="H400" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9776,7 +9750,7 @@
       <c r="G401" t="s">
         <v>192</v>
       </c>
-      <c r="H401" s="2">
+      <c r="H401" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9793,7 +9767,7 @@
       <c r="D402" t="s">
         <v>143</v>
       </c>
-      <c r="H402" s="2">
+      <c r="H402" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9816,7 +9790,7 @@
       <c r="G403" t="s">
         <v>193</v>
       </c>
-      <c r="H403" s="2">
+      <c r="H403" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9833,13 +9807,13 @@
       <c r="D404" t="s">
         <v>165</v>
       </c>
-      <c r="E404" s="2">
+      <c r="E404" s="1">
         <v>46295</v>
       </c>
       <c r="G404" t="s">
         <v>219</v>
       </c>
-      <c r="H404" s="2">
+      <c r="H404" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9862,7 +9836,7 @@
       <c r="G405" t="s">
         <v>194</v>
       </c>
-      <c r="H405" s="2">
+      <c r="H405" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9885,7 +9859,7 @@
       <c r="G406" t="s">
         <v>194</v>
       </c>
-      <c r="H406" s="2">
+      <c r="H406" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9908,7 +9882,7 @@
       <c r="G407" t="s">
         <v>195</v>
       </c>
-      <c r="H407" s="2">
+      <c r="H407" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9922,7 +9896,7 @@
       <c r="C408" t="s">
         <v>126</v>
       </c>
-      <c r="H408" s="2">
+      <c r="H408" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9939,13 +9913,13 @@
       <c r="D409" t="s">
         <v>153</v>
       </c>
-      <c r="E409" s="2">
+      <c r="E409" s="1">
         <v>46231</v>
       </c>
       <c r="G409" t="s">
         <v>225</v>
       </c>
-      <c r="H409" s="2">
+      <c r="H409" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9959,7 +9933,7 @@
       <c r="C410" t="s">
         <v>126</v>
       </c>
-      <c r="H410" s="2">
+      <c r="H410" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9973,7 +9947,7 @@
       <c r="C411" t="s">
         <v>126</v>
       </c>
-      <c r="H411" s="2">
+      <c r="H411" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -9987,7 +9961,7 @@
       <c r="C412" t="s">
         <v>126</v>
       </c>
-      <c r="H412" s="2">
+      <c r="H412" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10001,7 +9975,7 @@
       <c r="C413" t="s">
         <v>130</v>
       </c>
-      <c r="H413" s="2">
+      <c r="H413" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10015,7 +9989,7 @@
       <c r="C414" t="s">
         <v>130</v>
       </c>
-      <c r="H414" s="2">
+      <c r="H414" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10032,13 +10006,13 @@
       <c r="D415" t="s">
         <v>185</v>
       </c>
-      <c r="E415" s="2">
+      <c r="E415" s="1">
         <v>46234</v>
       </c>
       <c r="G415" t="s">
         <v>222</v>
       </c>
-      <c r="H415" s="2">
+      <c r="H415" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10052,7 +10026,7 @@
       <c r="C416" t="s">
         <v>126</v>
       </c>
-      <c r="H416" s="2">
+      <c r="H416" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10066,7 +10040,7 @@
       <c r="C417" t="s">
         <v>130</v>
       </c>
-      <c r="H417" s="2">
+      <c r="H417" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10080,7 +10054,7 @@
       <c r="C418" t="s">
         <v>126</v>
       </c>
-      <c r="H418" s="2">
+      <c r="H418" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10094,7 +10068,7 @@
       <c r="C419" t="s">
         <v>126</v>
       </c>
-      <c r="H419" s="2">
+      <c r="H419" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10111,13 +10085,13 @@
       <c r="D420" t="s">
         <v>139</v>
       </c>
-      <c r="E420" s="2">
+      <c r="E420" s="1">
         <v>46237</v>
       </c>
       <c r="G420" t="s">
         <v>224</v>
       </c>
-      <c r="H420" s="2">
+      <c r="H420" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10131,7 +10105,7 @@
       <c r="C421" t="s">
         <v>126</v>
       </c>
-      <c r="H421" s="2">
+      <c r="H421" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10148,13 +10122,13 @@
       <c r="D422" t="s">
         <v>171</v>
       </c>
-      <c r="E422" s="2">
+      <c r="E422" s="1">
         <v>46227</v>
       </c>
       <c r="G422" t="s">
         <v>223</v>
       </c>
-      <c r="H422" s="2">
+      <c r="H422" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10168,7 +10142,7 @@
       <c r="C423" t="s">
         <v>126</v>
       </c>
-      <c r="H423" s="2">
+      <c r="H423" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10182,7 +10156,7 @@
       <c r="C424" t="s">
         <v>126</v>
       </c>
-      <c r="H424" s="2">
+      <c r="H424" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10199,13 +10173,13 @@
       <c r="D425" t="s">
         <v>176</v>
       </c>
-      <c r="E425" s="2">
+      <c r="E425" s="1">
         <v>46234</v>
       </c>
       <c r="G425" t="s">
         <v>222</v>
       </c>
-      <c r="H425" s="2">
+      <c r="H425" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10222,13 +10196,13 @@
       <c r="D426" t="s">
         <v>183</v>
       </c>
-      <c r="E426" s="2">
+      <c r="E426" s="1">
         <v>46227</v>
       </c>
       <c r="G426" t="s">
         <v>223</v>
       </c>
-      <c r="H426" s="2">
+      <c r="H426" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10245,7 +10219,7 @@
       <c r="D427" t="s">
         <v>182</v>
       </c>
-      <c r="H427" s="2">
+      <c r="H427" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10259,7 +10233,7 @@
       <c r="C428" t="s">
         <v>126</v>
       </c>
-      <c r="H428" s="2">
+      <c r="H428" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10282,7 +10256,7 @@
       <c r="G429" t="s">
         <v>192</v>
       </c>
-      <c r="H429" s="2">
+      <c r="H429" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10299,7 +10273,7 @@
       <c r="D430" t="s">
         <v>143</v>
       </c>
-      <c r="H430" s="2">
+      <c r="H430" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10322,7 +10296,7 @@
       <c r="G431" t="s">
         <v>193</v>
       </c>
-      <c r="H431" s="2">
+      <c r="H431" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10339,13 +10313,13 @@
       <c r="D432" t="s">
         <v>165</v>
       </c>
-      <c r="E432" s="2">
+      <c r="E432" s="1">
         <v>46295</v>
       </c>
       <c r="G432" t="s">
         <v>219</v>
       </c>
-      <c r="H432" s="2">
+      <c r="H432" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10368,7 +10342,7 @@
       <c r="G433" t="s">
         <v>194</v>
       </c>
-      <c r="H433" s="2">
+      <c r="H433" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10391,7 +10365,7 @@
       <c r="G434" t="s">
         <v>194</v>
       </c>
-      <c r="H434" s="2">
+      <c r="H434" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10414,7 +10388,7 @@
       <c r="G435" t="s">
         <v>195</v>
       </c>
-      <c r="H435" s="2">
+      <c r="H435" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10431,13 +10405,13 @@
       <c r="D436" t="s">
         <v>186</v>
       </c>
-      <c r="E436" s="2">
+      <c r="E436" s="1">
         <v>46230</v>
       </c>
       <c r="G436" t="s">
         <v>226</v>
       </c>
-      <c r="H436" s="2">
+      <c r="H436" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10451,7 +10425,7 @@
       <c r="C437" t="s">
         <v>126</v>
       </c>
-      <c r="H437" s="2">
+      <c r="H437" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10468,13 +10442,13 @@
       <c r="D438" t="s">
         <v>153</v>
       </c>
-      <c r="E438" s="2">
+      <c r="E438" s="1">
         <v>46231</v>
       </c>
       <c r="G438" t="s">
         <v>225</v>
       </c>
-      <c r="H438" s="2">
+      <c r="H438" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10488,7 +10462,7 @@
       <c r="C439" t="s">
         <v>126</v>
       </c>
-      <c r="H439" s="2">
+      <c r="H439" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10502,7 +10476,7 @@
       <c r="C440" t="s">
         <v>126</v>
       </c>
-      <c r="H440" s="2">
+      <c r="H440" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10516,7 +10490,7 @@
       <c r="C441" t="s">
         <v>126</v>
       </c>
-      <c r="H441" s="2">
+      <c r="H441" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10530,7 +10504,7 @@
       <c r="C442" t="s">
         <v>130</v>
       </c>
-      <c r="H442" s="2">
+      <c r="H442" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10544,7 +10518,7 @@
       <c r="C443" t="s">
         <v>130</v>
       </c>
-      <c r="H443" s="2">
+      <c r="H443" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10561,13 +10535,13 @@
       <c r="D444" t="s">
         <v>185</v>
       </c>
-      <c r="E444" s="2">
+      <c r="E444" s="1">
         <v>46234</v>
       </c>
       <c r="G444" t="s">
         <v>222</v>
       </c>
-      <c r="H444" s="2">
+      <c r="H444" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10581,7 +10555,7 @@
       <c r="C445" t="s">
         <v>126</v>
       </c>
-      <c r="H445" s="2">
+      <c r="H445" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10598,13 +10572,13 @@
       <c r="D446" t="s">
         <v>187</v>
       </c>
-      <c r="E446" s="2">
+      <c r="E446" s="1">
         <v>46230</v>
       </c>
       <c r="G446" t="s">
         <v>226</v>
       </c>
-      <c r="H446" s="2">
+      <c r="H446" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10618,7 +10592,7 @@
       <c r="C447" t="s">
         <v>126</v>
       </c>
-      <c r="H447" s="2">
+      <c r="H447" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10632,7 +10606,7 @@
       <c r="C448" t="s">
         <v>126</v>
       </c>
-      <c r="H448" s="2">
+      <c r="H448" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10649,13 +10623,13 @@
       <c r="D449" t="s">
         <v>139</v>
       </c>
-      <c r="E449" s="2">
+      <c r="E449" s="1">
         <v>46237</v>
       </c>
       <c r="G449" t="s">
         <v>224</v>
       </c>
-      <c r="H449" s="2">
+      <c r="H449" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10669,7 +10643,7 @@
       <c r="C450" t="s">
         <v>126</v>
       </c>
-      <c r="H450" s="2">
+      <c r="H450" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10683,7 +10657,7 @@
       <c r="C451" t="s">
         <v>126</v>
       </c>
-      <c r="H451" s="2">
+      <c r="H451" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10697,7 +10671,7 @@
       <c r="C452" t="s">
         <v>126</v>
       </c>
-      <c r="H452" s="2">
+      <c r="H452" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10711,7 +10685,7 @@
       <c r="C453" t="s">
         <v>126</v>
       </c>
-      <c r="H453" s="2">
+      <c r="H453" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10728,13 +10702,13 @@
       <c r="D454" t="s">
         <v>176</v>
       </c>
-      <c r="E454" s="2">
+      <c r="E454" s="1">
         <v>46234</v>
       </c>
       <c r="G454" t="s">
         <v>222</v>
       </c>
-      <c r="H454" s="2">
+      <c r="H454" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10748,7 +10722,7 @@
       <c r="C455" t="s">
         <v>130</v>
       </c>
-      <c r="H455" s="2">
+      <c r="H455" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10765,7 +10739,7 @@
       <c r="D456" t="s">
         <v>182</v>
       </c>
-      <c r="H456" s="2">
+      <c r="H456" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10779,7 +10753,7 @@
       <c r="C457" t="s">
         <v>126</v>
       </c>
-      <c r="H457" s="2">
+      <c r="H457" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10802,7 +10776,7 @@
       <c r="G458" t="s">
         <v>192</v>
       </c>
-      <c r="H458" s="2">
+      <c r="H458" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10819,7 +10793,7 @@
       <c r="D459" t="s">
         <v>143</v>
       </c>
-      <c r="H459" s="2">
+      <c r="H459" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10842,7 +10816,7 @@
       <c r="G460" t="s">
         <v>193</v>
       </c>
-      <c r="H460" s="2">
+      <c r="H460" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10859,13 +10833,13 @@
       <c r="D461" t="s">
         <v>165</v>
       </c>
-      <c r="E461" s="2">
+      <c r="E461" s="1">
         <v>46295</v>
       </c>
       <c r="G461" t="s">
         <v>219</v>
       </c>
-      <c r="H461" s="2">
+      <c r="H461" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10888,7 +10862,7 @@
       <c r="G462" t="s">
         <v>194</v>
       </c>
-      <c r="H462" s="2">
+      <c r="H462" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10911,7 +10885,7 @@
       <c r="G463" t="s">
         <v>194</v>
       </c>
-      <c r="H463" s="2">
+      <c r="H463" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10934,7 +10908,7 @@
       <c r="G464" t="s">
         <v>195</v>
       </c>
-      <c r="H464" s="2">
+      <c r="H464" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10951,13 +10925,13 @@
       <c r="D465" t="s">
         <v>186</v>
       </c>
-      <c r="E465" s="2">
+      <c r="E465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
         <v>226</v>
       </c>
-      <c r="H465" s="2">
+      <c r="H465" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10974,13 +10948,13 @@
       <c r="D466" t="s">
         <v>188</v>
       </c>
-      <c r="E466" s="2">
+      <c r="E466" s="1">
         <v>46231</v>
       </c>
       <c r="G466" t="s">
         <v>225</v>
       </c>
-      <c r="H466" s="2">
+      <c r="H466" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -10997,13 +10971,13 @@
       <c r="D467" t="s">
         <v>153</v>
       </c>
-      <c r="E467" s="2">
+      <c r="E467" s="1">
         <v>46231</v>
       </c>
       <c r="G467" t="s">
         <v>225</v>
       </c>
-      <c r="H467" s="2">
+      <c r="H467" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11017,7 +10991,7 @@
       <c r="C468" t="s">
         <v>126</v>
       </c>
-      <c r="H468" s="2">
+      <c r="H468" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11031,7 +11005,7 @@
       <c r="C469" t="s">
         <v>126</v>
       </c>
-      <c r="H469" s="2">
+      <c r="H469" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11045,7 +11019,7 @@
       <c r="C470" t="s">
         <v>126</v>
       </c>
-      <c r="H470" s="2">
+      <c r="H470" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11059,7 +11033,7 @@
       <c r="C471" t="s">
         <v>130</v>
       </c>
-      <c r="H471" s="2">
+      <c r="H471" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11073,7 +11047,7 @@
       <c r="C472" t="s">
         <v>130</v>
       </c>
-      <c r="H472" s="2">
+      <c r="H472" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11090,13 +11064,13 @@
       <c r="D473" t="s">
         <v>185</v>
       </c>
-      <c r="E473" s="2">
+      <c r="E473" s="1">
         <v>46234</v>
       </c>
       <c r="G473" t="s">
         <v>222</v>
       </c>
-      <c r="H473" s="2">
+      <c r="H473" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11110,7 +11084,7 @@
       <c r="C474" t="s">
         <v>126</v>
       </c>
-      <c r="H474" s="2">
+      <c r="H474" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11127,13 +11101,13 @@
       <c r="D475" t="s">
         <v>189</v>
       </c>
-      <c r="E475" s="2">
+      <c r="E475" s="1">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
         <v>225</v>
       </c>
-      <c r="H475" s="2">
+      <c r="H475" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11147,7 +11121,7 @@
       <c r="C476" t="s">
         <v>126</v>
       </c>
-      <c r="H476" s="2">
+      <c r="H476" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11161,7 +11135,7 @@
       <c r="C477" t="s">
         <v>126</v>
       </c>
-      <c r="H477" s="2">
+      <c r="H477" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11178,13 +11152,13 @@
       <c r="D478" t="s">
         <v>139</v>
       </c>
-      <c r="E478" s="2">
+      <c r="E478" s="1">
         <v>46237</v>
       </c>
       <c r="G478" t="s">
         <v>224</v>
       </c>
-      <c r="H478" s="2">
+      <c r="H478" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11198,7 +11172,7 @@
       <c r="C479" t="s">
         <v>126</v>
       </c>
-      <c r="H479" s="2">
+      <c r="H479" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11212,7 +11186,7 @@
       <c r="C480" t="s">
         <v>126</v>
       </c>
-      <c r="H480" s="2">
+      <c r="H480" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11226,7 +11200,7 @@
       <c r="C481" t="s">
         <v>126</v>
       </c>
-      <c r="H481" s="2">
+      <c r="H481" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11240,7 +11214,7 @@
       <c r="C482" t="s">
         <v>126</v>
       </c>
-      <c r="H482" s="2">
+      <c r="H482" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11257,13 +11231,13 @@
       <c r="D483" t="s">
         <v>176</v>
       </c>
-      <c r="E483" s="2">
+      <c r="E483" s="1">
         <v>46234</v>
       </c>
       <c r="G483" t="s">
         <v>222</v>
       </c>
-      <c r="H483" s="2">
+      <c r="H483" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11277,7 +11251,7 @@
       <c r="C484" t="s">
         <v>130</v>
       </c>
-      <c r="H484" s="2">
+      <c r="H484" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11294,7 +11268,7 @@
       <c r="D485" t="s">
         <v>182</v>
       </c>
-      <c r="H485" s="2">
+      <c r="H485" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11308,7 +11282,7 @@
       <c r="C486" t="s">
         <v>126</v>
       </c>
-      <c r="H486" s="2">
+      <c r="H486" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11331,7 +11305,7 @@
       <c r="G487" t="s">
         <v>192</v>
       </c>
-      <c r="H487" s="2">
+      <c r="H487" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11348,7 +11322,7 @@
       <c r="D488" t="s">
         <v>143</v>
       </c>
-      <c r="H488" s="2">
+      <c r="H488" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11371,7 +11345,7 @@
       <c r="G489" t="s">
         <v>193</v>
       </c>
-      <c r="H489" s="2">
+      <c r="H489" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11388,13 +11362,13 @@
       <c r="D490" t="s">
         <v>165</v>
       </c>
-      <c r="E490" s="2">
+      <c r="E490" s="1">
         <v>46295</v>
       </c>
       <c r="G490" t="s">
         <v>219</v>
       </c>
-      <c r="H490" s="2">
+      <c r="H490" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11417,7 +11391,7 @@
       <c r="G491" t="s">
         <v>194</v>
       </c>
-      <c r="H491" s="2">
+      <c r="H491" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11440,7 +11414,7 @@
       <c r="G492" t="s">
         <v>194</v>
       </c>
-      <c r="H492" s="2">
+      <c r="H492" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11463,7 +11437,7 @@
       <c r="G493" t="s">
         <v>195</v>
       </c>
-      <c r="H493" s="2">
+      <c r="H493" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11480,13 +11454,13 @@
       <c r="D494" t="s">
         <v>186</v>
       </c>
-      <c r="E494" s="2">
+      <c r="E494" s="1">
         <v>46233</v>
       </c>
       <c r="G494" t="s">
         <v>227</v>
       </c>
-      <c r="H494" s="2">
+      <c r="H494" s="1">
         <v>46231</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -786,16 +786,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -811,7 +803,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -819,30 +811,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1142,72 +1116,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1272,7 +1246,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1337,7 +1311,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1402,7 +1376,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1467,7 +1441,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1532,7 +1506,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1597,7 +1571,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1662,7 +1636,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1727,7 +1701,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1792,7 +1766,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1857,7 +1831,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1922,7 +1896,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -1987,7 +1961,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -2052,7 +2026,7 @@
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>46226</v>
       </c>
       <c r="B15">
@@ -2117,7 +2091,7 @@
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>46227</v>
       </c>
       <c r="B16">
@@ -2182,7 +2156,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>46230</v>
       </c>
       <c r="B17">
@@ -2247,7 +2221,7 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>46231</v>
       </c>
       <c r="B18">
@@ -2309,7 +2283,7 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>46232</v>
       </c>
       <c r="B19">
@@ -2374,7 +2348,7 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>46233</v>
       </c>
       <c r="B20">
@@ -2439,7 +2413,7 @@
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>46234</v>
       </c>
       <c r="B21">
@@ -2501,7 +2475,7 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>46237</v>
       </c>
       <c r="B22">
@@ -2573,28 +2547,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2608,7 +2582,7 @@
       <c r="C2" t="s">
         <v>138</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2622,7 +2596,7 @@
       <c r="C3" t="s">
         <v>138</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2645,7 +2619,7 @@
       <c r="G4" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2659,7 +2633,7 @@
       <c r="C5" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2673,7 +2647,7 @@
       <c r="C6" t="s">
         <v>138</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2690,13 +2664,13 @@
       <c r="D7" t="s">
         <v>146</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>220</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2713,13 +2687,13 @@
       <c r="D8" t="s">
         <v>147</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>220</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2736,13 +2710,13 @@
       <c r="D9" t="s">
         <v>148</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>221</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2759,13 +2733,13 @@
       <c r="D10" t="s">
         <v>149</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>222</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2779,7 +2753,7 @@
       <c r="C11" t="s">
         <v>138</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2793,7 +2767,7 @@
       <c r="C12" t="s">
         <v>138</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2810,13 +2784,13 @@
       <c r="D13" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>220</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2830,7 +2804,7 @@
       <c r="C14" t="s">
         <v>142</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2847,13 +2821,13 @@
       <c r="D15" t="s">
         <v>151</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>223</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2867,7 +2841,7 @@
       <c r="C16" t="s">
         <v>138</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2881,7 +2855,7 @@
       <c r="C17" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2898,13 +2872,13 @@
       <c r="D18" t="s">
         <v>152</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>224</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2918,7 +2892,7 @@
       <c r="C19" t="s">
         <v>138</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2935,13 +2909,13 @@
       <c r="D20" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>220</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2964,7 +2938,7 @@
       <c r="G21" t="s">
         <v>212</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2978,7 +2952,7 @@
       <c r="C22" t="s">
         <v>142</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2992,7 +2966,7 @@
       <c r="C23" t="s">
         <v>138</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3015,7 +2989,7 @@
       <c r="G24" t="s">
         <v>213</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3032,7 +3006,7 @@
       <c r="D25" t="s">
         <v>155</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3055,7 +3029,7 @@
       <c r="G26" t="s">
         <v>214</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3072,13 +3046,13 @@
       <c r="D27" t="s">
         <v>157</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>225</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3101,7 +3075,7 @@
       <c r="G28" t="s">
         <v>215</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3124,7 +3098,7 @@
       <c r="G29" t="s">
         <v>215</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3147,7 +3121,7 @@
       <c r="G30" t="s">
         <v>216</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3161,7 +3135,7 @@
       <c r="C31" t="s">
         <v>138</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3175,7 +3149,7 @@
       <c r="C32" t="s">
         <v>138</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3198,7 +3172,7 @@
       <c r="G33" t="s">
         <v>217</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3212,7 +3186,7 @@
       <c r="C34" t="s">
         <v>138</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3226,7 +3200,7 @@
       <c r="C35" t="s">
         <v>138</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3243,13 +3217,13 @@
       <c r="D36" t="s">
         <v>146</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>220</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3266,13 +3240,13 @@
       <c r="D37" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>220</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3289,13 +3263,13 @@
       <c r="D38" t="s">
         <v>148</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>221</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3312,13 +3286,13 @@
       <c r="D39" t="s">
         <v>149</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3332,7 +3306,7 @@
       <c r="C40" t="s">
         <v>138</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3346,7 +3320,7 @@
       <c r="C41" t="s">
         <v>138</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3363,13 +3337,13 @@
       <c r="D42" t="s">
         <v>150</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>220</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3383,7 +3357,7 @@
       <c r="C43" t="s">
         <v>138</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3400,13 +3374,13 @@
       <c r="D44" t="s">
         <v>151</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>223</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3420,7 +3394,7 @@
       <c r="C45" t="s">
         <v>138</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3434,7 +3408,7 @@
       <c r="C46" t="s">
         <v>138</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3448,7 +3422,7 @@
       <c r="C47" t="s">
         <v>142</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3462,7 +3436,7 @@
       <c r="C48" t="s">
         <v>138</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3479,13 +3453,13 @@
       <c r="D49" t="s">
         <v>162</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>220</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3508,7 +3482,7 @@
       <c r="G50" t="s">
         <v>212</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3522,7 +3496,7 @@
       <c r="C51" t="s">
         <v>142</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3536,7 +3510,7 @@
       <c r="C52" t="s">
         <v>138</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3559,7 +3533,7 @@
       <c r="G53" t="s">
         <v>213</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3576,7 +3550,7 @@
       <c r="D54" t="s">
         <v>155</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3599,7 +3573,7 @@
       <c r="G55" t="s">
         <v>214</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3616,13 +3590,13 @@
       <c r="D56" t="s">
         <v>157</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>225</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3645,7 +3619,7 @@
       <c r="G57" t="s">
         <v>215</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3668,7 +3642,7 @@
       <c r="G58" t="s">
         <v>215</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3691,7 +3665,7 @@
       <c r="G59" t="s">
         <v>216</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3705,7 +3679,7 @@
       <c r="C60" t="s">
         <v>138</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3719,7 +3693,7 @@
       <c r="C61" t="s">
         <v>138</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3736,13 +3710,13 @@
       <c r="D62" t="s">
         <v>161</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>226</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3756,7 +3730,7 @@
       <c r="C63" t="s">
         <v>138</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3773,13 +3747,13 @@
       <c r="D64" t="s">
         <v>163</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>227</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3793,7 +3767,7 @@
       <c r="C65" t="s">
         <v>138</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3807,7 +3781,7 @@
       <c r="C66" t="s">
         <v>142</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3824,13 +3798,13 @@
       <c r="D67" t="s">
         <v>148</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>221</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3847,13 +3821,13 @@
       <c r="D68" t="s">
         <v>149</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>222</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3867,7 +3841,7 @@
       <c r="C69" t="s">
         <v>138</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3881,7 +3855,7 @@
       <c r="C70" t="s">
         <v>138</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3898,13 +3872,13 @@
       <c r="D71" t="s">
         <v>150</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>226</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3918,7 +3892,7 @@
       <c r="C72" t="s">
         <v>138</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3935,13 +3909,13 @@
       <c r="D73" t="s">
         <v>151</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>223</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3955,7 +3929,7 @@
       <c r="C74" t="s">
         <v>138</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3969,7 +3943,7 @@
       <c r="C75" t="s">
         <v>138</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3983,7 +3957,7 @@
       <c r="C76" t="s">
         <v>138</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3997,7 +3971,7 @@
       <c r="C77" t="s">
         <v>138</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4014,13 +3988,13 @@
       <c r="D78" t="s">
         <v>162</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>226</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4043,7 +4017,7 @@
       <c r="G79" t="s">
         <v>218</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4057,7 +4031,7 @@
       <c r="C80" t="s">
         <v>142</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4071,7 +4045,7 @@
       <c r="C81" t="s">
         <v>138</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4094,7 +4068,7 @@
       <c r="G82" t="s">
         <v>213</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4111,7 +4085,7 @@
       <c r="D83" t="s">
         <v>155</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4134,7 +4108,7 @@
       <c r="G84" t="s">
         <v>214</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4151,13 +4125,13 @@
       <c r="D85" t="s">
         <v>157</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>225</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4180,7 +4154,7 @@
       <c r="G86" t="s">
         <v>215</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4203,7 +4177,7 @@
       <c r="G87" t="s">
         <v>215</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4226,7 +4200,7 @@
       <c r="G88" t="s">
         <v>216</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4240,7 +4214,7 @@
       <c r="C89" t="s">
         <v>138</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4257,13 +4231,13 @@
       <c r="D90" t="s">
         <v>165</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>227</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4280,13 +4254,13 @@
       <c r="D91" t="s">
         <v>161</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>226</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4300,7 +4274,7 @@
       <c r="C92" t="s">
         <v>138</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4317,13 +4291,13 @@
       <c r="D93" t="s">
         <v>163</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>227</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4337,7 +4311,7 @@
       <c r="C94" t="s">
         <v>138</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4351,7 +4325,7 @@
       <c r="C95" t="s">
         <v>142</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4368,13 +4342,13 @@
       <c r="D96" t="s">
         <v>148</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>221</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4391,13 +4365,13 @@
       <c r="D97" t="s">
         <v>149</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>222</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4411,7 +4385,7 @@
       <c r="C98" t="s">
         <v>138</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4428,13 +4402,13 @@
       <c r="D99" t="s">
         <v>166</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>222</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4451,13 +4425,13 @@
       <c r="D100" t="s">
         <v>150</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>222</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4471,7 +4445,7 @@
       <c r="C101" t="s">
         <v>138</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4488,13 +4462,13 @@
       <c r="D102" t="s">
         <v>151</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>223</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4511,13 +4485,13 @@
       <c r="D103" t="s">
         <v>167</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>222</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4531,7 +4505,7 @@
       <c r="C104" t="s">
         <v>138</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4545,7 +4519,7 @@
       <c r="C105" t="s">
         <v>138</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4559,7 +4533,7 @@
       <c r="C106" t="s">
         <v>138</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4576,13 +4550,13 @@
       <c r="D107" t="s">
         <v>168</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>222</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4605,7 +4579,7 @@
       <c r="G108" t="s">
         <v>218</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4619,7 +4593,7 @@
       <c r="C109" t="s">
         <v>142</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4633,7 +4607,7 @@
       <c r="C110" t="s">
         <v>138</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4656,7 +4630,7 @@
       <c r="G111" t="s">
         <v>213</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4673,7 +4647,7 @@
       <c r="D112" t="s">
         <v>155</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4696,7 +4670,7 @@
       <c r="G113" t="s">
         <v>214</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4713,13 +4687,13 @@
       <c r="D114" t="s">
         <v>157</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>225</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4742,7 +4716,7 @@
       <c r="G115" t="s">
         <v>215</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4765,7 +4739,7 @@
       <c r="G116" t="s">
         <v>215</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4788,7 +4762,7 @@
       <c r="G117" t="s">
         <v>216</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4802,7 +4776,7 @@
       <c r="C118" t="s">
         <v>138</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4819,13 +4793,13 @@
       <c r="D119" t="s">
         <v>165</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>227</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4839,7 +4813,7 @@
       <c r="C120" t="s">
         <v>142</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4853,7 +4827,7 @@
       <c r="C121" t="s">
         <v>138</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4867,7 +4841,7 @@
       <c r="C122" t="s">
         <v>142</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4881,7 +4855,7 @@
       <c r="C123" t="s">
         <v>142</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4895,7 +4869,7 @@
       <c r="C124" t="s">
         <v>142</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4912,13 +4886,13 @@
       <c r="D125" t="s">
         <v>148</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>221</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4935,13 +4909,13 @@
       <c r="D126" t="s">
         <v>149</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>222</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4955,7 +4929,7 @@
       <c r="C127" t="s">
         <v>138</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4972,13 +4946,13 @@
       <c r="D128" t="s">
         <v>166</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>222</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4995,13 +4969,13 @@
       <c r="D129" t="s">
         <v>150</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>222</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5015,7 +4989,7 @@
       <c r="C130" t="s">
         <v>138</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5032,13 +5006,13 @@
       <c r="D131" t="s">
         <v>151</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>223</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5055,13 +5029,13 @@
       <c r="D132" t="s">
         <v>167</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>222</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5075,7 +5049,7 @@
       <c r="C133" t="s">
         <v>138</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5089,7 +5063,7 @@
       <c r="C134" t="s">
         <v>138</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5103,7 +5077,7 @@
       <c r="C135" t="s">
         <v>138</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5120,13 +5094,13 @@
       <c r="D136" t="s">
         <v>169</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>222</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5149,7 +5123,7 @@
       <c r="G137" t="s">
         <v>218</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5163,7 +5137,7 @@
       <c r="C138" t="s">
         <v>142</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5177,7 +5151,7 @@
       <c r="C139" t="s">
         <v>138</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5200,7 +5174,7 @@
       <c r="G140" t="s">
         <v>213</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5217,7 +5191,7 @@
       <c r="D141" t="s">
         <v>155</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5240,7 +5214,7 @@
       <c r="G142" t="s">
         <v>214</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5257,13 +5231,13 @@
       <c r="D143" t="s">
         <v>157</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>225</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5286,7 +5260,7 @@
       <c r="G144" t="s">
         <v>215</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5309,7 +5283,7 @@
       <c r="G145" t="s">
         <v>215</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5332,7 +5306,7 @@
       <c r="G146" t="s">
         <v>216</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5346,7 +5320,7 @@
       <c r="C147" t="s">
         <v>138</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5363,13 +5337,13 @@
       <c r="D148" t="s">
         <v>165</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>227</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5383,7 +5357,7 @@
       <c r="C149" t="s">
         <v>142</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5397,7 +5371,7 @@
       <c r="C150" t="s">
         <v>138</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5411,7 +5385,7 @@
       <c r="C151" t="s">
         <v>138</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5425,7 +5399,7 @@
       <c r="C152" t="s">
         <v>142</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5439,7 +5413,7 @@
       <c r="C153" t="s">
         <v>142</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5456,13 +5430,13 @@
       <c r="D154" t="s">
         <v>148</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>221</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5479,13 +5453,13 @@
       <c r="D155" t="s">
         <v>149</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>222</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5499,7 +5473,7 @@
       <c r="C156" t="s">
         <v>138</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5516,13 +5490,13 @@
       <c r="D157" t="s">
         <v>166</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>222</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5539,13 +5513,13 @@
       <c r="D158" t="s">
         <v>150</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>222</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5562,13 +5536,13 @@
       <c r="D159" t="s">
         <v>170</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>228</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5585,13 +5559,13 @@
       <c r="D160" t="s">
         <v>151</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>223</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5608,13 +5582,13 @@
       <c r="D161" t="s">
         <v>167</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>222</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5628,7 +5602,7 @@
       <c r="C162" t="s">
         <v>138</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5642,7 +5616,7 @@
       <c r="C163" t="s">
         <v>138</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5656,7 +5630,7 @@
       <c r="C164" t="s">
         <v>138</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5673,13 +5647,13 @@
       <c r="D165" t="s">
         <v>169</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>222</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5702,7 +5676,7 @@
       <c r="G166" t="s">
         <v>218</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5716,7 +5690,7 @@
       <c r="C167" t="s">
         <v>142</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5730,7 +5704,7 @@
       <c r="C168" t="s">
         <v>138</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5753,7 +5727,7 @@
       <c r="G169" t="s">
         <v>213</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5770,7 +5744,7 @@
       <c r="D170" t="s">
         <v>155</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5793,7 +5767,7 @@
       <c r="G171" t="s">
         <v>214</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5810,13 +5784,13 @@
       <c r="D172" t="s">
         <v>157</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>225</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5839,7 +5813,7 @@
       <c r="G173" t="s">
         <v>215</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5862,7 +5836,7 @@
       <c r="G174" t="s">
         <v>215</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5885,7 +5859,7 @@
       <c r="G175" t="s">
         <v>216</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5899,7 +5873,7 @@
       <c r="C176" t="s">
         <v>138</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5916,13 +5890,13 @@
       <c r="D177" t="s">
         <v>171</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>227</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5936,7 +5910,7 @@
       <c r="C178" t="s">
         <v>138</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5953,13 +5927,13 @@
       <c r="D179" t="s">
         <v>172</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>223</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5973,7 +5947,7 @@
       <c r="C180" t="s">
         <v>138</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -5987,7 +5961,7 @@
       <c r="C181" t="s">
         <v>142</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6001,7 +5975,7 @@
       <c r="C182" t="s">
         <v>142</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6018,13 +5992,13 @@
       <c r="D183" t="s">
         <v>148</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>221</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6041,13 +6015,13 @@
       <c r="D184" t="s">
         <v>149</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>222</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6061,7 +6035,7 @@
       <c r="C185" t="s">
         <v>138</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6078,13 +6052,13 @@
       <c r="D186" t="s">
         <v>166</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>222</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6101,13 +6075,13 @@
       <c r="D187" t="s">
         <v>173</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>222</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6124,13 +6098,13 @@
       <c r="D188" t="s">
         <v>174</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>222</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6147,13 +6121,13 @@
       <c r="D189" t="s">
         <v>151</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>223</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6170,13 +6144,13 @@
       <c r="D190" t="s">
         <v>167</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>222</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6190,7 +6164,7 @@
       <c r="C191" t="s">
         <v>138</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6204,7 +6178,7 @@
       <c r="C192" t="s">
         <v>138</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6218,7 +6192,7 @@
       <c r="C193" t="s">
         <v>138</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6235,13 +6209,13 @@
       <c r="D194" t="s">
         <v>169</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>229</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6264,7 +6238,7 @@
       <c r="G195" t="s">
         <v>218</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6278,7 +6252,7 @@
       <c r="C196" t="s">
         <v>142</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6292,7 +6266,7 @@
       <c r="C197" t="s">
         <v>138</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6315,7 +6289,7 @@
       <c r="G198" t="s">
         <v>213</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6332,7 +6306,7 @@
       <c r="D199" t="s">
         <v>155</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6355,7 +6329,7 @@
       <c r="G200" t="s">
         <v>214</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6372,13 +6346,13 @@
       <c r="D201" t="s">
         <v>157</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>225</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6401,7 +6375,7 @@
       <c r="G202" t="s">
         <v>215</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6424,7 +6398,7 @@
       <c r="G203" t="s">
         <v>215</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6447,7 +6421,7 @@
       <c r="G204" t="s">
         <v>216</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6461,7 +6435,7 @@
       <c r="C205" t="s">
         <v>138</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6478,13 +6452,13 @@
       <c r="D206" t="s">
         <v>171</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>227</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6498,7 +6472,7 @@
       <c r="C207" t="s">
         <v>138</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6512,7 +6486,7 @@
       <c r="C208" t="s">
         <v>142</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6526,7 +6500,7 @@
       <c r="C209" t="s">
         <v>138</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6540,7 +6514,7 @@
       <c r="C210" t="s">
         <v>142</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6554,7 +6528,7 @@
       <c r="C211" t="s">
         <v>142</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6571,13 +6545,13 @@
       <c r="D212" t="s">
         <v>148</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>221</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6591,7 +6565,7 @@
       <c r="C213" t="s">
         <v>142</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6605,7 +6579,7 @@
       <c r="C214" t="s">
         <v>138</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6622,13 +6596,13 @@
       <c r="D215" t="s">
         <v>166</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>230</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6645,13 +6619,13 @@
       <c r="D216" t="s">
         <v>173</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>223</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6665,7 +6639,7 @@
       <c r="C217" t="s">
         <v>138</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6682,13 +6656,13 @@
       <c r="D218" t="s">
         <v>151</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>223</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6702,7 +6676,7 @@
       <c r="C219" t="s">
         <v>138</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6716,7 +6690,7 @@
       <c r="C220" t="s">
         <v>138</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6733,13 +6707,13 @@
       <c r="D221" t="s">
         <v>175</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>227</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6753,7 +6727,7 @@
       <c r="C222" t="s">
         <v>138</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6770,13 +6744,13 @@
       <c r="D223" t="s">
         <v>176</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>231</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6799,7 +6773,7 @@
       <c r="G224" t="s">
         <v>218</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6813,7 +6787,7 @@
       <c r="C225" t="s">
         <v>142</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6827,7 +6801,7 @@
       <c r="C226" t="s">
         <v>138</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6850,7 +6824,7 @@
       <c r="G227" t="s">
         <v>213</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6867,7 +6841,7 @@
       <c r="D228" t="s">
         <v>155</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6890,7 +6864,7 @@
       <c r="G229" t="s">
         <v>214</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6907,13 +6881,13 @@
       <c r="D230" t="s">
         <v>177</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>232</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6936,7 +6910,7 @@
       <c r="G231" t="s">
         <v>215</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6959,7 +6933,7 @@
       <c r="G232" t="s">
         <v>215</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6982,7 +6956,7 @@
       <c r="G233" t="s">
         <v>216</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6996,7 +6970,7 @@
       <c r="C234" t="s">
         <v>138</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7013,13 +6987,13 @@
       <c r="D235" t="s">
         <v>178</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>227</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7033,7 +7007,7 @@
       <c r="C236" t="s">
         <v>138</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7047,7 +7021,7 @@
       <c r="C237" t="s">
         <v>142</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7061,7 +7035,7 @@
       <c r="C238" t="s">
         <v>138</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7075,7 +7049,7 @@
       <c r="C239" t="s">
         <v>142</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7089,7 +7063,7 @@
       <c r="C240" t="s">
         <v>142</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7106,13 +7080,13 @@
       <c r="D241" t="s">
         <v>148</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>221</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7126,7 +7100,7 @@
       <c r="C242" t="s">
         <v>142</v>
       </c>
-      <c r="H242" s="2">
+      <c r="H242" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7143,13 +7117,13 @@
       <c r="D243" t="s">
         <v>179</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>233</v>
       </c>
-      <c r="H243" s="2">
+      <c r="H243" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7166,13 +7140,13 @@
       <c r="D244" t="s">
         <v>180</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>230</v>
       </c>
-      <c r="H244" s="2">
+      <c r="H244" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7186,7 +7160,7 @@
       <c r="C245" t="s">
         <v>142</v>
       </c>
-      <c r="H245" s="2">
+      <c r="H245" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7200,7 +7174,7 @@
       <c r="C246" t="s">
         <v>138</v>
       </c>
-      <c r="H246" s="2">
+      <c r="H246" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7217,13 +7191,13 @@
       <c r="D247" t="s">
         <v>151</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>234</v>
       </c>
-      <c r="H247" s="2">
+      <c r="H247" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7237,7 +7211,7 @@
       <c r="C248" t="s">
         <v>138</v>
       </c>
-      <c r="H248" s="2">
+      <c r="H248" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7251,7 +7225,7 @@
       <c r="C249" t="s">
         <v>138</v>
       </c>
-      <c r="H249" s="2">
+      <c r="H249" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7268,13 +7242,13 @@
       <c r="D250" t="s">
         <v>181</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>229</v>
       </c>
-      <c r="H250" s="2">
+      <c r="H250" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7288,7 +7262,7 @@
       <c r="C251" t="s">
         <v>138</v>
       </c>
-      <c r="H251" s="2">
+      <c r="H251" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7305,13 +7279,13 @@
       <c r="D252" t="s">
         <v>182</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>231</v>
       </c>
-      <c r="H252" s="2">
+      <c r="H252" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7334,7 +7308,7 @@
       <c r="G253" t="s">
         <v>218</v>
       </c>
-      <c r="H253" s="2">
+      <c r="H253" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7348,7 +7322,7 @@
       <c r="C254" t="s">
         <v>142</v>
       </c>
-      <c r="H254" s="2">
+      <c r="H254" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7362,7 +7336,7 @@
       <c r="C255" t="s">
         <v>138</v>
       </c>
-      <c r="H255" s="2">
+      <c r="H255" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7385,7 +7359,7 @@
       <c r="G256" t="s">
         <v>213</v>
       </c>
-      <c r="H256" s="2">
+      <c r="H256" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7402,7 +7376,7 @@
       <c r="D257" t="s">
         <v>155</v>
       </c>
-      <c r="H257" s="2">
+      <c r="H257" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7425,7 +7399,7 @@
       <c r="G258" t="s">
         <v>214</v>
       </c>
-      <c r="H258" s="2">
+      <c r="H258" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7442,13 +7416,13 @@
       <c r="D259" t="s">
         <v>177</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>232</v>
       </c>
-      <c r="H259" s="2">
+      <c r="H259" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7471,7 +7445,7 @@
       <c r="G260" t="s">
         <v>215</v>
       </c>
-      <c r="H260" s="2">
+      <c r="H260" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7494,7 +7468,7 @@
       <c r="G261" t="s">
         <v>215</v>
       </c>
-      <c r="H261" s="2">
+      <c r="H261" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7517,7 +7491,7 @@
       <c r="G262" t="s">
         <v>216</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7531,7 +7505,7 @@
       <c r="C263" t="s">
         <v>138</v>
       </c>
-      <c r="H263" s="2">
+      <c r="H263" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7548,13 +7522,13 @@
       <c r="D264" t="s">
         <v>178</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>227</v>
       </c>
-      <c r="H264" s="2">
+      <c r="H264" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7568,7 +7542,7 @@
       <c r="C265" t="s">
         <v>138</v>
       </c>
-      <c r="H265" s="2">
+      <c r="H265" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7582,7 +7556,7 @@
       <c r="C266" t="s">
         <v>142</v>
       </c>
-      <c r="H266" s="2">
+      <c r="H266" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7596,7 +7570,7 @@
       <c r="C267" t="s">
         <v>138</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H267" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7610,7 +7584,7 @@
       <c r="C268" t="s">
         <v>142</v>
       </c>
-      <c r="H268" s="2">
+      <c r="H268" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7624,7 +7598,7 @@
       <c r="C269" t="s">
         <v>142</v>
       </c>
-      <c r="H269" s="2">
+      <c r="H269" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7641,13 +7615,13 @@
       <c r="D270" t="s">
         <v>148</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>221</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H270" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7661,7 +7635,7 @@
       <c r="C271" t="s">
         <v>142</v>
       </c>
-      <c r="H271" s="2">
+      <c r="H271" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7678,13 +7652,13 @@
       <c r="D272" t="s">
         <v>179</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>233</v>
       </c>
-      <c r="H272" s="2">
+      <c r="H272" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7701,13 +7675,13 @@
       <c r="D273" t="s">
         <v>180</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>235</v>
       </c>
-      <c r="H273" s="2">
+      <c r="H273" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7721,7 +7695,7 @@
       <c r="C274" t="s">
         <v>138</v>
       </c>
-      <c r="H274" s="2">
+      <c r="H274" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7735,7 +7709,7 @@
       <c r="C275" t="s">
         <v>138</v>
       </c>
-      <c r="H275" s="2">
+      <c r="H275" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7752,13 +7726,13 @@
       <c r="D276" t="s">
         <v>151</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>234</v>
       </c>
-      <c r="H276" s="2">
+      <c r="H276" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7772,7 +7746,7 @@
       <c r="C277" t="s">
         <v>138</v>
       </c>
-      <c r="H277" s="2">
+      <c r="H277" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7789,13 +7763,13 @@
       <c r="D278" t="s">
         <v>183</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>236</v>
       </c>
-      <c r="H278" s="2">
+      <c r="H278" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7812,13 +7786,13 @@
       <c r="D279" t="s">
         <v>181</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>235</v>
       </c>
-      <c r="H279" s="2">
+      <c r="H279" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7832,7 +7806,7 @@
       <c r="C280" t="s">
         <v>138</v>
       </c>
-      <c r="H280" s="2">
+      <c r="H280" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7849,13 +7823,13 @@
       <c r="D281" t="s">
         <v>184</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>231</v>
       </c>
-      <c r="H281" s="2">
+      <c r="H281" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7878,7 +7852,7 @@
       <c r="G282" t="s">
         <v>218</v>
       </c>
-      <c r="H282" s="2">
+      <c r="H282" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7892,7 +7866,7 @@
       <c r="C283" t="s">
         <v>142</v>
       </c>
-      <c r="H283" s="2">
+      <c r="H283" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7906,7 +7880,7 @@
       <c r="C284" t="s">
         <v>138</v>
       </c>
-      <c r="H284" s="2">
+      <c r="H284" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7929,7 +7903,7 @@
       <c r="G285" t="s">
         <v>213</v>
       </c>
-      <c r="H285" s="2">
+      <c r="H285" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7946,7 +7920,7 @@
       <c r="D286" t="s">
         <v>155</v>
       </c>
-      <c r="H286" s="2">
+      <c r="H286" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7969,7 +7943,7 @@
       <c r="G287" t="s">
         <v>214</v>
       </c>
-      <c r="H287" s="2">
+      <c r="H287" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7986,13 +7960,13 @@
       <c r="D288" t="s">
         <v>177</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>232</v>
       </c>
-      <c r="H288" s="2">
+      <c r="H288" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8015,7 +7989,7 @@
       <c r="G289" t="s">
         <v>215</v>
       </c>
-      <c r="H289" s="2">
+      <c r="H289" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8038,7 +8012,7 @@
       <c r="G290" t="s">
         <v>215</v>
       </c>
-      <c r="H290" s="2">
+      <c r="H290" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8061,7 +8035,7 @@
       <c r="G291" t="s">
         <v>216</v>
       </c>
-      <c r="H291" s="2">
+      <c r="H291" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8075,7 +8049,7 @@
       <c r="C292" t="s">
         <v>138</v>
       </c>
-      <c r="H292" s="2">
+      <c r="H292" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8092,13 +8066,13 @@
       <c r="D293" t="s">
         <v>178</v>
       </c>
-      <c r="E293" s="2">
+      <c r="E293" s="1">
         <v>46220</v>
       </c>
       <c r="G293" t="s">
         <v>237</v>
       </c>
-      <c r="H293" s="2">
+      <c r="H293" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8112,7 +8086,7 @@
       <c r="C294" t="s">
         <v>138</v>
       </c>
-      <c r="H294" s="2">
+      <c r="H294" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8135,7 +8109,7 @@
       <c r="G295" t="s">
         <v>219</v>
       </c>
-      <c r="H295" s="2">
+      <c r="H295" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8149,7 +8123,7 @@
       <c r="C296" t="s">
         <v>138</v>
       </c>
-      <c r="H296" s="2">
+      <c r="H296" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8163,7 +8137,7 @@
       <c r="C297" t="s">
         <v>142</v>
       </c>
-      <c r="H297" s="2">
+      <c r="H297" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8180,13 +8154,13 @@
       <c r="D298" t="s">
         <v>186</v>
       </c>
-      <c r="E298" s="2">
+      <c r="E298" s="1">
         <v>46223</v>
       </c>
       <c r="G298" t="s">
         <v>238</v>
       </c>
-      <c r="H298" s="2">
+      <c r="H298" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8203,13 +8177,13 @@
       <c r="D299" t="s">
         <v>148</v>
       </c>
-      <c r="E299" s="2">
+      <c r="E299" s="1">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>221</v>
       </c>
-      <c r="H299" s="2">
+      <c r="H299" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8223,7 +8197,7 @@
       <c r="C300" t="s">
         <v>138</v>
       </c>
-      <c r="H300" s="2">
+      <c r="H300" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8240,13 +8214,13 @@
       <c r="D301" t="s">
         <v>179</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301" s="1">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>233</v>
       </c>
-      <c r="H301" s="2">
+      <c r="H301" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8263,13 +8237,13 @@
       <c r="D302" t="s">
         <v>180</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302" s="1">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>230</v>
       </c>
-      <c r="H302" s="2">
+      <c r="H302" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8283,7 +8257,7 @@
       <c r="C303" t="s">
         <v>138</v>
       </c>
-      <c r="H303" s="2">
+      <c r="H303" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8297,7 +8271,7 @@
       <c r="C304" t="s">
         <v>138</v>
       </c>
-      <c r="H304" s="2">
+      <c r="H304" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8314,13 +8288,13 @@
       <c r="D305" t="s">
         <v>151</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305" s="1">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>234</v>
       </c>
-      <c r="H305" s="2">
+      <c r="H305" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8334,7 +8308,7 @@
       <c r="C306" t="s">
         <v>138</v>
       </c>
-      <c r="H306" s="2">
+      <c r="H306" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8351,13 +8325,13 @@
       <c r="D307" t="s">
         <v>183</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307" s="1">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>236</v>
       </c>
-      <c r="H307" s="2">
+      <c r="H307" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8371,7 +8345,7 @@
       <c r="C308" t="s">
         <v>142</v>
       </c>
-      <c r="H308" s="2">
+      <c r="H308" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8388,13 +8362,13 @@
       <c r="D309" t="s">
         <v>187</v>
       </c>
-      <c r="E309" s="2">
+      <c r="E309" s="1">
         <v>46220</v>
       </c>
       <c r="G309" t="s">
         <v>237</v>
       </c>
-      <c r="H309" s="2">
+      <c r="H309" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8411,13 +8385,13 @@
       <c r="D310" t="s">
         <v>188</v>
       </c>
-      <c r="E310" s="2">
+      <c r="E310" s="1">
         <v>46265</v>
       </c>
       <c r="G310" t="s">
         <v>239</v>
       </c>
-      <c r="H310" s="2">
+      <c r="H310" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8434,7 +8408,7 @@
       <c r="D311" t="s">
         <v>189</v>
       </c>
-      <c r="H311" s="2">
+      <c r="H311" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8448,7 +8422,7 @@
       <c r="C312" t="s">
         <v>142</v>
       </c>
-      <c r="H312" s="2">
+      <c r="H312" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8462,7 +8436,7 @@
       <c r="C313" t="s">
         <v>138</v>
       </c>
-      <c r="H313" s="2">
+      <c r="H313" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8485,7 +8459,7 @@
       <c r="G314" t="s">
         <v>213</v>
       </c>
-      <c r="H314" s="2">
+      <c r="H314" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8502,7 +8476,7 @@
       <c r="D315" t="s">
         <v>155</v>
       </c>
-      <c r="H315" s="2">
+      <c r="H315" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8525,7 +8499,7 @@
       <c r="G316" t="s">
         <v>214</v>
       </c>
-      <c r="H316" s="2">
+      <c r="H316" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8542,13 +8516,13 @@
       <c r="D317" t="s">
         <v>177</v>
       </c>
-      <c r="E317" s="2">
+      <c r="E317" s="1">
         <v>46295</v>
       </c>
       <c r="G317" t="s">
         <v>240</v>
       </c>
-      <c r="H317" s="2">
+      <c r="H317" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8571,7 +8545,7 @@
       <c r="G318" t="s">
         <v>215</v>
       </c>
-      <c r="H318" s="2">
+      <c r="H318" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8594,7 +8568,7 @@
       <c r="G319" t="s">
         <v>215</v>
       </c>
-      <c r="H319" s="2">
+      <c r="H319" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8617,7 +8591,7 @@
       <c r="G320" t="s">
         <v>216</v>
       </c>
-      <c r="H320" s="2">
+      <c r="H320" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8631,7 +8605,7 @@
       <c r="C321" t="s">
         <v>138</v>
       </c>
-      <c r="H321" s="2">
+      <c r="H321" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8648,13 +8622,13 @@
       <c r="D322" t="s">
         <v>178</v>
       </c>
-      <c r="E322" s="2">
+      <c r="E322" s="1">
         <v>46225</v>
       </c>
       <c r="G322" t="s">
         <v>241</v>
       </c>
-      <c r="H322" s="2">
+      <c r="H322" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8668,7 +8642,7 @@
       <c r="C323" t="s">
         <v>138</v>
       </c>
-      <c r="H323" s="2">
+      <c r="H323" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8685,13 +8659,13 @@
       <c r="D324" t="s">
         <v>190</v>
       </c>
-      <c r="E324" s="2">
+      <c r="E324" s="1">
         <v>46224</v>
       </c>
       <c r="G324" t="s">
         <v>242</v>
       </c>
-      <c r="H324" s="2">
+      <c r="H324" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8705,7 +8679,7 @@
       <c r="C325" t="s">
         <v>138</v>
       </c>
-      <c r="H325" s="2">
+      <c r="H325" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8719,7 +8693,7 @@
       <c r="C326" t="s">
         <v>142</v>
       </c>
-      <c r="H326" s="2">
+      <c r="H326" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8733,7 +8707,7 @@
       <c r="C327" t="s">
         <v>142</v>
       </c>
-      <c r="H327" s="2">
+      <c r="H327" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8750,13 +8724,13 @@
       <c r="D328" t="s">
         <v>148</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328" s="1">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>221</v>
       </c>
-      <c r="H328" s="2">
+      <c r="H328" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8773,13 +8747,13 @@
       <c r="D329" t="s">
         <v>191</v>
       </c>
-      <c r="E329" s="2">
+      <c r="E329" s="1">
         <v>46224</v>
       </c>
       <c r="G329" t="s">
         <v>242</v>
       </c>
-      <c r="H329" s="2">
+      <c r="H329" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8796,13 +8770,13 @@
       <c r="D330" t="s">
         <v>179</v>
       </c>
-      <c r="E330" s="2">
+      <c r="E330" s="1">
         <v>46224</v>
       </c>
       <c r="G330" t="s">
         <v>242</v>
       </c>
-      <c r="H330" s="2">
+      <c r="H330" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8816,7 +8790,7 @@
       <c r="C331" t="s">
         <v>138</v>
       </c>
-      <c r="H331" s="2">
+      <c r="H331" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8833,13 +8807,13 @@
       <c r="D332" t="s">
         <v>192</v>
       </c>
-      <c r="E332" s="2">
+      <c r="E332" s="1">
         <v>46224</v>
       </c>
       <c r="G332" t="s">
         <v>242</v>
       </c>
-      <c r="H332" s="2">
+      <c r="H332" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8856,13 +8830,13 @@
       <c r="D333" t="s">
         <v>193</v>
       </c>
-      <c r="E333" s="2">
+      <c r="E333" s="1">
         <v>46225</v>
       </c>
       <c r="G333" t="s">
         <v>241</v>
       </c>
-      <c r="H333" s="2">
+      <c r="H333" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8879,13 +8853,13 @@
       <c r="D334" t="s">
         <v>151</v>
       </c>
-      <c r="E334" s="2">
+      <c r="E334" s="1">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>234</v>
       </c>
-      <c r="H334" s="2">
+      <c r="H334" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8899,7 +8873,7 @@
       <c r="C335" t="s">
         <v>138</v>
       </c>
-      <c r="H335" s="2">
+      <c r="H335" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8916,13 +8890,13 @@
       <c r="D336" t="s">
         <v>183</v>
       </c>
-      <c r="E336" s="2">
+      <c r="E336" s="1">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>236</v>
       </c>
-      <c r="H336" s="2">
+      <c r="H336" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8936,7 +8910,7 @@
       <c r="C337" t="s">
         <v>138</v>
       </c>
-      <c r="H337" s="2">
+      <c r="H337" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8950,7 +8924,7 @@
       <c r="C338" t="s">
         <v>138</v>
       </c>
-      <c r="H338" s="2">
+      <c r="H338" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8967,13 +8941,13 @@
       <c r="D339" t="s">
         <v>188</v>
       </c>
-      <c r="E339" s="2">
+      <c r="E339" s="1">
         <v>46265</v>
       </c>
       <c r="G339" t="s">
         <v>239</v>
       </c>
-      <c r="H339" s="2">
+      <c r="H339" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8990,7 +8964,7 @@
       <c r="D340" t="s">
         <v>194</v>
       </c>
-      <c r="H340" s="2">
+      <c r="H340" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9004,7 +8978,7 @@
       <c r="C341" t="s">
         <v>142</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9018,7 +8992,7 @@
       <c r="C342" t="s">
         <v>138</v>
       </c>
-      <c r="H342" s="2">
+      <c r="H342" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9041,7 +9015,7 @@
       <c r="G343" t="s">
         <v>213</v>
       </c>
-      <c r="H343" s="2">
+      <c r="H343" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9058,7 +9032,7 @@
       <c r="D344" t="s">
         <v>155</v>
       </c>
-      <c r="H344" s="2">
+      <c r="H344" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9081,7 +9055,7 @@
       <c r="G345" t="s">
         <v>214</v>
       </c>
-      <c r="H345" s="2">
+      <c r="H345" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9098,13 +9072,13 @@
       <c r="D346" t="s">
         <v>177</v>
       </c>
-      <c r="E346" s="2">
+      <c r="E346" s="1">
         <v>46295</v>
       </c>
       <c r="G346" t="s">
         <v>240</v>
       </c>
-      <c r="H346" s="2">
+      <c r="H346" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9127,7 +9101,7 @@
       <c r="G347" t="s">
         <v>215</v>
       </c>
-      <c r="H347" s="2">
+      <c r="H347" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9150,7 +9124,7 @@
       <c r="G348" t="s">
         <v>215</v>
       </c>
-      <c r="H348" s="2">
+      <c r="H348" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9173,7 +9147,7 @@
       <c r="G349" t="s">
         <v>216</v>
       </c>
-      <c r="H349" s="2">
+      <c r="H349" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9187,7 +9161,7 @@
       <c r="C350" t="s">
         <v>138</v>
       </c>
-      <c r="H350" s="2">
+      <c r="H350" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9204,13 +9178,13 @@
       <c r="D351" t="s">
         <v>178</v>
       </c>
-      <c r="E351" s="2">
+      <c r="E351" s="1">
         <v>46225</v>
       </c>
       <c r="G351" t="s">
         <v>241</v>
       </c>
-      <c r="H351" s="2">
+      <c r="H351" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9224,7 +9198,7 @@
       <c r="C352" t="s">
         <v>138</v>
       </c>
-      <c r="H352" s="2">
+      <c r="H352" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9238,7 +9212,7 @@
       <c r="C353" t="s">
         <v>138</v>
       </c>
-      <c r="H353" s="2">
+      <c r="H353" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9252,7 +9226,7 @@
       <c r="C354" t="s">
         <v>138</v>
       </c>
-      <c r="H354" s="2">
+      <c r="H354" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9266,7 +9240,7 @@
       <c r="C355" t="s">
         <v>142</v>
       </c>
-      <c r="H355" s="2">
+      <c r="H355" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9280,7 +9254,7 @@
       <c r="C356" t="s">
         <v>142</v>
       </c>
-      <c r="H356" s="2">
+      <c r="H356" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9297,13 +9271,13 @@
       <c r="D357" t="s">
         <v>148</v>
       </c>
-      <c r="E357" s="2">
+      <c r="E357" s="1">
         <v>46234</v>
       </c>
       <c r="G357" t="s">
         <v>243</v>
       </c>
-      <c r="H357" s="2">
+      <c r="H357" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9317,7 +9291,7 @@
       <c r="C358" t="s">
         <v>138</v>
       </c>
-      <c r="H358" s="2">
+      <c r="H358" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9334,13 +9308,13 @@
       <c r="D359" t="s">
         <v>179</v>
       </c>
-      <c r="E359" s="2">
+      <c r="E359" s="1">
         <v>46227</v>
       </c>
       <c r="G359" t="s">
         <v>244</v>
       </c>
-      <c r="H359" s="2">
+      <c r="H359" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9354,7 +9328,7 @@
       <c r="C360" t="s">
         <v>138</v>
       </c>
-      <c r="H360" s="2">
+      <c r="H360" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9368,7 +9342,7 @@
       <c r="C361" t="s">
         <v>138</v>
       </c>
-      <c r="H361" s="2">
+      <c r="H361" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9385,13 +9359,13 @@
       <c r="D362" t="s">
         <v>193</v>
       </c>
-      <c r="E362" s="2">
+      <c r="E362" s="1">
         <v>46225</v>
       </c>
       <c r="G362" t="s">
         <v>241</v>
       </c>
-      <c r="H362" s="2">
+      <c r="H362" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9408,13 +9382,13 @@
       <c r="D363" t="s">
         <v>151</v>
       </c>
-      <c r="E363" s="2">
+      <c r="E363" s="1">
         <v>46237</v>
       </c>
       <c r="G363" t="s">
         <v>245</v>
       </c>
-      <c r="H363" s="2">
+      <c r="H363" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9428,7 +9402,7 @@
       <c r="C364" t="s">
         <v>138</v>
       </c>
-      <c r="H364" s="2">
+      <c r="H364" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9445,13 +9419,13 @@
       <c r="D365" t="s">
         <v>183</v>
       </c>
-      <c r="E365" s="2">
+      <c r="E365" s="1">
         <v>46227</v>
       </c>
       <c r="G365" t="s">
         <v>244</v>
       </c>
-      <c r="H365" s="2">
+      <c r="H365" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9465,7 +9439,7 @@
       <c r="C366" t="s">
         <v>138</v>
       </c>
-      <c r="H366" s="2">
+      <c r="H366" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9479,7 +9453,7 @@
       <c r="C367" t="s">
         <v>138</v>
       </c>
-      <c r="H367" s="2">
+      <c r="H367" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9496,13 +9470,13 @@
       <c r="D368" t="s">
         <v>188</v>
       </c>
-      <c r="E368" s="2">
+      <c r="E368" s="1">
         <v>46234</v>
       </c>
       <c r="G368" t="s">
         <v>243</v>
       </c>
-      <c r="H368" s="2">
+      <c r="H368" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9519,13 +9493,13 @@
       <c r="D369" t="s">
         <v>195</v>
       </c>
-      <c r="E369" s="2">
+      <c r="E369" s="1">
         <v>46227</v>
       </c>
       <c r="G369" t="s">
         <v>244</v>
       </c>
-      <c r="H369" s="2">
+      <c r="H369" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9542,7 +9516,7 @@
       <c r="D370" t="s">
         <v>194</v>
       </c>
-      <c r="H370" s="2">
+      <c r="H370" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9556,7 +9530,7 @@
       <c r="C371" t="s">
         <v>138</v>
       </c>
-      <c r="H371" s="2">
+      <c r="H371" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9579,7 +9553,7 @@
       <c r="G372" t="s">
         <v>213</v>
       </c>
-      <c r="H372" s="2">
+      <c r="H372" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9596,7 +9570,7 @@
       <c r="D373" t="s">
         <v>155</v>
       </c>
-      <c r="H373" s="2">
+      <c r="H373" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9619,7 +9593,7 @@
       <c r="G374" t="s">
         <v>214</v>
       </c>
-      <c r="H374" s="2">
+      <c r="H374" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9636,13 +9610,13 @@
       <c r="D375" t="s">
         <v>177</v>
       </c>
-      <c r="E375" s="2">
+      <c r="E375" s="1">
         <v>46295</v>
       </c>
       <c r="G375" t="s">
         <v>240</v>
       </c>
-      <c r="H375" s="2">
+      <c r="H375" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9665,7 +9639,7 @@
       <c r="G376" t="s">
         <v>215</v>
       </c>
-      <c r="H376" s="2">
+      <c r="H376" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9688,7 +9662,7 @@
       <c r="G377" t="s">
         <v>215</v>
       </c>
-      <c r="H377" s="2">
+      <c r="H377" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9711,7 +9685,7 @@
       <c r="G378" t="s">
         <v>216</v>
       </c>
-      <c r="H378" s="2">
+      <c r="H378" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9725,7 +9699,7 @@
       <c r="C379" t="s">
         <v>138</v>
       </c>
-      <c r="H379" s="2">
+      <c r="H379" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9742,13 +9716,13 @@
       <c r="D380" t="s">
         <v>178</v>
       </c>
-      <c r="E380" s="2">
+      <c r="E380" s="1">
         <v>46227</v>
       </c>
       <c r="G380" t="s">
         <v>244</v>
       </c>
-      <c r="H380" s="2">
+      <c r="H380" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9762,7 +9736,7 @@
       <c r="C381" t="s">
         <v>138</v>
       </c>
-      <c r="H381" s="2">
+      <c r="H381" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9776,7 +9750,7 @@
       <c r="C382" t="s">
         <v>138</v>
       </c>
-      <c r="H382" s="2">
+      <c r="H382" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9790,7 +9764,7 @@
       <c r="C383" t="s">
         <v>138</v>
       </c>
-      <c r="H383" s="2">
+      <c r="H383" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9804,7 +9778,7 @@
       <c r="C384" t="s">
         <v>142</v>
       </c>
-      <c r="H384" s="2">
+      <c r="H384" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9818,7 +9792,7 @@
       <c r="C385" t="s">
         <v>142</v>
       </c>
-      <c r="H385" s="2">
+      <c r="H385" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9835,13 +9809,13 @@
       <c r="D386" t="s">
         <v>148</v>
       </c>
-      <c r="E386" s="2">
+      <c r="E386" s="1">
         <v>46234</v>
       </c>
       <c r="G386" t="s">
         <v>243</v>
       </c>
-      <c r="H386" s="2">
+      <c r="H386" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9855,7 +9829,7 @@
       <c r="C387" t="s">
         <v>138</v>
       </c>
-      <c r="H387" s="2">
+      <c r="H387" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9869,7 +9843,7 @@
       <c r="C388" t="s">
         <v>142</v>
       </c>
-      <c r="H388" s="2">
+      <c r="H388" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9883,7 +9857,7 @@
       <c r="C389" t="s">
         <v>138</v>
       </c>
-      <c r="H389" s="2">
+      <c r="H389" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9897,7 +9871,7 @@
       <c r="C390" t="s">
         <v>138</v>
       </c>
-      <c r="H390" s="2">
+      <c r="H390" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9914,13 +9888,13 @@
       <c r="D391" t="s">
         <v>196</v>
       </c>
-      <c r="E391" s="2">
+      <c r="E391" s="1">
         <v>46227</v>
       </c>
       <c r="G391" t="s">
         <v>244</v>
       </c>
-      <c r="H391" s="2">
+      <c r="H391" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9937,13 +9911,13 @@
       <c r="D392" t="s">
         <v>151</v>
       </c>
-      <c r="E392" s="2">
+      <c r="E392" s="1">
         <v>46237</v>
       </c>
       <c r="G392" t="s">
         <v>245</v>
       </c>
-      <c r="H392" s="2">
+      <c r="H392" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9957,7 +9931,7 @@
       <c r="C393" t="s">
         <v>138</v>
       </c>
-      <c r="H393" s="2">
+      <c r="H393" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9974,13 +9948,13 @@
       <c r="D394" t="s">
         <v>183</v>
       </c>
-      <c r="E394" s="2">
+      <c r="E394" s="1">
         <v>46227</v>
       </c>
       <c r="G394" t="s">
         <v>244</v>
       </c>
-      <c r="H394" s="2">
+      <c r="H394" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9994,7 +9968,7 @@
       <c r="C395" t="s">
         <v>138</v>
       </c>
-      <c r="H395" s="2">
+      <c r="H395" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10008,7 +9982,7 @@
       <c r="C396" t="s">
         <v>138</v>
       </c>
-      <c r="H396" s="2">
+      <c r="H396" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10025,13 +9999,13 @@
       <c r="D397" t="s">
         <v>188</v>
       </c>
-      <c r="E397" s="2">
+      <c r="E397" s="1">
         <v>46234</v>
       </c>
       <c r="G397" t="s">
         <v>243</v>
       </c>
-      <c r="H397" s="2">
+      <c r="H397" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10048,13 +10022,13 @@
       <c r="D398" t="s">
         <v>195</v>
       </c>
-      <c r="E398" s="2">
+      <c r="E398" s="1">
         <v>46227</v>
       </c>
       <c r="G398" t="s">
         <v>244</v>
       </c>
-      <c r="H398" s="2">
+      <c r="H398" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10071,7 +10045,7 @@
       <c r="D399" t="s">
         <v>194</v>
       </c>
-      <c r="H399" s="2">
+      <c r="H399" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10085,7 +10059,7 @@
       <c r="C400" t="s">
         <v>138</v>
       </c>
-      <c r="H400" s="2">
+      <c r="H400" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10108,7 +10082,7 @@
       <c r="G401" t="s">
         <v>213</v>
       </c>
-      <c r="H401" s="2">
+      <c r="H401" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10125,7 +10099,7 @@
       <c r="D402" t="s">
         <v>155</v>
       </c>
-      <c r="H402" s="2">
+      <c r="H402" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10148,7 +10122,7 @@
       <c r="G403" t="s">
         <v>214</v>
       </c>
-      <c r="H403" s="2">
+      <c r="H403" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10165,13 +10139,13 @@
       <c r="D404" t="s">
         <v>177</v>
       </c>
-      <c r="E404" s="2">
+      <c r="E404" s="1">
         <v>46295</v>
       </c>
       <c r="G404" t="s">
         <v>240</v>
       </c>
-      <c r="H404" s="2">
+      <c r="H404" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10194,7 +10168,7 @@
       <c r="G405" t="s">
         <v>215</v>
       </c>
-      <c r="H405" s="2">
+      <c r="H405" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10217,7 +10191,7 @@
       <c r="G406" t="s">
         <v>215</v>
       </c>
-      <c r="H406" s="2">
+      <c r="H406" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10240,7 +10214,7 @@
       <c r="G407" t="s">
         <v>216</v>
       </c>
-      <c r="H407" s="2">
+      <c r="H407" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10254,7 +10228,7 @@
       <c r="C408" t="s">
         <v>138</v>
       </c>
-      <c r="H408" s="2">
+      <c r="H408" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10271,13 +10245,13 @@
       <c r="D409" t="s">
         <v>165</v>
       </c>
-      <c r="E409" s="2">
+      <c r="E409" s="1">
         <v>46231</v>
       </c>
       <c r="G409" t="s">
         <v>246</v>
       </c>
-      <c r="H409" s="2">
+      <c r="H409" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10291,7 +10265,7 @@
       <c r="C410" t="s">
         <v>138</v>
       </c>
-      <c r="H410" s="2">
+      <c r="H410" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10305,7 +10279,7 @@
       <c r="C411" t="s">
         <v>138</v>
       </c>
-      <c r="H411" s="2">
+      <c r="H411" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10319,7 +10293,7 @@
       <c r="C412" t="s">
         <v>138</v>
       </c>
-      <c r="H412" s="2">
+      <c r="H412" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10333,7 +10307,7 @@
       <c r="C413" t="s">
         <v>142</v>
       </c>
-      <c r="H413" s="2">
+      <c r="H413" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10347,7 +10321,7 @@
       <c r="C414" t="s">
         <v>142</v>
       </c>
-      <c r="H414" s="2">
+      <c r="H414" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10364,13 +10338,13 @@
       <c r="D415" t="s">
         <v>197</v>
       </c>
-      <c r="E415" s="2">
+      <c r="E415" s="1">
         <v>46234</v>
       </c>
       <c r="G415" t="s">
         <v>243</v>
       </c>
-      <c r="H415" s="2">
+      <c r="H415" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10384,7 +10358,7 @@
       <c r="C416" t="s">
         <v>138</v>
       </c>
-      <c r="H416" s="2">
+      <c r="H416" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10398,7 +10372,7 @@
       <c r="C417" t="s">
         <v>142</v>
       </c>
-      <c r="H417" s="2">
+      <c r="H417" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10412,7 +10386,7 @@
       <c r="C418" t="s">
         <v>138</v>
       </c>
-      <c r="H418" s="2">
+      <c r="H418" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10426,7 +10400,7 @@
       <c r="C419" t="s">
         <v>138</v>
       </c>
-      <c r="H419" s="2">
+      <c r="H419" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10443,13 +10417,13 @@
       <c r="D420" t="s">
         <v>151</v>
       </c>
-      <c r="E420" s="2">
+      <c r="E420" s="1">
         <v>46237</v>
       </c>
       <c r="G420" t="s">
         <v>245</v>
       </c>
-      <c r="H420" s="2">
+      <c r="H420" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10463,7 +10437,7 @@
       <c r="C421" t="s">
         <v>138</v>
       </c>
-      <c r="H421" s="2">
+      <c r="H421" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10480,13 +10454,13 @@
       <c r="D422" t="s">
         <v>183</v>
       </c>
-      <c r="E422" s="2">
+      <c r="E422" s="1">
         <v>46227</v>
       </c>
       <c r="G422" t="s">
         <v>244</v>
       </c>
-      <c r="H422" s="2">
+      <c r="H422" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10500,7 +10474,7 @@
       <c r="C423" t="s">
         <v>138</v>
       </c>
-      <c r="H423" s="2">
+      <c r="H423" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10514,7 +10488,7 @@
       <c r="C424" t="s">
         <v>138</v>
       </c>
-      <c r="H424" s="2">
+      <c r="H424" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10531,13 +10505,13 @@
       <c r="D425" t="s">
         <v>188</v>
       </c>
-      <c r="E425" s="2">
+      <c r="E425" s="1">
         <v>46234</v>
       </c>
       <c r="G425" t="s">
         <v>243</v>
       </c>
-      <c r="H425" s="2">
+      <c r="H425" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10554,13 +10528,13 @@
       <c r="D426" t="s">
         <v>195</v>
       </c>
-      <c r="E426" s="2">
+      <c r="E426" s="1">
         <v>46227</v>
       </c>
       <c r="G426" t="s">
         <v>244</v>
       </c>
-      <c r="H426" s="2">
+      <c r="H426" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10577,7 +10551,7 @@
       <c r="D427" t="s">
         <v>194</v>
       </c>
-      <c r="H427" s="2">
+      <c r="H427" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10591,7 +10565,7 @@
       <c r="C428" t="s">
         <v>138</v>
       </c>
-      <c r="H428" s="2">
+      <c r="H428" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10614,7 +10588,7 @@
       <c r="G429" t="s">
         <v>213</v>
       </c>
-      <c r="H429" s="2">
+      <c r="H429" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10631,7 +10605,7 @@
       <c r="D430" t="s">
         <v>155</v>
       </c>
-      <c r="H430" s="2">
+      <c r="H430" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10654,7 +10628,7 @@
       <c r="G431" t="s">
         <v>214</v>
       </c>
-      <c r="H431" s="2">
+      <c r="H431" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10671,13 +10645,13 @@
       <c r="D432" t="s">
         <v>177</v>
       </c>
-      <c r="E432" s="2">
+      <c r="E432" s="1">
         <v>46295</v>
       </c>
       <c r="G432" t="s">
         <v>240</v>
       </c>
-      <c r="H432" s="2">
+      <c r="H432" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10700,7 +10674,7 @@
       <c r="G433" t="s">
         <v>215</v>
       </c>
-      <c r="H433" s="2">
+      <c r="H433" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10723,7 +10697,7 @@
       <c r="G434" t="s">
         <v>215</v>
       </c>
-      <c r="H434" s="2">
+      <c r="H434" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10746,7 +10720,7 @@
       <c r="G435" t="s">
         <v>216</v>
       </c>
-      <c r="H435" s="2">
+      <c r="H435" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10763,13 +10737,13 @@
       <c r="D436" t="s">
         <v>198</v>
       </c>
-      <c r="E436" s="2">
+      <c r="E436" s="1">
         <v>46230</v>
       </c>
       <c r="G436" t="s">
         <v>247</v>
       </c>
-      <c r="H436" s="2">
+      <c r="H436" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10783,7 +10757,7 @@
       <c r="C437" t="s">
         <v>138</v>
       </c>
-      <c r="H437" s="2">
+      <c r="H437" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10800,13 +10774,13 @@
       <c r="D438" t="s">
         <v>165</v>
       </c>
-      <c r="E438" s="2">
+      <c r="E438" s="1">
         <v>46231</v>
       </c>
       <c r="G438" t="s">
         <v>246</v>
       </c>
-      <c r="H438" s="2">
+      <c r="H438" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10820,7 +10794,7 @@
       <c r="C439" t="s">
         <v>138</v>
       </c>
-      <c r="H439" s="2">
+      <c r="H439" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10834,7 +10808,7 @@
       <c r="C440" t="s">
         <v>138</v>
       </c>
-      <c r="H440" s="2">
+      <c r="H440" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10848,7 +10822,7 @@
       <c r="C441" t="s">
         <v>138</v>
       </c>
-      <c r="H441" s="2">
+      <c r="H441" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10862,7 +10836,7 @@
       <c r="C442" t="s">
         <v>142</v>
       </c>
-      <c r="H442" s="2">
+      <c r="H442" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10876,7 +10850,7 @@
       <c r="C443" t="s">
         <v>142</v>
       </c>
-      <c r="H443" s="2">
+      <c r="H443" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10893,13 +10867,13 @@
       <c r="D444" t="s">
         <v>197</v>
       </c>
-      <c r="E444" s="2">
+      <c r="E444" s="1">
         <v>46234</v>
       </c>
       <c r="G444" t="s">
         <v>243</v>
       </c>
-      <c r="H444" s="2">
+      <c r="H444" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10913,7 +10887,7 @@
       <c r="C445" t="s">
         <v>138</v>
       </c>
-      <c r="H445" s="2">
+      <c r="H445" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10930,13 +10904,13 @@
       <c r="D446" t="s">
         <v>199</v>
       </c>
-      <c r="E446" s="2">
+      <c r="E446" s="1">
         <v>46230</v>
       </c>
       <c r="G446" t="s">
         <v>247</v>
       </c>
-      <c r="H446" s="2">
+      <c r="H446" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10950,7 +10924,7 @@
       <c r="C447" t="s">
         <v>138</v>
       </c>
-      <c r="H447" s="2">
+      <c r="H447" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10964,7 +10938,7 @@
       <c r="C448" t="s">
         <v>138</v>
       </c>
-      <c r="H448" s="2">
+      <c r="H448" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10981,13 +10955,13 @@
       <c r="D449" t="s">
         <v>151</v>
       </c>
-      <c r="E449" s="2">
+      <c r="E449" s="1">
         <v>46237</v>
       </c>
       <c r="G449" t="s">
         <v>245</v>
       </c>
-      <c r="H449" s="2">
+      <c r="H449" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11001,7 +10975,7 @@
       <c r="C450" t="s">
         <v>138</v>
       </c>
-      <c r="H450" s="2">
+      <c r="H450" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11015,7 +10989,7 @@
       <c r="C451" t="s">
         <v>138</v>
       </c>
-      <c r="H451" s="2">
+      <c r="H451" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11029,7 +11003,7 @@
       <c r="C452" t="s">
         <v>138</v>
       </c>
-      <c r="H452" s="2">
+      <c r="H452" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11043,7 +11017,7 @@
       <c r="C453" t="s">
         <v>138</v>
       </c>
-      <c r="H453" s="2">
+      <c r="H453" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11060,13 +11034,13 @@
       <c r="D454" t="s">
         <v>188</v>
       </c>
-      <c r="E454" s="2">
+      <c r="E454" s="1">
         <v>46234</v>
       </c>
       <c r="G454" t="s">
         <v>243</v>
       </c>
-      <c r="H454" s="2">
+      <c r="H454" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11080,7 +11054,7 @@
       <c r="C455" t="s">
         <v>142</v>
       </c>
-      <c r="H455" s="2">
+      <c r="H455" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11097,7 +11071,7 @@
       <c r="D456" t="s">
         <v>194</v>
       </c>
-      <c r="H456" s="2">
+      <c r="H456" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11111,7 +11085,7 @@
       <c r="C457" t="s">
         <v>138</v>
       </c>
-      <c r="H457" s="2">
+      <c r="H457" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11134,7 +11108,7 @@
       <c r="G458" t="s">
         <v>213</v>
       </c>
-      <c r="H458" s="2">
+      <c r="H458" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11151,7 +11125,7 @@
       <c r="D459" t="s">
         <v>155</v>
       </c>
-      <c r="H459" s="2">
+      <c r="H459" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11174,7 +11148,7 @@
       <c r="G460" t="s">
         <v>214</v>
       </c>
-      <c r="H460" s="2">
+      <c r="H460" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11191,13 +11165,13 @@
       <c r="D461" t="s">
         <v>177</v>
       </c>
-      <c r="E461" s="2">
+      <c r="E461" s="1">
         <v>46295</v>
       </c>
       <c r="G461" t="s">
         <v>240</v>
       </c>
-      <c r="H461" s="2">
+      <c r="H461" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11220,7 +11194,7 @@
       <c r="G462" t="s">
         <v>215</v>
       </c>
-      <c r="H462" s="2">
+      <c r="H462" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11243,7 +11217,7 @@
       <c r="G463" t="s">
         <v>215</v>
       </c>
-      <c r="H463" s="2">
+      <c r="H463" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11266,7 +11240,7 @@
       <c r="G464" t="s">
         <v>216</v>
       </c>
-      <c r="H464" s="2">
+      <c r="H464" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11283,13 +11257,13 @@
       <c r="D465" t="s">
         <v>198</v>
       </c>
-      <c r="E465" s="2">
+      <c r="E465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
         <v>247</v>
       </c>
-      <c r="H465" s="2">
+      <c r="H465" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11306,13 +11280,13 @@
       <c r="D466" t="s">
         <v>200</v>
       </c>
-      <c r="E466" s="2">
+      <c r="E466" s="1">
         <v>46231</v>
       </c>
       <c r="G466" t="s">
         <v>246</v>
       </c>
-      <c r="H466" s="2">
+      <c r="H466" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11329,13 +11303,13 @@
       <c r="D467" t="s">
         <v>165</v>
       </c>
-      <c r="E467" s="2">
+      <c r="E467" s="1">
         <v>46231</v>
       </c>
       <c r="G467" t="s">
         <v>246</v>
       </c>
-      <c r="H467" s="2">
+      <c r="H467" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11349,7 +11323,7 @@
       <c r="C468" t="s">
         <v>138</v>
       </c>
-      <c r="H468" s="2">
+      <c r="H468" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11363,7 +11337,7 @@
       <c r="C469" t="s">
         <v>138</v>
       </c>
-      <c r="H469" s="2">
+      <c r="H469" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11377,7 +11351,7 @@
       <c r="C470" t="s">
         <v>138</v>
       </c>
-      <c r="H470" s="2">
+      <c r="H470" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11391,7 +11365,7 @@
       <c r="C471" t="s">
         <v>142</v>
       </c>
-      <c r="H471" s="2">
+      <c r="H471" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11405,7 +11379,7 @@
       <c r="C472" t="s">
         <v>142</v>
       </c>
-      <c r="H472" s="2">
+      <c r="H472" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11422,13 +11396,13 @@
       <c r="D473" t="s">
         <v>197</v>
       </c>
-      <c r="E473" s="2">
+      <c r="E473" s="1">
         <v>46234</v>
       </c>
       <c r="G473" t="s">
         <v>243</v>
       </c>
-      <c r="H473" s="2">
+      <c r="H473" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11442,7 +11416,7 @@
       <c r="C474" t="s">
         <v>138</v>
       </c>
-      <c r="H474" s="2">
+      <c r="H474" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11459,13 +11433,13 @@
       <c r="D475" t="s">
         <v>201</v>
       </c>
-      <c r="E475" s="2">
+      <c r="E475" s="1">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
         <v>246</v>
       </c>
-      <c r="H475" s="2">
+      <c r="H475" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11479,7 +11453,7 @@
       <c r="C476" t="s">
         <v>138</v>
       </c>
-      <c r="H476" s="2">
+      <c r="H476" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11493,7 +11467,7 @@
       <c r="C477" t="s">
         <v>138</v>
       </c>
-      <c r="H477" s="2">
+      <c r="H477" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11510,13 +11484,13 @@
       <c r="D478" t="s">
         <v>151</v>
       </c>
-      <c r="E478" s="2">
+      <c r="E478" s="1">
         <v>46237</v>
       </c>
       <c r="G478" t="s">
         <v>245</v>
       </c>
-      <c r="H478" s="2">
+      <c r="H478" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11530,7 +11504,7 @@
       <c r="C479" t="s">
         <v>138</v>
       </c>
-      <c r="H479" s="2">
+      <c r="H479" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11544,7 +11518,7 @@
       <c r="C480" t="s">
         <v>138</v>
       </c>
-      <c r="H480" s="2">
+      <c r="H480" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11558,7 +11532,7 @@
       <c r="C481" t="s">
         <v>138</v>
       </c>
-      <c r="H481" s="2">
+      <c r="H481" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11572,7 +11546,7 @@
       <c r="C482" t="s">
         <v>138</v>
       </c>
-      <c r="H482" s="2">
+      <c r="H482" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11589,13 +11563,13 @@
       <c r="D483" t="s">
         <v>188</v>
       </c>
-      <c r="E483" s="2">
+      <c r="E483" s="1">
         <v>46234</v>
       </c>
       <c r="G483" t="s">
         <v>243</v>
       </c>
-      <c r="H483" s="2">
+      <c r="H483" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11609,7 +11583,7 @@
       <c r="C484" t="s">
         <v>142</v>
       </c>
-      <c r="H484" s="2">
+      <c r="H484" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11626,7 +11600,7 @@
       <c r="D485" t="s">
         <v>194</v>
       </c>
-      <c r="H485" s="2">
+      <c r="H485" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11640,7 +11614,7 @@
       <c r="C486" t="s">
         <v>138</v>
       </c>
-      <c r="H486" s="2">
+      <c r="H486" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11663,7 +11637,7 @@
       <c r="G487" t="s">
         <v>213</v>
       </c>
-      <c r="H487" s="2">
+      <c r="H487" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11680,7 +11654,7 @@
       <c r="D488" t="s">
         <v>155</v>
       </c>
-      <c r="H488" s="2">
+      <c r="H488" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11703,7 +11677,7 @@
       <c r="G489" t="s">
         <v>214</v>
       </c>
-      <c r="H489" s="2">
+      <c r="H489" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11720,13 +11694,13 @@
       <c r="D490" t="s">
         <v>177</v>
       </c>
-      <c r="E490" s="2">
+      <c r="E490" s="1">
         <v>46295</v>
       </c>
       <c r="G490" t="s">
         <v>240</v>
       </c>
-      <c r="H490" s="2">
+      <c r="H490" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11749,7 +11723,7 @@
       <c r="G491" t="s">
         <v>215</v>
       </c>
-      <c r="H491" s="2">
+      <c r="H491" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11772,7 +11746,7 @@
       <c r="G492" t="s">
         <v>215</v>
       </c>
-      <c r="H492" s="2">
+      <c r="H492" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11795,7 +11769,7 @@
       <c r="G493" t="s">
         <v>216</v>
       </c>
-      <c r="H493" s="2">
+      <c r="H493" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11812,13 +11786,13 @@
       <c r="D494" t="s">
         <v>198</v>
       </c>
-      <c r="E494" s="2">
+      <c r="E494" s="1">
         <v>46233</v>
       </c>
       <c r="G494" t="s">
         <v>248</v>
       </c>
-      <c r="H494" s="2">
+      <c r="H494" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11832,7 +11806,7 @@
       <c r="C495" t="s">
         <v>138</v>
       </c>
-      <c r="H495" s="2">
+      <c r="H495" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11849,13 +11823,13 @@
       <c r="D496" t="s">
         <v>202</v>
       </c>
-      <c r="E496" s="2">
+      <c r="E496" s="1">
         <v>46233</v>
       </c>
       <c r="G496" t="s">
         <v>249</v>
       </c>
-      <c r="H496" s="2">
+      <c r="H496" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11869,7 +11843,7 @@
       <c r="C497" t="s">
         <v>138</v>
       </c>
-      <c r="H497" s="2">
+      <c r="H497" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11883,7 +11857,7 @@
       <c r="C498" t="s">
         <v>138</v>
       </c>
-      <c r="H498" s="2">
+      <c r="H498" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11897,7 +11871,7 @@
       <c r="C499" t="s">
         <v>138</v>
       </c>
-      <c r="H499" s="2">
+      <c r="H499" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11911,7 +11885,7 @@
       <c r="C500" t="s">
         <v>142</v>
       </c>
-      <c r="H500" s="2">
+      <c r="H500" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11925,7 +11899,7 @@
       <c r="C501" t="s">
         <v>142</v>
       </c>
-      <c r="H501" s="2">
+      <c r="H501" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11942,13 +11916,13 @@
       <c r="D502" t="s">
         <v>197</v>
       </c>
-      <c r="E502" s="2">
+      <c r="E502" s="1">
         <v>46248</v>
       </c>
       <c r="G502" t="s">
         <v>250</v>
       </c>
-      <c r="H502" s="2">
+      <c r="H502" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11962,7 +11936,7 @@
       <c r="C503" t="s">
         <v>138</v>
       </c>
-      <c r="H503" s="2">
+      <c r="H503" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11976,7 +11950,7 @@
       <c r="C504" t="s">
         <v>142</v>
       </c>
-      <c r="H504" s="2">
+      <c r="H504" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11990,7 +11964,7 @@
       <c r="C505" t="s">
         <v>138</v>
       </c>
-      <c r="H505" s="2">
+      <c r="H505" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12004,7 +11978,7 @@
       <c r="C506" t="s">
         <v>138</v>
       </c>
-      <c r="H506" s="2">
+      <c r="H506" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12021,13 +11995,13 @@
       <c r="D507" t="s">
         <v>151</v>
       </c>
-      <c r="E507" s="2">
+      <c r="E507" s="1">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
         <v>234</v>
       </c>
-      <c r="H507" s="2">
+      <c r="H507" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12041,7 +12015,7 @@
       <c r="C508" t="s">
         <v>138</v>
       </c>
-      <c r="H508" s="2">
+      <c r="H508" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12055,7 +12029,7 @@
       <c r="C509" t="s">
         <v>138</v>
       </c>
-      <c r="H509" s="2">
+      <c r="H509" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12069,7 +12043,7 @@
       <c r="C510" t="s">
         <v>138</v>
       </c>
-      <c r="H510" s="2">
+      <c r="H510" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12083,7 +12057,7 @@
       <c r="C511" t="s">
         <v>138</v>
       </c>
-      <c r="H511" s="2">
+      <c r="H511" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12100,13 +12074,13 @@
       <c r="D512" t="s">
         <v>203</v>
       </c>
-      <c r="E512" s="2">
+      <c r="E512" s="1">
         <v>46234</v>
       </c>
       <c r="G512" t="s">
         <v>221</v>
       </c>
-      <c r="H512" s="2">
+      <c r="H512" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12123,13 +12097,13 @@
       <c r="D513" t="s">
         <v>204</v>
       </c>
-      <c r="E513" s="2">
+      <c r="E513" s="1">
         <v>46238</v>
       </c>
       <c r="G513" t="s">
         <v>251</v>
       </c>
-      <c r="H513" s="2">
+      <c r="H513" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12143,7 +12117,7 @@
       <c r="C514" t="s">
         <v>142</v>
       </c>
-      <c r="H514" s="2">
+      <c r="H514" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12157,7 +12131,7 @@
       <c r="C515" t="s">
         <v>138</v>
       </c>
-      <c r="H515" s="2">
+      <c r="H515" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12180,7 +12154,7 @@
       <c r="G516" t="s">
         <v>213</v>
       </c>
-      <c r="H516" s="2">
+      <c r="H516" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12197,7 +12171,7 @@
       <c r="D517" t="s">
         <v>155</v>
       </c>
-      <c r="H517" s="2">
+      <c r="H517" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12220,7 +12194,7 @@
       <c r="G518" t="s">
         <v>214</v>
       </c>
-      <c r="H518" s="2">
+      <c r="H518" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12237,13 +12211,13 @@
       <c r="D519" t="s">
         <v>177</v>
       </c>
-      <c r="E519" s="2">
+      <c r="E519" s="1">
         <v>46295</v>
       </c>
       <c r="G519" t="s">
         <v>232</v>
       </c>
-      <c r="H519" s="2">
+      <c r="H519" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12266,7 +12240,7 @@
       <c r="G520" t="s">
         <v>215</v>
       </c>
-      <c r="H520" s="2">
+      <c r="H520" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12289,7 +12263,7 @@
       <c r="G521" t="s">
         <v>215</v>
       </c>
-      <c r="H521" s="2">
+      <c r="H521" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12312,7 +12286,7 @@
       <c r="G522" t="s">
         <v>216</v>
       </c>
-      <c r="H522" s="2">
+      <c r="H522" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12329,13 +12303,13 @@
       <c r="D523" t="s">
         <v>205</v>
       </c>
-      <c r="E523" s="2">
+      <c r="E523" s="1">
         <v>46233</v>
       </c>
       <c r="G523" t="s">
         <v>248</v>
       </c>
-      <c r="H523" s="2">
+      <c r="H523" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12349,7 +12323,7 @@
       <c r="C524" t="s">
         <v>138</v>
       </c>
-      <c r="H524" s="2">
+      <c r="H524" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12366,13 +12340,13 @@
       <c r="D525" t="s">
         <v>202</v>
       </c>
-      <c r="E525" s="2">
+      <c r="E525" s="1">
         <v>46233</v>
       </c>
       <c r="G525" t="s">
         <v>249</v>
       </c>
-      <c r="H525" s="2">
+      <c r="H525" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12386,7 +12360,7 @@
       <c r="C526" t="s">
         <v>138</v>
       </c>
-      <c r="H526" s="2">
+      <c r="H526" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12400,7 +12374,7 @@
       <c r="C527" t="s">
         <v>138</v>
       </c>
-      <c r="H527" s="2">
+      <c r="H527" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12414,7 +12388,7 @@
       <c r="C528" t="s">
         <v>138</v>
       </c>
-      <c r="H528" s="2">
+      <c r="H528" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12428,7 +12402,7 @@
       <c r="C529" t="s">
         <v>142</v>
       </c>
-      <c r="H529" s="2">
+      <c r="H529" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12442,7 +12416,7 @@
       <c r="C530" t="s">
         <v>142</v>
       </c>
-      <c r="H530" s="2">
+      <c r="H530" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12459,13 +12433,13 @@
       <c r="D531" t="s">
         <v>197</v>
       </c>
-      <c r="E531" s="2">
+      <c r="E531" s="1">
         <v>46248</v>
       </c>
       <c r="G531" t="s">
         <v>250</v>
       </c>
-      <c r="H531" s="2">
+      <c r="H531" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12479,7 +12453,7 @@
       <c r="C532" t="s">
         <v>138</v>
       </c>
-      <c r="H532" s="2">
+      <c r="H532" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12493,7 +12467,7 @@
       <c r="C533" t="s">
         <v>142</v>
       </c>
-      <c r="H533" s="2">
+      <c r="H533" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12507,7 +12481,7 @@
       <c r="C534" t="s">
         <v>138</v>
       </c>
-      <c r="H534" s="2">
+      <c r="H534" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12521,7 +12495,7 @@
       <c r="C535" t="s">
         <v>138</v>
       </c>
-      <c r="H535" s="2">
+      <c r="H535" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12538,13 +12512,13 @@
       <c r="D536" t="s">
         <v>151</v>
       </c>
-      <c r="E536" s="2">
+      <c r="E536" s="1">
         <v>46237</v>
       </c>
       <c r="G536" t="s">
         <v>234</v>
       </c>
-      <c r="H536" s="2">
+      <c r="H536" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12558,7 +12532,7 @@
       <c r="C537" t="s">
         <v>138</v>
       </c>
-      <c r="H537" s="2">
+      <c r="H537" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12572,7 +12546,7 @@
       <c r="C538" t="s">
         <v>138</v>
       </c>
-      <c r="H538" s="2">
+      <c r="H538" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12586,7 +12560,7 @@
       <c r="C539" t="s">
         <v>138</v>
       </c>
-      <c r="H539" s="2">
+      <c r="H539" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12600,7 +12574,7 @@
       <c r="C540" t="s">
         <v>138</v>
       </c>
-      <c r="H540" s="2">
+      <c r="H540" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12614,7 +12588,7 @@
       <c r="C541" t="s">
         <v>142</v>
       </c>
-      <c r="H541" s="2">
+      <c r="H541" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12631,13 +12605,13 @@
       <c r="D542" t="s">
         <v>204</v>
       </c>
-      <c r="E542" s="2">
+      <c r="E542" s="1">
         <v>46238</v>
       </c>
       <c r="G542" t="s">
         <v>251</v>
       </c>
-      <c r="H542" s="2">
+      <c r="H542" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12651,7 +12625,7 @@
       <c r="C543" t="s">
         <v>142</v>
       </c>
-      <c r="H543" s="2">
+      <c r="H543" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12665,7 +12639,7 @@
       <c r="C544" t="s">
         <v>138</v>
       </c>
-      <c r="H544" s="2">
+      <c r="H544" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12688,7 +12662,7 @@
       <c r="G545" t="s">
         <v>213</v>
       </c>
-      <c r="H545" s="2">
+      <c r="H545" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12705,7 +12679,7 @@
       <c r="D546" t="s">
         <v>155</v>
       </c>
-      <c r="H546" s="2">
+      <c r="H546" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12728,7 +12702,7 @@
       <c r="G547" t="s">
         <v>214</v>
       </c>
-      <c r="H547" s="2">
+      <c r="H547" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12745,13 +12719,13 @@
       <c r="D548" t="s">
         <v>177</v>
       </c>
-      <c r="E548" s="2">
+      <c r="E548" s="1">
         <v>46295</v>
       </c>
       <c r="G548" t="s">
         <v>232</v>
       </c>
-      <c r="H548" s="2">
+      <c r="H548" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12774,7 +12748,7 @@
       <c r="G549" t="s">
         <v>215</v>
       </c>
-      <c r="H549" s="2">
+      <c r="H549" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12797,7 +12771,7 @@
       <c r="G550" t="s">
         <v>215</v>
       </c>
-      <c r="H550" s="2">
+      <c r="H550" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12820,7 +12794,7 @@
       <c r="G551" t="s">
         <v>216</v>
       </c>
-      <c r="H551" s="2">
+      <c r="H551" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12837,13 +12811,13 @@
       <c r="D552" t="s">
         <v>206</v>
       </c>
-      <c r="E552" s="2">
+      <c r="E552" s="1">
         <v>46233</v>
       </c>
       <c r="G552" t="s">
         <v>248</v>
       </c>
-      <c r="H552" s="2">
+      <c r="H552" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12857,7 +12831,7 @@
       <c r="C553" t="s">
         <v>138</v>
       </c>
-      <c r="H553" s="2">
+      <c r="H553" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12880,7 +12854,7 @@
       <c r="G554" t="s">
         <v>211</v>
       </c>
-      <c r="H554" s="2">
+      <c r="H554" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12894,7 +12868,7 @@
       <c r="C555" t="s">
         <v>138</v>
       </c>
-      <c r="H555" s="2">
+      <c r="H555" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12908,7 +12882,7 @@
       <c r="C556" t="s">
         <v>138</v>
       </c>
-      <c r="H556" s="2">
+      <c r="H556" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12922,7 +12896,7 @@
       <c r="C557" t="s">
         <v>138</v>
       </c>
-      <c r="H557" s="2">
+      <c r="H557" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12936,7 +12910,7 @@
       <c r="C558" t="s">
         <v>142</v>
       </c>
-      <c r="H558" s="2">
+      <c r="H558" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12950,7 +12924,7 @@
       <c r="C559" t="s">
         <v>142</v>
       </c>
-      <c r="H559" s="2">
+      <c r="H559" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12967,13 +12941,13 @@
       <c r="D560" t="s">
         <v>197</v>
       </c>
-      <c r="E560" s="2">
+      <c r="E560" s="1">
         <v>46248</v>
       </c>
       <c r="G560" t="s">
         <v>250</v>
       </c>
-      <c r="H560" s="2">
+      <c r="H560" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12987,7 +12961,7 @@
       <c r="C561" t="s">
         <v>138</v>
       </c>
-      <c r="H561" s="2">
+      <c r="H561" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13001,7 +12975,7 @@
       <c r="C562" t="s">
         <v>142</v>
       </c>
-      <c r="H562" s="2">
+      <c r="H562" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13015,7 +12989,7 @@
       <c r="C563" t="s">
         <v>138</v>
       </c>
-      <c r="H563" s="2">
+      <c r="H563" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13029,7 +13003,7 @@
       <c r="C564" t="s">
         <v>138</v>
       </c>
-      <c r="H564" s="2">
+      <c r="H564" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13043,7 +13017,7 @@
       <c r="C565" t="s">
         <v>138</v>
       </c>
-      <c r="H565" s="2">
+      <c r="H565" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13060,13 +13034,13 @@
       <c r="D566" t="s">
         <v>151</v>
       </c>
-      <c r="E566" s="2">
+      <c r="E566" s="1">
         <v>46262</v>
       </c>
       <c r="G566" t="s">
         <v>252</v>
       </c>
-      <c r="H566" s="2">
+      <c r="H566" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13080,7 +13054,7 @@
       <c r="C567" t="s">
         <v>138</v>
       </c>
-      <c r="H567" s="2">
+      <c r="H567" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13094,7 +13068,7 @@
       <c r="C568" t="s">
         <v>138</v>
       </c>
-      <c r="H568" s="2">
+      <c r="H568" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13108,7 +13082,7 @@
       <c r="C569" t="s">
         <v>138</v>
       </c>
-      <c r="H569" s="2">
+      <c r="H569" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13122,7 +13096,7 @@
       <c r="C570" t="s">
         <v>138</v>
       </c>
-      <c r="H570" s="2">
+      <c r="H570" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13136,7 +13110,7 @@
       <c r="C571" t="s">
         <v>138</v>
       </c>
-      <c r="H571" s="2">
+      <c r="H571" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13153,13 +13127,13 @@
       <c r="D572" t="s">
         <v>204</v>
       </c>
-      <c r="E572" s="2">
+      <c r="E572" s="1">
         <v>46238</v>
       </c>
       <c r="G572" t="s">
         <v>251</v>
       </c>
-      <c r="H572" s="2">
+      <c r="H572" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13173,7 +13147,7 @@
       <c r="C573" t="s">
         <v>142</v>
       </c>
-      <c r="H573" s="2">
+      <c r="H573" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13187,7 +13161,7 @@
       <c r="C574" t="s">
         <v>138</v>
       </c>
-      <c r="H574" s="2">
+      <c r="H574" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13210,7 +13184,7 @@
       <c r="G575" t="s">
         <v>213</v>
       </c>
-      <c r="H575" s="2">
+      <c r="H575" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13227,7 +13201,7 @@
       <c r="D576" t="s">
         <v>155</v>
       </c>
-      <c r="H576" s="2">
+      <c r="H576" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13250,7 +13224,7 @@
       <c r="G577" t="s">
         <v>214</v>
       </c>
-      <c r="H577" s="2">
+      <c r="H577" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13267,13 +13241,13 @@
       <c r="D578" t="s">
         <v>177</v>
       </c>
-      <c r="E578" s="2">
+      <c r="E578" s="1">
         <v>46295</v>
       </c>
       <c r="G578" t="s">
         <v>232</v>
       </c>
-      <c r="H578" s="2">
+      <c r="H578" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13296,7 +13270,7 @@
       <c r="G579" t="s">
         <v>215</v>
       </c>
-      <c r="H579" s="2">
+      <c r="H579" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13319,7 +13293,7 @@
       <c r="G580" t="s">
         <v>215</v>
       </c>
-      <c r="H580" s="2">
+      <c r="H580" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13342,7 +13316,7 @@
       <c r="G581" t="s">
         <v>216</v>
       </c>
-      <c r="H581" s="2">
+      <c r="H581" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13356,7 +13330,7 @@
       <c r="C582" t="s">
         <v>138</v>
       </c>
-      <c r="H582" s="2">
+      <c r="H582" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13379,7 +13353,7 @@
       <c r="G583" t="s">
         <v>211</v>
       </c>
-      <c r="H583" s="2">
+      <c r="H583" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13393,7 +13367,7 @@
       <c r="C584" t="s">
         <v>138</v>
       </c>
-      <c r="H584" s="2">
+      <c r="H584" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13407,7 +13381,7 @@
       <c r="C585" t="s">
         <v>138</v>
       </c>
-      <c r="H585" s="2">
+      <c r="H585" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13421,7 +13395,7 @@
       <c r="C586" t="s">
         <v>142</v>
       </c>
-      <c r="H586" s="2">
+      <c r="H586" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13435,7 +13409,7 @@
       <c r="C587" t="s">
         <v>142</v>
       </c>
-      <c r="H587" s="2">
+      <c r="H587" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13452,13 +13426,13 @@
       <c r="D588" t="s">
         <v>197</v>
       </c>
-      <c r="E588" s="2">
+      <c r="E588" s="1">
         <v>46248</v>
       </c>
       <c r="G588" t="s">
         <v>250</v>
       </c>
-      <c r="H588" s="2">
+      <c r="H588" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13472,7 +13446,7 @@
       <c r="C589" t="s">
         <v>138</v>
       </c>
-      <c r="H589" s="2">
+      <c r="H589" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13486,7 +13460,7 @@
       <c r="C590" t="s">
         <v>142</v>
       </c>
-      <c r="H590" s="2">
+      <c r="H590" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13500,7 +13474,7 @@
       <c r="C591" t="s">
         <v>138</v>
       </c>
-      <c r="H591" s="2">
+      <c r="H591" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13514,7 +13488,7 @@
       <c r="C592" t="s">
         <v>138</v>
       </c>
-      <c r="H592" s="2">
+      <c r="H592" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13531,13 +13505,13 @@
       <c r="D593" t="s">
         <v>208</v>
       </c>
-      <c r="E593" s="2">
+      <c r="E593" s="1">
         <v>46240</v>
       </c>
       <c r="G593" t="s">
         <v>253</v>
       </c>
-      <c r="H593" s="2">
+      <c r="H593" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13554,13 +13528,13 @@
       <c r="D594" t="s">
         <v>151</v>
       </c>
-      <c r="E594" s="2">
+      <c r="E594" s="1">
         <v>46262</v>
       </c>
       <c r="G594" t="s">
         <v>252</v>
       </c>
-      <c r="H594" s="2">
+      <c r="H594" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13574,7 +13548,7 @@
       <c r="C595" t="s">
         <v>138</v>
       </c>
-      <c r="H595" s="2">
+      <c r="H595" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13588,7 +13562,7 @@
       <c r="C596" t="s">
         <v>138</v>
       </c>
-      <c r="H596" s="2">
+      <c r="H596" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13602,7 +13576,7 @@
       <c r="C597" t="s">
         <v>138</v>
       </c>
-      <c r="H597" s="2">
+      <c r="H597" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13616,7 +13590,7 @@
       <c r="C598" t="s">
         <v>138</v>
       </c>
-      <c r="H598" s="2">
+      <c r="H598" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13633,13 +13607,13 @@
       <c r="D599" t="s">
         <v>209</v>
       </c>
-      <c r="E599" s="2">
+      <c r="E599" s="1">
         <v>46237</v>
       </c>
       <c r="G599" t="s">
         <v>234</v>
       </c>
-      <c r="H599" s="2">
+      <c r="H599" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13656,13 +13630,13 @@
       <c r="D600" t="s">
         <v>210</v>
       </c>
-      <c r="E600" s="2">
+      <c r="E600" s="1">
         <v>46237</v>
       </c>
       <c r="G600" t="s">
         <v>234</v>
       </c>
-      <c r="H600" s="2">
+      <c r="H600" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13679,13 +13653,13 @@
       <c r="D601" t="s">
         <v>204</v>
       </c>
-      <c r="E601" s="2">
+      <c r="E601" s="1">
         <v>46238</v>
       </c>
       <c r="G601" t="s">
         <v>251</v>
       </c>
-      <c r="H601" s="2">
+      <c r="H601" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13699,7 +13673,7 @@
       <c r="C602" t="s">
         <v>142</v>
       </c>
-      <c r="H602" s="2">
+      <c r="H602" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13713,7 +13687,7 @@
       <c r="C603" t="s">
         <v>138</v>
       </c>
-      <c r="H603" s="2">
+      <c r="H603" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13736,7 +13710,7 @@
       <c r="G604" t="s">
         <v>213</v>
       </c>
-      <c r="H604" s="2">
+      <c r="H604" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13753,7 +13727,7 @@
       <c r="D605" t="s">
         <v>155</v>
       </c>
-      <c r="H605" s="2">
+      <c r="H605" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13776,7 +13750,7 @@
       <c r="G606" t="s">
         <v>214</v>
       </c>
-      <c r="H606" s="2">
+      <c r="H606" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13793,13 +13767,13 @@
       <c r="D607" t="s">
         <v>177</v>
       </c>
-      <c r="E607" s="2">
+      <c r="E607" s="1">
         <v>46295</v>
       </c>
       <c r="G607" t="s">
         <v>232</v>
       </c>
-      <c r="H607" s="2">
+      <c r="H607" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13822,7 +13796,7 @@
       <c r="G608" t="s">
         <v>215</v>
       </c>
-      <c r="H608" s="2">
+      <c r="H608" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13845,7 +13819,7 @@
       <c r="G609" t="s">
         <v>215</v>
       </c>
-      <c r="H609" s="2">
+      <c r="H609" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13868,7 +13842,7 @@
       <c r="G610" t="s">
         <v>216</v>
       </c>
-      <c r="H610" s="2">
+      <c r="H610" s="1">
         <v>46237</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -813,16 +813,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -838,7 +830,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -846,30 +838,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1169,72 +1143,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1299,7 +1273,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1364,7 +1338,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1429,7 +1403,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1494,7 +1468,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1559,7 +1533,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1624,7 +1598,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1689,7 +1663,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1754,7 +1728,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1819,7 +1793,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1884,7 +1858,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -1949,7 +1923,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -2014,7 +1988,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -2079,7 +2053,7 @@
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>46226</v>
       </c>
       <c r="B15">
@@ -2144,7 +2118,7 @@
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>46227</v>
       </c>
       <c r="B16">
@@ -2209,7 +2183,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>46230</v>
       </c>
       <c r="B17">
@@ -2274,7 +2248,7 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>46231</v>
       </c>
       <c r="B18">
@@ -2336,7 +2310,7 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>46232</v>
       </c>
       <c r="B19">
@@ -2401,7 +2375,7 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>46233</v>
       </c>
       <c r="B20">
@@ -2466,7 +2440,7 @@
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>46234</v>
       </c>
       <c r="B21">
@@ -2528,7 +2502,7 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>46237</v>
       </c>
       <c r="B22">
@@ -2590,7 +2564,7 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>46238</v>
       </c>
       <c r="B23">
@@ -2665,28 +2639,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2700,7 +2674,7 @@
       <c r="C2" t="s">
         <v>142</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2714,7 +2688,7 @@
       <c r="C3" t="s">
         <v>142</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2737,7 +2711,7 @@
       <c r="G4" t="s">
         <v>218</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2751,7 +2725,7 @@
       <c r="C5" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2765,7 +2739,7 @@
       <c r="C6" t="s">
         <v>142</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2782,13 +2756,13 @@
       <c r="D7" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2805,13 +2779,13 @@
       <c r="D8" t="s">
         <v>151</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>227</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2828,13 +2802,13 @@
       <c r="D9" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2851,13 +2825,13 @@
       <c r="D10" t="s">
         <v>153</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>229</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2871,7 +2845,7 @@
       <c r="C11" t="s">
         <v>142</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2885,7 +2859,7 @@
       <c r="C12" t="s">
         <v>142</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2902,13 +2876,13 @@
       <c r="D13" t="s">
         <v>154</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>227</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2922,7 +2896,7 @@
       <c r="C14" t="s">
         <v>146</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2939,13 +2913,13 @@
       <c r="D15" t="s">
         <v>155</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>230</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2959,7 +2933,7 @@
       <c r="C16" t="s">
         <v>142</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2973,7 +2947,7 @@
       <c r="C17" t="s">
         <v>142</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -2990,13 +2964,13 @@
       <c r="D18" t="s">
         <v>156</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>231</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3010,7 +2984,7 @@
       <c r="C19" t="s">
         <v>142</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3027,13 +3001,13 @@
       <c r="D20" t="s">
         <v>157</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>227</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3056,7 +3030,7 @@
       <c r="G21" t="s">
         <v>219</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3070,7 +3044,7 @@
       <c r="C22" t="s">
         <v>146</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3084,7 +3058,7 @@
       <c r="C23" t="s">
         <v>142</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3107,7 +3081,7 @@
       <c r="G24" t="s">
         <v>220</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3124,7 +3098,7 @@
       <c r="D25" t="s">
         <v>159</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3147,7 +3121,7 @@
       <c r="G26" t="s">
         <v>221</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3164,13 +3138,13 @@
       <c r="D27" t="s">
         <v>161</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>232</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3193,7 +3167,7 @@
       <c r="G28" t="s">
         <v>222</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3216,7 +3190,7 @@
       <c r="G29" t="s">
         <v>222</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3239,7 +3213,7 @@
       <c r="G30" t="s">
         <v>223</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3253,7 +3227,7 @@
       <c r="C31" t="s">
         <v>142</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3267,7 +3241,7 @@
       <c r="C32" t="s">
         <v>142</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3290,7 +3264,7 @@
       <c r="G33" t="s">
         <v>224</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3304,7 +3278,7 @@
       <c r="C34" t="s">
         <v>142</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3318,7 +3292,7 @@
       <c r="C35" t="s">
         <v>142</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3335,13 +3309,13 @@
       <c r="D36" t="s">
         <v>150</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>227</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3358,13 +3332,13 @@
       <c r="D37" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>227</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3381,13 +3355,13 @@
       <c r="D38" t="s">
         <v>152</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>228</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3404,13 +3378,13 @@
       <c r="D39" t="s">
         <v>153</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>229</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3424,7 +3398,7 @@
       <c r="C40" t="s">
         <v>142</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3438,7 +3412,7 @@
       <c r="C41" t="s">
         <v>142</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3455,13 +3429,13 @@
       <c r="D42" t="s">
         <v>154</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>227</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3475,7 +3449,7 @@
       <c r="C43" t="s">
         <v>142</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3492,13 +3466,13 @@
       <c r="D44" t="s">
         <v>155</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>230</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3512,7 +3486,7 @@
       <c r="C45" t="s">
         <v>142</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3526,7 +3500,7 @@
       <c r="C46" t="s">
         <v>142</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3540,7 +3514,7 @@
       <c r="C47" t="s">
         <v>146</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3554,7 +3528,7 @@
       <c r="C48" t="s">
         <v>142</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3571,13 +3545,13 @@
       <c r="D49" t="s">
         <v>166</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>227</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3600,7 +3574,7 @@
       <c r="G50" t="s">
         <v>219</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3614,7 +3588,7 @@
       <c r="C51" t="s">
         <v>146</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3628,7 +3602,7 @@
       <c r="C52" t="s">
         <v>142</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3651,7 +3625,7 @@
       <c r="G53" t="s">
         <v>220</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3668,7 +3642,7 @@
       <c r="D54" t="s">
         <v>159</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3691,7 +3665,7 @@
       <c r="G55" t="s">
         <v>221</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3708,13 +3682,13 @@
       <c r="D56" t="s">
         <v>161</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>232</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3737,7 +3711,7 @@
       <c r="G57" t="s">
         <v>222</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3760,7 +3734,7 @@
       <c r="G58" t="s">
         <v>222</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3783,7 +3757,7 @@
       <c r="G59" t="s">
         <v>223</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3797,7 +3771,7 @@
       <c r="C60" t="s">
         <v>142</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3811,7 +3785,7 @@
       <c r="C61" t="s">
         <v>142</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3828,13 +3802,13 @@
       <c r="D62" t="s">
         <v>165</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>233</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3848,7 +3822,7 @@
       <c r="C63" t="s">
         <v>142</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3865,13 +3839,13 @@
       <c r="D64" t="s">
         <v>167</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>234</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3885,7 +3859,7 @@
       <c r="C65" t="s">
         <v>142</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3899,7 +3873,7 @@
       <c r="C66" t="s">
         <v>146</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3916,13 +3890,13 @@
       <c r="D67" t="s">
         <v>152</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>228</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3939,13 +3913,13 @@
       <c r="D68" t="s">
         <v>153</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>229</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3959,7 +3933,7 @@
       <c r="C69" t="s">
         <v>142</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3973,7 +3947,7 @@
       <c r="C70" t="s">
         <v>142</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -3990,13 +3964,13 @@
       <c r="D71" t="s">
         <v>154</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>233</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4010,7 +3984,7 @@
       <c r="C72" t="s">
         <v>142</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4027,13 +4001,13 @@
       <c r="D73" t="s">
         <v>155</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>230</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4047,7 +4021,7 @@
       <c r="C74" t="s">
         <v>142</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4061,7 +4035,7 @@
       <c r="C75" t="s">
         <v>142</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4075,7 +4049,7 @@
       <c r="C76" t="s">
         <v>142</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4089,7 +4063,7 @@
       <c r="C77" t="s">
         <v>142</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4106,13 +4080,13 @@
       <c r="D78" t="s">
         <v>166</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>233</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4135,7 +4109,7 @@
       <c r="G79" t="s">
         <v>225</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4149,7 +4123,7 @@
       <c r="C80" t="s">
         <v>146</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4163,7 +4137,7 @@
       <c r="C81" t="s">
         <v>142</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4186,7 +4160,7 @@
       <c r="G82" t="s">
         <v>220</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4203,7 +4177,7 @@
       <c r="D83" t="s">
         <v>159</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4226,7 +4200,7 @@
       <c r="G84" t="s">
         <v>221</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4243,13 +4217,13 @@
       <c r="D85" t="s">
         <v>161</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>232</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4272,7 +4246,7 @@
       <c r="G86" t="s">
         <v>222</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4295,7 +4269,7 @@
       <c r="G87" t="s">
         <v>222</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4318,7 +4292,7 @@
       <c r="G88" t="s">
         <v>223</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4332,7 +4306,7 @@
       <c r="C89" t="s">
         <v>142</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4349,13 +4323,13 @@
       <c r="D90" t="s">
         <v>169</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>234</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4372,13 +4346,13 @@
       <c r="D91" t="s">
         <v>165</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>233</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4392,7 +4366,7 @@
       <c r="C92" t="s">
         <v>142</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4409,13 +4383,13 @@
       <c r="D93" t="s">
         <v>167</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>234</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4429,7 +4403,7 @@
       <c r="C94" t="s">
         <v>142</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4443,7 +4417,7 @@
       <c r="C95" t="s">
         <v>146</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4460,13 +4434,13 @@
       <c r="D96" t="s">
         <v>152</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>228</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4483,13 +4457,13 @@
       <c r="D97" t="s">
         <v>153</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>229</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4503,7 +4477,7 @@
       <c r="C98" t="s">
         <v>142</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4520,13 +4494,13 @@
       <c r="D99" t="s">
         <v>170</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>229</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4543,13 +4517,13 @@
       <c r="D100" t="s">
         <v>154</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>229</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4563,7 +4537,7 @@
       <c r="C101" t="s">
         <v>142</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4580,13 +4554,13 @@
       <c r="D102" t="s">
         <v>155</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>230</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4603,13 +4577,13 @@
       <c r="D103" t="s">
         <v>171</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>229</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4623,7 +4597,7 @@
       <c r="C104" t="s">
         <v>142</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4637,7 +4611,7 @@
       <c r="C105" t="s">
         <v>142</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4651,7 +4625,7 @@
       <c r="C106" t="s">
         <v>142</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4668,13 +4642,13 @@
       <c r="D107" t="s">
         <v>172</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>229</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4697,7 +4671,7 @@
       <c r="G108" t="s">
         <v>225</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4711,7 +4685,7 @@
       <c r="C109" t="s">
         <v>146</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4725,7 +4699,7 @@
       <c r="C110" t="s">
         <v>142</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4748,7 +4722,7 @@
       <c r="G111" t="s">
         <v>220</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4765,7 +4739,7 @@
       <c r="D112" t="s">
         <v>159</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4788,7 +4762,7 @@
       <c r="G113" t="s">
         <v>221</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4805,13 +4779,13 @@
       <c r="D114" t="s">
         <v>161</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>232</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4834,7 +4808,7 @@
       <c r="G115" t="s">
         <v>222</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4857,7 +4831,7 @@
       <c r="G116" t="s">
         <v>222</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4880,7 +4854,7 @@
       <c r="G117" t="s">
         <v>223</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4894,7 +4868,7 @@
       <c r="C118" t="s">
         <v>142</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4911,13 +4885,13 @@
       <c r="D119" t="s">
         <v>169</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>234</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4931,7 +4905,7 @@
       <c r="C120" t="s">
         <v>146</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4945,7 +4919,7 @@
       <c r="C121" t="s">
         <v>142</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4959,7 +4933,7 @@
       <c r="C122" t="s">
         <v>146</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4973,7 +4947,7 @@
       <c r="C123" t="s">
         <v>146</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -4987,7 +4961,7 @@
       <c r="C124" t="s">
         <v>146</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5004,13 +4978,13 @@
       <c r="D125" t="s">
         <v>152</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>228</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5027,13 +5001,13 @@
       <c r="D126" t="s">
         <v>153</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>229</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5047,7 +5021,7 @@
       <c r="C127" t="s">
         <v>142</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5064,13 +5038,13 @@
       <c r="D128" t="s">
         <v>170</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>229</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5087,13 +5061,13 @@
       <c r="D129" t="s">
         <v>154</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>229</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5107,7 +5081,7 @@
       <c r="C130" t="s">
         <v>142</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5124,13 +5098,13 @@
       <c r="D131" t="s">
         <v>155</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>230</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5147,13 +5121,13 @@
       <c r="D132" t="s">
         <v>171</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>229</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5167,7 +5141,7 @@
       <c r="C133" t="s">
         <v>142</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5181,7 +5155,7 @@
       <c r="C134" t="s">
         <v>142</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5195,7 +5169,7 @@
       <c r="C135" t="s">
         <v>142</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5212,13 +5186,13 @@
       <c r="D136" t="s">
         <v>173</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>229</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5241,7 +5215,7 @@
       <c r="G137" t="s">
         <v>225</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5255,7 +5229,7 @@
       <c r="C138" t="s">
         <v>146</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5269,7 +5243,7 @@
       <c r="C139" t="s">
         <v>142</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5292,7 +5266,7 @@
       <c r="G140" t="s">
         <v>220</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5309,7 +5283,7 @@
       <c r="D141" t="s">
         <v>159</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5332,7 +5306,7 @@
       <c r="G142" t="s">
         <v>221</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5349,13 +5323,13 @@
       <c r="D143" t="s">
         <v>161</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>232</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5378,7 +5352,7 @@
       <c r="G144" t="s">
         <v>222</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5401,7 +5375,7 @@
       <c r="G145" t="s">
         <v>222</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5424,7 +5398,7 @@
       <c r="G146" t="s">
         <v>223</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5438,7 +5412,7 @@
       <c r="C147" t="s">
         <v>142</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5455,13 +5429,13 @@
       <c r="D148" t="s">
         <v>169</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>234</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5475,7 +5449,7 @@
       <c r="C149" t="s">
         <v>146</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5489,7 +5463,7 @@
       <c r="C150" t="s">
         <v>142</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5503,7 +5477,7 @@
       <c r="C151" t="s">
         <v>142</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5517,7 +5491,7 @@
       <c r="C152" t="s">
         <v>146</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5531,7 +5505,7 @@
       <c r="C153" t="s">
         <v>146</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5548,13 +5522,13 @@
       <c r="D154" t="s">
         <v>152</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>228</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5571,13 +5545,13 @@
       <c r="D155" t="s">
         <v>153</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>229</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5591,7 +5565,7 @@
       <c r="C156" t="s">
         <v>142</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5608,13 +5582,13 @@
       <c r="D157" t="s">
         <v>170</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>229</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5631,13 +5605,13 @@
       <c r="D158" t="s">
         <v>154</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>229</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5654,13 +5628,13 @@
       <c r="D159" t="s">
         <v>174</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>235</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5677,13 +5651,13 @@
       <c r="D160" t="s">
         <v>155</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>230</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5700,13 +5674,13 @@
       <c r="D161" t="s">
         <v>171</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>229</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5720,7 +5694,7 @@
       <c r="C162" t="s">
         <v>142</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5734,7 +5708,7 @@
       <c r="C163" t="s">
         <v>142</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5748,7 +5722,7 @@
       <c r="C164" t="s">
         <v>142</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5765,13 +5739,13 @@
       <c r="D165" t="s">
         <v>173</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>229</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5794,7 +5768,7 @@
       <c r="G166" t="s">
         <v>225</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5808,7 +5782,7 @@
       <c r="C167" t="s">
         <v>146</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5822,7 +5796,7 @@
       <c r="C168" t="s">
         <v>142</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5845,7 +5819,7 @@
       <c r="G169" t="s">
         <v>220</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5862,7 +5836,7 @@
       <c r="D170" t="s">
         <v>159</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5885,7 +5859,7 @@
       <c r="G171" t="s">
         <v>221</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5902,13 +5876,13 @@
       <c r="D172" t="s">
         <v>161</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>232</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5931,7 +5905,7 @@
       <c r="G173" t="s">
         <v>222</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5954,7 +5928,7 @@
       <c r="G174" t="s">
         <v>222</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5977,7 +5951,7 @@
       <c r="G175" t="s">
         <v>223</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5991,7 +5965,7 @@
       <c r="C176" t="s">
         <v>142</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6008,13 +5982,13 @@
       <c r="D177" t="s">
         <v>175</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>234</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6028,7 +6002,7 @@
       <c r="C178" t="s">
         <v>142</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6045,13 +6019,13 @@
       <c r="D179" t="s">
         <v>176</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>230</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6065,7 +6039,7 @@
       <c r="C180" t="s">
         <v>142</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6079,7 +6053,7 @@
       <c r="C181" t="s">
         <v>146</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6093,7 +6067,7 @@
       <c r="C182" t="s">
         <v>146</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6110,13 +6084,13 @@
       <c r="D183" t="s">
         <v>152</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>228</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6133,13 +6107,13 @@
       <c r="D184" t="s">
         <v>153</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>229</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6153,7 +6127,7 @@
       <c r="C185" t="s">
         <v>142</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6170,13 +6144,13 @@
       <c r="D186" t="s">
         <v>170</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>229</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6193,13 +6167,13 @@
       <c r="D187" t="s">
         <v>177</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>229</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6216,13 +6190,13 @@
       <c r="D188" t="s">
         <v>178</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>229</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6239,13 +6213,13 @@
       <c r="D189" t="s">
         <v>155</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>230</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6262,13 +6236,13 @@
       <c r="D190" t="s">
         <v>171</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>229</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6282,7 +6256,7 @@
       <c r="C191" t="s">
         <v>142</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6296,7 +6270,7 @@
       <c r="C192" t="s">
         <v>142</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6310,7 +6284,7 @@
       <c r="C193" t="s">
         <v>142</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6327,13 +6301,13 @@
       <c r="D194" t="s">
         <v>173</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>236</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6356,7 +6330,7 @@
       <c r="G195" t="s">
         <v>225</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6370,7 +6344,7 @@
       <c r="C196" t="s">
         <v>146</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6384,7 +6358,7 @@
       <c r="C197" t="s">
         <v>142</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6407,7 +6381,7 @@
       <c r="G198" t="s">
         <v>220</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6424,7 +6398,7 @@
       <c r="D199" t="s">
         <v>159</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6447,7 +6421,7 @@
       <c r="G200" t="s">
         <v>221</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6464,13 +6438,13 @@
       <c r="D201" t="s">
         <v>161</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>232</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6493,7 +6467,7 @@
       <c r="G202" t="s">
         <v>222</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6516,7 +6490,7 @@
       <c r="G203" t="s">
         <v>222</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6539,7 +6513,7 @@
       <c r="G204" t="s">
         <v>223</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6553,7 +6527,7 @@
       <c r="C205" t="s">
         <v>142</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6570,13 +6544,13 @@
       <c r="D206" t="s">
         <v>175</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>234</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6590,7 +6564,7 @@
       <c r="C207" t="s">
         <v>142</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6604,7 +6578,7 @@
       <c r="C208" t="s">
         <v>146</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6618,7 +6592,7 @@
       <c r="C209" t="s">
         <v>142</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6632,7 +6606,7 @@
       <c r="C210" t="s">
         <v>146</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6646,7 +6620,7 @@
       <c r="C211" t="s">
         <v>146</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6663,13 +6637,13 @@
       <c r="D212" t="s">
         <v>152</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>228</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6683,7 +6657,7 @@
       <c r="C213" t="s">
         <v>146</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6697,7 +6671,7 @@
       <c r="C214" t="s">
         <v>142</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6714,13 +6688,13 @@
       <c r="D215" t="s">
         <v>170</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>237</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6737,13 +6711,13 @@
       <c r="D216" t="s">
         <v>177</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>230</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6757,7 +6731,7 @@
       <c r="C217" t="s">
         <v>142</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6774,13 +6748,13 @@
       <c r="D218" t="s">
         <v>155</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>230</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6794,7 +6768,7 @@
       <c r="C219" t="s">
         <v>142</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6808,7 +6782,7 @@
       <c r="C220" t="s">
         <v>142</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6825,13 +6799,13 @@
       <c r="D221" t="s">
         <v>179</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>234</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6845,7 +6819,7 @@
       <c r="C222" t="s">
         <v>142</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6862,13 +6836,13 @@
       <c r="D223" t="s">
         <v>180</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>238</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6891,7 +6865,7 @@
       <c r="G224" t="s">
         <v>225</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6905,7 +6879,7 @@
       <c r="C225" t="s">
         <v>146</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6919,7 +6893,7 @@
       <c r="C226" t="s">
         <v>142</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6942,7 +6916,7 @@
       <c r="G227" t="s">
         <v>220</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6959,7 +6933,7 @@
       <c r="D228" t="s">
         <v>159</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6982,7 +6956,7 @@
       <c r="G229" t="s">
         <v>221</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6999,13 +6973,13 @@
       <c r="D230" t="s">
         <v>181</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>239</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7028,7 +7002,7 @@
       <c r="G231" t="s">
         <v>222</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7051,7 +7025,7 @@
       <c r="G232" t="s">
         <v>222</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7074,7 +7048,7 @@
       <c r="G233" t="s">
         <v>223</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7088,7 +7062,7 @@
       <c r="C234" t="s">
         <v>142</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7105,13 +7079,13 @@
       <c r="D235" t="s">
         <v>182</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>234</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7125,7 +7099,7 @@
       <c r="C236" t="s">
         <v>142</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7139,7 +7113,7 @@
       <c r="C237" t="s">
         <v>146</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7153,7 +7127,7 @@
       <c r="C238" t="s">
         <v>142</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7167,7 +7141,7 @@
       <c r="C239" t="s">
         <v>146</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7181,7 +7155,7 @@
       <c r="C240" t="s">
         <v>146</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7198,13 +7172,13 @@
       <c r="D241" t="s">
         <v>152</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>228</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7218,7 +7192,7 @@
       <c r="C242" t="s">
         <v>146</v>
       </c>
-      <c r="H242" s="2">
+      <c r="H242" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7235,13 +7209,13 @@
       <c r="D243" t="s">
         <v>183</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>46224</v>
       </c>
       <c r="G243" t="s">
         <v>240</v>
       </c>
-      <c r="H243" s="2">
+      <c r="H243" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7258,13 +7232,13 @@
       <c r="D244" t="s">
         <v>184</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>46220</v>
       </c>
       <c r="G244" t="s">
         <v>237</v>
       </c>
-      <c r="H244" s="2">
+      <c r="H244" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7278,7 +7252,7 @@
       <c r="C245" t="s">
         <v>146</v>
       </c>
-      <c r="H245" s="2">
+      <c r="H245" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7292,7 +7266,7 @@
       <c r="C246" t="s">
         <v>142</v>
       </c>
-      <c r="H246" s="2">
+      <c r="H246" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7309,13 +7283,13 @@
       <c r="D247" t="s">
         <v>155</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>46237</v>
       </c>
       <c r="G247" t="s">
         <v>241</v>
       </c>
-      <c r="H247" s="2">
+      <c r="H247" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7329,7 +7303,7 @@
       <c r="C248" t="s">
         <v>142</v>
       </c>
-      <c r="H248" s="2">
+      <c r="H248" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7343,7 +7317,7 @@
       <c r="C249" t="s">
         <v>142</v>
       </c>
-      <c r="H249" s="2">
+      <c r="H249" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7360,13 +7334,13 @@
       <c r="D250" t="s">
         <v>185</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>46218</v>
       </c>
       <c r="G250" t="s">
         <v>236</v>
       </c>
-      <c r="H250" s="2">
+      <c r="H250" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7380,7 +7354,7 @@
       <c r="C251" t="s">
         <v>142</v>
       </c>
-      <c r="H251" s="2">
+      <c r="H251" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7397,13 +7371,13 @@
       <c r="D252" t="s">
         <v>186</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>46241</v>
       </c>
       <c r="G252" t="s">
         <v>238</v>
       </c>
-      <c r="H252" s="2">
+      <c r="H252" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7426,7 +7400,7 @@
       <c r="G253" t="s">
         <v>225</v>
       </c>
-      <c r="H253" s="2">
+      <c r="H253" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7440,7 +7414,7 @@
       <c r="C254" t="s">
         <v>146</v>
       </c>
-      <c r="H254" s="2">
+      <c r="H254" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7454,7 +7428,7 @@
       <c r="C255" t="s">
         <v>142</v>
       </c>
-      <c r="H255" s="2">
+      <c r="H255" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7477,7 +7451,7 @@
       <c r="G256" t="s">
         <v>220</v>
       </c>
-      <c r="H256" s="2">
+      <c r="H256" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7494,7 +7468,7 @@
       <c r="D257" t="s">
         <v>159</v>
       </c>
-      <c r="H257" s="2">
+      <c r="H257" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7517,7 +7491,7 @@
       <c r="G258" t="s">
         <v>221</v>
       </c>
-      <c r="H258" s="2">
+      <c r="H258" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7534,13 +7508,13 @@
       <c r="D259" t="s">
         <v>181</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>46295</v>
       </c>
       <c r="G259" t="s">
         <v>239</v>
       </c>
-      <c r="H259" s="2">
+      <c r="H259" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7563,7 +7537,7 @@
       <c r="G260" t="s">
         <v>222</v>
       </c>
-      <c r="H260" s="2">
+      <c r="H260" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7586,7 +7560,7 @@
       <c r="G261" t="s">
         <v>222</v>
       </c>
-      <c r="H261" s="2">
+      <c r="H261" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7609,7 +7583,7 @@
       <c r="G262" t="s">
         <v>223</v>
       </c>
-      <c r="H262" s="2">
+      <c r="H262" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7623,7 +7597,7 @@
       <c r="C263" t="s">
         <v>142</v>
       </c>
-      <c r="H263" s="2">
+      <c r="H263" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7640,13 +7614,13 @@
       <c r="D264" t="s">
         <v>182</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>46217</v>
       </c>
       <c r="G264" t="s">
         <v>234</v>
       </c>
-      <c r="H264" s="2">
+      <c r="H264" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7660,7 +7634,7 @@
       <c r="C265" t="s">
         <v>142</v>
       </c>
-      <c r="H265" s="2">
+      <c r="H265" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7674,7 +7648,7 @@
       <c r="C266" t="s">
         <v>146</v>
       </c>
-      <c r="H266" s="2">
+      <c r="H266" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7688,7 +7662,7 @@
       <c r="C267" t="s">
         <v>142</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H267" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7702,7 +7676,7 @@
       <c r="C268" t="s">
         <v>146</v>
       </c>
-      <c r="H268" s="2">
+      <c r="H268" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7716,7 +7690,7 @@
       <c r="C269" t="s">
         <v>146</v>
       </c>
-      <c r="H269" s="2">
+      <c r="H269" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7733,13 +7707,13 @@
       <c r="D270" t="s">
         <v>152</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>46234</v>
       </c>
       <c r="G270" t="s">
         <v>228</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H270" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7753,7 +7727,7 @@
       <c r="C271" t="s">
         <v>146</v>
       </c>
-      <c r="H271" s="2">
+      <c r="H271" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7770,13 +7744,13 @@
       <c r="D272" t="s">
         <v>183</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>46224</v>
       </c>
       <c r="G272" t="s">
         <v>240</v>
       </c>
-      <c r="H272" s="2">
+      <c r="H272" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7793,13 +7767,13 @@
       <c r="D273" t="s">
         <v>184</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>46219</v>
       </c>
       <c r="G273" t="s">
         <v>242</v>
       </c>
-      <c r="H273" s="2">
+      <c r="H273" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7813,7 +7787,7 @@
       <c r="C274" t="s">
         <v>142</v>
       </c>
-      <c r="H274" s="2">
+      <c r="H274" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7827,7 +7801,7 @@
       <c r="C275" t="s">
         <v>142</v>
       </c>
-      <c r="H275" s="2">
+      <c r="H275" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7844,13 +7818,13 @@
       <c r="D276" t="s">
         <v>155</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>46237</v>
       </c>
       <c r="G276" t="s">
         <v>241</v>
       </c>
-      <c r="H276" s="2">
+      <c r="H276" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7864,7 +7838,7 @@
       <c r="C277" t="s">
         <v>142</v>
       </c>
-      <c r="H277" s="2">
+      <c r="H277" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7881,13 +7855,13 @@
       <c r="D278" t="s">
         <v>187</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>46227</v>
       </c>
       <c r="G278" t="s">
         <v>243</v>
       </c>
-      <c r="H278" s="2">
+      <c r="H278" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7904,13 +7878,13 @@
       <c r="D279" t="s">
         <v>185</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>46219</v>
       </c>
       <c r="G279" t="s">
         <v>242</v>
       </c>
-      <c r="H279" s="2">
+      <c r="H279" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7924,7 +7898,7 @@
       <c r="C280" t="s">
         <v>142</v>
       </c>
-      <c r="H280" s="2">
+      <c r="H280" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7941,13 +7915,13 @@
       <c r="D281" t="s">
         <v>188</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>46241</v>
       </c>
       <c r="G281" t="s">
         <v>238</v>
       </c>
-      <c r="H281" s="2">
+      <c r="H281" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7970,7 +7944,7 @@
       <c r="G282" t="s">
         <v>225</v>
       </c>
-      <c r="H282" s="2">
+      <c r="H282" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7984,7 +7958,7 @@
       <c r="C283" t="s">
         <v>146</v>
       </c>
-      <c r="H283" s="2">
+      <c r="H283" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -7998,7 +7972,7 @@
       <c r="C284" t="s">
         <v>142</v>
       </c>
-      <c r="H284" s="2">
+      <c r="H284" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8021,7 +7995,7 @@
       <c r="G285" t="s">
         <v>220</v>
       </c>
-      <c r="H285" s="2">
+      <c r="H285" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8038,7 +8012,7 @@
       <c r="D286" t="s">
         <v>159</v>
       </c>
-      <c r="H286" s="2">
+      <c r="H286" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8061,7 +8035,7 @@
       <c r="G287" t="s">
         <v>221</v>
       </c>
-      <c r="H287" s="2">
+      <c r="H287" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8078,13 +8052,13 @@
       <c r="D288" t="s">
         <v>181</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>46295</v>
       </c>
       <c r="G288" t="s">
         <v>239</v>
       </c>
-      <c r="H288" s="2">
+      <c r="H288" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8107,7 +8081,7 @@
       <c r="G289" t="s">
         <v>222</v>
       </c>
-      <c r="H289" s="2">
+      <c r="H289" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8130,7 +8104,7 @@
       <c r="G290" t="s">
         <v>222</v>
       </c>
-      <c r="H290" s="2">
+      <c r="H290" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8153,7 +8127,7 @@
       <c r="G291" t="s">
         <v>223</v>
       </c>
-      <c r="H291" s="2">
+      <c r="H291" s="1">
         <v>46218</v>
       </c>
     </row>
@@ -8167,7 +8141,7 @@
       <c r="C292" t="s">
         <v>142</v>
       </c>
-      <c r="H292" s="2">
+      <c r="H292" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8184,13 +8158,13 @@
       <c r="D293" t="s">
         <v>182</v>
       </c>
-      <c r="E293" s="2">
+      <c r="E293" s="1">
         <v>46220</v>
       </c>
       <c r="G293" t="s">
         <v>244</v>
       </c>
-      <c r="H293" s="2">
+      <c r="H293" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8204,7 +8178,7 @@
       <c r="C294" t="s">
         <v>142</v>
       </c>
-      <c r="H294" s="2">
+      <c r="H294" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8227,7 +8201,7 @@
       <c r="G295" t="s">
         <v>226</v>
       </c>
-      <c r="H295" s="2">
+      <c r="H295" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8241,7 +8215,7 @@
       <c r="C296" t="s">
         <v>142</v>
       </c>
-      <c r="H296" s="2">
+      <c r="H296" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8255,7 +8229,7 @@
       <c r="C297" t="s">
         <v>146</v>
       </c>
-      <c r="H297" s="2">
+      <c r="H297" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8272,13 +8246,13 @@
       <c r="D298" t="s">
         <v>190</v>
       </c>
-      <c r="E298" s="2">
+      <c r="E298" s="1">
         <v>46223</v>
       </c>
       <c r="G298" t="s">
         <v>245</v>
       </c>
-      <c r="H298" s="2">
+      <c r="H298" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8295,13 +8269,13 @@
       <c r="D299" t="s">
         <v>152</v>
       </c>
-      <c r="E299" s="2">
+      <c r="E299" s="1">
         <v>46234</v>
       </c>
       <c r="G299" t="s">
         <v>228</v>
       </c>
-      <c r="H299" s="2">
+      <c r="H299" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8315,7 +8289,7 @@
       <c r="C300" t="s">
         <v>142</v>
       </c>
-      <c r="H300" s="2">
+      <c r="H300" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8332,13 +8306,13 @@
       <c r="D301" t="s">
         <v>183</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301" s="1">
         <v>46224</v>
       </c>
       <c r="G301" t="s">
         <v>240</v>
       </c>
-      <c r="H301" s="2">
+      <c r="H301" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8355,13 +8329,13 @@
       <c r="D302" t="s">
         <v>184</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302" s="1">
         <v>46220</v>
       </c>
       <c r="G302" t="s">
         <v>237</v>
       </c>
-      <c r="H302" s="2">
+      <c r="H302" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8375,7 +8349,7 @@
       <c r="C303" t="s">
         <v>142</v>
       </c>
-      <c r="H303" s="2">
+      <c r="H303" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8389,7 +8363,7 @@
       <c r="C304" t="s">
         <v>142</v>
       </c>
-      <c r="H304" s="2">
+      <c r="H304" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8406,13 +8380,13 @@
       <c r="D305" t="s">
         <v>155</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305" s="1">
         <v>46237</v>
       </c>
       <c r="G305" t="s">
         <v>241</v>
       </c>
-      <c r="H305" s="2">
+      <c r="H305" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8426,7 +8400,7 @@
       <c r="C306" t="s">
         <v>142</v>
       </c>
-      <c r="H306" s="2">
+      <c r="H306" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8443,13 +8417,13 @@
       <c r="D307" t="s">
         <v>187</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307" s="1">
         <v>46227</v>
       </c>
       <c r="G307" t="s">
         <v>243</v>
       </c>
-      <c r="H307" s="2">
+      <c r="H307" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8463,7 +8437,7 @@
       <c r="C308" t="s">
         <v>146</v>
       </c>
-      <c r="H308" s="2">
+      <c r="H308" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8480,13 +8454,13 @@
       <c r="D309" t="s">
         <v>191</v>
       </c>
-      <c r="E309" s="2">
+      <c r="E309" s="1">
         <v>46220</v>
       </c>
       <c r="G309" t="s">
         <v>244</v>
       </c>
-      <c r="H309" s="2">
+      <c r="H309" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8503,13 +8477,13 @@
       <c r="D310" t="s">
         <v>192</v>
       </c>
-      <c r="E310" s="2">
+      <c r="E310" s="1">
         <v>46265</v>
       </c>
       <c r="G310" t="s">
         <v>246</v>
       </c>
-      <c r="H310" s="2">
+      <c r="H310" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8526,7 +8500,7 @@
       <c r="D311" t="s">
         <v>193</v>
       </c>
-      <c r="H311" s="2">
+      <c r="H311" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8540,7 +8514,7 @@
       <c r="C312" t="s">
         <v>146</v>
       </c>
-      <c r="H312" s="2">
+      <c r="H312" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8554,7 +8528,7 @@
       <c r="C313" t="s">
         <v>142</v>
       </c>
-      <c r="H313" s="2">
+      <c r="H313" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8577,7 +8551,7 @@
       <c r="G314" t="s">
         <v>220</v>
       </c>
-      <c r="H314" s="2">
+      <c r="H314" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8594,7 +8568,7 @@
       <c r="D315" t="s">
         <v>159</v>
       </c>
-      <c r="H315" s="2">
+      <c r="H315" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8617,7 +8591,7 @@
       <c r="G316" t="s">
         <v>221</v>
       </c>
-      <c r="H316" s="2">
+      <c r="H316" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8634,13 +8608,13 @@
       <c r="D317" t="s">
         <v>181</v>
       </c>
-      <c r="E317" s="2">
+      <c r="E317" s="1">
         <v>46295</v>
       </c>
       <c r="G317" t="s">
         <v>247</v>
       </c>
-      <c r="H317" s="2">
+      <c r="H317" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8663,7 +8637,7 @@
       <c r="G318" t="s">
         <v>222</v>
       </c>
-      <c r="H318" s="2">
+      <c r="H318" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8686,7 +8660,7 @@
       <c r="G319" t="s">
         <v>222</v>
       </c>
-      <c r="H319" s="2">
+      <c r="H319" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8709,7 +8683,7 @@
       <c r="G320" t="s">
         <v>223</v>
       </c>
-      <c r="H320" s="2">
+      <c r="H320" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -8723,7 +8697,7 @@
       <c r="C321" t="s">
         <v>142</v>
       </c>
-      <c r="H321" s="2">
+      <c r="H321" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8740,13 +8714,13 @@
       <c r="D322" t="s">
         <v>182</v>
       </c>
-      <c r="E322" s="2">
+      <c r="E322" s="1">
         <v>46225</v>
       </c>
       <c r="G322" t="s">
         <v>248</v>
       </c>
-      <c r="H322" s="2">
+      <c r="H322" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8760,7 +8734,7 @@
       <c r="C323" t="s">
         <v>142</v>
       </c>
-      <c r="H323" s="2">
+      <c r="H323" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8777,13 +8751,13 @@
       <c r="D324" t="s">
         <v>194</v>
       </c>
-      <c r="E324" s="2">
+      <c r="E324" s="1">
         <v>46224</v>
       </c>
       <c r="G324" t="s">
         <v>249</v>
       </c>
-      <c r="H324" s="2">
+      <c r="H324" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8797,7 +8771,7 @@
       <c r="C325" t="s">
         <v>142</v>
       </c>
-      <c r="H325" s="2">
+      <c r="H325" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8811,7 +8785,7 @@
       <c r="C326" t="s">
         <v>146</v>
       </c>
-      <c r="H326" s="2">
+      <c r="H326" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8825,7 +8799,7 @@
       <c r="C327" t="s">
         <v>146</v>
       </c>
-      <c r="H327" s="2">
+      <c r="H327" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8842,13 +8816,13 @@
       <c r="D328" t="s">
         <v>152</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328" s="1">
         <v>46234</v>
       </c>
       <c r="G328" t="s">
         <v>228</v>
       </c>
-      <c r="H328" s="2">
+      <c r="H328" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8865,13 +8839,13 @@
       <c r="D329" t="s">
         <v>195</v>
       </c>
-      <c r="E329" s="2">
+      <c r="E329" s="1">
         <v>46224</v>
       </c>
       <c r="G329" t="s">
         <v>249</v>
       </c>
-      <c r="H329" s="2">
+      <c r="H329" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8888,13 +8862,13 @@
       <c r="D330" t="s">
         <v>183</v>
       </c>
-      <c r="E330" s="2">
+      <c r="E330" s="1">
         <v>46224</v>
       </c>
       <c r="G330" t="s">
         <v>249</v>
       </c>
-      <c r="H330" s="2">
+      <c r="H330" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8908,7 +8882,7 @@
       <c r="C331" t="s">
         <v>142</v>
       </c>
-      <c r="H331" s="2">
+      <c r="H331" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8925,13 +8899,13 @@
       <c r="D332" t="s">
         <v>196</v>
       </c>
-      <c r="E332" s="2">
+      <c r="E332" s="1">
         <v>46224</v>
       </c>
       <c r="G332" t="s">
         <v>249</v>
       </c>
-      <c r="H332" s="2">
+      <c r="H332" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8948,13 +8922,13 @@
       <c r="D333" t="s">
         <v>197</v>
       </c>
-      <c r="E333" s="2">
+      <c r="E333" s="1">
         <v>46225</v>
       </c>
       <c r="G333" t="s">
         <v>248</v>
       </c>
-      <c r="H333" s="2">
+      <c r="H333" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8971,13 +8945,13 @@
       <c r="D334" t="s">
         <v>155</v>
       </c>
-      <c r="E334" s="2">
+      <c r="E334" s="1">
         <v>46237</v>
       </c>
       <c r="G334" t="s">
         <v>241</v>
       </c>
-      <c r="H334" s="2">
+      <c r="H334" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -8991,7 +8965,7 @@
       <c r="C335" t="s">
         <v>142</v>
       </c>
-      <c r="H335" s="2">
+      <c r="H335" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9008,13 +8982,13 @@
       <c r="D336" t="s">
         <v>187</v>
       </c>
-      <c r="E336" s="2">
+      <c r="E336" s="1">
         <v>46227</v>
       </c>
       <c r="G336" t="s">
         <v>243</v>
       </c>
-      <c r="H336" s="2">
+      <c r="H336" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9028,7 +9002,7 @@
       <c r="C337" t="s">
         <v>142</v>
       </c>
-      <c r="H337" s="2">
+      <c r="H337" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9042,7 +9016,7 @@
       <c r="C338" t="s">
         <v>142</v>
       </c>
-      <c r="H338" s="2">
+      <c r="H338" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9059,13 +9033,13 @@
       <c r="D339" t="s">
         <v>192</v>
       </c>
-      <c r="E339" s="2">
+      <c r="E339" s="1">
         <v>46265</v>
       </c>
       <c r="G339" t="s">
         <v>246</v>
       </c>
-      <c r="H339" s="2">
+      <c r="H339" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9082,7 +9056,7 @@
       <c r="D340" t="s">
         <v>198</v>
       </c>
-      <c r="H340" s="2">
+      <c r="H340" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9096,7 +9070,7 @@
       <c r="C341" t="s">
         <v>146</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9110,7 +9084,7 @@
       <c r="C342" t="s">
         <v>142</v>
       </c>
-      <c r="H342" s="2">
+      <c r="H342" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9133,7 +9107,7 @@
       <c r="G343" t="s">
         <v>220</v>
       </c>
-      <c r="H343" s="2">
+      <c r="H343" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9150,7 +9124,7 @@
       <c r="D344" t="s">
         <v>159</v>
       </c>
-      <c r="H344" s="2">
+      <c r="H344" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9173,7 +9147,7 @@
       <c r="G345" t="s">
         <v>221</v>
       </c>
-      <c r="H345" s="2">
+      <c r="H345" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9190,13 +9164,13 @@
       <c r="D346" t="s">
         <v>181</v>
       </c>
-      <c r="E346" s="2">
+      <c r="E346" s="1">
         <v>46295</v>
       </c>
       <c r="G346" t="s">
         <v>247</v>
       </c>
-      <c r="H346" s="2">
+      <c r="H346" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9219,7 +9193,7 @@
       <c r="G347" t="s">
         <v>222</v>
       </c>
-      <c r="H347" s="2">
+      <c r="H347" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9242,7 +9216,7 @@
       <c r="G348" t="s">
         <v>222</v>
       </c>
-      <c r="H348" s="2">
+      <c r="H348" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9265,7 +9239,7 @@
       <c r="G349" t="s">
         <v>223</v>
       </c>
-      <c r="H349" s="2">
+      <c r="H349" s="1">
         <v>46224</v>
       </c>
     </row>
@@ -9279,7 +9253,7 @@
       <c r="C350" t="s">
         <v>142</v>
       </c>
-      <c r="H350" s="2">
+      <c r="H350" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9296,13 +9270,13 @@
       <c r="D351" t="s">
         <v>182</v>
       </c>
-      <c r="E351" s="2">
+      <c r="E351" s="1">
         <v>46225</v>
       </c>
       <c r="G351" t="s">
         <v>248</v>
       </c>
-      <c r="H351" s="2">
+      <c r="H351" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9316,7 +9290,7 @@
       <c r="C352" t="s">
         <v>142</v>
       </c>
-      <c r="H352" s="2">
+      <c r="H352" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9330,7 +9304,7 @@
       <c r="C353" t="s">
         <v>142</v>
       </c>
-      <c r="H353" s="2">
+      <c r="H353" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9344,7 +9318,7 @@
       <c r="C354" t="s">
         <v>142</v>
       </c>
-      <c r="H354" s="2">
+      <c r="H354" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9358,7 +9332,7 @@
       <c r="C355" t="s">
         <v>146</v>
       </c>
-      <c r="H355" s="2">
+      <c r="H355" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9372,7 +9346,7 @@
       <c r="C356" t="s">
         <v>146</v>
       </c>
-      <c r="H356" s="2">
+      <c r="H356" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9389,13 +9363,13 @@
       <c r="D357" t="s">
         <v>152</v>
       </c>
-      <c r="E357" s="2">
+      <c r="E357" s="1">
         <v>46234</v>
       </c>
       <c r="G357" t="s">
         <v>250</v>
       </c>
-      <c r="H357" s="2">
+      <c r="H357" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9409,7 +9383,7 @@
       <c r="C358" t="s">
         <v>142</v>
       </c>
-      <c r="H358" s="2">
+      <c r="H358" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9426,13 +9400,13 @@
       <c r="D359" t="s">
         <v>183</v>
       </c>
-      <c r="E359" s="2">
+      <c r="E359" s="1">
         <v>46227</v>
       </c>
       <c r="G359" t="s">
         <v>251</v>
       </c>
-      <c r="H359" s="2">
+      <c r="H359" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9446,7 +9420,7 @@
       <c r="C360" t="s">
         <v>142</v>
       </c>
-      <c r="H360" s="2">
+      <c r="H360" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9460,7 +9434,7 @@
       <c r="C361" t="s">
         <v>142</v>
       </c>
-      <c r="H361" s="2">
+      <c r="H361" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9477,13 +9451,13 @@
       <c r="D362" t="s">
         <v>197</v>
       </c>
-      <c r="E362" s="2">
+      <c r="E362" s="1">
         <v>46225</v>
       </c>
       <c r="G362" t="s">
         <v>248</v>
       </c>
-      <c r="H362" s="2">
+      <c r="H362" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9500,13 +9474,13 @@
       <c r="D363" t="s">
         <v>155</v>
       </c>
-      <c r="E363" s="2">
+      <c r="E363" s="1">
         <v>46237</v>
       </c>
       <c r="G363" t="s">
         <v>252</v>
       </c>
-      <c r="H363" s="2">
+      <c r="H363" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9520,7 +9494,7 @@
       <c r="C364" t="s">
         <v>142</v>
       </c>
-      <c r="H364" s="2">
+      <c r="H364" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9537,13 +9511,13 @@
       <c r="D365" t="s">
         <v>187</v>
       </c>
-      <c r="E365" s="2">
+      <c r="E365" s="1">
         <v>46227</v>
       </c>
       <c r="G365" t="s">
         <v>251</v>
       </c>
-      <c r="H365" s="2">
+      <c r="H365" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9557,7 +9531,7 @@
       <c r="C366" t="s">
         <v>142</v>
       </c>
-      <c r="H366" s="2">
+      <c r="H366" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9571,7 +9545,7 @@
       <c r="C367" t="s">
         <v>142</v>
       </c>
-      <c r="H367" s="2">
+      <c r="H367" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9588,13 +9562,13 @@
       <c r="D368" t="s">
         <v>192</v>
       </c>
-      <c r="E368" s="2">
+      <c r="E368" s="1">
         <v>46234</v>
       </c>
       <c r="G368" t="s">
         <v>250</v>
       </c>
-      <c r="H368" s="2">
+      <c r="H368" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9611,13 +9585,13 @@
       <c r="D369" t="s">
         <v>199</v>
       </c>
-      <c r="E369" s="2">
+      <c r="E369" s="1">
         <v>46227</v>
       </c>
       <c r="G369" t="s">
         <v>251</v>
       </c>
-      <c r="H369" s="2">
+      <c r="H369" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9634,7 +9608,7 @@
       <c r="D370" t="s">
         <v>198</v>
       </c>
-      <c r="H370" s="2">
+      <c r="H370" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9648,7 +9622,7 @@
       <c r="C371" t="s">
         <v>142</v>
       </c>
-      <c r="H371" s="2">
+      <c r="H371" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9671,7 +9645,7 @@
       <c r="G372" t="s">
         <v>220</v>
       </c>
-      <c r="H372" s="2">
+      <c r="H372" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9688,7 +9662,7 @@
       <c r="D373" t="s">
         <v>159</v>
       </c>
-      <c r="H373" s="2">
+      <c r="H373" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9711,7 +9685,7 @@
       <c r="G374" t="s">
         <v>221</v>
       </c>
-      <c r="H374" s="2">
+      <c r="H374" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9728,13 +9702,13 @@
       <c r="D375" t="s">
         <v>181</v>
       </c>
-      <c r="E375" s="2">
+      <c r="E375" s="1">
         <v>46295</v>
       </c>
       <c r="G375" t="s">
         <v>247</v>
       </c>
-      <c r="H375" s="2">
+      <c r="H375" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9757,7 +9731,7 @@
       <c r="G376" t="s">
         <v>222</v>
       </c>
-      <c r="H376" s="2">
+      <c r="H376" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9780,7 +9754,7 @@
       <c r="G377" t="s">
         <v>222</v>
       </c>
-      <c r="H377" s="2">
+      <c r="H377" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9803,7 +9777,7 @@
       <c r="G378" t="s">
         <v>223</v>
       </c>
-      <c r="H378" s="2">
+      <c r="H378" s="1">
         <v>46225</v>
       </c>
     </row>
@@ -9817,7 +9791,7 @@
       <c r="C379" t="s">
         <v>142</v>
       </c>
-      <c r="H379" s="2">
+      <c r="H379" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9834,13 +9808,13 @@
       <c r="D380" t="s">
         <v>182</v>
       </c>
-      <c r="E380" s="2">
+      <c r="E380" s="1">
         <v>46227</v>
       </c>
       <c r="G380" t="s">
         <v>251</v>
       </c>
-      <c r="H380" s="2">
+      <c r="H380" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9854,7 +9828,7 @@
       <c r="C381" t="s">
         <v>142</v>
       </c>
-      <c r="H381" s="2">
+      <c r="H381" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9868,7 +9842,7 @@
       <c r="C382" t="s">
         <v>142</v>
       </c>
-      <c r="H382" s="2">
+      <c r="H382" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9882,7 +9856,7 @@
       <c r="C383" t="s">
         <v>142</v>
       </c>
-      <c r="H383" s="2">
+      <c r="H383" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9896,7 +9870,7 @@
       <c r="C384" t="s">
         <v>146</v>
       </c>
-      <c r="H384" s="2">
+      <c r="H384" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9910,7 +9884,7 @@
       <c r="C385" t="s">
         <v>146</v>
       </c>
-      <c r="H385" s="2">
+      <c r="H385" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9927,13 +9901,13 @@
       <c r="D386" t="s">
         <v>152</v>
       </c>
-      <c r="E386" s="2">
+      <c r="E386" s="1">
         <v>46234</v>
       </c>
       <c r="G386" t="s">
         <v>250</v>
       </c>
-      <c r="H386" s="2">
+      <c r="H386" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9947,7 +9921,7 @@
       <c r="C387" t="s">
         <v>142</v>
       </c>
-      <c r="H387" s="2">
+      <c r="H387" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9961,7 +9935,7 @@
       <c r="C388" t="s">
         <v>146</v>
       </c>
-      <c r="H388" s="2">
+      <c r="H388" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9975,7 +9949,7 @@
       <c r="C389" t="s">
         <v>142</v>
       </c>
-      <c r="H389" s="2">
+      <c r="H389" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -9989,7 +9963,7 @@
       <c r="C390" t="s">
         <v>142</v>
       </c>
-      <c r="H390" s="2">
+      <c r="H390" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10006,13 +9980,13 @@
       <c r="D391" t="s">
         <v>200</v>
       </c>
-      <c r="E391" s="2">
+      <c r="E391" s="1">
         <v>46227</v>
       </c>
       <c r="G391" t="s">
         <v>251</v>
       </c>
-      <c r="H391" s="2">
+      <c r="H391" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10029,13 +10003,13 @@
       <c r="D392" t="s">
         <v>155</v>
       </c>
-      <c r="E392" s="2">
+      <c r="E392" s="1">
         <v>46237</v>
       </c>
       <c r="G392" t="s">
         <v>252</v>
       </c>
-      <c r="H392" s="2">
+      <c r="H392" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10049,7 +10023,7 @@
       <c r="C393" t="s">
         <v>142</v>
       </c>
-      <c r="H393" s="2">
+      <c r="H393" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10066,13 +10040,13 @@
       <c r="D394" t="s">
         <v>187</v>
       </c>
-      <c r="E394" s="2">
+      <c r="E394" s="1">
         <v>46227</v>
       </c>
       <c r="G394" t="s">
         <v>251</v>
       </c>
-      <c r="H394" s="2">
+      <c r="H394" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10086,7 +10060,7 @@
       <c r="C395" t="s">
         <v>142</v>
       </c>
-      <c r="H395" s="2">
+      <c r="H395" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10100,7 +10074,7 @@
       <c r="C396" t="s">
         <v>142</v>
       </c>
-      <c r="H396" s="2">
+      <c r="H396" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10117,13 +10091,13 @@
       <c r="D397" t="s">
         <v>192</v>
       </c>
-      <c r="E397" s="2">
+      <c r="E397" s="1">
         <v>46234</v>
       </c>
       <c r="G397" t="s">
         <v>250</v>
       </c>
-      <c r="H397" s="2">
+      <c r="H397" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10140,13 +10114,13 @@
       <c r="D398" t="s">
         <v>199</v>
       </c>
-      <c r="E398" s="2">
+      <c r="E398" s="1">
         <v>46227</v>
       </c>
       <c r="G398" t="s">
         <v>251</v>
       </c>
-      <c r="H398" s="2">
+      <c r="H398" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10163,7 +10137,7 @@
       <c r="D399" t="s">
         <v>198</v>
       </c>
-      <c r="H399" s="2">
+      <c r="H399" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10177,7 +10151,7 @@
       <c r="C400" t="s">
         <v>142</v>
       </c>
-      <c r="H400" s="2">
+      <c r="H400" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10200,7 +10174,7 @@
       <c r="G401" t="s">
         <v>220</v>
       </c>
-      <c r="H401" s="2">
+      <c r="H401" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10217,7 +10191,7 @@
       <c r="D402" t="s">
         <v>159</v>
       </c>
-      <c r="H402" s="2">
+      <c r="H402" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10240,7 +10214,7 @@
       <c r="G403" t="s">
         <v>221</v>
       </c>
-      <c r="H403" s="2">
+      <c r="H403" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10257,13 +10231,13 @@
       <c r="D404" t="s">
         <v>181</v>
       </c>
-      <c r="E404" s="2">
+      <c r="E404" s="1">
         <v>46295</v>
       </c>
       <c r="G404" t="s">
         <v>247</v>
       </c>
-      <c r="H404" s="2">
+      <c r="H404" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10286,7 +10260,7 @@
       <c r="G405" t="s">
         <v>222</v>
       </c>
-      <c r="H405" s="2">
+      <c r="H405" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10309,7 +10283,7 @@
       <c r="G406" t="s">
         <v>222</v>
       </c>
-      <c r="H406" s="2">
+      <c r="H406" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10332,7 +10306,7 @@
       <c r="G407" t="s">
         <v>223</v>
       </c>
-      <c r="H407" s="2">
+      <c r="H407" s="1">
         <v>46226</v>
       </c>
     </row>
@@ -10346,7 +10320,7 @@
       <c r="C408" t="s">
         <v>142</v>
       </c>
-      <c r="H408" s="2">
+      <c r="H408" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10363,13 +10337,13 @@
       <c r="D409" t="s">
         <v>169</v>
       </c>
-      <c r="E409" s="2">
+      <c r="E409" s="1">
         <v>46231</v>
       </c>
       <c r="G409" t="s">
         <v>253</v>
       </c>
-      <c r="H409" s="2">
+      <c r="H409" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10383,7 +10357,7 @@
       <c r="C410" t="s">
         <v>142</v>
       </c>
-      <c r="H410" s="2">
+      <c r="H410" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10397,7 +10371,7 @@
       <c r="C411" t="s">
         <v>142</v>
       </c>
-      <c r="H411" s="2">
+      <c r="H411" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10411,7 +10385,7 @@
       <c r="C412" t="s">
         <v>142</v>
       </c>
-      <c r="H412" s="2">
+      <c r="H412" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10425,7 +10399,7 @@
       <c r="C413" t="s">
         <v>146</v>
       </c>
-      <c r="H413" s="2">
+      <c r="H413" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10439,7 +10413,7 @@
       <c r="C414" t="s">
         <v>146</v>
       </c>
-      <c r="H414" s="2">
+      <c r="H414" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10456,13 +10430,13 @@
       <c r="D415" t="s">
         <v>201</v>
       </c>
-      <c r="E415" s="2">
+      <c r="E415" s="1">
         <v>46234</v>
       </c>
       <c r="G415" t="s">
         <v>250</v>
       </c>
-      <c r="H415" s="2">
+      <c r="H415" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10476,7 +10450,7 @@
       <c r="C416" t="s">
         <v>142</v>
       </c>
-      <c r="H416" s="2">
+      <c r="H416" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10490,7 +10464,7 @@
       <c r="C417" t="s">
         <v>146</v>
       </c>
-      <c r="H417" s="2">
+      <c r="H417" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10504,7 +10478,7 @@
       <c r="C418" t="s">
         <v>142</v>
       </c>
-      <c r="H418" s="2">
+      <c r="H418" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10518,7 +10492,7 @@
       <c r="C419" t="s">
         <v>142</v>
       </c>
-      <c r="H419" s="2">
+      <c r="H419" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10535,13 +10509,13 @@
       <c r="D420" t="s">
         <v>155</v>
       </c>
-      <c r="E420" s="2">
+      <c r="E420" s="1">
         <v>46237</v>
       </c>
       <c r="G420" t="s">
         <v>252</v>
       </c>
-      <c r="H420" s="2">
+      <c r="H420" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10555,7 +10529,7 @@
       <c r="C421" t="s">
         <v>142</v>
       </c>
-      <c r="H421" s="2">
+      <c r="H421" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10572,13 +10546,13 @@
       <c r="D422" t="s">
         <v>187</v>
       </c>
-      <c r="E422" s="2">
+      <c r="E422" s="1">
         <v>46227</v>
       </c>
       <c r="G422" t="s">
         <v>251</v>
       </c>
-      <c r="H422" s="2">
+      <c r="H422" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10592,7 +10566,7 @@
       <c r="C423" t="s">
         <v>142</v>
       </c>
-      <c r="H423" s="2">
+      <c r="H423" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10606,7 +10580,7 @@
       <c r="C424" t="s">
         <v>142</v>
       </c>
-      <c r="H424" s="2">
+      <c r="H424" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10623,13 +10597,13 @@
       <c r="D425" t="s">
         <v>192</v>
       </c>
-      <c r="E425" s="2">
+      <c r="E425" s="1">
         <v>46234</v>
       </c>
       <c r="G425" t="s">
         <v>250</v>
       </c>
-      <c r="H425" s="2">
+      <c r="H425" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10646,13 +10620,13 @@
       <c r="D426" t="s">
         <v>199</v>
       </c>
-      <c r="E426" s="2">
+      <c r="E426" s="1">
         <v>46227</v>
       </c>
       <c r="G426" t="s">
         <v>251</v>
       </c>
-      <c r="H426" s="2">
+      <c r="H426" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10669,7 +10643,7 @@
       <c r="D427" t="s">
         <v>198</v>
       </c>
-      <c r="H427" s="2">
+      <c r="H427" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10683,7 +10657,7 @@
       <c r="C428" t="s">
         <v>142</v>
       </c>
-      <c r="H428" s="2">
+      <c r="H428" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10706,7 +10680,7 @@
       <c r="G429" t="s">
         <v>220</v>
       </c>
-      <c r="H429" s="2">
+      <c r="H429" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10723,7 +10697,7 @@
       <c r="D430" t="s">
         <v>159</v>
       </c>
-      <c r="H430" s="2">
+      <c r="H430" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10746,7 +10720,7 @@
       <c r="G431" t="s">
         <v>221</v>
       </c>
-      <c r="H431" s="2">
+      <c r="H431" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10763,13 +10737,13 @@
       <c r="D432" t="s">
         <v>181</v>
       </c>
-      <c r="E432" s="2">
+      <c r="E432" s="1">
         <v>46295</v>
       </c>
       <c r="G432" t="s">
         <v>247</v>
       </c>
-      <c r="H432" s="2">
+      <c r="H432" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10792,7 +10766,7 @@
       <c r="G433" t="s">
         <v>222</v>
       </c>
-      <c r="H433" s="2">
+      <c r="H433" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10815,7 +10789,7 @@
       <c r="G434" t="s">
         <v>222</v>
       </c>
-      <c r="H434" s="2">
+      <c r="H434" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10838,7 +10812,7 @@
       <c r="G435" t="s">
         <v>223</v>
       </c>
-      <c r="H435" s="2">
+      <c r="H435" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10855,13 +10829,13 @@
       <c r="D436" t="s">
         <v>202</v>
       </c>
-      <c r="E436" s="2">
+      <c r="E436" s="1">
         <v>46230</v>
       </c>
       <c r="G436" t="s">
         <v>254</v>
       </c>
-      <c r="H436" s="2">
+      <c r="H436" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -10875,7 +10849,7 @@
       <c r="C437" t="s">
         <v>142</v>
       </c>
-      <c r="H437" s="2">
+      <c r="H437" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10892,13 +10866,13 @@
       <c r="D438" t="s">
         <v>169</v>
       </c>
-      <c r="E438" s="2">
+      <c r="E438" s="1">
         <v>46231</v>
       </c>
       <c r="G438" t="s">
         <v>253</v>
       </c>
-      <c r="H438" s="2">
+      <c r="H438" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10912,7 +10886,7 @@
       <c r="C439" t="s">
         <v>142</v>
       </c>
-      <c r="H439" s="2">
+      <c r="H439" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10926,7 +10900,7 @@
       <c r="C440" t="s">
         <v>142</v>
       </c>
-      <c r="H440" s="2">
+      <c r="H440" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10940,7 +10914,7 @@
       <c r="C441" t="s">
         <v>142</v>
       </c>
-      <c r="H441" s="2">
+      <c r="H441" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10954,7 +10928,7 @@
       <c r="C442" t="s">
         <v>146</v>
       </c>
-      <c r="H442" s="2">
+      <c r="H442" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10968,7 +10942,7 @@
       <c r="C443" t="s">
         <v>146</v>
       </c>
-      <c r="H443" s="2">
+      <c r="H443" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -10985,13 +10959,13 @@
       <c r="D444" t="s">
         <v>201</v>
       </c>
-      <c r="E444" s="2">
+      <c r="E444" s="1">
         <v>46234</v>
       </c>
       <c r="G444" t="s">
         <v>250</v>
       </c>
-      <c r="H444" s="2">
+      <c r="H444" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11005,7 +10979,7 @@
       <c r="C445" t="s">
         <v>142</v>
       </c>
-      <c r="H445" s="2">
+      <c r="H445" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11022,13 +10996,13 @@
       <c r="D446" t="s">
         <v>203</v>
       </c>
-      <c r="E446" s="2">
+      <c r="E446" s="1">
         <v>46230</v>
       </c>
       <c r="G446" t="s">
         <v>254</v>
       </c>
-      <c r="H446" s="2">
+      <c r="H446" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11042,7 +11016,7 @@
       <c r="C447" t="s">
         <v>142</v>
       </c>
-      <c r="H447" s="2">
+      <c r="H447" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11056,7 +11030,7 @@
       <c r="C448" t="s">
         <v>142</v>
       </c>
-      <c r="H448" s="2">
+      <c r="H448" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11073,13 +11047,13 @@
       <c r="D449" t="s">
         <v>155</v>
       </c>
-      <c r="E449" s="2">
+      <c r="E449" s="1">
         <v>46237</v>
       </c>
       <c r="G449" t="s">
         <v>252</v>
       </c>
-      <c r="H449" s="2">
+      <c r="H449" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11093,7 +11067,7 @@
       <c r="C450" t="s">
         <v>142</v>
       </c>
-      <c r="H450" s="2">
+      <c r="H450" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11107,7 +11081,7 @@
       <c r="C451" t="s">
         <v>142</v>
       </c>
-      <c r="H451" s="2">
+      <c r="H451" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11121,7 +11095,7 @@
       <c r="C452" t="s">
         <v>142</v>
       </c>
-      <c r="H452" s="2">
+      <c r="H452" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11135,7 +11109,7 @@
       <c r="C453" t="s">
         <v>142</v>
       </c>
-      <c r="H453" s="2">
+      <c r="H453" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11152,13 +11126,13 @@
       <c r="D454" t="s">
         <v>192</v>
       </c>
-      <c r="E454" s="2">
+      <c r="E454" s="1">
         <v>46234</v>
       </c>
       <c r="G454" t="s">
         <v>250</v>
       </c>
-      <c r="H454" s="2">
+      <c r="H454" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11172,7 +11146,7 @@
       <c r="C455" t="s">
         <v>146</v>
       </c>
-      <c r="H455" s="2">
+      <c r="H455" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11189,7 +11163,7 @@
       <c r="D456" t="s">
         <v>198</v>
       </c>
-      <c r="H456" s="2">
+      <c r="H456" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11203,7 +11177,7 @@
       <c r="C457" t="s">
         <v>142</v>
       </c>
-      <c r="H457" s="2">
+      <c r="H457" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11226,7 +11200,7 @@
       <c r="G458" t="s">
         <v>220</v>
       </c>
-      <c r="H458" s="2">
+      <c r="H458" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11243,7 +11217,7 @@
       <c r="D459" t="s">
         <v>159</v>
       </c>
-      <c r="H459" s="2">
+      <c r="H459" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11266,7 +11240,7 @@
       <c r="G460" t="s">
         <v>221</v>
       </c>
-      <c r="H460" s="2">
+      <c r="H460" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11283,13 +11257,13 @@
       <c r="D461" t="s">
         <v>181</v>
       </c>
-      <c r="E461" s="2">
+      <c r="E461" s="1">
         <v>46295</v>
       </c>
       <c r="G461" t="s">
         <v>247</v>
       </c>
-      <c r="H461" s="2">
+      <c r="H461" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11312,7 +11286,7 @@
       <c r="G462" t="s">
         <v>222</v>
       </c>
-      <c r="H462" s="2">
+      <c r="H462" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11335,7 +11309,7 @@
       <c r="G463" t="s">
         <v>222</v>
       </c>
-      <c r="H463" s="2">
+      <c r="H463" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11358,7 +11332,7 @@
       <c r="G464" t="s">
         <v>223</v>
       </c>
-      <c r="H464" s="2">
+      <c r="H464" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11375,13 +11349,13 @@
       <c r="D465" t="s">
         <v>202</v>
       </c>
-      <c r="E465" s="2">
+      <c r="E465" s="1">
         <v>46230</v>
       </c>
       <c r="G465" t="s">
         <v>254</v>
       </c>
-      <c r="H465" s="2">
+      <c r="H465" s="1">
         <v>46230</v>
       </c>
     </row>
@@ -11398,13 +11372,13 @@
       <c r="D466" t="s">
         <v>204</v>
       </c>
-      <c r="E466" s="2">
+      <c r="E466" s="1">
         <v>46231</v>
       </c>
       <c r="G466" t="s">
         <v>253</v>
       </c>
-      <c r="H466" s="2">
+      <c r="H466" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11421,13 +11395,13 @@
       <c r="D467" t="s">
         <v>169</v>
       </c>
-      <c r="E467" s="2">
+      <c r="E467" s="1">
         <v>46231</v>
       </c>
       <c r="G467" t="s">
         <v>253</v>
       </c>
-      <c r="H467" s="2">
+      <c r="H467" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11441,7 +11415,7 @@
       <c r="C468" t="s">
         <v>142</v>
       </c>
-      <c r="H468" s="2">
+      <c r="H468" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11455,7 +11429,7 @@
       <c r="C469" t="s">
         <v>142</v>
       </c>
-      <c r="H469" s="2">
+      <c r="H469" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11469,7 +11443,7 @@
       <c r="C470" t="s">
         <v>142</v>
       </c>
-      <c r="H470" s="2">
+      <c r="H470" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11483,7 +11457,7 @@
       <c r="C471" t="s">
         <v>146</v>
       </c>
-      <c r="H471" s="2">
+      <c r="H471" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11497,7 +11471,7 @@
       <c r="C472" t="s">
         <v>146</v>
       </c>
-      <c r="H472" s="2">
+      <c r="H472" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11514,13 +11488,13 @@
       <c r="D473" t="s">
         <v>201</v>
       </c>
-      <c r="E473" s="2">
+      <c r="E473" s="1">
         <v>46234</v>
       </c>
       <c r="G473" t="s">
         <v>250</v>
       </c>
-      <c r="H473" s="2">
+      <c r="H473" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11534,7 +11508,7 @@
       <c r="C474" t="s">
         <v>142</v>
       </c>
-      <c r="H474" s="2">
+      <c r="H474" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11551,13 +11525,13 @@
       <c r="D475" t="s">
         <v>205</v>
       </c>
-      <c r="E475" s="2">
+      <c r="E475" s="1">
         <v>46231</v>
       </c>
       <c r="G475" t="s">
         <v>253</v>
       </c>
-      <c r="H475" s="2">
+      <c r="H475" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11571,7 +11545,7 @@
       <c r="C476" t="s">
         <v>142</v>
       </c>
-      <c r="H476" s="2">
+      <c r="H476" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11585,7 +11559,7 @@
       <c r="C477" t="s">
         <v>142</v>
       </c>
-      <c r="H477" s="2">
+      <c r="H477" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11602,13 +11576,13 @@
       <c r="D478" t="s">
         <v>155</v>
       </c>
-      <c r="E478" s="2">
+      <c r="E478" s="1">
         <v>46237</v>
       </c>
       <c r="G478" t="s">
         <v>252</v>
       </c>
-      <c r="H478" s="2">
+      <c r="H478" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11622,7 +11596,7 @@
       <c r="C479" t="s">
         <v>142</v>
       </c>
-      <c r="H479" s="2">
+      <c r="H479" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11636,7 +11610,7 @@
       <c r="C480" t="s">
         <v>142</v>
       </c>
-      <c r="H480" s="2">
+      <c r="H480" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11650,7 +11624,7 @@
       <c r="C481" t="s">
         <v>142</v>
       </c>
-      <c r="H481" s="2">
+      <c r="H481" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11664,7 +11638,7 @@
       <c r="C482" t="s">
         <v>142</v>
       </c>
-      <c r="H482" s="2">
+      <c r="H482" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11681,13 +11655,13 @@
       <c r="D483" t="s">
         <v>192</v>
       </c>
-      <c r="E483" s="2">
+      <c r="E483" s="1">
         <v>46234</v>
       </c>
       <c r="G483" t="s">
         <v>250</v>
       </c>
-      <c r="H483" s="2">
+      <c r="H483" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11701,7 +11675,7 @@
       <c r="C484" t="s">
         <v>146</v>
       </c>
-      <c r="H484" s="2">
+      <c r="H484" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11718,7 +11692,7 @@
       <c r="D485" t="s">
         <v>198</v>
       </c>
-      <c r="H485" s="2">
+      <c r="H485" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11732,7 +11706,7 @@
       <c r="C486" t="s">
         <v>142</v>
       </c>
-      <c r="H486" s="2">
+      <c r="H486" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11755,7 +11729,7 @@
       <c r="G487" t="s">
         <v>220</v>
       </c>
-      <c r="H487" s="2">
+      <c r="H487" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11772,7 +11746,7 @@
       <c r="D488" t="s">
         <v>159</v>
       </c>
-      <c r="H488" s="2">
+      <c r="H488" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11795,7 +11769,7 @@
       <c r="G489" t="s">
         <v>221</v>
       </c>
-      <c r="H489" s="2">
+      <c r="H489" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11812,13 +11786,13 @@
       <c r="D490" t="s">
         <v>181</v>
       </c>
-      <c r="E490" s="2">
+      <c r="E490" s="1">
         <v>46295</v>
       </c>
       <c r="G490" t="s">
         <v>247</v>
       </c>
-      <c r="H490" s="2">
+      <c r="H490" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11841,7 +11815,7 @@
       <c r="G491" t="s">
         <v>222</v>
       </c>
-      <c r="H491" s="2">
+      <c r="H491" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11864,7 +11838,7 @@
       <c r="G492" t="s">
         <v>222</v>
       </c>
-      <c r="H492" s="2">
+      <c r="H492" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11887,7 +11861,7 @@
       <c r="G493" t="s">
         <v>223</v>
       </c>
-      <c r="H493" s="2">
+      <c r="H493" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11904,13 +11878,13 @@
       <c r="D494" t="s">
         <v>202</v>
       </c>
-      <c r="E494" s="2">
+      <c r="E494" s="1">
         <v>46233</v>
       </c>
       <c r="G494" t="s">
         <v>255</v>
       </c>
-      <c r="H494" s="2">
+      <c r="H494" s="1">
         <v>46231</v>
       </c>
     </row>
@@ -11924,7 +11898,7 @@
       <c r="C495" t="s">
         <v>142</v>
       </c>
-      <c r="H495" s="2">
+      <c r="H495" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11941,13 +11915,13 @@
       <c r="D496" t="s">
         <v>206</v>
       </c>
-      <c r="E496" s="2">
+      <c r="E496" s="1">
         <v>46233</v>
       </c>
       <c r="G496" t="s">
         <v>256</v>
       </c>
-      <c r="H496" s="2">
+      <c r="H496" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11961,7 +11935,7 @@
       <c r="C497" t="s">
         <v>142</v>
       </c>
-      <c r="H497" s="2">
+      <c r="H497" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11975,7 +11949,7 @@
       <c r="C498" t="s">
         <v>142</v>
       </c>
-      <c r="H498" s="2">
+      <c r="H498" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -11989,7 +11963,7 @@
       <c r="C499" t="s">
         <v>142</v>
       </c>
-      <c r="H499" s="2">
+      <c r="H499" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12003,7 +11977,7 @@
       <c r="C500" t="s">
         <v>146</v>
       </c>
-      <c r="H500" s="2">
+      <c r="H500" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12017,7 +11991,7 @@
       <c r="C501" t="s">
         <v>146</v>
       </c>
-      <c r="H501" s="2">
+      <c r="H501" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12034,13 +12008,13 @@
       <c r="D502" t="s">
         <v>201</v>
       </c>
-      <c r="E502" s="2">
+      <c r="E502" s="1">
         <v>46248</v>
       </c>
       <c r="G502" t="s">
         <v>257</v>
       </c>
-      <c r="H502" s="2">
+      <c r="H502" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12054,7 +12028,7 @@
       <c r="C503" t="s">
         <v>142</v>
       </c>
-      <c r="H503" s="2">
+      <c r="H503" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12068,7 +12042,7 @@
       <c r="C504" t="s">
         <v>146</v>
       </c>
-      <c r="H504" s="2">
+      <c r="H504" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12082,7 +12056,7 @@
       <c r="C505" t="s">
         <v>142</v>
       </c>
-      <c r="H505" s="2">
+      <c r="H505" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12096,7 +12070,7 @@
       <c r="C506" t="s">
         <v>142</v>
       </c>
-      <c r="H506" s="2">
+      <c r="H506" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12113,13 +12087,13 @@
       <c r="D507" t="s">
         <v>155</v>
       </c>
-      <c r="E507" s="2">
+      <c r="E507" s="1">
         <v>46237</v>
       </c>
       <c r="G507" t="s">
         <v>241</v>
       </c>
-      <c r="H507" s="2">
+      <c r="H507" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12133,7 +12107,7 @@
       <c r="C508" t="s">
         <v>142</v>
       </c>
-      <c r="H508" s="2">
+      <c r="H508" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12147,7 +12121,7 @@
       <c r="C509" t="s">
         <v>142</v>
       </c>
-      <c r="H509" s="2">
+      <c r="H509" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12161,7 +12135,7 @@
       <c r="C510" t="s">
         <v>142</v>
       </c>
-      <c r="H510" s="2">
+      <c r="H510" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12175,7 +12149,7 @@
       <c r="C511" t="s">
         <v>142</v>
       </c>
-      <c r="H511" s="2">
+      <c r="H511" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12192,13 +12166,13 @@
       <c r="D512" t="s">
         <v>207</v>
       </c>
-      <c r="E512" s="2">
+      <c r="E512" s="1">
         <v>46234</v>
       </c>
       <c r="G512" t="s">
         <v>228</v>
       </c>
-      <c r="H512" s="2">
+      <c r="H512" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12215,13 +12189,13 @@
       <c r="D513" t="s">
         <v>208</v>
       </c>
-      <c r="E513" s="2">
+      <c r="E513" s="1">
         <v>46238</v>
       </c>
       <c r="G513" t="s">
         <v>258</v>
       </c>
-      <c r="H513" s="2">
+      <c r="H513" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12235,7 +12209,7 @@
       <c r="C514" t="s">
         <v>146</v>
       </c>
-      <c r="H514" s="2">
+      <c r="H514" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12249,7 +12223,7 @@
       <c r="C515" t="s">
         <v>142</v>
       </c>
-      <c r="H515" s="2">
+      <c r="H515" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12272,7 +12246,7 @@
       <c r="G516" t="s">
         <v>220</v>
       </c>
-      <c r="H516" s="2">
+      <c r="H516" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12289,7 +12263,7 @@
       <c r="D517" t="s">
         <v>159</v>
       </c>
-      <c r="H517" s="2">
+      <c r="H517" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12312,7 +12286,7 @@
       <c r="G518" t="s">
         <v>221</v>
       </c>
-      <c r="H518" s="2">
+      <c r="H518" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12329,13 +12303,13 @@
       <c r="D519" t="s">
         <v>181</v>
       </c>
-      <c r="E519" s="2">
+      <c r="E519" s="1">
         <v>46295</v>
       </c>
       <c r="G519" t="s">
         <v>239</v>
       </c>
-      <c r="H519" s="2">
+      <c r="H519" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12358,7 +12332,7 @@
       <c r="G520" t="s">
         <v>222</v>
       </c>
-      <c r="H520" s="2">
+      <c r="H520" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12381,7 +12355,7 @@
       <c r="G521" t="s">
         <v>222</v>
       </c>
-      <c r="H521" s="2">
+      <c r="H521" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12404,7 +12378,7 @@
       <c r="G522" t="s">
         <v>223</v>
       </c>
-      <c r="H522" s="2">
+      <c r="H522" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12421,13 +12395,13 @@
       <c r="D523" t="s">
         <v>209</v>
       </c>
-      <c r="E523" s="2">
+      <c r="E523" s="1">
         <v>46233</v>
       </c>
       <c r="G523" t="s">
         <v>255</v>
       </c>
-      <c r="H523" s="2">
+      <c r="H523" s="1">
         <v>46232</v>
       </c>
     </row>
@@ -12441,7 +12415,7 @@
       <c r="C524" t="s">
         <v>142</v>
       </c>
-      <c r="H524" s="2">
+      <c r="H524" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12458,13 +12432,13 @@
       <c r="D525" t="s">
         <v>206</v>
       </c>
-      <c r="E525" s="2">
+      <c r="E525" s="1">
         <v>46233</v>
       </c>
       <c r="G525" t="s">
         <v>256</v>
       </c>
-      <c r="H525" s="2">
+      <c r="H525" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12478,7 +12452,7 @@
       <c r="C526" t="s">
         <v>142</v>
       </c>
-      <c r="H526" s="2">
+      <c r="H526" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12492,7 +12466,7 @@
       <c r="C527" t="s">
         <v>142</v>
       </c>
-      <c r="H527" s="2">
+      <c r="H527" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12506,7 +12480,7 @@
       <c r="C528" t="s">
         <v>142</v>
       </c>
-      <c r="H528" s="2">
+      <c r="H528" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12520,7 +12494,7 @@
       <c r="C529" t="s">
         <v>146</v>
       </c>
-      <c r="H529" s="2">
+      <c r="H529" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12534,7 +12508,7 @@
       <c r="C530" t="s">
         <v>146</v>
       </c>
-      <c r="H530" s="2">
+      <c r="H530" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12551,13 +12525,13 @@
       <c r="D531" t="s">
         <v>201</v>
       </c>
-      <c r="E531" s="2">
+      <c r="E531" s="1">
         <v>46248</v>
       </c>
       <c r="G531" t="s">
         <v>257</v>
       </c>
-      <c r="H531" s="2">
+      <c r="H531" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12571,7 +12545,7 @@
       <c r="C532" t="s">
         <v>142</v>
       </c>
-      <c r="H532" s="2">
+      <c r="H532" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12585,7 +12559,7 @@
       <c r="C533" t="s">
         <v>146</v>
       </c>
-      <c r="H533" s="2">
+      <c r="H533" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12599,7 +12573,7 @@
       <c r="C534" t="s">
         <v>142</v>
       </c>
-      <c r="H534" s="2">
+      <c r="H534" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12613,7 +12587,7 @@
       <c r="C535" t="s">
         <v>142</v>
       </c>
-      <c r="H535" s="2">
+      <c r="H535" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12630,13 +12604,13 @@
       <c r="D536" t="s">
         <v>155</v>
       </c>
-      <c r="E536" s="2">
+      <c r="E536" s="1">
         <v>46237</v>
       </c>
       <c r="G536" t="s">
         <v>241</v>
       </c>
-      <c r="H536" s="2">
+      <c r="H536" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12650,7 +12624,7 @@
       <c r="C537" t="s">
         <v>142</v>
       </c>
-      <c r="H537" s="2">
+      <c r="H537" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12664,7 +12638,7 @@
       <c r="C538" t="s">
         <v>142</v>
       </c>
-      <c r="H538" s="2">
+      <c r="H538" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12678,7 +12652,7 @@
       <c r="C539" t="s">
         <v>142</v>
       </c>
-      <c r="H539" s="2">
+      <c r="H539" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12692,7 +12666,7 @@
       <c r="C540" t="s">
         <v>142</v>
       </c>
-      <c r="H540" s="2">
+      <c r="H540" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12706,7 +12680,7 @@
       <c r="C541" t="s">
         <v>146</v>
       </c>
-      <c r="H541" s="2">
+      <c r="H541" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12723,13 +12697,13 @@
       <c r="D542" t="s">
         <v>208</v>
       </c>
-      <c r="E542" s="2">
+      <c r="E542" s="1">
         <v>46238</v>
       </c>
       <c r="G542" t="s">
         <v>258</v>
       </c>
-      <c r="H542" s="2">
+      <c r="H542" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12743,7 +12717,7 @@
       <c r="C543" t="s">
         <v>146</v>
       </c>
-      <c r="H543" s="2">
+      <c r="H543" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12757,7 +12731,7 @@
       <c r="C544" t="s">
         <v>142</v>
       </c>
-      <c r="H544" s="2">
+      <c r="H544" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12780,7 +12754,7 @@
       <c r="G545" t="s">
         <v>220</v>
       </c>
-      <c r="H545" s="2">
+      <c r="H545" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12797,7 +12771,7 @@
       <c r="D546" t="s">
         <v>159</v>
       </c>
-      <c r="H546" s="2">
+      <c r="H546" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12820,7 +12794,7 @@
       <c r="G547" t="s">
         <v>221</v>
       </c>
-      <c r="H547" s="2">
+      <c r="H547" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12837,13 +12811,13 @@
       <c r="D548" t="s">
         <v>181</v>
       </c>
-      <c r="E548" s="2">
+      <c r="E548" s="1">
         <v>46295</v>
       </c>
       <c r="G548" t="s">
         <v>239</v>
       </c>
-      <c r="H548" s="2">
+      <c r="H548" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12866,7 +12840,7 @@
       <c r="G549" t="s">
         <v>222</v>
       </c>
-      <c r="H549" s="2">
+      <c r="H549" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12889,7 +12863,7 @@
       <c r="G550" t="s">
         <v>222</v>
       </c>
-      <c r="H550" s="2">
+      <c r="H550" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12912,7 +12886,7 @@
       <c r="G551" t="s">
         <v>223</v>
       </c>
-      <c r="H551" s="2">
+      <c r="H551" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12929,13 +12903,13 @@
       <c r="D552" t="s">
         <v>210</v>
       </c>
-      <c r="E552" s="2">
+      <c r="E552" s="1">
         <v>46233</v>
       </c>
       <c r="G552" t="s">
         <v>255</v>
       </c>
-      <c r="H552" s="2">
+      <c r="H552" s="1">
         <v>46233</v>
       </c>
     </row>
@@ -12949,7 +12923,7 @@
       <c r="C553" t="s">
         <v>142</v>
       </c>
-      <c r="H553" s="2">
+      <c r="H553" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12972,7 +12946,7 @@
       <c r="G554" t="s">
         <v>218</v>
       </c>
-      <c r="H554" s="2">
+      <c r="H554" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -12986,7 +12960,7 @@
       <c r="C555" t="s">
         <v>142</v>
       </c>
-      <c r="H555" s="2">
+      <c r="H555" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13000,7 +12974,7 @@
       <c r="C556" t="s">
         <v>142</v>
       </c>
-      <c r="H556" s="2">
+      <c r="H556" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13014,7 +12988,7 @@
       <c r="C557" t="s">
         <v>142</v>
       </c>
-      <c r="H557" s="2">
+      <c r="H557" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13028,7 +13002,7 @@
       <c r="C558" t="s">
         <v>146</v>
       </c>
-      <c r="H558" s="2">
+      <c r="H558" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13042,7 +13016,7 @@
       <c r="C559" t="s">
         <v>146</v>
       </c>
-      <c r="H559" s="2">
+      <c r="H559" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13059,13 +13033,13 @@
       <c r="D560" t="s">
         <v>201</v>
       </c>
-      <c r="E560" s="2">
+      <c r="E560" s="1">
         <v>46248</v>
       </c>
       <c r="G560" t="s">
         <v>257</v>
       </c>
-      <c r="H560" s="2">
+      <c r="H560" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13079,7 +13053,7 @@
       <c r="C561" t="s">
         <v>142</v>
       </c>
-      <c r="H561" s="2">
+      <c r="H561" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13093,7 +13067,7 @@
       <c r="C562" t="s">
         <v>146</v>
       </c>
-      <c r="H562" s="2">
+      <c r="H562" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13107,7 +13081,7 @@
       <c r="C563" t="s">
         <v>142</v>
       </c>
-      <c r="H563" s="2">
+      <c r="H563" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13121,7 +13095,7 @@
       <c r="C564" t="s">
         <v>142</v>
       </c>
-      <c r="H564" s="2">
+      <c r="H564" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13135,7 +13109,7 @@
       <c r="C565" t="s">
         <v>142</v>
       </c>
-      <c r="H565" s="2">
+      <c r="H565" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13152,13 +13126,13 @@
       <c r="D566" t="s">
         <v>155</v>
       </c>
-      <c r="E566" s="2">
+      <c r="E566" s="1">
         <v>46262</v>
       </c>
       <c r="G566" t="s">
         <v>259</v>
       </c>
-      <c r="H566" s="2">
+      <c r="H566" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13172,7 +13146,7 @@
       <c r="C567" t="s">
         <v>142</v>
       </c>
-      <c r="H567" s="2">
+      <c r="H567" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13186,7 +13160,7 @@
       <c r="C568" t="s">
         <v>142</v>
       </c>
-      <c r="H568" s="2">
+      <c r="H568" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13200,7 +13174,7 @@
       <c r="C569" t="s">
         <v>142</v>
       </c>
-      <c r="H569" s="2">
+      <c r="H569" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13214,7 +13188,7 @@
       <c r="C570" t="s">
         <v>142</v>
       </c>
-      <c r="H570" s="2">
+      <c r="H570" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13228,7 +13202,7 @@
       <c r="C571" t="s">
         <v>142</v>
       </c>
-      <c r="H571" s="2">
+      <c r="H571" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13245,13 +13219,13 @@
       <c r="D572" t="s">
         <v>208</v>
       </c>
-      <c r="E572" s="2">
+      <c r="E572" s="1">
         <v>46238</v>
       </c>
       <c r="G572" t="s">
         <v>258</v>
       </c>
-      <c r="H572" s="2">
+      <c r="H572" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13265,7 +13239,7 @@
       <c r="C573" t="s">
         <v>146</v>
       </c>
-      <c r="H573" s="2">
+      <c r="H573" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13279,7 +13253,7 @@
       <c r="C574" t="s">
         <v>142</v>
       </c>
-      <c r="H574" s="2">
+      <c r="H574" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13302,7 +13276,7 @@
       <c r="G575" t="s">
         <v>220</v>
       </c>
-      <c r="H575" s="2">
+      <c r="H575" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13319,7 +13293,7 @@
       <c r="D576" t="s">
         <v>159</v>
       </c>
-      <c r="H576" s="2">
+      <c r="H576" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13342,7 +13316,7 @@
       <c r="G577" t="s">
         <v>221</v>
       </c>
-      <c r="H577" s="2">
+      <c r="H577" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13359,13 +13333,13 @@
       <c r="D578" t="s">
         <v>181</v>
       </c>
-      <c r="E578" s="2">
+      <c r="E578" s="1">
         <v>46295</v>
       </c>
       <c r="G578" t="s">
         <v>239</v>
       </c>
-      <c r="H578" s="2">
+      <c r="H578" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13388,7 +13362,7 @@
       <c r="G579" t="s">
         <v>222</v>
       </c>
-      <c r="H579" s="2">
+      <c r="H579" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13411,7 +13385,7 @@
       <c r="G580" t="s">
         <v>222</v>
       </c>
-      <c r="H580" s="2">
+      <c r="H580" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13434,7 +13408,7 @@
       <c r="G581" t="s">
         <v>223</v>
       </c>
-      <c r="H581" s="2">
+      <c r="H581" s="1">
         <v>46234</v>
       </c>
     </row>
@@ -13448,7 +13422,7 @@
       <c r="C582" t="s">
         <v>142</v>
       </c>
-      <c r="H582" s="2">
+      <c r="H582" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13471,7 +13445,7 @@
       <c r="G583" t="s">
         <v>218</v>
       </c>
-      <c r="H583" s="2">
+      <c r="H583" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13485,7 +13459,7 @@
       <c r="C584" t="s">
         <v>142</v>
       </c>
-      <c r="H584" s="2">
+      <c r="H584" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13499,7 +13473,7 @@
       <c r="C585" t="s">
         <v>142</v>
       </c>
-      <c r="H585" s="2">
+      <c r="H585" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13513,7 +13487,7 @@
       <c r="C586" t="s">
         <v>146</v>
       </c>
-      <c r="H586" s="2">
+      <c r="H586" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13527,7 +13501,7 @@
       <c r="C587" t="s">
         <v>146</v>
       </c>
-      <c r="H587" s="2">
+      <c r="H587" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13544,13 +13518,13 @@
       <c r="D588" t="s">
         <v>201</v>
       </c>
-      <c r="E588" s="2">
+      <c r="E588" s="1">
         <v>46248</v>
       </c>
       <c r="G588" t="s">
         <v>257</v>
       </c>
-      <c r="H588" s="2">
+      <c r="H588" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13564,7 +13538,7 @@
       <c r="C589" t="s">
         <v>142</v>
       </c>
-      <c r="H589" s="2">
+      <c r="H589" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13578,7 +13552,7 @@
       <c r="C590" t="s">
         <v>146</v>
       </c>
-      <c r="H590" s="2">
+      <c r="H590" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13592,7 +13566,7 @@
       <c r="C591" t="s">
         <v>142</v>
       </c>
-      <c r="H591" s="2">
+      <c r="H591" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13606,7 +13580,7 @@
       <c r="C592" t="s">
         <v>142</v>
       </c>
-      <c r="H592" s="2">
+      <c r="H592" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13623,13 +13597,13 @@
       <c r="D593" t="s">
         <v>212</v>
       </c>
-      <c r="E593" s="2">
+      <c r="E593" s="1">
         <v>46240</v>
       </c>
       <c r="G593" t="s">
         <v>260</v>
       </c>
-      <c r="H593" s="2">
+      <c r="H593" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13646,13 +13620,13 @@
       <c r="D594" t="s">
         <v>155</v>
       </c>
-      <c r="E594" s="2">
+      <c r="E594" s="1">
         <v>46262</v>
       </c>
       <c r="G594" t="s">
         <v>259</v>
       </c>
-      <c r="H594" s="2">
+      <c r="H594" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13666,7 +13640,7 @@
       <c r="C595" t="s">
         <v>142</v>
       </c>
-      <c r="H595" s="2">
+      <c r="H595" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13680,7 +13654,7 @@
       <c r="C596" t="s">
         <v>142</v>
       </c>
-      <c r="H596" s="2">
+      <c r="H596" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13694,7 +13668,7 @@
       <c r="C597" t="s">
         <v>142</v>
       </c>
-      <c r="H597" s="2">
+      <c r="H597" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13708,7 +13682,7 @@
       <c r="C598" t="s">
         <v>142</v>
       </c>
-      <c r="H598" s="2">
+      <c r="H598" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13725,13 +13699,13 @@
       <c r="D599" t="s">
         <v>213</v>
       </c>
-      <c r="E599" s="2">
+      <c r="E599" s="1">
         <v>46237</v>
       </c>
       <c r="G599" t="s">
         <v>241</v>
       </c>
-      <c r="H599" s="2">
+      <c r="H599" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13748,13 +13722,13 @@
       <c r="D600" t="s">
         <v>214</v>
       </c>
-      <c r="E600" s="2">
+      <c r="E600" s="1">
         <v>46237</v>
       </c>
       <c r="G600" t="s">
         <v>241</v>
       </c>
-      <c r="H600" s="2">
+      <c r="H600" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13771,13 +13745,13 @@
       <c r="D601" t="s">
         <v>208</v>
       </c>
-      <c r="E601" s="2">
+      <c r="E601" s="1">
         <v>46238</v>
       </c>
       <c r="G601" t="s">
         <v>258</v>
       </c>
-      <c r="H601" s="2">
+      <c r="H601" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13791,7 +13765,7 @@
       <c r="C602" t="s">
         <v>146</v>
       </c>
-      <c r="H602" s="2">
+      <c r="H602" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13805,7 +13779,7 @@
       <c r="C603" t="s">
         <v>142</v>
       </c>
-      <c r="H603" s="2">
+      <c r="H603" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13828,7 +13802,7 @@
       <c r="G604" t="s">
         <v>220</v>
       </c>
-      <c r="H604" s="2">
+      <c r="H604" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13845,7 +13819,7 @@
       <c r="D605" t="s">
         <v>159</v>
       </c>
-      <c r="H605" s="2">
+      <c r="H605" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13868,7 +13842,7 @@
       <c r="G606" t="s">
         <v>221</v>
       </c>
-      <c r="H606" s="2">
+      <c r="H606" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13885,13 +13859,13 @@
       <c r="D607" t="s">
         <v>181</v>
       </c>
-      <c r="E607" s="2">
+      <c r="E607" s="1">
         <v>46295</v>
       </c>
       <c r="G607" t="s">
         <v>239</v>
       </c>
-      <c r="H607" s="2">
+      <c r="H607" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13914,7 +13888,7 @@
       <c r="G608" t="s">
         <v>222</v>
       </c>
-      <c r="H608" s="2">
+      <c r="H608" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13937,7 +13911,7 @@
       <c r="G609" t="s">
         <v>222</v>
       </c>
-      <c r="H609" s="2">
+      <c r="H609" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13960,7 +13934,7 @@
       <c r="G610" t="s">
         <v>223</v>
       </c>
-      <c r="H610" s="2">
+      <c r="H610" s="1">
         <v>46237</v>
       </c>
     </row>
@@ -13974,7 +13948,7 @@
       <c r="C611" t="s">
         <v>142</v>
       </c>
-      <c r="H611" s="2">
+      <c r="H611" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -13997,7 +13971,7 @@
       <c r="G612" t="s">
         <v>218</v>
       </c>
-      <c r="H612" s="2">
+      <c r="H612" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14011,7 +13985,7 @@
       <c r="C613" t="s">
         <v>142</v>
       </c>
-      <c r="H613" s="2">
+      <c r="H613" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14025,7 +13999,7 @@
       <c r="C614" t="s">
         <v>142</v>
       </c>
-      <c r="H614" s="2">
+      <c r="H614" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14042,13 +14016,13 @@
       <c r="D615" t="s">
         <v>215</v>
       </c>
-      <c r="E615" s="2">
+      <c r="E615" s="1">
         <v>46252</v>
       </c>
       <c r="G615" t="s">
         <v>261</v>
       </c>
-      <c r="H615" s="2">
+      <c r="H615" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14062,7 +14036,7 @@
       <c r="C616" t="s">
         <v>146</v>
       </c>
-      <c r="H616" s="2">
+      <c r="H616" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14079,13 +14053,13 @@
       <c r="D617" t="s">
         <v>201</v>
       </c>
-      <c r="E617" s="2">
+      <c r="E617" s="1">
         <v>46248</v>
       </c>
       <c r="G617" t="s">
         <v>257</v>
       </c>
-      <c r="H617" s="2">
+      <c r="H617" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14099,7 +14073,7 @@
       <c r="C618" t="s">
         <v>142</v>
       </c>
-      <c r="H618" s="2">
+      <c r="H618" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14113,7 +14087,7 @@
       <c r="C619" t="s">
         <v>146</v>
       </c>
-      <c r="H619" s="2">
+      <c r="H619" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14127,7 +14101,7 @@
       <c r="C620" t="s">
         <v>142</v>
       </c>
-      <c r="H620" s="2">
+      <c r="H620" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14144,13 +14118,13 @@
       <c r="D621" t="s">
         <v>216</v>
       </c>
-      <c r="E621" s="2">
+      <c r="E621" s="1">
         <v>46241</v>
       </c>
       <c r="G621" t="s">
         <v>238</v>
       </c>
-      <c r="H621" s="2">
+      <c r="H621" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14167,13 +14141,13 @@
       <c r="D622" t="s">
         <v>212</v>
       </c>
-      <c r="E622" s="2">
+      <c r="E622" s="1">
         <v>46240</v>
       </c>
       <c r="G622" t="s">
         <v>260</v>
       </c>
-      <c r="H622" s="2">
+      <c r="H622" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14190,13 +14164,13 @@
       <c r="D623" t="s">
         <v>155</v>
       </c>
-      <c r="E623" s="2">
+      <c r="E623" s="1">
         <v>46276</v>
       </c>
       <c r="G623" t="s">
         <v>262</v>
       </c>
-      <c r="H623" s="2">
+      <c r="H623" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14210,7 +14184,7 @@
       <c r="C624" t="s">
         <v>142</v>
       </c>
-      <c r="H624" s="2">
+      <c r="H624" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14224,7 +14198,7 @@
       <c r="C625" t="s">
         <v>142</v>
       </c>
-      <c r="H625" s="2">
+      <c r="H625" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14241,7 +14215,7 @@
       <c r="D626" t="s">
         <v>217</v>
       </c>
-      <c r="H626" s="2">
+      <c r="H626" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14255,7 +14229,7 @@
       <c r="C627" t="s">
         <v>142</v>
       </c>
-      <c r="H627" s="2">
+      <c r="H627" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14269,7 +14243,7 @@
       <c r="C628" t="s">
         <v>142</v>
       </c>
-      <c r="H628" s="2">
+      <c r="H628" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14283,7 +14257,7 @@
       <c r="C629" t="s">
         <v>146</v>
       </c>
-      <c r="H629" s="2">
+      <c r="H629" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14300,13 +14274,13 @@
       <c r="D630" t="s">
         <v>208</v>
       </c>
-      <c r="E630" s="2">
+      <c r="E630" s="1">
         <v>46238</v>
       </c>
       <c r="G630" t="s">
         <v>258</v>
       </c>
-      <c r="H630" s="2">
+      <c r="H630" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14320,7 +14294,7 @@
       <c r="C631" t="s">
         <v>146</v>
       </c>
-      <c r="H631" s="2">
+      <c r="H631" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14334,7 +14308,7 @@
       <c r="C632" t="s">
         <v>142</v>
       </c>
-      <c r="H632" s="2">
+      <c r="H632" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14357,7 +14331,7 @@
       <c r="G633" t="s">
         <v>220</v>
       </c>
-      <c r="H633" s="2">
+      <c r="H633" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14374,7 +14348,7 @@
       <c r="D634" t="s">
         <v>159</v>
       </c>
-      <c r="H634" s="2">
+      <c r="H634" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14397,7 +14371,7 @@
       <c r="G635" t="s">
         <v>221</v>
       </c>
-      <c r="H635" s="2">
+      <c r="H635" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14414,13 +14388,13 @@
       <c r="D636" t="s">
         <v>181</v>
       </c>
-      <c r="E636" s="2">
+      <c r="E636" s="1">
         <v>46295</v>
       </c>
       <c r="G636" t="s">
         <v>239</v>
       </c>
-      <c r="H636" s="2">
+      <c r="H636" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14443,7 +14417,7 @@
       <c r="G637" t="s">
         <v>222</v>
       </c>
-      <c r="H637" s="2">
+      <c r="H637" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14466,7 +14440,7 @@
       <c r="G638" t="s">
         <v>222</v>
       </c>
-      <c r="H638" s="2">
+      <c r="H638" s="1">
         <v>46238</v>
       </c>
     </row>
@@ -14489,7 +14463,7 @@
       <c r="G639" t="s">
         <v>223</v>
       </c>
-      <c r="H639" s="2">
+      <c r="H639" s="1">
         <v>46238</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_disponibilidade_diaria.xlsx
@@ -888,16 +888,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -913,7 +905,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -921,30 +913,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1244,72 +1218,72 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>46204</v>
       </c>
       <c r="B2">
@@ -1374,7 +1348,7 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>46205</v>
       </c>
       <c r="B3">
@@ -1439,7 +1413,7 @@
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>46209</v>
       </c>
       <c r="B4">
@@ -1504,7 +1478,7 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>46210</v>
       </c>
       <c r="B5">
@@ -1569,7 +1543,7 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>46211</v>
       </c>
       <c r="B6">
@@ -1634,7 +1608,7 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>46212</v>
       </c>
       <c r="B7">
@@ -1699,7 +1673,7 @@
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>46213</v>
       </c>
       <c r="B8">
@@ -1764,7 +1738,7 @@
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>46216</v>
       </c>
       <c r="B9">
@@ -1829,7 +1803,7 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>46217</v>
       </c>
       <c r="B10">
@@ -1894,7 +1868,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>46218</v>
       </c>
       <c r="B11">
@@ -1959,7 +1933,7 @@
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>46220</v>
       </c>
       <c r="B12">
@@ -2024,7 +1998,7 @@
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>46224</v>
       </c>
       <c r="B13">
@@ -2089,7 +2063,7 @@
       </c>
     </row>
     <row r="14" spans="1:21">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>46225</v>
       </c>
       <c r="B14">
@@ -2154,7 +2128,7 @@
       </c>
     </row>
     <row r="15" spans="1:21">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>46226</v>
       </c>
       <c r="B15">
@@ -2219,7 +2193,7 @@
       </c>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>46227</v>
       </c>
       <c r="B16">
@@ -2284,7 +2258,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>46230</v>
       </c>
       <c r="B17">
@@ -2349,7 +2323,7 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>46231</v>
       </c>
       <c r="B18">
@@ -2411,7 +2385,7 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>46232</v>
       </c>
       <c r="B19">
@@ -2476,7 +2450,7 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>46233</v>
       </c>
       <c r="B20">
@@ -2541,7 +2515,7 @@
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>46234</v>
       </c>
       <c r="B21">
@@ -2603,7 +2577,7 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>46237</v>
       </c>
       <c r="B22">
@@ -2665,7 +2639,7 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>46238</v>
       </c>
       <c r="B23">
@@ -2730,7 +2704,7 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>46239</v>
       </c>
       <c r="B24">
@@ -2792,7 +2766,7 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>46240</v>
       </c>
       <c r="B25">
@@ -2854,7 +2828,7 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>46241</v>
       </c>
       <c r="B26">
@@ -2916,7 +2890,7 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>46241</v>
       </c>
       <c r="B27">
@@ -2988,28 +2962,28 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>111</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>112</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3023,7 +2997,7 @@
       <c r="C2" t="s">
         <v>153</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3037,7 +3011,7 @@
       <c r="C3" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3060,7 +3034,7 @@
       <c r="G4" t="s">
         <v>239</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3074,7 +3048,7 @@
       <c r="C5" t="s">
         <v>153</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3088,7 +3062,7 @@
       <c r="C6" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3105,13 +3079,13 @@
       <c r="D7" t="s">
         <v>161</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>46206</v>
       </c>
       <c r="G7" t="s">
         <v>250</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3128,13 +3102,13 @@
       <c r="D8" t="s">
         <v>162</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>46206</v>
       </c>
       <c r="G8" t="s">
         <v>250</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3151,13 +3125,13 @@
       <c r="D9" t="s">
         <v>163</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>46234</v>
       </c>
       <c r="G9" t="s">
         <v>251</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3174,13 +3148,13 @@
       <c r="D10" t="s">
         <v>164</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>46213</v>
       </c>
       <c r="G10" t="s">
         <v>252</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3194,7 +3168,7 @@
       <c r="C11" t="s">
         <v>153</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3208,7 +3182,7 @@
       <c r="C12" t="s">
         <v>153</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3225,13 +3199,13 @@
       <c r="D13" t="s">
         <v>165</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>46206</v>
       </c>
       <c r="G13" t="s">
         <v>250</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3245,7 +3219,7 @@
       <c r="C14" t="s">
         <v>157</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3262,13 +3236,13 @@
       <c r="D15" t="s">
         <v>166</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>46216</v>
       </c>
       <c r="G15" t="s">
         <v>253</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3282,7 +3256,7 @@
       <c r="C16" t="s">
         <v>153</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3296,7 +3270,7 @@
       <c r="C17" t="s">
         <v>153</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3313,13 +3287,13 @@
       <c r="D18" t="s">
         <v>167</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>46204</v>
       </c>
       <c r="G18" t="s">
         <v>254</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3333,7 +3307,7 @@
       <c r="C19" t="s">
         <v>153</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3350,13 +3324,13 @@
       <c r="D20" t="s">
         <v>168</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>46206</v>
       </c>
       <c r="G20" t="s">
         <v>250</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3379,7 +3353,7 @@
       <c r="G21" t="s">
         <v>240</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3393,7 +3367,7 @@
       <c r="C22" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3407,7 +3381,7 @@
       <c r="C23" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3430,7 +3404,7 @@
       <c r="G24" t="s">
         <v>241</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3447,7 +3421,7 @@
       <c r="D25" t="s">
         <v>170</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3470,7 +3444,7 @@
       <c r="G26" t="s">
         <v>242</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3487,13 +3461,13 @@
       <c r="D27" t="s">
         <v>172</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>46209</v>
       </c>
       <c r="G27" t="s">
         <v>255</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3516,7 +3490,7 @@
       <c r="G28" t="s">
         <v>243</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3539,7 +3513,7 @@
       <c r="G29" t="s">
         <v>243</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3562,7 +3536,7 @@
       <c r="G30" t="s">
         <v>244</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="1">
         <v>46204</v>
       </c>
     </row>
@@ -3576,7 +3550,7 @@
       <c r="C31" t="s">
         <v>153</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3590,7 +3564,7 @@
       <c r="C32" t="s">
         <v>153</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3613,7 +3587,7 @@
       <c r="G33" t="s">
         <v>245</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3627,7 +3601,7 @@
       <c r="C34" t="s">
         <v>153</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3641,7 +3615,7 @@
       <c r="C35" t="s">
         <v>153</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3658,13 +3632,13 @@
       <c r="D36" t="s">
         <v>161</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>46206</v>
       </c>
       <c r="G36" t="s">
         <v>250</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3681,13 +3655,13 @@
       <c r="D37" t="s">
         <v>162</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>46206</v>
       </c>
       <c r="G37" t="s">
         <v>250</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3704,13 +3678,13 @@
       <c r="D38" t="s">
         <v>163</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>46234</v>
       </c>
       <c r="G38" t="s">
         <v>251</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3727,13 +3701,13 @@
       <c r="D39" t="s">
         <v>164</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>46213</v>
       </c>
       <c r="G39" t="s">
         <v>252</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3747,7 +3721,7 @@
       <c r="C40" t="s">
         <v>153</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3761,7 +3735,7 @@
       <c r="C41" t="s">
         <v>153</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3778,13 +3752,13 @@
       <c r="D42" t="s">
         <v>165</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>46206</v>
       </c>
       <c r="G42" t="s">
         <v>250</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3798,7 +3772,7 @@
       <c r="C43" t="s">
         <v>153</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3815,13 +3789,13 @@
       <c r="D44" t="s">
         <v>166</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>46216</v>
       </c>
       <c r="G44" t="s">
         <v>253</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3835,7 +3809,7 @@
       <c r="C45" t="s">
         <v>153</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3849,7 +3823,7 @@
       <c r="C46" t="s">
         <v>153</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3863,7 +3837,7 @@
       <c r="C47" t="s">
         <v>157</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3877,7 +3851,7 @@
       <c r="C48" t="s">
         <v>153</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3894,13 +3868,13 @@
       <c r="D49" t="s">
         <v>177</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>46206</v>
       </c>
       <c r="G49" t="s">
         <v>250</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3923,7 +3897,7 @@
       <c r="G50" t="s">
         <v>240</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3937,7 +3911,7 @@
       <c r="C51" t="s">
         <v>157</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3951,7 +3925,7 @@
       <c r="C52" t="s">
         <v>153</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3974,7 +3948,7 @@
       <c r="G53" t="s">
         <v>241</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -3991,7 +3965,7 @@
       <c r="D54" t="s">
         <v>170</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -4014,7 +3988,7 @@
       <c r="G55" t="s">
         <v>242</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -4031,13 +4005,13 @@
       <c r="D56" t="s">
         <v>172</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>46209</v>
       </c>
       <c r="G56" t="s">
         <v>255</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -4060,7 +4034,7 @@
       <c r="G57" t="s">
         <v>243</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -4083,7 +4057,7 @@
       <c r="G58" t="s">
         <v>243</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -4106,7 +4080,7 @@
       <c r="G59" t="s">
         <v>244</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59" s="1">
         <v>46205</v>
       </c>
     </row>
@@ -4120,7 +4094,7 @@
       <c r="C60" t="s">
         <v>153</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4134,7 +4108,7 @@
       <c r="C61" t="s">
         <v>153</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4151,13 +4125,13 @@
       <c r="D62" t="s">
         <v>176</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>46210</v>
       </c>
       <c r="G62" t="s">
         <v>256</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4171,7 +4145,7 @@
       <c r="C63" t="s">
         <v>153</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4188,13 +4162,13 @@
       <c r="D64" t="s">
         <v>178</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>46217</v>
       </c>
       <c r="G64" t="s">
         <v>257</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4208,7 +4182,7 @@
       <c r="C65" t="s">
         <v>153</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4222,7 +4196,7 @@
       <c r="C66" t="s">
         <v>157</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4239,13 +4213,13 @@
       <c r="D67" t="s">
         <v>163</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>46234</v>
       </c>
       <c r="G67" t="s">
         <v>251</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4262,13 +4236,13 @@
       <c r="D68" t="s">
         <v>164</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>46213</v>
       </c>
       <c r="G68" t="s">
         <v>252</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4282,7 +4256,7 @@
       <c r="C69" t="s">
         <v>153</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4296,7 +4270,7 @@
       <c r="C70" t="s">
         <v>153</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4313,13 +4287,13 @@
       <c r="D71" t="s">
         <v>165</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="G71" t="s">
         <v>256</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4333,7 +4307,7 @@
       <c r="C72" t="s">
         <v>153</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4350,13 +4324,13 @@
       <c r="D73" t="s">
         <v>166</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>46216</v>
       </c>
       <c r="G73" t="s">
         <v>253</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4370,7 +4344,7 @@
       <c r="C74" t="s">
         <v>153</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4384,7 +4358,7 @@
       <c r="C75" t="s">
         <v>153</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4398,7 +4372,7 @@
       <c r="C76" t="s">
         <v>153</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4412,7 +4386,7 @@
       <c r="C77" t="s">
         <v>153</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4429,13 +4403,13 @@
       <c r="D78" t="s">
         <v>177</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>46210</v>
       </c>
       <c r="G78" t="s">
         <v>256</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4458,7 +4432,7 @@
       <c r="G79" t="s">
         <v>246</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4472,7 +4446,7 @@
       <c r="C80" t="s">
         <v>157</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4486,7 +4460,7 @@
       <c r="C81" t="s">
         <v>153</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4509,7 +4483,7 @@
       <c r="G82" t="s">
         <v>241</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4526,7 +4500,7 @@
       <c r="D83" t="s">
         <v>170</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4549,7 +4523,7 @@
       <c r="G84" t="s">
         <v>242</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4566,13 +4540,13 @@
       <c r="D85" t="s">
         <v>172</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>46209</v>
       </c>
       <c r="G85" t="s">
         <v>255</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4595,7 +4569,7 @@
       <c r="G86" t="s">
         <v>243</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4618,7 +4592,7 @@
       <c r="G87" t="s">
         <v>243</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4641,7 +4615,7 @@
       <c r="G88" t="s">
         <v>244</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -4655,7 +4629,7 @@
       <c r="C89" t="s">
         <v>153</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4672,13 +4646,13 @@
       <c r="D90" t="s">
         <v>180</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>46217</v>
       </c>
       <c r="G90" t="s">
         <v>257</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4695,13 +4669,13 @@
       <c r="D91" t="s">
         <v>176</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>46210</v>
       </c>
       <c r="G91" t="s">
         <v>256</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4715,7 +4689,7 @@
       <c r="C92" t="s">
         <v>153</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4732,13 +4706,13 @@
       <c r="D93" t="s">
         <v>178</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>46217</v>
       </c>
       <c r="G93" t="s">
         <v>257</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4752,7 +4726,7 @@
       <c r="C94" t="s">
         <v>153</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4766,7 +4740,7 @@
       <c r="C95" t="s">
         <v>157</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4783,13 +4757,13 @@
       <c r="D96" t="s">
         <v>163</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>46234</v>
       </c>
       <c r="G96" t="s">
         <v>251</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4806,13 +4780,13 @@
       <c r="D97" t="s">
         <v>164</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>46213</v>
       </c>
       <c r="G97" t="s">
         <v>252</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4826,7 +4800,7 @@
       <c r="C98" t="s">
         <v>153</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4843,13 +4817,13 @@
       <c r="D99" t="s">
         <v>181</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>46213</v>
       </c>
       <c r="G99" t="s">
         <v>252</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4866,13 +4840,13 @@
       <c r="D100" t="s">
         <v>165</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>46213</v>
       </c>
       <c r="G100" t="s">
         <v>252</v>
       </c>
-      <c r="H100" s="2">
+      <c r="H100" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4886,7 +4860,7 @@
       <c r="C101" t="s">
         <v>153</v>
       </c>
-      <c r="H101" s="2">
+      <c r="H101" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4903,13 +4877,13 @@
       <c r="D102" t="s">
         <v>166</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>46216</v>
       </c>
       <c r="G102" t="s">
         <v>253</v>
       </c>
-      <c r="H102" s="2">
+      <c r="H102" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4926,13 +4900,13 @@
       <c r="D103" t="s">
         <v>182</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>46213</v>
       </c>
       <c r="G103" t="s">
         <v>252</v>
       </c>
-      <c r="H103" s="2">
+      <c r="H103" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4946,7 +4920,7 @@
       <c r="C104" t="s">
         <v>153</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4960,7 +4934,7 @@
       <c r="C105" t="s">
         <v>153</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4974,7 +4948,7 @@
       <c r="C106" t="s">
         <v>153</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -4991,13 +4965,13 @@
       <c r="D107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>46213</v>
       </c>
       <c r="G107" t="s">
         <v>252</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5020,7 +4994,7 @@
       <c r="G108" t="s">
         <v>246</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5034,7 +5008,7 @@
       <c r="C109" t="s">
         <v>157</v>
       </c>
-      <c r="H109" s="2">
+      <c r="H109" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5048,7 +5022,7 @@
       <c r="C110" t="s">
         <v>153</v>
       </c>
-      <c r="H110" s="2">
+      <c r="H110" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5071,7 +5045,7 @@
       <c r="G111" t="s">
         <v>241</v>
       </c>
-      <c r="H111" s="2">
+      <c r="H111" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5088,7 +5062,7 @@
       <c r="D112" t="s">
         <v>170</v>
       </c>
-      <c r="H112" s="2">
+      <c r="H112" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5111,7 +5085,7 @@
       <c r="G113" t="s">
         <v>242</v>
       </c>
-      <c r="H113" s="2">
+      <c r="H113" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5128,13 +5102,13 @@
       <c r="D114" t="s">
         <v>172</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>46209</v>
       </c>
       <c r="G114" t="s">
         <v>255</v>
       </c>
-      <c r="H114" s="2">
+      <c r="H114" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5157,7 +5131,7 @@
       <c r="G115" t="s">
         <v>243</v>
       </c>
-      <c r="H115" s="2">
+      <c r="H115" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5180,7 +5154,7 @@
       <c r="G116" t="s">
         <v>243</v>
       </c>
-      <c r="H116" s="2">
+      <c r="H116" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5203,7 +5177,7 @@
       <c r="G117" t="s">
         <v>244</v>
       </c>
-      <c r="H117" s="2">
+      <c r="H117" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -5217,7 +5191,7 @@
       <c r="C118" t="s">
         <v>153</v>
       </c>
-      <c r="H118" s="2">
+      <c r="H118" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5234,13 +5208,13 @@
       <c r="D119" t="s">
         <v>180</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>46217</v>
       </c>
       <c r="G119" t="s">
         <v>257</v>
       </c>
-      <c r="H119" s="2">
+      <c r="H119" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5254,7 +5228,7 @@
       <c r="C120" t="s">
         <v>157</v>
       </c>
-      <c r="H120" s="2">
+      <c r="H120" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5268,7 +5242,7 @@
       <c r="C121" t="s">
         <v>153</v>
       </c>
-      <c r="H121" s="2">
+      <c r="H121" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5282,7 +5256,7 @@
       <c r="C122" t="s">
         <v>157</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5296,7 +5270,7 @@
       <c r="C123" t="s">
         <v>157</v>
       </c>
-      <c r="H123" s="2">
+      <c r="H123" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5310,7 +5284,7 @@
       <c r="C124" t="s">
         <v>157</v>
       </c>
-      <c r="H124" s="2">
+      <c r="H124" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5327,13 +5301,13 @@
       <c r="D125" t="s">
         <v>163</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" t="s">
         <v>251</v>
       </c>
-      <c r="H125" s="2">
+      <c r="H125" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5350,13 +5324,13 @@
       <c r="D126" t="s">
         <v>164</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>46213</v>
       </c>
       <c r="G126" t="s">
         <v>252</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H126" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5370,7 +5344,7 @@
       <c r="C127" t="s">
         <v>153</v>
       </c>
-      <c r="H127" s="2">
+      <c r="H127" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5387,13 +5361,13 @@
       <c r="D128" t="s">
         <v>181</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>46213</v>
       </c>
       <c r="G128" t="s">
         <v>252</v>
       </c>
-      <c r="H128" s="2">
+      <c r="H128" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5410,13 +5384,13 @@
       <c r="D129" t="s">
         <v>165</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>46213</v>
       </c>
       <c r="G129" t="s">
         <v>252</v>
       </c>
-      <c r="H129" s="2">
+      <c r="H129" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5430,7 +5404,7 @@
       <c r="C130" t="s">
         <v>153</v>
       </c>
-      <c r="H130" s="2">
+      <c r="H130" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5447,13 +5421,13 @@
       <c r="D131" t="s">
         <v>166</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>46216</v>
       </c>
       <c r="G131" t="s">
         <v>253</v>
       </c>
-      <c r="H131" s="2">
+      <c r="H131" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5470,13 +5444,13 @@
       <c r="D132" t="s">
         <v>182</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>46213</v>
       </c>
       <c r="G132" t="s">
         <v>252</v>
       </c>
-      <c r="H132" s="2">
+      <c r="H132" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5490,7 +5464,7 @@
       <c r="C133" t="s">
         <v>153</v>
       </c>
-      <c r="H133" s="2">
+      <c r="H133" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5504,7 +5478,7 @@
       <c r="C134" t="s">
         <v>153</v>
       </c>
-      <c r="H134" s="2">
+      <c r="H134" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5518,7 +5492,7 @@
       <c r="C135" t="s">
         <v>153</v>
       </c>
-      <c r="H135" s="2">
+      <c r="H135" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5535,13 +5509,13 @@
       <c r="D136" t="s">
         <v>184</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>46213</v>
       </c>
       <c r="G136" t="s">
         <v>252</v>
       </c>
-      <c r="H136" s="2">
+      <c r="H136" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5564,7 +5538,7 @@
       <c r="G137" t="s">
         <v>246</v>
       </c>
-      <c r="H137" s="2">
+      <c r="H137" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5578,7 +5552,7 @@
       <c r="C138" t="s">
         <v>157</v>
       </c>
-      <c r="H138" s="2">
+      <c r="H138" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5592,7 +5566,7 @@
       <c r="C139" t="s">
         <v>153</v>
       </c>
-      <c r="H139" s="2">
+      <c r="H139" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5615,7 +5589,7 @@
       <c r="G140" t="s">
         <v>241</v>
       </c>
-      <c r="H140" s="2">
+      <c r="H140" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5632,7 +5606,7 @@
       <c r="D141" t="s">
         <v>170</v>
       </c>
-      <c r="H141" s="2">
+      <c r="H141" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5655,7 +5629,7 @@
       <c r="G142" t="s">
         <v>242</v>
       </c>
-      <c r="H142" s="2">
+      <c r="H142" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5672,13 +5646,13 @@
       <c r="D143" t="s">
         <v>172</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>46209</v>
       </c>
       <c r="G143" t="s">
         <v>255</v>
       </c>
-      <c r="H143" s="2">
+      <c r="H143" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5701,7 +5675,7 @@
       <c r="G144" t="s">
         <v>243</v>
       </c>
-      <c r="H144" s="2">
+      <c r="H144" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5724,7 +5698,7 @@
       <c r="G145" t="s">
         <v>243</v>
       </c>
-      <c r="H145" s="2">
+      <c r="H145" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5747,7 +5721,7 @@
       <c r="G146" t="s">
         <v>244</v>
       </c>
-      <c r="H146" s="2">
+      <c r="H146" s="1">
         <v>46211</v>
       </c>
     </row>
@@ -5761,7 +5735,7 @@
       <c r="C147" t="s">
         <v>153</v>
       </c>
-      <c r="H147" s="2">
+      <c r="H147" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5778,13 +5752,13 @@
       <c r="D148" t="s">
         <v>180</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>46217</v>
       </c>
       <c r="G148" t="s">
         <v>257</v>
       </c>
-      <c r="H148" s="2">
+      <c r="H148" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5798,7 +5772,7 @@
       <c r="C149" t="s">
         <v>157</v>
       </c>
-      <c r="H149" s="2">
+      <c r="H149" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5812,7 +5786,7 @@
       <c r="C150" t="s">
         <v>153</v>
       </c>
-      <c r="H150" s="2">
+      <c r="H150" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5826,7 +5800,7 @@
       <c r="C151" t="s">
         <v>153</v>
       </c>
-      <c r="H151" s="2">
+      <c r="H151" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5840,7 +5814,7 @@
       <c r="C152" t="s">
         <v>157</v>
       </c>
-      <c r="H152" s="2">
+      <c r="H152" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5854,7 +5828,7 @@
       <c r="C153" t="s">
         <v>157</v>
       </c>
-      <c r="H153" s="2">
+      <c r="H153" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5871,13 +5845,13 @@
       <c r="D154" t="s">
         <v>163</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>46234</v>
       </c>
       <c r="G154" t="s">
         <v>251</v>
       </c>
-      <c r="H154" s="2">
+      <c r="H154" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5894,13 +5868,13 @@
       <c r="D155" t="s">
         <v>164</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>46213</v>
       </c>
       <c r="G155" t="s">
         <v>252</v>
       </c>
-      <c r="H155" s="2">
+      <c r="H155" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5914,7 +5888,7 @@
       <c r="C156" t="s">
         <v>153</v>
       </c>
-      <c r="H156" s="2">
+      <c r="H156" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5931,13 +5905,13 @@
       <c r="D157" t="s">
         <v>181</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>46213</v>
       </c>
       <c r="G157" t="s">
         <v>252</v>
       </c>
-      <c r="H157" s="2">
+      <c r="H157" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5954,13 +5928,13 @@
       <c r="D158" t="s">
         <v>165</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>46213</v>
       </c>
       <c r="G158" t="s">
         <v>252</v>
       </c>
-      <c r="H158" s="2">
+      <c r="H158" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -5977,13 +5951,13 @@
       <c r="D159" t="s">
         <v>185</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>46212</v>
       </c>
       <c r="G159" t="s">
         <v>258</v>
       </c>
-      <c r="H159" s="2">
+      <c r="H159" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6000,13 +5974,13 @@
       <c r="D160" t="s">
         <v>166</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>46216</v>
       </c>
       <c r="G160" t="s">
         <v>253</v>
       </c>
-      <c r="H160" s="2">
+      <c r="H160" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6023,13 +5997,13 @@
       <c r="D161" t="s">
         <v>182</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>46213</v>
       </c>
       <c r="G161" t="s">
         <v>252</v>
       </c>
-      <c r="H161" s="2">
+      <c r="H161" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6043,7 +6017,7 @@
       <c r="C162" t="s">
         <v>153</v>
       </c>
-      <c r="H162" s="2">
+      <c r="H162" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6057,7 +6031,7 @@
       <c r="C163" t="s">
         <v>153</v>
       </c>
-      <c r="H163" s="2">
+      <c r="H163" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6071,7 +6045,7 @@
       <c r="C164" t="s">
         <v>153</v>
       </c>
-      <c r="H164" s="2">
+      <c r="H164" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6088,13 +6062,13 @@
       <c r="D165" t="s">
         <v>184</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>46213</v>
       </c>
       <c r="G165" t="s">
         <v>252</v>
       </c>
-      <c r="H165" s="2">
+      <c r="H165" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6117,7 +6091,7 @@
       <c r="G166" t="s">
         <v>246</v>
       </c>
-      <c r="H166" s="2">
+      <c r="H166" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6131,7 +6105,7 @@
       <c r="C167" t="s">
         <v>157</v>
       </c>
-      <c r="H167" s="2">
+      <c r="H167" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6145,7 +6119,7 @@
       <c r="C168" t="s">
         <v>153</v>
       </c>
-      <c r="H168" s="2">
+      <c r="H168" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6168,7 +6142,7 @@
       <c r="G169" t="s">
         <v>241</v>
       </c>
-      <c r="H169" s="2">
+      <c r="H169" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6185,7 +6159,7 @@
       <c r="D170" t="s">
         <v>170</v>
       </c>
-      <c r="H170" s="2">
+      <c r="H170" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6208,7 +6182,7 @@
       <c r="G171" t="s">
         <v>242</v>
       </c>
-      <c r="H171" s="2">
+      <c r="H171" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6225,13 +6199,13 @@
       <c r="D172" t="s">
         <v>172</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>46209</v>
       </c>
       <c r="G172" t="s">
         <v>255</v>
       </c>
-      <c r="H172" s="2">
+      <c r="H172" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6254,7 +6228,7 @@
       <c r="G173" t="s">
         <v>243</v>
       </c>
-      <c r="H173" s="2">
+      <c r="H173" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6277,7 +6251,7 @@
       <c r="G174" t="s">
         <v>243</v>
       </c>
-      <c r="H174" s="2">
+      <c r="H174" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6300,7 +6274,7 @@
       <c r="G175" t="s">
         <v>244</v>
       </c>
-      <c r="H175" s="2">
+      <c r="H175" s="1">
         <v>46212</v>
       </c>
     </row>
@@ -6314,7 +6288,7 @@
       <c r="C176" t="s">
         <v>153</v>
       </c>
-      <c r="H176" s="2">
+      <c r="H176" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6331,13 +6305,13 @@
       <c r="D177" t="s">
         <v>186</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>46217</v>
       </c>
       <c r="G177" t="s">
         <v>257</v>
       </c>
-      <c r="H177" s="2">
+      <c r="H177" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6351,7 +6325,7 @@
       <c r="C178" t="s">
         <v>153</v>
       </c>
-      <c r="H178" s="2">
+      <c r="H178" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6368,13 +6342,13 @@
       <c r="D179" t="s">
         <v>187</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>46216</v>
       </c>
       <c r="G179" t="s">
         <v>253</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H179" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6388,7 +6362,7 @@
       <c r="C180" t="s">
         <v>153</v>
       </c>
-      <c r="H180" s="2">
+      <c r="H180" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6402,7 +6376,7 @@
       <c r="C181" t="s">
         <v>157</v>
       </c>
-      <c r="H181" s="2">
+      <c r="H181" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6416,7 +6390,7 @@
       <c r="C182" t="s">
         <v>157</v>
       </c>
-      <c r="H182" s="2">
+      <c r="H182" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6433,13 +6407,13 @@
       <c r="D183" t="s">
         <v>163</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" t="s">
         <v>251</v>
       </c>
-      <c r="H183" s="2">
+      <c r="H183" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6456,13 +6430,13 @@
       <c r="D184" t="s">
         <v>164</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>46213</v>
       </c>
       <c r="G184" t="s">
         <v>252</v>
       </c>
-      <c r="H184" s="2">
+      <c r="H184" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6476,7 +6450,7 @@
       <c r="C185" t="s">
         <v>153</v>
       </c>
-      <c r="H185" s="2">
+      <c r="H185" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6493,13 +6467,13 @@
       <c r="D186" t="s">
         <v>181</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>46213</v>
       </c>
       <c r="G186" t="s">
         <v>252</v>
       </c>
-      <c r="H186" s="2">
+      <c r="H186" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6516,13 +6490,13 @@
       <c r="D187" t="s">
         <v>188</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>46213</v>
       </c>
       <c r="G187" t="s">
         <v>252</v>
       </c>
-      <c r="H187" s="2">
+      <c r="H187" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6539,13 +6513,13 @@
       <c r="D188" t="s">
         <v>189</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>46213</v>
       </c>
       <c r="G188" t="s">
         <v>252</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6562,13 +6536,13 @@
       <c r="D189" t="s">
         <v>166</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>46216</v>
       </c>
       <c r="G189" t="s">
         <v>253</v>
       </c>
-      <c r="H189" s="2">
+      <c r="H189" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6585,13 +6559,13 @@
       <c r="D190" t="s">
         <v>182</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>46213</v>
       </c>
       <c r="G190" t="s">
         <v>252</v>
       </c>
-      <c r="H190" s="2">
+      <c r="H190" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6605,7 +6579,7 @@
       <c r="C191" t="s">
         <v>153</v>
       </c>
-      <c r="H191" s="2">
+      <c r="H191" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6619,7 +6593,7 @@
       <c r="C192" t="s">
         <v>153</v>
       </c>
-      <c r="H192" s="2">
+      <c r="H192" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6633,7 +6607,7 @@
       <c r="C193" t="s">
         <v>153</v>
       </c>
-      <c r="H193" s="2">
+      <c r="H193" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6650,13 +6624,13 @@
       <c r="D194" t="s">
         <v>184</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>46218</v>
       </c>
       <c r="G194" t="s">
         <v>259</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6679,7 +6653,7 @@
       <c r="G195" t="s">
         <v>246</v>
       </c>
-      <c r="H195" s="2">
+      <c r="H195" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6693,7 +6667,7 @@
       <c r="C196" t="s">
         <v>157</v>
       </c>
-      <c r="H196" s="2">
+      <c r="H196" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6707,7 +6681,7 @@
       <c r="C197" t="s">
         <v>153</v>
       </c>
-      <c r="H197" s="2">
+      <c r="H197" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6730,7 +6704,7 @@
       <c r="G198" t="s">
         <v>241</v>
       </c>
-      <c r="H198" s="2">
+      <c r="H198" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6747,7 +6721,7 @@
       <c r="D199" t="s">
         <v>170</v>
       </c>
-      <c r="H199" s="2">
+      <c r="H199" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6770,7 +6744,7 @@
       <c r="G200" t="s">
         <v>242</v>
       </c>
-      <c r="H200" s="2">
+      <c r="H200" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6787,13 +6761,13 @@
       <c r="D201" t="s">
         <v>172</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>46209</v>
       </c>
       <c r="G201" t="s">
         <v>255</v>
       </c>
-      <c r="H201" s="2">
+      <c r="H201" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6816,7 +6790,7 @@
       <c r="G202" t="s">
         <v>243</v>
       </c>
-      <c r="H202" s="2">
+      <c r="H202" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6839,7 +6813,7 @@
       <c r="G203" t="s">
         <v>243</v>
       </c>
-      <c r="H203" s="2">
+      <c r="H203" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6862,7 +6836,7 @@
       <c r="G204" t="s">
         <v>244</v>
       </c>
-      <c r="H204" s="2">
+      <c r="H204" s="1">
         <v>46213</v>
       </c>
     </row>
@@ -6876,7 +6850,7 @@
       <c r="C205" t="s">
         <v>153</v>
       </c>
-      <c r="H205" s="2">
+      <c r="H205" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6893,13 +6867,13 @@
       <c r="D206" t="s">
         <v>186</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>46217</v>
       </c>
       <c r="G206" t="s">
         <v>257</v>
       </c>
-      <c r="H206" s="2">
+      <c r="H206" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6913,7 +6887,7 @@
       <c r="C207" t="s">
         <v>153</v>
       </c>
-      <c r="H207" s="2">
+      <c r="H207" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6927,7 +6901,7 @@
       <c r="C208" t="s">
         <v>157</v>
       </c>
-      <c r="H208" s="2">
+      <c r="H208" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6941,7 +6915,7 @@
       <c r="C209" t="s">
         <v>153</v>
       </c>
-      <c r="H209" s="2">
+      <c r="H209" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6955,7 +6929,7 @@
       <c r="C210" t="s">
         <v>157</v>
       </c>
-      <c r="H210" s="2">
+      <c r="H210" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6969,7 +6943,7 @@
       <c r="C211" t="s">
         <v>157</v>
       </c>
-      <c r="H211" s="2">
+      <c r="H211" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -6986,13 +6960,13 @@
       <c r="D212" t="s">
         <v>163</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" t="s">
         <v>251</v>
       </c>
-      <c r="H212" s="2">
+      <c r="H212" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7006,7 +6980,7 @@
       <c r="C213" t="s">
         <v>157</v>
       </c>
-      <c r="H213" s="2">
+      <c r="H213" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7020,7 +6994,7 @@
       <c r="C214" t="s">
         <v>153</v>
       </c>
-      <c r="H214" s="2">
+      <c r="H214" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7037,13 +7011,13 @@
       <c r="D215" t="s">
         <v>181</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>46220</v>
       </c>
       <c r="G215" t="s">
         <v>260</v>
       </c>
-      <c r="H215" s="2">
+      <c r="H215" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7060,13 +7034,13 @@
       <c r="D216" t="s">
         <v>188</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>46216</v>
       </c>
       <c r="G216" t="s">
         <v>253</v>
       </c>
-      <c r="H216" s="2">
+      <c r="H216" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7080,7 +7054,7 @@
       <c r="C217" t="s">
         <v>153</v>
       </c>
-      <c r="H217" s="2">
+      <c r="H217" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7097,13 +7071,13 @@
       <c r="D218" t="s">
         <v>166</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>46216</v>
       </c>
       <c r="G218" t="s">
         <v>253</v>
       </c>
-      <c r="H218" s="2">
+      <c r="H218" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7117,7 +7091,7 @@
       <c r="C219" t="s">
         <v>153</v>
       </c>
-      <c r="H219" s="2">
+      <c r="H219" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7131,7 +7105,7 @@
       <c r="C220" t="s">
         <v>153</v>
       </c>
-      <c r="H220" s="2">
+      <c r="H220" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7148,13 +7122,13 @@
       <c r="D221" t="s">
         <v>190</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>46217</v>
       </c>
       <c r="G221" t="s">
         <v>257</v>
       </c>
-      <c r="H221" s="2">
+      <c r="H221" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7168,7 +7142,7 @@
       <c r="C222" t="s">
         <v>153</v>
       </c>
-      <c r="H222" s="2">
+      <c r="H222" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7185,13 +7159,13 @@
       <c r="D223" t="s">
         <v>191</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>46241</v>
       </c>
       <c r="G223" t="s">
         <v>261</v>
       </c>
-      <c r="H223" s="2">
+      <c r="H223" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7214,7 +7188,7 @@
       <c r="G224" t="s">
         <v>246</v>
       </c>
-      <c r="H224" s="2">
+      <c r="H224" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7228,7 +7202,7 @@
       <c r="C225" t="s">
         <v>157</v>
       </c>
-      <c r="H225" s="2">
+      <c r="H225" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7242,7 +7216,7 @@
       <c r="C226" t="s">
         <v>153</v>
       </c>
-      <c r="H226" s="2">
+      <c r="H226" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7265,7 +7239,7 @@
       <c r="G227" t="s">
         <v>241</v>
       </c>
-      <c r="H227" s="2">
+      <c r="H227" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7282,7 +7256,7 @@
       <c r="D228" t="s">
         <v>170</v>
       </c>
-      <c r="H228" s="2">
+      <c r="H228" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7305,7 +7279,7 @@
       <c r="G229" t="s">
         <v>242</v>
       </c>
-      <c r="H229" s="2">
+      <c r="H229" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7322,13 +7296,13 @@
       <c r="D230" t="s">
         <v>192</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>46295</v>
       </c>
       <c r="G230" t="s">
         <v>262</v>
       </c>
-      <c r="H230" s="2">
+      <c r="H230" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7351,7 +7325,7 @@
       <c r="G231" t="s">
         <v>243</v>
       </c>
-      <c r="H231" s="2">
+      <c r="H231" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7374,7 +7348,7 @@
       <c r="G232" t="s">
         <v>243</v>
       </c>
-      <c r="H232" s="2">
+      <c r="H232" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7397,7 +7371,7 @@
       <c r="G233" t="s">
         <v>244</v>
       </c>
-      <c r="H233" s="2">
+      <c r="H233" s="1">
         <v>46216</v>
       </c>
     </row>
@@ -7411,7 +7385,7 @@
       <c r="C234" t="s">
         <v>153</v>
       </c>
-      <c r="H234" s="2">
+      <c r="H234" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7428,13 +7402,13 @@
       <c r="D235" t="s">
         <v>193</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>46217</v>
       </c>
       <c r="G235" t="s">
         <v>257</v>
       </c>
-      <c r="H235" s="2">
+      <c r="H235" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7448,7 +7422,7 @@
       <c r="C236" t="s">
         <v>153</v>
       </c>
-      <c r="H236" s="2">
+      <c r="H236" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7462,7 +7436,7 @@
       <c r="C237" t="s">
         <v>157</v>
       </c>
-      <c r="H237" s="2">
+      <c r="H237" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7476,7 +7450,7 @@
       <c r="C238" t="s">
         <v>153</v>
       </c>
-      <c r="H238" s="2">
+      <c r="H238" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7490,7 +7464,7 @@
       <c r="C239" t="s">
         <v>157</v>
       </c>
-      <c r="H239" s="2">
+      <c r="H239" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7504,7 +7478,7 @@
       <c r="C240" t="s">
         <v>157</v>
       </c>
-      <c r="H240" s="2">
+      <c r="H240" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7521,13 +7495,13 @@
       <c r="D241" t="s">
         <v>163</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" t="s">
         <v>251</v>
       </c>
-      <c r="H241" s="2">
+      <c r="H241" s="1">
         <v>46217</v>
       </c>
     </row>
@@ -7541,7 +7515,7 @@
       <c r="C242" t="s">
         <v>157</v>
       